--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="110">
   <si>
     <t>Symbol</t>
   </si>
@@ -292,25 +292,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>55.4 → 45.2</t>
+    <t>50.6 → 31.5</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>55.4</t>
-  </si>
-  <si>
-    <t>45.2</t>
-  </si>
-  <si>
-    <t>50.3 → 49.7</t>
-  </si>
-  <si>
-    <t>50.3</t>
-  </si>
-  <si>
-    <t>49.7</t>
+    <t>50.6</t>
+  </si>
+  <si>
+    <t>31.5</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1040,10 +1040,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>27304.5</v>
+        <v>26756.6</v>
       </c>
       <c r="E2">
-        <v>-0.86</v>
+        <v>-2.01</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1052,43 +1052,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-7.9</v>
+        <v>-9.75</v>
       </c>
       <c r="I2">
-        <v>14.87</v>
+        <v>12.57</v>
       </c>
       <c r="J2">
-        <v>-1.47</v>
+        <v>-3.4</v>
       </c>
       <c r="K2">
-        <v>-7.1</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="L2">
-        <v>1.21</v>
+        <v>-0.5</v>
       </c>
       <c r="M2">
-        <v>5.04</v>
+        <v>1.66</v>
       </c>
       <c r="N2">
-        <v>21.99</v>
+        <v>21.05</v>
       </c>
       <c r="O2">
         <v>62</v>
       </c>
       <c r="Q2">
-        <v>27594.58</v>
+        <v>27406.15</v>
       </c>
       <c r="R2">
-        <v>28506.05</v>
+        <v>28384.97</v>
       </c>
       <c r="S2">
-        <v>28127.53</v>
+        <v>28115.58</v>
       </c>
       <c r="T2">
-        <v>27139.21</v>
+        <v>27135.3</v>
       </c>
       <c r="U2">
-        <v>0.61</v>
+        <v>-1.4</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1100,43 +1100,43 @@
         <v>79</v>
       </c>
       <c r="Y2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z2">
-        <v>27.65</v>
+        <v>21.9</v>
       </c>
       <c r="AA2">
-        <v>-267.73</v>
+        <v>-344.52</v>
       </c>
       <c r="AB2">
-        <v>-68.58</v>
+        <v>-123.77</v>
       </c>
       <c r="AC2">
-        <v>-199.15</v>
+        <v>-220.75</v>
       </c>
       <c r="AD2">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="AE2">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="AF2">
-        <v>366.79</v>
+        <v>394.12</v>
       </c>
       <c r="AH2">
-        <v>29947.92</v>
+        <v>29987.01</v>
       </c>
       <c r="AI2">
-        <v>27064.17</v>
+        <v>26782.94</v>
       </c>
       <c r="AJ2">
-        <v>28350.6</v>
+        <v>28309.42</v>
       </c>
       <c r="AK2" t="s">
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>66.5</v>
+        <v>69.73</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1150,55 +1150,55 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9579.799999999999</v>
+        <v>9407.549999999999</v>
       </c>
       <c r="E3">
-        <v>-1.34</v>
+        <v>-1.8</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
       </c>
       <c r="G3">
-        <v>8787.4</v>
+        <v>8813</v>
       </c>
       <c r="H3">
-        <v>-8.789999999999999</v>
+        <v>-10.43</v>
       </c>
       <c r="I3">
-        <v>9.02</v>
+        <v>6.75</v>
       </c>
       <c r="J3">
-        <v>-2.29</v>
+        <v>-3.04</v>
       </c>
       <c r="K3">
-        <v>-3.02</v>
+        <v>-4.23</v>
       </c>
       <c r="L3">
-        <v>-4.41</v>
+        <v>-6.01</v>
       </c>
       <c r="M3">
-        <v>9.119999999999999</v>
+        <v>7.06</v>
       </c>
       <c r="N3">
-        <v>11.02</v>
+        <v>10.45</v>
       </c>
       <c r="O3">
         <v>68</v>
       </c>
       <c r="Q3">
-        <v>9681.32</v>
+        <v>9622.41</v>
       </c>
       <c r="R3">
-        <v>9765.35</v>
+        <v>9743.559999999999</v>
       </c>
       <c r="S3">
-        <v>9831.139999999999</v>
+        <v>9820.32</v>
       </c>
       <c r="T3">
-        <v>9755.33</v>
+        <v>9756.51</v>
       </c>
       <c r="U3">
-        <v>-1.8</v>
+        <v>-3.58</v>
       </c>
       <c r="V3" t="s">
         <v>80</v>
@@ -1213,40 +1213,40 @@
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>34.25</v>
+        <v>26.94</v>
       </c>
       <c r="AA3">
-        <v>-53.17</v>
+        <v>-74.44</v>
       </c>
       <c r="AB3">
-        <v>-40.22</v>
+        <v>-47.07</v>
       </c>
       <c r="AC3">
-        <v>-12.94</v>
+        <v>-27.37</v>
       </c>
       <c r="AD3">
-        <v>34.74</v>
+        <v>15.08</v>
       </c>
       <c r="AE3">
-        <v>37.1</v>
+        <v>30.23</v>
       </c>
       <c r="AF3">
-        <v>99.98999999999999</v>
+        <v>107.61</v>
       </c>
       <c r="AH3">
-        <v>9913.48</v>
+        <v>9957.139999999999</v>
       </c>
       <c r="AI3">
-        <v>9617.209999999999</v>
+        <v>9529.98</v>
       </c>
       <c r="AJ3">
-        <v>9892.459999999999</v>
+        <v>9832.969999999999</v>
       </c>
       <c r="AK3" t="s">
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>31.28</v>
+        <v>35.09</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1260,10 +1260,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11460.6</v>
+        <v>11282.8</v>
       </c>
       <c r="E4">
-        <v>-0.47</v>
+        <v>-1.55</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1272,43 +1272,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-9.32</v>
+        <v>-10.73</v>
       </c>
       <c r="I4">
-        <v>10.9</v>
+        <v>9.18</v>
       </c>
       <c r="J4">
-        <v>-1.18</v>
+        <v>-2.4</v>
       </c>
       <c r="K4">
-        <v>-5.58</v>
+        <v>-7.08</v>
       </c>
       <c r="L4">
-        <v>0.33</v>
+        <v>-1.77</v>
       </c>
       <c r="M4">
-        <v>-7.27</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="N4">
-        <v>10.05</v>
+        <v>9.41</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q4">
-        <v>11527.42</v>
+        <v>11471.83</v>
       </c>
       <c r="R4">
-        <v>11812.83</v>
+        <v>11773.74</v>
       </c>
       <c r="S4">
-        <v>11859.41</v>
+        <v>11847.6</v>
       </c>
       <c r="T4">
-        <v>11648.95</v>
+        <v>11642.86</v>
       </c>
       <c r="U4">
-        <v>-1.62</v>
+        <v>-3.09</v>
       </c>
       <c r="V4" t="s">
         <v>80</v>
@@ -1323,40 +1323,40 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>25.13</v>
+        <v>19.64</v>
       </c>
       <c r="AA4">
-        <v>-120.51</v>
+        <v>-141.09</v>
       </c>
       <c r="AB4">
-        <v>-70.76000000000001</v>
+        <v>-84.83</v>
       </c>
       <c r="AC4">
-        <v>-49.75</v>
+        <v>-56.26</v>
       </c>
       <c r="AD4">
         <v>0</v>
       </c>
       <c r="AE4">
-        <v>0.65</v>
+        <v>0.32</v>
       </c>
       <c r="AF4">
-        <v>99.09</v>
+        <v>109.2</v>
       </c>
       <c r="AH4">
-        <v>12254.01</v>
+        <v>12257.49</v>
       </c>
       <c r="AI4">
-        <v>11371.65</v>
+        <v>11290</v>
       </c>
       <c r="AJ4">
-        <v>11731.39</v>
+        <v>11730.69</v>
       </c>
       <c r="AK4" t="s">
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>53.63</v>
+        <v>57.58</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1370,10 +1370,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>37935.2</v>
+        <v>37147.95</v>
       </c>
       <c r="E5">
-        <v>-0.75</v>
+        <v>-2.08</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1382,43 +1382,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-8.67</v>
+        <v>-10.56</v>
       </c>
       <c r="I5">
-        <v>14.61</v>
+        <v>12.24</v>
       </c>
       <c r="J5">
-        <v>-0.35</v>
+        <v>-2.17</v>
       </c>
       <c r="K5">
-        <v>-1.95</v>
+        <v>-3.65</v>
       </c>
       <c r="L5">
-        <v>-3.95</v>
+        <v>-6.93</v>
       </c>
       <c r="M5">
-        <v>10.65</v>
+        <v>8.31</v>
       </c>
       <c r="N5">
-        <v>12.58</v>
+        <v>11.71</v>
       </c>
       <c r="O5">
         <v>81</v>
       </c>
       <c r="Q5">
-        <v>38111.82</v>
+        <v>37946.74</v>
       </c>
       <c r="R5">
-        <v>38153.28</v>
+        <v>38078.05</v>
       </c>
       <c r="S5">
-        <v>38673.68</v>
+        <v>38627.01</v>
       </c>
       <c r="T5">
-        <v>37540.26</v>
+        <v>37546.74</v>
       </c>
       <c r="U5">
-        <v>1.05</v>
+        <v>-1.06</v>
       </c>
       <c r="V5" t="s">
         <v>80</v>
@@ -1430,43 +1430,43 @@
         <v>80</v>
       </c>
       <c r="Y5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>39.53</v>
+        <v>27.62</v>
       </c>
       <c r="AA5">
-        <v>-180.11</v>
+        <v>-244.54</v>
       </c>
       <c r="AB5">
-        <v>-220.47</v>
+        <v>-225.28</v>
       </c>
       <c r="AC5">
-        <v>40.36</v>
+        <v>-19.25</v>
       </c>
       <c r="AD5">
-        <v>79.54000000000001</v>
+        <v>46.21</v>
       </c>
       <c r="AE5">
-        <v>88.16</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="AF5">
-        <v>344.86</v>
+        <v>388.97</v>
       </c>
       <c r="AH5">
-        <v>38569.61</v>
+        <v>38634.62</v>
       </c>
       <c r="AI5">
-        <v>37736.95</v>
+        <v>37521.47</v>
       </c>
       <c r="AJ5">
-        <v>38783.5</v>
+        <v>38726.95</v>
       </c>
       <c r="AK5" t="s">
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>17.69</v>
+        <v>21.32</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1480,55 +1480,55 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>45053.75</v>
+        <v>44829.95</v>
       </c>
       <c r="E6">
-        <v>-0.29</v>
+        <v>-0.5</v>
       </c>
       <c r="F6">
         <v>56960.6</v>
       </c>
       <c r="G6">
-        <v>45053.75</v>
+        <v>44829.95</v>
       </c>
       <c r="H6">
-        <v>-20.9</v>
+        <v>-21.3</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>-1.83</v>
+        <v>-1.67</v>
       </c>
       <c r="K6">
-        <v>-7.75</v>
+        <v>-7.79</v>
       </c>
       <c r="L6">
-        <v>-8.130000000000001</v>
+        <v>-9.69</v>
       </c>
       <c r="M6">
-        <v>-21.1</v>
+        <v>-20.36</v>
       </c>
       <c r="N6">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>45378.12</v>
+        <v>45225.68</v>
       </c>
       <c r="R6">
-        <v>46641.78</v>
+        <v>46478.02</v>
       </c>
       <c r="S6">
-        <v>48082.83</v>
+        <v>47975.5</v>
       </c>
       <c r="T6">
-        <v>50307.44</v>
+        <v>50254.07</v>
       </c>
       <c r="U6">
-        <v>-10.44</v>
+        <v>-10.79</v>
       </c>
       <c r="V6" t="s">
         <v>80</v>
@@ -1543,31 +1543,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>24.38</v>
+        <v>22.94</v>
       </c>
       <c r="AA6">
-        <v>-882.3099999999999</v>
+        <v>-906.63</v>
       </c>
       <c r="AB6">
-        <v>-763.15</v>
+        <v>-791.85</v>
       </c>
       <c r="AC6">
-        <v>-119.16</v>
+        <v>-114.78</v>
       </c>
       <c r="AD6">
-        <v>2.35</v>
+        <v>0.2</v>
       </c>
       <c r="AE6">
-        <v>9.539999999999999</v>
+        <v>4.83</v>
       </c>
       <c r="AF6">
-        <v>518.64</v>
+        <v>533.9400000000001</v>
       </c>
       <c r="AH6">
-        <v>48663.15</v>
+        <v>48530.67</v>
       </c>
       <c r="AI6">
-        <v>44620.41</v>
+        <v>44425.38</v>
       </c>
       <c r="AJ6">
         <v>46607.06</v>
@@ -1576,7 +1576,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>74.98999999999999</v>
+        <v>72.29000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1590,10 +1590,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25545.4</v>
+        <v>25076.65</v>
       </c>
       <c r="E7">
-        <v>0.1</v>
+        <v>-1.83</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1602,43 +1602,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-10.25</v>
+        <v>-11.9</v>
       </c>
       <c r="I7">
-        <v>8.6</v>
+        <v>6.61</v>
       </c>
       <c r="J7">
-        <v>-1.94</v>
+        <v>-3.31</v>
       </c>
       <c r="K7">
-        <v>-2.97</v>
+        <v>-4.34</v>
       </c>
       <c r="L7">
-        <v>-2.78</v>
+        <v>-5.16</v>
       </c>
       <c r="M7">
-        <v>-1.19</v>
+        <v>-3.14</v>
       </c>
       <c r="N7">
-        <v>7.11</v>
+        <v>6.67</v>
       </c>
       <c r="O7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Q7">
-        <v>25614.73</v>
+        <v>25442.94</v>
       </c>
       <c r="R7">
-        <v>26013.18</v>
+        <v>25956.16</v>
       </c>
       <c r="S7">
-        <v>26428.53</v>
+        <v>26390.19</v>
       </c>
       <c r="T7">
-        <v>26585.44</v>
+        <v>26573</v>
       </c>
       <c r="U7">
-        <v>-3.91</v>
+        <v>-5.63</v>
       </c>
       <c r="V7" t="s">
         <v>80</v>
@@ -1653,31 +1653,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>35.05</v>
+        <v>27.63</v>
       </c>
       <c r="AA7">
-        <v>-234.89</v>
+        <v>-276.92</v>
       </c>
       <c r="AB7">
-        <v>-177.71</v>
+        <v>-197.55</v>
       </c>
       <c r="AC7">
-        <v>-57.18</v>
+        <v>-79.36</v>
       </c>
       <c r="AD7">
         <v>18.42</v>
       </c>
       <c r="AE7">
-        <v>14.49</v>
+        <v>15.67</v>
       </c>
       <c r="AF7">
-        <v>271.34</v>
+        <v>298.58</v>
       </c>
       <c r="AH7">
-        <v>26591.18</v>
+        <v>26660.63</v>
       </c>
       <c r="AI7">
-        <v>25435.18</v>
+        <v>25251.68</v>
       </c>
       <c r="AJ7">
         <v>26164.61</v>
@@ -1686,7 +1686,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>34.14</v>
+        <v>34.83</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1700,10 +1700,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>28921.5</v>
+        <v>29555.3</v>
       </c>
       <c r="E8">
-        <v>0.11</v>
+        <v>2.19</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1712,43 +1712,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-26.76</v>
+        <v>-25.15</v>
       </c>
       <c r="I8">
-        <v>12.23</v>
+        <v>14.69</v>
       </c>
       <c r="J8">
-        <v>-5.78</v>
+        <v>-1.47</v>
       </c>
       <c r="K8">
-        <v>-8.050000000000001</v>
+        <v>-5.75</v>
       </c>
       <c r="L8">
-        <v>3.04</v>
+        <v>3.46</v>
       </c>
       <c r="M8">
-        <v>-17.7</v>
+        <v>-14.67</v>
       </c>
       <c r="N8">
-        <v>-3.82</v>
+        <v>-3.91</v>
       </c>
       <c r="O8">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q8">
-        <v>29321</v>
+        <v>29233.02</v>
       </c>
       <c r="R8">
-        <v>30416.5</v>
+        <v>30326.37</v>
       </c>
       <c r="S8">
-        <v>30052.25</v>
+        <v>30097.83</v>
       </c>
       <c r="T8">
-        <v>32007.52</v>
+        <v>31970.87</v>
       </c>
       <c r="U8">
-        <v>-9.640000000000001</v>
+        <v>-7.56</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1763,34 +1763,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>34.68</v>
+        <v>43.12</v>
       </c>
       <c r="AA8">
-        <v>-284.84</v>
+        <v>-294.98</v>
       </c>
       <c r="AB8">
-        <v>8.640000000000001</v>
+        <v>-52.09</v>
       </c>
       <c r="AC8">
-        <v>-293.47</v>
+        <v>-242.89</v>
       </c>
       <c r="AD8">
-        <v>0.5600000000000001</v>
+        <v>11.97</v>
       </c>
       <c r="AE8">
-        <v>0.19</v>
+        <v>4.18</v>
       </c>
       <c r="AF8">
-        <v>636.9299999999999</v>
+        <v>699.54</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>31988.49</v>
+        <v>31877.69</v>
       </c>
       <c r="AI8">
-        <v>28844.5</v>
+        <v>28775.06</v>
       </c>
       <c r="AJ8">
         <v>30808.98</v>
@@ -1799,7 +1799,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>34.75</v>
+        <v>31.19</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1813,43 +1813,43 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15967.45</v>
+        <v>15584.65</v>
       </c>
       <c r="E9">
-        <v>-0.92</v>
+        <v>-2.4</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
       </c>
       <c r="G9">
-        <v>15663.1</v>
+        <v>15584.65</v>
       </c>
       <c r="H9">
-        <v>-4.17</v>
+        <v>-6.47</v>
       </c>
       <c r="I9">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>-1.57</v>
+        <v>-3.72</v>
       </c>
       <c r="K9">
-        <v>-3.93</v>
+        <v>-5.81</v>
       </c>
       <c r="L9">
-        <v>1.94</v>
+        <v>-1.85</v>
       </c>
       <c r="N9">
-        <v>8.029999999999999</v>
+        <v>-1.91</v>
       </c>
       <c r="Q9">
-        <v>16145.68</v>
+        <v>16025.21</v>
       </c>
       <c r="R9">
-        <v>16394.37</v>
+        <v>16344.43</v>
       </c>
       <c r="S9">
-        <v>16265.41</v>
+        <v>16254.56</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1861,40 +1861,40 @@
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>28.43</v>
+        <v>19.31</v>
       </c>
       <c r="AA9">
-        <v>-66.34999999999999</v>
+        <v>-114.6</v>
       </c>
       <c r="AB9">
-        <v>-1.87</v>
+        <v>-24.42</v>
       </c>
       <c r="AC9">
-        <v>-64.47</v>
+        <v>-90.18000000000001</v>
       </c>
       <c r="AD9">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>7.98</v>
+        <v>4.62</v>
       </c>
       <c r="AF9">
-        <v>137.28</v>
+        <v>159.59</v>
       </c>
       <c r="AH9">
-        <v>16773.16</v>
+        <v>16857.72</v>
       </c>
       <c r="AI9">
-        <v>16015.58</v>
+        <v>15831.13</v>
       </c>
       <c r="AJ9">
-        <v>16341.24</v>
+        <v>16286.43</v>
       </c>
       <c r="AK9" t="s">
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>45.55</v>
+        <v>50.68</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1908,10 +1908,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9077.15</v>
+        <v>8910.75</v>
       </c>
       <c r="E10">
-        <v>-0.62</v>
+        <v>-1.83</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1920,91 +1920,91 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-7.05</v>
+        <v>-8.76</v>
       </c>
       <c r="I10">
-        <v>6.03</v>
+        <v>4.09</v>
       </c>
       <c r="J10">
-        <v>-1.31</v>
+        <v>-3.02</v>
       </c>
       <c r="K10">
-        <v>-3.36</v>
+        <v>-5.4</v>
       </c>
       <c r="L10">
-        <v>-3.13</v>
+        <v>-5.47</v>
       </c>
       <c r="M10">
-        <v>1.56</v>
+        <v>-0.5</v>
       </c>
       <c r="N10">
-        <v>13.41</v>
+        <v>12.56</v>
       </c>
       <c r="O10">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="Q10">
-        <v>9132.57</v>
+        <v>9076.98</v>
       </c>
       <c r="R10">
-        <v>9248.799999999999</v>
+        <v>9223.51</v>
       </c>
       <c r="S10">
-        <v>9338.33</v>
+        <v>9326.15</v>
       </c>
       <c r="T10">
-        <v>9332.51</v>
+        <v>9328.76</v>
       </c>
       <c r="U10">
-        <v>-2.74</v>
+        <v>-4.48</v>
       </c>
       <c r="V10" t="s">
         <v>80</v>
       </c>
       <c r="W10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="s">
         <v>80</v>
       </c>
       <c r="Y10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z10">
-        <v>28.79</v>
+        <v>20.64</v>
       </c>
       <c r="AA10">
-        <v>-69.95999999999999</v>
+        <v>-86.45</v>
       </c>
       <c r="AB10">
-        <v>-55.06</v>
+        <v>-61.33</v>
       </c>
       <c r="AC10">
-        <v>-14.91</v>
+        <v>-25.12</v>
       </c>
       <c r="AD10">
         <v>3.64</v>
       </c>
       <c r="AE10">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="AF10">
-        <v>75.45999999999999</v>
+        <v>84.58</v>
       </c>
       <c r="AH10">
-        <v>9447.790000000001</v>
+        <v>9458.129999999999</v>
       </c>
       <c r="AI10">
-        <v>9049.809999999999</v>
+        <v>8988.9</v>
       </c>
       <c r="AJ10">
-        <v>9301.85</v>
+        <v>9266.09</v>
       </c>
       <c r="AK10" t="s">
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>51.9</v>
+        <v>55.97</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2018,10 +2018,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1537.2</v>
+        <v>1503.9</v>
       </c>
       <c r="E11">
-        <v>0.16</v>
+        <v>-2.17</v>
       </c>
       <c r="F11">
         <v>1632.5</v>
@@ -2030,43 +2030,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-5.84</v>
+        <v>-7.88</v>
       </c>
       <c r="I11">
-        <v>22.65</v>
+        <v>19.99</v>
       </c>
       <c r="J11">
-        <v>-1.8</v>
+        <v>-1.1</v>
       </c>
       <c r="K11">
-        <v>-2.4</v>
+        <v>-5.42</v>
       </c>
       <c r="L11">
-        <v>3.48</v>
+        <v>-0.16</v>
       </c>
       <c r="M11">
-        <v>-4.58</v>
+        <v>-7.19</v>
       </c>
       <c r="N11">
-        <v>-2.27</v>
+        <v>-4.99</v>
       </c>
       <c r="O11">
         <v>44</v>
       </c>
       <c r="Q11">
-        <v>1531.94</v>
+        <v>1528.59</v>
       </c>
       <c r="R11">
-        <v>1574.55</v>
+        <v>1569.96</v>
       </c>
       <c r="S11">
-        <v>1551.05</v>
+        <v>1551.17</v>
       </c>
       <c r="T11">
-        <v>1449.59</v>
+        <v>1449.89</v>
       </c>
       <c r="U11">
-        <v>6.04</v>
+        <v>3.73</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2081,40 +2081,40 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>44.65</v>
+        <v>38.31</v>
       </c>
       <c r="AA11">
-        <v>-8.01</v>
+        <v>-11.16</v>
       </c>
       <c r="AB11">
-        <v>-0.25</v>
+        <v>-2.44</v>
       </c>
       <c r="AC11">
-        <v>-7.75</v>
+        <v>-8.73</v>
       </c>
       <c r="AD11">
-        <v>17.57</v>
+        <v>14.58</v>
       </c>
       <c r="AE11">
-        <v>14.36</v>
+        <v>16.11</v>
       </c>
       <c r="AF11">
-        <v>30.48</v>
+        <v>31.36</v>
       </c>
       <c r="AH11">
-        <v>1642.93</v>
+        <v>1644.41</v>
       </c>
       <c r="AI11">
-        <v>1506.18</v>
+        <v>1495.52</v>
       </c>
       <c r="AJ11">
-        <v>1626.15</v>
+        <v>1614.42</v>
       </c>
       <c r="AK11" t="s">
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>47.93</v>
+        <v>48.93</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2128,55 +2128,55 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>12999.05</v>
+        <v>12669.15</v>
       </c>
       <c r="E12">
-        <v>-2.3</v>
+        <v>-2.54</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
       </c>
       <c r="G12">
-        <v>9681.65</v>
+        <v>9717.85</v>
       </c>
       <c r="H12">
-        <v>-5.24</v>
+        <v>-7.65</v>
       </c>
       <c r="I12">
-        <v>34.26</v>
+        <v>30.37</v>
       </c>
       <c r="J12">
-        <v>-2.39</v>
+        <v>-3.68</v>
       </c>
       <c r="K12">
-        <v>-0.27</v>
+        <v>-2.11</v>
       </c>
       <c r="L12">
-        <v>-0.65</v>
+        <v>-1.65</v>
       </c>
       <c r="M12">
-        <v>35.18</v>
+        <v>30.86</v>
       </c>
       <c r="N12">
-        <v>17.38</v>
+        <v>16.68</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13200.85</v>
+        <v>13104.1</v>
       </c>
       <c r="R12">
-        <v>13227.92</v>
+        <v>13206.15</v>
       </c>
       <c r="S12">
-        <v>12924.02</v>
+        <v>12922.95</v>
       </c>
       <c r="T12">
-        <v>12202.11</v>
+        <v>12214.75</v>
       </c>
       <c r="U12">
-        <v>6.53</v>
+        <v>3.72</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2191,40 +2191,40 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>45.23</v>
+        <v>37.28</v>
       </c>
       <c r="AA12">
-        <v>61.12</v>
+        <v>13.19</v>
       </c>
       <c r="AB12">
-        <v>96.02</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="AC12">
-        <v>-34.9</v>
+        <v>-66.27</v>
       </c>
       <c r="AD12">
-        <v>20.57</v>
+        <v>7.37</v>
       </c>
       <c r="AE12">
-        <v>18.24</v>
+        <v>16.23</v>
       </c>
       <c r="AF12">
-        <v>224.3</v>
+        <v>235.46</v>
       </c>
       <c r="AH12">
-        <v>13564.71</v>
+        <v>13623.24</v>
       </c>
       <c r="AI12">
-        <v>12891.14</v>
+        <v>12789.07</v>
       </c>
       <c r="AJ12">
-        <v>12921.88</v>
+        <v>13565.64</v>
       </c>
       <c r="AK12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL12">
-        <v>25.62</v>
+        <v>27.2</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2238,10 +2238,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9688.4</v>
+        <v>9467</v>
       </c>
       <c r="E13">
-        <v>-0.64</v>
+        <v>-2.29</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2250,43 +2250,43 @@
         <v>9390.25</v>
       </c>
       <c r="H13">
-        <v>-10.01</v>
+        <v>-12.07</v>
       </c>
       <c r="I13">
-        <v>3.18</v>
+        <v>0.82</v>
       </c>
       <c r="J13">
-        <v>-0.22</v>
+        <v>-2.2</v>
       </c>
       <c r="K13">
-        <v>-2.09</v>
+        <v>-3.84</v>
       </c>
       <c r="L13">
-        <v>-2.67</v>
+        <v>-5.49</v>
       </c>
       <c r="M13">
-        <v>3.11</v>
+        <v>0.66</v>
       </c>
       <c r="N13">
-        <v>20.84</v>
+        <v>19.55</v>
       </c>
       <c r="O13">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Q13">
-        <v>9713.07</v>
+        <v>9670.459999999999</v>
       </c>
       <c r="R13">
-        <v>9733.85</v>
+        <v>9714.120000000001</v>
       </c>
       <c r="S13">
-        <v>9844.389999999999</v>
+        <v>9833.15</v>
       </c>
       <c r="T13">
-        <v>10025.81</v>
+        <v>10023.81</v>
       </c>
       <c r="U13">
-        <v>-3.37</v>
+        <v>-5.55</v>
       </c>
       <c r="V13" t="s">
         <v>80</v>
@@ -2301,40 +2301,40 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>39.59</v>
+        <v>25.24</v>
       </c>
       <c r="AA13">
-        <v>-44.78</v>
+        <v>-61.74</v>
       </c>
       <c r="AB13">
-        <v>-52.84</v>
+        <v>-54.62</v>
       </c>
       <c r="AC13">
-        <v>8.06</v>
+        <v>-7.12</v>
       </c>
       <c r="AD13">
-        <v>85.34999999999999</v>
+        <v>52.02</v>
       </c>
       <c r="AE13">
-        <v>88.62</v>
+        <v>78.7</v>
       </c>
       <c r="AF13">
-        <v>84.59</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="AH13">
-        <v>9838.6</v>
+        <v>9858.66</v>
       </c>
       <c r="AI13">
-        <v>9629.110000000001</v>
+        <v>9569.59</v>
       </c>
       <c r="AJ13">
-        <v>9905.1</v>
+        <v>9868.6</v>
       </c>
       <c r="AK13" t="s">
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>30.48</v>
+        <v>34.84</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2348,55 +2348,55 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8349.9</v>
+        <v>8158.5</v>
       </c>
       <c r="E14">
-        <v>-0.62</v>
+        <v>-2.29</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
       </c>
       <c r="G14">
-        <v>6855.7</v>
+        <v>6879.9</v>
       </c>
       <c r="H14">
-        <v>-15.49</v>
+        <v>-17.42</v>
       </c>
       <c r="I14">
-        <v>21.8</v>
+        <v>18.58</v>
       </c>
       <c r="J14">
-        <v>-1.94</v>
+        <v>-3.16</v>
       </c>
       <c r="K14">
-        <v>-5</v>
+        <v>-6.64</v>
       </c>
       <c r="L14">
-        <v>-2.7</v>
+        <v>-4.73</v>
       </c>
       <c r="M14">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="N14">
-        <v>29.01</v>
+        <v>27.61</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8391.59</v>
+        <v>8338.360000000001</v>
       </c>
       <c r="R14">
-        <v>8541.65</v>
+        <v>8514.27</v>
       </c>
       <c r="S14">
-        <v>8489.5</v>
+        <v>8485.99</v>
       </c>
       <c r="T14">
-        <v>8597.809999999999</v>
+        <v>8596.709999999999</v>
       </c>
       <c r="U14">
-        <v>-2.88</v>
+        <v>-5.1</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2411,40 +2411,40 @@
         <v>1</v>
       </c>
       <c r="Z14">
-        <v>37.15</v>
+        <v>28.5</v>
       </c>
       <c r="AA14">
-        <v>-45</v>
+        <v>-66.20999999999999</v>
       </c>
       <c r="AB14">
-        <v>-13.83</v>
+        <v>-24.3</v>
       </c>
       <c r="AC14">
-        <v>-31.17</v>
+        <v>-41.91</v>
       </c>
       <c r="AD14">
         <v>5.31</v>
       </c>
       <c r="AE14">
-        <v>3.54</v>
+        <v>5.31</v>
       </c>
       <c r="AF14">
-        <v>122.3</v>
+        <v>129.04</v>
       </c>
       <c r="AH14">
-        <v>8747.030000000001</v>
+        <v>8767.700000000001</v>
       </c>
       <c r="AI14">
-        <v>8336.280000000001</v>
+        <v>8260.84</v>
       </c>
       <c r="AJ14">
-        <v>8686.389999999999</v>
+        <v>8653.85</v>
       </c>
       <c r="AK14" t="s">
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>24.97</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2458,10 +2458,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26532.4</v>
+        <v>26188.4</v>
       </c>
       <c r="E15">
-        <v>-0.09</v>
+        <v>-1.3</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2470,43 +2470,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-2.41</v>
+        <v>-3.67</v>
       </c>
       <c r="I15">
-        <v>23.67</v>
+        <v>22.07</v>
       </c>
       <c r="J15">
-        <v>0.21</v>
+        <v>-1.83</v>
       </c>
       <c r="K15">
-        <v>-0.58</v>
+        <v>-0.97</v>
       </c>
       <c r="L15">
-        <v>9.550000000000001</v>
+        <v>8.41</v>
       </c>
       <c r="M15">
-        <v>21.07</v>
+        <v>19.45</v>
       </c>
       <c r="N15">
-        <v>13.05</v>
+        <v>12.57</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26667.27</v>
+        <v>26569.85</v>
       </c>
       <c r="R15">
-        <v>26625.01</v>
+        <v>26612.15</v>
       </c>
       <c r="S15">
-        <v>26326.31</v>
+        <v>26332.75</v>
       </c>
       <c r="T15">
-        <v>23903.35</v>
+        <v>23921.39</v>
       </c>
       <c r="U15">
-        <v>11</v>
+        <v>9.48</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2521,34 +2521,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>49.68</v>
+        <v>41.78</v>
       </c>
       <c r="AA15">
-        <v>101.52</v>
+        <v>56.59</v>
       </c>
       <c r="AB15">
-        <v>153.32</v>
+        <v>133.97</v>
       </c>
       <c r="AC15">
-        <v>-51.8</v>
+        <v>-77.38</v>
       </c>
       <c r="AD15">
-        <v>7.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE15">
-        <v>18.13</v>
+        <v>9.6</v>
       </c>
       <c r="AF15">
-        <v>302.06</v>
+        <v>314.95</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27097.04</v>
+        <v>27117.59</v>
       </c>
       <c r="AI15">
-        <v>26152.97</v>
+        <v>26106.7</v>
       </c>
       <c r="AJ15">
         <v>26048.62</v>
@@ -2557,7 +2557,7 @@
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>24.08</v>
+        <v>24.57</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2571,10 +2571,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>848.5</v>
+        <v>814.25</v>
       </c>
       <c r="E16">
-        <v>-2.7</v>
+        <v>-4.04</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2583,43 +2583,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-12.4</v>
+        <v>-15.94</v>
       </c>
       <c r="I16">
-        <v>30.31</v>
+        <v>25.05</v>
       </c>
       <c r="J16">
-        <v>-6.54</v>
+        <v>-8.77</v>
       </c>
       <c r="K16">
-        <v>-5.55</v>
+        <v>-9.09</v>
       </c>
       <c r="L16">
-        <v>6.06</v>
+        <v>-0.47</v>
       </c>
       <c r="M16">
-        <v>-3.88</v>
+        <v>-6.68</v>
       </c>
       <c r="N16">
-        <v>15.1</v>
+        <v>14.01</v>
       </c>
       <c r="O16">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="Q16">
-        <v>875.46</v>
+        <v>859.8099999999999</v>
       </c>
       <c r="R16">
-        <v>898.46</v>
+        <v>893.74</v>
       </c>
       <c r="S16">
-        <v>903.67</v>
+        <v>901.8099999999999</v>
       </c>
       <c r="T16">
-        <v>830.0599999999999</v>
+        <v>829.6</v>
       </c>
       <c r="U16">
-        <v>2.22</v>
+        <v>-1.85</v>
       </c>
       <c r="V16" t="s">
         <v>80</v>
@@ -2631,43 +2631,43 @@
         <v>80</v>
       </c>
       <c r="Y16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z16">
-        <v>31.07</v>
+        <v>24.06</v>
       </c>
       <c r="AA16">
-        <v>-6.71</v>
+        <v>-11.96</v>
       </c>
       <c r="AB16">
-        <v>-0.53</v>
+        <v>-2.82</v>
       </c>
       <c r="AC16">
-        <v>-6.18</v>
+        <v>-9.15</v>
       </c>
       <c r="AD16">
         <v>0</v>
       </c>
       <c r="AE16">
-        <v>2.46</v>
+        <v>0.77</v>
       </c>
       <c r="AF16">
-        <v>19.05</v>
+        <v>20.43</v>
       </c>
       <c r="AH16">
-        <v>933.6</v>
+        <v>944.84</v>
       </c>
       <c r="AI16">
-        <v>863.3200000000001</v>
+        <v>842.63</v>
       </c>
       <c r="AJ16">
-        <v>905.49</v>
+        <v>894.74</v>
       </c>
       <c r="AK16" t="s">
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>30.39</v>
+        <v>35.37</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2681,10 +2681,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29969.35</v>
+        <v>29728.85</v>
       </c>
       <c r="E17">
-        <v>0.11</v>
+        <v>-0.8</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2693,43 +2693,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-12.12</v>
+        <v>-12.82</v>
       </c>
       <c r="I17">
-        <v>5.66</v>
+        <v>4.81</v>
       </c>
       <c r="J17">
-        <v>-1.98</v>
+        <v>-2.28</v>
       </c>
       <c r="K17">
-        <v>-3.64</v>
+        <v>-4.5</v>
       </c>
       <c r="L17">
-        <v>-1.29</v>
+        <v>-2.75</v>
       </c>
       <c r="M17">
-        <v>-6.45</v>
+        <v>-7.13</v>
       </c>
       <c r="N17">
-        <v>4.27</v>
+        <v>3.85</v>
       </c>
       <c r="O17">
         <v>26</v>
       </c>
       <c r="Q17">
-        <v>30066.54</v>
+        <v>29927.77</v>
       </c>
       <c r="R17">
-        <v>30610.11</v>
+        <v>30547.97</v>
       </c>
       <c r="S17">
-        <v>31022.68</v>
+        <v>30992.3</v>
       </c>
       <c r="T17">
-        <v>31534.37</v>
+        <v>31513.97</v>
       </c>
       <c r="U17">
-        <v>-4.96</v>
+        <v>-5.66</v>
       </c>
       <c r="V17" t="s">
         <v>80</v>
@@ -2744,31 +2744,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>29.87</v>
+        <v>26.12</v>
       </c>
       <c r="AA17">
-        <v>-282.41</v>
+        <v>-311.06</v>
       </c>
       <c r="AB17">
-        <v>-193.64</v>
+        <v>-217.12</v>
       </c>
       <c r="AC17">
-        <v>-88.77</v>
+        <v>-93.94</v>
       </c>
       <c r="AD17">
-        <v>15.29</v>
+        <v>18.81</v>
       </c>
       <c r="AE17">
-        <v>7.34</v>
+        <v>13.61</v>
       </c>
       <c r="AF17">
-        <v>258.54</v>
+        <v>283.09</v>
       </c>
       <c r="AH17">
-        <v>31336.28</v>
+        <v>31352.36</v>
       </c>
       <c r="AI17">
-        <v>29883.93</v>
+        <v>29743.57</v>
       </c>
       <c r="AJ17">
         <v>30589.09</v>
@@ -2777,7 +2777,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>44.79</v>
+        <v>42.53</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2791,10 +2791,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16492.1</v>
+        <v>16299</v>
       </c>
       <c r="E18">
-        <v>-0.16</v>
+        <v>-1.17</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2803,31 +2803,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-2.65</v>
+        <v>-3.79</v>
       </c>
       <c r="I18">
-        <v>7.07</v>
+        <v>5.82</v>
       </c>
       <c r="J18">
-        <v>0.51</v>
+        <v>-1.34</v>
       </c>
       <c r="K18">
-        <v>-0.54</v>
+        <v>-1.25</v>
       </c>
       <c r="L18">
-        <v>6.05</v>
+        <v>5.61</v>
       </c>
       <c r="N18">
-        <v>26.57</v>
+        <v>19.78</v>
       </c>
       <c r="Q18">
-        <v>16547.36</v>
+        <v>16503.1</v>
       </c>
       <c r="R18">
-        <v>16564.1</v>
+        <v>16557.58</v>
       </c>
       <c r="S18">
-        <v>16534.06</v>
+        <v>16530.41</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2839,31 +2839,31 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>47.06</v>
+        <v>39.84</v>
       </c>
       <c r="AA18">
-        <v>8.380000000000001</v>
+        <v>-13.55</v>
       </c>
       <c r="AB18">
-        <v>30.92</v>
+        <v>22.03</v>
       </c>
       <c r="AC18">
-        <v>-22.54</v>
+        <v>-35.58</v>
       </c>
       <c r="AD18">
-        <v>19.93</v>
+        <v>10.58</v>
       </c>
       <c r="AE18">
-        <v>24.8</v>
+        <v>19.19</v>
       </c>
       <c r="AF18">
-        <v>175.87</v>
+        <v>183.37</v>
       </c>
       <c r="AH18">
-        <v>16841.18</v>
+        <v>16853.5</v>
       </c>
       <c r="AI18">
-        <v>16287.01</v>
+        <v>16261.66</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2872,7 +2872,7 @@
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>20.02</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2886,10 +2886,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9723.85</v>
+        <v>9144.15</v>
       </c>
       <c r="E19">
-        <v>-0.73</v>
+        <v>-5.96</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2898,31 +2898,31 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-2.75</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="I19">
-        <v>8.1</v>
+        <v>1.65</v>
       </c>
       <c r="J19">
+        <v>-6.26</v>
+      </c>
+      <c r="K19">
+        <v>-6.8</v>
+      </c>
+      <c r="L19">
         <v>0.15</v>
       </c>
-      <c r="K19">
-        <v>-0.89</v>
-      </c>
-      <c r="L19">
-        <v>8.1</v>
-      </c>
       <c r="N19">
-        <v>36.69</v>
+        <v>6.51</v>
       </c>
       <c r="Q19">
-        <v>9832.98</v>
+        <v>9710.9</v>
       </c>
       <c r="R19">
-        <v>9778.280000000001</v>
+        <v>9743.41</v>
       </c>
       <c r="S19">
-        <v>9580.280000000001</v>
+        <v>9570.33</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2934,40 +2934,40 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>50.65</v>
+        <v>31.51</v>
       </c>
       <c r="AA19">
-        <v>56.73</v>
+        <v>2.38</v>
       </c>
       <c r="AB19">
-        <v>64.72</v>
+        <v>52.25</v>
       </c>
       <c r="AC19">
-        <v>-7.99</v>
+        <v>-49.87</v>
       </c>
       <c r="AD19">
-        <v>37.2</v>
+        <v>16.15</v>
       </c>
       <c r="AE19">
-        <v>59.06</v>
+        <v>39.69</v>
       </c>
       <c r="AF19">
-        <v>148.65</v>
+        <v>182.15</v>
       </c>
       <c r="AH19">
-        <v>9969.629999999999</v>
+        <v>10082.99</v>
       </c>
       <c r="AI19">
-        <v>9586.92</v>
+        <v>9403.83</v>
       </c>
       <c r="AJ19">
-        <v>9528.309999999999</v>
+        <v>9986.059999999999</v>
       </c>
       <c r="AK19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL19">
-        <v>21.92</v>
+        <v>25.85</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2981,43 +2981,43 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10937</v>
+        <v>10796.4</v>
       </c>
       <c r="E20">
-        <v>-0.84</v>
+        <v>-1.29</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
       </c>
       <c r="G20">
-        <v>10937</v>
+        <v>10796.4</v>
       </c>
       <c r="H20">
-        <v>-3.8</v>
+        <v>-5.04</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>-2.24</v>
+        <v>-2.9</v>
       </c>
       <c r="K20">
-        <v>-2.8</v>
+        <v>-3.6</v>
       </c>
       <c r="L20">
-        <v>-0.68</v>
+        <v>-4.41</v>
       </c>
       <c r="N20">
-        <v>-2.72</v>
+        <v>-7.33</v>
       </c>
       <c r="Q20">
-        <v>11031.9</v>
+        <v>10967.41</v>
       </c>
       <c r="R20">
-        <v>11129.96</v>
+        <v>11109.36</v>
       </c>
       <c r="S20">
-        <v>11174.07</v>
+        <v>11164.77</v>
       </c>
       <c r="V20" t="s">
         <v>80</v>
@@ -3029,40 +3029,40 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>32.09</v>
+        <v>25.42</v>
       </c>
       <c r="AA20">
-        <v>-46.17</v>
+        <v>-65.47</v>
       </c>
       <c r="AB20">
-        <v>-26.07</v>
+        <v>-33.95</v>
       </c>
       <c r="AC20">
-        <v>-20.1</v>
+        <v>-31.52</v>
       </c>
       <c r="AD20">
         <v>0.27</v>
       </c>
       <c r="AE20">
-        <v>7.17</v>
+        <v>0.97</v>
       </c>
       <c r="AF20">
-        <v>119.48</v>
+        <v>124.44</v>
       </c>
       <c r="AH20">
-        <v>11286.64</v>
+        <v>11321.22</v>
       </c>
       <c r="AI20">
-        <v>10973.28</v>
+        <v>10897.49</v>
       </c>
       <c r="AJ20">
-        <v>10895.17</v>
+        <v>11256.37</v>
       </c>
       <c r="AK20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="AL20">
-        <v>24.89</v>
+        <v>29.15</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3076,10 +3076,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27436</v>
+        <v>27069.8</v>
       </c>
       <c r="E21">
-        <v>0.48</v>
+        <v>-1.33</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3088,43 +3088,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6</v>
+        <v>-7.26</v>
       </c>
       <c r="I21">
-        <v>13.63</v>
+        <v>12.11</v>
       </c>
       <c r="J21">
-        <v>-1.4</v>
+        <v>-2.44</v>
       </c>
       <c r="K21">
-        <v>0.64</v>
+        <v>-0.65</v>
       </c>
       <c r="L21">
-        <v>-1.35</v>
+        <v>-3.03</v>
       </c>
       <c r="M21">
-        <v>4.37</v>
+        <v>2.78</v>
       </c>
       <c r="N21">
-        <v>7.78</v>
+        <v>7.13</v>
       </c>
       <c r="O21">
         <v>74</v>
       </c>
       <c r="Q21">
-        <v>27435.33</v>
+        <v>27300.14</v>
       </c>
       <c r="R21">
-        <v>27548.34</v>
+        <v>27536.28</v>
       </c>
       <c r="S21">
-        <v>27804.26</v>
+        <v>27778.71</v>
       </c>
       <c r="T21">
-        <v>27607.34</v>
+        <v>27600.71</v>
       </c>
       <c r="U21">
-        <v>-0.62</v>
+        <v>-1.92</v>
       </c>
       <c r="V21" t="s">
         <v>80</v>
@@ -3139,31 +3139,31 @@
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>45.6</v>
+        <v>38.17</v>
       </c>
       <c r="AA21">
-        <v>-65.95999999999999</v>
+        <v>-97.95</v>
       </c>
       <c r="AB21">
-        <v>-41.66</v>
+        <v>-52.92</v>
       </c>
       <c r="AC21">
-        <v>-24.3</v>
+        <v>-45.03</v>
       </c>
       <c r="AD21">
         <v>14.59</v>
       </c>
       <c r="AE21">
-        <v>13.31</v>
+        <v>11.17</v>
       </c>
       <c r="AF21">
-        <v>296.31</v>
+        <v>315.44</v>
       </c>
       <c r="AH21">
-        <v>28009.51</v>
+        <v>28034.7</v>
       </c>
       <c r="AI21">
-        <v>27087.16</v>
+        <v>27037.85</v>
       </c>
       <c r="AJ21">
         <v>28092.43</v>
@@ -3172,7 +3172,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>30.34</v>
+        <v>28.76</v>
       </c>
     </row>
   </sheetData>
@@ -3313,7 +3313,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3373,22 +3373,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -3425,13 +3425,13 @@
         <v>10</v>
       </c>
       <c r="C8" s="6">
-        <v>-6.21</v>
+        <v>-7.1</v>
       </c>
       <c r="D8" s="6">
-        <v>-7.1</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.89</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3442,13 +3442,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.12</v>
+        <v>-3.02</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.02</v>
+        <v>-4.23</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.9</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3459,13 +3459,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.78</v>
+        <v>-5.58</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.58</v>
+        <v>-7.08</v>
       </c>
       <c r="E10" s="7">
-        <v>-0.8</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3476,13 +3476,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.43</v>
+        <v>-1.95</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.95</v>
+        <v>-3.65</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.52</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3493,13 +3493,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.7</v>
+        <v>-7.75</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.75</v>
+        <v>-7.79</v>
       </c>
       <c r="E12" s="7">
-        <v>-1.05</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3510,13 +3510,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-3.43</v>
+        <v>-2.97</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.97</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.46</v>
+        <v>-4.34</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3527,13 +3527,13 @@
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.79</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="D14" s="6">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.26</v>
+        <v>-5.75</v>
+      </c>
+      <c r="E14" s="8">
+        <v>2.3</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3544,13 +3544,13 @@
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.1</v>
+        <v>-3.93</v>
       </c>
       <c r="D15" s="6">
-        <v>-3.93</v>
+        <v>-5.81</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.83</v>
+        <v>-1.88</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3561,13 +3561,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.94</v>
+        <v>-3.36</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.36</v>
+        <v>-5.4</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.42</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3578,13 +3578,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.19</v>
+        <v>-2.4</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.4</v>
+        <v>-5.42</v>
       </c>
       <c r="E17" s="7">
-        <v>-0.21</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3595,13 +3595,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>1.01</v>
+        <v>-0.27</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.27</v>
+        <v>-2.11</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.28</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3612,13 +3612,13 @@
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.2</v>
+        <v>-2.09</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.09</v>
+        <v>-3.84</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.89</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3629,13 +3629,13 @@
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.71</v>
+        <v>-5</v>
       </c>
       <c r="D20" s="6">
-        <v>-5</v>
+        <v>-6.64</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.29</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3646,13 +3646,13 @@
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-0.77</v>
+        <v>-0.58</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.58</v>
-      </c>
-      <c r="E21" s="8">
-        <v>0.19</v>
+        <v>-0.97</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3663,13 +3663,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-1.99</v>
+        <v>-5.55</v>
       </c>
       <c r="D22" s="6">
-        <v>-5.55</v>
+        <v>-9.09</v>
       </c>
       <c r="E22" s="7">
-        <v>-3.56</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3680,13 +3680,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.98</v>
+        <v>-3.64</v>
       </c>
       <c r="D23" s="6">
-        <v>-3.64</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.34</v>
+        <v>-4.5</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3697,13 +3697,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.68</v>
+        <v>-0.54</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.54</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.14</v>
+        <v>-1.25</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3714,13 +3714,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>1.4</v>
+        <v>-0.89</v>
       </c>
       <c r="D25" s="6">
-        <v>-0.89</v>
+        <v>-6.8</v>
       </c>
       <c r="E25" s="7">
-        <v>-2.29</v>
+        <v>-5.91</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3731,13 +3731,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-2.34</v>
+        <v>-2.8</v>
       </c>
       <c r="D26" s="6">
-        <v>-2.8</v>
+        <v>-3.6</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.46</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3748,13 +3748,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-0.37</v>
+        <v>0.64</v>
       </c>
       <c r="D27" s="6">
-        <v>0.64</v>
-      </c>
-      <c r="E27" s="8">
-        <v>1.01</v>
+        <v>-0.65</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3765,13 +3765,13 @@
         <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>-1.06</v>
+        <v>-1.47</v>
       </c>
       <c r="D28" s="6">
-        <v>-1.47</v>
+        <v>-3.4</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.41</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3782,13 +3782,13 @@
         <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-0.42</v>
+        <v>-2.29</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.29</v>
+        <v>-3.04</v>
       </c>
       <c r="E29" s="7">
-        <v>-1.87</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3799,13 +3799,13 @@
         <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>-1.12</v>
+        <v>-1.18</v>
       </c>
       <c r="D30" s="6">
-        <v>-1.18</v>
+        <v>-2.4</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.06</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3816,13 +3816,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>0.22</v>
+        <v>-0.35</v>
       </c>
       <c r="D31" s="6">
-        <v>-0.35</v>
+        <v>-2.17</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.57</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3833,13 +3833,13 @@
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-1.68</v>
+        <v>-1.83</v>
       </c>
       <c r="D32" s="6">
-        <v>-1.83</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.15</v>
+        <v>-1.67</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.16</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3850,13 +3850,13 @@
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-1.55</v>
+        <v>-1.94</v>
       </c>
       <c r="D33" s="6">
-        <v>-1.94</v>
+        <v>-3.31</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.39</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3867,13 +3867,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>-6.32</v>
+        <v>-5.78</v>
       </c>
       <c r="D34" s="6">
-        <v>-5.78</v>
+        <v>-1.47</v>
       </c>
       <c r="E34" s="8">
-        <v>0.54</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3884,13 +3884,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>-0.96</v>
+        <v>-1.57</v>
       </c>
       <c r="D35" s="6">
-        <v>-1.57</v>
+        <v>-3.72</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.61</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3901,13 +3901,13 @@
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-0.77</v>
+        <v>-1.31</v>
       </c>
       <c r="D36" s="6">
-        <v>-1.31</v>
+        <v>-3.02</v>
       </c>
       <c r="E36" s="7">
-        <v>-0.54</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3918,13 +3918,13 @@
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.66</v>
+        <v>-1.8</v>
       </c>
       <c r="D37" s="6">
-        <v>-1.8</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.14</v>
+        <v>-1.1</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.7</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3935,13 +3935,13 @@
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>0.98</v>
+        <v>-2.39</v>
       </c>
       <c r="D38" s="6">
-        <v>-2.39</v>
+        <v>-3.68</v>
       </c>
       <c r="E38" s="7">
-        <v>-3.37</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3952,13 +3952,13 @@
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>0.45</v>
+        <v>-0.22</v>
       </c>
       <c r="D39" s="6">
-        <v>-0.22</v>
+        <v>-2.2</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.67</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3969,13 +3969,13 @@
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-1.76</v>
+        <v>-1.94</v>
       </c>
       <c r="D40" s="6">
-        <v>-1.94</v>
+        <v>-3.16</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.18</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3986,13 +3986,13 @@
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>-0.39</v>
+        <v>0.21</v>
       </c>
       <c r="D41" s="6">
-        <v>0.21</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.6</v>
+        <v>-1.83</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -4003,13 +4003,13 @@
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>-4.81</v>
+        <v>-6.54</v>
       </c>
       <c r="D42" s="6">
-        <v>-6.54</v>
+        <v>-8.77</v>
       </c>
       <c r="E42" s="7">
-        <v>-1.73</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -4020,13 +4020,13 @@
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-2.09</v>
+        <v>-1.98</v>
       </c>
       <c r="D43" s="6">
-        <v>-1.98</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.11</v>
+        <v>-2.28</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -4037,13 +4037,13 @@
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>-0.2</v>
+        <v>0.51</v>
       </c>
       <c r="D44" s="6">
-        <v>0.51</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.71</v>
+        <v>-1.34</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-1.85</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4054,13 +4054,13 @@
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>1.29</v>
+        <v>0.15</v>
       </c>
       <c r="D45" s="6">
-        <v>0.15</v>
+        <v>-6.26</v>
       </c>
       <c r="E45" s="7">
-        <v>-1.14</v>
+        <v>-6.41</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -4071,13 +4071,13 @@
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-1.21</v>
+        <v>-2.24</v>
       </c>
       <c r="D46" s="6">
-        <v>-2.24</v>
+        <v>-2.9</v>
       </c>
       <c r="E46" s="7">
-        <v>-1.03</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -4088,13 +4088,13 @@
         <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>-1.59</v>
+        <v>-1.4</v>
       </c>
       <c r="D47" s="6">
-        <v>-1.4</v>
-      </c>
-      <c r="E47" s="8">
-        <v>0.19</v>
+        <v>-2.44</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4105,13 +4105,13 @@
         <v>12</v>
       </c>
       <c r="C48" s="6">
-        <v>6.85</v>
+        <v>5.04</v>
       </c>
       <c r="D48" s="6">
-        <v>5.04</v>
+        <v>1.66</v>
       </c>
       <c r="E48" s="7">
-        <v>-1.81</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -4122,13 +4122,13 @@
         <v>12</v>
       </c>
       <c r="C49" s="6">
-        <v>9.85</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="D49" s="6">
-        <v>9.119999999999999</v>
+        <v>7.06</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.73</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -4139,13 +4139,13 @@
         <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>-6.36</v>
+        <v>-7.27</v>
       </c>
       <c r="D50" s="6">
-        <v>-7.27</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="E50" s="7">
-        <v>-0.91</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4156,13 +4156,13 @@
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>10.39</v>
+        <v>10.65</v>
       </c>
       <c r="D51" s="6">
-        <v>10.65</v>
-      </c>
-      <c r="E51" s="8">
-        <v>0.26</v>
+        <v>8.31</v>
+      </c>
+      <c r="E51" s="7">
+        <v>-2.34</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -4173,13 +4173,13 @@
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-20.68</v>
+        <v>-21.1</v>
       </c>
       <c r="D52" s="6">
-        <v>-21.1</v>
-      </c>
-      <c r="E52" s="7">
-        <v>-0.42</v>
+        <v>-20.36</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0.74</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4190,13 +4190,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-0.82</v>
+        <v>-1.19</v>
       </c>
       <c r="D53" s="6">
-        <v>-1.19</v>
+        <v>-3.14</v>
       </c>
       <c r="E53" s="7">
-        <v>-0.37</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -4207,13 +4207,13 @@
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-18.56</v>
+        <v>-17.7</v>
       </c>
       <c r="D54" s="6">
-        <v>-17.7</v>
+        <v>-14.67</v>
       </c>
       <c r="E54" s="8">
-        <v>0.86</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -4224,13 +4224,13 @@
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="D55" s="6">
-        <v>1.56</v>
+        <v>-0.5</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.09</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -4241,13 +4241,13 @@
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-5.37</v>
+        <v>-4.58</v>
       </c>
       <c r="D56" s="6">
-        <v>-4.58</v>
-      </c>
-      <c r="E56" s="8">
-        <v>0.79</v>
+        <v>-7.19</v>
+      </c>
+      <c r="E56" s="7">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -4258,13 +4258,13 @@
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>37.5</v>
+        <v>35.18</v>
       </c>
       <c r="D57" s="6">
-        <v>35.18</v>
+        <v>30.86</v>
       </c>
       <c r="E57" s="7">
-        <v>-2.32</v>
+        <v>-4.32</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -4275,13 +4275,13 @@
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>2.59</v>
+        <v>3.11</v>
       </c>
       <c r="D58" s="6">
-        <v>3.11</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.52</v>
+        <v>0.66</v>
+      </c>
+      <c r="E58" s="7">
+        <v>-2.45</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -4292,13 +4292,13 @@
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>21.4</v>
+        <v>22</v>
       </c>
       <c r="D59" s="6">
-        <v>22</v>
-      </c>
-      <c r="E59" s="8">
-        <v>0.6</v>
+        <v>19</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -4309,13 +4309,13 @@
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>20.93</v>
+        <v>21.07</v>
       </c>
       <c r="D60" s="6">
-        <v>21.07</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.14</v>
+        <v>19.45</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-1.62</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -4326,13 +4326,13 @@
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>-1.98</v>
+        <v>-3.88</v>
       </c>
       <c r="D61" s="6">
-        <v>-3.88</v>
+        <v>-6.68</v>
       </c>
       <c r="E61" s="7">
-        <v>-1.9</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -4343,13 +4343,13 @@
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>-6.52</v>
+        <v>-6.45</v>
       </c>
       <c r="D62" s="6">
-        <v>-6.45</v>
-      </c>
-      <c r="E62" s="8">
-        <v>0.07000000000000001</v>
+        <v>-7.13</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -4360,13 +4360,13 @@
         <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>3.9</v>
+        <v>4.37</v>
       </c>
       <c r="D63" s="6">
-        <v>4.37</v>
-      </c>
-      <c r="E63" s="8">
-        <v>0.47</v>
+        <v>2.78</v>
+      </c>
+      <c r="E63" s="7">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -4377,13 +4377,13 @@
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>4.74</v>
+        <v>1.21</v>
       </c>
       <c r="D64" s="6">
-        <v>1.21</v>
+        <v>-0.5</v>
       </c>
       <c r="E64" s="7">
-        <v>-3.53</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -4394,13 +4394,13 @@
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-1.89</v>
+        <v>-4.41</v>
       </c>
       <c r="D65" s="6">
-        <v>-4.41</v>
+        <v>-6.01</v>
       </c>
       <c r="E65" s="7">
-        <v>-2.52</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4411,13 +4411,13 @@
         <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>2.54</v>
+        <v>0.33</v>
       </c>
       <c r="D66" s="6">
-        <v>0.33</v>
+        <v>-1.77</v>
       </c>
       <c r="E66" s="7">
-        <v>-2.21</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4428,13 +4428,13 @@
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-2.6</v>
+        <v>-3.95</v>
       </c>
       <c r="D67" s="6">
-        <v>-3.95</v>
+        <v>-6.93</v>
       </c>
       <c r="E67" s="7">
-        <v>-1.35</v>
+        <v>-2.98</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4445,13 +4445,13 @@
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-7.46</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="D68" s="6">
-        <v>-8.130000000000001</v>
+        <v>-9.69</v>
       </c>
       <c r="E68" s="7">
-        <v>-0.67</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4462,13 +4462,13 @@
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-1.63</v>
+        <v>-2.78</v>
       </c>
       <c r="D69" s="6">
-        <v>-2.78</v>
+        <v>-5.16</v>
       </c>
       <c r="E69" s="7">
-        <v>-1.15</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4479,13 +4479,13 @@
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>3.94</v>
+        <v>3.04</v>
       </c>
       <c r="D70" s="6">
-        <v>3.04</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-0.9</v>
+        <v>3.46</v>
+      </c>
+      <c r="E70" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4496,13 +4496,13 @@
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>2.89</v>
+        <v>1.94</v>
       </c>
       <c r="D71" s="6">
-        <v>1.94</v>
+        <v>-1.85</v>
       </c>
       <c r="E71" s="7">
-        <v>-0.95</v>
+        <v>-3.79</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4513,13 +4513,13 @@
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-1.12</v>
+        <v>-3.13</v>
       </c>
       <c r="D72" s="6">
-        <v>-3.13</v>
+        <v>-5.47</v>
       </c>
       <c r="E72" s="7">
-        <v>-2.01</v>
+        <v>-2.34</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4530,13 +4530,13 @@
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>3.17</v>
+        <v>3.48</v>
       </c>
       <c r="D73" s="6">
-        <v>3.48</v>
-      </c>
-      <c r="E73" s="8">
-        <v>0.31</v>
+        <v>-0.16</v>
+      </c>
+      <c r="E73" s="7">
+        <v>-3.64</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4547,13 +4547,13 @@
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>3.5</v>
+        <v>-0.65</v>
       </c>
       <c r="D74" s="6">
-        <v>-0.65</v>
+        <v>-1.65</v>
       </c>
       <c r="E74" s="7">
-        <v>-4.15</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4564,13 +4564,13 @@
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-1.48</v>
+        <v>-2.67</v>
       </c>
       <c r="D75" s="6">
-        <v>-2.67</v>
+        <v>-5.49</v>
       </c>
       <c r="E75" s="7">
-        <v>-1.19</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4581,13 +4581,13 @@
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-1.49</v>
+        <v>-2.7</v>
       </c>
       <c r="D76" s="6">
-        <v>-2.7</v>
+        <v>-4.73</v>
       </c>
       <c r="E76" s="7">
-        <v>-1.21</v>
+        <v>-2.03</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4598,13 +4598,13 @@
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>8.92</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="D77" s="6">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="E77" s="8">
-        <v>0.63</v>
+        <v>8.41</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4615,13 +4615,13 @@
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>13.31</v>
+        <v>6.06</v>
       </c>
       <c r="D78" s="6">
-        <v>6.06</v>
+        <v>-0.47</v>
       </c>
       <c r="E78" s="7">
-        <v>-7.25</v>
+        <v>-6.53</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4632,13 +4632,13 @@
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-0.54</v>
+        <v>-1.29</v>
       </c>
       <c r="D79" s="6">
-        <v>-1.29</v>
+        <v>-2.75</v>
       </c>
       <c r="E79" s="7">
-        <v>-0.75</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4649,13 +4649,13 @@
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>6.22</v>
+        <v>6.05</v>
       </c>
       <c r="D80" s="6">
-        <v>6.05</v>
+        <v>5.61</v>
       </c>
       <c r="E80" s="7">
-        <v>-0.17</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
       <c r="D81" s="6">
-        <v>8.1</v>
+        <v>0.15</v>
       </c>
       <c r="E81" s="7">
-        <v>-0.8</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4683,13 +4683,13 @@
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>0.16</v>
+        <v>-0.68</v>
       </c>
       <c r="D82" s="6">
-        <v>-0.68</v>
+        <v>-4.41</v>
       </c>
       <c r="E82" s="7">
-        <v>-0.84</v>
+        <v>-3.73</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4700,13 +4700,13 @@
         <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-1.24</v>
+        <v>-1.35</v>
       </c>
       <c r="D83" s="6">
-        <v>-1.35</v>
+        <v>-3.03</v>
       </c>
       <c r="E83" s="7">
-        <v>-0.11</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4717,13 +4717,13 @@
         <v>7</v>
       </c>
       <c r="C84" s="6">
-        <v>-7.11</v>
+        <v>-7.9</v>
       </c>
       <c r="D84" s="6">
-        <v>-7.9</v>
+        <v>-9.75</v>
       </c>
       <c r="E84" s="7">
-        <v>-0.79</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4734,13 +4734,13 @@
         <v>7</v>
       </c>
       <c r="C85" s="6">
-        <v>-7.55</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="D85" s="6">
-        <v>-8.789999999999999</v>
+        <v>-10.43</v>
       </c>
       <c r="E85" s="7">
-        <v>-1.24</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4751,13 +4751,13 @@
         <v>7</v>
       </c>
       <c r="C86" s="6">
-        <v>-8.9</v>
+        <v>-9.32</v>
       </c>
       <c r="D86" s="6">
-        <v>-9.32</v>
+        <v>-10.73</v>
       </c>
       <c r="E86" s="7">
-        <v>-0.42</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4768,13 +4768,13 @@
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-7.97</v>
+        <v>-8.67</v>
       </c>
       <c r="D87" s="6">
-        <v>-8.67</v>
+        <v>-10.56</v>
       </c>
       <c r="E87" s="7">
-        <v>-0.7</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4785,13 +4785,13 @@
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-20.87</v>
+        <v>-20.9</v>
       </c>
       <c r="D88" s="6">
-        <v>-20.9</v>
+        <v>-21.3</v>
       </c>
       <c r="E88" s="7">
-        <v>-0.03</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4802,13 +4802,13 @@
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-10.34</v>
+        <v>-10.25</v>
       </c>
       <c r="D89" s="6">
-        <v>-10.25</v>
-      </c>
-      <c r="E89" s="8">
-        <v>0.09</v>
+        <v>-11.9</v>
+      </c>
+      <c r="E89" s="7">
+        <v>-1.65</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4819,13 +4819,13 @@
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-26.84</v>
+        <v>-26.76</v>
       </c>
       <c r="D90" s="6">
-        <v>-26.76</v>
+        <v>-25.15</v>
       </c>
       <c r="E90" s="8">
-        <v>0.08</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4836,13 +4836,13 @@
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-3.28</v>
+        <v>-4.17</v>
       </c>
       <c r="D91" s="6">
-        <v>-4.17</v>
+        <v>-6.47</v>
       </c>
       <c r="E91" s="7">
-        <v>-0.89</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4853,13 +4853,13 @@
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-6.47</v>
+        <v>-7.05</v>
       </c>
       <c r="D92" s="6">
-        <v>-7.05</v>
+        <v>-8.76</v>
       </c>
       <c r="E92" s="7">
-        <v>-0.58</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4870,13 +4870,13 @@
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-5.98</v>
+        <v>-5.84</v>
       </c>
       <c r="D93" s="6">
-        <v>-5.84</v>
-      </c>
-      <c r="E93" s="8">
-        <v>0.14</v>
+        <v>-7.88</v>
+      </c>
+      <c r="E93" s="7">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4887,13 +4887,13 @@
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-3.01</v>
+        <v>-5.24</v>
       </c>
       <c r="D94" s="6">
-        <v>-5.24</v>
+        <v>-7.65</v>
       </c>
       <c r="E94" s="7">
-        <v>-2.23</v>
+        <v>-2.41</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4904,13 +4904,13 @@
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-9.44</v>
+        <v>-10.01</v>
       </c>
       <c r="D95" s="6">
-        <v>-10.01</v>
+        <v>-12.07</v>
       </c>
       <c r="E95" s="7">
-        <v>-0.57</v>
+        <v>-2.06</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-14.96</v>
+        <v>-15.49</v>
       </c>
       <c r="D96" s="6">
-        <v>-15.49</v>
+        <v>-17.42</v>
       </c>
       <c r="E96" s="7">
-        <v>-0.53</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4938,13 +4938,13 @@
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-2.32</v>
+        <v>-2.41</v>
       </c>
       <c r="D97" s="6">
-        <v>-2.41</v>
+        <v>-3.67</v>
       </c>
       <c r="E97" s="7">
-        <v>-0.09</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4955,13 +4955,13 @@
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-9.970000000000001</v>
+        <v>-12.4</v>
       </c>
       <c r="D98" s="6">
-        <v>-12.4</v>
+        <v>-15.94</v>
       </c>
       <c r="E98" s="7">
-        <v>-2.43</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4972,13 +4972,13 @@
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-12.21</v>
+        <v>-12.12</v>
       </c>
       <c r="D99" s="6">
-        <v>-12.12</v>
-      </c>
-      <c r="E99" s="8">
-        <v>0.09</v>
+        <v>-12.82</v>
+      </c>
+      <c r="E99" s="7">
+        <v>-0.7</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4989,13 +4989,13 @@
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-2.5</v>
+        <v>-2.65</v>
       </c>
       <c r="D100" s="6">
-        <v>-2.65</v>
+        <v>-3.79</v>
       </c>
       <c r="E100" s="7">
-        <v>-0.15</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -5006,13 +5006,13 @@
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-2.03</v>
+        <v>-2.75</v>
       </c>
       <c r="D101" s="6">
-        <v>-2.75</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="E101" s="7">
-        <v>-0.72</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -5023,13 +5023,13 @@
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-2.98</v>
+        <v>-3.8</v>
       </c>
       <c r="D102" s="6">
-        <v>-3.8</v>
+        <v>-5.04</v>
       </c>
       <c r="E102" s="7">
-        <v>-0.82</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5040,13 +5040,13 @@
         <v>7</v>
       </c>
       <c r="C103" s="6">
-        <v>-6.45</v>
+        <v>-6</v>
       </c>
       <c r="D103" s="6">
-        <v>-6</v>
-      </c>
-      <c r="E103" s="8">
-        <v>0.45</v>
+        <v>-7.26</v>
+      </c>
+      <c r="E103" s="7">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5057,13 +5057,13 @@
         <v>3</v>
       </c>
       <c r="C104" s="6">
-        <v>27540.95</v>
+        <v>27304.5</v>
       </c>
       <c r="D104" s="6">
-        <v>27304.5</v>
+        <v>26756.6</v>
       </c>
       <c r="E104" s="7">
-        <v>-236.45</v>
+        <v>-547.9</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5074,13 +5074,13 @@
         <v>3</v>
       </c>
       <c r="C105" s="6">
-        <v>9709.9</v>
+        <v>9579.799999999999</v>
       </c>
       <c r="D105" s="6">
-        <v>9579.799999999999</v>
+        <v>9407.549999999999</v>
       </c>
       <c r="E105" s="7">
-        <v>-130.1</v>
+        <v>-172.25</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5091,13 +5091,13 @@
         <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>11514.75</v>
+        <v>11460.6</v>
       </c>
       <c r="D106" s="6">
-        <v>11460.6</v>
+        <v>11282.8</v>
       </c>
       <c r="E106" s="7">
-        <v>-54.15</v>
+        <v>-177.8</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5108,13 +5108,13 @@
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>38223.4</v>
+        <v>37935.2</v>
       </c>
       <c r="D107" s="6">
-        <v>37935.2</v>
+        <v>37147.95</v>
       </c>
       <c r="E107" s="7">
-        <v>-288.2</v>
+        <v>-787.25</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5125,13 +5125,13 @@
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>45185.6</v>
+        <v>45053.75</v>
       </c>
       <c r="D108" s="6">
-        <v>45053.75</v>
+        <v>44829.95</v>
       </c>
       <c r="E108" s="7">
-        <v>-131.85</v>
+        <v>-223.8</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5142,13 +5142,13 @@
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>25520.3</v>
+        <v>25545.4</v>
       </c>
       <c r="D109" s="6">
-        <v>25545.4</v>
-      </c>
-      <c r="E109" s="8">
-        <v>25.1</v>
+        <v>25076.65</v>
+      </c>
+      <c r="E109" s="7">
+        <v>-468.75</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5159,13 +5159,13 @@
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>28890.9</v>
+        <v>28921.5</v>
       </c>
       <c r="D110" s="6">
-        <v>28921.5</v>
+        <v>29555.3</v>
       </c>
       <c r="E110" s="8">
-        <v>30.6</v>
+        <v>633.8</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>16115.7</v>
+        <v>15967.45</v>
       </c>
       <c r="D111" s="6">
-        <v>15967.45</v>
+        <v>15584.65</v>
       </c>
       <c r="E111" s="7">
-        <v>-148.25</v>
+        <v>-382.8</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5193,13 +5193,13 @@
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>9133.450000000001</v>
+        <v>9077.15</v>
       </c>
       <c r="D112" s="6">
-        <v>9077.15</v>
+        <v>8910.75</v>
       </c>
       <c r="E112" s="7">
-        <v>-56.3</v>
+        <v>-166.4</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5210,13 +5210,13 @@
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>1534.8</v>
+        <v>1537.2</v>
       </c>
       <c r="D113" s="6">
-        <v>1537.2</v>
-      </c>
-      <c r="E113" s="8">
-        <v>2.4</v>
+        <v>1503.9</v>
+      </c>
+      <c r="E113" s="7">
+        <v>-33.3</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5227,13 +5227,13 @@
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>13304.95</v>
+        <v>12999.05</v>
       </c>
       <c r="D114" s="6">
-        <v>12999.05</v>
+        <v>12669.15</v>
       </c>
       <c r="E114" s="7">
-        <v>-305.9</v>
+        <v>-329.9</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5244,13 +5244,13 @@
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>9750.35</v>
+        <v>9688.4</v>
       </c>
       <c r="D115" s="6">
-        <v>9688.4</v>
+        <v>9467</v>
       </c>
       <c r="E115" s="7">
-        <v>-61.95</v>
+        <v>-221.4</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5261,13 +5261,13 @@
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>8401.85</v>
+        <v>8349.9</v>
       </c>
       <c r="D116" s="6">
-        <v>8349.9</v>
+        <v>8158.5</v>
       </c>
       <c r="E116" s="7">
-        <v>-51.95</v>
+        <v>-191.4</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5278,13 +5278,13 @@
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>26555.85</v>
+        <v>26532.4</v>
       </c>
       <c r="D117" s="6">
-        <v>26532.4</v>
+        <v>26188.4</v>
       </c>
       <c r="E117" s="7">
-        <v>-23.45</v>
+        <v>-344</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -5295,13 +5295,13 @@
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>872.05</v>
+        <v>848.5</v>
       </c>
       <c r="D118" s="6">
-        <v>848.5</v>
+        <v>814.25</v>
       </c>
       <c r="E118" s="7">
-        <v>-23.55</v>
+        <v>-34.25</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -5312,13 +5312,13 @@
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>29936.6</v>
+        <v>29969.35</v>
       </c>
       <c r="D119" s="6">
-        <v>29969.35</v>
-      </c>
-      <c r="E119" s="8">
-        <v>32.75</v>
+        <v>29728.85</v>
+      </c>
+      <c r="E119" s="7">
+        <v>-240.5</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -5329,13 +5329,13 @@
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>16518.65</v>
+        <v>16492.1</v>
       </c>
       <c r="D120" s="6">
-        <v>16492.1</v>
+        <v>16299</v>
       </c>
       <c r="E120" s="7">
-        <v>-26.55</v>
+        <v>-193.1</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5346,13 +5346,13 @@
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>9795.700000000001</v>
+        <v>9723.85</v>
       </c>
       <c r="D121" s="6">
-        <v>9723.85</v>
+        <v>9144.15</v>
       </c>
       <c r="E121" s="7">
-        <v>-71.84999999999999</v>
+        <v>-579.7</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -5363,13 +5363,13 @@
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>11029.9</v>
+        <v>10937</v>
       </c>
       <c r="D122" s="6">
-        <v>10937</v>
+        <v>10796.4</v>
       </c>
       <c r="E122" s="7">
-        <v>-92.90000000000001</v>
+        <v>-140.6</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -5380,44 +5380,44 @@
         <v>3</v>
       </c>
       <c r="C123" s="6">
-        <v>27305.9</v>
+        <v>27436</v>
       </c>
       <c r="D123" s="6">
-        <v>27436</v>
-      </c>
-      <c r="E123" s="8">
-        <v>130.1</v>
+        <v>27069.8</v>
+      </c>
+      <c r="E123" s="7">
+        <v>-366.2</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C124" s="6">
-        <v>74</v>
+        <v>19</v>
       </c>
       <c r="D124" s="6">
-        <v>62</v>
+        <v>13</v>
       </c>
       <c r="E124" s="7">
-        <v>-12</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C125" s="6">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D125" s="6">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="E125" s="8">
         <v>6</v>
@@ -5425,461 +5425,410 @@
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="6">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D126" s="6">
         <v>19</v>
       </c>
-      <c r="E126" s="7">
-        <v>-7</v>
+      <c r="E126" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="D127" s="6">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="E127" s="8">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D128" s="6">
-        <v>38</v>
-      </c>
-      <c r="E128" s="7">
-        <v>-6</v>
+        <v>56</v>
+      </c>
+      <c r="E128" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="D129" s="6">
-        <v>44</v>
-      </c>
-      <c r="E129" s="8">
-        <v>6</v>
+        <v>32</v>
+      </c>
+      <c r="E129" s="7">
+        <v>-24</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C130" s="6">
-        <v>81</v>
+        <v>27.65</v>
       </c>
       <c r="D130" s="6">
-        <v>56</v>
+        <v>21.9</v>
       </c>
       <c r="E130" s="7">
-        <v>-25</v>
+        <v>-5.75</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C131" s="6">
-        <v>19</v>
+        <v>34.25</v>
       </c>
       <c r="D131" s="6">
-        <v>26</v>
-      </c>
-      <c r="E131" s="8">
-        <v>7</v>
+        <v>26.94</v>
+      </c>
+      <c r="E131" s="7">
+        <v>-7.31</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C132" s="6">
-        <v>56</v>
+        <v>25.13</v>
       </c>
       <c r="D132" s="6">
-        <v>74</v>
-      </c>
-      <c r="E132" s="8">
-        <v>18</v>
+        <v>19.64</v>
+      </c>
+      <c r="E132" s="7">
+        <v>-5.49</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="6">
-        <v>30.91</v>
+        <v>39.53</v>
       </c>
       <c r="D133" s="6">
-        <v>27.65</v>
+        <v>27.62</v>
       </c>
       <c r="E133" s="7">
-        <v>-3.26</v>
+        <v>-11.91</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="6">
-        <v>42.31</v>
+        <v>24.38</v>
       </c>
       <c r="D134" s="6">
-        <v>34.25</v>
+        <v>22.94</v>
       </c>
       <c r="E134" s="7">
-        <v>-8.06</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>27.29</v>
+        <v>35.05</v>
       </c>
       <c r="D135" s="6">
-        <v>25.13</v>
+        <v>27.63</v>
       </c>
       <c r="E135" s="7">
-        <v>-2.16</v>
+        <v>-7.42</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>46.32</v>
+        <v>34.68</v>
       </c>
       <c r="D136" s="6">
-        <v>39.53</v>
-      </c>
-      <c r="E136" s="7">
-        <v>-6.79</v>
+        <v>43.12</v>
+      </c>
+      <c r="E136" s="8">
+        <v>8.44</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>25.24</v>
+        <v>28.43</v>
       </c>
       <c r="D137" s="6">
-        <v>24.38</v>
+        <v>19.31</v>
       </c>
       <c r="E137" s="7">
-        <v>-0.86</v>
+        <v>-9.119999999999999</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>34.17</v>
+        <v>28.79</v>
       </c>
       <c r="D138" s="6">
-        <v>35.05</v>
-      </c>
-      <c r="E138" s="8">
-        <v>0.88</v>
+        <v>20.64</v>
+      </c>
+      <c r="E138" s="7">
+        <v>-8.15</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>34.24</v>
+        <v>44.65</v>
       </c>
       <c r="D139" s="6">
-        <v>34.68</v>
-      </c>
-      <c r="E139" s="8">
-        <v>0.44</v>
+        <v>38.31</v>
+      </c>
+      <c r="E139" s="7">
+        <v>-6.34</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>34.25</v>
+        <v>45.23</v>
       </c>
       <c r="D140" s="6">
-        <v>28.43</v>
+        <v>37.28</v>
       </c>
       <c r="E140" s="7">
-        <v>-5.82</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>32.88</v>
+        <v>39.59</v>
       </c>
       <c r="D141" s="6">
-        <v>28.79</v>
+        <v>25.24</v>
       </c>
       <c r="E141" s="7">
-        <v>-4.09</v>
+        <v>-14.35</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>44.03</v>
+        <v>37.15</v>
       </c>
       <c r="D142" s="6">
-        <v>44.65</v>
-      </c>
-      <c r="E142" s="8">
-        <v>0.62</v>
+        <v>28.5</v>
+      </c>
+      <c r="E142" s="7">
+        <v>-8.65</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>55.41</v>
+        <v>49.68</v>
       </c>
       <c r="D143" s="6">
-        <v>45.23</v>
+        <v>41.78</v>
       </c>
       <c r="E143" s="7">
-        <v>-10.18</v>
+        <v>-7.9</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>46.46</v>
+        <v>31.07</v>
       </c>
       <c r="D144" s="6">
-        <v>39.59</v>
+        <v>24.06</v>
       </c>
       <c r="E144" s="7">
-        <v>-6.87</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>40.22</v>
+        <v>29.87</v>
       </c>
       <c r="D145" s="6">
-        <v>37.15</v>
+        <v>26.12</v>
       </c>
       <c r="E145" s="7">
-        <v>-3.07</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>50.28</v>
+        <v>47.06</v>
       </c>
       <c r="D146" s="6">
-        <v>49.68</v>
+        <v>39.84</v>
       </c>
       <c r="E146" s="7">
-        <v>-0.6</v>
+        <v>-7.22</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>38.17</v>
+        <v>50.65</v>
       </c>
       <c r="D147" s="6">
-        <v>31.07</v>
+        <v>31.51</v>
       </c>
       <c r="E147" s="7">
-        <v>-7.1</v>
+        <v>-19.14</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>28.57</v>
+        <v>32.09</v>
       </c>
       <c r="D148" s="6">
-        <v>29.87</v>
-      </c>
-      <c r="E148" s="8">
-        <v>1.3</v>
+        <v>25.42</v>
+      </c>
+      <c r="E148" s="7">
+        <v>-6.67</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>48.17</v>
+        <v>45.6</v>
       </c>
       <c r="D149" s="6">
-        <v>47.06</v>
+        <v>38.17</v>
       </c>
       <c r="E149" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C150" s="6">
-        <v>54.46</v>
-      </c>
-      <c r="D150" s="6">
-        <v>50.65</v>
-      </c>
-      <c r="E150" s="7">
-        <v>-3.81</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C151" s="6">
-        <v>38.24</v>
-      </c>
-      <c r="D151" s="6">
-        <v>32.09</v>
-      </c>
-      <c r="E151" s="7">
-        <v>-6.15</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C152" s="6">
-        <v>41.87</v>
-      </c>
-      <c r="D152" s="6">
-        <v>45.6</v>
-      </c>
-      <c r="E152" s="8">
-        <v>3.73</v>
+        <v>-7.43</v>
       </c>
     </row>
   </sheetData>
@@ -5938,22 +5887,22 @@
         <v>78</v>
       </c>
       <c r="B2" s="11">
-        <v>43.24</v>
+        <v>39.24</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>36.5</v>
+        <v>29.3</v>
       </c>
       <c r="E2" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.3</v>
+        <v>-4.9</v>
       </c>
       <c r="G2" s="11">
-        <v>0.4</v>
+        <v>-2.1</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -6061,130 +6010,130 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="13" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C1" s="13" t="s">
         <v>54</v>
       </c>
       <c r="D1" s="13" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F1" s="13" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H1" s="13" t="s">
         <v>46</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.3669</v>
+        <v>0.2761</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2901</v>
+        <v>0.2105</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2657</v>
+        <v>0.1978</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2199</v>
+        <v>0.1955</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2084</v>
+        <v>0.1668</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1738</v>
+        <v>0.1401</v>
       </c>
       <c r="G2" s="14">
-        <v>0.151</v>
+        <v>0.1257</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1341</v>
+        <v>0.1256</v>
       </c>
       <c r="I2" s="14">
-        <v>0.1305</v>
+        <v>0.1171</v>
       </c>
       <c r="J2" s="14">
-        <v>0.1258</v>
+        <v>0.1045</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>42</v>
-      </c>
       <c r="H3" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="J3" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.1102</v>
+        <v>0.0941</v>
       </c>
       <c r="B4" s="14">
-        <v>0.1005</v>
+        <v>0.0713</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0803</v>
+        <v>0.0667</v>
       </c>
       <c r="D4" s="14">
-        <v>0.07780000000000001</v>
+        <v>0.06509999999999999</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0711</v>
+        <v>0.0385</v>
       </c>
       <c r="F4" s="14">
-        <v>0.04269999999999999</v>
+        <v>0.0205</v>
       </c>
       <c r="G4" s="14">
-        <v>0.0211</v>
+        <v>-0.0191</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0227</v>
+        <v>-0.0391</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.0272</v>
+        <v>-0.0499</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.0382</v>
+        <v>-0.0733</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="119">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,28 +289,55 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.6 → 31.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.6</t>
-  </si>
-  <si>
-    <t>31.5</t>
-  </si>
-  <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.9 → 30.2</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>26.9</t>
+  </si>
+  <si>
+    <t>30.2</t>
+  </si>
+  <si>
+    <t>22.9 → 36.1</t>
+  </si>
+  <si>
+    <t>22.9</t>
+  </si>
+  <si>
+    <t>36.1</t>
+  </si>
+  <si>
+    <t>27.6 → 33.6</t>
+  </si>
+  <si>
+    <t>27.6</t>
+  </si>
+  <si>
+    <t>33.6</t>
+  </si>
+  <si>
+    <t>28.5 → 38.0</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>38.0</t>
+  </si>
+  <si>
+    <t>25.4 → 33.5</t>
+  </si>
+  <si>
+    <t>25.4</t>
+  </si>
+  <si>
+    <t>33.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -396,14 +423,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -436,13 +463,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1040,10 +1067,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>26756.6</v>
+        <v>26893.65</v>
       </c>
       <c r="E2">
-        <v>-2.01</v>
+        <v>0.51</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1052,43 +1079,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-9.75</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="I2">
-        <v>12.57</v>
+        <v>13.14</v>
       </c>
       <c r="J2">
-        <v>-3.4</v>
+        <v>-3.17</v>
       </c>
       <c r="K2">
-        <v>-8.390000000000001</v>
+        <v>-7.83</v>
       </c>
       <c r="L2">
-        <v>-0.5</v>
+        <v>0.63</v>
       </c>
       <c r="M2">
-        <v>1.66</v>
+        <v>-1.09</v>
       </c>
       <c r="N2">
-        <v>21.05</v>
+        <v>21.04</v>
       </c>
       <c r="O2">
         <v>62</v>
       </c>
       <c r="Q2">
-        <v>27406.15</v>
+        <v>27229.81</v>
       </c>
       <c r="R2">
-        <v>28384.97</v>
+        <v>28266.43</v>
       </c>
       <c r="S2">
-        <v>28115.58</v>
+        <v>28106.58</v>
       </c>
       <c r="T2">
-        <v>27135.3</v>
+        <v>27132.56</v>
       </c>
       <c r="U2">
-        <v>-1.4</v>
+        <v>-0.88</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1103,40 +1130,40 @@
         <v>2</v>
       </c>
       <c r="Z2">
-        <v>21.9</v>
+        <v>26.04</v>
       </c>
       <c r="AA2">
-        <v>-344.52</v>
+        <v>-389.83</v>
       </c>
       <c r="AB2">
-        <v>-123.77</v>
+        <v>-176.98</v>
       </c>
       <c r="AC2">
-        <v>-220.75</v>
+        <v>-212.84</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="AE2">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="AF2">
-        <v>394.12</v>
+        <v>391.23</v>
       </c>
       <c r="AH2">
-        <v>29987.01</v>
+        <v>29943.53</v>
       </c>
       <c r="AI2">
-        <v>26782.94</v>
+        <v>26589.32</v>
       </c>
       <c r="AJ2">
-        <v>28309.42</v>
+        <v>28052.54</v>
       </c>
       <c r="AK2" t="s">
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>69.73</v>
+        <v>72.59</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1150,10 +1177,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9407.549999999999</v>
+        <v>9442.15</v>
       </c>
       <c r="E3">
-        <v>-1.8</v>
+        <v>0.37</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1162,43 +1189,43 @@
         <v>8813</v>
       </c>
       <c r="H3">
-        <v>-10.43</v>
+        <v>-10.1</v>
       </c>
       <c r="I3">
-        <v>6.75</v>
+        <v>7.14</v>
       </c>
       <c r="J3">
-        <v>-3.04</v>
+        <v>-2.42</v>
       </c>
       <c r="K3">
-        <v>-4.23</v>
+        <v>-4.08</v>
       </c>
       <c r="L3">
-        <v>-6.01</v>
+        <v>-6</v>
       </c>
       <c r="M3">
-        <v>7.06</v>
+        <v>7.03</v>
       </c>
       <c r="N3">
-        <v>10.45</v>
+        <v>10.54</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="Q3">
-        <v>9622.41</v>
+        <v>9575.6</v>
       </c>
       <c r="R3">
-        <v>9743.559999999999</v>
+        <v>9724.92</v>
       </c>
       <c r="S3">
-        <v>9820.32</v>
+        <v>9811.01</v>
       </c>
       <c r="T3">
-        <v>9756.51</v>
+        <v>9758.379999999999</v>
       </c>
       <c r="U3">
-        <v>-3.58</v>
+        <v>-3.24</v>
       </c>
       <c r="V3" t="s">
         <v>80</v>
@@ -1213,40 +1240,40 @@
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>26.94</v>
+        <v>30.16</v>
       </c>
       <c r="AA3">
-        <v>-74.44</v>
+        <v>-87.5</v>
       </c>
       <c r="AB3">
-        <v>-47.07</v>
+        <v>-55.15</v>
       </c>
       <c r="AC3">
-        <v>-27.37</v>
+        <v>-32.35</v>
       </c>
       <c r="AD3">
-        <v>15.08</v>
+        <v>5.13</v>
       </c>
       <c r="AE3">
-        <v>30.23</v>
+        <v>18.32</v>
       </c>
       <c r="AF3">
-        <v>107.61</v>
+        <v>107.38</v>
       </c>
       <c r="AH3">
-        <v>9957.139999999999</v>
+        <v>9974.33</v>
       </c>
       <c r="AI3">
-        <v>9529.98</v>
+        <v>9475.51</v>
       </c>
       <c r="AJ3">
-        <v>9832.969999999999</v>
+        <v>9750.9</v>
       </c>
       <c r="AK3" t="s">
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>35.09</v>
+        <v>38.75</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1260,10 +1287,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11282.8</v>
+        <v>11361.65</v>
       </c>
       <c r="E4">
-        <v>-1.55</v>
+        <v>0.7</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1272,43 +1299,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-10.73</v>
+        <v>-10.11</v>
       </c>
       <c r="I4">
-        <v>9.18</v>
+        <v>9.94</v>
       </c>
       <c r="J4">
-        <v>-2.4</v>
+        <v>-1.8</v>
       </c>
       <c r="K4">
-        <v>-7.08</v>
+        <v>-5.83</v>
       </c>
       <c r="L4">
-        <v>-1.77</v>
+        <v>-1.68</v>
       </c>
       <c r="M4">
-        <v>-8.789999999999999</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="N4">
-        <v>9.41</v>
+        <v>9.42</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q4">
-        <v>11471.83</v>
+        <v>11430.29</v>
       </c>
       <c r="R4">
-        <v>11773.74</v>
+        <v>11741.59</v>
       </c>
       <c r="S4">
-        <v>11847.6</v>
+        <v>11837.35</v>
       </c>
       <c r="T4">
-        <v>11642.86</v>
+        <v>11637.56</v>
       </c>
       <c r="U4">
-        <v>-3.09</v>
+        <v>-2.37</v>
       </c>
       <c r="V4" t="s">
         <v>80</v>
@@ -1323,40 +1350,40 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>19.64</v>
+        <v>27.24</v>
       </c>
       <c r="AA4">
-        <v>-141.09</v>
+        <v>-149.31</v>
       </c>
       <c r="AB4">
-        <v>-84.83</v>
+        <v>-97.72</v>
       </c>
       <c r="AC4">
-        <v>-56.26</v>
+        <v>-51.58</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="AE4">
-        <v>0.32</v>
+        <v>3.2</v>
       </c>
       <c r="AF4">
-        <v>109.2</v>
+        <v>110.35</v>
       </c>
       <c r="AH4">
-        <v>12257.49</v>
+        <v>12245.75</v>
       </c>
       <c r="AI4">
-        <v>11290</v>
+        <v>11237.43</v>
       </c>
       <c r="AJ4">
-        <v>11730.69</v>
+        <v>11665.92</v>
       </c>
       <c r="AK4" t="s">
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>57.58</v>
+        <v>61.06</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1370,10 +1397,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>37147.95</v>
+        <v>37183.4</v>
       </c>
       <c r="E5">
-        <v>-2.08</v>
+        <v>0.1</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1382,43 +1409,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-10.56</v>
+        <v>-10.48</v>
       </c>
       <c r="I5">
-        <v>12.24</v>
+        <v>12.34</v>
       </c>
       <c r="J5">
-        <v>-2.17</v>
+        <v>-2.39</v>
       </c>
       <c r="K5">
-        <v>-3.65</v>
+        <v>-3.8</v>
       </c>
       <c r="L5">
-        <v>-6.93</v>
+        <v>-7.59</v>
       </c>
       <c r="M5">
-        <v>8.31</v>
+        <v>8.44</v>
       </c>
       <c r="N5">
-        <v>11.71</v>
+        <v>11.41</v>
       </c>
       <c r="O5">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="Q5">
-        <v>37946.74</v>
+        <v>37764.72</v>
       </c>
       <c r="R5">
-        <v>38078.05</v>
+        <v>38008.27</v>
       </c>
       <c r="S5">
-        <v>38627.01</v>
+        <v>38586.91</v>
       </c>
       <c r="T5">
-        <v>37546.74</v>
+        <v>37555.51</v>
       </c>
       <c r="U5">
-        <v>-1.06</v>
+        <v>-0.99</v>
       </c>
       <c r="V5" t="s">
         <v>80</v>
@@ -1433,40 +1460,40 @@
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>27.62</v>
+        <v>28.66</v>
       </c>
       <c r="AA5">
-        <v>-244.54</v>
+        <v>-289.4</v>
       </c>
       <c r="AB5">
-        <v>-225.28</v>
+        <v>-238.11</v>
       </c>
       <c r="AC5">
-        <v>-19.25</v>
+        <v>-51.29</v>
       </c>
       <c r="AD5">
-        <v>46.21</v>
+        <v>19.28</v>
       </c>
       <c r="AE5">
-        <v>73.65000000000001</v>
+        <v>48.35</v>
       </c>
       <c r="AF5">
-        <v>388.97</v>
+        <v>395.49</v>
       </c>
       <c r="AH5">
-        <v>38634.62</v>
+        <v>38644.66</v>
       </c>
       <c r="AI5">
-        <v>37521.47</v>
+        <v>37371.89</v>
       </c>
       <c r="AJ5">
-        <v>38726.95</v>
+        <v>38269.93</v>
       </c>
       <c r="AK5" t="s">
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>21.32</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1480,10 +1507,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>44829.95</v>
+        <v>45559</v>
       </c>
       <c r="E6">
-        <v>-0.5</v>
+        <v>1.63</v>
       </c>
       <c r="F6">
         <v>56960.6</v>
@@ -1492,43 +1519,43 @@
         <v>44829.95</v>
       </c>
       <c r="H6">
-        <v>-21.3</v>
+        <v>-20.02</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="J6">
-        <v>-1.67</v>
+        <v>-0.42</v>
       </c>
       <c r="K6">
-        <v>-7.79</v>
+        <v>-5.29</v>
       </c>
       <c r="L6">
-        <v>-9.69</v>
+        <v>-8.07</v>
       </c>
       <c r="M6">
-        <v>-20.36</v>
+        <v>-18.89</v>
       </c>
       <c r="N6">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>45225.68</v>
+        <v>45187.51</v>
       </c>
       <c r="R6">
-        <v>46478.02</v>
+        <v>46369.23</v>
       </c>
       <c r="S6">
-        <v>47975.5</v>
+        <v>47882.16</v>
       </c>
       <c r="T6">
-        <v>50254.07</v>
+        <v>50206.17</v>
       </c>
       <c r="U6">
-        <v>-10.79</v>
+        <v>-9.26</v>
       </c>
       <c r="V6" t="s">
         <v>80</v>
@@ -1543,31 +1570,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>22.94</v>
+        <v>36.15</v>
       </c>
       <c r="AA6">
-        <v>-906.63</v>
+        <v>-857.2</v>
       </c>
       <c r="AB6">
-        <v>-791.85</v>
+        <v>-804.92</v>
       </c>
       <c r="AC6">
-        <v>-114.78</v>
+        <v>-52.28</v>
       </c>
       <c r="AD6">
-        <v>0.2</v>
+        <v>33.33</v>
       </c>
       <c r="AE6">
-        <v>4.83</v>
+        <v>11.96</v>
       </c>
       <c r="AF6">
-        <v>533.9400000000001</v>
+        <v>561.4299999999999</v>
       </c>
       <c r="AH6">
-        <v>48530.67</v>
+        <v>48371.44</v>
       </c>
       <c r="AI6">
-        <v>44425.38</v>
+        <v>44367.03</v>
       </c>
       <c r="AJ6">
         <v>46607.06</v>
@@ -1576,7 +1603,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>72.29000000000001</v>
+        <v>67.45999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1590,10 +1617,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25076.65</v>
+        <v>25262.4</v>
       </c>
       <c r="E7">
-        <v>-1.83</v>
+        <v>0.74</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1602,43 +1629,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-11.9</v>
+        <v>-11.25</v>
       </c>
       <c r="I7">
-        <v>6.61</v>
+        <v>7.4</v>
       </c>
       <c r="J7">
-        <v>-3.31</v>
+        <v>-1.69</v>
       </c>
       <c r="K7">
-        <v>-4.34</v>
+        <v>-3.64</v>
       </c>
       <c r="L7">
-        <v>-5.16</v>
+        <v>-4.33</v>
       </c>
       <c r="M7">
-        <v>-3.14</v>
+        <v>-2.62</v>
       </c>
       <c r="N7">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="O7">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q7">
-        <v>25442.94</v>
+        <v>25356.31</v>
       </c>
       <c r="R7">
-        <v>25956.16</v>
+        <v>25913.88</v>
       </c>
       <c r="S7">
-        <v>26390.19</v>
+        <v>26355.74</v>
       </c>
       <c r="T7">
-        <v>26573</v>
+        <v>26561.81</v>
       </c>
       <c r="U7">
-        <v>-5.63</v>
+        <v>-4.89</v>
       </c>
       <c r="V7" t="s">
         <v>80</v>
@@ -1653,40 +1680,40 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>27.63</v>
+        <v>33.63</v>
       </c>
       <c r="AA7">
-        <v>-276.92</v>
+        <v>-291.87</v>
       </c>
       <c r="AB7">
-        <v>-197.55</v>
+        <v>-216.42</v>
       </c>
       <c r="AC7">
-        <v>-79.36</v>
+        <v>-75.45</v>
       </c>
       <c r="AD7">
-        <v>18.42</v>
+        <v>20.58</v>
       </c>
       <c r="AE7">
-        <v>15.67</v>
+        <v>19.14</v>
       </c>
       <c r="AF7">
-        <v>298.58</v>
+        <v>294.99</v>
       </c>
       <c r="AH7">
-        <v>26660.63</v>
+        <v>26678.88</v>
       </c>
       <c r="AI7">
-        <v>25251.68</v>
+        <v>25148.87</v>
       </c>
       <c r="AJ7">
-        <v>26164.61</v>
+        <v>26066.31</v>
       </c>
       <c r="AK7" t="s">
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>34.83</v>
+        <v>35.57</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1700,10 +1727,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>29555.3</v>
+        <v>29087.65</v>
       </c>
       <c r="E8">
-        <v>2.19</v>
+        <v>-1.58</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1712,43 +1739,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-25.15</v>
+        <v>-26.34</v>
       </c>
       <c r="I8">
-        <v>14.69</v>
+        <v>12.87</v>
       </c>
       <c r="J8">
-        <v>-1.47</v>
+        <v>-2.66</v>
       </c>
       <c r="K8">
-        <v>-5.75</v>
+        <v>-7.24</v>
       </c>
       <c r="L8">
-        <v>3.46</v>
+        <v>0.97</v>
       </c>
       <c r="M8">
-        <v>-14.67</v>
+        <v>-15.22</v>
       </c>
       <c r="N8">
-        <v>-3.91</v>
+        <v>-4.1</v>
       </c>
       <c r="O8">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q8">
-        <v>29233.02</v>
+        <v>29073.86</v>
       </c>
       <c r="R8">
-        <v>30326.37</v>
+        <v>30270.08</v>
       </c>
       <c r="S8">
-        <v>30097.83</v>
+        <v>30120.8</v>
       </c>
       <c r="T8">
-        <v>31970.87</v>
+        <v>31931.11</v>
       </c>
       <c r="U8">
-        <v>-7.56</v>
+        <v>-8.9</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1763,34 +1790,34 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>43.12</v>
+        <v>39.1</v>
       </c>
       <c r="AA8">
-        <v>-294.98</v>
+        <v>-336.87</v>
       </c>
       <c r="AB8">
-        <v>-52.09</v>
+        <v>-109.04</v>
       </c>
       <c r="AC8">
-        <v>-242.89</v>
+        <v>-227.83</v>
       </c>
       <c r="AD8">
-        <v>11.97</v>
+        <v>18.22</v>
       </c>
       <c r="AE8">
-        <v>4.18</v>
+        <v>10.25</v>
       </c>
       <c r="AF8">
-        <v>699.54</v>
+        <v>705.89</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>31877.69</v>
+        <v>31917.39</v>
       </c>
       <c r="AI8">
-        <v>28775.06</v>
+        <v>28622.78</v>
       </c>
       <c r="AJ8">
         <v>30808.98</v>
@@ -1799,7 +1826,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>31.19</v>
+        <v>28.51</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1813,10 +1840,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15584.65</v>
+        <v>15615.9</v>
       </c>
       <c r="E9">
-        <v>-2.4</v>
+        <v>0.2</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1825,31 +1852,31 @@
         <v>15584.65</v>
       </c>
       <c r="H9">
-        <v>-6.47</v>
+        <v>-6.28</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J9">
-        <v>-3.72</v>
+        <v>-3.89</v>
       </c>
       <c r="K9">
-        <v>-5.81</v>
+        <v>-5.84</v>
       </c>
       <c r="L9">
-        <v>-1.85</v>
+        <v>-2.34</v>
       </c>
       <c r="N9">
-        <v>-1.91</v>
+        <v>-1.14</v>
       </c>
       <c r="Q9">
-        <v>16025.21</v>
+        <v>15898.77</v>
       </c>
       <c r="R9">
-        <v>16344.43</v>
+        <v>16297.55</v>
       </c>
       <c r="S9">
-        <v>16254.56</v>
+        <v>16246.66</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1861,40 +1888,40 @@
         <v>1</v>
       </c>
       <c r="Z9">
-        <v>19.31</v>
+        <v>21.53</v>
       </c>
       <c r="AA9">
-        <v>-114.6</v>
+        <v>-148.62</v>
       </c>
       <c r="AB9">
-        <v>-24.42</v>
+        <v>-49.26</v>
       </c>
       <c r="AC9">
-        <v>-90.18000000000001</v>
+        <v>-99.36</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AE9">
-        <v>4.62</v>
+        <v>1.82</v>
       </c>
       <c r="AF9">
-        <v>159.59</v>
+        <v>162.83</v>
       </c>
       <c r="AH9">
-        <v>16857.72</v>
+        <v>16894.85</v>
       </c>
       <c r="AI9">
-        <v>15831.13</v>
+        <v>15700.25</v>
       </c>
       <c r="AJ9">
-        <v>16286.43</v>
+        <v>16050.69</v>
       </c>
       <c r="AK9" t="s">
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>50.68</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1908,10 +1935,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8910.75</v>
+        <v>8908.700000000001</v>
       </c>
       <c r="E10">
-        <v>-1.83</v>
+        <v>-0.02</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1920,43 +1947,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-8.76</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="I10">
-        <v>4.09</v>
+        <v>4.06</v>
       </c>
       <c r="J10">
-        <v>-3.02</v>
+        <v>-2.57</v>
       </c>
       <c r="K10">
-        <v>-5.4</v>
+        <v>-5.39</v>
       </c>
       <c r="L10">
-        <v>-5.47</v>
+        <v>-5.93</v>
       </c>
       <c r="M10">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="N10">
-        <v>12.56</v>
+        <v>12.45</v>
       </c>
       <c r="O10">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Q10">
-        <v>9076.98</v>
+        <v>9029.91</v>
       </c>
       <c r="R10">
-        <v>9223.51</v>
+        <v>9200.120000000001</v>
       </c>
       <c r="S10">
-        <v>9326.15</v>
+        <v>9315.24</v>
       </c>
       <c r="T10">
-        <v>9328.76</v>
+        <v>9325.35</v>
       </c>
       <c r="U10">
-        <v>-4.48</v>
+        <v>-4.47</v>
       </c>
       <c r="V10" t="s">
         <v>80</v>
@@ -1971,40 +1998,40 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>20.64</v>
+        <v>20.56</v>
       </c>
       <c r="AA10">
-        <v>-86.45</v>
+        <v>-98.54000000000001</v>
       </c>
       <c r="AB10">
-        <v>-61.33</v>
+        <v>-68.78</v>
       </c>
       <c r="AC10">
-        <v>-25.12</v>
+        <v>-29.77</v>
       </c>
       <c r="AD10">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AE10">
-        <v>3.64</v>
+        <v>2.43</v>
       </c>
       <c r="AF10">
-        <v>84.58</v>
+        <v>84.73</v>
       </c>
       <c r="AH10">
-        <v>9458.129999999999</v>
+        <v>9462.18</v>
       </c>
       <c r="AI10">
-        <v>8988.9</v>
+        <v>8938.07</v>
       </c>
       <c r="AJ10">
-        <v>9266.09</v>
+        <v>9179.950000000001</v>
       </c>
       <c r="AK10" t="s">
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>55.97</v>
+        <v>59.71</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2018,10 +2045,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1503.9</v>
+        <v>1515.05</v>
       </c>
       <c r="E11">
-        <v>-2.17</v>
+        <v>0.74</v>
       </c>
       <c r="F11">
         <v>1632.5</v>
@@ -2030,43 +2057,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-7.88</v>
+        <v>-7.19</v>
       </c>
       <c r="I11">
-        <v>19.99</v>
+        <v>20.88</v>
       </c>
       <c r="J11">
-        <v>-1.1</v>
+        <v>-1.66</v>
       </c>
       <c r="K11">
-        <v>-5.42</v>
+        <v>-5.06</v>
       </c>
       <c r="L11">
-        <v>-0.16</v>
+        <v>0.62</v>
       </c>
       <c r="M11">
-        <v>-7.19</v>
+        <v>-6.55</v>
       </c>
       <c r="N11">
-        <v>-4.99</v>
+        <v>-4.52</v>
       </c>
       <c r="O11">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q11">
-        <v>1528.59</v>
+        <v>1523.48</v>
       </c>
       <c r="R11">
-        <v>1569.96</v>
+        <v>1565.6</v>
       </c>
       <c r="S11">
-        <v>1551.17</v>
+        <v>1551.74</v>
       </c>
       <c r="T11">
-        <v>1449.89</v>
+        <v>1450.28</v>
       </c>
       <c r="U11">
-        <v>3.73</v>
+        <v>4.47</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2081,40 +2108,40 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>38.31</v>
+        <v>41.31</v>
       </c>
       <c r="AA11">
-        <v>-11.16</v>
+        <v>-12.62</v>
       </c>
       <c r="AB11">
-        <v>-2.44</v>
+        <v>-4.47</v>
       </c>
       <c r="AC11">
-        <v>-8.73</v>
+        <v>-8.15</v>
       </c>
       <c r="AD11">
-        <v>14.58</v>
+        <v>12.86</v>
       </c>
       <c r="AE11">
-        <v>16.11</v>
+        <v>15.01</v>
       </c>
       <c r="AF11">
-        <v>31.36</v>
+        <v>32.19</v>
       </c>
       <c r="AH11">
-        <v>1644.41</v>
+        <v>1642.28</v>
       </c>
       <c r="AI11">
-        <v>1495.52</v>
+        <v>1488.93</v>
       </c>
       <c r="AJ11">
-        <v>1614.42</v>
+        <v>1604.15</v>
       </c>
       <c r="AK11" t="s">
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>48.93</v>
+        <v>50.65</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2128,55 +2155,55 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>12669.15</v>
+        <v>12739.1</v>
       </c>
       <c r="E12">
-        <v>-2.54</v>
+        <v>0.55</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
       </c>
       <c r="G12">
-        <v>9717.85</v>
+        <v>9734.200000000001</v>
       </c>
       <c r="H12">
-        <v>-7.65</v>
+        <v>-7.14</v>
       </c>
       <c r="I12">
-        <v>30.37</v>
+        <v>30.87</v>
       </c>
       <c r="J12">
-        <v>-3.68</v>
+        <v>-3.17</v>
       </c>
       <c r="K12">
-        <v>-2.11</v>
+        <v>-2.79</v>
       </c>
       <c r="L12">
-        <v>-1.65</v>
+        <v>-2.09</v>
       </c>
       <c r="M12">
-        <v>30.86</v>
+        <v>31.09</v>
       </c>
       <c r="N12">
-        <v>16.68</v>
+        <v>16.95</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13104.1</v>
+        <v>13020.73</v>
       </c>
       <c r="R12">
-        <v>13206.15</v>
+        <v>13191.84</v>
       </c>
       <c r="S12">
-        <v>12922.95</v>
+        <v>12926.08</v>
       </c>
       <c r="T12">
-        <v>12214.75</v>
+        <v>12228.35</v>
       </c>
       <c r="U12">
-        <v>3.72</v>
+        <v>4.18</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2191,40 +2218,40 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>37.28</v>
+        <v>39.7</v>
       </c>
       <c r="AA12">
-        <v>13.19</v>
+        <v>-18.93</v>
       </c>
       <c r="AB12">
-        <v>79.45999999999999</v>
+        <v>59.78</v>
       </c>
       <c r="AC12">
-        <v>-66.27</v>
+        <v>-78.70999999999999</v>
       </c>
       <c r="AD12">
-        <v>7.37</v>
+        <v>2.68</v>
       </c>
       <c r="AE12">
-        <v>16.23</v>
+        <v>10.21</v>
       </c>
       <c r="AF12">
-        <v>235.46</v>
+        <v>236.53</v>
       </c>
       <c r="AH12">
-        <v>13623.24</v>
+        <v>13652.43</v>
       </c>
       <c r="AI12">
-        <v>12789.07</v>
+        <v>12731.26</v>
       </c>
       <c r="AJ12">
-        <v>13565.64</v>
+        <v>13387.91</v>
       </c>
       <c r="AK12" t="s">
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>27.2</v>
+        <v>29.58</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2238,10 +2265,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9467</v>
+        <v>9494.700000000001</v>
       </c>
       <c r="E13">
-        <v>-2.29</v>
+        <v>0.29</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2250,43 +2277,43 @@
         <v>9390.25</v>
       </c>
       <c r="H13">
-        <v>-12.07</v>
+        <v>-11.81</v>
       </c>
       <c r="I13">
-        <v>0.82</v>
+        <v>1.11</v>
       </c>
       <c r="J13">
-        <v>-2.2</v>
+        <v>-2.21</v>
       </c>
       <c r="K13">
-        <v>-3.84</v>
+        <v>-3.72</v>
       </c>
       <c r="L13">
-        <v>-5.49</v>
+        <v>-6.16</v>
       </c>
       <c r="M13">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="N13">
-        <v>19.55</v>
+        <v>19.5</v>
       </c>
       <c r="O13">
         <v>56</v>
       </c>
       <c r="Q13">
-        <v>9670.459999999999</v>
+        <v>9627.530000000001</v>
       </c>
       <c r="R13">
-        <v>9714.120000000001</v>
+        <v>9696.940000000001</v>
       </c>
       <c r="S13">
-        <v>9833.15</v>
+        <v>9823.879999999999</v>
       </c>
       <c r="T13">
-        <v>10023.81</v>
+        <v>10022.65</v>
       </c>
       <c r="U13">
-        <v>-5.55</v>
+        <v>-5.27</v>
       </c>
       <c r="V13" t="s">
         <v>80</v>
@@ -2301,40 +2328,40 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>25.24</v>
+        <v>28.72</v>
       </c>
       <c r="AA13">
-        <v>-61.74</v>
+        <v>-72.12</v>
       </c>
       <c r="AB13">
-        <v>-54.62</v>
+        <v>-58.12</v>
       </c>
       <c r="AC13">
-        <v>-7.12</v>
+        <v>-14</v>
       </c>
       <c r="AD13">
-        <v>52.02</v>
+        <v>24.15</v>
       </c>
       <c r="AE13">
-        <v>78.7</v>
+        <v>53.84</v>
       </c>
       <c r="AF13">
-        <v>95.18000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="AH13">
-        <v>9858.66</v>
+        <v>9859.799999999999</v>
       </c>
       <c r="AI13">
-        <v>9569.59</v>
+        <v>9534.07</v>
       </c>
       <c r="AJ13">
-        <v>9868.6</v>
+        <v>9761.77</v>
       </c>
       <c r="AK13" t="s">
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>34.84</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2348,10 +2375,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8158.5</v>
+        <v>8275.9</v>
       </c>
       <c r="E14">
-        <v>-2.29</v>
+        <v>1.44</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2360,43 +2387,43 @@
         <v>6879.9</v>
       </c>
       <c r="H14">
-        <v>-17.42</v>
+        <v>-16.23</v>
       </c>
       <c r="I14">
-        <v>18.58</v>
+        <v>20.29</v>
       </c>
       <c r="J14">
-        <v>-3.16</v>
+        <v>-1.62</v>
       </c>
       <c r="K14">
-        <v>-6.64</v>
+        <v>-4.94</v>
       </c>
       <c r="L14">
-        <v>-4.73</v>
+        <v>-5.02</v>
       </c>
       <c r="M14">
-        <v>19</v>
+        <v>20.13</v>
       </c>
       <c r="N14">
-        <v>27.61</v>
+        <v>26.63</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8338.360000000001</v>
+        <v>8311.07</v>
       </c>
       <c r="R14">
-        <v>8514.27</v>
+        <v>8497.139999999999</v>
       </c>
       <c r="S14">
-        <v>8485.99</v>
+        <v>8485.540000000001</v>
       </c>
       <c r="T14">
-        <v>8596.709999999999</v>
+        <v>8596.26</v>
       </c>
       <c r="U14">
-        <v>-5.1</v>
+        <v>-3.73</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2411,40 +2438,40 @@
         <v>1</v>
       </c>
       <c r="Z14">
-        <v>28.5</v>
+        <v>38.03</v>
       </c>
       <c r="AA14">
-        <v>-66.20999999999999</v>
+        <v>-72.70999999999999</v>
       </c>
       <c r="AB14">
-        <v>-24.3</v>
+        <v>-33.99</v>
       </c>
       <c r="AC14">
-        <v>-41.91</v>
+        <v>-38.73</v>
       </c>
       <c r="AD14">
-        <v>5.31</v>
+        <v>13.51</v>
       </c>
       <c r="AE14">
-        <v>5.31</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="AF14">
-        <v>129.04</v>
+        <v>129.93</v>
       </c>
       <c r="AH14">
-        <v>8767.700000000001</v>
+        <v>8766.709999999999</v>
       </c>
       <c r="AI14">
-        <v>8260.84</v>
+        <v>8227.57</v>
       </c>
       <c r="AJ14">
-        <v>8653.85</v>
+        <v>8626.549999999999</v>
       </c>
       <c r="AK14" t="s">
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>28.37</v>
+        <v>31.32</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2458,10 +2485,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26188.4</v>
+        <v>26146.2</v>
       </c>
       <c r="E15">
-        <v>-1.3</v>
+        <v>-0.16</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2470,43 +2497,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-3.67</v>
+        <v>-3.83</v>
       </c>
       <c r="I15">
-        <v>22.07</v>
+        <v>21.87</v>
       </c>
       <c r="J15">
-        <v>-1.83</v>
+        <v>-2.73</v>
       </c>
       <c r="K15">
-        <v>-0.97</v>
+        <v>-1.13</v>
       </c>
       <c r="L15">
-        <v>8.41</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M15">
-        <v>19.45</v>
+        <v>19.58</v>
       </c>
       <c r="N15">
-        <v>12.57</v>
+        <v>12.53</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26569.85</v>
+        <v>26422.93</v>
       </c>
       <c r="R15">
-        <v>26612.15</v>
+        <v>26601.36</v>
       </c>
       <c r="S15">
-        <v>26332.75</v>
+        <v>26342.12</v>
       </c>
       <c r="T15">
-        <v>23921.39</v>
+        <v>23939.66</v>
       </c>
       <c r="U15">
-        <v>9.48</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2521,34 +2548,34 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>41.78</v>
+        <v>40.92</v>
       </c>
       <c r="AA15">
-        <v>56.59</v>
+        <v>17.38</v>
       </c>
       <c r="AB15">
-        <v>133.97</v>
+        <v>110.66</v>
       </c>
       <c r="AC15">
-        <v>-77.38</v>
+        <v>-93.27</v>
       </c>
       <c r="AD15">
-        <v>1.12</v>
+        <v>0.13</v>
       </c>
       <c r="AE15">
-        <v>9.6</v>
+        <v>2.79</v>
       </c>
       <c r="AF15">
-        <v>314.95</v>
+        <v>324.15</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27117.59</v>
+        <v>27137.56</v>
       </c>
       <c r="AI15">
-        <v>26106.7</v>
+        <v>26065.17</v>
       </c>
       <c r="AJ15">
         <v>26048.62</v>
@@ -2557,7 +2584,7 @@
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>24.57</v>
+        <v>27.66</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2571,10 +2598,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>814.25</v>
+        <v>822.3</v>
       </c>
       <c r="E16">
-        <v>-4.04</v>
+        <v>0.99</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2583,43 +2610,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-15.94</v>
+        <v>-15.11</v>
       </c>
       <c r="I16">
-        <v>25.05</v>
+        <v>26.28</v>
       </c>
       <c r="J16">
-        <v>-8.77</v>
+        <v>-7.82</v>
       </c>
       <c r="K16">
-        <v>-9.09</v>
+        <v>-9.51</v>
       </c>
       <c r="L16">
-        <v>-0.47</v>
+        <v>0.95</v>
       </c>
       <c r="M16">
-        <v>-6.68</v>
+        <v>-6.19</v>
       </c>
       <c r="N16">
-        <v>14.01</v>
+        <v>14.19</v>
       </c>
       <c r="O16">
         <v>32</v>
       </c>
       <c r="Q16">
-        <v>859.8099999999999</v>
+        <v>845.86</v>
       </c>
       <c r="R16">
-        <v>893.74</v>
+        <v>890.0599999999999</v>
       </c>
       <c r="S16">
-        <v>901.8099999999999</v>
+        <v>900.41</v>
       </c>
       <c r="T16">
-        <v>829.6</v>
+        <v>829.27</v>
       </c>
       <c r="U16">
-        <v>-1.85</v>
+        <v>-0.84</v>
       </c>
       <c r="V16" t="s">
         <v>80</v>
@@ -2634,40 +2661,40 @@
         <v>1</v>
       </c>
       <c r="Z16">
-        <v>24.06</v>
+        <v>28.16</v>
       </c>
       <c r="AA16">
-        <v>-11.96</v>
+        <v>-15.3</v>
       </c>
       <c r="AB16">
-        <v>-2.82</v>
+        <v>-5.31</v>
       </c>
       <c r="AC16">
-        <v>-9.15</v>
+        <v>-9.98</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="AE16">
-        <v>0.77</v>
+        <v>1.36</v>
       </c>
       <c r="AF16">
-        <v>20.43</v>
+        <v>20.48</v>
       </c>
       <c r="AH16">
-        <v>944.84</v>
+        <v>950.3</v>
       </c>
       <c r="AI16">
-        <v>842.63</v>
+        <v>829.83</v>
       </c>
       <c r="AJ16">
-        <v>894.74</v>
+        <v>877.53</v>
       </c>
       <c r="AK16" t="s">
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>35.37</v>
+        <v>40.09</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2681,10 +2708,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29728.85</v>
+        <v>29802.35</v>
       </c>
       <c r="E17">
-        <v>-0.8</v>
+        <v>0.25</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2693,43 +2720,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-12.82</v>
+        <v>-12.61</v>
       </c>
       <c r="I17">
-        <v>4.81</v>
+        <v>5.07</v>
       </c>
       <c r="J17">
-        <v>-2.28</v>
+        <v>-1.27</v>
       </c>
       <c r="K17">
-        <v>-4.5</v>
+        <v>-3.78</v>
       </c>
       <c r="L17">
-        <v>-2.75</v>
+        <v>-2.82</v>
       </c>
       <c r="M17">
-        <v>-7.13</v>
+        <v>-6.76</v>
       </c>
       <c r="N17">
-        <v>3.85</v>
+        <v>3.78</v>
       </c>
       <c r="O17">
         <v>26</v>
       </c>
       <c r="Q17">
-        <v>29927.77</v>
+        <v>29850.81</v>
       </c>
       <c r="R17">
-        <v>30547.97</v>
+        <v>30500.1</v>
       </c>
       <c r="S17">
-        <v>30992.3</v>
+        <v>30961.58</v>
       </c>
       <c r="T17">
-        <v>31513.97</v>
+        <v>31494.32</v>
       </c>
       <c r="U17">
-        <v>-5.66</v>
+        <v>-5.37</v>
       </c>
       <c r="V17" t="s">
         <v>80</v>
@@ -2744,31 +2771,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>26.12</v>
+        <v>29.05</v>
       </c>
       <c r="AA17">
-        <v>-311.06</v>
+        <v>-324.1</v>
       </c>
       <c r="AB17">
-        <v>-217.12</v>
+        <v>-238.52</v>
       </c>
       <c r="AC17">
-        <v>-93.94</v>
+        <v>-85.58</v>
       </c>
       <c r="AD17">
-        <v>18.81</v>
+        <v>20.05</v>
       </c>
       <c r="AE17">
-        <v>13.61</v>
+        <v>18.05</v>
       </c>
       <c r="AF17">
-        <v>283.09</v>
+        <v>279.79</v>
       </c>
       <c r="AH17">
-        <v>31352.36</v>
+        <v>31363.23</v>
       </c>
       <c r="AI17">
-        <v>29743.57</v>
+        <v>29636.96</v>
       </c>
       <c r="AJ17">
         <v>30589.09</v>
@@ -2777,7 +2804,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>42.53</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2791,10 +2818,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16299</v>
+        <v>16274.65</v>
       </c>
       <c r="E18">
-        <v>-1.17</v>
+        <v>-0.15</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2803,31 +2830,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-3.79</v>
+        <v>-3.94</v>
       </c>
       <c r="I18">
-        <v>5.82</v>
+        <v>5.66</v>
       </c>
       <c r="J18">
-        <v>-1.34</v>
+        <v>-2.11</v>
       </c>
       <c r="K18">
-        <v>-1.25</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L18">
-        <v>5.61</v>
+        <v>5.66</v>
       </c>
       <c r="N18">
-        <v>19.78</v>
+        <v>18.87</v>
       </c>
       <c r="Q18">
-        <v>16503.1</v>
+        <v>16433.11</v>
       </c>
       <c r="R18">
-        <v>16557.58</v>
+        <v>16548.13</v>
       </c>
       <c r="S18">
-        <v>16530.41</v>
+        <v>16529.03</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2839,31 +2866,31 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>39.84</v>
+        <v>39.03</v>
       </c>
       <c r="AA18">
-        <v>-13.55</v>
+        <v>-32.51</v>
       </c>
       <c r="AB18">
-        <v>22.03</v>
+        <v>11.12</v>
       </c>
       <c r="AC18">
-        <v>-35.58</v>
+        <v>-43.64</v>
       </c>
       <c r="AD18">
-        <v>10.58</v>
+        <v>4.58</v>
       </c>
       <c r="AE18">
-        <v>19.19</v>
+        <v>11.7</v>
       </c>
       <c r="AF18">
-        <v>183.37</v>
+        <v>188.2</v>
       </c>
       <c r="AH18">
-        <v>16853.5</v>
+        <v>16867.8</v>
       </c>
       <c r="AI18">
-        <v>16261.66</v>
+        <v>16228.45</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2872,7 +2899,7 @@
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>20.48</v>
+        <v>23.55</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2886,10 +2913,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9144.15</v>
+        <v>9129.1</v>
       </c>
       <c r="E19">
-        <v>-5.96</v>
+        <v>-0.16</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2898,31 +2925,31 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-8.550000000000001</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="I19">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="J19">
-        <v>-6.26</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="K19">
-        <v>-6.8</v>
+        <v>-7.24</v>
       </c>
       <c r="L19">
-        <v>0.15</v>
+        <v>-3.78</v>
       </c>
       <c r="N19">
-        <v>6.51</v>
+        <v>5.78</v>
       </c>
       <c r="Q19">
-        <v>9710.9</v>
+        <v>9536.98</v>
       </c>
       <c r="R19">
-        <v>9743.41</v>
+        <v>9701.450000000001</v>
       </c>
       <c r="S19">
-        <v>9570.33</v>
+        <v>9563.27</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2934,40 +2961,40 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>31.51</v>
+        <v>31.18</v>
       </c>
       <c r="AA19">
-        <v>2.38</v>
+        <v>-41.43</v>
       </c>
       <c r="AB19">
-        <v>52.25</v>
+        <v>33.52</v>
       </c>
       <c r="AC19">
-        <v>-49.87</v>
+        <v>-74.95</v>
       </c>
       <c r="AD19">
-        <v>16.15</v>
+        <v>4.8</v>
       </c>
       <c r="AE19">
-        <v>39.69</v>
+        <v>19.38</v>
       </c>
       <c r="AF19">
-        <v>182.15</v>
+        <v>186.48</v>
       </c>
       <c r="AH19">
-        <v>10082.99</v>
+        <v>10121.81</v>
       </c>
       <c r="AI19">
-        <v>9403.83</v>
+        <v>9281.09</v>
       </c>
       <c r="AJ19">
-        <v>9986.059999999999</v>
+        <v>9616.870000000001</v>
       </c>
       <c r="AK19" t="s">
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>25.85</v>
+        <v>30.39</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2981,10 +3008,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10796.4</v>
+        <v>10872.45</v>
       </c>
       <c r="E20">
-        <v>-1.29</v>
+        <v>0.7</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -2993,31 +3020,31 @@
         <v>10796.4</v>
       </c>
       <c r="H20">
-        <v>-5.04</v>
+        <v>-4.37</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="J20">
-        <v>-2.9</v>
+        <v>-1.56</v>
       </c>
       <c r="K20">
-        <v>-3.6</v>
+        <v>-3</v>
       </c>
       <c r="L20">
-        <v>-4.41</v>
+        <v>-3.82</v>
       </c>
       <c r="N20">
-        <v>-7.33</v>
+        <v>-4.75</v>
       </c>
       <c r="Q20">
-        <v>10967.41</v>
+        <v>10932.95</v>
       </c>
       <c r="R20">
-        <v>11109.36</v>
+        <v>11091.42</v>
       </c>
       <c r="S20">
-        <v>11164.77</v>
+        <v>11157.24</v>
       </c>
       <c r="V20" t="s">
         <v>80</v>
@@ -3029,40 +3056,40 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>25.42</v>
+        <v>33.47</v>
       </c>
       <c r="AA20">
-        <v>-65.47</v>
+        <v>-73.78</v>
       </c>
       <c r="AB20">
-        <v>-33.95</v>
+        <v>-41.92</v>
       </c>
       <c r="AC20">
-        <v>-31.52</v>
+        <v>-31.86</v>
       </c>
       <c r="AD20">
-        <v>0.27</v>
+        <v>10.37</v>
       </c>
       <c r="AE20">
-        <v>0.97</v>
+        <v>3.64</v>
       </c>
       <c r="AF20">
-        <v>124.44</v>
+        <v>124.09</v>
       </c>
       <c r="AH20">
-        <v>11321.22</v>
+        <v>11319.94</v>
       </c>
       <c r="AI20">
-        <v>10897.49</v>
+        <v>10862.9</v>
       </c>
       <c r="AJ20">
-        <v>11256.37</v>
+        <v>11213.36</v>
       </c>
       <c r="AK20" t="s">
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>29.15</v>
+        <v>32.95</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3076,10 +3103,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27069.8</v>
+        <v>27284.25</v>
       </c>
       <c r="E21">
-        <v>-1.33</v>
+        <v>0.79</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3088,43 +3115,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-7.26</v>
+        <v>-6.52</v>
       </c>
       <c r="I21">
-        <v>12.11</v>
+        <v>13</v>
       </c>
       <c r="J21">
-        <v>-2.44</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K21">
-        <v>-0.65</v>
+        <v>-0.1</v>
       </c>
       <c r="L21">
-        <v>-3.03</v>
+        <v>-2.18</v>
       </c>
       <c r="M21">
-        <v>2.78</v>
+        <v>3.61</v>
       </c>
       <c r="N21">
-        <v>7.13</v>
+        <v>6.73</v>
       </c>
       <c r="O21">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="Q21">
-        <v>27300.14</v>
+        <v>27262.05</v>
       </c>
       <c r="R21">
-        <v>27536.28</v>
+        <v>27538.09</v>
       </c>
       <c r="S21">
-        <v>27778.71</v>
+        <v>27758.29</v>
       </c>
       <c r="T21">
-        <v>27600.71</v>
+        <v>27595.39</v>
       </c>
       <c r="U21">
-        <v>-1.92</v>
+        <v>-1.13</v>
       </c>
       <c r="V21" t="s">
         <v>80</v>
@@ -3139,31 +3166,31 @@
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>38.17</v>
+        <v>43.93</v>
       </c>
       <c r="AA21">
-        <v>-97.95</v>
+        <v>-104.8</v>
       </c>
       <c r="AB21">
-        <v>-52.92</v>
+        <v>-63.29</v>
       </c>
       <c r="AC21">
-        <v>-45.03</v>
+        <v>-41.5</v>
       </c>
       <c r="AD21">
-        <v>14.59</v>
+        <v>18.99</v>
       </c>
       <c r="AE21">
-        <v>11.17</v>
+        <v>16.06</v>
       </c>
       <c r="AF21">
-        <v>315.44</v>
+        <v>313.2</v>
       </c>
       <c r="AH21">
-        <v>28034.7</v>
+        <v>28032.34</v>
       </c>
       <c r="AI21">
-        <v>27037.85</v>
+        <v>27043.85</v>
       </c>
       <c r="AJ21">
         <v>28092.43</v>
@@ -3172,7 +3199,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>28.76</v>
+        <v>27.54</v>
       </c>
     </row>
   </sheetData>
@@ -3313,7 +3340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3353,7 +3380,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3373,2468 +3400,2562 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="F4" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>80</v>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-7.1</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-8.390000000000001</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-3.02</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-4.23</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-1.21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.58</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-7.08</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.5</v>
+      <c r="B10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-1.95</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.65</v>
+        <v>-7.83</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.7</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-7.75</v>
+        <v>-4.23</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.79</v>
+        <v>-4.08</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.04</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.97</v>
+        <v>-7.08</v>
       </c>
       <c r="D13" s="6">
-        <v>-4.34</v>
+        <v>-5.83</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.37</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-8.050000000000001</v>
+        <v>-3.65</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.75</v>
+        <v>-3.8</v>
       </c>
       <c r="E14" s="8">
-        <v>2.3</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.93</v>
+        <v>-7.79</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.81</v>
+        <v>-5.29</v>
       </c>
       <c r="E15" s="7">
-        <v>-1.88</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.36</v>
+        <v>-4.34</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.4</v>
+        <v>-3.64</v>
       </c>
       <c r="E16" s="7">
-        <v>-2.04</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.4</v>
+        <v>-5.75</v>
       </c>
       <c r="D17" s="6">
-        <v>-5.42</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-3.02</v>
+        <v>-7.24</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.27</v>
+        <v>-5.81</v>
       </c>
       <c r="D18" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.84</v>
+        <v>-5.84</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.09</v>
+        <v>-5.4</v>
       </c>
       <c r="D19" s="6">
-        <v>-3.84</v>
+        <v>-5.39</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.75</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-5</v>
+        <v>-5.42</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.64</v>
+        <v>-5.06</v>
       </c>
       <c r="E20" s="7">
-        <v>-1.64</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-0.58</v>
+        <v>-2.11</v>
       </c>
       <c r="D21" s="6">
-        <v>-0.97</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.39</v>
+        <v>-2.79</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-5.55</v>
+        <v>-3.84</v>
       </c>
       <c r="D22" s="6">
-        <v>-9.09</v>
+        <v>-3.72</v>
       </c>
       <c r="E22" s="7">
-        <v>-3.54</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-3.64</v>
+        <v>-6.64</v>
       </c>
       <c r="D23" s="6">
-        <v>-4.5</v>
+        <v>-4.94</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.86</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-0.54</v>
+        <v>-0.97</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.71</v>
+        <v>-1.13</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-0.89</v>
+        <v>-9.09</v>
       </c>
       <c r="D25" s="6">
-        <v>-6.8</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-5.91</v>
+        <v>-9.51</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-2.8</v>
+        <v>-4.5</v>
       </c>
       <c r="D26" s="6">
-        <v>-3.6</v>
+        <v>-3.78</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.8</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>0.64</v>
+        <v>-1.25</v>
       </c>
       <c r="D27" s="6">
-        <v>-0.65</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.29</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-1.47</v>
+        <v>-6.8</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.93</v>
+        <v>-7.24</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-2.29</v>
+        <v>-3.6</v>
       </c>
       <c r="D29" s="6">
-        <v>-3.04</v>
+        <v>-3</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.75</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-1.18</v>
+        <v>-0.65</v>
       </c>
       <c r="D30" s="6">
-        <v>-2.4</v>
+        <v>-0.1</v>
       </c>
       <c r="E30" s="7">
-        <v>-1.22</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-0.35</v>
+        <v>-3.4</v>
       </c>
       <c r="D31" s="6">
-        <v>-2.17</v>
+        <v>-3.17</v>
       </c>
       <c r="E31" s="7">
-        <v>-1.82</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-1.83</v>
+        <v>-3.04</v>
       </c>
       <c r="D32" s="6">
-        <v>-1.67</v>
-      </c>
-      <c r="E32" s="8">
-        <v>0.16</v>
+        <v>-2.42</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.62</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-1.94</v>
+        <v>-2.4</v>
       </c>
       <c r="D33" s="6">
-        <v>-3.31</v>
+        <v>-1.8</v>
       </c>
       <c r="E33" s="7">
-        <v>-1.37</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>-5.78</v>
+        <v>-2.17</v>
       </c>
       <c r="D34" s="6">
-        <v>-1.47</v>
+        <v>-2.39</v>
       </c>
       <c r="E34" s="8">
-        <v>4.31</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.57</v>
+        <v>-1.67</v>
       </c>
       <c r="D35" s="6">
-        <v>-3.72</v>
+        <v>-0.42</v>
       </c>
       <c r="E35" s="7">
-        <v>-2.15</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.31</v>
+        <v>-3.31</v>
       </c>
       <c r="D36" s="6">
-        <v>-3.02</v>
+        <v>-1.69</v>
       </c>
       <c r="E36" s="7">
-        <v>-1.71</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.8</v>
+        <v>-1.47</v>
       </c>
       <c r="D37" s="6">
-        <v>-1.1</v>
+        <v>-2.66</v>
       </c>
       <c r="E37" s="8">
-        <v>0.7</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-2.39</v>
+        <v>-3.72</v>
       </c>
       <c r="D38" s="6">
-        <v>-3.68</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-1.29</v>
+        <v>-3.89</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.22</v>
+        <v>-3.02</v>
       </c>
       <c r="D39" s="6">
-        <v>-2.2</v>
+        <v>-2.57</v>
       </c>
       <c r="E39" s="7">
-        <v>-1.98</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-1.94</v>
+        <v>-1.1</v>
       </c>
       <c r="D40" s="6">
-        <v>-3.16</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.22</v>
+        <v>-1.66</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>0.21</v>
+        <v>-3.68</v>
       </c>
       <c r="D41" s="6">
-        <v>-1.83</v>
+        <v>-3.17</v>
       </c>
       <c r="E41" s="7">
-        <v>-2.04</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>-6.54</v>
+        <v>-2.2</v>
       </c>
       <c r="D42" s="6">
-        <v>-8.77</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.23</v>
+        <v>-2.21</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-1.98</v>
+        <v>-3.16</v>
       </c>
       <c r="D43" s="6">
-        <v>-2.28</v>
+        <v>-1.62</v>
       </c>
       <c r="E43" s="7">
-        <v>-0.3</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>0.51</v>
+        <v>-1.83</v>
       </c>
       <c r="D44" s="6">
-        <v>-1.34</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-1.85</v>
+        <v>-2.73</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>0.15</v>
+        <v>-8.77</v>
       </c>
       <c r="D45" s="6">
-        <v>-6.26</v>
+        <v>-7.82</v>
       </c>
       <c r="E45" s="7">
-        <v>-6.41</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-2.24</v>
+        <v>-2.28</v>
       </c>
       <c r="D46" s="6">
-        <v>-2.9</v>
+        <v>-1.27</v>
       </c>
       <c r="E46" s="7">
-        <v>-0.66</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>-1.4</v>
+        <v>-1.34</v>
       </c>
       <c r="D47" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-1.04</v>
+        <v>-2.11</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C48" s="6">
-        <v>5.04</v>
+        <v>-6.26</v>
       </c>
       <c r="D48" s="6">
-        <v>1.66</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-3.38</v>
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-2.44</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C49" s="6">
-        <v>9.119999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="D49" s="6">
-        <v>7.06</v>
+        <v>-1.56</v>
       </c>
       <c r="E49" s="7">
-        <v>-2.06</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" s="6">
-        <v>-7.27</v>
+        <v>-2.44</v>
       </c>
       <c r="D50" s="6">
-        <v>-8.789999999999999</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="E50" s="7">
-        <v>-1.52</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>10.65</v>
+        <v>1.66</v>
       </c>
       <c r="D51" s="6">
-        <v>8.31</v>
-      </c>
-      <c r="E51" s="7">
-        <v>-2.34</v>
+        <v>-1.09</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-2.75</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-21.1</v>
+        <v>7.06</v>
       </c>
       <c r="D52" s="6">
-        <v>-20.36</v>
+        <v>7.03</v>
       </c>
       <c r="E52" s="8">
-        <v>0.74</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-1.19</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="D53" s="6">
-        <v>-3.14</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="E53" s="7">
-        <v>-1.95</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-17.7</v>
+        <v>8.31</v>
       </c>
       <c r="D54" s="6">
-        <v>-14.67</v>
-      </c>
-      <c r="E54" s="8">
-        <v>3.03</v>
+        <v>8.44</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.13</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>1.56</v>
+        <v>-20.36</v>
       </c>
       <c r="D55" s="6">
-        <v>-0.5</v>
+        <v>-18.89</v>
       </c>
       <c r="E55" s="7">
-        <v>-2.06</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-4.58</v>
+        <v>-3.14</v>
       </c>
       <c r="D56" s="6">
-        <v>-7.19</v>
+        <v>-2.62</v>
       </c>
       <c r="E56" s="7">
-        <v>-2.61</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>35.18</v>
+        <v>-14.67</v>
       </c>
       <c r="D57" s="6">
-        <v>30.86</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-4.32</v>
+        <v>-15.22</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>3.11</v>
+        <v>-0.5</v>
       </c>
       <c r="D58" s="6">
-        <v>0.66</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-2.45</v>
+        <v>-0.7</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>22</v>
+        <v>-7.19</v>
       </c>
       <c r="D59" s="6">
-        <v>19</v>
+        <v>-6.55</v>
       </c>
       <c r="E59" s="7">
-        <v>-3</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>21.07</v>
+        <v>30.86</v>
       </c>
       <c r="D60" s="6">
-        <v>19.45</v>
+        <v>31.09</v>
       </c>
       <c r="E60" s="7">
-        <v>-1.62</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>-3.88</v>
+        <v>0.66</v>
       </c>
       <c r="D61" s="6">
-        <v>-6.68</v>
+        <v>0.92</v>
       </c>
       <c r="E61" s="7">
-        <v>-2.8</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>-6.45</v>
+        <v>19</v>
       </c>
       <c r="D62" s="6">
-        <v>-7.13</v>
+        <v>20.13</v>
       </c>
       <c r="E62" s="7">
-        <v>-0.68</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>4.37</v>
+        <v>19.45</v>
       </c>
       <c r="D63" s="6">
-        <v>2.78</v>
+        <v>19.58</v>
       </c>
       <c r="E63" s="7">
-        <v>-1.59</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" s="6">
-        <v>1.21</v>
+        <v>-6.68</v>
       </c>
       <c r="D64" s="6">
-        <v>-0.5</v>
+        <v>-6.19</v>
       </c>
       <c r="E64" s="7">
-        <v>-1.71</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" s="6">
-        <v>-4.41</v>
+        <v>-7.13</v>
       </c>
       <c r="D65" s="6">
-        <v>-6.01</v>
+        <v>-6.76</v>
       </c>
       <c r="E65" s="7">
-        <v>-1.6</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="6">
-        <v>0.33</v>
+        <v>2.78</v>
       </c>
       <c r="D66" s="6">
-        <v>-1.77</v>
+        <v>3.61</v>
       </c>
       <c r="E66" s="7">
-        <v>-2.1</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-3.95</v>
+        <v>-0.5</v>
       </c>
       <c r="D67" s="6">
-        <v>-6.93</v>
+        <v>0.63</v>
       </c>
       <c r="E67" s="7">
-        <v>-2.98</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-8.130000000000001</v>
+        <v>-6.01</v>
       </c>
       <c r="D68" s="6">
-        <v>-9.69</v>
+        <v>-6</v>
       </c>
       <c r="E68" s="7">
-        <v>-1.56</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-2.78</v>
+        <v>-1.77</v>
       </c>
       <c r="D69" s="6">
-        <v>-5.16</v>
+        <v>-1.68</v>
       </c>
       <c r="E69" s="7">
-        <v>-2.38</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>3.04</v>
+        <v>-6.93</v>
       </c>
       <c r="D70" s="6">
-        <v>3.46</v>
+        <v>-7.59</v>
       </c>
       <c r="E70" s="8">
-        <v>0.42</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>1.94</v>
+        <v>-9.69</v>
       </c>
       <c r="D71" s="6">
-        <v>-1.85</v>
+        <v>-8.07</v>
       </c>
       <c r="E71" s="7">
-        <v>-3.79</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-3.13</v>
+        <v>-5.16</v>
       </c>
       <c r="D72" s="6">
-        <v>-5.47</v>
+        <v>-4.33</v>
       </c>
       <c r="E72" s="7">
-        <v>-2.34</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="D73" s="6">
-        <v>-0.16</v>
-      </c>
-      <c r="E73" s="7">
-        <v>-3.64</v>
+        <v>0.97</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-2.49</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-0.65</v>
+        <v>-1.85</v>
       </c>
       <c r="D74" s="6">
-        <v>-1.65</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-1</v>
+        <v>-2.34</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-2.67</v>
+        <v>-5.47</v>
       </c>
       <c r="D75" s="6">
-        <v>-5.49</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-2.82</v>
+        <v>-5.93</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-2.7</v>
+        <v>-0.16</v>
       </c>
       <c r="D76" s="6">
-        <v>-4.73</v>
+        <v>0.62</v>
       </c>
       <c r="E76" s="7">
-        <v>-2.03</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>9.550000000000001</v>
+        <v>-1.65</v>
       </c>
       <c r="D77" s="6">
-        <v>8.41</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-1.14</v>
+        <v>-2.09</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>6.06</v>
+        <v>-5.49</v>
       </c>
       <c r="D78" s="6">
-        <v>-0.47</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-6.53</v>
+        <v>-6.16</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-1.29</v>
+        <v>-4.73</v>
       </c>
       <c r="D79" s="6">
-        <v>-2.75</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-1.46</v>
+        <v>-5.02</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>6.05</v>
+        <v>8.41</v>
       </c>
       <c r="D80" s="6">
-        <v>5.61</v>
-      </c>
-      <c r="E80" s="7">
-        <v>-0.44</v>
+        <v>8.279999999999999</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>8.1</v>
+        <v>-0.47</v>
       </c>
       <c r="D81" s="6">
-        <v>0.15</v>
+        <v>0.95</v>
       </c>
       <c r="E81" s="7">
-        <v>-7.95</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-0.68</v>
+        <v>-2.75</v>
       </c>
       <c r="D82" s="6">
-        <v>-4.41</v>
-      </c>
-      <c r="E82" s="7">
-        <v>-3.73</v>
+        <v>-2.82</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-1.35</v>
+        <v>5.61</v>
       </c>
       <c r="D83" s="6">
-        <v>-3.03</v>
+        <v>5.66</v>
       </c>
       <c r="E83" s="7">
-        <v>-1.68</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C84" s="6">
-        <v>-7.9</v>
+        <v>0.15</v>
       </c>
       <c r="D84" s="6">
-        <v>-9.75</v>
-      </c>
-      <c r="E84" s="7">
-        <v>-1.85</v>
+        <v>-3.78</v>
+      </c>
+      <c r="E84" s="8">
+        <v>-3.93</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C85" s="6">
-        <v>-8.789999999999999</v>
+        <v>-4.41</v>
       </c>
       <c r="D85" s="6">
-        <v>-10.43</v>
+        <v>-3.82</v>
       </c>
       <c r="E85" s="7">
-        <v>-1.64</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C86" s="6">
-        <v>-9.32</v>
+        <v>-3.03</v>
       </c>
       <c r="D86" s="6">
-        <v>-10.73</v>
+        <v>-2.18</v>
       </c>
       <c r="E86" s="7">
-        <v>-1.41</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-8.67</v>
+        <v>-9.75</v>
       </c>
       <c r="D87" s="6">
-        <v>-10.56</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="E87" s="7">
-        <v>-1.89</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-20.9</v>
+        <v>-10.43</v>
       </c>
       <c r="D88" s="6">
-        <v>-21.3</v>
+        <v>-10.1</v>
       </c>
       <c r="E88" s="7">
-        <v>-0.4</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-10.25</v>
+        <v>-10.73</v>
       </c>
       <c r="D89" s="6">
-        <v>-11.9</v>
+        <v>-10.11</v>
       </c>
       <c r="E89" s="7">
-        <v>-1.65</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-26.76</v>
+        <v>-10.56</v>
       </c>
       <c r="D90" s="6">
-        <v>-25.15</v>
-      </c>
-      <c r="E90" s="8">
-        <v>1.61</v>
+        <v>-10.48</v>
+      </c>
+      <c r="E90" s="7">
+        <v>0.08</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-4.17</v>
+        <v>-21.3</v>
       </c>
       <c r="D91" s="6">
-        <v>-6.47</v>
+        <v>-20.02</v>
       </c>
       <c r="E91" s="7">
-        <v>-2.3</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-7.05</v>
+        <v>-11.9</v>
       </c>
       <c r="D92" s="6">
-        <v>-8.76</v>
+        <v>-11.25</v>
       </c>
       <c r="E92" s="7">
-        <v>-1.71</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-5.84</v>
+        <v>-25.15</v>
       </c>
       <c r="D93" s="6">
-        <v>-7.88</v>
-      </c>
-      <c r="E93" s="7">
-        <v>-2.04</v>
+        <v>-26.34</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-5.24</v>
+        <v>-6.47</v>
       </c>
       <c r="D94" s="6">
-        <v>-7.65</v>
+        <v>-6.28</v>
       </c>
       <c r="E94" s="7">
-        <v>-2.41</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-10.01</v>
+        <v>-8.76</v>
       </c>
       <c r="D95" s="6">
-        <v>-12.07</v>
-      </c>
-      <c r="E95" s="7">
-        <v>-2.06</v>
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-15.49</v>
+        <v>-7.88</v>
       </c>
       <c r="D96" s="6">
-        <v>-17.42</v>
+        <v>-7.19</v>
       </c>
       <c r="E96" s="7">
-        <v>-1.93</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-2.41</v>
+        <v>-7.65</v>
       </c>
       <c r="D97" s="6">
-        <v>-3.67</v>
+        <v>-7.14</v>
       </c>
       <c r="E97" s="7">
-        <v>-1.26</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-12.4</v>
+        <v>-12.07</v>
       </c>
       <c r="D98" s="6">
-        <v>-15.94</v>
+        <v>-11.81</v>
       </c>
       <c r="E98" s="7">
-        <v>-3.54</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-12.12</v>
+        <v>-17.42</v>
       </c>
       <c r="D99" s="6">
-        <v>-12.82</v>
+        <v>-16.23</v>
       </c>
       <c r="E99" s="7">
-        <v>-0.7</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-2.65</v>
+        <v>-3.67</v>
       </c>
       <c r="D100" s="6">
-        <v>-3.79</v>
-      </c>
-      <c r="E100" s="7">
-        <v>-1.14</v>
+        <v>-3.83</v>
+      </c>
+      <c r="E100" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-2.75</v>
+        <v>-15.94</v>
       </c>
       <c r="D101" s="6">
-        <v>-8.550000000000001</v>
+        <v>-15.11</v>
       </c>
       <c r="E101" s="7">
-        <v>-5.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-3.8</v>
+        <v>-12.82</v>
       </c>
       <c r="D102" s="6">
-        <v>-5.04</v>
+        <v>-12.61</v>
       </c>
       <c r="E102" s="7">
-        <v>-1.24</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="6">
-        <v>-6</v>
+        <v>-3.79</v>
       </c>
       <c r="D103" s="6">
-        <v>-7.26</v>
-      </c>
-      <c r="E103" s="7">
-        <v>-1.26</v>
+        <v>-3.94</v>
+      </c>
+      <c r="E103" s="8">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C104" s="6">
-        <v>27304.5</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="D104" s="6">
-        <v>26756.6</v>
-      </c>
-      <c r="E104" s="7">
-        <v>-547.9</v>
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="E104" s="8">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C105" s="6">
-        <v>9579.799999999999</v>
+        <v>-5.04</v>
       </c>
       <c r="D105" s="6">
-        <v>9407.549999999999</v>
+        <v>-4.37</v>
       </c>
       <c r="E105" s="7">
-        <v>-172.25</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C106" s="6">
-        <v>11460.6</v>
+        <v>-7.26</v>
       </c>
       <c r="D106" s="6">
-        <v>11282.8</v>
+        <v>-6.52</v>
       </c>
       <c r="E106" s="7">
-        <v>-177.8</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>37935.2</v>
+        <v>26756.6</v>
       </c>
       <c r="D107" s="6">
-        <v>37147.95</v>
+        <v>26893.65</v>
       </c>
       <c r="E107" s="7">
-        <v>-787.25</v>
+        <v>137.05</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>45053.75</v>
+        <v>9407.549999999999</v>
       </c>
       <c r="D108" s="6">
-        <v>44829.95</v>
+        <v>9442.15</v>
       </c>
       <c r="E108" s="7">
-        <v>-223.8</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>25545.4</v>
+        <v>11282.8</v>
       </c>
       <c r="D109" s="6">
-        <v>25076.65</v>
+        <v>11361.65</v>
       </c>
       <c r="E109" s="7">
-        <v>-468.75</v>
+        <v>78.84999999999999</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>28921.5</v>
+        <v>37147.95</v>
       </c>
       <c r="D110" s="6">
-        <v>29555.3</v>
-      </c>
-      <c r="E110" s="8">
-        <v>633.8</v>
+        <v>37183.4</v>
+      </c>
+      <c r="E110" s="7">
+        <v>35.45</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>15967.45</v>
+        <v>44829.95</v>
       </c>
       <c r="D111" s="6">
-        <v>15584.65</v>
+        <v>45559</v>
       </c>
       <c r="E111" s="7">
-        <v>-382.8</v>
+        <v>729.05</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>9077.15</v>
+        <v>25076.65</v>
       </c>
       <c r="D112" s="6">
-        <v>8910.75</v>
+        <v>25262.4</v>
       </c>
       <c r="E112" s="7">
-        <v>-166.4</v>
+        <v>185.75</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>1537.2</v>
+        <v>29555.3</v>
       </c>
       <c r="D113" s="6">
-        <v>1503.9</v>
-      </c>
-      <c r="E113" s="7">
-        <v>-33.3</v>
+        <v>29087.65</v>
+      </c>
+      <c r="E113" s="8">
+        <v>-467.65</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>12999.05</v>
+        <v>15584.65</v>
       </c>
       <c r="D114" s="6">
-        <v>12669.15</v>
+        <v>15615.9</v>
       </c>
       <c r="E114" s="7">
-        <v>-329.9</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>9688.4</v>
+        <v>8910.75</v>
       </c>
       <c r="D115" s="6">
-        <v>9467</v>
-      </c>
-      <c r="E115" s="7">
-        <v>-221.4</v>
+        <v>8908.700000000001</v>
+      </c>
+      <c r="E115" s="8">
+        <v>-2.05</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>8349.9</v>
+        <v>1503.9</v>
       </c>
       <c r="D116" s="6">
-        <v>8158.5</v>
+        <v>1515.05</v>
       </c>
       <c r="E116" s="7">
-        <v>-191.4</v>
+        <v>11.15</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>26532.4</v>
+        <v>12669.15</v>
       </c>
       <c r="D117" s="6">
-        <v>26188.4</v>
+        <v>12739.1</v>
       </c>
       <c r="E117" s="7">
-        <v>-344</v>
+        <v>69.95</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>848.5</v>
+        <v>9467</v>
       </c>
       <c r="D118" s="6">
-        <v>814.25</v>
+        <v>9494.700000000001</v>
       </c>
       <c r="E118" s="7">
-        <v>-34.25</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>29969.35</v>
+        <v>8158.5</v>
       </c>
       <c r="D119" s="6">
-        <v>29728.85</v>
+        <v>8275.9</v>
       </c>
       <c r="E119" s="7">
-        <v>-240.5</v>
+        <v>117.4</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>16492.1</v>
+        <v>26188.4</v>
       </c>
       <c r="D120" s="6">
-        <v>16299</v>
-      </c>
-      <c r="E120" s="7">
-        <v>-193.1</v>
+        <v>26146.2</v>
+      </c>
+      <c r="E120" s="8">
+        <v>-42.2</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>9723.85</v>
+        <v>814.25</v>
       </c>
       <c r="D121" s="6">
-        <v>9144.15</v>
+        <v>822.3</v>
       </c>
       <c r="E121" s="7">
-        <v>-579.7</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>10937</v>
+        <v>29728.85</v>
       </c>
       <c r="D122" s="6">
-        <v>10796.4</v>
+        <v>29802.35</v>
       </c>
       <c r="E122" s="7">
-        <v>-140.6</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="6">
-        <v>27436</v>
+        <v>16299</v>
       </c>
       <c r="D123" s="6">
-        <v>27069.8</v>
-      </c>
-      <c r="E123" s="7">
-        <v>-366.2</v>
+        <v>16274.65</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-24.35</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C124" s="6">
-        <v>19</v>
+        <v>9144.15</v>
       </c>
       <c r="D124" s="6">
-        <v>13</v>
-      </c>
-      <c r="E124" s="7">
-        <v>-6</v>
+        <v>9129.1</v>
+      </c>
+      <c r="E124" s="8">
+        <v>-15.05</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C125" s="6">
-        <v>32</v>
+        <v>10796.4</v>
       </c>
       <c r="D125" s="6">
-        <v>38</v>
-      </c>
-      <c r="E125" s="8">
-        <v>6</v>
+        <v>10872.45</v>
+      </c>
+      <c r="E125" s="7">
+        <v>76.05</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C126" s="6">
-        <v>13</v>
+        <v>27069.8</v>
       </c>
       <c r="D126" s="6">
-        <v>19</v>
-      </c>
-      <c r="E126" s="8">
-        <v>6</v>
+        <v>27284.25</v>
+      </c>
+      <c r="E126" s="7">
+        <v>214.45</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="D127" s="6">
-        <v>50</v>
-      </c>
-      <c r="E127" s="8">
-        <v>12</v>
+        <v>74</v>
+      </c>
+      <c r="E127" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="D128" s="6">
-        <v>56</v>
-      </c>
-      <c r="E128" s="8">
+        <v>19</v>
+      </c>
+      <c r="E128" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="D129" s="6">
-        <v>32</v>
-      </c>
-      <c r="E129" s="7">
-        <v>-24</v>
+        <v>68</v>
+      </c>
+      <c r="E129" s="8">
+        <v>-13</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C130" s="6">
         <v>38</v>
       </c>
-      <c r="B130" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C130" s="6">
-        <v>27.65</v>
-      </c>
       <c r="D130" s="6">
-        <v>21.9</v>
+        <v>44</v>
       </c>
       <c r="E130" s="7">
-        <v>-5.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C131" s="6">
-        <v>34.25</v>
+        <v>19</v>
       </c>
       <c r="D131" s="6">
-        <v>26.94</v>
-      </c>
-      <c r="E131" s="7">
-        <v>-7.31</v>
+        <v>13</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C132" s="6">
-        <v>25.13</v>
+        <v>50</v>
       </c>
       <c r="D132" s="6">
-        <v>19.64</v>
-      </c>
-      <c r="E132" s="7">
-        <v>-5.49</v>
+        <v>38</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-12</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C133" s="6">
-        <v>39.53</v>
+        <v>44</v>
       </c>
       <c r="D133" s="6">
-        <v>27.62</v>
+        <v>50</v>
       </c>
       <c r="E133" s="7">
-        <v>-11.91</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C134" s="6">
-        <v>24.38</v>
+        <v>74</v>
       </c>
       <c r="D134" s="6">
-        <v>22.94</v>
+        <v>81</v>
       </c>
       <c r="E134" s="7">
-        <v>-1.44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>35.05</v>
+        <v>21.9</v>
       </c>
       <c r="D135" s="6">
-        <v>27.63</v>
+        <v>26.04</v>
       </c>
       <c r="E135" s="7">
-        <v>-7.42</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>34.68</v>
+        <v>26.94</v>
       </c>
       <c r="D136" s="6">
-        <v>43.12</v>
-      </c>
-      <c r="E136" s="8">
-        <v>8.44</v>
+        <v>30.16</v>
+      </c>
+      <c r="E136" s="7">
+        <v>3.22</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>28.43</v>
+        <v>19.64</v>
       </c>
       <c r="D137" s="6">
-        <v>19.31</v>
+        <v>27.24</v>
       </c>
       <c r="E137" s="7">
-        <v>-9.119999999999999</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>28.79</v>
+        <v>27.62</v>
       </c>
       <c r="D138" s="6">
-        <v>20.64</v>
+        <v>28.66</v>
       </c>
       <c r="E138" s="7">
-        <v>-8.15</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>44.65</v>
+        <v>22.94</v>
       </c>
       <c r="D139" s="6">
-        <v>38.31</v>
+        <v>36.15</v>
       </c>
       <c r="E139" s="7">
-        <v>-6.34</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>45.23</v>
+        <v>27.63</v>
       </c>
       <c r="D140" s="6">
-        <v>37.28</v>
+        <v>33.63</v>
       </c>
       <c r="E140" s="7">
-        <v>-7.95</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>39.59</v>
+        <v>43.12</v>
       </c>
       <c r="D141" s="6">
-        <v>25.24</v>
-      </c>
-      <c r="E141" s="7">
-        <v>-14.35</v>
+        <v>39.1</v>
+      </c>
+      <c r="E141" s="8">
+        <v>-4.02</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>37.15</v>
+        <v>19.31</v>
       </c>
       <c r="D142" s="6">
-        <v>28.5</v>
+        <v>21.53</v>
       </c>
       <c r="E142" s="7">
-        <v>-8.65</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>49.68</v>
+        <v>20.64</v>
       </c>
       <c r="D143" s="6">
-        <v>41.78</v>
-      </c>
-      <c r="E143" s="7">
-        <v>-7.9</v>
+        <v>20.56</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>31.07</v>
+        <v>38.31</v>
       </c>
       <c r="D144" s="6">
-        <v>24.06</v>
+        <v>41.31</v>
       </c>
       <c r="E144" s="7">
-        <v>-7.01</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>29.87</v>
+        <v>37.28</v>
       </c>
       <c r="D145" s="6">
-        <v>26.12</v>
+        <v>39.7</v>
       </c>
       <c r="E145" s="7">
-        <v>-3.75</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>47.06</v>
+        <v>25.24</v>
       </c>
       <c r="D146" s="6">
-        <v>39.84</v>
+        <v>28.72</v>
       </c>
       <c r="E146" s="7">
-        <v>-7.22</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>50.65</v>
+        <v>28.5</v>
       </c>
       <c r="D147" s="6">
-        <v>31.51</v>
+        <v>38.03</v>
       </c>
       <c r="E147" s="7">
-        <v>-19.14</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>32.09</v>
+        <v>41.78</v>
       </c>
       <c r="D148" s="6">
-        <v>25.42</v>
-      </c>
-      <c r="E148" s="7">
-        <v>-6.67</v>
+        <v>40.92</v>
+      </c>
+      <c r="E148" s="8">
+        <v>-0.86</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>45.6</v>
+        <v>24.06</v>
       </c>
       <c r="D149" s="6">
+        <v>28.16</v>
+      </c>
+      <c r="E149" s="7">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
+      <c r="A150" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C150" s="6">
+        <v>26.12</v>
+      </c>
+      <c r="D150" s="6">
+        <v>29.05</v>
+      </c>
+      <c r="E150" s="7">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
+      <c r="A151" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C151" s="6">
+        <v>39.84</v>
+      </c>
+      <c r="D151" s="6">
+        <v>39.03</v>
+      </c>
+      <c r="E151" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C152" s="6">
+        <v>31.51</v>
+      </c>
+      <c r="D152" s="6">
+        <v>31.18</v>
+      </c>
+      <c r="E152" s="8">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C153" s="6">
+        <v>25.42</v>
+      </c>
+      <c r="D153" s="6">
+        <v>33.47</v>
+      </c>
+      <c r="E153" s="7">
+        <v>8.050000000000001</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C154" s="6">
         <v>38.17</v>
       </c>
-      <c r="E149" s="7">
-        <v>-7.43</v>
+      <c r="D154" s="6">
+        <v>43.93</v>
+      </c>
+      <c r="E154" s="7">
+        <v>5.76</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5858,28 +5979,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5893,16 +6014,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>29.3</v>
+        <v>32.8</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.9</v>
+        <v>-4.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -6016,10 +6137,10 @@
         <v>38</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>49</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>48</v>
@@ -6042,34 +6163,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2761</v>
+        <v>0.2663</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2105</v>
+        <v>0.2104</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1978</v>
+        <v>0.195</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1955</v>
+        <v>0.1887</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1668</v>
+        <v>0.1695</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1401</v>
+        <v>0.1419</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1257</v>
+        <v>0.1253</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1256</v>
+        <v>0.1245</v>
       </c>
       <c r="I2" s="14">
-        <v>0.1171</v>
+        <v>0.1141</v>
       </c>
       <c r="J2" s="14">
-        <v>0.1045</v>
+        <v>0.1054</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6106,34 +6227,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0941</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0713</v>
+        <v>0.0673</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0667</v>
+        <v>0.066</v>
       </c>
       <c r="D4" s="14">
-        <v>0.06509999999999999</v>
+        <v>0.0578</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0385</v>
+        <v>0.0378</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0205</v>
+        <v>0.0213</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0191</v>
+        <v>-0.0114</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0391</v>
+        <v>-0.04099999999999999</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.0499</v>
+        <v>-0.0452</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.0733</v>
+        <v>-0.0475</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="122">
   <si>
     <t>Symbol</t>
   </si>
@@ -259,12 +259,12 @@
     <t>Unknown</t>
   </si>
   <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>DOWN</t>
   </si>
   <si>
@@ -289,100 +289,64 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.2% → -1.8%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.2%</t>
+  </si>
+  <si>
+    <t>-1.8%</t>
+  </si>
+  <si>
+    <t>-2.4% → -1.9%</t>
+  </si>
+  <si>
+    <t>-2.4%</t>
+  </si>
+  <si>
+    <t>-1.9%</t>
+  </si>
+  <si>
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>26.0 → 33.4</t>
+    <t>29.0 → 40.5</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>33.4</t>
-  </si>
-  <si>
-    <t>27.2 → 33.0</t>
-  </si>
-  <si>
-    <t>27.2</t>
-  </si>
-  <si>
-    <t>33.0</t>
-  </si>
-  <si>
-    <t>28.7 → 34.4</t>
-  </si>
-  <si>
-    <t>28.7</t>
-  </si>
-  <si>
-    <t>34.4</t>
-  </si>
-  <si>
-    <t>21.5 → 34.6</t>
-  </si>
-  <si>
-    <t>21.5</t>
-  </si>
-  <si>
-    <t>34.6</t>
-  </si>
-  <si>
-    <t>28.7 → 35.7</t>
-  </si>
-  <si>
-    <t>35.7</t>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>40.5</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>40.9 → 51.9</t>
-  </si>
-  <si>
-    <t>40.9</t>
-  </si>
-  <si>
-    <t>51.9</t>
-  </si>
-  <si>
-    <t>28.2 → 33.9</t>
-  </si>
-  <si>
-    <t>28.2</t>
-  </si>
-  <si>
-    <t>33.9</t>
-  </si>
-  <si>
-    <t>29.1 → 30.3</t>
-  </si>
-  <si>
-    <t>29.1</t>
-  </si>
-  <si>
-    <t>30.3</t>
-  </si>
-  <si>
-    <t>39.0 → 50.4</t>
-  </si>
-  <si>
-    <t>39.0</t>
-  </si>
-  <si>
-    <t>50.4</t>
+    <t>45.9 → 50.7</t>
+  </si>
+  <si>
+    <t>45.9</t>
+  </si>
+  <si>
+    <t>50.7</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1113,10 +1077,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>27159.15</v>
+        <v>27129</v>
       </c>
       <c r="E2">
-        <v>0.99</v>
+        <v>-0.11</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1125,43 +1089,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-8.390000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="I2">
-        <v>14.26</v>
+        <v>14.13</v>
       </c>
       <c r="J2">
-        <v>-1.79</v>
+        <v>-1.5</v>
       </c>
       <c r="K2">
-        <v>-7.19</v>
+        <v>-7.05</v>
       </c>
       <c r="L2">
-        <v>1.54</v>
+        <v>2.05</v>
       </c>
       <c r="M2">
-        <v>-0.09</v>
+        <v>1.1</v>
       </c>
       <c r="N2">
-        <v>21.28</v>
+        <v>21.63</v>
       </c>
       <c r="O2">
         <v>62</v>
       </c>
       <c r="Q2">
-        <v>27130.97</v>
+        <v>27048.58</v>
       </c>
       <c r="R2">
-        <v>28165.11</v>
+        <v>28056.48</v>
       </c>
       <c r="S2">
-        <v>28115.1</v>
+        <v>28124.15</v>
       </c>
       <c r="T2">
-        <v>27131.46</v>
+        <v>27128.62</v>
       </c>
       <c r="U2">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1173,34 +1137,34 @@
         <v>79</v>
       </c>
       <c r="Y2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z2">
-        <v>33.42</v>
+        <v>33.02</v>
       </c>
       <c r="AA2">
-        <v>-399.7</v>
+        <v>-405.28</v>
       </c>
       <c r="AB2">
-        <v>-221.52</v>
+        <v>-258.28</v>
       </c>
       <c r="AC2">
-        <v>-178.17</v>
+        <v>-147.01</v>
       </c>
       <c r="AD2">
-        <v>16.44</v>
+        <v>28.29</v>
       </c>
       <c r="AE2">
-        <v>6.91</v>
+        <v>16.34</v>
       </c>
       <c r="AF2">
-        <v>396.6</v>
+        <v>383.58</v>
       </c>
       <c r="AH2">
-        <v>29853.25</v>
+        <v>29716.03</v>
       </c>
       <c r="AI2">
-        <v>26476.98</v>
+        <v>26396.92</v>
       </c>
       <c r="AJ2">
         <v>28052.54</v>
@@ -1209,7 +1173,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>69.94</v>
+        <v>67.37</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1223,94 +1187,94 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9501.549999999999</v>
+        <v>9566.549999999999</v>
       </c>
       <c r="E3">
-        <v>0.63</v>
+        <v>0.68</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
       </c>
       <c r="G3">
-        <v>8829.25</v>
+        <v>8864.799999999999</v>
       </c>
       <c r="H3">
-        <v>-9.539999999999999</v>
+        <v>-8.92</v>
       </c>
       <c r="I3">
-        <v>7.61</v>
+        <v>7.92</v>
       </c>
       <c r="J3">
-        <v>-2.43</v>
+        <v>-1.48</v>
       </c>
       <c r="K3">
-        <v>-3.19</v>
+        <v>-1.93</v>
       </c>
       <c r="L3">
-        <v>-5.83</v>
+        <v>-4.87</v>
       </c>
       <c r="M3">
-        <v>7.81</v>
+        <v>8.35</v>
       </c>
       <c r="N3">
-        <v>11.02</v>
+        <v>11.95</v>
       </c>
       <c r="O3">
         <v>81</v>
       </c>
       <c r="Q3">
-        <v>9528.190000000001</v>
+        <v>9499.52</v>
       </c>
       <c r="R3">
-        <v>9712.24</v>
+        <v>9701.41</v>
       </c>
       <c r="S3">
-        <v>9805.83</v>
+        <v>9801.67</v>
       </c>
       <c r="T3">
-        <v>9760.48</v>
+        <v>9762.09</v>
       </c>
       <c r="U3">
-        <v>-2.65</v>
+        <v>-2</v>
       </c>
       <c r="V3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W3" t="b">
         <v>1</v>
       </c>
       <c r="X3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y3">
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>35.43</v>
+        <v>40.71</v>
       </c>
       <c r="AA3">
-        <v>-92</v>
+        <v>-89.29000000000001</v>
       </c>
       <c r="AB3">
-        <v>-62.52</v>
+        <v>-67.88</v>
       </c>
       <c r="AC3">
-        <v>-29.47</v>
+        <v>-21.41</v>
       </c>
       <c r="AD3">
-        <v>18.65</v>
+        <v>40.55</v>
       </c>
       <c r="AE3">
-        <v>12.95</v>
+        <v>21.44</v>
       </c>
       <c r="AF3">
-        <v>104.45</v>
+        <v>102.88</v>
       </c>
       <c r="AH3">
-        <v>9980.27</v>
+        <v>9974.82</v>
       </c>
       <c r="AI3">
-        <v>9444.209999999999</v>
+        <v>9427.99</v>
       </c>
       <c r="AJ3">
         <v>9750.9</v>
@@ -1319,7 +1283,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>40.46</v>
+        <v>38.37</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1333,10 +1297,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11428</v>
+        <v>11460.7</v>
       </c>
       <c r="E4">
-        <v>0.58</v>
+        <v>0.29</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1345,82 +1309,82 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-9.58</v>
+        <v>-9.32</v>
       </c>
       <c r="I4">
-        <v>10.58</v>
+        <v>10.9</v>
       </c>
       <c r="J4">
-        <v>-0.9</v>
+        <v>-0.47</v>
       </c>
       <c r="K4">
-        <v>-4.8</v>
+        <v>-4.39</v>
       </c>
       <c r="L4">
-        <v>-1.62</v>
+        <v>-1.38</v>
       </c>
       <c r="M4">
-        <v>-8.16</v>
+        <v>-7.62</v>
       </c>
       <c r="N4">
-        <v>9.52</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="O4">
         <v>19</v>
       </c>
       <c r="Q4">
-        <v>11409.56</v>
+        <v>11398.75</v>
       </c>
       <c r="R4">
-        <v>11713.65</v>
+        <v>11683.3</v>
       </c>
       <c r="S4">
-        <v>11833.34</v>
+        <v>11828.54</v>
       </c>
       <c r="T4">
-        <v>11632.67</v>
+        <v>11627.48</v>
       </c>
       <c r="U4">
-        <v>-1.76</v>
+        <v>-1.43</v>
       </c>
       <c r="V4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W4" t="b">
         <v>1</v>
       </c>
       <c r="X4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y4">
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>32.98</v>
+        <v>35.67</v>
       </c>
       <c r="AA4">
-        <v>-148.75</v>
+        <v>-144.02</v>
       </c>
       <c r="AB4">
-        <v>-107.93</v>
+        <v>-115.15</v>
       </c>
       <c r="AC4">
-        <v>-40.82</v>
+        <v>-28.87</v>
       </c>
       <c r="AD4">
-        <v>27.17</v>
+        <v>54.24</v>
       </c>
       <c r="AE4">
-        <v>12.26</v>
+        <v>30.34</v>
       </c>
       <c r="AF4">
-        <v>111.08</v>
+        <v>107.64</v>
       </c>
       <c r="AH4">
-        <v>12222.5</v>
+        <v>12175.4</v>
       </c>
       <c r="AI4">
-        <v>11204.8</v>
+        <v>11191.21</v>
       </c>
       <c r="AJ4">
         <v>11665.92</v>
@@ -1429,7 +1393,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>59.02</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1443,10 +1407,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>37381.75</v>
+        <v>37773.55</v>
       </c>
       <c r="E5">
-        <v>0.53</v>
+        <v>1.05</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1455,82 +1419,82 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-10</v>
+        <v>-9.06</v>
       </c>
       <c r="I5">
-        <v>12.94</v>
+        <v>14.13</v>
       </c>
       <c r="J5">
-        <v>-2.48</v>
+        <v>-1.18</v>
       </c>
       <c r="K5">
-        <v>-3.1</v>
+        <v>-0.92</v>
       </c>
       <c r="L5">
-        <v>-7.6</v>
+        <v>-6.84</v>
       </c>
       <c r="M5">
-        <v>9.140000000000001</v>
+        <v>9.42</v>
       </c>
       <c r="N5">
-        <v>11.76</v>
+        <v>12.25</v>
       </c>
       <c r="O5">
         <v>74</v>
       </c>
       <c r="Q5">
-        <v>37574.34</v>
+        <v>37484.37</v>
       </c>
       <c r="R5">
-        <v>37971.14</v>
+        <v>37952.22</v>
       </c>
       <c r="S5">
-        <v>38560.63</v>
+        <v>38539.34</v>
       </c>
       <c r="T5">
-        <v>37565.67</v>
+        <v>37574.71</v>
       </c>
       <c r="U5">
-        <v>-0.49</v>
+        <v>0.53</v>
       </c>
       <c r="V5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W5" t="b">
         <v>1</v>
       </c>
       <c r="X5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z5">
-        <v>34.36</v>
+        <v>43.89</v>
       </c>
       <c r="AA5">
-        <v>-305.42</v>
+        <v>-283.24</v>
       </c>
       <c r="AB5">
-        <v>-251.57</v>
+        <v>-257.9</v>
       </c>
       <c r="AC5">
-        <v>-53.85</v>
+        <v>-25.34</v>
       </c>
       <c r="AD5">
-        <v>11.95</v>
+        <v>36.92</v>
       </c>
       <c r="AE5">
-        <v>25.81</v>
+        <v>22.72</v>
       </c>
       <c r="AF5">
-        <v>384.72</v>
+        <v>389.53</v>
       </c>
       <c r="AH5">
-        <v>38663.22</v>
+        <v>38644.17</v>
       </c>
       <c r="AI5">
-        <v>37279.06</v>
+        <v>37260.26</v>
       </c>
       <c r="AJ5">
         <v>38269.93</v>
@@ -1539,7 +1503,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>27.71</v>
+        <v>25.46</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1553,10 +1517,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>45572.7</v>
+        <v>45466.8</v>
       </c>
       <c r="E6">
-        <v>0.03</v>
+        <v>-0.23</v>
       </c>
       <c r="F6">
         <v>56960.6</v>
@@ -1565,82 +1529,82 @@
         <v>44829.95</v>
       </c>
       <c r="H6">
-        <v>-19.99</v>
+        <v>-20.18</v>
       </c>
       <c r="I6">
-        <v>1.66</v>
+        <v>1.42</v>
       </c>
       <c r="J6">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="K6">
-        <v>-4.53</v>
+        <v>-4.23</v>
       </c>
       <c r="L6">
-        <v>-8.220000000000001</v>
+        <v>-8.26</v>
       </c>
       <c r="M6">
-        <v>-19.34</v>
+        <v>-20.03</v>
       </c>
       <c r="N6">
-        <v>2.24</v>
+        <v>2.01</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>45240.2</v>
+        <v>45296.44</v>
       </c>
       <c r="R6">
-        <v>46274.17</v>
+        <v>46154.35</v>
       </c>
       <c r="S6">
-        <v>47814.07</v>
+        <v>47736.4</v>
       </c>
       <c r="T6">
-        <v>50158.77</v>
+        <v>50108.89</v>
       </c>
       <c r="U6">
-        <v>-9.140000000000001</v>
+        <v>-9.26</v>
       </c>
       <c r="V6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W6" t="b">
         <v>0</v>
       </c>
       <c r="X6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y6">
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>36.37</v>
+        <v>35.35</v>
       </c>
       <c r="AA6">
-        <v>-807.61</v>
+        <v>-768</v>
       </c>
       <c r="AB6">
-        <v>-805.46</v>
+        <v>-797.97</v>
       </c>
       <c r="AC6">
-        <v>-2.15</v>
+        <v>29.97</v>
       </c>
       <c r="AD6">
-        <v>66.67</v>
+        <v>97.48</v>
       </c>
       <c r="AE6">
-        <v>33.4</v>
+        <v>65.83</v>
       </c>
       <c r="AF6">
-        <v>544.48</v>
+        <v>528.6799999999999</v>
       </c>
       <c r="AH6">
-        <v>48235.67</v>
+        <v>47996.26</v>
       </c>
       <c r="AI6">
-        <v>44312.68</v>
+        <v>44312.45</v>
       </c>
       <c r="AJ6">
         <v>46607.06</v>
@@ -1649,7 +1613,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>61.61</v>
+        <v>57.24</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1663,10 +1627,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25318.35</v>
+        <v>25510</v>
       </c>
       <c r="E7">
-        <v>0.22</v>
+        <v>0.76</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1675,82 +1639,82 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-11.05</v>
+        <v>-10.38</v>
       </c>
       <c r="I7">
-        <v>7.64</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="J7">
-        <v>-0.23</v>
+        <v>-0.04</v>
       </c>
       <c r="K7">
-        <v>-3.02</v>
+        <v>-1.93</v>
       </c>
       <c r="L7">
-        <v>-4.75</v>
+        <v>-3.49</v>
       </c>
       <c r="M7">
-        <v>-2.48</v>
+        <v>-2.35</v>
       </c>
       <c r="N7">
-        <v>6.5</v>
+        <v>7.02</v>
       </c>
       <c r="O7">
         <v>32</v>
       </c>
       <c r="Q7">
-        <v>25344.62</v>
+        <v>25342.56</v>
       </c>
       <c r="R7">
-        <v>25879.14</v>
+        <v>25844.45</v>
       </c>
       <c r="S7">
-        <v>26335.63</v>
+        <v>26316.18</v>
       </c>
       <c r="T7">
-        <v>26551.36</v>
+        <v>26539.91</v>
       </c>
       <c r="U7">
-        <v>-4.64</v>
+        <v>-3.88</v>
       </c>
       <c r="V7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W7" t="b">
         <v>0</v>
       </c>
       <c r="X7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y7">
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>35.36</v>
+        <v>41.05</v>
       </c>
       <c r="AA7">
-        <v>-295.79</v>
+        <v>-280.21</v>
       </c>
       <c r="AB7">
-        <v>-232.29</v>
+        <v>-241.88</v>
       </c>
       <c r="AC7">
-        <v>-63.5</v>
+        <v>-38.33</v>
       </c>
       <c r="AD7">
-        <v>24.36</v>
+        <v>48.18</v>
       </c>
       <c r="AE7">
-        <v>21.12</v>
+        <v>31.04</v>
       </c>
       <c r="AF7">
-        <v>291.66</v>
+        <v>289.27</v>
       </c>
       <c r="AH7">
-        <v>26687.07</v>
+        <v>26653.25</v>
       </c>
       <c r="AI7">
-        <v>25071.22</v>
+        <v>25035.65</v>
       </c>
       <c r="AJ7">
         <v>26066.31</v>
@@ -1759,7 +1723,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>33.63</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1773,10 +1737,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>29155.6</v>
+        <v>28854.55</v>
       </c>
       <c r="E8">
-        <v>0.23</v>
+        <v>-1.03</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1785,43 +1749,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-26.17</v>
+        <v>-26.93</v>
       </c>
       <c r="I8">
-        <v>13.14</v>
+        <v>11.97</v>
       </c>
       <c r="J8">
-        <v>0.84</v>
+        <v>-0.13</v>
       </c>
       <c r="K8">
-        <v>-3.5</v>
+        <v>-5.19</v>
       </c>
       <c r="L8">
-        <v>2.42</v>
+        <v>5.21</v>
       </c>
       <c r="M8">
-        <v>-17.3</v>
+        <v>-20.26</v>
       </c>
       <c r="N8">
-        <v>-3.94</v>
+        <v>-4.01</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>29122.19</v>
+        <v>29114.92</v>
       </c>
       <c r="R8">
-        <v>30206.21</v>
+        <v>30115.29</v>
       </c>
       <c r="S8">
-        <v>30152.81</v>
+        <v>30180.47</v>
       </c>
       <c r="T8">
-        <v>31892.76</v>
+        <v>31850.21</v>
       </c>
       <c r="U8">
-        <v>-8.58</v>
+        <v>-9.41</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1830,40 +1794,40 @@
         <v>0</v>
       </c>
       <c r="X8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>39.98</v>
+        <v>37.41</v>
       </c>
       <c r="AA8">
-        <v>-360.43</v>
+        <v>-398.8</v>
       </c>
       <c r="AB8">
-        <v>-159.32</v>
+        <v>-207.22</v>
       </c>
       <c r="AC8">
-        <v>-201.11</v>
+        <v>-191.58</v>
       </c>
       <c r="AD8">
-        <v>25.03</v>
+        <v>17.7</v>
       </c>
       <c r="AE8">
-        <v>18.41</v>
+        <v>20.32</v>
       </c>
       <c r="AF8">
-        <v>698.42</v>
+        <v>690.46</v>
       </c>
       <c r="AG8">
         <v>-100</v>
       </c>
       <c r="AH8">
-        <v>31924.44</v>
+        <v>31919.8</v>
       </c>
       <c r="AI8">
-        <v>28487.98</v>
+        <v>28310.78</v>
       </c>
       <c r="AJ8">
         <v>30808.98</v>
@@ -1872,7 +1836,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>26.85</v>
+        <v>26.35</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1886,10 +1850,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15826.65</v>
+        <v>15929.65</v>
       </c>
       <c r="E9">
-        <v>1.35</v>
+        <v>0.65</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1898,67 +1862,67 @@
         <v>15584.65</v>
       </c>
       <c r="H9">
-        <v>-5.02</v>
+        <v>-4.4</v>
       </c>
       <c r="I9">
-        <v>1.55</v>
+        <v>2.21</v>
       </c>
       <c r="J9">
-        <v>-2.37</v>
+        <v>-1.15</v>
       </c>
       <c r="K9">
-        <v>-4.39</v>
+        <v>-3.31</v>
       </c>
       <c r="L9">
-        <v>-1.29</v>
+        <v>-0.57</v>
       </c>
       <c r="N9">
-        <v>3.99</v>
+        <v>6.49</v>
       </c>
       <c r="Q9">
-        <v>15822.07</v>
+        <v>15784.86</v>
       </c>
       <c r="R9">
-        <v>16265.16</v>
+        <v>16236.05</v>
       </c>
       <c r="S9">
-        <v>16248.4</v>
+        <v>16251.12</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
       </c>
       <c r="X9" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>34.56</v>
+        <v>39.82</v>
       </c>
       <c r="AA9">
-        <v>-156.76</v>
+        <v>-153.13</v>
       </c>
       <c r="AB9">
-        <v>-70.76000000000001</v>
+        <v>-87.23</v>
       </c>
       <c r="AC9">
-        <v>-86</v>
+        <v>-65.90000000000001</v>
       </c>
       <c r="AD9">
-        <v>13.36</v>
+        <v>29.05</v>
       </c>
       <c r="AE9">
-        <v>5.02</v>
+        <v>14.7</v>
       </c>
       <c r="AF9">
-        <v>168.07</v>
+        <v>166.11</v>
       </c>
       <c r="AH9">
-        <v>16891.62</v>
+        <v>16868.3</v>
       </c>
       <c r="AI9">
-        <v>15638.71</v>
+        <v>15603.79</v>
       </c>
       <c r="AJ9">
         <v>16050.69</v>
@@ -1967,7 +1931,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>54.26</v>
+        <v>50.63</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1981,10 +1945,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8969.299999999999</v>
+        <v>9071.299999999999</v>
       </c>
       <c r="E10">
-        <v>0.68</v>
+        <v>1.14</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1993,82 +1957,82 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-8.16</v>
+        <v>-7.11</v>
       </c>
       <c r="I10">
-        <v>4.77</v>
+        <v>5.96</v>
       </c>
       <c r="J10">
-        <v>-1.65</v>
+        <v>-0.68</v>
       </c>
       <c r="K10">
-        <v>-4.34</v>
+        <v>-2.52</v>
       </c>
       <c r="L10">
-        <v>-5.58</v>
+        <v>-4.63</v>
       </c>
       <c r="M10">
-        <v>0.05</v>
+        <v>0.87</v>
       </c>
       <c r="N10">
-        <v>12.71</v>
+        <v>13.23</v>
       </c>
       <c r="O10">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q10">
-        <v>8999.870000000001</v>
+        <v>8987.440000000001</v>
       </c>
       <c r="R10">
-        <v>9183.309999999999</v>
+        <v>9169.41</v>
       </c>
       <c r="S10">
-        <v>9309.629999999999</v>
+        <v>9304.540000000001</v>
       </c>
       <c r="T10">
-        <v>9322.25</v>
+        <v>9319.120000000001</v>
       </c>
       <c r="U10">
-        <v>-3.79</v>
+        <v>-2.66</v>
       </c>
       <c r="V10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y10">
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>29.02</v>
+        <v>40.51</v>
       </c>
       <c r="AA10">
-        <v>-102.06</v>
+        <v>-95.52</v>
       </c>
       <c r="AB10">
-        <v>-75.43000000000001</v>
+        <v>-79.45</v>
       </c>
       <c r="AC10">
-        <v>-26.63</v>
+        <v>-16.07</v>
       </c>
       <c r="AD10">
-        <v>15.99</v>
+        <v>49.33</v>
       </c>
       <c r="AE10">
-        <v>6.55</v>
+        <v>21.77</v>
       </c>
       <c r="AF10">
-        <v>85.04000000000001</v>
+        <v>86.25</v>
       </c>
       <c r="AH10">
-        <v>9459.639999999999</v>
+        <v>9438.459999999999</v>
       </c>
       <c r="AI10">
-        <v>8906.98</v>
+        <v>8900.360000000001</v>
       </c>
       <c r="AJ10">
         <v>9179.950000000001</v>
@@ -2077,7 +2041,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>60.57</v>
+        <v>56.35</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2091,10 +2055,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1533.15</v>
+        <v>1553.75</v>
       </c>
       <c r="E11">
-        <v>1.19</v>
+        <v>1.34</v>
       </c>
       <c r="F11">
         <v>1632.5</v>
@@ -2103,82 +2067,82 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-6.09</v>
+        <v>-4.82</v>
       </c>
       <c r="I11">
-        <v>22.32</v>
+        <v>23.97</v>
       </c>
       <c r="J11">
-        <v>0.44</v>
+        <v>1.23</v>
       </c>
       <c r="K11">
-        <v>-4.31</v>
+        <v>-2.14</v>
       </c>
       <c r="L11">
-        <v>1.27</v>
+        <v>2.53</v>
       </c>
       <c r="M11">
-        <v>-5.43</v>
+        <v>-3.55</v>
       </c>
       <c r="N11">
-        <v>-4.48</v>
+        <v>-4.14</v>
       </c>
       <c r="O11">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="Q11">
-        <v>1524.82</v>
+        <v>1528.61</v>
       </c>
       <c r="R11">
-        <v>1562.88</v>
+        <v>1559.5</v>
       </c>
       <c r="S11">
-        <v>1553.35</v>
+        <v>1554.77</v>
       </c>
       <c r="T11">
-        <v>1450.82</v>
+        <v>1451.35</v>
       </c>
       <c r="U11">
-        <v>5.67</v>
+        <v>7.06</v>
       </c>
       <c r="V11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
       </c>
       <c r="X11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y11">
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>45.92</v>
+        <v>50.66</v>
       </c>
       <c r="AA11">
-        <v>-12.17</v>
+        <v>-10.04</v>
       </c>
       <c r="AB11">
-        <v>-6.01</v>
+        <v>-6.82</v>
       </c>
       <c r="AC11">
-        <v>-6.16</v>
+        <v>-3.22</v>
       </c>
       <c r="AD11">
-        <v>17.99</v>
+        <v>51.32</v>
       </c>
       <c r="AE11">
-        <v>15.14</v>
+        <v>27.39</v>
       </c>
       <c r="AF11">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="AH11">
-        <v>1640.12</v>
+        <v>1631.71</v>
       </c>
       <c r="AI11">
-        <v>1485.64</v>
+        <v>1487.28</v>
       </c>
       <c r="AJ11">
         <v>1604.15</v>
@@ -2187,7 +2151,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>50.02</v>
+        <v>44.57</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2201,94 +2165,94 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>12858.45</v>
+        <v>13052.6</v>
       </c>
       <c r="E12">
-        <v>0.9399999999999999</v>
+        <v>1.51</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
       </c>
       <c r="G12">
-        <v>9759.450000000001</v>
+        <v>9792.950000000001</v>
       </c>
       <c r="H12">
-        <v>-6.27</v>
+        <v>-4.85</v>
       </c>
       <c r="I12">
-        <v>31.75</v>
+        <v>33.29</v>
       </c>
       <c r="J12">
-        <v>-3.98</v>
+        <v>-1.9</v>
       </c>
       <c r="K12">
-        <v>-1.28</v>
+        <v>0.23</v>
       </c>
       <c r="L12">
-        <v>-1.17</v>
+        <v>0.24</v>
       </c>
       <c r="M12">
-        <v>32.1</v>
+        <v>33.74</v>
       </c>
       <c r="N12">
-        <v>17.74</v>
+        <v>19.74</v>
       </c>
       <c r="O12">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="Q12">
-        <v>12914.14</v>
+        <v>12863.67</v>
       </c>
       <c r="R12">
-        <v>13183.6</v>
+        <v>13183.22</v>
       </c>
       <c r="S12">
-        <v>12933.87</v>
+        <v>12944.86</v>
       </c>
       <c r="T12">
-        <v>12242.28</v>
+        <v>12256.14</v>
       </c>
       <c r="U12">
-        <v>5.03</v>
+        <v>6.5</v>
       </c>
       <c r="V12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W12" t="b">
         <v>1</v>
       </c>
       <c r="X12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y12">
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>43.69</v>
+        <v>49.55</v>
       </c>
       <c r="AA12">
-        <v>-34.36</v>
+        <v>-30.57</v>
       </c>
       <c r="AB12">
-        <v>40.95</v>
+        <v>26.65</v>
       </c>
       <c r="AC12">
-        <v>-75.31</v>
+        <v>-57.22</v>
       </c>
       <c r="AD12">
-        <v>9.779999999999999</v>
+        <v>28.7</v>
       </c>
       <c r="AE12">
-        <v>6.61</v>
+        <v>13.72</v>
       </c>
       <c r="AF12">
-        <v>231.73</v>
+        <v>229.2</v>
       </c>
       <c r="AH12">
-        <v>13662.42</v>
+        <v>13662.47</v>
       </c>
       <c r="AI12">
-        <v>12704.78</v>
+        <v>12703.97</v>
       </c>
       <c r="AJ12">
         <v>13387.91</v>
@@ -2297,7 +2261,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>29.7</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2311,10 +2275,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9554.35</v>
+        <v>9597</v>
       </c>
       <c r="E13">
-        <v>0.63</v>
+        <v>0.45</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2323,82 +2287,82 @@
         <v>9428.700000000001</v>
       </c>
       <c r="H13">
-        <v>-11.26</v>
+        <v>-10.86</v>
       </c>
       <c r="I13">
-        <v>1.33</v>
+        <v>1.78</v>
       </c>
       <c r="J13">
-        <v>-1.88</v>
+        <v>-1.57</v>
       </c>
       <c r="K13">
-        <v>-2.89</v>
+        <v>-1.58</v>
       </c>
       <c r="L13">
-        <v>-6.21</v>
+        <v>-5.71</v>
       </c>
       <c r="M13">
-        <v>1.75</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
-        <v>19.86</v>
+        <v>20.61</v>
       </c>
       <c r="O13">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="Q13">
-        <v>9590.959999999999</v>
+        <v>9560.290000000001</v>
       </c>
       <c r="R13">
-        <v>9687.110000000001</v>
+        <v>9679.799999999999</v>
       </c>
       <c r="S13">
-        <v>9818.879999999999</v>
+        <v>9814.719999999999</v>
       </c>
       <c r="T13">
-        <v>10021.87</v>
+        <v>10020.65</v>
       </c>
       <c r="U13">
-        <v>-4.67</v>
+        <v>-4.23</v>
       </c>
       <c r="V13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W13" t="b">
         <v>0</v>
       </c>
       <c r="X13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y13">
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>35.67</v>
+        <v>40.16</v>
       </c>
       <c r="AA13">
-        <v>-74.67</v>
+        <v>-72.41</v>
       </c>
       <c r="AB13">
-        <v>-61.43</v>
+        <v>-63.62</v>
       </c>
       <c r="AC13">
-        <v>-13.24</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="AD13">
-        <v>21.86</v>
+        <v>45.3</v>
       </c>
       <c r="AE13">
-        <v>32.68</v>
+        <v>30.44</v>
       </c>
       <c r="AF13">
-        <v>95.95</v>
+        <v>94.67</v>
       </c>
       <c r="AH13">
-        <v>9859.700000000001</v>
+        <v>9854.76</v>
       </c>
       <c r="AI13">
-        <v>9514.52</v>
+        <v>9504.85</v>
       </c>
       <c r="AJ13">
         <v>9761.77</v>
@@ -2407,7 +2371,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>40.21</v>
+        <v>38.52</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2421,94 +2385,94 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8262.799999999999</v>
+        <v>8317.549999999999</v>
       </c>
       <c r="E14">
-        <v>-0.16</v>
+        <v>0.66</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
       </c>
       <c r="G14">
-        <v>7023.85</v>
+        <v>7057.05</v>
       </c>
       <c r="H14">
-        <v>-16.37</v>
+        <v>-15.81</v>
       </c>
       <c r="I14">
-        <v>17.64</v>
+        <v>17.86</v>
       </c>
       <c r="J14">
-        <v>-1.27</v>
+        <v>-1</v>
       </c>
       <c r="K14">
-        <v>-4.13</v>
+        <v>-3.48</v>
       </c>
       <c r="L14">
-        <v>-5.79</v>
+        <v>-4.58</v>
       </c>
       <c r="M14">
-        <v>20.1</v>
+        <v>18.42</v>
       </c>
       <c r="N14">
-        <v>27.36</v>
+        <v>28.65</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8289.790000000001</v>
+        <v>8272.93</v>
       </c>
       <c r="R14">
-        <v>8479.4</v>
+        <v>8464.440000000001</v>
       </c>
       <c r="S14">
-        <v>8489.35</v>
+        <v>8491.639999999999</v>
       </c>
       <c r="T14">
-        <v>8595.139999999999</v>
+        <v>8593.969999999999</v>
       </c>
       <c r="U14">
-        <v>-3.87</v>
+        <v>-3.22</v>
       </c>
       <c r="V14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W14" t="b">
         <v>0</v>
       </c>
       <c r="X14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y14">
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>37.43</v>
+        <v>41.57</v>
       </c>
       <c r="AA14">
-        <v>-78.02</v>
+        <v>-76.93000000000001</v>
       </c>
       <c r="AB14">
-        <v>-42.79</v>
+        <v>-49.62</v>
       </c>
       <c r="AC14">
-        <v>-35.23</v>
+        <v>-27.31</v>
       </c>
       <c r="AD14">
-        <v>26.18</v>
+        <v>44.72</v>
       </c>
       <c r="AE14">
-        <v>15</v>
+        <v>28.14</v>
       </c>
       <c r="AF14">
-        <v>131.47</v>
+        <v>126.54</v>
       </c>
       <c r="AH14">
-        <v>8761.959999999999</v>
+        <v>8748.08</v>
       </c>
       <c r="AI14">
-        <v>8196.83</v>
+        <v>8180.8</v>
       </c>
       <c r="AJ14">
         <v>8626.549999999999</v>
@@ -2517,7 +2481,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>29.87</v>
+        <v>28.61</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2531,10 +2495,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26579.25</v>
+        <v>26710.1</v>
       </c>
       <c r="E15">
-        <v>1.66</v>
+        <v>0.49</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2543,85 +2507,85 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-2.23</v>
+        <v>-1.75</v>
       </c>
       <c r="I15">
-        <v>23.89</v>
+        <v>24.5</v>
       </c>
       <c r="J15">
-        <v>-0.42</v>
+        <v>0.58</v>
       </c>
       <c r="K15">
-        <v>0.82</v>
+        <v>1.51</v>
       </c>
       <c r="L15">
-        <v>9.460000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M15">
-        <v>20.53</v>
+        <v>20.74</v>
       </c>
       <c r="N15">
-        <v>13.11</v>
+        <v>13.65</v>
       </c>
       <c r="O15">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="Q15">
-        <v>26400.42</v>
+        <v>26431.27</v>
       </c>
       <c r="R15">
-        <v>26614.64</v>
+        <v>26629.34</v>
       </c>
       <c r="S15">
-        <v>26365.11</v>
+        <v>26386.19</v>
       </c>
       <c r="T15">
-        <v>23959.6</v>
+        <v>23978.84</v>
       </c>
       <c r="U15">
-        <v>10.93</v>
+        <v>11.39</v>
       </c>
       <c r="V15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W15" t="b">
         <v>1</v>
       </c>
       <c r="X15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y15">
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>51.87</v>
+        <v>54.6</v>
       </c>
       <c r="AA15">
-        <v>21.01</v>
+        <v>34.05</v>
       </c>
       <c r="AB15">
-        <v>92.73</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="AC15">
-        <v>-71.72</v>
+        <v>-46.94</v>
       </c>
       <c r="AD15">
-        <v>11.38</v>
+        <v>25.61</v>
       </c>
       <c r="AE15">
-        <v>4.21</v>
+        <v>12.38</v>
       </c>
       <c r="AF15">
-        <v>335.88</v>
+        <v>331.15</v>
       </c>
       <c r="AG15">
         <v>-100</v>
       </c>
       <c r="AH15">
-        <v>27133.73</v>
+        <v>27141.36</v>
       </c>
       <c r="AI15">
-        <v>26095.54</v>
+        <v>26117.32</v>
       </c>
       <c r="AJ15">
         <v>26048.62</v>
@@ -2630,7 +2594,7 @@
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>25.65</v>
+        <v>23.4</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2644,10 +2608,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>834.25</v>
+        <v>844.2</v>
       </c>
       <c r="E16">
-        <v>1.45</v>
+        <v>1.19</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2656,82 +2620,82 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-13.87</v>
+        <v>-12.85</v>
       </c>
       <c r="I16">
-        <v>28.12</v>
+        <v>29.65</v>
       </c>
       <c r="J16">
-        <v>-4.35</v>
+        <v>-3.19</v>
       </c>
       <c r="K16">
-        <v>-6.87</v>
+        <v>-5.71</v>
       </c>
       <c r="L16">
-        <v>1.71</v>
+        <v>3.98</v>
       </c>
       <c r="M16">
-        <v>-4.54</v>
+        <v>-4.48</v>
       </c>
       <c r="N16">
-        <v>15.07</v>
+        <v>15.86</v>
       </c>
       <c r="O16">
         <v>50</v>
       </c>
       <c r="Q16">
-        <v>838.27</v>
+        <v>832.7</v>
       </c>
       <c r="R16">
-        <v>887.01</v>
+        <v>883.8200000000001</v>
       </c>
       <c r="S16">
-        <v>899.5700000000001</v>
+        <v>898.3200000000001</v>
       </c>
       <c r="T16">
-        <v>828.9400000000001</v>
+        <v>828.6</v>
       </c>
       <c r="U16">
-        <v>0.64</v>
+        <v>1.88</v>
       </c>
       <c r="V16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W16" t="b">
         <v>1</v>
       </c>
       <c r="X16" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y16">
         <v>2</v>
       </c>
       <c r="Z16">
-        <v>33.87</v>
+        <v>38.27</v>
       </c>
       <c r="AA16">
-        <v>-16.78</v>
+        <v>-16.96</v>
       </c>
       <c r="AB16">
-        <v>-7.61</v>
+        <v>-9.48</v>
       </c>
       <c r="AC16">
-        <v>-9.17</v>
+        <v>-7.48</v>
       </c>
       <c r="AD16">
-        <v>13.83</v>
+        <v>27.95</v>
       </c>
       <c r="AE16">
-        <v>5.97</v>
+        <v>15.28</v>
       </c>
       <c r="AF16">
-        <v>20.43</v>
+        <v>20.21</v>
       </c>
       <c r="AH16">
-        <v>952.12</v>
+        <v>950.83</v>
       </c>
       <c r="AI16">
-        <v>821.9</v>
+        <v>816.8099999999999</v>
       </c>
       <c r="AJ16">
         <v>877.53</v>
@@ -2740,7 +2704,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>40.94</v>
+        <v>39.29</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2754,10 +2718,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29833.2</v>
+        <v>30073.1</v>
       </c>
       <c r="E17">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2766,82 +2730,82 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-12.52</v>
+        <v>-11.81</v>
       </c>
       <c r="I17">
-        <v>5.18</v>
+        <v>6.03</v>
       </c>
       <c r="J17">
-        <v>0.05</v>
+        <v>0.46</v>
       </c>
       <c r="K17">
-        <v>-3.01</v>
+        <v>-1.99</v>
       </c>
       <c r="L17">
-        <v>-3.17</v>
+        <v>-1.6</v>
       </c>
       <c r="M17">
-        <v>-7.2</v>
+        <v>-7.13</v>
       </c>
       <c r="N17">
-        <v>3.77</v>
+        <v>4.16</v>
       </c>
       <c r="O17">
         <v>26</v>
       </c>
       <c r="Q17">
-        <v>29854.07</v>
+        <v>29881.37</v>
       </c>
       <c r="R17">
-        <v>30457.61</v>
+        <v>30416.77</v>
       </c>
       <c r="S17">
-        <v>30944.66</v>
+        <v>30928.89</v>
       </c>
       <c r="T17">
-        <v>31475.43</v>
+        <v>31455.71</v>
       </c>
       <c r="U17">
-        <v>-5.22</v>
+        <v>-4.4</v>
       </c>
       <c r="V17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W17" t="b">
         <v>0</v>
       </c>
       <c r="X17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y17">
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>30.3</v>
+        <v>39.26</v>
       </c>
       <c r="AA17">
-        <v>-328.16</v>
+        <v>-308.46</v>
       </c>
       <c r="AB17">
-        <v>-256.44</v>
+        <v>-266.85</v>
       </c>
       <c r="AC17">
-        <v>-71.70999999999999</v>
+        <v>-41.61</v>
       </c>
       <c r="AD17">
-        <v>21.36</v>
+        <v>43.4</v>
       </c>
       <c r="AE17">
-        <v>20.08</v>
+        <v>28.27</v>
       </c>
       <c r="AF17">
-        <v>277.04</v>
+        <v>274.39</v>
       </c>
       <c r="AH17">
-        <v>31365.35</v>
+        <v>31316.09</v>
       </c>
       <c r="AI17">
-        <v>29549.87</v>
+        <v>29517.46</v>
       </c>
       <c r="AJ17">
         <v>30589.09</v>
@@ -2850,7 +2814,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>38.8</v>
+        <v>35.07</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2864,10 +2828,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16529.15</v>
+        <v>16613.9</v>
       </c>
       <c r="E18">
-        <v>1.56</v>
+        <v>0.51</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2876,67 +2840,67 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-2.43</v>
+        <v>-1.93</v>
       </c>
       <c r="I18">
-        <v>7.31</v>
+        <v>7.86</v>
       </c>
       <c r="J18">
-        <v>-0.31</v>
+        <v>0.58</v>
       </c>
       <c r="K18">
-        <v>0.4</v>
+        <v>1.23</v>
       </c>
       <c r="L18">
-        <v>6.27</v>
+        <v>6.03</v>
       </c>
       <c r="N18">
-        <v>25.8</v>
+        <v>27.92</v>
       </c>
       <c r="Q18">
-        <v>16422.71</v>
+        <v>16441.76</v>
       </c>
       <c r="R18">
-        <v>16553.95</v>
+        <v>16561.38</v>
       </c>
       <c r="S18">
-        <v>16536.7</v>
+        <v>16542.83</v>
       </c>
       <c r="V18" t="s">
+        <v>80</v>
+      </c>
+      <c r="X18" t="s">
         <v>79</v>
-      </c>
-      <c r="X18" t="s">
-        <v>80</v>
       </c>
       <c r="Y18">
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>50.42</v>
+        <v>53.53</v>
       </c>
       <c r="AA18">
-        <v>-26.7</v>
+        <v>-15.08</v>
       </c>
       <c r="AB18">
-        <v>3.56</v>
+        <v>-0.17</v>
       </c>
       <c r="AC18">
-        <v>-30.26</v>
+        <v>-14.91</v>
       </c>
       <c r="AD18">
-        <v>12.39</v>
+        <v>28.17</v>
       </c>
       <c r="AE18">
-        <v>9.19</v>
+        <v>15.05</v>
       </c>
       <c r="AF18">
-        <v>195.55</v>
+        <v>193.1</v>
       </c>
       <c r="AH18">
-        <v>16867.42</v>
+        <v>16873.05</v>
       </c>
       <c r="AI18">
-        <v>16240.47</v>
+        <v>16249.72</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2945,7 +2909,7 @@
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>21.73</v>
+        <v>20.19</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2959,10 +2923,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9271.9</v>
+        <v>9351.700000000001</v>
       </c>
       <c r="E19">
-        <v>1.56</v>
+        <v>0.86</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2971,67 +2935,67 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-7.27</v>
+        <v>-6.47</v>
       </c>
       <c r="I19">
-        <v>3.07</v>
+        <v>3.96</v>
       </c>
       <c r="J19">
-        <v>-6.27</v>
+        <v>-4.53</v>
       </c>
       <c r="K19">
-        <v>-6.99</v>
+        <v>-4.76</v>
       </c>
       <c r="L19">
-        <v>-2.64</v>
+        <v>-2.46</v>
       </c>
       <c r="N19">
-        <v>12.08</v>
+        <v>15.58</v>
       </c>
       <c r="Q19">
-        <v>9412.940000000001</v>
+        <v>9324.139999999999</v>
       </c>
       <c r="R19">
-        <v>9674.07</v>
+        <v>9651.6</v>
       </c>
       <c r="S19">
-        <v>9562.219999999999</v>
+        <v>9563.07</v>
       </c>
       <c r="V19" t="s">
+        <v>80</v>
+      </c>
+      <c r="X19" t="s">
         <v>79</v>
-      </c>
-      <c r="X19" t="s">
-        <v>80</v>
       </c>
       <c r="Y19">
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>37.82</v>
+        <v>41.24</v>
       </c>
       <c r="AA19">
-        <v>-63.89</v>
+        <v>-74.40000000000001</v>
       </c>
       <c r="AB19">
-        <v>14.03</v>
+        <v>-3.65</v>
       </c>
       <c r="AC19">
-        <v>-77.93000000000001</v>
+        <v>-70.75</v>
       </c>
       <c r="AD19">
-        <v>6.14</v>
+        <v>15.45</v>
       </c>
       <c r="AE19">
-        <v>9.029999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AF19">
-        <v>185.01</v>
+        <v>183.54</v>
       </c>
       <c r="AH19">
-        <v>10131.74</v>
+        <v>10126.8</v>
       </c>
       <c r="AI19">
-        <v>9216.4</v>
+        <v>9176.4</v>
       </c>
       <c r="AJ19">
         <v>9616.870000000001</v>
@@ -3040,7 +3004,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>32.03</v>
+        <v>30.94</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3054,10 +3018,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10857.35</v>
+        <v>10948.7</v>
       </c>
       <c r="E20">
-        <v>-0.14</v>
+        <v>0.84</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3066,67 +3030,67 @@
         <v>10796.4</v>
       </c>
       <c r="H20">
-        <v>-4.5</v>
+        <v>-3.7</v>
       </c>
       <c r="I20">
-        <v>0.5600000000000001</v>
+        <v>1.41</v>
       </c>
       <c r="J20">
-        <v>-1.56</v>
+        <v>-0.74</v>
       </c>
       <c r="K20">
-        <v>-3.33</v>
+        <v>-2.04</v>
       </c>
       <c r="L20">
-        <v>-3.95</v>
+        <v>-1.98</v>
       </c>
       <c r="N20">
-        <v>-5.2</v>
+        <v>-2.14</v>
       </c>
       <c r="Q20">
-        <v>10898.62</v>
+        <v>10882.38</v>
       </c>
       <c r="R20">
-        <v>11075.44</v>
+        <v>11063.97</v>
       </c>
       <c r="S20">
-        <v>11154.42</v>
+        <v>11152.74</v>
       </c>
       <c r="V20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="X20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y20">
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>32.72</v>
+        <v>41.34</v>
       </c>
       <c r="AA20">
-        <v>-80.66</v>
+        <v>-77.84</v>
       </c>
       <c r="AB20">
-        <v>-49.67</v>
+        <v>-55.3</v>
       </c>
       <c r="AC20">
-        <v>-30.99</v>
+        <v>-22.54</v>
       </c>
       <c r="AD20">
-        <v>19.78</v>
+        <v>40.29</v>
       </c>
       <c r="AE20">
-        <v>10.14</v>
+        <v>23.48</v>
       </c>
       <c r="AF20">
-        <v>122.1</v>
+        <v>123.67</v>
       </c>
       <c r="AH20">
-        <v>11322.72</v>
+        <v>11312.47</v>
       </c>
       <c r="AI20">
-        <v>10828.17</v>
+        <v>10815.47</v>
       </c>
       <c r="AJ20">
         <v>11213.36</v>
@@ -3135,7 +3099,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>34.84</v>
+        <v>32.59</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3149,10 +3113,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27169.2</v>
+        <v>27290</v>
       </c>
       <c r="E21">
-        <v>-0.42</v>
+        <v>0.44</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3161,82 +3125,82 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6.92</v>
+        <v>-6.5</v>
       </c>
       <c r="I21">
-        <v>12.53</v>
+        <v>13.03</v>
       </c>
       <c r="J21">
-        <v>-0.17</v>
+        <v>-0.06</v>
       </c>
       <c r="K21">
-        <v>-0.29</v>
+        <v>0.3</v>
       </c>
       <c r="L21">
-        <v>-3.08</v>
+        <v>-2.16</v>
       </c>
       <c r="M21">
-        <v>3.04</v>
+        <v>2.86</v>
       </c>
       <c r="N21">
-        <v>6.59</v>
+        <v>7.07</v>
       </c>
       <c r="O21">
         <v>68</v>
       </c>
       <c r="Q21">
-        <v>27253.03</v>
+        <v>27249.85</v>
       </c>
       <c r="R21">
-        <v>27536.17</v>
+        <v>27528.2</v>
       </c>
       <c r="S21">
-        <v>27749.84</v>
+        <v>27740.38</v>
       </c>
       <c r="T21">
-        <v>27589.81</v>
+        <v>27582.79</v>
       </c>
       <c r="U21">
-        <v>-1.52</v>
+        <v>-1.06</v>
       </c>
       <c r="V21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="W21" t="b">
         <v>1</v>
       </c>
       <c r="X21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Y21">
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>41.69</v>
+        <v>44.87</v>
       </c>
       <c r="AA21">
-        <v>-118.14</v>
+        <v>-117.61</v>
       </c>
       <c r="AB21">
-        <v>-74.26000000000001</v>
+        <v>-82.93000000000001</v>
       </c>
       <c r="AC21">
-        <v>-43.88</v>
+        <v>-34.68</v>
       </c>
       <c r="AD21">
-        <v>14.07</v>
+        <v>24.23</v>
       </c>
       <c r="AE21">
-        <v>15.88</v>
+        <v>19.1</v>
       </c>
       <c r="AF21">
-        <v>306.06</v>
+        <v>301.31</v>
       </c>
       <c r="AH21">
-        <v>28036.1</v>
+        <v>28038.92</v>
       </c>
       <c r="AI21">
-        <v>27036.24</v>
+        <v>27017.49</v>
       </c>
       <c r="AJ21">
         <v>28092.43</v>
@@ -3245,7 +3209,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>25.77</v>
+        <v>23.66</v>
       </c>
     </row>
   </sheetData>
@@ -3386,7 +3350,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3426,7 +3390,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3446,7 +3410,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>89</v>
@@ -3466,2174 +3430,2168 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="B10" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="E10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="4" t="s">
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="A14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-7.19</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-7.05</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.14</v>
+      </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>125</v>
+      <c r="A15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-3.19</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-1.93</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.26</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="7">
-        <v>-7.83</v>
+        <v>-4.8</v>
       </c>
       <c r="D16" s="7">
-        <v>-7.19</v>
+        <v>-4.39</v>
       </c>
       <c r="E16" s="8">
-        <v>0.64</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="7">
-        <v>-4.08</v>
+        <v>-3.1</v>
       </c>
       <c r="D17" s="7">
-        <v>-3.19</v>
+        <v>-0.92</v>
       </c>
       <c r="E17" s="8">
-        <v>0.89</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="7">
-        <v>-5.83</v>
+        <v>-4.53</v>
       </c>
       <c r="D18" s="7">
-        <v>-4.8</v>
+        <v>-4.23</v>
       </c>
       <c r="E18" s="8">
-        <v>1.03</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="7">
-        <v>-3.8</v>
+        <v>-3.02</v>
       </c>
       <c r="D19" s="7">
-        <v>-3.1</v>
+        <v>-1.93</v>
       </c>
       <c r="E19" s="8">
-        <v>0.7</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="7">
-        <v>-5.29</v>
+        <v>-3.5</v>
       </c>
       <c r="D20" s="7">
-        <v>-4.53</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.76</v>
+        <v>-5.19</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="7">
-        <v>-3.64</v>
+        <v>-4.39</v>
       </c>
       <c r="D21" s="7">
-        <v>-3.02</v>
+        <v>-3.31</v>
       </c>
       <c r="E21" s="8">
-        <v>0.62</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="7">
-        <v>-7.24</v>
+        <v>-4.34</v>
       </c>
       <c r="D22" s="7">
-        <v>-3.5</v>
+        <v>-2.52</v>
       </c>
       <c r="E22" s="8">
-        <v>3.74</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="7">
-        <v>-5.84</v>
+        <v>-4.31</v>
       </c>
       <c r="D23" s="7">
-        <v>-4.39</v>
+        <v>-2.14</v>
       </c>
       <c r="E23" s="8">
-        <v>1.45</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="7">
-        <v>-5.39</v>
+        <v>-1.28</v>
       </c>
       <c r="D24" s="7">
-        <v>-4.34</v>
+        <v>0.23</v>
       </c>
       <c r="E24" s="8">
-        <v>1.05</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="7">
-        <v>-5.06</v>
+        <v>-2.89</v>
       </c>
       <c r="D25" s="7">
-        <v>-4.31</v>
+        <v>-1.58</v>
       </c>
       <c r="E25" s="8">
-        <v>0.75</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="7">
-        <v>-2.79</v>
+        <v>-4.13</v>
       </c>
       <c r="D26" s="7">
-        <v>-1.28</v>
+        <v>-3.48</v>
       </c>
       <c r="E26" s="8">
-        <v>1.51</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="7">
-        <v>-3.72</v>
+        <v>0.82</v>
       </c>
       <c r="D27" s="7">
-        <v>-2.89</v>
+        <v>1.51</v>
       </c>
       <c r="E27" s="8">
-        <v>0.83</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="7">
-        <v>-4.94</v>
+        <v>-6.87</v>
       </c>
       <c r="D28" s="7">
-        <v>-4.13</v>
+        <v>-5.71</v>
       </c>
       <c r="E28" s="8">
-        <v>0.8100000000000001</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="7">
-        <v>-1.13</v>
+        <v>-3.01</v>
       </c>
       <c r="D29" s="7">
-        <v>0.82</v>
+        <v>-1.99</v>
       </c>
       <c r="E29" s="8">
-        <v>1.95</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="7">
-        <v>-9.51</v>
+        <v>0.4</v>
       </c>
       <c r="D30" s="7">
-        <v>-6.87</v>
+        <v>1.23</v>
       </c>
       <c r="E30" s="8">
-        <v>2.64</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="7">
-        <v>-3.78</v>
+        <v>-6.99</v>
       </c>
       <c r="D31" s="7">
-        <v>-3.01</v>
+        <v>-4.76</v>
       </c>
       <c r="E31" s="8">
-        <v>0.77</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="7">
-        <v>-0.9399999999999999</v>
+        <v>-3.33</v>
       </c>
       <c r="D32" s="7">
-        <v>0.4</v>
+        <v>-2.04</v>
       </c>
       <c r="E32" s="8">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="7">
-        <v>-7.24</v>
+        <v>-0.29</v>
       </c>
       <c r="D33" s="7">
-        <v>-6.99</v>
+        <v>0.3</v>
       </c>
       <c r="E33" s="8">
-        <v>0.25</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" s="7">
-        <v>-3</v>
+        <v>-1.79</v>
       </c>
       <c r="D34" s="7">
-        <v>-3.33</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-0.33</v>
+        <v>-1.5</v>
+      </c>
+      <c r="E34" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" s="7">
-        <v>-0.1</v>
+        <v>-2.43</v>
       </c>
       <c r="D35" s="7">
-        <v>-0.29</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-0.19</v>
+        <v>-1.48</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.95</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="7">
-        <v>-3.17</v>
+        <v>-0.9</v>
       </c>
       <c r="D36" s="7">
-        <v>-1.79</v>
+        <v>-0.47</v>
       </c>
       <c r="E36" s="8">
-        <v>1.38</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="7">
-        <v>-2.42</v>
+        <v>-2.48</v>
       </c>
       <c r="D37" s="7">
-        <v>-2.43</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.01</v>
+        <v>-1.18</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.3</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="7">
-        <v>-1.8</v>
+        <v>0.58</v>
       </c>
       <c r="D38" s="7">
-        <v>-0.9</v>
+        <v>0.62</v>
       </c>
       <c r="E38" s="8">
-        <v>0.9</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="7">
-        <v>-2.39</v>
+        <v>-0.23</v>
       </c>
       <c r="D39" s="7">
-        <v>-2.48</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-0.09</v>
+        <v>-0.04</v>
+      </c>
+      <c r="E39" s="8">
+        <v>0.19</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="7">
-        <v>-0.42</v>
+        <v>0.84</v>
       </c>
       <c r="D40" s="7">
-        <v>0.58</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1</v>
+        <v>-0.13</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-0.97</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="7">
-        <v>-1.69</v>
+        <v>-2.37</v>
       </c>
       <c r="D41" s="7">
-        <v>-0.23</v>
+        <v>-1.15</v>
       </c>
       <c r="E41" s="8">
-        <v>1.46</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="7">
-        <v>-2.66</v>
+        <v>-1.65</v>
       </c>
       <c r="D42" s="7">
-        <v>0.84</v>
+        <v>-0.68</v>
       </c>
       <c r="E42" s="8">
-        <v>3.5</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="7">
-        <v>-3.89</v>
+        <v>0.44</v>
       </c>
       <c r="D43" s="7">
-        <v>-2.37</v>
+        <v>1.23</v>
       </c>
       <c r="E43" s="8">
-        <v>1.52</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="7">
-        <v>-2.57</v>
+        <v>-3.98</v>
       </c>
       <c r="D44" s="7">
-        <v>-1.65</v>
+        <v>-1.9</v>
       </c>
       <c r="E44" s="8">
-        <v>0.92</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="7">
-        <v>-1.66</v>
+        <v>-1.88</v>
       </c>
       <c r="D45" s="7">
-        <v>0.44</v>
+        <v>-1.57</v>
       </c>
       <c r="E45" s="8">
-        <v>2.1</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="7">
-        <v>-3.17</v>
+        <v>-1.27</v>
       </c>
       <c r="D46" s="7">
-        <v>-3.98</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-0.8100000000000001</v>
+        <v>-1</v>
+      </c>
+      <c r="E46" s="8">
+        <v>0.27</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="7">
-        <v>-2.21</v>
+        <v>-0.42</v>
       </c>
       <c r="D47" s="7">
-        <v>-1.88</v>
+        <v>0.58</v>
       </c>
       <c r="E47" s="8">
-        <v>0.33</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="7">
-        <v>-1.62</v>
+        <v>-4.35</v>
       </c>
       <c r="D48" s="7">
-        <v>-1.27</v>
+        <v>-3.19</v>
       </c>
       <c r="E48" s="8">
-        <v>0.35</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="7">
-        <v>-2.73</v>
+        <v>0.05</v>
       </c>
       <c r="D49" s="7">
-        <v>-0.42</v>
+        <v>0.46</v>
       </c>
       <c r="E49" s="8">
-        <v>2.31</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C50" s="7">
-        <v>-7.82</v>
+        <v>-0.31</v>
       </c>
       <c r="D50" s="7">
-        <v>-4.35</v>
+        <v>0.58</v>
       </c>
       <c r="E50" s="8">
-        <v>3.47</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C51" s="7">
-        <v>-1.27</v>
+        <v>-6.27</v>
       </c>
       <c r="D51" s="7">
-        <v>0.05</v>
+        <v>-4.53</v>
       </c>
       <c r="E51" s="8">
-        <v>1.32</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C52" s="7">
-        <v>-2.11</v>
+        <v>-1.56</v>
       </c>
       <c r="D52" s="7">
-        <v>-0.31</v>
+        <v>-0.74</v>
       </c>
       <c r="E52" s="8">
-        <v>1.8</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C53" s="7">
-        <v>-8.699999999999999</v>
+        <v>-0.17</v>
       </c>
       <c r="D53" s="7">
-        <v>-6.27</v>
+        <v>-0.06</v>
       </c>
       <c r="E53" s="8">
-        <v>2.43</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C54" s="7">
-        <v>-0.6899999999999999</v>
+        <v>-0.09</v>
       </c>
       <c r="D54" s="7">
-        <v>-0.17</v>
+        <v>1.1</v>
       </c>
       <c r="E54" s="8">
-        <v>0.52</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="7">
-        <v>-1.09</v>
+        <v>7.81</v>
       </c>
       <c r="D55" s="7">
-        <v>-0.09</v>
+        <v>8.35</v>
       </c>
       <c r="E55" s="8">
-        <v>1</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="7">
-        <v>7.03</v>
+        <v>-8.16</v>
       </c>
       <c r="D56" s="7">
-        <v>7.81</v>
+        <v>-7.62</v>
       </c>
       <c r="E56" s="8">
-        <v>0.78</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="7">
-        <v>-8.609999999999999</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="D57" s="7">
-        <v>-8.16</v>
+        <v>9.42</v>
       </c>
       <c r="E57" s="8">
-        <v>0.45</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="7">
-        <v>8.44</v>
+        <v>-19.34</v>
       </c>
       <c r="D58" s="7">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="E58" s="8">
-        <v>0.7</v>
+        <v>-20.03</v>
+      </c>
+      <c r="E58" s="9">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="7">
-        <v>-18.89</v>
+        <v>-2.48</v>
       </c>
       <c r="D59" s="7">
-        <v>-19.34</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-0.45</v>
+        <v>-2.35</v>
+      </c>
+      <c r="E59" s="8">
+        <v>0.13</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="7">
-        <v>-2.62</v>
+        <v>-17.3</v>
       </c>
       <c r="D60" s="7">
-        <v>-2.48</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.14</v>
+        <v>-20.26</v>
+      </c>
+      <c r="E60" s="9">
+        <v>-2.96</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="7">
-        <v>-15.22</v>
+        <v>0.05</v>
       </c>
       <c r="D61" s="7">
-        <v>-17.3</v>
-      </c>
-      <c r="E61" s="9">
-        <v>-2.08</v>
+        <v>0.87</v>
+      </c>
+      <c r="E61" s="8">
+        <v>0.82</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="7">
-        <v>-0.7</v>
+        <v>-5.43</v>
       </c>
       <c r="D62" s="7">
-        <v>0.05</v>
+        <v>-3.55</v>
       </c>
       <c r="E62" s="8">
-        <v>0.75</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="7">
-        <v>-6.55</v>
+        <v>32.1</v>
       </c>
       <c r="D63" s="7">
-        <v>-5.43</v>
+        <v>33.74</v>
       </c>
       <c r="E63" s="8">
-        <v>1.12</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="7">
-        <v>31.09</v>
+        <v>1.75</v>
       </c>
       <c r="D64" s="7">
-        <v>32.1</v>
-      </c>
-      <c r="E64" s="8">
-        <v>1.01</v>
+        <v>1.04</v>
+      </c>
+      <c r="E64" s="9">
+        <v>-0.71</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="7">
-        <v>0.92</v>
+        <v>20.1</v>
       </c>
       <c r="D65" s="7">
-        <v>1.75</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0.83</v>
+        <v>18.42</v>
+      </c>
+      <c r="E65" s="9">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C66" s="7">
-        <v>20.13</v>
+        <v>20.53</v>
       </c>
       <c r="D66" s="7">
-        <v>20.1</v>
-      </c>
-      <c r="E66" s="9">
-        <v>-0.03</v>
+        <v>20.74</v>
+      </c>
+      <c r="E66" s="8">
+        <v>0.21</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C67" s="7">
-        <v>19.58</v>
+        <v>-4.54</v>
       </c>
       <c r="D67" s="7">
-        <v>20.53</v>
+        <v>-4.48</v>
       </c>
       <c r="E67" s="8">
-        <v>0.95</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="7">
-        <v>-6.19</v>
+        <v>-7.2</v>
       </c>
       <c r="D68" s="7">
-        <v>-4.54</v>
+        <v>-7.13</v>
       </c>
       <c r="E68" s="8">
-        <v>1.65</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C69" s="7">
-        <v>-6.76</v>
+        <v>3.04</v>
       </c>
       <c r="D69" s="7">
-        <v>-7.2</v>
+        <v>2.86</v>
       </c>
       <c r="E69" s="9">
-        <v>-0.44</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C70" s="7">
-        <v>3.61</v>
+        <v>1.54</v>
       </c>
       <c r="D70" s="7">
-        <v>3.04</v>
-      </c>
-      <c r="E70" s="9">
-        <v>-0.57</v>
+        <v>2.05</v>
+      </c>
+      <c r="E70" s="8">
+        <v>0.51</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="7">
-        <v>0.63</v>
+        <v>-5.83</v>
       </c>
       <c r="D71" s="7">
-        <v>1.54</v>
+        <v>-4.87</v>
       </c>
       <c r="E71" s="8">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="7">
-        <v>-6</v>
+        <v>-1.62</v>
       </c>
       <c r="D72" s="7">
-        <v>-5.83</v>
+        <v>-1.38</v>
       </c>
       <c r="E72" s="8">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="7">
-        <v>-1.68</v>
+        <v>-7.6</v>
       </c>
       <c r="D73" s="7">
-        <v>-1.62</v>
+        <v>-6.84</v>
       </c>
       <c r="E73" s="8">
-        <v>0.06</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="7">
-        <v>-7.59</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="D74" s="7">
-        <v>-7.6</v>
+        <v>-8.26</v>
       </c>
       <c r="E74" s="9">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="7">
-        <v>-8.07</v>
+        <v>-4.75</v>
       </c>
       <c r="D75" s="7">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E75" s="9">
-        <v>-0.15</v>
+        <v>-3.49</v>
+      </c>
+      <c r="E75" s="8">
+        <v>1.26</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="7">
-        <v>-4.33</v>
+        <v>2.42</v>
       </c>
       <c r="D76" s="7">
-        <v>-4.75</v>
-      </c>
-      <c r="E76" s="9">
-        <v>-0.42</v>
+        <v>5.21</v>
+      </c>
+      <c r="E76" s="8">
+        <v>2.79</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="7">
-        <v>0.97</v>
+        <v>-1.29</v>
       </c>
       <c r="D77" s="7">
-        <v>2.42</v>
+        <v>-0.57</v>
       </c>
       <c r="E77" s="8">
-        <v>1.45</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="7">
-        <v>-2.34</v>
+        <v>-5.58</v>
       </c>
       <c r="D78" s="7">
-        <v>-1.29</v>
+        <v>-4.63</v>
       </c>
       <c r="E78" s="8">
-        <v>1.05</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="7">
-        <v>-5.93</v>
+        <v>1.27</v>
       </c>
       <c r="D79" s="7">
-        <v>-5.58</v>
+        <v>2.53</v>
       </c>
       <c r="E79" s="8">
-        <v>0.35</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="7">
-        <v>0.62</v>
+        <v>-1.17</v>
       </c>
       <c r="D80" s="7">
-        <v>1.27</v>
+        <v>0.24</v>
       </c>
       <c r="E80" s="8">
-        <v>0.65</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="7">
-        <v>-2.09</v>
+        <v>-6.21</v>
       </c>
       <c r="D81" s="7">
-        <v>-1.17</v>
+        <v>-5.71</v>
       </c>
       <c r="E81" s="8">
-        <v>0.92</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="7">
-        <v>-6.16</v>
+        <v>-5.79</v>
       </c>
       <c r="D82" s="7">
-        <v>-6.21</v>
-      </c>
-      <c r="E82" s="9">
-        <v>-0.05</v>
+        <v>-4.58</v>
+      </c>
+      <c r="E82" s="8">
+        <v>1.21</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="7">
-        <v>-5.02</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="D83" s="7">
-        <v>-5.79</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="E83" s="9">
-        <v>-0.77</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="7">
-        <v>8.279999999999999</v>
+        <v>1.71</v>
       </c>
       <c r="D84" s="7">
-        <v>9.460000000000001</v>
+        <v>3.98</v>
       </c>
       <c r="E84" s="8">
-        <v>1.18</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="7">
-        <v>0.95</v>
+        <v>-3.17</v>
       </c>
       <c r="D85" s="7">
-        <v>1.71</v>
+        <v>-1.6</v>
       </c>
       <c r="E85" s="8">
-        <v>0.76</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C86" s="7">
-        <v>-2.82</v>
+        <v>6.27</v>
       </c>
       <c r="D86" s="7">
-        <v>-3.17</v>
+        <v>6.03</v>
       </c>
       <c r="E86" s="9">
-        <v>-0.35</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C87" s="7">
-        <v>5.66</v>
+        <v>-2.64</v>
       </c>
       <c r="D87" s="7">
-        <v>6.27</v>
+        <v>-2.46</v>
       </c>
       <c r="E87" s="8">
-        <v>0.61</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C88" s="7">
-        <v>-3.78</v>
+        <v>-3.95</v>
       </c>
       <c r="D88" s="7">
-        <v>-2.64</v>
+        <v>-1.98</v>
       </c>
       <c r="E88" s="8">
-        <v>1.14</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C89" s="7">
-        <v>-3.82</v>
+        <v>-3.08</v>
       </c>
       <c r="D89" s="7">
-        <v>-3.95</v>
-      </c>
-      <c r="E89" s="9">
-        <v>-0.13</v>
+        <v>-2.16</v>
+      </c>
+      <c r="E89" s="8">
+        <v>0.92</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C90" s="7">
-        <v>-2.18</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="D90" s="7">
-        <v>-3.08</v>
+        <v>-8.5</v>
       </c>
       <c r="E90" s="9">
-        <v>-0.9</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="7">
-        <v>-9.289999999999999</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="D91" s="7">
-        <v>-8.390000000000001</v>
+        <v>-8.92</v>
       </c>
       <c r="E91" s="8">
-        <v>0.9</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="7">
-        <v>-10.1</v>
+        <v>-9.58</v>
       </c>
       <c r="D92" s="7">
-        <v>-9.539999999999999</v>
+        <v>-9.32</v>
       </c>
       <c r="E92" s="8">
-        <v>0.5600000000000001</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="7">
-        <v>-10.11</v>
+        <v>-10</v>
       </c>
       <c r="D93" s="7">
-        <v>-9.58</v>
+        <v>-9.06</v>
       </c>
       <c r="E93" s="8">
-        <v>0.53</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="7">
-        <v>-10.48</v>
+        <v>-19.99</v>
       </c>
       <c r="D94" s="7">
-        <v>-10</v>
-      </c>
-      <c r="E94" s="8">
-        <v>0.48</v>
+        <v>-20.18</v>
+      </c>
+      <c r="E94" s="9">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="7">
-        <v>-20.02</v>
+        <v>-11.05</v>
       </c>
       <c r="D95" s="7">
-        <v>-19.99</v>
+        <v>-10.38</v>
       </c>
       <c r="E95" s="8">
-        <v>0.03</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="7">
-        <v>-11.25</v>
+        <v>-26.17</v>
       </c>
       <c r="D96" s="7">
-        <v>-11.05</v>
-      </c>
-      <c r="E96" s="8">
-        <v>0.2</v>
+        <v>-26.93</v>
+      </c>
+      <c r="E96" s="9">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="7">
-        <v>-26.34</v>
+        <v>-5.02</v>
       </c>
       <c r="D97" s="7">
-        <v>-26.17</v>
+        <v>-4.4</v>
       </c>
       <c r="E97" s="8">
-        <v>0.17</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="7">
-        <v>-6.28</v>
+        <v>-8.16</v>
       </c>
       <c r="D98" s="7">
-        <v>-5.02</v>
+        <v>-7.11</v>
       </c>
       <c r="E98" s="8">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="7">
-        <v>-8.779999999999999</v>
+        <v>-6.09</v>
       </c>
       <c r="D99" s="7">
-        <v>-8.16</v>
+        <v>-4.82</v>
       </c>
       <c r="E99" s="8">
-        <v>0.62</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="7">
-        <v>-7.19</v>
+        <v>-6.27</v>
       </c>
       <c r="D100" s="7">
-        <v>-6.09</v>
+        <v>-4.85</v>
       </c>
       <c r="E100" s="8">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="7">
-        <v>-7.14</v>
+        <v>-11.26</v>
       </c>
       <c r="D101" s="7">
-        <v>-6.27</v>
+        <v>-10.86</v>
       </c>
       <c r="E101" s="8">
-        <v>0.87</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="7">
-        <v>-11.81</v>
+        <v>-16.37</v>
       </c>
       <c r="D102" s="7">
-        <v>-11.26</v>
+        <v>-15.81</v>
       </c>
       <c r="E102" s="8">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="7">
-        <v>-16.23</v>
+        <v>-2.23</v>
       </c>
       <c r="D103" s="7">
-        <v>-16.37</v>
-      </c>
-      <c r="E103" s="9">
-        <v>-0.14</v>
+        <v>-1.75</v>
+      </c>
+      <c r="E103" s="8">
+        <v>0.48</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="7">
-        <v>-3.83</v>
+        <v>-13.87</v>
       </c>
       <c r="D104" s="7">
-        <v>-2.23</v>
+        <v>-12.85</v>
       </c>
       <c r="E104" s="8">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C105" s="7">
-        <v>-15.11</v>
+        <v>-12.52</v>
       </c>
       <c r="D105" s="7">
-        <v>-13.87</v>
+        <v>-11.81</v>
       </c>
       <c r="E105" s="8">
-        <v>1.24</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C106" s="7">
-        <v>-12.61</v>
+        <v>-2.43</v>
       </c>
       <c r="D106" s="7">
-        <v>-12.52</v>
+        <v>-1.93</v>
       </c>
       <c r="E106" s="8">
-        <v>0.09</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C107" s="7">
-        <v>-3.94</v>
+        <v>-7.27</v>
       </c>
       <c r="D107" s="7">
-        <v>-2.43</v>
+        <v>-6.47</v>
       </c>
       <c r="E107" s="8">
-        <v>1.51</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C108" s="7">
-        <v>-8.699999999999999</v>
+        <v>-4.5</v>
       </c>
       <c r="D108" s="7">
-        <v>-7.27</v>
+        <v>-3.7</v>
       </c>
       <c r="E108" s="8">
-        <v>1.43</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="7">
-        <v>-4.37</v>
+        <v>-6.92</v>
       </c>
       <c r="D109" s="7">
-        <v>-4.5</v>
-      </c>
-      <c r="E109" s="9">
-        <v>-0.13</v>
+        <v>-6.5</v>
+      </c>
+      <c r="E109" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C110" s="7">
-        <v>-6.52</v>
+        <v>27159.15</v>
       </c>
       <c r="D110" s="7">
-        <v>-6.92</v>
+        <v>27129</v>
       </c>
       <c r="E110" s="9">
-        <v>-0.4</v>
+        <v>-30.15</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="7">
-        <v>26893.65</v>
+        <v>9501.549999999999</v>
       </c>
       <c r="D111" s="7">
-        <v>27159.15</v>
+        <v>9566.549999999999</v>
       </c>
       <c r="E111" s="8">
-        <v>265.5</v>
+        <v>65</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="7">
-        <v>9442.15</v>
+        <v>11428</v>
       </c>
       <c r="D112" s="7">
-        <v>9501.549999999999</v>
+        <v>11460.7</v>
       </c>
       <c r="E112" s="8">
-        <v>59.4</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="7">
-        <v>11361.65</v>
+        <v>37381.75</v>
       </c>
       <c r="D113" s="7">
-        <v>11428</v>
+        <v>37773.55</v>
       </c>
       <c r="E113" s="8">
-        <v>66.34999999999999</v>
+        <v>391.8</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="7">
-        <v>37183.4</v>
+        <v>45572.7</v>
       </c>
       <c r="D114" s="7">
-        <v>37381.75</v>
-      </c>
-      <c r="E114" s="8">
-        <v>198.35</v>
+        <v>45466.8</v>
+      </c>
+      <c r="E114" s="9">
+        <v>-105.9</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="7">
-        <v>45559</v>
+        <v>25318.35</v>
       </c>
       <c r="D115" s="7">
-        <v>45572.7</v>
+        <v>25510</v>
       </c>
       <c r="E115" s="8">
-        <v>13.7</v>
+        <v>191.65</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="7">
-        <v>25262.4</v>
+        <v>29155.6</v>
       </c>
       <c r="D116" s="7">
-        <v>25318.35</v>
-      </c>
-      <c r="E116" s="8">
-        <v>55.95</v>
+        <v>28854.55</v>
+      </c>
+      <c r="E116" s="9">
+        <v>-301.05</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="7">
-        <v>29087.65</v>
+        <v>15826.65</v>
       </c>
       <c r="D117" s="7">
-        <v>29155.6</v>
+        <v>15929.65</v>
       </c>
       <c r="E117" s="8">
-        <v>67.95</v>
+        <v>103</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="7">
-        <v>15615.9</v>
+        <v>8969.299999999999</v>
       </c>
       <c r="D118" s="7">
-        <v>15826.65</v>
+        <v>9071.299999999999</v>
       </c>
       <c r="E118" s="8">
-        <v>210.75</v>
+        <v>102</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="7">
-        <v>8908.700000000001</v>
+        <v>1533.15</v>
       </c>
       <c r="D119" s="7">
-        <v>8969.299999999999</v>
+        <v>1553.75</v>
       </c>
       <c r="E119" s="8">
-        <v>60.6</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="7">
-        <v>1515.05</v>
+        <v>12858.45</v>
       </c>
       <c r="D120" s="7">
-        <v>1533.15</v>
+        <v>13052.6</v>
       </c>
       <c r="E120" s="8">
-        <v>18.1</v>
+        <v>194.15</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="7">
-        <v>12739.1</v>
+        <v>9554.35</v>
       </c>
       <c r="D121" s="7">
-        <v>12858.45</v>
+        <v>9597</v>
       </c>
       <c r="E121" s="8">
-        <v>119.35</v>
+        <v>42.65</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="7">
-        <v>9494.700000000001</v>
+        <v>8262.799999999999</v>
       </c>
       <c r="D122" s="7">
-        <v>9554.35</v>
+        <v>8317.549999999999</v>
       </c>
       <c r="E122" s="8">
-        <v>59.65</v>
+        <v>54.75</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="7">
-        <v>8275.9</v>
+        <v>26579.25</v>
       </c>
       <c r="D123" s="7">
-        <v>8262.799999999999</v>
-      </c>
-      <c r="E123" s="9">
-        <v>-13.1</v>
+        <v>26710.1</v>
+      </c>
+      <c r="E123" s="8">
+        <v>130.85</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C124" s="7">
-        <v>26146.2</v>
+        <v>834.25</v>
       </c>
       <c r="D124" s="7">
-        <v>26579.25</v>
+        <v>844.2</v>
       </c>
       <c r="E124" s="8">
-        <v>433.05</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C125" s="7">
-        <v>822.3</v>
+        <v>29833.2</v>
       </c>
       <c r="D125" s="7">
-        <v>834.25</v>
+        <v>30073.1</v>
       </c>
       <c r="E125" s="8">
-        <v>11.95</v>
+        <v>239.9</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C126" s="7">
-        <v>29802.35</v>
+        <v>16529.15</v>
       </c>
       <c r="D126" s="7">
-        <v>29833.2</v>
+        <v>16613.9</v>
       </c>
       <c r="E126" s="8">
-        <v>30.85</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C127" s="7">
-        <v>16274.65</v>
+        <v>9271.9</v>
       </c>
       <c r="D127" s="7">
-        <v>16529.15</v>
+        <v>9351.700000000001</v>
       </c>
       <c r="E127" s="8">
-        <v>254.5</v>
+        <v>79.8</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C128" s="7">
-        <v>9129.1</v>
+        <v>10857.35</v>
       </c>
       <c r="D128" s="7">
-        <v>9271.9</v>
+        <v>10948.7</v>
       </c>
       <c r="E128" s="8">
-        <v>142.8</v>
+        <v>91.34999999999999</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C129" s="7">
-        <v>10872.45</v>
+        <v>27169.2</v>
       </c>
       <c r="D129" s="7">
-        <v>10857.35</v>
-      </c>
-      <c r="E129" s="9">
-        <v>-15.1</v>
+        <v>27290</v>
+      </c>
+      <c r="E129" s="8">
+        <v>120.8</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C130" s="7">
-        <v>27284.25</v>
+        <v>38</v>
       </c>
       <c r="D130" s="7">
-        <v>27169.2</v>
-      </c>
-      <c r="E130" s="9">
-        <v>-115.05</v>
+        <v>44</v>
+      </c>
+      <c r="E130" s="8">
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="7">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D131" s="7">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="E131" s="8">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C132" s="7">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D132" s="7">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="E132" s="8">
         <v>6</v>
@@ -5641,33 +5599,33 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C133" s="7">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D133" s="7">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E133" s="9">
-        <v>-12</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C134" s="7">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="D134" s="7">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="E134" s="9">
         <v>-6</v>
@@ -5675,416 +5633,348 @@
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C135" s="7">
-        <v>99</v>
+        <v>33.42</v>
       </c>
       <c r="D135" s="7">
-        <v>93</v>
+        <v>33.02</v>
       </c>
       <c r="E135" s="9">
-        <v>-6</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C136" s="7">
-        <v>93</v>
+        <v>35.43</v>
       </c>
       <c r="D136" s="7">
-        <v>99</v>
+        <v>40.71</v>
       </c>
       <c r="E136" s="8">
-        <v>6</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C137" s="7">
-        <v>32</v>
+        <v>32.98</v>
       </c>
       <c r="D137" s="7">
-        <v>50</v>
+        <v>35.67</v>
       </c>
       <c r="E137" s="8">
-        <v>18</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C138" s="7">
-        <v>81</v>
+        <v>34.36</v>
       </c>
       <c r="D138" s="7">
-        <v>68</v>
-      </c>
-      <c r="E138" s="9">
-        <v>-13</v>
+        <v>43.89</v>
+      </c>
+      <c r="E138" s="8">
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="7">
-        <v>26.04</v>
+        <v>36.37</v>
       </c>
       <c r="D139" s="7">
-        <v>33.42</v>
-      </c>
-      <c r="E139" s="8">
-        <v>7.38</v>
+        <v>35.35</v>
+      </c>
+      <c r="E139" s="9">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="7">
-        <v>30.16</v>
+        <v>35.36</v>
       </c>
       <c r="D140" s="7">
-        <v>35.43</v>
+        <v>41.05</v>
       </c>
       <c r="E140" s="8">
-        <v>5.27</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="7">
-        <v>27.24</v>
+        <v>39.98</v>
       </c>
       <c r="D141" s="7">
-        <v>32.98</v>
-      </c>
-      <c r="E141" s="8">
-        <v>5.74</v>
+        <v>37.41</v>
+      </c>
+      <c r="E141" s="9">
+        <v>-2.57</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="7">
-        <v>28.66</v>
+        <v>34.56</v>
       </c>
       <c r="D142" s="7">
-        <v>34.36</v>
+        <v>39.82</v>
       </c>
       <c r="E142" s="8">
-        <v>5.7</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="7">
-        <v>36.15</v>
+        <v>29.02</v>
       </c>
       <c r="D143" s="7">
-        <v>36.37</v>
+        <v>40.51</v>
       </c>
       <c r="E143" s="8">
-        <v>0.22</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="7">
-        <v>33.63</v>
+        <v>45.92</v>
       </c>
       <c r="D144" s="7">
-        <v>35.36</v>
+        <v>50.66</v>
       </c>
       <c r="E144" s="8">
-        <v>1.73</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="6" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="7">
-        <v>39.1</v>
+        <v>43.69</v>
       </c>
       <c r="D145" s="7">
-        <v>39.98</v>
+        <v>49.55</v>
       </c>
       <c r="E145" s="8">
-        <v>0.88</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="7">
-        <v>21.53</v>
+        <v>35.67</v>
       </c>
       <c r="D146" s="7">
-        <v>34.56</v>
+        <v>40.16</v>
       </c>
       <c r="E146" s="8">
-        <v>13.03</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="7">
-        <v>20.56</v>
+        <v>37.43</v>
       </c>
       <c r="D147" s="7">
-        <v>29.02</v>
+        <v>41.57</v>
       </c>
       <c r="E147" s="8">
-        <v>8.460000000000001</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="7">
-        <v>41.31</v>
+        <v>51.87</v>
       </c>
       <c r="D148" s="7">
-        <v>45.92</v>
+        <v>54.6</v>
       </c>
       <c r="E148" s="8">
-        <v>4.61</v>
+        <v>2.73</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="7">
-        <v>39.7</v>
+        <v>33.87</v>
       </c>
       <c r="D149" s="7">
-        <v>43.69</v>
+        <v>38.27</v>
       </c>
       <c r="E149" s="8">
-        <v>3.99</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="7">
-        <v>28.72</v>
+        <v>30.3</v>
       </c>
       <c r="D150" s="7">
-        <v>35.67</v>
+        <v>39.26</v>
       </c>
       <c r="E150" s="8">
-        <v>6.95</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="6" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="7">
-        <v>38.03</v>
+        <v>50.42</v>
       </c>
       <c r="D151" s="7">
-        <v>37.43</v>
-      </c>
-      <c r="E151" s="9">
-        <v>-0.6</v>
+        <v>53.53</v>
+      </c>
+      <c r="E151" s="8">
+        <v>3.11</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="6" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C152" s="7">
-        <v>40.92</v>
+        <v>37.82</v>
       </c>
       <c r="D152" s="7">
-        <v>51.87</v>
+        <v>41.24</v>
       </c>
       <c r="E152" s="8">
-        <v>10.95</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C153" s="7">
-        <v>28.16</v>
+        <v>32.72</v>
       </c>
       <c r="D153" s="7">
-        <v>33.87</v>
+        <v>41.34</v>
       </c>
       <c r="E153" s="8">
-        <v>5.71</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C154" s="7">
-        <v>29.05</v>
+        <v>41.69</v>
       </c>
       <c r="D154" s="7">
-        <v>30.3</v>
+        <v>44.87</v>
       </c>
       <c r="E154" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C155" s="7">
-        <v>39.03</v>
-      </c>
-      <c r="D155" s="7">
-        <v>50.42</v>
-      </c>
-      <c r="E155" s="8">
-        <v>11.39</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C156" s="7">
-        <v>31.18</v>
-      </c>
-      <c r="D156" s="7">
-        <v>37.82</v>
-      </c>
-      <c r="E156" s="8">
-        <v>6.64</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
-      <c r="A157" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C157" s="7">
-        <v>33.47</v>
-      </c>
-      <c r="D157" s="7">
-        <v>32.72</v>
-      </c>
-      <c r="E157" s="9">
-        <v>-0.75</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
-      <c r="A158" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C158" s="7">
-        <v>43.93</v>
-      </c>
-      <c r="D158" s="7">
-        <v>41.69</v>
-      </c>
-      <c r="E158" s="9">
-        <v>-2.24</v>
+        <v>3.18</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6108,28 +5998,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6137,22 +6027,22 @@
         <v>78</v>
       </c>
       <c r="B2" s="12">
-        <v>39.24</v>
+        <v>43.24</v>
       </c>
       <c r="C2" s="13">
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>37.6</v>
+        <v>42.1</v>
       </c>
       <c r="E2" s="12">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F2" s="12">
-        <v>-3.5</v>
+        <v>-2.5</v>
       </c>
       <c r="G2" s="12">
-        <v>-1.9</v>
+        <v>-1</v>
       </c>
       <c r="H2" s="12">
         <v>53.1</v>
@@ -6278,13 +6168,13 @@
         <v>52</v>
       </c>
       <c r="G1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="I1" s="14" t="s">
         <v>46</v>
-      </c>
-      <c r="I1" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="J1" s="14" t="s">
         <v>41</v>
@@ -6292,34 +6182,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.2736</v>
+        <v>0.2865</v>
       </c>
       <c r="B2" s="15">
-        <v>0.258</v>
+        <v>0.2792</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2128</v>
+        <v>0.2163</v>
       </c>
       <c r="D2" s="15">
-        <v>0.1986</v>
+        <v>0.2061</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1774</v>
+        <v>0.1974</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1507</v>
+        <v>0.1586</v>
       </c>
       <c r="G2" s="15">
-        <v>0.1311</v>
+        <v>0.1558</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1271</v>
+        <v>0.1365</v>
       </c>
       <c r="I2" s="15">
-        <v>0.1208</v>
+        <v>0.1323</v>
       </c>
       <c r="J2" s="15">
-        <v>0.1176</v>
+        <v>0.1225</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6345,45 +6235,45 @@
         <v>42</v>
       </c>
       <c r="H3" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="J3" s="14" t="s">
         <v>47</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.1102</v>
+        <v>0.1195</v>
       </c>
       <c r="B4" s="15">
-        <v>0.09519999999999999</v>
+        <v>0.0964</v>
       </c>
       <c r="C4" s="15">
-        <v>0.0659</v>
+        <v>0.0707</v>
       </c>
       <c r="D4" s="15">
-        <v>0.065</v>
+        <v>0.0702</v>
       </c>
       <c r="E4" s="15">
-        <v>0.0399</v>
+        <v>0.0649</v>
       </c>
       <c r="F4" s="15">
-        <v>0.0377</v>
+        <v>0.0416</v>
       </c>
       <c r="G4" s="15">
-        <v>0.0224</v>
+        <v>0.0201</v>
       </c>
       <c r="H4" s="15">
-        <v>-0.0394</v>
+        <v>-0.0214</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.04480000000000001</v>
+        <v>-0.0401</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.052</v>
+        <v>-0.0414</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="107">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,13 +289,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>47.9 → 56.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>56.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -381,14 +387,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -421,13 +427,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1025,10 +1031,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>27086.3</v>
+        <v>27157.55</v>
       </c>
       <c r="E2">
-        <v>-0.24</v>
+        <v>0.26</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1037,43 +1043,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-8.640000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="I2">
-        <v>13.95</v>
+        <v>14.25</v>
       </c>
       <c r="J2">
-        <v>1.23</v>
+        <v>0.98</v>
       </c>
       <c r="K2">
-        <v>-7.56</v>
+        <v>-6.68</v>
       </c>
       <c r="L2">
-        <v>2.23</v>
+        <v>2.93</v>
       </c>
       <c r="M2">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="N2">
-        <v>21.37</v>
+        <v>21.23</v>
       </c>
       <c r="O2">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="Q2">
-        <v>27083.84</v>
+        <v>27136.62</v>
       </c>
       <c r="R2">
-        <v>27848.19</v>
+        <v>27745.23</v>
       </c>
       <c r="S2">
-        <v>28132.05</v>
+        <v>28144.25</v>
       </c>
       <c r="T2">
-        <v>27122.92</v>
+        <v>27118.74</v>
       </c>
       <c r="U2">
-        <v>-0.14</v>
+        <v>0.14</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1085,34 +1091,34 @@
         <v>79</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z2">
-        <v>32.67</v>
+        <v>34.9</v>
       </c>
       <c r="AA2">
-        <v>-402.28</v>
+        <v>-391.23</v>
       </c>
       <c r="AB2">
-        <v>-310.28</v>
+        <v>-326.47</v>
       </c>
       <c r="AC2">
-        <v>-92</v>
+        <v>-64.76000000000001</v>
       </c>
       <c r="AD2">
-        <v>54.11</v>
+        <v>75.59</v>
       </c>
       <c r="AE2">
-        <v>41.14</v>
+        <v>56.91</v>
       </c>
       <c r="AF2">
-        <v>365.36</v>
+        <v>353.59</v>
       </c>
       <c r="AH2">
-        <v>29392.83</v>
+        <v>29176.06</v>
       </c>
       <c r="AI2">
-        <v>26303.56</v>
+        <v>26314.39</v>
       </c>
       <c r="AJ2">
         <v>28052.54</v>
@@ -1121,7 +1127,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>63.69</v>
+        <v>62.7</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1135,10 +1141,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9549.35</v>
+        <v>9646.5</v>
       </c>
       <c r="E3">
-        <v>0.06</v>
+        <v>1.02</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1147,43 +1153,43 @@
         <v>8890.35</v>
       </c>
       <c r="H3">
-        <v>-9.08</v>
+        <v>-8.16</v>
       </c>
       <c r="I3">
-        <v>7.41</v>
+        <v>8.51</v>
       </c>
       <c r="J3">
-        <v>1.51</v>
+        <v>2.16</v>
       </c>
       <c r="K3">
-        <v>-2.39</v>
+        <v>-2.04</v>
       </c>
       <c r="L3">
-        <v>-4.1</v>
+        <v>-3</v>
       </c>
       <c r="M3">
-        <v>7.28</v>
+        <v>8.24</v>
       </c>
       <c r="N3">
-        <v>11.39</v>
+        <v>11.33</v>
       </c>
       <c r="O3">
         <v>81</v>
       </c>
       <c r="Q3">
-        <v>9520.65</v>
+        <v>9561.52</v>
       </c>
       <c r="R3">
-        <v>9674.52</v>
+        <v>9663.530000000001</v>
       </c>
       <c r="S3">
-        <v>9788.860000000001</v>
+        <v>9784.559999999999</v>
       </c>
       <c r="T3">
-        <v>9765.41</v>
+        <v>9767.51</v>
       </c>
       <c r="U3">
-        <v>-2.21</v>
+        <v>-1.24</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1198,31 +1204,31 @@
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>39.97</v>
+        <v>47.65</v>
       </c>
       <c r="AA3">
-        <v>-85.48999999999999</v>
+        <v>-74.81</v>
       </c>
       <c r="AB3">
-        <v>-74.61</v>
+        <v>-74.65000000000001</v>
       </c>
       <c r="AC3">
-        <v>-10.87</v>
+        <v>-0.16</v>
       </c>
       <c r="AD3">
-        <v>62.58</v>
+        <v>73.62</v>
       </c>
       <c r="AE3">
-        <v>52.84</v>
+        <v>63.86</v>
       </c>
       <c r="AF3">
-        <v>97.41</v>
+        <v>97.42</v>
       </c>
       <c r="AH3">
-        <v>9950.059999999999</v>
+        <v>9923.969999999999</v>
       </c>
       <c r="AI3">
-        <v>9398.99</v>
+        <v>9403.09</v>
       </c>
       <c r="AJ3">
         <v>9750.9</v>
@@ -1231,7 +1237,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>34.54</v>
+        <v>30.75</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1245,10 +1251,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11487.2</v>
+        <v>11546.05</v>
       </c>
       <c r="E4">
-        <v>-0.19</v>
+        <v>0.51</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1257,43 +1263,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-9.109999999999999</v>
+        <v>-8.65</v>
       </c>
       <c r="I4">
-        <v>11.16</v>
+        <v>11.72</v>
       </c>
       <c r="J4">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="K4">
-        <v>-4.81</v>
+        <v>-3.86</v>
       </c>
       <c r="L4">
-        <v>-0.2</v>
+        <v>0.32</v>
       </c>
       <c r="M4">
-        <v>-7.18</v>
+        <v>-6.49</v>
       </c>
       <c r="N4">
-        <v>9.470000000000001</v>
+        <v>9.49</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q4">
-        <v>11449.37</v>
+        <v>11486.25</v>
       </c>
       <c r="R4">
-        <v>11629.28</v>
+        <v>11601.88</v>
       </c>
       <c r="S4">
-        <v>11820.38</v>
+        <v>11819.07</v>
       </c>
       <c r="T4">
-        <v>11617.85</v>
+        <v>11613.27</v>
       </c>
       <c r="U4">
-        <v>-1.12</v>
+        <v>-0.58</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1308,31 +1314,31 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>38.43</v>
+        <v>43.12</v>
       </c>
       <c r="AA4">
-        <v>-127.78</v>
+        <v>-116.15</v>
       </c>
       <c r="AB4">
-        <v>-120.82</v>
+        <v>-119.88</v>
       </c>
       <c r="AC4">
-        <v>-6.97</v>
+        <v>3.74</v>
       </c>
       <c r="AD4">
-        <v>91.84</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AE4">
-        <v>74.68000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="AF4">
-        <v>105.31</v>
+        <v>102.2</v>
       </c>
       <c r="AH4">
-        <v>12066.13</v>
+        <v>11980.9</v>
       </c>
       <c r="AI4">
-        <v>11192.42</v>
+        <v>11222.85</v>
       </c>
       <c r="AJ4">
         <v>11665.92</v>
@@ -1341,7 +1347,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>47.57</v>
+        <v>43.36</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1355,10 +1361,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>37727</v>
+        <v>37759.75</v>
       </c>
       <c r="E5">
-        <v>-0.24</v>
+        <v>0.09</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1367,43 +1373,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-9.17</v>
+        <v>-9.09</v>
       </c>
       <c r="I5">
-        <v>13.98</v>
+        <v>14.08</v>
       </c>
       <c r="J5">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="K5">
-        <v>-1.11</v>
+        <v>-1.5</v>
       </c>
       <c r="L5">
-        <v>-6.31</v>
+        <v>-5.38</v>
       </c>
       <c r="M5">
-        <v>7.98</v>
+        <v>7.49</v>
       </c>
       <c r="N5">
-        <v>11.91</v>
+        <v>11.52</v>
       </c>
       <c r="O5">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="Q5">
-        <v>37576.85</v>
+        <v>37692.12</v>
       </c>
       <c r="R5">
-        <v>37905.1</v>
+        <v>37877.55</v>
       </c>
       <c r="S5">
-        <v>38481</v>
+        <v>38452.13</v>
       </c>
       <c r="T5">
-        <v>37595.92</v>
+        <v>37607.02</v>
       </c>
       <c r="U5">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1418,31 +1424,31 @@
         <v>2</v>
       </c>
       <c r="Z5">
-        <v>43.21</v>
+        <v>44.01</v>
       </c>
       <c r="AA5">
-        <v>-244.44</v>
+        <v>-227.6</v>
       </c>
       <c r="AB5">
-        <v>-255.39</v>
+        <v>-249.84</v>
       </c>
       <c r="AC5">
-        <v>10.95</v>
+        <v>22.23</v>
       </c>
       <c r="AD5">
-        <v>75.40000000000001</v>
+        <v>75.59</v>
       </c>
       <c r="AE5">
-        <v>58.05</v>
+        <v>70.94</v>
       </c>
       <c r="AF5">
-        <v>379.5</v>
+        <v>368.98</v>
       </c>
       <c r="AH5">
-        <v>38571.81</v>
+        <v>38518.71</v>
       </c>
       <c r="AI5">
-        <v>37238.39</v>
+        <v>37236.38</v>
       </c>
       <c r="AJ5">
         <v>38269.93</v>
@@ -1451,7 +1457,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>20.7</v>
+        <v>18.16</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1465,10 +1471,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>45657.75</v>
+        <v>46259.35</v>
       </c>
       <c r="E6">
-        <v>-0.53</v>
+        <v>1.32</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1477,43 +1483,43 @@
         <v>44829.95</v>
       </c>
       <c r="H6">
-        <v>-19.58</v>
+        <v>-18.52</v>
       </c>
       <c r="I6">
-        <v>1.85</v>
+        <v>3.19</v>
       </c>
       <c r="J6">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="K6">
-        <v>-4.61</v>
+        <v>-2.67</v>
       </c>
       <c r="L6">
-        <v>-6.93</v>
+        <v>-5.76</v>
       </c>
       <c r="M6">
-        <v>-19.27</v>
+        <v>-18.2</v>
       </c>
       <c r="N6">
-        <v>1.92</v>
+        <v>2.17</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>45631.43</v>
+        <v>45771.5</v>
       </c>
       <c r="R6">
-        <v>45962.73</v>
+        <v>45890.35</v>
       </c>
       <c r="S6">
-        <v>47605.16</v>
+        <v>47559.85</v>
       </c>
       <c r="T6">
-        <v>50011.36</v>
+        <v>49965.15</v>
       </c>
       <c r="U6">
-        <v>-8.710000000000001</v>
+        <v>-7.42</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1528,31 +1534,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>39.82</v>
+        <v>48.37</v>
       </c>
       <c r="AA6">
-        <v>-646.78</v>
+        <v>-554.74</v>
       </c>
       <c r="AB6">
-        <v>-751.03</v>
+        <v>-711.77</v>
       </c>
       <c r="AC6">
-        <v>104.25</v>
+        <v>157.03</v>
       </c>
       <c r="AD6">
-        <v>92.97</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="AE6">
-        <v>95.97</v>
+        <v>95.31</v>
       </c>
       <c r="AF6">
-        <v>527.62</v>
+        <v>535.53</v>
       </c>
       <c r="AH6">
-        <v>47476.51</v>
+        <v>47173.9</v>
       </c>
       <c r="AI6">
-        <v>44448.96</v>
+        <v>44606.8</v>
       </c>
       <c r="AJ6">
         <v>46607.06</v>
@@ -1561,7 +1567,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>44.06</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1575,10 +1581,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25417.95</v>
+        <v>25564.85</v>
       </c>
       <c r="E7">
-        <v>-0.42</v>
+        <v>0.58</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1587,43 +1593,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-10.7</v>
+        <v>-10.18</v>
       </c>
       <c r="I7">
-        <v>8.06</v>
+        <v>8.69</v>
       </c>
       <c r="J7">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="K7">
-        <v>-3</v>
+        <v>-2.27</v>
       </c>
       <c r="L7">
-        <v>-3.46</v>
+        <v>-4.38</v>
       </c>
       <c r="M7">
-        <v>-3.59</v>
+        <v>-3.14</v>
       </c>
       <c r="N7">
-        <v>6.97</v>
+        <v>6.61</v>
       </c>
       <c r="O7">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Q7">
-        <v>25406.68</v>
+        <v>25467.17</v>
       </c>
       <c r="R7">
-        <v>25773.46</v>
+        <v>25739.36</v>
       </c>
       <c r="S7">
-        <v>26261.69</v>
+        <v>26242.25</v>
       </c>
       <c r="T7">
-        <v>26515.44</v>
+        <v>26504.19</v>
       </c>
       <c r="U7">
-        <v>-4.14</v>
+        <v>-3.54</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1638,31 +1644,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>39.26</v>
+        <v>43.72</v>
       </c>
       <c r="AA7">
-        <v>-256.16</v>
+        <v>-235.66</v>
       </c>
       <c r="AB7">
-        <v>-248.21</v>
+        <v>-245.7</v>
       </c>
       <c r="AC7">
-        <v>-7.94</v>
+        <v>10.04</v>
       </c>
       <c r="AD7">
-        <v>79.70999999999999</v>
+        <v>89.22</v>
       </c>
       <c r="AE7">
-        <v>65.27</v>
+        <v>78.95</v>
       </c>
       <c r="AF7">
-        <v>279</v>
+        <v>271.68</v>
       </c>
       <c r="AH7">
-        <v>26576.45</v>
+        <v>26515.15</v>
       </c>
       <c r="AI7">
-        <v>24970.47</v>
+        <v>24963.56</v>
       </c>
       <c r="AJ7">
         <v>26066.31</v>
@@ -1671,7 +1677,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>23.61</v>
+        <v>21.53</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1685,10 +1691,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>28582.1</v>
+        <v>28334.05</v>
       </c>
       <c r="E8">
-        <v>-0.86</v>
+        <v>-0.87</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1697,43 +1703,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-27.62</v>
+        <v>-28.25</v>
       </c>
       <c r="I8">
-        <v>10.91</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="J8">
-        <v>-3.29</v>
+        <v>-2.59</v>
       </c>
       <c r="K8">
-        <v>-6.39</v>
+        <v>-7.4</v>
       </c>
       <c r="L8">
-        <v>5.81</v>
+        <v>2.78</v>
       </c>
       <c r="M8">
-        <v>-20.85</v>
+        <v>-21.08</v>
       </c>
       <c r="N8">
-        <v>-4.73</v>
+        <v>-5.1</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>28902.16</v>
+        <v>28751.44</v>
       </c>
       <c r="R8">
-        <v>29929.48</v>
+        <v>29807.59</v>
       </c>
       <c r="S8">
-        <v>30188.21</v>
+        <v>30180.39</v>
       </c>
       <c r="T8">
-        <v>31763.01</v>
+        <v>31716.93</v>
       </c>
       <c r="U8">
-        <v>-10.01</v>
+        <v>-10.67</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1748,43 +1754,40 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>35.07</v>
+        <v>33.03</v>
       </c>
       <c r="AA8">
-        <v>-462.66</v>
+        <v>-505.74</v>
       </c>
       <c r="AB8">
-        <v>-293.34</v>
+        <v>-335.82</v>
       </c>
       <c r="AC8">
-        <v>-169.32</v>
+        <v>-169.92</v>
       </c>
       <c r="AD8">
-        <v>9.210000000000001</v>
+        <v>5.13</v>
       </c>
       <c r="AE8">
-        <v>14.06</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AF8">
-        <v>659.5</v>
-      </c>
-      <c r="AG8">
-        <v>-100</v>
+        <v>641.34</v>
       </c>
       <c r="AH8">
-        <v>31896.11</v>
+        <v>31854.93</v>
       </c>
       <c r="AI8">
-        <v>27962.85</v>
+        <v>27760.26</v>
       </c>
       <c r="AJ8">
-        <v>30556.87</v>
+        <v>30355.42</v>
       </c>
       <c r="AK8" t="s">
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>26.84</v>
+        <v>27.76</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1798,10 +1801,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15890.5</v>
+        <v>16017.7</v>
       </c>
       <c r="E9">
-        <v>-0.34</v>
+        <v>0.8</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1810,31 +1813,31 @@
         <v>15584.65</v>
       </c>
       <c r="H9">
-        <v>-4.63</v>
+        <v>-3.87</v>
       </c>
       <c r="I9">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="J9">
-        <v>1.96</v>
+        <v>2.57</v>
       </c>
       <c r="K9">
-        <v>-3.76</v>
+        <v>-2.99</v>
       </c>
       <c r="L9">
-        <v>-0.41</v>
+        <v>0.83</v>
       </c>
       <c r="N9">
-        <v>5.3</v>
+        <v>8.26</v>
       </c>
       <c r="Q9">
-        <v>15841.57</v>
+        <v>15921.93</v>
       </c>
       <c r="R9">
-        <v>16176.66</v>
+        <v>16148.57</v>
       </c>
       <c r="S9">
-        <v>16251.05</v>
+        <v>16254.4</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1846,31 +1849,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>38.7</v>
+        <v>45.11</v>
       </c>
       <c r="AA9">
-        <v>-145.43</v>
+        <v>-132.15</v>
       </c>
       <c r="AB9">
-        <v>-108.49</v>
+        <v>-113.22</v>
       </c>
       <c r="AC9">
-        <v>-36.95</v>
+        <v>-18.93</v>
       </c>
       <c r="AD9">
-        <v>70.36</v>
+        <v>88</v>
       </c>
       <c r="AE9">
-        <v>50.58</v>
+        <v>70.23</v>
       </c>
       <c r="AF9">
-        <v>159.55</v>
+        <v>157.26</v>
       </c>
       <c r="AH9">
-        <v>16805.84</v>
+        <v>16751.65</v>
       </c>
       <c r="AI9">
-        <v>15547.48</v>
+        <v>15545.5</v>
       </c>
       <c r="AJ9">
         <v>16050.69</v>
@@ -1879,7 +1882,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>44.69</v>
+        <v>42.77</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1893,10 +1896,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9020.799999999999</v>
+        <v>9095.049999999999</v>
       </c>
       <c r="E10">
-        <v>-0.41</v>
+        <v>0.82</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1905,43 +1908,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-7.63</v>
+        <v>-6.87</v>
       </c>
       <c r="I10">
-        <v>5.37</v>
+        <v>6.24</v>
       </c>
       <c r="J10">
-        <v>1.24</v>
+        <v>2.09</v>
       </c>
       <c r="K10">
-        <v>-3.51</v>
+        <v>-2.65</v>
       </c>
       <c r="L10">
-        <v>-4.65</v>
+        <v>-3.89</v>
       </c>
       <c r="M10">
-        <v>-0.59</v>
+        <v>-0.03</v>
       </c>
       <c r="N10">
-        <v>12.82</v>
+        <v>12.62</v>
       </c>
       <c r="O10">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q10">
-        <v>9005.66</v>
+        <v>9042.93</v>
       </c>
       <c r="R10">
-        <v>9138.76</v>
+        <v>9123.450000000001</v>
       </c>
       <c r="S10">
-        <v>9289.91</v>
+        <v>9284.790000000001</v>
       </c>
       <c r="T10">
-        <v>9312.83</v>
+        <v>9310.15</v>
       </c>
       <c r="U10">
-        <v>-3.14</v>
+        <v>-2.31</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1956,31 +1959,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>37.12</v>
+        <v>44.59</v>
       </c>
       <c r="AA10">
-        <v>-88.25</v>
+        <v>-79.68000000000001</v>
       </c>
       <c r="AB10">
-        <v>-82.95</v>
+        <v>-82.3</v>
       </c>
       <c r="AC10">
-        <v>-5.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD10">
         <v>92.86</v>
       </c>
       <c r="AE10">
-        <v>74.45999999999999</v>
+        <v>88.97</v>
       </c>
       <c r="AF10">
-        <v>83.29000000000001</v>
+        <v>82.83</v>
       </c>
       <c r="AH10">
-        <v>9388.879999999999</v>
+        <v>9341.299999999999</v>
       </c>
       <c r="AI10">
-        <v>8888.65</v>
+        <v>8905.6</v>
       </c>
       <c r="AJ10">
         <v>9179.950000000001</v>
@@ -1989,7 +1992,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>50.03</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2003,10 +2006,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1574.7</v>
+        <v>1566.85</v>
       </c>
       <c r="E11">
-        <v>1.21</v>
+        <v>-0.5</v>
       </c>
       <c r="F11">
         <v>1632.5</v>
@@ -2015,43 +2018,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-3.54</v>
+        <v>-4.02</v>
       </c>
       <c r="I11">
-        <v>25.64</v>
+        <v>25.01</v>
       </c>
       <c r="J11">
-        <v>4.71</v>
+        <v>3.42</v>
       </c>
       <c r="K11">
-        <v>-2.88</v>
+        <v>-2.27</v>
       </c>
       <c r="L11">
-        <v>3.98</v>
+        <v>3.13</v>
       </c>
       <c r="M11">
-        <v>-2.86</v>
+        <v>-2.9</v>
       </c>
       <c r="N11">
-        <v>-6.51</v>
+        <v>-6.28</v>
       </c>
       <c r="O11">
         <v>56</v>
       </c>
       <c r="Q11">
-        <v>1546.52</v>
+        <v>1556.88</v>
       </c>
       <c r="R11">
-        <v>1554.79</v>
+        <v>1552.64</v>
       </c>
       <c r="S11">
-        <v>1557.39</v>
+        <v>1558.51</v>
       </c>
       <c r="T11">
-        <v>1452.36</v>
+        <v>1452.87</v>
       </c>
       <c r="U11">
-        <v>8.42</v>
+        <v>7.84</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2066,31 +2069,31 @@
         <v>2</v>
       </c>
       <c r="Z11">
-        <v>55.25</v>
+        <v>53.24</v>
       </c>
       <c r="AA11">
-        <v>-4.95</v>
+        <v>-3.08</v>
       </c>
       <c r="AB11">
-        <v>-6.65</v>
+        <v>-5.93</v>
       </c>
       <c r="AC11">
-        <v>1.69</v>
+        <v>2.86</v>
       </c>
       <c r="AD11">
-        <v>100</v>
+        <v>96.04000000000001</v>
       </c>
       <c r="AE11">
-        <v>76.95999999999999</v>
+        <v>91.87</v>
       </c>
       <c r="AF11">
-        <v>30.55</v>
+        <v>29.73</v>
       </c>
       <c r="AH11">
-        <v>1617.74</v>
+        <v>1610.36</v>
       </c>
       <c r="AI11">
-        <v>1491.85</v>
+        <v>1494.91</v>
       </c>
       <c r="AJ11">
         <v>1604.15</v>
@@ -2099,7 +2102,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>36.16</v>
+        <v>32.97</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2113,10 +2116,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>12990.35</v>
+        <v>13302.35</v>
       </c>
       <c r="E12">
-        <v>0.14</v>
+        <v>2.4</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2125,43 +2128,43 @@
         <v>9888.25</v>
       </c>
       <c r="H12">
-        <v>-5.31</v>
+        <v>-3.03</v>
       </c>
       <c r="I12">
-        <v>31.37</v>
+        <v>34.53</v>
       </c>
       <c r="J12">
-        <v>2.54</v>
+        <v>4.42</v>
       </c>
       <c r="K12">
-        <v>-0.54</v>
+        <v>-0.59</v>
       </c>
       <c r="L12">
-        <v>2.54</v>
+        <v>5.42</v>
       </c>
       <c r="M12">
-        <v>31.43</v>
+        <v>34.49</v>
       </c>
       <c r="N12">
-        <v>18.65</v>
+        <v>18.83</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>12922.64</v>
+        <v>13035.29</v>
       </c>
       <c r="R12">
-        <v>13159.29</v>
+        <v>13155.79</v>
       </c>
       <c r="S12">
-        <v>12958.31</v>
+        <v>12970.81</v>
       </c>
       <c r="T12">
-        <v>12283.12</v>
+        <v>12297.86</v>
       </c>
       <c r="U12">
-        <v>5.76</v>
+        <v>8.17</v>
       </c>
       <c r="V12" t="s">
         <v>80</v>
@@ -2176,31 +2179,31 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>47.91</v>
+        <v>56.5</v>
       </c>
       <c r="AA12">
-        <v>-34.23</v>
+        <v>-9.43</v>
       </c>
       <c r="AB12">
-        <v>4.83</v>
+        <v>1.98</v>
       </c>
       <c r="AC12">
-        <v>-39.06</v>
+        <v>-11.4</v>
       </c>
       <c r="AD12">
-        <v>50.89</v>
+        <v>61.61</v>
       </c>
       <c r="AE12">
-        <v>40.39</v>
+        <v>51.36</v>
       </c>
       <c r="AF12">
-        <v>214.19</v>
+        <v>221.23</v>
       </c>
       <c r="AH12">
-        <v>13641.96</v>
+        <v>13632.94</v>
       </c>
       <c r="AI12">
-        <v>12676.62</v>
+        <v>12678.64</v>
       </c>
       <c r="AJ12">
         <v>13387.91</v>
@@ -2209,7 +2212,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>21.6</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2223,10 +2226,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9616.700000000001</v>
+        <v>9637.6</v>
       </c>
       <c r="E13">
-        <v>0.13</v>
+        <v>0.22</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2235,43 +2238,43 @@
         <v>9428.700000000001</v>
       </c>
       <c r="H13">
-        <v>-10.68</v>
+        <v>-10.48</v>
       </c>
       <c r="I13">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="J13">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="K13">
-        <v>-1.3</v>
+        <v>-1.47</v>
       </c>
       <c r="L13">
-        <v>-5.14</v>
+        <v>-4.48</v>
       </c>
       <c r="M13">
-        <v>-0.43</v>
+        <v>-0.52</v>
       </c>
       <c r="N13">
-        <v>20.21</v>
+        <v>19.96</v>
       </c>
       <c r="O13">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Q13">
-        <v>9573.35</v>
+        <v>9601.93</v>
       </c>
       <c r="R13">
-        <v>9664.59</v>
+        <v>9656.6</v>
       </c>
       <c r="S13">
-        <v>9801.74</v>
+        <v>9796.040000000001</v>
       </c>
       <c r="T13">
-        <v>10019</v>
+        <v>10018.39</v>
       </c>
       <c r="U13">
-        <v>-4.02</v>
+        <v>-3.8</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2286,31 +2289,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>42.26</v>
+        <v>44.55</v>
       </c>
       <c r="AA13">
-        <v>-64.98999999999999</v>
+        <v>-59.23</v>
       </c>
       <c r="AB13">
-        <v>-64.8</v>
+        <v>-63.68</v>
       </c>
       <c r="AC13">
-        <v>-0.19</v>
+        <v>4.45</v>
       </c>
       <c r="AD13">
-        <v>74.78</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="AE13">
-        <v>61.5</v>
+        <v>73.62</v>
       </c>
       <c r="AF13">
-        <v>91.41</v>
+        <v>88.95</v>
       </c>
       <c r="AH13">
-        <v>9833.84</v>
+        <v>9814.139999999999</v>
       </c>
       <c r="AI13">
-        <v>9495.34</v>
+        <v>9499.059999999999</v>
       </c>
       <c r="AJ13">
         <v>9761.77</v>
@@ -2319,7 +2322,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>33.67</v>
+        <v>31.04</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2333,55 +2336,55 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8271.299999999999</v>
+        <v>8365.450000000001</v>
       </c>
       <c r="E14">
-        <v>-0.49</v>
+        <v>1.14</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
       </c>
       <c r="G14">
-        <v>7099.3</v>
+        <v>7129.65</v>
       </c>
       <c r="H14">
-        <v>-16.28</v>
+        <v>-15.33</v>
       </c>
       <c r="I14">
-        <v>16.51</v>
+        <v>17.33</v>
       </c>
       <c r="J14">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="K14">
-        <v>-4.01</v>
+        <v>-2.04</v>
       </c>
       <c r="L14">
-        <v>-3.72</v>
+        <v>-3.05</v>
       </c>
       <c r="M14">
-        <v>17.21</v>
+        <v>17.83</v>
       </c>
       <c r="N14">
-        <v>28.37</v>
+        <v>28.35</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8287.99</v>
+        <v>8305.9</v>
       </c>
       <c r="R14">
-        <v>8435.799999999999</v>
+        <v>8423.889999999999</v>
       </c>
       <c r="S14">
-        <v>8485.07</v>
+        <v>8486.219999999999</v>
       </c>
       <c r="T14">
-        <v>8591.799999999999</v>
+        <v>8590.950000000001</v>
       </c>
       <c r="U14">
-        <v>-3.73</v>
+        <v>-2.62</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2396,31 +2399,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>39.06</v>
+        <v>46.25</v>
       </c>
       <c r="AA14">
-        <v>-76.98</v>
+        <v>-69.67</v>
       </c>
       <c r="AB14">
-        <v>-59.25</v>
+        <v>-61.33</v>
       </c>
       <c r="AC14">
-        <v>-17.73</v>
+        <v>-8.34</v>
       </c>
       <c r="AD14">
-        <v>57.28</v>
+        <v>68.17</v>
       </c>
       <c r="AE14">
-        <v>51.48</v>
+        <v>59.3</v>
       </c>
       <c r="AF14">
-        <v>120.24</v>
+        <v>119.36</v>
       </c>
       <c r="AH14">
-        <v>8725.02</v>
+        <v>8703.469999999999</v>
       </c>
       <c r="AI14">
-        <v>8146.59</v>
+        <v>8144.32</v>
       </c>
       <c r="AJ14">
         <v>8626.549999999999</v>
@@ -2429,7 +2432,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>27.2</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2443,10 +2446,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26909.6</v>
+        <v>27152.1</v>
       </c>
       <c r="E15">
-        <v>-0.41</v>
+        <v>0.9</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2455,43 +2458,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-1.02</v>
+        <v>-0.13</v>
       </c>
       <c r="I15">
-        <v>25.43</v>
+        <v>26.56</v>
       </c>
       <c r="J15">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
-        <v>2.09</v>
+        <v>3.09</v>
       </c>
       <c r="L15">
-        <v>7.68</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="M15">
-        <v>20.45</v>
+        <v>22.31</v>
       </c>
       <c r="N15">
-        <v>13.43</v>
+        <v>13.56</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26673.26</v>
+        <v>26874.44</v>
       </c>
       <c r="R15">
-        <v>26690.92</v>
+        <v>26720.33</v>
       </c>
       <c r="S15">
-        <v>26438.45</v>
+        <v>26463.35</v>
       </c>
       <c r="T15">
-        <v>24019.19</v>
+        <v>24040.51</v>
       </c>
       <c r="U15">
-        <v>12.03</v>
+        <v>12.94</v>
       </c>
       <c r="V15" t="s">
         <v>80</v>
@@ -2506,34 +2509,31 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>57.55</v>
+        <v>61.74</v>
       </c>
       <c r="AA15">
-        <v>86.15000000000001</v>
+        <v>118.2</v>
       </c>
       <c r="AB15">
-        <v>80.06</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="AC15">
-        <v>6.1</v>
+        <v>30.51</v>
       </c>
       <c r="AD15">
-        <v>76.06</v>
+        <v>95.16</v>
       </c>
       <c r="AE15">
-        <v>53.54</v>
+        <v>76.72</v>
       </c>
       <c r="AF15">
-        <v>331.64</v>
-      </c>
-      <c r="AG15">
-        <v>-100</v>
+        <v>331.12</v>
       </c>
       <c r="AH15">
-        <v>27202.82</v>
+        <v>27267.85</v>
       </c>
       <c r="AI15">
-        <v>26179.03</v>
+        <v>26172.81</v>
       </c>
       <c r="AJ15">
         <v>26048.62</v>
@@ -2542,7 +2542,7 @@
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>24.01</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2556,10 +2556,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>861.5</v>
+        <v>871</v>
       </c>
       <c r="E16">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2568,43 +2568,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-11.06</v>
+        <v>-10.08</v>
       </c>
       <c r="I16">
-        <v>32.3</v>
+        <v>33.76</v>
       </c>
       <c r="J16">
-        <v>5.8</v>
+        <v>5.92</v>
       </c>
       <c r="K16">
-        <v>-5.12</v>
+        <v>-5.03</v>
       </c>
       <c r="L16">
-        <v>6.88</v>
+        <v>5.76</v>
       </c>
       <c r="M16">
-        <v>-2.58</v>
+        <v>-3.83</v>
       </c>
       <c r="N16">
-        <v>13.64</v>
+        <v>12.02</v>
       </c>
       <c r="O16">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="Q16">
-        <v>843.22</v>
+        <v>852.96</v>
       </c>
       <c r="R16">
-        <v>878.34</v>
+        <v>876</v>
       </c>
       <c r="S16">
-        <v>895.11</v>
+        <v>894.16</v>
       </c>
       <c r="T16">
-        <v>828.14</v>
+        <v>828.03</v>
       </c>
       <c r="U16">
-        <v>4.03</v>
+        <v>5.19</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2619,31 +2619,31 @@
         <v>2</v>
       </c>
       <c r="Z16">
-        <v>45.32</v>
+        <v>48.91</v>
       </c>
       <c r="AA16">
-        <v>-14.69</v>
+        <v>-12.64</v>
       </c>
       <c r="AB16">
-        <v>-11.59</v>
+        <v>-11.8</v>
       </c>
       <c r="AC16">
-        <v>-3.11</v>
+        <v>-0.84</v>
       </c>
       <c r="AD16">
-        <v>53.35</v>
+        <v>63.92</v>
       </c>
       <c r="AE16">
-        <v>41.1</v>
+        <v>53.09</v>
       </c>
       <c r="AF16">
-        <v>19.06</v>
+        <v>18.77</v>
       </c>
       <c r="AH16">
-        <v>943.92</v>
+        <v>938.9400000000001</v>
       </c>
       <c r="AI16">
-        <v>812.75</v>
+        <v>813.05</v>
       </c>
       <c r="AJ16">
         <v>877.53</v>
@@ -2652,7 +2652,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>33.12</v>
+        <v>29.51</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2666,10 +2666,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29970.75</v>
+        <v>30064.25</v>
       </c>
       <c r="E17">
-        <v>-0.3</v>
+        <v>0.31</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2678,43 +2678,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-12.11</v>
+        <v>-11.84</v>
       </c>
       <c r="I17">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="J17">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="K17">
-        <v>-2.98</v>
+        <v>-2.57</v>
       </c>
       <c r="L17">
-        <v>-1.14</v>
+        <v>-2.14</v>
       </c>
       <c r="M17">
-        <v>-8.050000000000001</v>
+        <v>-7.69</v>
       </c>
       <c r="N17">
-        <v>3.95</v>
+        <v>3.67</v>
       </c>
       <c r="O17">
         <v>19</v>
       </c>
       <c r="Q17">
-        <v>29948.18</v>
+        <v>30000.56</v>
       </c>
       <c r="R17">
-        <v>30331.02</v>
+        <v>30284.25</v>
       </c>
       <c r="S17">
-        <v>30880.75</v>
+        <v>30860.96</v>
       </c>
       <c r="T17">
-        <v>31415.35</v>
+        <v>31396.02</v>
       </c>
       <c r="U17">
-        <v>-4.6</v>
+        <v>-4.24</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2729,31 +2729,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>36.93</v>
+        <v>40.44</v>
       </c>
       <c r="AA17">
-        <v>-280.25</v>
+        <v>-261.62</v>
       </c>
       <c r="AB17">
-        <v>-273.3</v>
+        <v>-270.97</v>
       </c>
       <c r="AC17">
-        <v>-6.95</v>
+        <v>9.35</v>
       </c>
       <c r="AD17">
-        <v>82.12</v>
+        <v>89.89</v>
       </c>
       <c r="AE17">
-        <v>63.06</v>
+        <v>78.56</v>
       </c>
       <c r="AF17">
-        <v>266.58</v>
+        <v>257.11</v>
       </c>
       <c r="AH17">
-        <v>31201.8</v>
+        <v>31102.74</v>
       </c>
       <c r="AI17">
-        <v>29460.24</v>
+        <v>29465.76</v>
       </c>
       <c r="AJ17">
         <v>30589.09</v>
@@ -2762,7 +2762,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>27.62</v>
+        <v>24.86</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2776,10 +2776,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16720</v>
+        <v>16868.15</v>
       </c>
       <c r="E18">
-        <v>-0.46</v>
+        <v>0.89</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2788,31 +2788,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-1.31</v>
+        <v>-0.43</v>
       </c>
       <c r="I18">
-        <v>8.550000000000001</v>
+        <v>9.51</v>
       </c>
       <c r="J18">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="K18">
-        <v>1.55</v>
+        <v>2.74</v>
       </c>
       <c r="L18">
-        <v>5.03</v>
+        <v>5.73</v>
       </c>
       <c r="N18">
-        <v>29.61</v>
+        <v>33.4</v>
       </c>
       <c r="Q18">
-        <v>16586.92</v>
+        <v>16705.62</v>
       </c>
       <c r="R18">
-        <v>16593.07</v>
+        <v>16606.61</v>
       </c>
       <c r="S18">
-        <v>16560.49</v>
+        <v>16569.03</v>
       </c>
       <c r="V18" t="s">
         <v>80</v>
@@ -2824,31 +2824,31 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>56.21</v>
+        <v>60.65</v>
       </c>
       <c r="AA18">
-        <v>21.26</v>
+        <v>42.6</v>
       </c>
       <c r="AB18">
-        <v>5.55</v>
+        <v>12.96</v>
       </c>
       <c r="AC18">
-        <v>15.71</v>
+        <v>29.64</v>
       </c>
       <c r="AD18">
-        <v>77.15000000000001</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="AE18">
-        <v>55.61</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="AF18">
-        <v>194.53</v>
+        <v>194.33</v>
       </c>
       <c r="AH18">
-        <v>16914.94</v>
+        <v>16951.22</v>
       </c>
       <c r="AI18">
-        <v>16271.2</v>
+        <v>16261.99</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2857,7 +2857,7 @@
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>21.66</v>
+        <v>22.76</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2871,10 +2871,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9471.549999999999</v>
+        <v>9461.299999999999</v>
       </c>
       <c r="E19">
-        <v>0.58</v>
+        <v>-0.11</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2883,31 +2883,31 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-5.27</v>
+        <v>-5.37</v>
       </c>
       <c r="I19">
-        <v>5.29</v>
+        <v>5.18</v>
       </c>
       <c r="J19">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="K19">
-        <v>-3.36</v>
+        <v>-2.86</v>
       </c>
       <c r="L19">
-        <v>-1.88</v>
+        <v>-0.01</v>
       </c>
       <c r="N19">
-        <v>20.29</v>
+        <v>19.61</v>
       </c>
       <c r="Q19">
-        <v>9328.23</v>
+        <v>9394.67</v>
       </c>
       <c r="R19">
-        <v>9618.99</v>
+        <v>9603.879999999999</v>
       </c>
       <c r="S19">
-        <v>9562.85</v>
+        <v>9565.57</v>
       </c>
       <c r="V19" t="s">
         <v>80</v>
@@ -2919,31 +2919,31 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>46.18</v>
+        <v>45.81</v>
       </c>
       <c r="AA19">
-        <v>-73.06</v>
+        <v>-70.28</v>
       </c>
       <c r="AB19">
-        <v>-29.2</v>
+        <v>-37.42</v>
       </c>
       <c r="AC19">
-        <v>-43.85</v>
+        <v>-32.86</v>
       </c>
       <c r="AD19">
-        <v>34.99</v>
+        <v>39.22</v>
       </c>
       <c r="AE19">
-        <v>25.9</v>
+        <v>33.82</v>
       </c>
       <c r="AF19">
-        <v>172.28</v>
+        <v>165.48</v>
       </c>
       <c r="AH19">
-        <v>10102.12</v>
+        <v>10086.9</v>
       </c>
       <c r="AI19">
-        <v>9135.85</v>
+        <v>9120.860000000001</v>
       </c>
       <c r="AJ19">
         <v>9616.870000000001</v>
@@ -2952,7 +2952,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>27.44</v>
+        <v>25.32</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2966,10 +2966,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10958.9</v>
+        <v>11005.2</v>
       </c>
       <c r="E20">
-        <v>-0.43</v>
+        <v>0.42</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -2978,31 +2978,31 @@
         <v>10796.4</v>
       </c>
       <c r="H20">
-        <v>-3.61</v>
+        <v>-3.2</v>
       </c>
       <c r="I20">
-        <v>1.51</v>
+        <v>1.93</v>
       </c>
       <c r="J20">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="K20">
-        <v>-1.96</v>
+        <v>-1.71</v>
       </c>
       <c r="L20">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="N20">
-        <v>-1.73</v>
+        <v>-0.23</v>
       </c>
       <c r="Q20">
-        <v>10928.73</v>
+        <v>10955.28</v>
       </c>
       <c r="R20">
-        <v>11043.47</v>
+        <v>11032.99</v>
       </c>
       <c r="S20">
-        <v>11144.96</v>
+        <v>11143.02</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3014,31 +3014,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>42.99</v>
+        <v>46.7</v>
       </c>
       <c r="AA20">
-        <v>-67.09999999999999</v>
+        <v>-60.26</v>
       </c>
       <c r="AB20">
-        <v>-60.04</v>
+        <v>-60.08</v>
       </c>
       <c r="AC20">
-        <v>-7.07</v>
+        <v>-0.18</v>
       </c>
       <c r="AD20">
-        <v>69.70999999999999</v>
+        <v>76.62</v>
       </c>
       <c r="AE20">
-        <v>55.49</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="AF20">
-        <v>122.41</v>
+        <v>118.81</v>
       </c>
       <c r="AH20">
-        <v>11281.25</v>
+        <v>11257.03</v>
       </c>
       <c r="AI20">
-        <v>10805.69</v>
+        <v>10808.94</v>
       </c>
       <c r="AJ20">
         <v>11213.36</v>
@@ -3047,7 +3047,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>28.94</v>
+        <v>28.09</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3061,10 +3061,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27286</v>
+        <v>27363.35</v>
       </c>
       <c r="E21">
-        <v>-0.31</v>
+        <v>0.28</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3073,43 +3073,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6.52</v>
+        <v>-6.25</v>
       </c>
       <c r="I21">
-        <v>13.01</v>
+        <v>13.33</v>
       </c>
       <c r="J21">
-        <v>0.8</v>
+        <v>0.29</v>
       </c>
       <c r="K21">
-        <v>-0.59</v>
+        <v>-0.5</v>
       </c>
       <c r="L21">
-        <v>-1.72</v>
+        <v>-3.23</v>
       </c>
       <c r="M21">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="N21">
-        <v>7.08</v>
+        <v>6.7</v>
       </c>
       <c r="O21">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="Q21">
-        <v>27279.91</v>
+        <v>27295.73</v>
       </c>
       <c r="R21">
-        <v>27513.45</v>
+        <v>27509.25</v>
       </c>
       <c r="S21">
-        <v>27708.75</v>
+        <v>27697.69</v>
       </c>
       <c r="T21">
-        <v>27568.16</v>
+        <v>27561.18</v>
       </c>
       <c r="U21">
-        <v>-1.02</v>
+        <v>-0.72</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3124,31 +3124,31 @@
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>45.03</v>
+        <v>47.16</v>
       </c>
       <c r="AA21">
-        <v>-108.55</v>
+        <v>-100.43</v>
       </c>
       <c r="AB21">
-        <v>-92.3</v>
+        <v>-93.93000000000001</v>
       </c>
       <c r="AC21">
-        <v>-16.25</v>
+        <v>-6.5</v>
       </c>
       <c r="AD21">
-        <v>42.92</v>
+        <v>51.59</v>
       </c>
       <c r="AE21">
-        <v>33.68</v>
+        <v>42.79</v>
       </c>
       <c r="AF21">
-        <v>290.11</v>
+        <v>282.47</v>
       </c>
       <c r="AH21">
-        <v>28038.88</v>
+        <v>28038.23</v>
       </c>
       <c r="AI21">
-        <v>26988.03</v>
+        <v>26980.27</v>
       </c>
       <c r="AJ21">
         <v>28092.43</v>
@@ -3157,7 +3157,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>18.52</v>
+        <v>16.57</v>
       </c>
     </row>
   </sheetData>
@@ -3298,7 +3298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3338,2091 +3338,2088 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>79</v>
-      </c>
+        <v>93</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>96</v>
+      <c r="A7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-7.56</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-6.68</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.88</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C8" s="6">
-        <v>-7.34</v>
+        <v>-2.39</v>
       </c>
       <c r="D8" s="6">
-        <v>-7.56</v>
+        <v>-2.04</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.22</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="6">
-        <v>-2.45</v>
+        <v>-4.81</v>
       </c>
       <c r="D9" s="6">
-        <v>-2.39</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.06</v>
+        <v>-3.86</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.63</v>
+        <v>-1.11</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.81</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-0.18</v>
+        <v>-1.5</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-0.87</v>
+        <v>-4.61</v>
       </c>
       <c r="D11" s="6">
-        <v>-1.11</v>
+        <v>-2.67</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.24</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-4.1</v>
+        <v>-3</v>
       </c>
       <c r="D12" s="6">
-        <v>-4.61</v>
+        <v>-2.27</v>
       </c>
       <c r="E12" s="7">
-        <v>-0.51</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.59</v>
+        <v>-6.39</v>
       </c>
       <c r="D13" s="6">
-        <v>-3</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-0.41</v>
+        <v>-7.4</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.01</v>
+        <v>-3.76</v>
       </c>
       <c r="D14" s="6">
-        <v>-6.39</v>
+        <v>-2.99</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.38</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.43</v>
+        <v>-3.51</v>
       </c>
       <c r="D15" s="6">
-        <v>-3.76</v>
+        <v>-2.65</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.33</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.11</v>
+        <v>-2.88</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.51</v>
+        <v>-2.27</v>
       </c>
       <c r="E16" s="7">
-        <v>-0.4</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-4.04</v>
+        <v>-0.54</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.88</v>
+        <v>-0.59</v>
       </c>
       <c r="E17" s="8">
-        <v>1.16</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-0.67</v>
+        <v>-1.3</v>
       </c>
       <c r="D18" s="6">
-        <v>-0.54</v>
+        <v>-1.47</v>
       </c>
       <c r="E18" s="8">
-        <v>0.13</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-1.43</v>
+        <v>-4.01</v>
       </c>
       <c r="D19" s="6">
-        <v>-1.3</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.13</v>
+        <v>-2.04</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.97</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.53</v>
+        <v>2.09</v>
       </c>
       <c r="D20" s="6">
-        <v>-4.01</v>
+        <v>3.09</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>2.29</v>
+        <v>-5.12</v>
       </c>
       <c r="D21" s="6">
-        <v>2.09</v>
+        <v>-5.03</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.2</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-5.96</v>
+        <v>-2.98</v>
       </c>
       <c r="D22" s="6">
-        <v>-5.12</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.84</v>
+        <v>-2.57</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.41</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-2.68</v>
+        <v>1.55</v>
       </c>
       <c r="D23" s="6">
-        <v>-2.98</v>
+        <v>2.74</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.3</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>2.01</v>
+        <v>-3.36</v>
       </c>
       <c r="D24" s="6">
-        <v>1.55</v>
+        <v>-2.86</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.46</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-3.92</v>
+        <v>-1.96</v>
       </c>
       <c r="D25" s="6">
-        <v>-3.36</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.5600000000000001</v>
+        <v>-1.71</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-1.54</v>
+        <v>-0.59</v>
       </c>
       <c r="D26" s="6">
-        <v>-1.96</v>
+        <v>-0.5</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.42</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" s="6">
-        <v>-0.29</v>
+        <v>1.23</v>
       </c>
       <c r="D27" s="6">
-        <v>-0.59</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.3</v>
+        <v>0.98</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>-0.5600000000000001</v>
+        <v>1.51</v>
       </c>
       <c r="D28" s="6">
-        <v>1.23</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.79</v>
+        <v>2.16</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.65</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-0.38</v>
+        <v>1.81</v>
       </c>
       <c r="D29" s="6">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="E29" s="8">
-        <v>1.89</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>0.42</v>
+        <v>1.56</v>
       </c>
       <c r="D30" s="6">
-        <v>1.81</v>
+        <v>1.55</v>
       </c>
       <c r="E30" s="8">
-        <v>1.39</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="6">
+        <v>1.85</v>
+      </c>
+      <c r="D31" s="6">
+        <v>1.54</v>
+      </c>
+      <c r="E31" s="8">
         <v>-0.31</v>
-      </c>
-      <c r="D31" s="6">
-        <v>1.56</v>
-      </c>
-      <c r="E31" s="8">
-        <v>1.87</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>1.88</v>
+        <v>1.36</v>
       </c>
       <c r="D32" s="6">
-        <v>1.85</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-0.03</v>
+        <v>1.2</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-0.08</v>
+        <v>-3.29</v>
       </c>
       <c r="D33" s="6">
-        <v>1.36</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1.44</v>
+        <v>-2.59</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>-0.31</v>
+        <v>1.96</v>
       </c>
       <c r="D34" s="6">
-        <v>-3.29</v>
+        <v>2.57</v>
       </c>
       <c r="E34" s="7">
-        <v>-2.98</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>-0.14</v>
+        <v>1.24</v>
       </c>
       <c r="D35" s="6">
-        <v>1.96</v>
-      </c>
-      <c r="E35" s="8">
-        <v>2.1</v>
+        <v>2.09</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.85</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-0.21</v>
+        <v>4.71</v>
       </c>
       <c r="D36" s="6">
-        <v>1.24</v>
+        <v>3.42</v>
       </c>
       <c r="E36" s="8">
-        <v>1.45</v>
+        <v>-1.29</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>1.22</v>
+        <v>2.54</v>
       </c>
       <c r="D37" s="6">
-        <v>4.71</v>
-      </c>
-      <c r="E37" s="8">
-        <v>3.49</v>
+        <v>4.42</v>
+      </c>
+      <c r="E37" s="7">
+        <v>1.88</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-0.2</v>
+        <v>1.58</v>
       </c>
       <c r="D38" s="6">
-        <v>2.54</v>
+        <v>1.51</v>
       </c>
       <c r="E38" s="8">
-        <v>2.74</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>-0.87</v>
+        <v>1.38</v>
       </c>
       <c r="D39" s="6">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="E39" s="8">
-        <v>2.45</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-0.45</v>
+        <v>2.75</v>
       </c>
       <c r="D40" s="6">
-        <v>1.38</v>
-      </c>
-      <c r="E40" s="8">
-        <v>1.83</v>
+        <v>3.85</v>
+      </c>
+      <c r="E40" s="7">
+        <v>1.1</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>1.84</v>
+        <v>5.8</v>
       </c>
       <c r="D41" s="6">
-        <v>2.75</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.91</v>
+        <v>5.92</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="D42" s="6">
-        <v>5.8</v>
-      </c>
-      <c r="E42" s="8">
-        <v>5.17</v>
+        <v>0.88</v>
+      </c>
+      <c r="E42" s="7">
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>0.31</v>
+        <v>2.58</v>
       </c>
       <c r="D43" s="6">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.5</v>
+        <v>3.65</v>
+      </c>
+      <c r="E43" s="7">
+        <v>1.07</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>1.85</v>
+        <v>3.58</v>
       </c>
       <c r="D44" s="6">
-        <v>2.58</v>
-      </c>
-      <c r="E44" s="8">
-        <v>0.73</v>
+        <v>3.64</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>-3.16</v>
+        <v>1.51</v>
       </c>
       <c r="D45" s="6">
-        <v>3.58</v>
+        <v>1.22</v>
       </c>
       <c r="E45" s="8">
-        <v>6.74</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>0.63</v>
+        <v>0.8</v>
       </c>
       <c r="D46" s="6">
-        <v>1.51</v>
+        <v>0.29</v>
       </c>
       <c r="E46" s="8">
-        <v>0.88</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C47" s="6">
-        <v>-0.24</v>
+        <v>0.82</v>
       </c>
       <c r="D47" s="6">
-        <v>0.8</v>
-      </c>
-      <c r="E47" s="8">
-        <v>1.04</v>
+        <v>1.48</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.66</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="6">
-        <v>1.52</v>
+        <v>7.28</v>
       </c>
       <c r="D48" s="6">
-        <v>0.82</v>
+        <v>8.24</v>
       </c>
       <c r="E48" s="7">
-        <v>-0.7</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="6">
-        <v>7.66</v>
+        <v>-7.18</v>
       </c>
       <c r="D49" s="6">
-        <v>7.28</v>
+        <v>-6.49</v>
       </c>
       <c r="E49" s="7">
-        <v>-0.38</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>-7.27</v>
+        <v>7.98</v>
       </c>
       <c r="D50" s="6">
-        <v>-7.18</v>
+        <v>7.49</v>
       </c>
       <c r="E50" s="8">
-        <v>0.09</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>8.59</v>
+        <v>-19.27</v>
       </c>
       <c r="D51" s="6">
-        <v>7.98</v>
+        <v>-18.2</v>
       </c>
       <c r="E51" s="7">
-        <v>-0.61</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-19.42</v>
+        <v>-3.59</v>
       </c>
       <c r="D52" s="6">
-        <v>-19.27</v>
-      </c>
-      <c r="E52" s="8">
-        <v>0.15</v>
+        <v>-3.14</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.45</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-2.5</v>
+        <v>-20.85</v>
       </c>
       <c r="D53" s="6">
-        <v>-3.59</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-1.09</v>
+        <v>-21.08</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-19.92</v>
+        <v>-0.59</v>
       </c>
       <c r="D54" s="6">
-        <v>-20.85</v>
+        <v>-0.03</v>
       </c>
       <c r="E54" s="7">
-        <v>-0.93</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>0.17</v>
+        <v>-2.86</v>
       </c>
       <c r="D55" s="6">
-        <v>-0.59</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-0.76</v>
+        <v>-2.9</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-4.39</v>
+        <v>31.43</v>
       </c>
       <c r="D56" s="6">
-        <v>-2.86</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.53</v>
+        <v>34.49</v>
+      </c>
+      <c r="E56" s="7">
+        <v>3.06</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>32.47</v>
+        <v>-0.43</v>
       </c>
       <c r="D57" s="6">
-        <v>31.43</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-1.04</v>
+        <v>-0.52</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>0.14</v>
+        <v>17.21</v>
       </c>
       <c r="D58" s="6">
-        <v>-0.43</v>
+        <v>17.83</v>
       </c>
       <c r="E58" s="7">
-        <v>-0.57</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>17.47</v>
+        <v>20.45</v>
       </c>
       <c r="D59" s="6">
-        <v>17.21</v>
+        <v>22.31</v>
       </c>
       <c r="E59" s="7">
-        <v>-0.26</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>21.59</v>
+        <v>-2.58</v>
       </c>
       <c r="D60" s="6">
-        <v>20.45</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.14</v>
+        <v>-3.83</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.25</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>-3.39</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="D61" s="6">
-        <v>-2.58</v>
-      </c>
-      <c r="E61" s="8">
-        <v>0.8100000000000001</v>
+        <v>-7.69</v>
+      </c>
+      <c r="E61" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>-7.37</v>
+        <v>2.13</v>
       </c>
       <c r="D62" s="6">
-        <v>-8.050000000000001</v>
+        <v>2.41</v>
       </c>
       <c r="E62" s="7">
-        <v>-0.68</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>2.86</v>
+        <v>2.23</v>
       </c>
       <c r="D63" s="6">
-        <v>2.13</v>
+        <v>2.93</v>
       </c>
       <c r="E63" s="7">
-        <v>-0.73</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>1.68</v>
+        <v>-4.1</v>
       </c>
       <c r="D64" s="6">
-        <v>2.23</v>
-      </c>
-      <c r="E64" s="8">
-        <v>0.55</v>
+        <v>-3</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.1</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-5.73</v>
+        <v>-0.2</v>
       </c>
       <c r="D65" s="6">
-        <v>-4.1</v>
-      </c>
-      <c r="E65" s="8">
-        <v>1.63</v>
+        <v>0.32</v>
+      </c>
+      <c r="E65" s="7">
+        <v>0.52</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-0.85</v>
+        <v>-6.31</v>
       </c>
       <c r="D66" s="6">
-        <v>-0.2</v>
-      </c>
-      <c r="E66" s="8">
-        <v>0.65</v>
+        <v>-5.38</v>
+      </c>
+      <c r="E66" s="7">
+        <v>0.93</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-7.25</v>
+        <v>-6.93</v>
       </c>
       <c r="D67" s="6">
-        <v>-6.31</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.9399999999999999</v>
+        <v>-5.76</v>
+      </c>
+      <c r="E67" s="7">
+        <v>1.17</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-7</v>
+        <v>-3.46</v>
       </c>
       <c r="D68" s="6">
-        <v>-6.93</v>
+        <v>-4.38</v>
       </c>
       <c r="E68" s="8">
-        <v>0.07000000000000001</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-3.99</v>
+        <v>5.81</v>
       </c>
       <c r="D69" s="6">
-        <v>-3.46</v>
+        <v>2.78</v>
       </c>
       <c r="E69" s="8">
-        <v>0.53</v>
+        <v>-3.03</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>4.35</v>
+        <v>-0.41</v>
       </c>
       <c r="D70" s="6">
-        <v>5.81</v>
-      </c>
-      <c r="E70" s="8">
-        <v>1.46</v>
+        <v>0.83</v>
+      </c>
+      <c r="E70" s="7">
+        <v>1.24</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-1.13</v>
+        <v>-4.65</v>
       </c>
       <c r="D71" s="6">
-        <v>-0.41</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.72</v>
+        <v>-3.89</v>
+      </c>
+      <c r="E71" s="7">
+        <v>0.76</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-5.16</v>
+        <v>3.98</v>
       </c>
       <c r="D72" s="6">
-        <v>-4.65</v>
+        <v>3.13</v>
       </c>
       <c r="E72" s="8">
-        <v>0.51</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>1.24</v>
+        <v>2.54</v>
       </c>
       <c r="D73" s="6">
-        <v>3.98</v>
-      </c>
-      <c r="E73" s="8">
-        <v>2.74</v>
+        <v>5.42</v>
+      </c>
+      <c r="E73" s="7">
+        <v>2.88</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-0.91</v>
+        <v>-5.14</v>
       </c>
       <c r="D74" s="6">
-        <v>2.54</v>
-      </c>
-      <c r="E74" s="8">
-        <v>3.45</v>
+        <v>-4.48</v>
+      </c>
+      <c r="E74" s="7">
+        <v>0.66</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-6.27</v>
+        <v>-3.72</v>
       </c>
       <c r="D75" s="6">
-        <v>-5.14</v>
-      </c>
-      <c r="E75" s="8">
-        <v>1.13</v>
+        <v>-3.05</v>
+      </c>
+      <c r="E75" s="7">
+        <v>0.67</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-5.15</v>
+        <v>7.68</v>
       </c>
       <c r="D76" s="6">
-        <v>-3.72</v>
-      </c>
-      <c r="E76" s="8">
-        <v>1.43</v>
+        <v>8.529999999999999</v>
+      </c>
+      <c r="E76" s="7">
+        <v>0.85</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>9.119999999999999</v>
+        <v>6.88</v>
       </c>
       <c r="D77" s="6">
-        <v>7.68</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-1.44</v>
+        <v>5.76</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>4.75</v>
+        <v>-1.14</v>
       </c>
       <c r="D78" s="6">
-        <v>6.88</v>
+        <v>-2.14</v>
       </c>
       <c r="E78" s="8">
-        <v>2.13</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-2.05</v>
+        <v>5.03</v>
       </c>
       <c r="D79" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E79" s="8">
-        <v>0.91</v>
+        <v>5.73</v>
+      </c>
+      <c r="E79" s="7">
+        <v>0.7</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>6.09</v>
+        <v>-1.88</v>
       </c>
       <c r="D80" s="6">
-        <v>5.03</v>
+        <v>-0.01</v>
       </c>
       <c r="E80" s="7">
-        <v>-1.06</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-3.2</v>
+        <v>-1.9</v>
       </c>
       <c r="D81" s="6">
-        <v>-1.88</v>
+        <v>-2.1</v>
       </c>
       <c r="E81" s="8">
-        <v>1.32</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-2.37</v>
+        <v>-1.72</v>
       </c>
       <c r="D82" s="6">
-        <v>-1.9</v>
+        <v>-3.23</v>
       </c>
       <c r="E82" s="8">
-        <v>0.47</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C83" s="6">
-        <v>-2.17</v>
+        <v>-8.640000000000001</v>
       </c>
       <c r="D83" s="6">
-        <v>-1.72</v>
-      </c>
-      <c r="E83" s="8">
-        <v>0.45</v>
+        <v>-8.4</v>
+      </c>
+      <c r="E83" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="6">
-        <v>-8.42</v>
+        <v>-9.08</v>
       </c>
       <c r="D84" s="6">
-        <v>-8.640000000000001</v>
+        <v>-8.16</v>
       </c>
       <c r="E84" s="7">
-        <v>-0.22</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="6">
-        <v>-9.140000000000001</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="D85" s="6">
-        <v>-9.08</v>
-      </c>
-      <c r="E85" s="8">
-        <v>0.06</v>
+        <v>-8.65</v>
+      </c>
+      <c r="E85" s="7">
+        <v>0.46</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="6">
-        <v>-8.94</v>
+        <v>-9.17</v>
       </c>
       <c r="D86" s="6">
-        <v>-9.109999999999999</v>
+        <v>-9.09</v>
       </c>
       <c r="E86" s="7">
-        <v>-0.17</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-8.949999999999999</v>
+        <v>-19.58</v>
       </c>
       <c r="D87" s="6">
-        <v>-9.17</v>
+        <v>-18.52</v>
       </c>
       <c r="E87" s="7">
-        <v>-0.22</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-19.15</v>
+        <v>-10.7</v>
       </c>
       <c r="D88" s="6">
-        <v>-19.58</v>
+        <v>-10.18</v>
       </c>
       <c r="E88" s="7">
-        <v>-0.43</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-10.32</v>
+        <v>-27.62</v>
       </c>
       <c r="D89" s="6">
-        <v>-10.7</v>
-      </c>
-      <c r="E89" s="7">
-        <v>-0.38</v>
+        <v>-28.25</v>
+      </c>
+      <c r="E89" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-26.99</v>
+        <v>-4.63</v>
       </c>
       <c r="D90" s="6">
-        <v>-27.62</v>
+        <v>-3.87</v>
       </c>
       <c r="E90" s="7">
-        <v>-0.63</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-4.3</v>
+        <v>-7.63</v>
       </c>
       <c r="D91" s="6">
-        <v>-4.63</v>
+        <v>-6.87</v>
       </c>
       <c r="E91" s="7">
-        <v>-0.33</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-7.25</v>
+        <v>-3.54</v>
       </c>
       <c r="D92" s="6">
-        <v>-7.63</v>
-      </c>
-      <c r="E92" s="7">
-        <v>-0.38</v>
+        <v>-4.02</v>
+      </c>
+      <c r="E92" s="8">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-4.69</v>
+        <v>-5.31</v>
       </c>
       <c r="D93" s="6">
-        <v>-3.54</v>
-      </c>
-      <c r="E93" s="8">
-        <v>1.15</v>
+        <v>-3.03</v>
+      </c>
+      <c r="E93" s="7">
+        <v>2.28</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-5.44</v>
+        <v>-10.68</v>
       </c>
       <c r="D94" s="6">
-        <v>-5.31</v>
-      </c>
-      <c r="E94" s="8">
-        <v>0.13</v>
+        <v>-10.48</v>
+      </c>
+      <c r="E94" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-10.8</v>
+        <v>-16.28</v>
       </c>
       <c r="D95" s="6">
-        <v>-10.68</v>
-      </c>
-      <c r="E95" s="8">
-        <v>0.12</v>
+        <v>-15.33</v>
+      </c>
+      <c r="E95" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-15.87</v>
+        <v>-1.02</v>
       </c>
       <c r="D96" s="6">
-        <v>-16.28</v>
+        <v>-0.13</v>
       </c>
       <c r="E96" s="7">
-        <v>-0.41</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-0.61</v>
+        <v>-11.06</v>
       </c>
       <c r="D97" s="6">
-        <v>-1.02</v>
+        <v>-10.08</v>
       </c>
       <c r="E97" s="7">
-        <v>-0.41</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-11.85</v>
+        <v>-12.11</v>
       </c>
       <c r="D98" s="6">
-        <v>-11.06</v>
-      </c>
-      <c r="E98" s="8">
-        <v>0.79</v>
+        <v>-11.84</v>
+      </c>
+      <c r="E98" s="7">
+        <v>0.27</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-11.85</v>
+        <v>-1.31</v>
       </c>
       <c r="D99" s="6">
-        <v>-12.11</v>
+        <v>-0.43</v>
       </c>
       <c r="E99" s="7">
-        <v>-0.26</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-0.85</v>
+        <v>-5.27</v>
       </c>
       <c r="D100" s="6">
-        <v>-1.31</v>
-      </c>
-      <c r="E100" s="7">
-        <v>-0.46</v>
+        <v>-5.37</v>
+      </c>
+      <c r="E100" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-5.82</v>
+        <v>-3.61</v>
       </c>
       <c r="D101" s="6">
-        <v>-5.27</v>
-      </c>
-      <c r="E101" s="8">
-        <v>0.55</v>
+        <v>-3.2</v>
+      </c>
+      <c r="E101" s="7">
+        <v>0.41</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-3.19</v>
+        <v>-6.52</v>
       </c>
       <c r="D102" s="6">
-        <v>-3.61</v>
+        <v>-6.25</v>
       </c>
       <c r="E102" s="7">
-        <v>-0.42</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C103" s="6">
-        <v>-6.23</v>
+        <v>27086.3</v>
       </c>
       <c r="D103" s="6">
-        <v>-6.52</v>
+        <v>27157.55</v>
       </c>
       <c r="E103" s="7">
-        <v>-0.29</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C104" s="6">
-        <v>27151.1</v>
+        <v>9549.35</v>
       </c>
       <c r="D104" s="6">
-        <v>27086.3</v>
+        <v>9646.5</v>
       </c>
       <c r="E104" s="7">
-        <v>-64.8</v>
+        <v>97.15000000000001</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C105" s="6">
-        <v>9543.65</v>
+        <v>11487.2</v>
       </c>
       <c r="D105" s="6">
-        <v>9549.35</v>
-      </c>
-      <c r="E105" s="8">
-        <v>5.7</v>
+        <v>11546.05</v>
+      </c>
+      <c r="E105" s="7">
+        <v>58.85</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>11509.3</v>
+        <v>37727</v>
       </c>
       <c r="D106" s="6">
-        <v>11487.2</v>
+        <v>37759.75</v>
       </c>
       <c r="E106" s="7">
-        <v>-22.1</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>37818.55</v>
+        <v>45657.75</v>
       </c>
       <c r="D107" s="6">
-        <v>37727</v>
+        <v>46259.35</v>
       </c>
       <c r="E107" s="7">
-        <v>-91.55</v>
+        <v>601.6</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>45900.9</v>
+        <v>25417.95</v>
       </c>
       <c r="D108" s="6">
-        <v>45657.75</v>
+        <v>25564.85</v>
       </c>
       <c r="E108" s="7">
-        <v>-243.15</v>
+        <v>146.9</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>25524.7</v>
+        <v>28582.1</v>
       </c>
       <c r="D109" s="6">
-        <v>25417.95</v>
-      </c>
-      <c r="E109" s="7">
-        <v>-106.75</v>
+        <v>28334.05</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-248.05</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>28830.9</v>
+        <v>15890.5</v>
       </c>
       <c r="D110" s="6">
-        <v>28582.1</v>
+        <v>16017.7</v>
       </c>
       <c r="E110" s="7">
-        <v>-248.8</v>
+        <v>127.2</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>15945.15</v>
+        <v>9020.799999999999</v>
       </c>
       <c r="D111" s="6">
-        <v>15890.5</v>
+        <v>9095.049999999999</v>
       </c>
       <c r="E111" s="7">
-        <v>-54.65</v>
+        <v>74.25</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>9058.200000000001</v>
+        <v>1574.7</v>
       </c>
       <c r="D112" s="6">
-        <v>9020.799999999999</v>
-      </c>
-      <c r="E112" s="7">
-        <v>-37.4</v>
+        <v>1566.85</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-7.85</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>1555.95</v>
+        <v>12990.35</v>
       </c>
       <c r="D113" s="6">
-        <v>1574.7</v>
-      </c>
-      <c r="E113" s="8">
-        <v>18.75</v>
+        <v>13302.35</v>
+      </c>
+      <c r="E113" s="7">
+        <v>312</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>12972.7</v>
+        <v>9616.700000000001</v>
       </c>
       <c r="D114" s="6">
-        <v>12990.35</v>
-      </c>
-      <c r="E114" s="8">
-        <v>17.65</v>
+        <v>9637.6</v>
+      </c>
+      <c r="E114" s="7">
+        <v>20.9</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>9604</v>
+        <v>8271.299999999999</v>
       </c>
       <c r="D115" s="6">
-        <v>9616.700000000001</v>
-      </c>
-      <c r="E115" s="8">
-        <v>12.7</v>
+        <v>8365.450000000001</v>
+      </c>
+      <c r="E115" s="7">
+        <v>94.15000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>8312.4</v>
+        <v>26909.6</v>
       </c>
       <c r="D116" s="6">
-        <v>8271.299999999999</v>
+        <v>27152.1</v>
       </c>
       <c r="E116" s="7">
-        <v>-41.1</v>
+        <v>242.5</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>27021.15</v>
+        <v>861.5</v>
       </c>
       <c r="D117" s="6">
-        <v>26909.6</v>
+        <v>871</v>
       </c>
       <c r="E117" s="7">
-        <v>-111.55</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>853.85</v>
+        <v>29970.75</v>
       </c>
       <c r="D118" s="6">
-        <v>861.5</v>
-      </c>
-      <c r="E118" s="8">
-        <v>7.65</v>
+        <v>30064.25</v>
+      </c>
+      <c r="E118" s="7">
+        <v>93.5</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>30061.5</v>
+        <v>16720</v>
       </c>
       <c r="D119" s="6">
-        <v>29970.75</v>
+        <v>16868.15</v>
       </c>
       <c r="E119" s="7">
-        <v>-90.75</v>
+        <v>148.15</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>16796.9</v>
+        <v>9471.549999999999</v>
       </c>
       <c r="D120" s="6">
-        <v>16720</v>
-      </c>
-      <c r="E120" s="7">
-        <v>-76.90000000000001</v>
+        <v>9461.299999999999</v>
+      </c>
+      <c r="E120" s="8">
+        <v>-10.25</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>9416.9</v>
+        <v>10958.9</v>
       </c>
       <c r="D121" s="6">
-        <v>9471.549999999999</v>
-      </c>
-      <c r="E121" s="8">
-        <v>54.65</v>
+        <v>11005.2</v>
+      </c>
+      <c r="E121" s="7">
+        <v>46.3</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>11006.25</v>
+        <v>27286</v>
       </c>
       <c r="D122" s="6">
-        <v>10958.9</v>
+        <v>27363.35</v>
       </c>
       <c r="E122" s="7">
-        <v>-47.35</v>
+        <v>77.34999999999999</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C123" s="6">
-        <v>27370.1</v>
+        <v>50</v>
       </c>
       <c r="D123" s="6">
-        <v>27286</v>
+        <v>68</v>
       </c>
       <c r="E123" s="7">
-        <v>-84.09999999999999</v>
+        <v>18</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C124" s="6">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="D124" s="6">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E124" s="7">
-        <v>-12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C125" s="6">
+        <v>68</v>
+      </c>
+      <c r="D125" s="6">
         <v>74</v>
       </c>
-      <c r="D125" s="6">
-        <v>81</v>
-      </c>
-      <c r="E125" s="8">
-        <v>7</v>
+      <c r="E125" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="6">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="D126" s="6">
-        <v>68</v>
-      </c>
-      <c r="E126" s="7">
-        <v>-13</v>
+        <v>26</v>
+      </c>
+      <c r="E126" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -5433,461 +5430,410 @@
         <v>14</v>
       </c>
       <c r="C127" s="6">
+        <v>38</v>
+      </c>
+      <c r="D127" s="6">
         <v>44</v>
       </c>
-      <c r="D127" s="6">
-        <v>38</v>
-      </c>
       <c r="E127" s="7">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D128" s="6">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="E128" s="8">
-        <v>6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D129" s="6">
-        <v>99</v>
+        <v>62</v>
       </c>
       <c r="E129" s="8">
-        <v>6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C130" s="6">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="D130" s="6">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E130" s="8">
-        <v>6</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C131" s="6">
-        <v>99</v>
+        <v>32.67</v>
       </c>
       <c r="D131" s="6">
-        <v>93</v>
+        <v>34.9</v>
       </c>
       <c r="E131" s="7">
-        <v>-6</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C132" s="6">
-        <v>56</v>
+        <v>39.97</v>
       </c>
       <c r="D132" s="6">
-        <v>74</v>
-      </c>
-      <c r="E132" s="8">
-        <v>18</v>
+        <v>47.65</v>
+      </c>
+      <c r="E132" s="7">
+        <v>7.68</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C133" s="6">
-        <v>68</v>
+        <v>38.43</v>
       </c>
       <c r="D133" s="6">
-        <v>62</v>
+        <v>43.12</v>
       </c>
       <c r="E133" s="7">
-        <v>-6</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="6">
-        <v>33.65</v>
+        <v>43.21</v>
       </c>
       <c r="D134" s="6">
-        <v>32.67</v>
+        <v>44.01</v>
       </c>
       <c r="E134" s="7">
-        <v>-0.98</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>39.48</v>
+        <v>39.82</v>
       </c>
       <c r="D135" s="6">
-        <v>39.97</v>
-      </c>
-      <c r="E135" s="8">
-        <v>0.49</v>
+        <v>48.37</v>
+      </c>
+      <c r="E135" s="7">
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>39.56</v>
+        <v>39.26</v>
       </c>
       <c r="D136" s="6">
-        <v>38.43</v>
+        <v>43.72</v>
       </c>
       <c r="E136" s="7">
-        <v>-1.13</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>44.88</v>
+        <v>35.07</v>
       </c>
       <c r="D137" s="6">
-        <v>43.21</v>
-      </c>
-      <c r="E137" s="7">
-        <v>-1.67</v>
+        <v>33.03</v>
+      </c>
+      <c r="E137" s="8">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>42.46</v>
+        <v>38.7</v>
       </c>
       <c r="D138" s="6">
-        <v>39.82</v>
+        <v>45.11</v>
       </c>
       <c r="E138" s="7">
-        <v>-2.64</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>41.48</v>
+        <v>37.12</v>
       </c>
       <c r="D139" s="6">
-        <v>39.26</v>
+        <v>44.59</v>
       </c>
       <c r="E139" s="7">
-        <v>-2.22</v>
+        <v>7.47</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>37.21</v>
+        <v>55.25</v>
       </c>
       <c r="D140" s="6">
-        <v>35.07</v>
-      </c>
-      <c r="E140" s="7">
-        <v>-2.14</v>
+        <v>53.24</v>
+      </c>
+      <c r="E140" s="8">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>40.59</v>
+        <v>47.91</v>
       </c>
       <c r="D141" s="6">
-        <v>38.7</v>
+        <v>56.5</v>
       </c>
       <c r="E141" s="7">
-        <v>-1.89</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>39.62</v>
+        <v>42.26</v>
       </c>
       <c r="D142" s="6">
-        <v>37.12</v>
+        <v>44.55</v>
       </c>
       <c r="E142" s="7">
-        <v>-2.5</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>51.15</v>
+        <v>39.06</v>
       </c>
       <c r="D143" s="6">
-        <v>55.25</v>
-      </c>
-      <c r="E143" s="8">
-        <v>4.1</v>
+        <v>46.25</v>
+      </c>
+      <c r="E143" s="7">
+        <v>7.19</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>47.36</v>
+        <v>57.55</v>
       </c>
       <c r="D144" s="6">
-        <v>47.91</v>
-      </c>
-      <c r="E144" s="8">
-        <v>0.55</v>
+        <v>61.74</v>
+      </c>
+      <c r="E144" s="7">
+        <v>4.19</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>40.89</v>
+        <v>45.32</v>
       </c>
       <c r="D145" s="6">
-        <v>42.26</v>
-      </c>
-      <c r="E145" s="8">
-        <v>1.37</v>
+        <v>48.91</v>
+      </c>
+      <c r="E145" s="7">
+        <v>3.59</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>41.3</v>
+        <v>36.93</v>
       </c>
       <c r="D146" s="6">
-        <v>39.06</v>
+        <v>40.44</v>
       </c>
       <c r="E146" s="7">
-        <v>-2.24</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>60.37</v>
+        <v>56.21</v>
       </c>
       <c r="D147" s="6">
-        <v>57.55</v>
+        <v>60.65</v>
       </c>
       <c r="E147" s="7">
-        <v>-2.82</v>
+        <v>4.44</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>42.29</v>
+        <v>46.18</v>
       </c>
       <c r="D148" s="6">
-        <v>45.32</v>
+        <v>45.81</v>
       </c>
       <c r="E148" s="8">
-        <v>3.03</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>39</v>
+        <v>42.99</v>
       </c>
       <c r="D149" s="6">
-        <v>36.93</v>
+        <v>46.7</v>
       </c>
       <c r="E149" s="7">
-        <v>-2.07</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>59.45</v>
+        <v>45.03</v>
       </c>
       <c r="D150" s="6">
-        <v>56.21</v>
+        <v>47.16</v>
       </c>
       <c r="E150" s="7">
-        <v>-3.24</v>
-      </c>
-    </row>
-    <row r="151" spans="1:5">
-      <c r="A151" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C151" s="6">
-        <v>43.94</v>
-      </c>
-      <c r="D151" s="6">
-        <v>46.18</v>
-      </c>
-      <c r="E151" s="8">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C152" s="6">
-        <v>46.03</v>
-      </c>
-      <c r="D152" s="6">
-        <v>42.99</v>
-      </c>
-      <c r="E152" s="7">
-        <v>-3.04</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C153" s="6">
-        <v>46.94</v>
-      </c>
-      <c r="D153" s="6">
-        <v>45.03</v>
-      </c>
-      <c r="E153" s="7">
-        <v>-1.91</v>
+        <v>2.13</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5911,28 +5857,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5940,22 +5886,22 @@
         <v>78</v>
       </c>
       <c r="B2" s="11">
-        <v>39.24</v>
+        <v>43.24</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>42.9</v>
+        <v>46.8</v>
       </c>
       <c r="E2" s="11">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.8</v>
+        <v>-2.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -6072,22 +6018,22 @@
         <v>38</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>49</v>
       </c>
       <c r="F1" s="13" t="s">
         <v>48</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>52</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>46</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>41</v>
@@ -6095,34 +6041,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2961</v>
+        <v>0.334</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2837</v>
+        <v>0.2835</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2137</v>
+        <v>0.2123</v>
       </c>
       <c r="D2" s="14">
-        <v>0.2029</v>
+        <v>0.1996</v>
       </c>
       <c r="E2" s="14">
-        <v>0.2021</v>
+        <v>0.1961</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1865</v>
+        <v>0.1883</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1364</v>
+        <v>0.1356</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1343</v>
+        <v>0.1262</v>
       </c>
       <c r="I2" s="14">
-        <v>0.1282</v>
+        <v>0.1202</v>
       </c>
       <c r="J2" s="14">
-        <v>0.1191</v>
+        <v>0.1152</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6133,13 +6079,13 @@
         <v>40</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>43</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>53</v>
@@ -6159,34 +6105,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.1139</v>
+        <v>0.1133</v>
       </c>
       <c r="B4" s="14">
-        <v>0.09470000000000001</v>
+        <v>0.0949</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0708</v>
+        <v>0.08259999999999999</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0697</v>
+        <v>0.067</v>
       </c>
       <c r="E4" s="14">
-        <v>0.053</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0395</v>
+        <v>0.0367</v>
       </c>
       <c r="G4" s="14">
-        <v>0.0192</v>
+        <v>0.0217</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0173</v>
+        <v>-0.0023</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.0473</v>
+        <v>-0.051</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.06509999999999999</v>
+        <v>-0.06280000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="107">
   <si>
     <t>Symbol</t>
   </si>
@@ -292,16 +292,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>47.9 → 56.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>47.9</t>
+    <t>56.5 → 49.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>56.5</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -387,14 +387,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -427,13 +427,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1031,10 +1031,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>27157.55</v>
+        <v>26730.1</v>
       </c>
       <c r="E2">
-        <v>0.26</v>
+        <v>-1.57</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1043,43 +1043,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-8.4</v>
+        <v>-9.84</v>
       </c>
       <c r="I2">
-        <v>14.25</v>
+        <v>12.45</v>
       </c>
       <c r="J2">
-        <v>0.98</v>
+        <v>-1.58</v>
       </c>
       <c r="K2">
-        <v>-6.68</v>
+        <v>-8.51</v>
       </c>
       <c r="L2">
-        <v>2.93</v>
+        <v>-0.92</v>
       </c>
       <c r="M2">
-        <v>1.48</v>
+        <v>-1.53</v>
       </c>
       <c r="N2">
-        <v>21.23</v>
+        <v>20.72</v>
       </c>
       <c r="O2">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="Q2">
-        <v>27136.62</v>
+        <v>27050.81</v>
       </c>
       <c r="R2">
-        <v>27745.23</v>
+        <v>27631.72</v>
       </c>
       <c r="S2">
-        <v>28144.25</v>
+        <v>28145.95</v>
       </c>
       <c r="T2">
-        <v>27118.74</v>
+        <v>27112.49</v>
       </c>
       <c r="U2">
-        <v>0.14</v>
+        <v>-1.41</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1091,43 +1091,43 @@
         <v>79</v>
       </c>
       <c r="Y2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z2">
-        <v>34.9</v>
+        <v>28.76</v>
       </c>
       <c r="AA2">
-        <v>-391.23</v>
+        <v>-412.21</v>
       </c>
       <c r="AB2">
-        <v>-326.47</v>
+        <v>-343.62</v>
       </c>
       <c r="AC2">
-        <v>-64.76000000000001</v>
+        <v>-68.59999999999999</v>
       </c>
       <c r="AD2">
-        <v>75.59</v>
+        <v>76.16</v>
       </c>
       <c r="AE2">
-        <v>56.91</v>
+        <v>68.62</v>
       </c>
       <c r="AF2">
-        <v>353.59</v>
+        <v>358.95</v>
       </c>
       <c r="AH2">
-        <v>29176.06</v>
+        <v>29002.28</v>
       </c>
       <c r="AI2">
-        <v>26314.39</v>
+        <v>26261.16</v>
       </c>
       <c r="AJ2">
-        <v>28052.54</v>
+        <v>27987.81</v>
       </c>
       <c r="AK2" t="s">
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>62.7</v>
+        <v>63.42</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1141,10 +1141,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9646.5</v>
+        <v>9515.6</v>
       </c>
       <c r="E3">
-        <v>1.02</v>
+        <v>-1.36</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1153,43 +1153,43 @@
         <v>8890.35</v>
       </c>
       <c r="H3">
-        <v>-8.16</v>
+        <v>-9.4</v>
       </c>
       <c r="I3">
-        <v>8.51</v>
+        <v>7.03</v>
       </c>
       <c r="J3">
-        <v>2.16</v>
+        <v>0.15</v>
       </c>
       <c r="K3">
-        <v>-2.04</v>
+        <v>-3.56</v>
       </c>
       <c r="L3">
-        <v>-3</v>
+        <v>-3.44</v>
       </c>
       <c r="M3">
-        <v>8.24</v>
+        <v>5.89</v>
       </c>
       <c r="N3">
-        <v>11.33</v>
+        <v>11.31</v>
       </c>
       <c r="O3">
         <v>81</v>
       </c>
       <c r="Q3">
-        <v>9561.52</v>
+        <v>9564.33</v>
       </c>
       <c r="R3">
-        <v>9663.530000000001</v>
+        <v>9645.48</v>
       </c>
       <c r="S3">
-        <v>9784.559999999999</v>
+        <v>9778.35</v>
       </c>
       <c r="T3">
-        <v>9767.51</v>
+        <v>9769.1</v>
       </c>
       <c r="U3">
-        <v>-1.24</v>
+        <v>-2.59</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1204,31 +1204,31 @@
         <v>1</v>
       </c>
       <c r="Z3">
-        <v>47.65</v>
+        <v>40.19</v>
       </c>
       <c r="AA3">
-        <v>-74.81</v>
+        <v>-76.04000000000001</v>
       </c>
       <c r="AB3">
-        <v>-74.65000000000001</v>
+        <v>-74.93000000000001</v>
       </c>
       <c r="AC3">
-        <v>-0.16</v>
+        <v>-1.11</v>
       </c>
       <c r="AD3">
-        <v>73.62</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="AE3">
-        <v>63.86</v>
+        <v>70.31999999999999</v>
       </c>
       <c r="AF3">
-        <v>97.42</v>
+        <v>100.93</v>
       </c>
       <c r="AH3">
-        <v>9923.969999999999</v>
+        <v>9893.48</v>
       </c>
       <c r="AI3">
-        <v>9403.09</v>
+        <v>9397.48</v>
       </c>
       <c r="AJ3">
         <v>9750.9</v>
@@ -1237,7 +1237,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>30.75</v>
+        <v>29.61</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1251,10 +1251,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11546.05</v>
+        <v>11353.45</v>
       </c>
       <c r="E4">
-        <v>0.51</v>
+        <v>-1.67</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1263,43 +1263,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-8.65</v>
+        <v>-10.17</v>
       </c>
       <c r="I4">
-        <v>11.72</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="J4">
-        <v>1.62</v>
+        <v>-0.65</v>
       </c>
       <c r="K4">
-        <v>-3.86</v>
+        <v>-6.12</v>
       </c>
       <c r="L4">
-        <v>0.32</v>
+        <v>-2.07</v>
       </c>
       <c r="M4">
-        <v>-6.49</v>
+        <v>-8.59</v>
       </c>
       <c r="N4">
-        <v>9.49</v>
+        <v>9.15</v>
       </c>
       <c r="O4">
         <v>32</v>
       </c>
       <c r="Q4">
-        <v>11486.25</v>
+        <v>11471.34</v>
       </c>
       <c r="R4">
-        <v>11601.88</v>
+        <v>11571.14</v>
       </c>
       <c r="S4">
-        <v>11819.07</v>
+        <v>11813.44</v>
       </c>
       <c r="T4">
-        <v>11613.27</v>
+        <v>11607.74</v>
       </c>
       <c r="U4">
-        <v>-0.58</v>
+        <v>-2.19</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1314,31 +1314,31 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>43.12</v>
+        <v>33.99</v>
       </c>
       <c r="AA4">
-        <v>-116.15</v>
+        <v>-121.07</v>
       </c>
       <c r="AB4">
-        <v>-119.88</v>
+        <v>-120.12</v>
       </c>
       <c r="AC4">
-        <v>3.74</v>
+        <v>-0.95</v>
       </c>
       <c r="AD4">
-        <v>98.09999999999999</v>
+        <v>85.14</v>
       </c>
       <c r="AE4">
-        <v>89.3</v>
+        <v>91.69</v>
       </c>
       <c r="AF4">
-        <v>102.2</v>
+        <v>108.78</v>
       </c>
       <c r="AH4">
-        <v>11980.9</v>
+        <v>11923.88</v>
       </c>
       <c r="AI4">
-        <v>11222.85</v>
+        <v>11218.4</v>
       </c>
       <c r="AJ4">
         <v>11665.92</v>
@@ -1347,7 +1347,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>43.36</v>
+        <v>43.64</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1361,10 +1361,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>37759.75</v>
+        <v>37360.95</v>
       </c>
       <c r="E5">
-        <v>0.09</v>
+        <v>-1.06</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1373,43 +1373,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-9.09</v>
+        <v>-10.05</v>
       </c>
       <c r="I5">
-        <v>14.08</v>
+        <v>12.88</v>
       </c>
       <c r="J5">
-        <v>1.55</v>
+        <v>-0.06</v>
       </c>
       <c r="K5">
-        <v>-1.5</v>
+        <v>-2.48</v>
       </c>
       <c r="L5">
-        <v>-5.38</v>
+        <v>-5.74</v>
       </c>
       <c r="M5">
-        <v>7.49</v>
+        <v>5.42</v>
       </c>
       <c r="N5">
-        <v>11.52</v>
+        <v>11.46</v>
       </c>
       <c r="O5">
         <v>74</v>
       </c>
       <c r="Q5">
-        <v>37692.12</v>
+        <v>37687.96</v>
       </c>
       <c r="R5">
-        <v>37877.55</v>
+        <v>37840.6</v>
       </c>
       <c r="S5">
-        <v>38452.13</v>
+        <v>38411.73</v>
       </c>
       <c r="T5">
-        <v>37607.02</v>
+        <v>37616.53</v>
       </c>
       <c r="U5">
-        <v>0.41</v>
+        <v>-0.68</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1421,34 +1421,34 @@
         <v>79</v>
       </c>
       <c r="Y5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z5">
-        <v>44.01</v>
+        <v>37.13</v>
       </c>
       <c r="AA5">
-        <v>-227.6</v>
+        <v>-243.63</v>
       </c>
       <c r="AB5">
-        <v>-249.84</v>
+        <v>-248.59</v>
       </c>
       <c r="AC5">
-        <v>22.23</v>
+        <v>4.97</v>
       </c>
       <c r="AD5">
-        <v>75.59</v>
+        <v>63.69</v>
       </c>
       <c r="AE5">
-        <v>70.94</v>
+        <v>71.56</v>
       </c>
       <c r="AF5">
-        <v>368.98</v>
+        <v>377.91</v>
       </c>
       <c r="AH5">
-        <v>38518.71</v>
+        <v>38512.26</v>
       </c>
       <c r="AI5">
-        <v>37236.38</v>
+        <v>37168.94</v>
       </c>
       <c r="AJ5">
         <v>38269.93</v>
@@ -1457,7 +1457,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>18.16</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1471,10 +1471,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>46259.35</v>
+        <v>45759.35</v>
       </c>
       <c r="E6">
-        <v>1.32</v>
+        <v>-1.08</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1483,43 +1483,43 @@
         <v>44829.95</v>
       </c>
       <c r="H6">
-        <v>-18.52</v>
+        <v>-19.4</v>
       </c>
       <c r="I6">
-        <v>3.19</v>
+        <v>2.07</v>
       </c>
       <c r="J6">
-        <v>1.54</v>
+        <v>0.41</v>
       </c>
       <c r="K6">
-        <v>-2.67</v>
+        <v>-4.08</v>
       </c>
       <c r="L6">
-        <v>-5.76</v>
+        <v>-7.41</v>
       </c>
       <c r="M6">
-        <v>-18.2</v>
+        <v>-18.86</v>
       </c>
       <c r="N6">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>45771.5</v>
+        <v>45808.83</v>
       </c>
       <c r="R6">
-        <v>45890.35</v>
+        <v>45815.68</v>
       </c>
       <c r="S6">
-        <v>47559.85</v>
+        <v>47509.31</v>
       </c>
       <c r="T6">
-        <v>49965.15</v>
+        <v>49916.99</v>
       </c>
       <c r="U6">
-        <v>-7.42</v>
+        <v>-8.33</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1534,31 +1534,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>48.37</v>
+        <v>42.91</v>
       </c>
       <c r="AA6">
-        <v>-554.74</v>
+        <v>-516.2</v>
       </c>
       <c r="AB6">
-        <v>-711.77</v>
+        <v>-672.65</v>
       </c>
       <c r="AC6">
-        <v>157.03</v>
+        <v>156.46</v>
       </c>
       <c r="AD6">
-        <v>95.48999999999999</v>
+        <v>88.34</v>
       </c>
       <c r="AE6">
-        <v>95.31</v>
+        <v>92.27</v>
       </c>
       <c r="AF6">
-        <v>535.53</v>
+        <v>541.38</v>
       </c>
       <c r="AH6">
-        <v>47173.9</v>
+        <v>46927.78</v>
       </c>
       <c r="AI6">
-        <v>44606.8</v>
+        <v>44703.57</v>
       </c>
       <c r="AJ6">
         <v>46607.06</v>
@@ -1567,7 +1567,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>40.07</v>
+        <v>36.3</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1581,10 +1581,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25564.85</v>
+        <v>24954.15</v>
       </c>
       <c r="E7">
-        <v>0.58</v>
+        <v>-2.39</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1593,43 +1593,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-10.18</v>
+        <v>-12.33</v>
       </c>
       <c r="I7">
-        <v>8.69</v>
+        <v>6.09</v>
       </c>
       <c r="J7">
-        <v>1.2</v>
+        <v>-1.44</v>
       </c>
       <c r="K7">
-        <v>-2.27</v>
+        <v>-4.93</v>
       </c>
       <c r="L7">
-        <v>-4.38</v>
+        <v>-6.79</v>
       </c>
       <c r="M7">
-        <v>-3.14</v>
+        <v>-5.82</v>
       </c>
       <c r="N7">
-        <v>6.61</v>
+        <v>6.02</v>
       </c>
       <c r="O7">
         <v>26</v>
       </c>
       <c r="Q7">
-        <v>25467.17</v>
+        <v>25394.33</v>
       </c>
       <c r="R7">
-        <v>25739.36</v>
+        <v>25667.73</v>
       </c>
       <c r="S7">
-        <v>26242.25</v>
+        <v>26207.47</v>
       </c>
       <c r="T7">
-        <v>26504.19</v>
+        <v>26491.14</v>
       </c>
       <c r="U7">
-        <v>-3.54</v>
+        <v>-5.8</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1644,40 +1644,40 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>43.72</v>
+        <v>32.91</v>
       </c>
       <c r="AA7">
-        <v>-235.66</v>
+        <v>-265.64</v>
       </c>
       <c r="AB7">
-        <v>-245.7</v>
+        <v>-249.69</v>
       </c>
       <c r="AC7">
-        <v>10.04</v>
+        <v>-15.95</v>
       </c>
       <c r="AD7">
-        <v>89.22</v>
+        <v>69.78</v>
       </c>
       <c r="AE7">
-        <v>78.95</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="AF7">
-        <v>271.68</v>
+        <v>299.68</v>
       </c>
       <c r="AH7">
-        <v>26515.15</v>
+        <v>26456.28</v>
       </c>
       <c r="AI7">
-        <v>24963.56</v>
+        <v>24879.17</v>
       </c>
       <c r="AJ7">
-        <v>26066.31</v>
+        <v>25935.89</v>
       </c>
       <c r="AK7" t="s">
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>21.53</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1691,10 +1691,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>28334.05</v>
+        <v>28208.85</v>
       </c>
       <c r="E8">
-        <v>-0.87</v>
+        <v>-0.44</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1703,43 +1703,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-28.25</v>
+        <v>-28.56</v>
       </c>
       <c r="I8">
-        <v>9.949999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J8">
-        <v>-2.59</v>
+        <v>-3.25</v>
       </c>
       <c r="K8">
-        <v>-7.4</v>
+        <v>-8.33</v>
       </c>
       <c r="L8">
-        <v>2.78</v>
+        <v>3.21</v>
       </c>
       <c r="M8">
-        <v>-21.08</v>
+        <v>-22.1</v>
       </c>
       <c r="N8">
-        <v>-5.1</v>
+        <v>-5.33</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>28751.44</v>
+        <v>28562.09</v>
       </c>
       <c r="R8">
-        <v>29807.59</v>
+        <v>29702.09</v>
       </c>
       <c r="S8">
-        <v>30180.39</v>
+        <v>30173.93</v>
       </c>
       <c r="T8">
-        <v>31716.93</v>
+        <v>31670.27</v>
       </c>
       <c r="U8">
-        <v>-10.67</v>
+        <v>-10.93</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1754,40 +1754,40 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>33.03</v>
+        <v>32.01</v>
       </c>
       <c r="AA8">
-        <v>-505.74</v>
+        <v>-543.72</v>
       </c>
       <c r="AB8">
-        <v>-335.82</v>
+        <v>-377.4</v>
       </c>
       <c r="AC8">
-        <v>-169.92</v>
+        <v>-166.32</v>
       </c>
       <c r="AD8">
-        <v>5.13</v>
+        <v>1.32</v>
       </c>
       <c r="AE8">
-        <v>9.869999999999999</v>
+        <v>5.22</v>
       </c>
       <c r="AF8">
-        <v>641.34</v>
+        <v>620.83</v>
       </c>
       <c r="AH8">
-        <v>31854.93</v>
+        <v>31853.32</v>
       </c>
       <c r="AI8">
-        <v>27760.26</v>
+        <v>27550.86</v>
       </c>
       <c r="AJ8">
-        <v>30355.42</v>
+        <v>30124.5</v>
       </c>
       <c r="AK8" t="s">
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>27.76</v>
+        <v>29.19</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1801,10 +1801,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>16017.7</v>
+        <v>15809.8</v>
       </c>
       <c r="E9">
-        <v>0.8</v>
+        <v>-1.3</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1813,31 +1813,31 @@
         <v>15584.65</v>
       </c>
       <c r="H9">
-        <v>-3.87</v>
+        <v>-5.12</v>
       </c>
       <c r="I9">
-        <v>2.78</v>
+        <v>1.44</v>
       </c>
       <c r="J9">
-        <v>2.57</v>
+        <v>-0.11</v>
       </c>
       <c r="K9">
-        <v>-2.99</v>
+        <v>-4.64</v>
       </c>
       <c r="L9">
-        <v>0.83</v>
+        <v>-0.72</v>
       </c>
       <c r="N9">
-        <v>8.26</v>
+        <v>3.33</v>
       </c>
       <c r="Q9">
-        <v>15921.93</v>
+        <v>15918.56</v>
       </c>
       <c r="R9">
-        <v>16148.57</v>
+        <v>16110.68</v>
       </c>
       <c r="S9">
-        <v>16254.4</v>
+        <v>16252.35</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1849,31 +1849,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>45.11</v>
+        <v>38.1</v>
       </c>
       <c r="AA9">
-        <v>-132.15</v>
+        <v>-136.83</v>
       </c>
       <c r="AB9">
-        <v>-113.22</v>
+        <v>-117.94</v>
       </c>
       <c r="AC9">
-        <v>-18.93</v>
+        <v>-18.89</v>
       </c>
       <c r="AD9">
-        <v>88</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="AE9">
-        <v>70.23</v>
+        <v>81.89</v>
       </c>
       <c r="AF9">
-        <v>157.26</v>
+        <v>161.13</v>
       </c>
       <c r="AH9">
-        <v>16751.65</v>
+        <v>16697.93</v>
       </c>
       <c r="AI9">
-        <v>15545.5</v>
+        <v>15523.44</v>
       </c>
       <c r="AJ9">
         <v>16050.69</v>
@@ -1882,7 +1882,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>42.77</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1896,10 +1896,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>9095.049999999999</v>
+        <v>8944.85</v>
       </c>
       <c r="E10">
-        <v>0.82</v>
+        <v>-1.65</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1908,43 +1908,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-6.87</v>
+        <v>-8.41</v>
       </c>
       <c r="I10">
-        <v>6.24</v>
+        <v>4.48</v>
       </c>
       <c r="J10">
-        <v>2.09</v>
+        <v>-0.27</v>
       </c>
       <c r="K10">
-        <v>-2.65</v>
+        <v>-4.86</v>
       </c>
       <c r="L10">
+        <v>-5.45</v>
+      </c>
+      <c r="M10">
+        <v>-2.67</v>
+      </c>
+      <c r="N10">
+        <v>12.34</v>
+      </c>
+      <c r="O10">
+        <v>38</v>
+      </c>
+      <c r="Q10">
+        <v>9038.040000000001</v>
+      </c>
+      <c r="R10">
+        <v>9106.25</v>
+      </c>
+      <c r="S10">
+        <v>9276.93</v>
+      </c>
+      <c r="T10">
+        <v>9306.940000000001</v>
+      </c>
+      <c r="U10">
         <v>-3.89</v>
-      </c>
-      <c r="M10">
-        <v>-0.03</v>
-      </c>
-      <c r="N10">
-        <v>12.62</v>
-      </c>
-      <c r="O10">
-        <v>44</v>
-      </c>
-      <c r="Q10">
-        <v>9042.93</v>
-      </c>
-      <c r="R10">
-        <v>9123.450000000001</v>
-      </c>
-      <c r="S10">
-        <v>9284.790000000001</v>
-      </c>
-      <c r="T10">
-        <v>9310.15</v>
-      </c>
-      <c r="U10">
-        <v>-2.31</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1959,31 +1959,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>44.59</v>
+        <v>35.42</v>
       </c>
       <c r="AA10">
-        <v>-79.68000000000001</v>
+        <v>-84.04000000000001</v>
       </c>
       <c r="AB10">
-        <v>-82.3</v>
+        <v>-82.65000000000001</v>
       </c>
       <c r="AC10">
-        <v>2.62</v>
+        <v>-1.39</v>
       </c>
       <c r="AD10">
-        <v>92.86</v>
+        <v>81.63</v>
       </c>
       <c r="AE10">
-        <v>88.97</v>
+        <v>89.12</v>
       </c>
       <c r="AF10">
-        <v>82.83</v>
+        <v>87.64</v>
       </c>
       <c r="AH10">
-        <v>9341.299999999999</v>
+        <v>9323.43</v>
       </c>
       <c r="AI10">
-        <v>8905.6</v>
+        <v>8889.07</v>
       </c>
       <c r="AJ10">
         <v>9179.950000000001</v>
@@ -1992,7 +1992,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>47.68</v>
+        <v>48.24</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2006,10 +2006,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1566.85</v>
+        <v>1554.25</v>
       </c>
       <c r="E11">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
       <c r="F11">
         <v>1632.5</v>
@@ -2018,43 +2018,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-4.02</v>
+        <v>-4.79</v>
       </c>
       <c r="I11">
-        <v>25.01</v>
+        <v>24.01</v>
       </c>
       <c r="J11">
-        <v>3.42</v>
+        <v>1.38</v>
       </c>
       <c r="K11">
-        <v>-2.27</v>
+        <v>-3.46</v>
       </c>
       <c r="L11">
-        <v>3.13</v>
+        <v>2.94</v>
       </c>
       <c r="M11">
-        <v>-2.9</v>
+        <v>-4.51</v>
       </c>
       <c r="N11">
-        <v>-6.28</v>
+        <v>-6.31</v>
       </c>
       <c r="O11">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="Q11">
-        <v>1556.88</v>
+        <v>1561.1</v>
       </c>
       <c r="R11">
-        <v>1552.64</v>
+        <v>1549.8</v>
       </c>
       <c r="S11">
-        <v>1558.51</v>
+        <v>1559.53</v>
       </c>
       <c r="T11">
-        <v>1452.87</v>
+        <v>1453.35</v>
       </c>
       <c r="U11">
-        <v>7.84</v>
+        <v>6.94</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2069,31 +2069,31 @@
         <v>2</v>
       </c>
       <c r="Z11">
-        <v>53.24</v>
+        <v>50.08</v>
       </c>
       <c r="AA11">
-        <v>-3.08</v>
+        <v>-2.57</v>
       </c>
       <c r="AB11">
-        <v>-5.93</v>
+        <v>-5.26</v>
       </c>
       <c r="AC11">
-        <v>2.86</v>
+        <v>2.69</v>
       </c>
       <c r="AD11">
-        <v>96.04000000000001</v>
+        <v>85.86</v>
       </c>
       <c r="AE11">
-        <v>91.87</v>
+        <v>93.95999999999999</v>
       </c>
       <c r="AF11">
-        <v>29.73</v>
+        <v>29.6</v>
       </c>
       <c r="AH11">
-        <v>1610.36</v>
+        <v>1600.61</v>
       </c>
       <c r="AI11">
-        <v>1494.91</v>
+        <v>1498.99</v>
       </c>
       <c r="AJ11">
         <v>1604.15</v>
@@ -2102,7 +2102,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>32.97</v>
+        <v>29.12</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2116,10 +2116,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13302.35</v>
+        <v>13041.95</v>
       </c>
       <c r="E12">
-        <v>2.4</v>
+        <v>-1.96</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2128,43 +2128,43 @@
         <v>9888.25</v>
       </c>
       <c r="H12">
-        <v>-3.03</v>
+        <v>-4.93</v>
       </c>
       <c r="I12">
-        <v>34.53</v>
+        <v>31.89</v>
       </c>
       <c r="J12">
-        <v>4.42</v>
+        <v>1.43</v>
       </c>
       <c r="K12">
-        <v>-0.59</v>
+        <v>-2.47</v>
       </c>
       <c r="L12">
-        <v>5.42</v>
+        <v>4.79</v>
       </c>
       <c r="M12">
-        <v>34.49</v>
+        <v>30.77</v>
       </c>
       <c r="N12">
-        <v>18.83</v>
+        <v>18.86</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13035.29</v>
+        <v>13071.99</v>
       </c>
       <c r="R12">
-        <v>13155.79</v>
+        <v>13130.8</v>
       </c>
       <c r="S12">
-        <v>12970.81</v>
+        <v>12980.91</v>
       </c>
       <c r="T12">
-        <v>12297.86</v>
+        <v>12311.49</v>
       </c>
       <c r="U12">
-        <v>8.17</v>
+        <v>5.93</v>
       </c>
       <c r="V12" t="s">
         <v>80</v>
@@ -2179,31 +2179,31 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>56.5</v>
+        <v>49.21</v>
       </c>
       <c r="AA12">
-        <v>-9.43</v>
+        <v>-10.66</v>
       </c>
       <c r="AB12">
-        <v>1.98</v>
+        <v>-0.55</v>
       </c>
       <c r="AC12">
-        <v>-11.4</v>
+        <v>-10.11</v>
       </c>
       <c r="AD12">
-        <v>61.61</v>
+        <v>64.45</v>
       </c>
       <c r="AE12">
-        <v>51.36</v>
+        <v>58.99</v>
       </c>
       <c r="AF12">
-        <v>221.23</v>
+        <v>225.22</v>
       </c>
       <c r="AH12">
-        <v>13632.94</v>
+        <v>13574</v>
       </c>
       <c r="AI12">
-        <v>12678.64</v>
+        <v>12687.61</v>
       </c>
       <c r="AJ12">
         <v>13387.91</v>
@@ -2212,7 +2212,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>21.66</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2226,10 +2226,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9637.6</v>
+        <v>9555.450000000001</v>
       </c>
       <c r="E13">
-        <v>0.22</v>
+        <v>-0.85</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2238,43 +2238,43 @@
         <v>9428.700000000001</v>
       </c>
       <c r="H13">
-        <v>-10.48</v>
+        <v>-11.25</v>
       </c>
       <c r="I13">
-        <v>2.22</v>
+        <v>1.34</v>
       </c>
       <c r="J13">
-        <v>1.51</v>
+        <v>0.01</v>
       </c>
       <c r="K13">
-        <v>-1.47</v>
+        <v>-2.47</v>
       </c>
       <c r="L13">
-        <v>-4.48</v>
+        <v>-4</v>
       </c>
       <c r="M13">
-        <v>-0.52</v>
+        <v>-2.22</v>
       </c>
       <c r="N13">
-        <v>19.96</v>
+        <v>20.04</v>
       </c>
       <c r="O13">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q13">
-        <v>9601.93</v>
+        <v>9602.15</v>
       </c>
       <c r="R13">
-        <v>9656.6</v>
+        <v>9647.98</v>
       </c>
       <c r="S13">
-        <v>9796.040000000001</v>
+        <v>9788.85</v>
       </c>
       <c r="T13">
-        <v>10018.39</v>
+        <v>10017.52</v>
       </c>
       <c r="U13">
-        <v>-3.8</v>
+        <v>-4.61</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2289,31 +2289,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>44.55</v>
+        <v>38.15</v>
       </c>
       <c r="AA13">
-        <v>-59.23</v>
+        <v>-60.6</v>
       </c>
       <c r="AB13">
-        <v>-63.68</v>
+        <v>-63.07</v>
       </c>
       <c r="AC13">
-        <v>4.45</v>
+        <v>2.47</v>
       </c>
       <c r="AD13">
-        <v>81.68000000000001</v>
+        <v>77.38</v>
       </c>
       <c r="AE13">
-        <v>73.62</v>
+        <v>77.94</v>
       </c>
       <c r="AF13">
-        <v>88.95</v>
+        <v>90.13</v>
       </c>
       <c r="AH13">
-        <v>9814.139999999999</v>
+        <v>9807.959999999999</v>
       </c>
       <c r="AI13">
-        <v>9499.059999999999</v>
+        <v>9488.01</v>
       </c>
       <c r="AJ13">
         <v>9761.77</v>
@@ -2322,7 +2322,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>31.04</v>
+        <v>31.23</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2336,55 +2336,55 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8365.450000000001</v>
+        <v>8271.15</v>
       </c>
       <c r="E14">
-        <v>1.14</v>
+        <v>-1.13</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
       </c>
       <c r="G14">
-        <v>7129.65</v>
+        <v>7261.45</v>
       </c>
       <c r="H14">
-        <v>-15.33</v>
+        <v>-16.28</v>
       </c>
       <c r="I14">
-        <v>17.33</v>
+        <v>13.9</v>
       </c>
       <c r="J14">
-        <v>1.08</v>
+        <v>0.1</v>
       </c>
       <c r="K14">
-        <v>-2.04</v>
+        <v>-3.86</v>
       </c>
       <c r="L14">
-        <v>-3.05</v>
+        <v>-4.23</v>
       </c>
       <c r="M14">
-        <v>17.83</v>
+        <v>16.01</v>
       </c>
       <c r="N14">
-        <v>28.35</v>
+        <v>28.54</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8305.9</v>
+        <v>8307.57</v>
       </c>
       <c r="R14">
-        <v>8423.889999999999</v>
+        <v>8403.98</v>
       </c>
       <c r="S14">
-        <v>8486.219999999999</v>
+        <v>8483.91</v>
       </c>
       <c r="T14">
-        <v>8590.950000000001</v>
+        <v>8589.73</v>
       </c>
       <c r="U14">
-        <v>-2.62</v>
+        <v>-3.71</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2399,31 +2399,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>46.25</v>
+        <v>41.03</v>
       </c>
       <c r="AA14">
-        <v>-69.67</v>
+        <v>-70.68000000000001</v>
       </c>
       <c r="AB14">
-        <v>-61.33</v>
+        <v>-63.2</v>
       </c>
       <c r="AC14">
-        <v>-8.34</v>
+        <v>-7.47</v>
       </c>
       <c r="AD14">
-        <v>68.17</v>
+        <v>70.48</v>
       </c>
       <c r="AE14">
-        <v>59.3</v>
+        <v>65.31</v>
       </c>
       <c r="AF14">
-        <v>119.36</v>
+        <v>119.21</v>
       </c>
       <c r="AH14">
-        <v>8703.469999999999</v>
+        <v>8666.09</v>
       </c>
       <c r="AI14">
-        <v>8144.32</v>
+        <v>8141.86</v>
       </c>
       <c r="AJ14">
         <v>8626.549999999999</v>
@@ -2432,7 +2432,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>25.99</v>
+        <v>25.64</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2446,10 +2446,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>27152.1</v>
+        <v>27028.7</v>
       </c>
       <c r="E15">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2458,43 +2458,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-0.13</v>
+        <v>-0.58</v>
       </c>
       <c r="I15">
-        <v>26.56</v>
+        <v>25.98</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>1.69</v>
       </c>
       <c r="K15">
-        <v>3.09</v>
+        <v>1.75</v>
       </c>
       <c r="L15">
-        <v>8.529999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="M15">
-        <v>22.31</v>
+        <v>21.4</v>
       </c>
       <c r="N15">
-        <v>13.56</v>
+        <v>13.6</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>26874.44</v>
+        <v>26964.33</v>
       </c>
       <c r="R15">
-        <v>26720.33</v>
+        <v>26740.45</v>
       </c>
       <c r="S15">
-        <v>26463.35</v>
+        <v>26483.85</v>
       </c>
       <c r="T15">
-        <v>24040.51</v>
+        <v>24061.13</v>
       </c>
       <c r="U15">
-        <v>12.94</v>
+        <v>12.33</v>
       </c>
       <c r="V15" t="s">
         <v>80</v>
@@ -2509,40 +2509,40 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>61.74</v>
+        <v>58.57</v>
       </c>
       <c r="AA15">
-        <v>118.2</v>
+        <v>132.11</v>
       </c>
       <c r="AB15">
-        <v>87.68000000000001</v>
+        <v>96.56999999999999</v>
       </c>
       <c r="AC15">
-        <v>30.51</v>
+        <v>35.54</v>
       </c>
       <c r="AD15">
-        <v>95.16</v>
+        <v>90.09</v>
       </c>
       <c r="AE15">
-        <v>76.72</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="AF15">
-        <v>331.12</v>
+        <v>324.67</v>
       </c>
       <c r="AH15">
-        <v>27267.85</v>
+        <v>27302.79</v>
       </c>
       <c r="AI15">
-        <v>26172.81</v>
+        <v>26178.1</v>
       </c>
       <c r="AJ15">
-        <v>26048.62</v>
+        <v>26160.58</v>
       </c>
       <c r="AK15" t="s">
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>24.86</v>
+        <v>26.43</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2556,10 +2556,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>871</v>
+        <v>861.4</v>
       </c>
       <c r="E16">
-        <v>1.1</v>
+        <v>-1.1</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2568,43 +2568,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-10.08</v>
+        <v>-11.07</v>
       </c>
       <c r="I16">
-        <v>33.76</v>
+        <v>32.29</v>
       </c>
       <c r="J16">
-        <v>5.92</v>
+        <v>3.25</v>
       </c>
       <c r="K16">
-        <v>-5.03</v>
+        <v>-6.15</v>
       </c>
       <c r="L16">
-        <v>5.76</v>
+        <v>4.25</v>
       </c>
       <c r="M16">
-        <v>-3.83</v>
+        <v>-5.89</v>
       </c>
       <c r="N16">
-        <v>12.02</v>
+        <v>11.44</v>
       </c>
       <c r="O16">
         <v>62</v>
       </c>
       <c r="Q16">
-        <v>852.96</v>
+        <v>858.39</v>
       </c>
       <c r="R16">
-        <v>876</v>
+        <v>873.5599999999999</v>
       </c>
       <c r="S16">
-        <v>894.16</v>
+        <v>893.08</v>
       </c>
       <c r="T16">
-        <v>828.03</v>
+        <v>827.87</v>
       </c>
       <c r="U16">
-        <v>5.19</v>
+        <v>4.05</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2619,31 +2619,31 @@
         <v>2</v>
       </c>
       <c r="Z16">
-        <v>48.91</v>
+        <v>45.65</v>
       </c>
       <c r="AA16">
-        <v>-12.64</v>
+        <v>-11.65</v>
       </c>
       <c r="AB16">
-        <v>-11.8</v>
+        <v>-11.77</v>
       </c>
       <c r="AC16">
-        <v>-0.84</v>
+        <v>0.11</v>
       </c>
       <c r="AD16">
-        <v>63.92</v>
+        <v>70.53</v>
       </c>
       <c r="AE16">
-        <v>53.09</v>
+        <v>62.6</v>
       </c>
       <c r="AF16">
-        <v>18.77</v>
+        <v>18.68</v>
       </c>
       <c r="AH16">
-        <v>938.9400000000001</v>
+        <v>934.6799999999999</v>
       </c>
       <c r="AI16">
-        <v>813.05</v>
+        <v>812.4400000000001</v>
       </c>
       <c r="AJ16">
         <v>877.53</v>
@@ -2652,7 +2652,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>29.51</v>
+        <v>26.67</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2666,10 +2666,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30064.25</v>
+        <v>29539.95</v>
       </c>
       <c r="E17">
-        <v>0.31</v>
+        <v>-1.74</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2678,43 +2678,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-11.84</v>
+        <v>-13.38</v>
       </c>
       <c r="I17">
-        <v>6</v>
+        <v>4.15</v>
       </c>
       <c r="J17">
-        <v>0.88</v>
+        <v>-0.98</v>
       </c>
       <c r="K17">
-        <v>-2.57</v>
+        <v>-4.71</v>
       </c>
       <c r="L17">
-        <v>-2.14</v>
+        <v>-3.77</v>
       </c>
       <c r="M17">
-        <v>-7.69</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="N17">
-        <v>3.67</v>
+        <v>3.21</v>
       </c>
       <c r="O17">
         <v>19</v>
       </c>
       <c r="Q17">
-        <v>30000.56</v>
+        <v>29941.91</v>
       </c>
       <c r="R17">
-        <v>30284.25</v>
+        <v>30216.28</v>
       </c>
       <c r="S17">
-        <v>30860.96</v>
+        <v>30828.76</v>
       </c>
       <c r="T17">
-        <v>31396.02</v>
+        <v>31375.07</v>
       </c>
       <c r="U17">
-        <v>-4.24</v>
+        <v>-5.85</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2729,40 +2729,40 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>40.44</v>
+        <v>30.27</v>
       </c>
       <c r="AA17">
-        <v>-261.62</v>
+        <v>-285.86</v>
       </c>
       <c r="AB17">
-        <v>-270.97</v>
+        <v>-273.95</v>
       </c>
       <c r="AC17">
-        <v>9.35</v>
+        <v>-11.91</v>
       </c>
       <c r="AD17">
-        <v>89.89</v>
+        <v>74.62</v>
       </c>
       <c r="AE17">
-        <v>78.56</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="AF17">
-        <v>257.11</v>
+        <v>280.08</v>
       </c>
       <c r="AH17">
-        <v>31102.74</v>
+        <v>31045.4</v>
       </c>
       <c r="AI17">
-        <v>29465.76</v>
+        <v>29387.16</v>
       </c>
       <c r="AJ17">
-        <v>30589.09</v>
+        <v>30478.6</v>
       </c>
       <c r="AK17" t="s">
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>24.86</v>
+        <v>27.81</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2776,10 +2776,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16868.15</v>
+        <v>16757.2</v>
       </c>
       <c r="E18">
-        <v>0.89</v>
+        <v>-0.66</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2788,31 +2788,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-0.43</v>
+        <v>-1.09</v>
       </c>
       <c r="I18">
-        <v>9.51</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="J18">
-        <v>3.65</v>
+        <v>1.38</v>
       </c>
       <c r="K18">
-        <v>2.74</v>
+        <v>0.96</v>
       </c>
       <c r="L18">
-        <v>5.73</v>
+        <v>4.97</v>
       </c>
       <c r="N18">
-        <v>33.4</v>
+        <v>29.98</v>
       </c>
       <c r="Q18">
-        <v>16705.62</v>
+        <v>16751.23</v>
       </c>
       <c r="R18">
-        <v>16606.61</v>
+        <v>16615.13</v>
       </c>
       <c r="S18">
-        <v>16569.03</v>
+        <v>16574.01</v>
       </c>
       <c r="V18" t="s">
         <v>80</v>
@@ -2824,31 +2824,31 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>60.65</v>
+        <v>56.06</v>
       </c>
       <c r="AA18">
-        <v>42.6</v>
+        <v>49.99</v>
       </c>
       <c r="AB18">
-        <v>12.96</v>
+        <v>20.37</v>
       </c>
       <c r="AC18">
-        <v>29.64</v>
+        <v>29.63</v>
       </c>
       <c r="AD18">
-        <v>94.70999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="AE18">
-        <v>77.79000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="AF18">
-        <v>194.33</v>
+        <v>191.03</v>
       </c>
       <c r="AH18">
-        <v>16951.22</v>
+        <v>16966.05</v>
       </c>
       <c r="AI18">
-        <v>16261.99</v>
+        <v>16264.22</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2857,7 +2857,7 @@
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>22.76</v>
+        <v>24.16</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2871,10 +2871,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9461.299999999999</v>
+        <v>9361.700000000001</v>
       </c>
       <c r="E19">
-        <v>-0.11</v>
+        <v>-1.05</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2883,31 +2883,31 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-5.37</v>
+        <v>-6.37</v>
       </c>
       <c r="I19">
-        <v>5.18</v>
+        <v>4.07</v>
       </c>
       <c r="J19">
-        <v>3.64</v>
+        <v>0.97</v>
       </c>
       <c r="K19">
-        <v>-2.86</v>
+        <v>-4.11</v>
       </c>
       <c r="L19">
-        <v>-0.01</v>
+        <v>-0.37</v>
       </c>
       <c r="N19">
-        <v>19.61</v>
+        <v>15.05</v>
       </c>
       <c r="Q19">
-        <v>9394.67</v>
+        <v>9412.629999999999</v>
       </c>
       <c r="R19">
-        <v>9603.879999999999</v>
+        <v>9584.719999999999</v>
       </c>
       <c r="S19">
-        <v>9565.57</v>
+        <v>9566.18</v>
       </c>
       <c r="V19" t="s">
         <v>80</v>
@@ -2919,31 +2919,31 @@
         <v>1</v>
       </c>
       <c r="Z19">
-        <v>45.81</v>
+        <v>42.27</v>
       </c>
       <c r="AA19">
-        <v>-70.28</v>
+        <v>-75.25</v>
       </c>
       <c r="AB19">
-        <v>-37.42</v>
+        <v>-44.98</v>
       </c>
       <c r="AC19">
-        <v>-32.86</v>
+        <v>-30.27</v>
       </c>
       <c r="AD19">
-        <v>39.22</v>
+        <v>37.68</v>
       </c>
       <c r="AE19">
-        <v>33.82</v>
+        <v>37.29</v>
       </c>
       <c r="AF19">
-        <v>165.48</v>
+        <v>162.31</v>
       </c>
       <c r="AH19">
-        <v>10086.9</v>
+        <v>10074.53</v>
       </c>
       <c r="AI19">
-        <v>9120.860000000001</v>
+        <v>9094.91</v>
       </c>
       <c r="AJ19">
         <v>9616.870000000001</v>
@@ -2952,7 +2952,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>25.32</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2966,10 +2966,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>11005.2</v>
+        <v>10869.85</v>
       </c>
       <c r="E20">
-        <v>0.42</v>
+        <v>-1.23</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -2978,31 +2978,31 @@
         <v>10796.4</v>
       </c>
       <c r="H20">
-        <v>-3.2</v>
+        <v>-4.39</v>
       </c>
       <c r="I20">
-        <v>1.93</v>
+        <v>0.68</v>
       </c>
       <c r="J20">
-        <v>1.22</v>
+        <v>0.12</v>
       </c>
       <c r="K20">
-        <v>-1.71</v>
+        <v>-3.08</v>
       </c>
       <c r="L20">
-        <v>-2.1</v>
+        <v>-2.45</v>
       </c>
       <c r="N20">
-        <v>-0.23</v>
+        <v>-4.47</v>
       </c>
       <c r="Q20">
-        <v>10955.28</v>
+        <v>10957.78</v>
       </c>
       <c r="R20">
-        <v>11032.99</v>
+        <v>11019.01</v>
       </c>
       <c r="S20">
-        <v>11143.02</v>
+        <v>11136.84</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3014,31 +3014,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>46.7</v>
+        <v>38.75</v>
       </c>
       <c r="AA20">
-        <v>-60.26</v>
+        <v>-65.01000000000001</v>
       </c>
       <c r="AB20">
-        <v>-60.08</v>
+        <v>-61.07</v>
       </c>
       <c r="AC20">
-        <v>-0.18</v>
+        <v>-3.94</v>
       </c>
       <c r="AD20">
-        <v>76.62</v>
+        <v>67.23</v>
       </c>
       <c r="AE20">
-        <v>67.59999999999999</v>
+        <v>71.19</v>
       </c>
       <c r="AF20">
-        <v>118.81</v>
+        <v>122.31</v>
       </c>
       <c r="AH20">
-        <v>11257.03</v>
+        <v>11247.32</v>
       </c>
       <c r="AI20">
-        <v>10808.94</v>
+        <v>10790.7</v>
       </c>
       <c r="AJ20">
         <v>11213.36</v>
@@ -3047,7 +3047,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>28.09</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3061,10 +3061,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27363.35</v>
+        <v>26763.95</v>
       </c>
       <c r="E21">
-        <v>0.28</v>
+        <v>-2.19</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3073,43 +3073,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6.25</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="I21">
-        <v>13.33</v>
+        <v>10.85</v>
       </c>
       <c r="J21">
-        <v>0.29</v>
+        <v>-1.49</v>
       </c>
       <c r="K21">
-        <v>-0.5</v>
+        <v>-2.49</v>
       </c>
       <c r="L21">
-        <v>-3.23</v>
+        <v>-5.5</v>
       </c>
       <c r="M21">
-        <v>2.41</v>
+        <v>-0.61</v>
       </c>
       <c r="N21">
-        <v>6.7</v>
+        <v>6.18</v>
       </c>
       <c r="O21">
         <v>50</v>
       </c>
       <c r="Q21">
-        <v>27295.73</v>
+        <v>27214.68</v>
       </c>
       <c r="R21">
-        <v>27509.25</v>
+        <v>27460.8</v>
       </c>
       <c r="S21">
-        <v>27697.69</v>
+        <v>27672.92</v>
       </c>
       <c r="T21">
-        <v>27561.18</v>
+        <v>27552.21</v>
       </c>
       <c r="U21">
-        <v>-0.72</v>
+        <v>-2.86</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3124,40 +3124,40 @@
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>47.16</v>
+        <v>35.63</v>
       </c>
       <c r="AA21">
-        <v>-100.43</v>
+        <v>-140.73</v>
       </c>
       <c r="AB21">
-        <v>-93.93000000000001</v>
+        <v>-103.29</v>
       </c>
       <c r="AC21">
-        <v>-6.5</v>
+        <v>-37.44</v>
       </c>
       <c r="AD21">
-        <v>51.59</v>
+        <v>33.21</v>
       </c>
       <c r="AE21">
-        <v>42.79</v>
+        <v>42.57</v>
       </c>
       <c r="AF21">
-        <v>282.47</v>
+        <v>308.78</v>
       </c>
       <c r="AH21">
-        <v>28038.23</v>
+        <v>28074.28</v>
       </c>
       <c r="AI21">
-        <v>26980.27</v>
+        <v>26847.32</v>
       </c>
       <c r="AJ21">
-        <v>28092.43</v>
+        <v>27796.52</v>
       </c>
       <c r="AK21" t="s">
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>16.57</v>
+        <v>21.59</v>
       </c>
     </row>
   </sheetData>
@@ -3298,7 +3298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F146"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3390,13 +3390,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="6">
-        <v>-7.56</v>
+        <v>-6.68</v>
       </c>
       <c r="D7" s="6">
-        <v>-6.68</v>
+        <v>-8.51</v>
       </c>
       <c r="E7" s="7">
-        <v>0.88</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -3407,13 +3407,13 @@
         <v>10</v>
       </c>
       <c r="C8" s="6">
-        <v>-2.39</v>
+        <v>-2.04</v>
       </c>
       <c r="D8" s="6">
-        <v>-2.04</v>
+        <v>-3.56</v>
       </c>
       <c r="E8" s="7">
-        <v>0.35</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -3424,13 +3424,13 @@
         <v>10</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.81</v>
+        <v>-3.86</v>
       </c>
       <c r="D9" s="6">
-        <v>-3.86</v>
+        <v>-6.12</v>
       </c>
       <c r="E9" s="7">
-        <v>0.95</v>
+        <v>-2.26</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3441,13 +3441,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="6">
-        <v>-1.11</v>
+        <v>-1.5</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.5</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-0.39</v>
+        <v>-2.48</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3458,13 +3458,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.61</v>
+        <v>-2.67</v>
       </c>
       <c r="D11" s="6">
-        <v>-2.67</v>
+        <v>-4.08</v>
       </c>
       <c r="E11" s="7">
-        <v>1.94</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3475,13 +3475,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-3</v>
+        <v>-2.27</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.27</v>
+        <v>-4.93</v>
       </c>
       <c r="E12" s="7">
-        <v>0.73</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3492,13 +3492,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.39</v>
+        <v>-7.4</v>
       </c>
       <c r="D13" s="6">
-        <v>-7.4</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-1.01</v>
+        <v>-8.33</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3509,13 +3509,13 @@
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-3.76</v>
+        <v>-2.99</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.99</v>
+        <v>-4.64</v>
       </c>
       <c r="E14" s="7">
-        <v>0.77</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3526,13 +3526,13 @@
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.51</v>
+        <v>-2.65</v>
       </c>
       <c r="D15" s="6">
-        <v>-2.65</v>
+        <v>-4.86</v>
       </c>
       <c r="E15" s="7">
-        <v>0.86</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3543,13 +3543,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.88</v>
+        <v>-2.27</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.27</v>
+        <v>-3.46</v>
       </c>
       <c r="E16" s="7">
-        <v>0.61</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3560,13 +3560,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-0.54</v>
+        <v>-0.59</v>
       </c>
       <c r="D17" s="6">
-        <v>-0.59</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.05</v>
+        <v>-2.47</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.88</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3577,13 +3577,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-1.3</v>
+        <v>-1.47</v>
       </c>
       <c r="D18" s="6">
-        <v>-1.47</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.17</v>
+        <v>-2.47</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3594,13 +3594,13 @@
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-4.01</v>
+        <v>-2.04</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.04</v>
+        <v>-3.86</v>
       </c>
       <c r="E19" s="7">
-        <v>1.97</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3611,13 +3611,13 @@
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>2.09</v>
+        <v>3.09</v>
       </c>
       <c r="D20" s="6">
-        <v>3.09</v>
+        <v>1.75</v>
       </c>
       <c r="E20" s="7">
-        <v>1</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3628,13 +3628,13 @@
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-5.12</v>
+        <v>-5.03</v>
       </c>
       <c r="D21" s="6">
-        <v>-5.03</v>
+        <v>-6.15</v>
       </c>
       <c r="E21" s="7">
-        <v>0.09</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3645,13 +3645,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.98</v>
+        <v>-2.57</v>
       </c>
       <c r="D22" s="6">
-        <v>-2.57</v>
+        <v>-4.71</v>
       </c>
       <c r="E22" s="7">
-        <v>0.41</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3662,13 +3662,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>1.55</v>
+        <v>2.74</v>
       </c>
       <c r="D23" s="6">
-        <v>2.74</v>
+        <v>0.96</v>
       </c>
       <c r="E23" s="7">
-        <v>1.19</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3679,13 +3679,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.36</v>
+        <v>-2.86</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.86</v>
+        <v>-4.11</v>
       </c>
       <c r="E24" s="7">
-        <v>0.5</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3696,13 +3696,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-1.96</v>
+        <v>-1.71</v>
       </c>
       <c r="D25" s="6">
-        <v>-1.71</v>
+        <v>-3.08</v>
       </c>
       <c r="E25" s="7">
-        <v>0.25</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3713,13 +3713,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-0.59</v>
+        <v>-0.5</v>
       </c>
       <c r="D26" s="6">
-        <v>-0.5</v>
+        <v>-2.49</v>
       </c>
       <c r="E26" s="7">
-        <v>0.09</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3730,13 +3730,13 @@
         <v>9</v>
       </c>
       <c r="C27" s="6">
-        <v>1.23</v>
+        <v>0.98</v>
       </c>
       <c r="D27" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.25</v>
+        <v>-1.58</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.56</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3747,13 +3747,13 @@
         <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>1.51</v>
+        <v>2.16</v>
       </c>
       <c r="D28" s="6">
-        <v>2.16</v>
+        <v>0.15</v>
       </c>
       <c r="E28" s="7">
-        <v>0.65</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3764,13 +3764,13 @@
         <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>1.81</v>
+        <v>1.62</v>
       </c>
       <c r="D29" s="6">
-        <v>1.62</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.19</v>
+        <v>-0.65</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3781,13 +3781,13 @@
         <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="D30" s="6">
-        <v>1.55</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.01</v>
+        <v>-0.06</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3798,13 +3798,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="D31" s="6">
-        <v>1.54</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-0.31</v>
+        <v>0.41</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3815,13 +3815,13 @@
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="D32" s="6">
-        <v>1.2</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-0.16</v>
+        <v>-1.44</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.64</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3832,13 +3832,13 @@
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-3.29</v>
+        <v>-2.59</v>
       </c>
       <c r="D33" s="6">
-        <v>-2.59</v>
+        <v>-3.25</v>
       </c>
       <c r="E33" s="7">
-        <v>0.7</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3849,13 +3849,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>1.96</v>
+        <v>2.57</v>
       </c>
       <c r="D34" s="6">
-        <v>2.57</v>
+        <v>-0.11</v>
       </c>
       <c r="E34" s="7">
-        <v>0.61</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3866,13 +3866,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>1.24</v>
+        <v>2.09</v>
       </c>
       <c r="D35" s="6">
-        <v>2.09</v>
+        <v>-0.27</v>
       </c>
       <c r="E35" s="7">
-        <v>0.85</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3883,13 +3883,13 @@
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>4.71</v>
+        <v>3.42</v>
       </c>
       <c r="D36" s="6">
-        <v>3.42</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-1.29</v>
+        <v>1.38</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-2.04</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3900,13 +3900,13 @@
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>2.54</v>
+        <v>4.42</v>
       </c>
       <c r="D37" s="6">
-        <v>4.42</v>
+        <v>1.43</v>
       </c>
       <c r="E37" s="7">
-        <v>1.88</v>
+        <v>-2.99</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3917,13 +3917,13 @@
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="D38" s="6">
-        <v>1.51</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.5</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3934,13 +3934,13 @@
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="D39" s="6">
-        <v>1.08</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-0.3</v>
+        <v>0.1</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3951,13 +3951,13 @@
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>2.75</v>
+        <v>3.85</v>
       </c>
       <c r="D40" s="6">
-        <v>3.85</v>
+        <v>1.69</v>
       </c>
       <c r="E40" s="7">
-        <v>1.1</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -3968,13 +3968,13 @@
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>5.8</v>
+        <v>5.92</v>
       </c>
       <c r="D41" s="6">
-        <v>5.92</v>
+        <v>3.25</v>
       </c>
       <c r="E41" s="7">
-        <v>0.12</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -3985,13 +3985,13 @@
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="D42" s="6">
-        <v>0.88</v>
+        <v>-0.98</v>
       </c>
       <c r="E42" s="7">
-        <v>0.07000000000000001</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -4002,13 +4002,13 @@
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>2.58</v>
+        <v>3.65</v>
       </c>
       <c r="D43" s="6">
-        <v>3.65</v>
+        <v>1.38</v>
       </c>
       <c r="E43" s="7">
-        <v>1.07</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -4019,13 +4019,13 @@
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>3.58</v>
+        <v>3.64</v>
       </c>
       <c r="D44" s="6">
-        <v>3.64</v>
+        <v>0.97</v>
       </c>
       <c r="E44" s="7">
-        <v>0.06</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4036,13 +4036,13 @@
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="D45" s="6">
-        <v>1.22</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.29</v>
+        <v>0.12</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -4053,13 +4053,13 @@
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>0.8</v>
+        <v>0.29</v>
       </c>
       <c r="D46" s="6">
-        <v>0.29</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.51</v>
+        <v>-1.49</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -4070,13 +4070,13 @@
         <v>12</v>
       </c>
       <c r="C47" s="6">
-        <v>0.82</v>
+        <v>1.48</v>
       </c>
       <c r="D47" s="6">
-        <v>1.48</v>
+        <v>-1.53</v>
       </c>
       <c r="E47" s="7">
-        <v>0.66</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4087,13 +4087,13 @@
         <v>12</v>
       </c>
       <c r="C48" s="6">
-        <v>7.28</v>
+        <v>8.24</v>
       </c>
       <c r="D48" s="6">
-        <v>8.24</v>
+        <v>5.89</v>
       </c>
       <c r="E48" s="7">
-        <v>0.96</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -4104,13 +4104,13 @@
         <v>12</v>
       </c>
       <c r="C49" s="6">
-        <v>-7.18</v>
+        <v>-6.49</v>
       </c>
       <c r="D49" s="6">
-        <v>-6.49</v>
+        <v>-8.59</v>
       </c>
       <c r="E49" s="7">
-        <v>0.6899999999999999</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -4121,13 +4121,13 @@
         <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>7.98</v>
+        <v>7.49</v>
       </c>
       <c r="D50" s="6">
-        <v>7.49</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.49</v>
+        <v>5.42</v>
+      </c>
+      <c r="E50" s="7">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -4138,13 +4138,13 @@
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>-19.27</v>
+        <v>-18.2</v>
       </c>
       <c r="D51" s="6">
-        <v>-18.2</v>
+        <v>-18.86</v>
       </c>
       <c r="E51" s="7">
-        <v>1.07</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -4155,13 +4155,13 @@
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-3.59</v>
+        <v>-3.14</v>
       </c>
       <c r="D52" s="6">
-        <v>-3.14</v>
+        <v>-5.82</v>
       </c>
       <c r="E52" s="7">
-        <v>0.45</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -4172,13 +4172,13 @@
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-20.85</v>
+        <v>-21.08</v>
       </c>
       <c r="D53" s="6">
-        <v>-21.08</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.23</v>
+        <v>-22.1</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-1.02</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -4189,13 +4189,13 @@
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-0.59</v>
+        <v>-0.03</v>
       </c>
       <c r="D54" s="6">
-        <v>-0.03</v>
+        <v>-2.67</v>
       </c>
       <c r="E54" s="7">
-        <v>0.5600000000000001</v>
+        <v>-2.64</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -4206,13 +4206,13 @@
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-2.86</v>
+        <v>-2.9</v>
       </c>
       <c r="D55" s="6">
-        <v>-2.9</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.04</v>
+        <v>-4.51</v>
+      </c>
+      <c r="E55" s="7">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -4223,13 +4223,13 @@
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>31.43</v>
+        <v>34.49</v>
       </c>
       <c r="D56" s="6">
-        <v>34.49</v>
+        <v>30.77</v>
       </c>
       <c r="E56" s="7">
-        <v>3.06</v>
+        <v>-3.72</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -4240,13 +4240,13 @@
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>-0.43</v>
+        <v>-0.52</v>
       </c>
       <c r="D57" s="6">
-        <v>-0.52</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.09</v>
+        <v>-2.22</v>
+      </c>
+      <c r="E57" s="7">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -4257,13 +4257,13 @@
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>17.21</v>
+        <v>17.83</v>
       </c>
       <c r="D58" s="6">
-        <v>17.83</v>
+        <v>16.01</v>
       </c>
       <c r="E58" s="7">
-        <v>0.62</v>
+        <v>-1.82</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -4274,13 +4274,13 @@
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>20.45</v>
+        <v>22.31</v>
       </c>
       <c r="D59" s="6">
-        <v>22.31</v>
+        <v>21.4</v>
       </c>
       <c r="E59" s="7">
-        <v>1.86</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -4291,13 +4291,13 @@
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>-2.58</v>
+        <v>-3.83</v>
       </c>
       <c r="D60" s="6">
-        <v>-3.83</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-1.25</v>
+        <v>-5.89</v>
+      </c>
+      <c r="E60" s="7">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -4308,13 +4308,13 @@
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>-8.050000000000001</v>
+        <v>-7.69</v>
       </c>
       <c r="D61" s="6">
-        <v>-7.69</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="E61" s="7">
-        <v>0.36</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -4325,13 +4325,13 @@
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>2.13</v>
+        <v>2.41</v>
       </c>
       <c r="D62" s="6">
-        <v>2.41</v>
+        <v>-0.61</v>
       </c>
       <c r="E62" s="7">
-        <v>0.28</v>
+        <v>-3.02</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -4342,13 +4342,13 @@
         <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>2.23</v>
+        <v>2.93</v>
       </c>
       <c r="D63" s="6">
-        <v>2.93</v>
+        <v>-0.92</v>
       </c>
       <c r="E63" s="7">
-        <v>0.7</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -4359,13 +4359,13 @@
         <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-4.1</v>
+        <v>-3</v>
       </c>
       <c r="D64" s="6">
-        <v>-3</v>
+        <v>-3.44</v>
       </c>
       <c r="E64" s="7">
-        <v>1.1</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -4376,13 +4376,13 @@
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-0.2</v>
+        <v>0.32</v>
       </c>
       <c r="D65" s="6">
-        <v>0.32</v>
+        <v>-2.07</v>
       </c>
       <c r="E65" s="7">
-        <v>0.52</v>
+        <v>-2.39</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -4393,13 +4393,13 @@
         <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-6.31</v>
+        <v>-5.38</v>
       </c>
       <c r="D66" s="6">
-        <v>-5.38</v>
+        <v>-5.74</v>
       </c>
       <c r="E66" s="7">
-        <v>0.93</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -4410,13 +4410,13 @@
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-6.93</v>
+        <v>-5.76</v>
       </c>
       <c r="D67" s="6">
-        <v>-5.76</v>
+        <v>-7.41</v>
       </c>
       <c r="E67" s="7">
-        <v>1.17</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -4427,13 +4427,13 @@
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-3.46</v>
+        <v>-4.38</v>
       </c>
       <c r="D68" s="6">
-        <v>-4.38</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-0.92</v>
+        <v>-6.79</v>
+      </c>
+      <c r="E68" s="7">
+        <v>-2.41</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -4444,13 +4444,13 @@
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>5.81</v>
+        <v>2.78</v>
       </c>
       <c r="D69" s="6">
-        <v>2.78</v>
+        <v>3.21</v>
       </c>
       <c r="E69" s="8">
-        <v>-3.03</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -4461,13 +4461,13 @@
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-0.41</v>
+        <v>0.83</v>
       </c>
       <c r="D70" s="6">
-        <v>0.83</v>
+        <v>-0.72</v>
       </c>
       <c r="E70" s="7">
-        <v>1.24</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -4478,13 +4478,13 @@
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-4.65</v>
+        <v>-3.89</v>
       </c>
       <c r="D71" s="6">
-        <v>-3.89</v>
+        <v>-5.45</v>
       </c>
       <c r="E71" s="7">
-        <v>0.76</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -4495,13 +4495,13 @@
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>3.98</v>
+        <v>3.13</v>
       </c>
       <c r="D72" s="6">
-        <v>3.13</v>
-      </c>
-      <c r="E72" s="8">
-        <v>-0.85</v>
+        <v>2.94</v>
+      </c>
+      <c r="E72" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -4512,13 +4512,13 @@
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>2.54</v>
+        <v>5.42</v>
       </c>
       <c r="D73" s="6">
-        <v>5.42</v>
+        <v>4.79</v>
       </c>
       <c r="E73" s="7">
-        <v>2.88</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -4529,13 +4529,13 @@
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-5.14</v>
+        <v>-4.48</v>
       </c>
       <c r="D74" s="6">
-        <v>-4.48</v>
-      </c>
-      <c r="E74" s="7">
-        <v>0.66</v>
+        <v>-4</v>
+      </c>
+      <c r="E74" s="8">
+        <v>0.48</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -4546,13 +4546,13 @@
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-3.72</v>
+        <v>-3.05</v>
       </c>
       <c r="D75" s="6">
-        <v>-3.05</v>
+        <v>-4.23</v>
       </c>
       <c r="E75" s="7">
-        <v>0.67</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -4563,13 +4563,13 @@
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>7.68</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="D76" s="6">
-        <v>8.529999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="E76" s="7">
-        <v>0.85</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -4580,13 +4580,13 @@
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>6.88</v>
+        <v>5.76</v>
       </c>
       <c r="D77" s="6">
-        <v>5.76</v>
-      </c>
-      <c r="E77" s="8">
-        <v>-1.12</v>
+        <v>4.25</v>
+      </c>
+      <c r="E77" s="7">
+        <v>-1.51</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -4597,13 +4597,13 @@
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>-1.14</v>
+        <v>-2.14</v>
       </c>
       <c r="D78" s="6">
-        <v>-2.14</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-1</v>
+        <v>-3.77</v>
+      </c>
+      <c r="E78" s="7">
+        <v>-1.63</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -4614,13 +4614,13 @@
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>5.03</v>
+        <v>5.73</v>
       </c>
       <c r="D79" s="6">
-        <v>5.73</v>
+        <v>4.97</v>
       </c>
       <c r="E79" s="7">
-        <v>0.7</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -4631,13 +4631,13 @@
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-1.88</v>
+        <v>-0.01</v>
       </c>
       <c r="D80" s="6">
-        <v>-0.01</v>
+        <v>-0.37</v>
       </c>
       <c r="E80" s="7">
-        <v>1.87</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -4648,13 +4648,13 @@
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-1.9</v>
+        <v>-2.1</v>
       </c>
       <c r="D81" s="6">
-        <v>-2.1</v>
-      </c>
-      <c r="E81" s="8">
-        <v>-0.2</v>
+        <v>-2.45</v>
+      </c>
+      <c r="E81" s="7">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -4665,13 +4665,13 @@
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-1.72</v>
+        <v>-3.23</v>
       </c>
       <c r="D82" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-1.51</v>
+        <v>-5.5</v>
+      </c>
+      <c r="E82" s="7">
+        <v>-2.27</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -4682,13 +4682,13 @@
         <v>7</v>
       </c>
       <c r="C83" s="6">
-        <v>-8.640000000000001</v>
+        <v>-8.4</v>
       </c>
       <c r="D83" s="6">
-        <v>-8.4</v>
+        <v>-9.84</v>
       </c>
       <c r="E83" s="7">
-        <v>0.24</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -4699,13 +4699,13 @@
         <v>7</v>
       </c>
       <c r="C84" s="6">
-        <v>-9.08</v>
+        <v>-8.16</v>
       </c>
       <c r="D84" s="6">
-        <v>-8.16</v>
+        <v>-9.4</v>
       </c>
       <c r="E84" s="7">
-        <v>0.92</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -4716,13 +4716,13 @@
         <v>7</v>
       </c>
       <c r="C85" s="6">
-        <v>-9.109999999999999</v>
+        <v>-8.65</v>
       </c>
       <c r="D85" s="6">
-        <v>-8.65</v>
+        <v>-10.17</v>
       </c>
       <c r="E85" s="7">
-        <v>0.46</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -4733,13 +4733,13 @@
         <v>7</v>
       </c>
       <c r="C86" s="6">
-        <v>-9.17</v>
+        <v>-9.09</v>
       </c>
       <c r="D86" s="6">
-        <v>-9.09</v>
+        <v>-10.05</v>
       </c>
       <c r="E86" s="7">
-        <v>0.08</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -4750,13 +4750,13 @@
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-19.58</v>
+        <v>-18.52</v>
       </c>
       <c r="D87" s="6">
-        <v>-18.52</v>
+        <v>-19.4</v>
       </c>
       <c r="E87" s="7">
-        <v>1.06</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -4767,13 +4767,13 @@
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-10.7</v>
+        <v>-10.18</v>
       </c>
       <c r="D88" s="6">
-        <v>-10.18</v>
+        <v>-12.33</v>
       </c>
       <c r="E88" s="7">
-        <v>0.52</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -4784,13 +4784,13 @@
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-27.62</v>
+        <v>-28.25</v>
       </c>
       <c r="D89" s="6">
-        <v>-28.25</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-0.63</v>
+        <v>-28.56</v>
+      </c>
+      <c r="E89" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -4801,13 +4801,13 @@
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-4.63</v>
+        <v>-3.87</v>
       </c>
       <c r="D90" s="6">
-        <v>-3.87</v>
+        <v>-5.12</v>
       </c>
       <c r="E90" s="7">
-        <v>0.76</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -4818,13 +4818,13 @@
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-7.63</v>
+        <v>-6.87</v>
       </c>
       <c r="D91" s="6">
-        <v>-6.87</v>
+        <v>-8.41</v>
       </c>
       <c r="E91" s="7">
-        <v>0.76</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -4835,13 +4835,13 @@
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-3.54</v>
+        <v>-4.02</v>
       </c>
       <c r="D92" s="6">
-        <v>-4.02</v>
-      </c>
-      <c r="E92" s="8">
-        <v>-0.48</v>
+        <v>-4.79</v>
+      </c>
+      <c r="E92" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -4852,13 +4852,13 @@
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-5.31</v>
+        <v>-3.03</v>
       </c>
       <c r="D93" s="6">
-        <v>-3.03</v>
+        <v>-4.93</v>
       </c>
       <c r="E93" s="7">
-        <v>2.28</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -4869,13 +4869,13 @@
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-10.68</v>
+        <v>-10.48</v>
       </c>
       <c r="D94" s="6">
-        <v>-10.48</v>
+        <v>-11.25</v>
       </c>
       <c r="E94" s="7">
-        <v>0.2</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -4886,13 +4886,13 @@
         <v>7</v>
       </c>
       <c r="C95" s="6">
+        <v>-15.33</v>
+      </c>
+      <c r="D95" s="6">
         <v>-16.28</v>
       </c>
-      <c r="D95" s="6">
-        <v>-15.33</v>
-      </c>
       <c r="E95" s="7">
-        <v>0.95</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -4903,13 +4903,13 @@
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-1.02</v>
+        <v>-0.13</v>
       </c>
       <c r="D96" s="6">
-        <v>-0.13</v>
+        <v>-0.58</v>
       </c>
       <c r="E96" s="7">
-        <v>0.89</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -4920,13 +4920,13 @@
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-11.06</v>
+        <v>-10.08</v>
       </c>
       <c r="D97" s="6">
-        <v>-10.08</v>
+        <v>-11.07</v>
       </c>
       <c r="E97" s="7">
-        <v>0.98</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -4937,13 +4937,13 @@
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-12.11</v>
+        <v>-11.84</v>
       </c>
       <c r="D98" s="6">
-        <v>-11.84</v>
+        <v>-13.38</v>
       </c>
       <c r="E98" s="7">
-        <v>0.27</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -4954,13 +4954,13 @@
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-1.31</v>
+        <v>-0.43</v>
       </c>
       <c r="D99" s="6">
-        <v>-0.43</v>
+        <v>-1.09</v>
       </c>
       <c r="E99" s="7">
-        <v>0.88</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -4971,13 +4971,13 @@
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-5.27</v>
+        <v>-5.37</v>
       </c>
       <c r="D100" s="6">
-        <v>-5.37</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-0.1</v>
+        <v>-6.37</v>
+      </c>
+      <c r="E100" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -4988,13 +4988,13 @@
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-3.61</v>
+        <v>-3.2</v>
       </c>
       <c r="D101" s="6">
-        <v>-3.2</v>
+        <v>-4.39</v>
       </c>
       <c r="E101" s="7">
-        <v>0.41</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -5005,13 +5005,13 @@
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-6.52</v>
+        <v>-6.25</v>
       </c>
       <c r="D102" s="6">
-        <v>-6.25</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="E102" s="7">
-        <v>0.27</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -5022,13 +5022,13 @@
         <v>3</v>
       </c>
       <c r="C103" s="6">
-        <v>27086.3</v>
+        <v>27157.55</v>
       </c>
       <c r="D103" s="6">
-        <v>27157.55</v>
+        <v>26730.1</v>
       </c>
       <c r="E103" s="7">
-        <v>71.25</v>
+        <v>-427.45</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -5039,13 +5039,13 @@
         <v>3</v>
       </c>
       <c r="C104" s="6">
-        <v>9549.35</v>
+        <v>9646.5</v>
       </c>
       <c r="D104" s="6">
-        <v>9646.5</v>
+        <v>9515.6</v>
       </c>
       <c r="E104" s="7">
-        <v>97.15000000000001</v>
+        <v>-130.9</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -5056,13 +5056,13 @@
         <v>3</v>
       </c>
       <c r="C105" s="6">
-        <v>11487.2</v>
+        <v>11546.05</v>
       </c>
       <c r="D105" s="6">
-        <v>11546.05</v>
+        <v>11353.45</v>
       </c>
       <c r="E105" s="7">
-        <v>58.85</v>
+        <v>-192.6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -5073,13 +5073,13 @@
         <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>37727</v>
+        <v>37759.75</v>
       </c>
       <c r="D106" s="6">
-        <v>37759.75</v>
+        <v>37360.95</v>
       </c>
       <c r="E106" s="7">
-        <v>32.75</v>
+        <v>-398.8</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -5090,13 +5090,13 @@
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>45657.75</v>
+        <v>46259.35</v>
       </c>
       <c r="D107" s="6">
-        <v>46259.35</v>
+        <v>45759.35</v>
       </c>
       <c r="E107" s="7">
-        <v>601.6</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -5107,13 +5107,13 @@
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>25417.95</v>
+        <v>25564.85</v>
       </c>
       <c r="D108" s="6">
-        <v>25564.85</v>
+        <v>24954.15</v>
       </c>
       <c r="E108" s="7">
-        <v>146.9</v>
+        <v>-610.7</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -5124,13 +5124,13 @@
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>28582.1</v>
+        <v>28334.05</v>
       </c>
       <c r="D109" s="6">
-        <v>28334.05</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-248.05</v>
+        <v>28208.85</v>
+      </c>
+      <c r="E109" s="7">
+        <v>-125.2</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -5141,13 +5141,13 @@
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>15890.5</v>
+        <v>16017.7</v>
       </c>
       <c r="D110" s="6">
-        <v>16017.7</v>
+        <v>15809.8</v>
       </c>
       <c r="E110" s="7">
-        <v>127.2</v>
+        <v>-207.9</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -5158,13 +5158,13 @@
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>9020.799999999999</v>
+        <v>9095.049999999999</v>
       </c>
       <c r="D111" s="6">
-        <v>9095.049999999999</v>
+        <v>8944.85</v>
       </c>
       <c r="E111" s="7">
-        <v>74.25</v>
+        <v>-150.2</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -5175,13 +5175,13 @@
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>1574.7</v>
+        <v>1566.85</v>
       </c>
       <c r="D112" s="6">
-        <v>1566.85</v>
-      </c>
-      <c r="E112" s="8">
-        <v>-7.85</v>
+        <v>1554.25</v>
+      </c>
+      <c r="E112" s="7">
+        <v>-12.6</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -5192,13 +5192,13 @@
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>12990.35</v>
+        <v>13302.35</v>
       </c>
       <c r="D113" s="6">
-        <v>13302.35</v>
+        <v>13041.95</v>
       </c>
       <c r="E113" s="7">
-        <v>312</v>
+        <v>-260.4</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -5209,13 +5209,13 @@
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>9616.700000000001</v>
+        <v>9637.6</v>
       </c>
       <c r="D114" s="6">
-        <v>9637.6</v>
+        <v>9555.450000000001</v>
       </c>
       <c r="E114" s="7">
-        <v>20.9</v>
+        <v>-82.15000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -5226,13 +5226,13 @@
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>8271.299999999999</v>
+        <v>8365.450000000001</v>
       </c>
       <c r="D115" s="6">
-        <v>8365.450000000001</v>
+        <v>8271.15</v>
       </c>
       <c r="E115" s="7">
-        <v>94.15000000000001</v>
+        <v>-94.3</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -5243,13 +5243,13 @@
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>26909.6</v>
+        <v>27152.1</v>
       </c>
       <c r="D116" s="6">
-        <v>27152.1</v>
+        <v>27028.7</v>
       </c>
       <c r="E116" s="7">
-        <v>242.5</v>
+        <v>-123.4</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -5260,13 +5260,13 @@
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>861.5</v>
+        <v>871</v>
       </c>
       <c r="D117" s="6">
-        <v>871</v>
+        <v>861.4</v>
       </c>
       <c r="E117" s="7">
-        <v>9.5</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -5277,13 +5277,13 @@
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>29970.75</v>
+        <v>30064.25</v>
       </c>
       <c r="D118" s="6">
-        <v>30064.25</v>
+        <v>29539.95</v>
       </c>
       <c r="E118" s="7">
-        <v>93.5</v>
+        <v>-524.3</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -5294,13 +5294,13 @@
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>16720</v>
+        <v>16868.15</v>
       </c>
       <c r="D119" s="6">
-        <v>16868.15</v>
+        <v>16757.2</v>
       </c>
       <c r="E119" s="7">
-        <v>148.15</v>
+        <v>-110.95</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -5311,13 +5311,13 @@
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>9471.549999999999</v>
+        <v>9461.299999999999</v>
       </c>
       <c r="D120" s="6">
-        <v>9461.299999999999</v>
-      </c>
-      <c r="E120" s="8">
-        <v>-10.25</v>
+        <v>9361.700000000001</v>
+      </c>
+      <c r="E120" s="7">
+        <v>-99.59999999999999</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -5328,13 +5328,13 @@
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>10958.9</v>
+        <v>11005.2</v>
       </c>
       <c r="D121" s="6">
-        <v>11005.2</v>
+        <v>10869.85</v>
       </c>
       <c r="E121" s="7">
-        <v>46.3</v>
+        <v>-135.35</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -5345,13 +5345,13 @@
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>27286</v>
+        <v>27363.35</v>
       </c>
       <c r="D122" s="6">
-        <v>27363.35</v>
+        <v>26763.95</v>
       </c>
       <c r="E122" s="7">
-        <v>77.34999999999999</v>
+        <v>-599.4</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -5362,472 +5362,404 @@
         <v>14</v>
       </c>
       <c r="C123" s="6">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D123" s="6">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="E123" s="7">
-        <v>18</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C124" s="6">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D124" s="6">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E124" s="7">
-        <v>6</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C125" s="6">
+        <v>56</v>
+      </c>
+      <c r="D125" s="6">
         <v>68</v>
       </c>
-      <c r="D125" s="6">
-        <v>74</v>
-      </c>
-      <c r="E125" s="7">
-        <v>6</v>
+      <c r="E125" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="6">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D126" s="6">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="E126" s="8">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C127" s="6">
-        <v>38</v>
+        <v>34.9</v>
       </c>
       <c r="D127" s="6">
-        <v>44</v>
+        <v>28.76</v>
       </c>
       <c r="E127" s="7">
-        <v>6</v>
+        <v>-6.14</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C128" s="6">
-        <v>44</v>
+        <v>47.65</v>
       </c>
       <c r="D128" s="6">
-        <v>38</v>
-      </c>
-      <c r="E128" s="8">
-        <v>-6</v>
+        <v>40.19</v>
+      </c>
+      <c r="E128" s="7">
+        <v>-7.46</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C129" s="6">
-        <v>74</v>
+        <v>43.12</v>
       </c>
       <c r="D129" s="6">
-        <v>62</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-12</v>
+        <v>33.99</v>
+      </c>
+      <c r="E129" s="7">
+        <v>-9.130000000000001</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C130" s="6">
-        <v>62</v>
+        <v>44.01</v>
       </c>
       <c r="D130" s="6">
-        <v>50</v>
-      </c>
-      <c r="E130" s="8">
-        <v>-12</v>
+        <v>37.13</v>
+      </c>
+      <c r="E130" s="7">
+        <v>-6.88</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C131" s="6">
-        <v>32.67</v>
+        <v>48.37</v>
       </c>
       <c r="D131" s="6">
-        <v>34.9</v>
+        <v>42.91</v>
       </c>
       <c r="E131" s="7">
-        <v>2.23</v>
+        <v>-5.46</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C132" s="6">
-        <v>39.97</v>
+        <v>43.72</v>
       </c>
       <c r="D132" s="6">
-        <v>47.65</v>
+        <v>32.91</v>
       </c>
       <c r="E132" s="7">
-        <v>7.68</v>
+        <v>-10.81</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="6">
-        <v>38.43</v>
+        <v>33.03</v>
       </c>
       <c r="D133" s="6">
-        <v>43.12</v>
+        <v>32.01</v>
       </c>
       <c r="E133" s="7">
-        <v>4.69</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="6">
-        <v>43.21</v>
+        <v>45.11</v>
       </c>
       <c r="D134" s="6">
-        <v>44.01</v>
+        <v>38.1</v>
       </c>
       <c r="E134" s="7">
-        <v>0.8</v>
+        <v>-7.01</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>39.82</v>
+        <v>44.59</v>
       </c>
       <c r="D135" s="6">
-        <v>48.37</v>
+        <v>35.42</v>
       </c>
       <c r="E135" s="7">
-        <v>8.550000000000001</v>
+        <v>-9.17</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>39.26</v>
+        <v>53.24</v>
       </c>
       <c r="D136" s="6">
-        <v>43.72</v>
+        <v>50.08</v>
       </c>
       <c r="E136" s="7">
-        <v>4.46</v>
+        <v>-3.16</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>35.07</v>
+        <v>56.5</v>
       </c>
       <c r="D137" s="6">
-        <v>33.03</v>
-      </c>
-      <c r="E137" s="8">
-        <v>-2.04</v>
+        <v>49.21</v>
+      </c>
+      <c r="E137" s="7">
+        <v>-7.29</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>38.7</v>
+        <v>44.55</v>
       </c>
       <c r="D138" s="6">
-        <v>45.11</v>
+        <v>38.15</v>
       </c>
       <c r="E138" s="7">
-        <v>6.41</v>
+        <v>-6.4</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>37.12</v>
+        <v>46.25</v>
       </c>
       <c r="D139" s="6">
-        <v>44.59</v>
+        <v>41.03</v>
       </c>
       <c r="E139" s="7">
-        <v>7.47</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>55.25</v>
+        <v>61.74</v>
       </c>
       <c r="D140" s="6">
-        <v>53.24</v>
-      </c>
-      <c r="E140" s="8">
-        <v>-2.01</v>
+        <v>58.57</v>
+      </c>
+      <c r="E140" s="7">
+        <v>-3.17</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>47.91</v>
+        <v>48.91</v>
       </c>
       <c r="D141" s="6">
-        <v>56.5</v>
+        <v>45.65</v>
       </c>
       <c r="E141" s="7">
-        <v>8.59</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>42.26</v>
+        <v>40.44</v>
       </c>
       <c r="D142" s="6">
-        <v>44.55</v>
+        <v>30.27</v>
       </c>
       <c r="E142" s="7">
-        <v>2.29</v>
+        <v>-10.17</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>39.06</v>
+        <v>60.65</v>
       </c>
       <c r="D143" s="6">
-        <v>46.25</v>
+        <v>56.06</v>
       </c>
       <c r="E143" s="7">
-        <v>7.19</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>57.55</v>
+        <v>45.81</v>
       </c>
       <c r="D144" s="6">
-        <v>61.74</v>
+        <v>42.27</v>
       </c>
       <c r="E144" s="7">
-        <v>4.19</v>
+        <v>-3.54</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>45.32</v>
+        <v>46.7</v>
       </c>
       <c r="D145" s="6">
-        <v>48.91</v>
+        <v>38.75</v>
       </c>
       <c r="E145" s="7">
-        <v>3.59</v>
+        <v>-7.95</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>36.93</v>
+        <v>47.16</v>
       </c>
       <c r="D146" s="6">
-        <v>40.44</v>
+        <v>35.63</v>
       </c>
       <c r="E146" s="7">
-        <v>3.51</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5">
-      <c r="A147" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C147" s="6">
-        <v>56.21</v>
-      </c>
-      <c r="D147" s="6">
-        <v>60.65</v>
-      </c>
-      <c r="E147" s="7">
-        <v>4.44</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5">
-      <c r="A148" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C148" s="6">
-        <v>46.18</v>
-      </c>
-      <c r="D148" s="6">
-        <v>45.81</v>
-      </c>
-      <c r="E148" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5">
-      <c r="A149" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C149" s="6">
-        <v>42.99</v>
-      </c>
-      <c r="D149" s="6">
-        <v>46.7</v>
-      </c>
-      <c r="E149" s="7">
-        <v>3.71</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5">
-      <c r="A150" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C150" s="6">
-        <v>45.03</v>
-      </c>
-      <c r="D150" s="6">
-        <v>47.16</v>
-      </c>
-      <c r="E150" s="7">
-        <v>2.13</v>
+        <v>-11.53</v>
       </c>
     </row>
   </sheetData>
@@ -5886,22 +5818,22 @@
         <v>78</v>
       </c>
       <c r="B2" s="11">
-        <v>43.24</v>
+        <v>39.24</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>46.8</v>
+        <v>40.4</v>
       </c>
       <c r="E2" s="11">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.3</v>
+        <v>-3.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-0.1</v>
+        <v>-1.2</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -6021,10 +5953,10 @@
         <v>49</v>
       </c>
       <c r="E1" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="G1" s="13" t="s">
         <v>51</v>
@@ -6033,42 +5965,42 @@
         <v>46</v>
       </c>
       <c r="I1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>52</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.334</v>
+        <v>0.2998</v>
       </c>
       <c r="B2" s="14">
-        <v>0.2835</v>
+        <v>0.2854</v>
       </c>
       <c r="C2" s="14">
-        <v>0.2123</v>
+        <v>0.2072</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1996</v>
+        <v>0.2004</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1961</v>
+        <v>0.1886</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1883</v>
+        <v>0.1505</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1356</v>
+        <v>0.136</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1262</v>
+        <v>0.1234</v>
       </c>
       <c r="I2" s="14">
-        <v>0.1202</v>
+        <v>0.1146</v>
       </c>
       <c r="J2" s="14">
-        <v>0.1152</v>
+        <v>0.1144</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6079,13 +6011,13 @@
         <v>40</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>45</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>43</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>53</v>
@@ -6105,34 +6037,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.1133</v>
+        <v>0.1131</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0949</v>
+        <v>0.0915</v>
       </c>
       <c r="C4" s="14">
-        <v>0.08259999999999999</v>
+        <v>0.06179999999999999</v>
       </c>
       <c r="D4" s="14">
-        <v>0.067</v>
+        <v>0.0602</v>
       </c>
       <c r="E4" s="14">
-        <v>0.06610000000000001</v>
+        <v>0.0333</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0367</v>
+        <v>0.0321</v>
       </c>
       <c r="G4" s="14">
-        <v>0.0217</v>
+        <v>0.0218</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0023</v>
+        <v>-0.0447</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.051</v>
+        <v>-0.0533</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.06280000000000001</v>
+        <v>-0.06309999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="118">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,46 +289,52 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>28.8 → 35.5</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>28.8</t>
-  </si>
-  <si>
-    <t>35.5</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.6% → -2.4%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
+  </si>
+  <si>
+    <t>-1.6%</t>
+  </si>
+  <si>
+    <t>-2.4%</t>
   </si>
   <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.2 → 50.4</t>
-  </si>
-  <si>
-    <t>49.2</t>
+    <t>50.4 → 44.6</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.4</t>
   </si>
   <si>
-    <t>50.1 → 49.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>44.6</t>
+  </si>
+  <si>
+    <t>53.0 → 47.9</t>
+  </si>
+  <si>
+    <t>53.0</t>
+  </si>
+  <si>
+    <t>47.9</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
   </si>
   <si>
     <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -380,7 +386,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -414,7 +420,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -426,8 +432,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -454,13 +467,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -541,12 +560,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -555,7 +574,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1059,10 +1078,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>26967.9</v>
+        <v>26525.05</v>
       </c>
       <c r="E2">
-        <v>0.89</v>
+        <v>-1.64</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1071,43 +1090,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-9.039999999999999</v>
+        <v>-10.53</v>
       </c>
       <c r="I2">
-        <v>13.46</v>
+        <v>11.59</v>
       </c>
       <c r="J2">
-        <v>-0.59</v>
+        <v>-2.31</v>
       </c>
       <c r="K2">
-        <v>-7.01</v>
+        <v>-8.17</v>
       </c>
       <c r="L2">
-        <v>2.08</v>
+        <v>0.17</v>
       </c>
       <c r="M2">
-        <v>-1.2</v>
+        <v>-2.94</v>
       </c>
       <c r="N2">
-        <v>20.19</v>
+        <v>19.92</v>
       </c>
       <c r="O2">
         <v>62</v>
       </c>
       <c r="Q2">
-        <v>27018.59</v>
+        <v>26893.38</v>
       </c>
       <c r="R2">
-        <v>27535.94</v>
+        <v>27419.61</v>
       </c>
       <c r="S2">
-        <v>28149.96</v>
+        <v>28138.47</v>
       </c>
       <c r="T2">
-        <v>27109.11</v>
+        <v>27103.08</v>
       </c>
       <c r="U2">
-        <v>-0.52</v>
+        <v>-2.13</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1122,40 +1141,40 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>35.55</v>
+        <v>29.84</v>
       </c>
       <c r="AA2">
-        <v>-404.98</v>
+        <v>-430.03</v>
       </c>
       <c r="AB2">
-        <v>-355.89</v>
+        <v>-370.72</v>
       </c>
       <c r="AC2">
-        <v>-49.09</v>
+        <v>-59.31</v>
       </c>
       <c r="AD2">
-        <v>84.25</v>
+        <v>70.31</v>
       </c>
       <c r="AE2">
-        <v>78.67</v>
+        <v>76.91</v>
       </c>
       <c r="AF2">
-        <v>355.4</v>
+        <v>365.09</v>
       </c>
       <c r="AH2">
-        <v>28801.92</v>
+        <v>28601.27</v>
       </c>
       <c r="AI2">
-        <v>26269.97</v>
+        <v>26237.94</v>
       </c>
       <c r="AJ2">
-        <v>27918.19</v>
+        <v>27782.04</v>
       </c>
       <c r="AK2" t="s">
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>64.18000000000001</v>
+        <v>65.72</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1169,10 +1188,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9540.75</v>
+        <v>9366.4</v>
       </c>
       <c r="E3">
-        <v>0.26</v>
+        <v>-1.83</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1181,82 +1200,82 @@
         <v>8890.35</v>
       </c>
       <c r="H3">
-        <v>-9.16</v>
+        <v>-10.82</v>
       </c>
       <c r="I3">
-        <v>7.32</v>
+        <v>5.35</v>
       </c>
       <c r="J3">
-        <v>-0.27</v>
+        <v>-1.86</v>
       </c>
       <c r="K3">
-        <v>-3.4</v>
+        <v>-4.57</v>
       </c>
       <c r="L3">
-        <v>-2.84</v>
+        <v>-4.36</v>
       </c>
       <c r="M3">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
       <c r="N3">
-        <v>11.26</v>
+        <v>10.67</v>
       </c>
       <c r="O3">
         <v>81</v>
       </c>
       <c r="Q3">
-        <v>9559.17</v>
+        <v>9523.719999999999</v>
       </c>
       <c r="R3">
-        <v>9631.780000000001</v>
+        <v>9609.639999999999</v>
       </c>
       <c r="S3">
-        <v>9772.82</v>
+        <v>9763.5</v>
       </c>
       <c r="T3">
-        <v>9771.120000000001</v>
+        <v>9772.27</v>
       </c>
       <c r="U3">
-        <v>-2.36</v>
+        <v>-4.15</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
       </c>
       <c r="W3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="s">
         <v>79</v>
       </c>
       <c r="Y3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3">
-        <v>42.06</v>
+        <v>34.08</v>
       </c>
       <c r="AA3">
-        <v>-74.13</v>
+        <v>-85.7</v>
       </c>
       <c r="AB3">
-        <v>-74.77</v>
+        <v>-76.95999999999999</v>
       </c>
       <c r="AC3">
-        <v>0.64</v>
+        <v>-8.74</v>
       </c>
       <c r="AD3">
-        <v>78.36</v>
+        <v>56.92</v>
       </c>
       <c r="AE3">
-        <v>75.58</v>
+        <v>70.01000000000001</v>
       </c>
       <c r="AF3">
-        <v>98.31</v>
+        <v>104.49</v>
       </c>
       <c r="AH3">
-        <v>9870.51</v>
+        <v>9860.9</v>
       </c>
       <c r="AI3">
-        <v>9393.049999999999</v>
+        <v>9358.389999999999</v>
       </c>
       <c r="AJ3">
         <v>9750.9</v>
@@ -1265,7 +1284,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>29.29</v>
+        <v>31.77</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1279,10 +1298,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11415.4</v>
+        <v>11270.1</v>
       </c>
       <c r="E4">
-        <v>0.55</v>
+        <v>-1.27</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1291,43 +1310,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-9.68</v>
+        <v>-10.83</v>
       </c>
       <c r="I4">
-        <v>10.46</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J4">
-        <v>-0.4</v>
+        <v>-2.08</v>
       </c>
       <c r="K4">
-        <v>-4.62</v>
+        <v>-5.46</v>
       </c>
       <c r="L4">
-        <v>-0.66</v>
+        <v>-2.13</v>
       </c>
       <c r="M4">
-        <v>-8.26</v>
+        <v>-9.73</v>
       </c>
       <c r="N4">
-        <v>9.279999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="O4">
         <v>32</v>
       </c>
       <c r="Q4">
-        <v>11462.28</v>
+        <v>11414.44</v>
       </c>
       <c r="R4">
-        <v>11545.85</v>
+        <v>11514.14</v>
       </c>
       <c r="S4">
-        <v>11808.54</v>
+        <v>11799.85</v>
       </c>
       <c r="T4">
-        <v>11603.19</v>
+        <v>11597.79</v>
       </c>
       <c r="U4">
-        <v>-1.62</v>
+        <v>-2.83</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1342,40 +1361,40 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>38.5</v>
+        <v>32.83</v>
       </c>
       <c r="AA4">
-        <v>-118.6</v>
+        <v>-126.91</v>
       </c>
       <c r="AB4">
-        <v>-119.82</v>
+        <v>-121.24</v>
       </c>
       <c r="AC4">
-        <v>1.21</v>
+        <v>-5.67</v>
       </c>
       <c r="AD4">
-        <v>80.48999999999999</v>
+        <v>65.89</v>
       </c>
       <c r="AE4">
-        <v>87.91</v>
+        <v>77.17</v>
       </c>
       <c r="AF4">
-        <v>107.14</v>
+        <v>111.09</v>
       </c>
       <c r="AH4">
-        <v>11863.72</v>
+        <v>11807.03</v>
       </c>
       <c r="AI4">
-        <v>11227.98</v>
+        <v>11221.26</v>
       </c>
       <c r="AJ4">
-        <v>11665.92</v>
+        <v>11652.13</v>
       </c>
       <c r="AK4" t="s">
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>44.1</v>
+        <v>46.11</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1389,10 +1408,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>37440.35</v>
+        <v>36693.2</v>
       </c>
       <c r="E5">
-        <v>0.21</v>
+        <v>-2</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1401,43 +1420,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-9.859999999999999</v>
+        <v>-11.66</v>
       </c>
       <c r="I5">
-        <v>13.12</v>
+        <v>10.86</v>
       </c>
       <c r="J5">
-        <v>-0.88</v>
+        <v>-2.98</v>
       </c>
       <c r="K5">
-        <v>-1.73</v>
+        <v>-3.7</v>
       </c>
       <c r="L5">
-        <v>-5.73</v>
+        <v>-7.67</v>
       </c>
       <c r="M5">
-        <v>5.26</v>
+        <v>3.53</v>
       </c>
       <c r="N5">
-        <v>11.23</v>
+        <v>10.33</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="Q5">
-        <v>37621.32</v>
+        <v>37396.25</v>
       </c>
       <c r="R5">
-        <v>37807.42</v>
+        <v>37741.9</v>
       </c>
       <c r="S5">
-        <v>38373.62</v>
+        <v>38321.94</v>
       </c>
       <c r="T5">
-        <v>37628.21</v>
+        <v>37636.74</v>
       </c>
       <c r="U5">
-        <v>-0.5</v>
+        <v>-2.51</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1452,40 +1471,40 @@
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>39.17</v>
+        <v>29.48</v>
       </c>
       <c r="AA5">
-        <v>-247.07</v>
+        <v>-306.56</v>
       </c>
       <c r="AB5">
-        <v>-248.29</v>
+        <v>-259.94</v>
       </c>
       <c r="AC5">
-        <v>1.22</v>
+        <v>-46.61</v>
       </c>
       <c r="AD5">
-        <v>57.49</v>
+        <v>35.18</v>
       </c>
       <c r="AE5">
-        <v>65.59</v>
+        <v>52.12</v>
       </c>
       <c r="AF5">
-        <v>368.52</v>
+        <v>399.43</v>
       </c>
       <c r="AH5">
-        <v>38489.78</v>
+        <v>38579.03</v>
       </c>
       <c r="AI5">
-        <v>37125.06</v>
+        <v>36904.76</v>
       </c>
       <c r="AJ5">
-        <v>38269.93</v>
+        <v>38228.57</v>
       </c>
       <c r="AK5" t="s">
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>18.87</v>
+        <v>22.54</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1499,10 +1518,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>45941.3</v>
+        <v>45264.35</v>
       </c>
       <c r="E6">
-        <v>0.4</v>
+        <v>-1.47</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1511,43 +1530,43 @@
         <v>44829.95</v>
       </c>
       <c r="H6">
-        <v>-19.08</v>
+        <v>-20.27</v>
       </c>
       <c r="I6">
-        <v>2.48</v>
+        <v>0.97</v>
       </c>
       <c r="J6">
-        <v>1.04</v>
+        <v>-1.39</v>
       </c>
       <c r="K6">
-        <v>-2.78</v>
+        <v>-3.76</v>
       </c>
       <c r="L6">
-        <v>-6.49</v>
+        <v>-7.23</v>
       </c>
       <c r="M6">
-        <v>-18.43</v>
+        <v>-19.92</v>
       </c>
       <c r="N6">
-        <v>2.44</v>
+        <v>2.16</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>45903.73</v>
+        <v>45776.42</v>
       </c>
       <c r="R6">
-        <v>45761.22</v>
+        <v>45683.69</v>
       </c>
       <c r="S6">
-        <v>47459.97</v>
+        <v>47390.29</v>
       </c>
       <c r="T6">
-        <v>49871.95</v>
+        <v>49822.23</v>
       </c>
       <c r="U6">
-        <v>-7.88</v>
+        <v>-9.15</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1562,31 +1581,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>45.33</v>
+        <v>38.75</v>
       </c>
       <c r="AA6">
-        <v>-465.6</v>
+        <v>-474.66</v>
       </c>
       <c r="AB6">
-        <v>-631.24</v>
+        <v>-599.9299999999999</v>
       </c>
       <c r="AC6">
-        <v>165.64</v>
+        <v>125.27</v>
       </c>
       <c r="AD6">
-        <v>88.86</v>
+        <v>76.25</v>
       </c>
       <c r="AE6">
-        <v>90.90000000000001</v>
+        <v>84.48</v>
       </c>
       <c r="AF6">
-        <v>531.05</v>
+        <v>544.49</v>
       </c>
       <c r="AH6">
-        <v>46718.79</v>
+        <v>46526.2</v>
       </c>
       <c r="AI6">
-        <v>44803.64</v>
+        <v>44841.17</v>
       </c>
       <c r="AJ6">
         <v>46607.06</v>
@@ -1595,7 +1614,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>31.74</v>
+        <v>30.62</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1609,10 +1628,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25094.85</v>
+        <v>24671.65</v>
       </c>
       <c r="E7">
-        <v>0.5600000000000001</v>
+        <v>-1.69</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1621,43 +1640,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-11.83</v>
+        <v>-13.32</v>
       </c>
       <c r="I7">
-        <v>6.69</v>
+        <v>4.89</v>
       </c>
       <c r="J7">
-        <v>-1.63</v>
+        <v>-3.34</v>
       </c>
       <c r="K7">
-        <v>-4.9</v>
+        <v>-6.12</v>
       </c>
       <c r="L7">
-        <v>-5.65</v>
+        <v>-7.09</v>
       </c>
       <c r="M7">
-        <v>-5.53</v>
+        <v>-7.59</v>
       </c>
       <c r="N7">
-        <v>6.06</v>
+        <v>5.89</v>
       </c>
       <c r="O7">
         <v>26</v>
       </c>
       <c r="Q7">
-        <v>25311.3</v>
+        <v>25140.69</v>
       </c>
       <c r="R7">
-        <v>25608.44</v>
+        <v>25527.69</v>
       </c>
       <c r="S7">
-        <v>26178.23</v>
+        <v>26133.6</v>
       </c>
       <c r="T7">
-        <v>26478.46</v>
+        <v>26463.77</v>
       </c>
       <c r="U7">
-        <v>-5.23</v>
+        <v>-6.77</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1672,40 +1691,40 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>36.79</v>
+        <v>30.98</v>
       </c>
       <c r="AA7">
-        <v>-274.87</v>
+        <v>-312.73</v>
       </c>
       <c r="AB7">
-        <v>-254.73</v>
+        <v>-266.33</v>
       </c>
       <c r="AC7">
-        <v>-20.14</v>
+        <v>-46.4</v>
       </c>
       <c r="AD7">
-        <v>63.23</v>
+        <v>36.85</v>
       </c>
       <c r="AE7">
-        <v>74.08</v>
+        <v>56.62</v>
       </c>
       <c r="AF7">
-        <v>292.44</v>
+        <v>304.72</v>
       </c>
       <c r="AH7">
-        <v>26381.11</v>
+        <v>26338.57</v>
       </c>
       <c r="AI7">
-        <v>24835.76</v>
+        <v>24716.81</v>
       </c>
       <c r="AJ7">
-        <v>25902.18</v>
+        <v>25727.13</v>
       </c>
       <c r="AK7" t="s">
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>28.96</v>
+        <v>33.51</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1719,10 +1738,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>28160.9</v>
+        <v>28086.5</v>
       </c>
       <c r="E8">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1731,43 +1750,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-28.68</v>
+        <v>-28.87</v>
       </c>
       <c r="I8">
-        <v>9.279999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="J8">
-        <v>-2.4</v>
+        <v>-2.58</v>
       </c>
       <c r="K8">
-        <v>-7.12</v>
+        <v>-7.06</v>
       </c>
       <c r="L8">
-        <v>4.15</v>
+        <v>6.8</v>
       </c>
       <c r="M8">
-        <v>-22.73</v>
+        <v>-23.57</v>
       </c>
       <c r="N8">
-        <v>-4.82</v>
+        <v>-4.44</v>
       </c>
       <c r="O8">
         <v>13</v>
       </c>
       <c r="Q8">
-        <v>28423.36</v>
+        <v>28274.48</v>
       </c>
       <c r="R8">
-        <v>29599.08</v>
+        <v>29439.32</v>
       </c>
       <c r="S8">
-        <v>30162.69</v>
+        <v>30139.89</v>
       </c>
       <c r="T8">
-        <v>31621.95</v>
+        <v>31570.58</v>
       </c>
       <c r="U8">
-        <v>-10.95</v>
+        <v>-11.04</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1782,31 +1801,31 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>31.61</v>
+        <v>30.97</v>
       </c>
       <c r="AA8">
-        <v>-571.1</v>
+        <v>-591.98</v>
       </c>
       <c r="AB8">
-        <v>-416.14</v>
+        <v>-451.31</v>
       </c>
       <c r="AC8">
-        <v>-154.96</v>
+        <v>-140.67</v>
       </c>
       <c r="AD8">
         <v>0</v>
       </c>
       <c r="AE8">
-        <v>2.15</v>
+        <v>0.44</v>
       </c>
       <c r="AF8">
-        <v>607.64</v>
+        <v>595.61</v>
       </c>
       <c r="AH8">
-        <v>31841.05</v>
+        <v>31631.26</v>
       </c>
       <c r="AI8">
-        <v>27357.11</v>
+        <v>27247.38</v>
       </c>
       <c r="AJ8">
         <v>29812.93</v>
@@ -1815,7 +1834,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>31.68</v>
+        <v>33.26</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1829,10 +1848,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15881.9</v>
+        <v>15641.05</v>
       </c>
       <c r="E9">
-        <v>0.46</v>
+        <v>-1.52</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1841,31 +1860,31 @@
         <v>15584.65</v>
       </c>
       <c r="H9">
-        <v>-4.68</v>
+        <v>-6.13</v>
       </c>
       <c r="I9">
-        <v>1.91</v>
+        <v>0.36</v>
       </c>
       <c r="J9">
-        <v>-0.3</v>
+        <v>-1.91</v>
       </c>
       <c r="K9">
-        <v>-4.14</v>
+        <v>-5.54</v>
       </c>
       <c r="L9">
-        <v>0.38</v>
+        <v>-1.48</v>
       </c>
       <c r="N9">
-        <v>4.94</v>
+        <v>-0.48</v>
       </c>
       <c r="Q9">
-        <v>15909.01</v>
+        <v>15848.19</v>
       </c>
       <c r="R9">
-        <v>16076.84</v>
+        <v>16030.97</v>
       </c>
       <c r="S9">
-        <v>16250.91</v>
+        <v>16245.22</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1877,31 +1896,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>41.5</v>
+        <v>34.66</v>
       </c>
       <c r="AA9">
-        <v>-133.18</v>
+        <v>-148.02</v>
       </c>
       <c r="AB9">
-        <v>-120.99</v>
+        <v>-126.4</v>
       </c>
       <c r="AC9">
-        <v>-12.19</v>
+        <v>-21.62</v>
       </c>
       <c r="AD9">
-        <v>86.27</v>
+        <v>72.77</v>
       </c>
       <c r="AE9">
-        <v>87.2</v>
+        <v>82.12</v>
       </c>
       <c r="AF9">
-        <v>157.27</v>
+        <v>164.71</v>
       </c>
       <c r="AH9">
-        <v>16632.51</v>
+        <v>16570.47</v>
       </c>
       <c r="AI9">
-        <v>15521.16</v>
+        <v>15491.46</v>
       </c>
       <c r="AJ9">
         <v>16050.69</v>
@@ -1910,7 +1929,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>42.46</v>
+        <v>44.28</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1924,10 +1943,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8957.450000000001</v>
+        <v>8782.5</v>
       </c>
       <c r="E10">
-        <v>0.14</v>
+        <v>-1.95</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1936,43 +1955,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-8.279999999999999</v>
+        <v>-10.07</v>
       </c>
       <c r="I10">
-        <v>4.63</v>
+        <v>2.59</v>
       </c>
       <c r="J10">
-        <v>-1.26</v>
+        <v>-3.04</v>
       </c>
       <c r="K10">
-        <v>-3.57</v>
+        <v>-4.93</v>
       </c>
       <c r="L10">
-        <v>-4.56</v>
+        <v>-6.49</v>
       </c>
       <c r="M10">
-        <v>-2.89</v>
+        <v>-4.85</v>
       </c>
       <c r="N10">
-        <v>12.29</v>
+        <v>11.82</v>
       </c>
       <c r="O10">
         <v>38</v>
       </c>
       <c r="Q10">
-        <v>9015.27</v>
+        <v>8960.129999999999</v>
       </c>
       <c r="R10">
-        <v>9092.23</v>
+        <v>9069.219999999999</v>
       </c>
       <c r="S10">
-        <v>9269.459999999999</v>
+        <v>9257.559999999999</v>
       </c>
       <c r="T10">
-        <v>9304.18</v>
+        <v>9300.58</v>
       </c>
       <c r="U10">
-        <v>-3.73</v>
+        <v>-5.57</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1987,40 +2006,40 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>36.6</v>
+        <v>28.76</v>
       </c>
       <c r="AA10">
-        <v>-85.48999999999999</v>
+        <v>-99.61</v>
       </c>
       <c r="AB10">
-        <v>-83.22</v>
+        <v>-86.48999999999999</v>
       </c>
       <c r="AC10">
-        <v>-2.27</v>
+        <v>-13.11</v>
       </c>
       <c r="AD10">
-        <v>76.2</v>
+        <v>54.24</v>
       </c>
       <c r="AE10">
-        <v>83.56</v>
+        <v>70.69</v>
       </c>
       <c r="AF10">
-        <v>86.09999999999999</v>
+        <v>92.45</v>
       </c>
       <c r="AH10">
-        <v>9309.85</v>
+        <v>9315.309999999999</v>
       </c>
       <c r="AI10">
-        <v>8874.610000000001</v>
+        <v>8823.129999999999</v>
       </c>
       <c r="AJ10">
-        <v>9179.950000000001</v>
+        <v>9132.469999999999</v>
       </c>
       <c r="AK10" t="s">
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>49.57</v>
+        <v>52.51</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2034,55 +2053,55 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1550.65</v>
+        <v>1539.25</v>
       </c>
       <c r="E11">
-        <v>-0.23</v>
+        <v>-0.74</v>
       </c>
       <c r="F11">
-        <v>1627.65</v>
+        <v>1627.3</v>
       </c>
       <c r="G11">
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-4.73</v>
+        <v>-5.41</v>
       </c>
       <c r="I11">
-        <v>23.72</v>
+        <v>22.81</v>
       </c>
       <c r="J11">
-        <v>-0.2</v>
+        <v>-1.07</v>
       </c>
       <c r="K11">
-        <v>-3.75</v>
+        <v>-3.6</v>
       </c>
       <c r="L11">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="M11">
-        <v>-5.01</v>
+        <v>-5.43</v>
       </c>
       <c r="N11">
-        <v>-6.67</v>
+        <v>-6.48</v>
       </c>
       <c r="O11">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="Q11">
-        <v>1560.48</v>
+        <v>1557.14</v>
       </c>
       <c r="R11">
-        <v>1547.5</v>
+        <v>1544.31</v>
       </c>
       <c r="S11">
-        <v>1560.11</v>
+        <v>1560.47</v>
       </c>
       <c r="T11">
-        <v>1453.79</v>
+        <v>1454.28</v>
       </c>
       <c r="U11">
-        <v>6.66</v>
+        <v>5.84</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2097,31 +2116,31 @@
         <v>2</v>
       </c>
       <c r="Z11">
-        <v>49.18</v>
+        <v>46.35</v>
       </c>
       <c r="AA11">
-        <v>-2.44</v>
+        <v>-3.22</v>
       </c>
       <c r="AB11">
-        <v>-4.7</v>
+        <v>-4.4</v>
       </c>
       <c r="AC11">
-        <v>2.26</v>
+        <v>1.18</v>
       </c>
       <c r="AD11">
-        <v>73.92</v>
+        <v>60.37</v>
       </c>
       <c r="AE11">
-        <v>85.27</v>
+        <v>73.38</v>
       </c>
       <c r="AF11">
-        <v>28.74</v>
+        <v>28.67</v>
       </c>
       <c r="AH11">
-        <v>1593.28</v>
+        <v>1582.02</v>
       </c>
       <c r="AI11">
-        <v>1501.71</v>
+        <v>1506.61</v>
       </c>
       <c r="AJ11">
         <v>1604.15</v>
@@ -2130,7 +2149,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>26.46</v>
+        <v>25.26</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2144,10 +2163,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>13087.15</v>
+        <v>12854.4</v>
       </c>
       <c r="E12">
-        <v>0.35</v>
+        <v>-1.78</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2156,43 +2175,43 @@
         <v>9888.25</v>
       </c>
       <c r="H12">
-        <v>-4.6</v>
+        <v>-6.3</v>
       </c>
       <c r="I12">
-        <v>32.35</v>
+        <v>30</v>
       </c>
       <c r="J12">
-        <v>0.26</v>
+        <v>-0.91</v>
       </c>
       <c r="K12">
-        <v>-3.36</v>
+        <v>-4.25</v>
       </c>
       <c r="L12">
-        <v>4.32</v>
+        <v>2.68</v>
       </c>
       <c r="M12">
-        <v>31.89</v>
+        <v>29.12</v>
       </c>
       <c r="N12">
-        <v>18.94</v>
+        <v>18.36</v>
       </c>
       <c r="O12">
         <v>99</v>
       </c>
       <c r="Q12">
-        <v>13078.9</v>
+        <v>13055.24</v>
       </c>
       <c r="R12">
-        <v>13113.9</v>
+        <v>13080.35</v>
       </c>
       <c r="S12">
-        <v>12992.73</v>
+        <v>13001.08</v>
       </c>
       <c r="T12">
-        <v>12325.6</v>
+        <v>12338.52</v>
       </c>
       <c r="U12">
-        <v>6.18</v>
+        <v>4.18</v>
       </c>
       <c r="V12" t="s">
         <v>80</v>
@@ -2207,31 +2226,31 @@
         <v>3</v>
       </c>
       <c r="Z12">
-        <v>50.4</v>
+        <v>44.58</v>
       </c>
       <c r="AA12">
-        <v>-7.89</v>
+        <v>-24.2</v>
       </c>
       <c r="AB12">
-        <v>-2.02</v>
+        <v>-6.46</v>
       </c>
       <c r="AC12">
-        <v>-5.87</v>
+        <v>-17.75</v>
       </c>
       <c r="AD12">
-        <v>68.3</v>
+        <v>49.91</v>
       </c>
       <c r="AE12">
-        <v>64.79000000000001</v>
+        <v>60.89</v>
       </c>
       <c r="AF12">
-        <v>218.48</v>
+        <v>222.51</v>
       </c>
       <c r="AH12">
-        <v>13535.06</v>
+        <v>13469.16</v>
       </c>
       <c r="AI12">
-        <v>12692.74</v>
+        <v>12691.54</v>
       </c>
       <c r="AJ12">
         <v>13387.91</v>
@@ -2240,7 +2259,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>21.47</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2254,55 +2273,55 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9572.85</v>
+        <v>9390.299999999999</v>
       </c>
       <c r="E13">
-        <v>0.18</v>
+        <v>-1.91</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
       </c>
       <c r="G13">
-        <v>9428.700000000001</v>
+        <v>9390.299999999999</v>
       </c>
       <c r="H13">
-        <v>-11.09</v>
+        <v>-12.78</v>
       </c>
       <c r="I13">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>-0.25</v>
+        <v>-2.23</v>
       </c>
       <c r="K13">
-        <v>-1.59</v>
+        <v>-3.21</v>
       </c>
       <c r="L13">
-        <v>-3.98</v>
+        <v>-5.92</v>
       </c>
       <c r="M13">
-        <v>-2.76</v>
+        <v>-4.57</v>
       </c>
       <c r="N13">
-        <v>19.85</v>
+        <v>18.64</v>
       </c>
       <c r="O13">
         <v>44</v>
       </c>
       <c r="Q13">
-        <v>9597.32</v>
+        <v>9554.58</v>
       </c>
       <c r="R13">
-        <v>9641.549999999999</v>
+        <v>9626.6</v>
       </c>
       <c r="S13">
-        <v>9782.09</v>
+        <v>9771.129999999999</v>
       </c>
       <c r="T13">
-        <v>10017.3</v>
+        <v>10016.03</v>
       </c>
       <c r="U13">
-        <v>-4.44</v>
+        <v>-6.25</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2317,31 +2336,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>40.12</v>
+        <v>29.53</v>
       </c>
       <c r="AA13">
-        <v>-59.6</v>
+        <v>-72.69</v>
       </c>
       <c r="AB13">
-        <v>-62.37</v>
+        <v>-64.44</v>
       </c>
       <c r="AC13">
-        <v>2.78</v>
+        <v>-8.26</v>
       </c>
       <c r="AD13">
-        <v>74.01000000000001</v>
+        <v>50.42</v>
       </c>
       <c r="AE13">
-        <v>77.69</v>
+        <v>67.27</v>
       </c>
       <c r="AF13">
-        <v>88.76000000000001</v>
+        <v>95.97</v>
       </c>
       <c r="AH13">
-        <v>9802.799999999999</v>
+        <v>9821.200000000001</v>
       </c>
       <c r="AI13">
-        <v>9480.290000000001</v>
+        <v>9431.99</v>
       </c>
       <c r="AJ13">
         <v>9761.77</v>
@@ -2350,7 +2369,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>32.15</v>
+        <v>35.59</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2364,10 +2383,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8294.5</v>
+        <v>8026.1</v>
       </c>
       <c r="E14">
-        <v>0.28</v>
+        <v>-3.24</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2376,43 +2395,43 @@
         <v>7261.45</v>
       </c>
       <c r="H14">
-        <v>-16.05</v>
+        <v>-18.76</v>
       </c>
       <c r="I14">
-        <v>14.23</v>
+        <v>10.53</v>
       </c>
       <c r="J14">
-        <v>-0.28</v>
+        <v>-3.44</v>
       </c>
       <c r="K14">
-        <v>-4.33</v>
+        <v>-6.54</v>
       </c>
       <c r="L14">
-        <v>-3.03</v>
+        <v>-5.49</v>
       </c>
       <c r="M14">
-        <v>13.38</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="N14">
-        <v>28.52</v>
+        <v>27.33</v>
       </c>
       <c r="O14">
         <v>87</v>
       </c>
       <c r="Q14">
-        <v>8302.959999999999</v>
+        <v>8245.700000000001</v>
       </c>
       <c r="R14">
-        <v>8389.309999999999</v>
+        <v>8360.4</v>
       </c>
       <c r="S14">
-        <v>8482.84</v>
+        <v>8475.719999999999</v>
       </c>
       <c r="T14">
-        <v>8589.940000000001</v>
+        <v>8588.790000000001</v>
       </c>
       <c r="U14">
-        <v>-3.44</v>
+        <v>-6.55</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2427,40 +2446,40 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>42.75</v>
+        <v>31.4</v>
       </c>
       <c r="AA14">
-        <v>-68.8</v>
+        <v>-87.95</v>
       </c>
       <c r="AB14">
-        <v>-64.31999999999999</v>
+        <v>-69.05</v>
       </c>
       <c r="AC14">
-        <v>-4.47</v>
+        <v>-18.9</v>
       </c>
       <c r="AD14">
-        <v>79.73</v>
+        <v>55.74</v>
       </c>
       <c r="AE14">
-        <v>72.79000000000001</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="AF14">
-        <v>115.24</v>
+        <v>126.75</v>
       </c>
       <c r="AH14">
-        <v>8640.719999999999</v>
+        <v>8639.200000000001</v>
       </c>
       <c r="AI14">
-        <v>8137.9</v>
+        <v>8081.6</v>
       </c>
       <c r="AJ14">
-        <v>8626.549999999999</v>
+        <v>8525.58</v>
       </c>
       <c r="AK14" t="s">
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>25.33</v>
+        <v>30.31</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2474,10 +2493,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>27003</v>
+        <v>26761.65</v>
       </c>
       <c r="E15">
-        <v>-0.1</v>
+        <v>-0.89</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2486,43 +2505,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-0.67</v>
+        <v>-1.56</v>
       </c>
       <c r="I15">
-        <v>25.86</v>
+        <v>24.74</v>
       </c>
       <c r="J15">
-        <v>1.1</v>
+        <v>-0.96</v>
       </c>
       <c r="K15">
-        <v>1.41</v>
+        <v>-0.32</v>
       </c>
       <c r="L15">
-        <v>7.04</v>
+        <v>5.67</v>
       </c>
       <c r="M15">
-        <v>21.41</v>
+        <v>18.55</v>
       </c>
       <c r="N15">
-        <v>13.8</v>
+        <v>13.56</v>
       </c>
       <c r="O15">
         <v>93</v>
       </c>
       <c r="Q15">
-        <v>27022.91</v>
+        <v>26971.01</v>
       </c>
       <c r="R15">
-        <v>26748.16</v>
+        <v>26736.65</v>
       </c>
       <c r="S15">
-        <v>26503.75</v>
+        <v>26526.09</v>
       </c>
       <c r="T15">
-        <v>24081.6</v>
+        <v>24100.62</v>
       </c>
       <c r="U15">
-        <v>12.13</v>
+        <v>11.04</v>
       </c>
       <c r="V15" t="s">
         <v>80</v>
@@ -2537,31 +2556,31 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>57.9</v>
+        <v>51.93</v>
       </c>
       <c r="AA15">
-        <v>139.45</v>
+        <v>124.37</v>
       </c>
       <c r="AB15">
-        <v>105.15</v>
+        <v>108.99</v>
       </c>
       <c r="AC15">
-        <v>34.31</v>
+        <v>15.38</v>
       </c>
       <c r="AD15">
-        <v>88.79000000000001</v>
+        <v>73.08</v>
       </c>
       <c r="AE15">
-        <v>91.34999999999999</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="AF15">
-        <v>319.5</v>
+        <v>317.68</v>
       </c>
       <c r="AH15">
-        <v>27320.9</v>
+        <v>27297.9</v>
       </c>
       <c r="AI15">
-        <v>26175.43</v>
+        <v>26175.4</v>
       </c>
       <c r="AJ15">
         <v>26160.58</v>
@@ -2570,7 +2589,7 @@
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>25.45</v>
+        <v>22.69</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2584,10 +2603,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>869.35</v>
+        <v>850.9</v>
       </c>
       <c r="E16">
-        <v>0.92</v>
+        <v>-2.12</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2596,43 +2615,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-10.25</v>
+        <v>-12.16</v>
       </c>
       <c r="I16">
-        <v>33.51</v>
+        <v>30.68</v>
       </c>
       <c r="J16">
-        <v>2.98</v>
+        <v>-0.35</v>
       </c>
       <c r="K16">
-        <v>-4.48</v>
+        <v>-6.45</v>
       </c>
       <c r="L16">
-        <v>6.17</v>
+        <v>2.57</v>
       </c>
       <c r="M16">
-        <v>-5.41</v>
+        <v>-7.35</v>
       </c>
       <c r="N16">
-        <v>11</v>
+        <v>11.19</v>
       </c>
       <c r="O16">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="Q16">
-        <v>863.42</v>
+        <v>862.83</v>
       </c>
       <c r="R16">
-        <v>871.55</v>
+        <v>868.65</v>
       </c>
       <c r="S16">
-        <v>892.34</v>
+        <v>890.99</v>
       </c>
       <c r="T16">
-        <v>827.79</v>
+        <v>827.6</v>
       </c>
       <c r="U16">
-        <v>5.02</v>
+        <v>2.82</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2647,31 +2666,31 @@
         <v>2</v>
       </c>
       <c r="Z16">
-        <v>48.7</v>
+        <v>42.71</v>
       </c>
       <c r="AA16">
-        <v>-10.11</v>
+        <v>-10.26</v>
       </c>
       <c r="AB16">
-        <v>-11.44</v>
+        <v>-11.2</v>
       </c>
       <c r="AC16">
-        <v>1.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AD16">
-        <v>82.45999999999999</v>
+        <v>82.78</v>
       </c>
       <c r="AE16">
-        <v>72.3</v>
+        <v>78.59</v>
       </c>
       <c r="AF16">
-        <v>18.37</v>
+        <v>18.54</v>
       </c>
       <c r="AH16">
-        <v>930.27</v>
+        <v>925.3099999999999</v>
       </c>
       <c r="AI16">
-        <v>812.8200000000001</v>
+        <v>811.99</v>
       </c>
       <c r="AJ16">
         <v>877.53</v>
@@ -2680,7 +2699,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>23.64</v>
+        <v>21.91</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2694,10 +2713,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29613.95</v>
+        <v>29193.7</v>
       </c>
       <c r="E17">
-        <v>0.25</v>
+        <v>-1.42</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2706,43 +2725,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-13.16</v>
+        <v>-14.39</v>
       </c>
       <c r="I17">
-        <v>4.41</v>
+        <v>2.93</v>
       </c>
       <c r="J17">
-        <v>-1.53</v>
+        <v>-2.89</v>
       </c>
       <c r="K17">
-        <v>-4.16</v>
+        <v>-5.06</v>
       </c>
       <c r="L17">
-        <v>-3.3</v>
+        <v>-4.3</v>
       </c>
       <c r="M17">
-        <v>-9.859999999999999</v>
+        <v>-11.63</v>
       </c>
       <c r="N17">
-        <v>3.34</v>
+        <v>3.29</v>
       </c>
       <c r="O17">
         <v>19</v>
       </c>
       <c r="Q17">
-        <v>29850.08</v>
+        <v>29676.52</v>
       </c>
       <c r="R17">
-        <v>30159.47</v>
+        <v>30074.15</v>
       </c>
       <c r="S17">
-        <v>30799.08</v>
+        <v>30754.16</v>
       </c>
       <c r="T17">
-        <v>31354.25</v>
+        <v>31330.99</v>
       </c>
       <c r="U17">
-        <v>-5.55</v>
+        <v>-6.82</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2757,40 +2776,40 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>32.84</v>
+        <v>26.81</v>
       </c>
       <c r="AA17">
-        <v>-295.69</v>
+        <v>-333.55</v>
       </c>
       <c r="AB17">
-        <v>-278.3</v>
+        <v>-289.35</v>
       </c>
       <c r="AC17">
-        <v>-17.4</v>
+        <v>-44.21</v>
       </c>
       <c r="AD17">
-        <v>64.43000000000001</v>
+        <v>37.13</v>
       </c>
       <c r="AE17">
-        <v>76.31999999999999</v>
+        <v>58.73</v>
       </c>
       <c r="AF17">
-        <v>273.7</v>
+        <v>287.56</v>
       </c>
       <c r="AH17">
-        <v>30990.28</v>
+        <v>30934.63</v>
       </c>
       <c r="AI17">
-        <v>29328.67</v>
+        <v>29213.66</v>
       </c>
       <c r="AJ17">
-        <v>30389.24</v>
+        <v>30206.14</v>
       </c>
       <c r="AK17" t="s">
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>30.46</v>
+        <v>34.64</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2804,10 +2823,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16678.55</v>
+        <v>16537.15</v>
       </c>
       <c r="E18">
-        <v>-0.47</v>
+        <v>-0.85</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2816,31 +2835,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
+        <v>-2.39</v>
+      </c>
+      <c r="I18">
+        <v>7.36</v>
+      </c>
+      <c r="J18">
         <v>-1.55</v>
       </c>
-      <c r="I18">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="J18">
-        <v>0.39</v>
-      </c>
       <c r="K18">
-        <v>0.55</v>
+        <v>-1.02</v>
       </c>
       <c r="L18">
-        <v>3.51</v>
+        <v>2.46</v>
       </c>
       <c r="N18">
-        <v>27.55</v>
+        <v>23.09</v>
       </c>
       <c r="Q18">
-        <v>16764.16</v>
+        <v>16712.21</v>
       </c>
       <c r="R18">
-        <v>16613.68</v>
+        <v>16600.61</v>
       </c>
       <c r="S18">
-        <v>16577.71</v>
+        <v>16582.8</v>
       </c>
       <c r="V18" t="s">
         <v>80</v>
@@ -2852,31 +2871,31 @@
         <v>1</v>
       </c>
       <c r="Z18">
-        <v>53</v>
+        <v>47.93</v>
       </c>
       <c r="AA18">
-        <v>48.94</v>
+        <v>36.27</v>
       </c>
       <c r="AB18">
-        <v>26.08</v>
+        <v>28.12</v>
       </c>
       <c r="AC18">
-        <v>22.86</v>
+        <v>8.15</v>
       </c>
       <c r="AD18">
-        <v>81.12</v>
+        <v>61.5</v>
       </c>
       <c r="AE18">
-        <v>87.81999999999999</v>
+        <v>76.75</v>
       </c>
       <c r="AF18">
-        <v>190.85</v>
+        <v>189.11</v>
       </c>
       <c r="AH18">
-        <v>16963.21</v>
+        <v>16940.46</v>
       </c>
       <c r="AI18">
-        <v>16264.14</v>
+        <v>16260.76</v>
       </c>
       <c r="AJ18">
         <v>16262.99</v>
@@ -2885,7 +2904,7 @@
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>21.47</v>
+        <v>19.69</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2899,10 +2918,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9401.65</v>
+        <v>9231.200000000001</v>
       </c>
       <c r="E19">
-        <v>0.43</v>
+        <v>-1.81</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2911,31 +2930,31 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-5.97</v>
+        <v>-7.68</v>
       </c>
       <c r="I19">
-        <v>4.52</v>
+        <v>2.62</v>
       </c>
       <c r="J19">
-        <v>0.53</v>
+        <v>-1.97</v>
       </c>
       <c r="K19">
-        <v>-3.52</v>
+        <v>-5.83</v>
       </c>
       <c r="L19">
-        <v>0.11</v>
+        <v>-3.03</v>
       </c>
       <c r="N19">
-        <v>16.61</v>
+        <v>9.15</v>
       </c>
       <c r="Q19">
-        <v>9422.620000000001</v>
+        <v>9385.48</v>
       </c>
       <c r="R19">
-        <v>9564.68</v>
+        <v>9538.66</v>
       </c>
       <c r="S19">
-        <v>9568.49</v>
+        <v>9566.200000000001</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2947,31 +2966,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>44.14</v>
+        <v>38.43</v>
       </c>
       <c r="AA19">
-        <v>-75.09999999999999</v>
+        <v>-87.72</v>
       </c>
       <c r="AB19">
-        <v>-51.01</v>
+        <v>-58.35</v>
       </c>
       <c r="AC19">
-        <v>-24.09</v>
+        <v>-29.37</v>
       </c>
       <c r="AD19">
-        <v>35.78</v>
+        <v>28.96</v>
       </c>
       <c r="AE19">
-        <v>37.56</v>
+        <v>34.14</v>
       </c>
       <c r="AF19">
-        <v>158.29</v>
+        <v>161.33</v>
       </c>
       <c r="AH19">
-        <v>10049.77</v>
+        <v>10037.17</v>
       </c>
       <c r="AI19">
-        <v>9079.6</v>
+        <v>9040.15</v>
       </c>
       <c r="AJ19">
         <v>9616.870000000001</v>
@@ -2980,7 +2999,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>25.19</v>
+        <v>26.94</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2994,43 +3013,43 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10862.15</v>
+        <v>10660.6</v>
       </c>
       <c r="E20">
-        <v>-0.07000000000000001</v>
+        <v>-1.86</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
       </c>
       <c r="G20">
-        <v>10796.4</v>
+        <v>10660.6</v>
       </c>
       <c r="H20">
-        <v>-4.46</v>
+        <v>-6.23</v>
       </c>
       <c r="I20">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>-0.79</v>
+        <v>-3.14</v>
       </c>
       <c r="K20">
-        <v>-2.58</v>
+        <v>-3.62</v>
       </c>
       <c r="L20">
-        <v>-1.36</v>
+        <v>-3.35</v>
       </c>
       <c r="N20">
-        <v>-4.66</v>
+        <v>-10.4</v>
       </c>
       <c r="Q20">
-        <v>10940.47</v>
+        <v>10871.34</v>
       </c>
       <c r="R20">
-        <v>11009.09</v>
+        <v>10988.73</v>
       </c>
       <c r="S20">
-        <v>11130.32</v>
+        <v>11117.55</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3042,40 +3061,40 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>38.35</v>
+        <v>29.71</v>
       </c>
       <c r="AA20">
-        <v>-68.59999999999999</v>
+        <v>-86.70999999999999</v>
       </c>
       <c r="AB20">
-        <v>-62.57</v>
+        <v>-67.40000000000001</v>
       </c>
       <c r="AC20">
-        <v>-6.03</v>
+        <v>-19.31</v>
       </c>
       <c r="AD20">
-        <v>64.84999999999999</v>
+        <v>44.15</v>
       </c>
       <c r="AE20">
-        <v>69.56999999999999</v>
+        <v>58.74</v>
       </c>
       <c r="AF20">
-        <v>118.94</v>
+        <v>125.95</v>
       </c>
       <c r="AH20">
-        <v>11246.84</v>
+        <v>11270.91</v>
       </c>
       <c r="AI20">
-        <v>10771.33</v>
+        <v>10706.55</v>
       </c>
       <c r="AJ20">
-        <v>11201.19</v>
+        <v>11119.35</v>
       </c>
       <c r="AK20" t="s">
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>33.26</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3089,10 +3108,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>26883.2</v>
+        <v>26476.4</v>
       </c>
       <c r="E21">
-        <v>0.45</v>
+        <v>-1.51</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3101,43 +3120,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-7.9</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="I21">
-        <v>11.34</v>
+        <v>9.66</v>
       </c>
       <c r="J21">
-        <v>-1.49</v>
+        <v>-3.27</v>
       </c>
       <c r="K21">
-        <v>-3.06</v>
+        <v>-4.62</v>
       </c>
       <c r="L21">
-        <v>-4.16</v>
+        <v>-5.2</v>
       </c>
       <c r="M21">
-        <v>-0.54</v>
+        <v>-2.47</v>
       </c>
       <c r="N21">
-        <v>6.15</v>
+        <v>5.97</v>
       </c>
       <c r="O21">
         <v>50</v>
       </c>
       <c r="Q21">
-        <v>27133.32</v>
+        <v>26954.58</v>
       </c>
       <c r="R21">
-        <v>27417.03</v>
+        <v>27353.99</v>
       </c>
       <c r="S21">
-        <v>27652.27</v>
+        <v>27611.63</v>
       </c>
       <c r="T21">
-        <v>27543.01</v>
+        <v>27531.79</v>
       </c>
       <c r="U21">
-        <v>-2.4</v>
+        <v>-3.83</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3152,40 +3171,40 @@
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>38.84</v>
+        <v>32.83</v>
       </c>
       <c r="AA21">
-        <v>-161.19</v>
+        <v>-207.83</v>
       </c>
       <c r="AB21">
-        <v>-114.87</v>
+        <v>-133.46</v>
       </c>
       <c r="AC21">
-        <v>-46.32</v>
+        <v>-74.37</v>
       </c>
       <c r="AD21">
-        <v>25.46</v>
+        <v>6.62</v>
       </c>
       <c r="AE21">
-        <v>36.75</v>
+        <v>21.76</v>
       </c>
       <c r="AF21">
-        <v>301.81</v>
+        <v>313.59</v>
       </c>
       <c r="AH21">
-        <v>28065</v>
+        <v>28107.53</v>
       </c>
       <c r="AI21">
-        <v>26769.07</v>
+        <v>26600.46</v>
       </c>
       <c r="AJ21">
-        <v>27749.6</v>
+        <v>27532.68</v>
       </c>
       <c r="AK21" t="s">
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>25.94</v>
+        <v>31.4</v>
       </c>
     </row>
   </sheetData>
@@ -3326,7 +3345,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3366,7 +3385,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3385,57 +3404,57 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>97</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>94</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>100</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="E6" s="5" t="s">
         <v>80</v>
@@ -3446,7 +3465,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
@@ -3458,16 +3477,16 @@
         <v>0</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -3478,13 +3497,13 @@
         <v>10</v>
       </c>
       <c r="C10" s="7">
-        <v>-8.51</v>
+        <v>-7.01</v>
       </c>
       <c r="D10" s="7">
-        <v>-7.01</v>
+        <v>-8.17</v>
       </c>
       <c r="E10" s="8">
-        <v>1.5</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -3495,13 +3514,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="7">
-        <v>-3.56</v>
+        <v>-3.4</v>
       </c>
       <c r="D11" s="7">
-        <v>-3.4</v>
+        <v>-4.57</v>
       </c>
       <c r="E11" s="8">
-        <v>0.16</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -3512,13 +3531,13 @@
         <v>10</v>
       </c>
       <c r="C12" s="7">
-        <v>-6.12</v>
+        <v>-4.62</v>
       </c>
       <c r="D12" s="7">
-        <v>-4.62</v>
+        <v>-5.46</v>
       </c>
       <c r="E12" s="8">
-        <v>1.5</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -3529,13 +3548,13 @@
         <v>10</v>
       </c>
       <c r="C13" s="7">
-        <v>-2.48</v>
+        <v>-1.73</v>
       </c>
       <c r="D13" s="7">
-        <v>-1.73</v>
+        <v>-3.7</v>
       </c>
       <c r="E13" s="8">
-        <v>0.75</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -3546,13 +3565,13 @@
         <v>10</v>
       </c>
       <c r="C14" s="7">
-        <v>-4.08</v>
+        <v>-2.78</v>
       </c>
       <c r="D14" s="7">
-        <v>-2.78</v>
+        <v>-3.76</v>
       </c>
       <c r="E14" s="8">
-        <v>1.3</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -3563,13 +3582,13 @@
         <v>10</v>
       </c>
       <c r="C15" s="7">
-        <v>-4.93</v>
+        <v>-4.9</v>
       </c>
       <c r="D15" s="7">
-        <v>-4.9</v>
+        <v>-6.12</v>
       </c>
       <c r="E15" s="8">
-        <v>0.03</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3580,13 +3599,13 @@
         <v>10</v>
       </c>
       <c r="C16" s="7">
-        <v>-8.33</v>
+        <v>-7.12</v>
       </c>
       <c r="D16" s="7">
-        <v>-7.12</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1.21</v>
+        <v>-7.06</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.06</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3597,13 +3616,13 @@
         <v>10</v>
       </c>
       <c r="C17" s="7">
-        <v>-4.64</v>
+        <v>-4.14</v>
       </c>
       <c r="D17" s="7">
-        <v>-4.14</v>
+        <v>-5.54</v>
       </c>
       <c r="E17" s="8">
-        <v>0.5</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3614,13 +3633,13 @@
         <v>10</v>
       </c>
       <c r="C18" s="7">
-        <v>-4.86</v>
+        <v>-3.57</v>
       </c>
       <c r="D18" s="7">
-        <v>-3.57</v>
+        <v>-4.93</v>
       </c>
       <c r="E18" s="8">
-        <v>1.29</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3631,13 +3650,13 @@
         <v>10</v>
       </c>
       <c r="C19" s="7">
-        <v>-3.46</v>
+        <v>-3.75</v>
       </c>
       <c r="D19" s="7">
-        <v>-3.75</v>
+        <v>-3.6</v>
       </c>
       <c r="E19" s="9">
-        <v>-0.29</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3648,12 +3667,12 @@
         <v>10</v>
       </c>
       <c r="C20" s="7">
-        <v>-2.47</v>
+        <v>-3.36</v>
       </c>
       <c r="D20" s="7">
-        <v>-3.36</v>
-      </c>
-      <c r="E20" s="9">
+        <v>-4.25</v>
+      </c>
+      <c r="E20" s="8">
         <v>-0.89</v>
       </c>
     </row>
@@ -3665,13 +3684,13 @@
         <v>10</v>
       </c>
       <c r="C21" s="7">
-        <v>-2.47</v>
+        <v>-1.59</v>
       </c>
       <c r="D21" s="7">
-        <v>-1.59</v>
+        <v>-3.21</v>
       </c>
       <c r="E21" s="8">
-        <v>0.88</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -3682,13 +3701,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="7">
-        <v>-3.86</v>
+        <v>-4.33</v>
       </c>
       <c r="D22" s="7">
-        <v>-4.33</v>
-      </c>
-      <c r="E22" s="9">
-        <v>-0.47</v>
+        <v>-6.54</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -3699,13 +3718,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="7">
-        <v>1.75</v>
+        <v>1.41</v>
       </c>
       <c r="D23" s="7">
-        <v>1.41</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-0.34</v>
+        <v>-0.32</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -3716,13 +3735,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="7">
-        <v>-6.15</v>
+        <v>-4.48</v>
       </c>
       <c r="D24" s="7">
-        <v>-4.48</v>
+        <v>-6.45</v>
       </c>
       <c r="E24" s="8">
-        <v>1.67</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -3733,13 +3752,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="7">
-        <v>-4.71</v>
+        <v>-4.16</v>
       </c>
       <c r="D25" s="7">
-        <v>-4.16</v>
+        <v>-5.06</v>
       </c>
       <c r="E25" s="8">
-        <v>0.55</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -3750,13 +3769,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="7">
-        <v>0.96</v>
+        <v>0.55</v>
       </c>
       <c r="D26" s="7">
-        <v>0.55</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-0.41</v>
+        <v>-1.02</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -3767,13 +3786,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="7">
-        <v>-4.11</v>
+        <v>-3.52</v>
       </c>
       <c r="D27" s="7">
-        <v>-3.52</v>
+        <v>-5.83</v>
       </c>
       <c r="E27" s="8">
-        <v>0.59</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -3784,13 +3803,13 @@
         <v>10</v>
       </c>
       <c r="C28" s="7">
-        <v>-3.08</v>
+        <v>-2.58</v>
       </c>
       <c r="D28" s="7">
-        <v>-2.58</v>
+        <v>-3.62</v>
       </c>
       <c r="E28" s="8">
-        <v>0.5</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -3801,13 +3820,13 @@
         <v>10</v>
       </c>
       <c r="C29" s="7">
-        <v>-2.49</v>
+        <v>-3.06</v>
       </c>
       <c r="D29" s="7">
-        <v>-3.06</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.57</v>
+        <v>-4.62</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -3818,13 +3837,13 @@
         <v>9</v>
       </c>
       <c r="C30" s="7">
-        <v>-1.58</v>
+        <v>-0.59</v>
       </c>
       <c r="D30" s="7">
-        <v>-0.59</v>
+        <v>-2.31</v>
       </c>
       <c r="E30" s="8">
-        <v>0.99</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -3835,13 +3854,13 @@
         <v>9</v>
       </c>
       <c r="C31" s="7">
-        <v>0.15</v>
+        <v>-0.27</v>
       </c>
       <c r="D31" s="7">
-        <v>-0.27</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-0.42</v>
+        <v>-1.86</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-1.59</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -3852,13 +3871,13 @@
         <v>9</v>
       </c>
       <c r="C32" s="7">
-        <v>-0.65</v>
+        <v>-0.4</v>
       </c>
       <c r="D32" s="7">
-        <v>-0.4</v>
+        <v>-2.08</v>
       </c>
       <c r="E32" s="8">
-        <v>0.25</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -3869,13 +3888,13 @@
         <v>9</v>
       </c>
       <c r="C33" s="7">
-        <v>-0.06</v>
+        <v>-0.88</v>
       </c>
       <c r="D33" s="7">
-        <v>-0.88</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-0.82</v>
+        <v>-2.98</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-2.1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -3886,13 +3905,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="7">
-        <v>0.41</v>
+        <v>1.04</v>
       </c>
       <c r="D34" s="7">
-        <v>1.04</v>
+        <v>-1.39</v>
       </c>
       <c r="E34" s="8">
-        <v>0.63</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -3903,13 +3922,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="7">
-        <v>-1.44</v>
+        <v>-1.63</v>
       </c>
       <c r="D35" s="7">
-        <v>-1.63</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-0.19</v>
+        <v>-3.34</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -3920,13 +3939,13 @@
         <v>9</v>
       </c>
       <c r="C36" s="7">
-        <v>-3.25</v>
+        <v>-2.4</v>
       </c>
       <c r="D36" s="7">
-        <v>-2.4</v>
+        <v>-2.58</v>
       </c>
       <c r="E36" s="8">
-        <v>0.85</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -3937,13 +3956,13 @@
         <v>9</v>
       </c>
       <c r="C37" s="7">
-        <v>-0.11</v>
+        <v>-0.3</v>
       </c>
       <c r="D37" s="7">
-        <v>-0.3</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.19</v>
+        <v>-1.91</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -3954,13 +3973,13 @@
         <v>9</v>
       </c>
       <c r="C38" s="7">
-        <v>-0.27</v>
+        <v>-1.26</v>
       </c>
       <c r="D38" s="7">
-        <v>-1.26</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.99</v>
+        <v>-3.04</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -3971,13 +3990,13 @@
         <v>9</v>
       </c>
       <c r="C39" s="7">
-        <v>1.38</v>
+        <v>-0.2</v>
       </c>
       <c r="D39" s="7">
-        <v>-0.2</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-1.58</v>
+        <v>-1.07</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -3988,12 +4007,12 @@
         <v>9</v>
       </c>
       <c r="C40" s="7">
-        <v>1.43</v>
+        <v>0.26</v>
       </c>
       <c r="D40" s="7">
-        <v>0.26</v>
-      </c>
-      <c r="E40" s="9">
+        <v>-0.91</v>
+      </c>
+      <c r="E40" s="8">
         <v>-1.17</v>
       </c>
     </row>
@@ -4005,13 +4024,13 @@
         <v>9</v>
       </c>
       <c r="C41" s="7">
-        <v>0.01</v>
+        <v>-0.25</v>
       </c>
       <c r="D41" s="7">
-        <v>-0.25</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-0.26</v>
+        <v>-2.23</v>
+      </c>
+      <c r="E41" s="8">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -4022,13 +4041,13 @@
         <v>9</v>
       </c>
       <c r="C42" s="7">
-        <v>0.1</v>
+        <v>-0.28</v>
       </c>
       <c r="D42" s="7">
-        <v>-0.28</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.38</v>
+        <v>-3.44</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-3.16</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -4039,13 +4058,13 @@
         <v>9</v>
       </c>
       <c r="C43" s="7">
-        <v>1.69</v>
+        <v>1.1</v>
       </c>
       <c r="D43" s="7">
-        <v>1.1</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-0.59</v>
+        <v>-0.96</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -4056,13 +4075,13 @@
         <v>9</v>
       </c>
       <c r="C44" s="7">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="D44" s="7">
-        <v>2.98</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-0.27</v>
+        <v>-0.35</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-3.33</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4073,13 +4092,13 @@
         <v>9</v>
       </c>
       <c r="C45" s="7">
-        <v>-0.98</v>
+        <v>-1.53</v>
       </c>
       <c r="D45" s="7">
-        <v>-1.53</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-0.55</v>
+        <v>-2.89</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-1.36</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -4090,13 +4109,13 @@
         <v>9</v>
       </c>
       <c r="C46" s="7">
-        <v>1.38</v>
+        <v>0.39</v>
       </c>
       <c r="D46" s="7">
-        <v>0.39</v>
-      </c>
-      <c r="E46" s="9">
-        <v>-0.99</v>
+        <v>-1.55</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -4107,13 +4126,13 @@
         <v>9</v>
       </c>
       <c r="C47" s="7">
-        <v>0.97</v>
+        <v>0.53</v>
       </c>
       <c r="D47" s="7">
-        <v>0.53</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-0.44</v>
+        <v>-1.97</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.5</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -4124,1696 +4143,1713 @@
         <v>9</v>
       </c>
       <c r="C48" s="7">
-        <v>0.12</v>
+        <v>-0.79</v>
       </c>
       <c r="D48" s="7">
-        <v>-0.79</v>
-      </c>
-      <c r="E48" s="9">
-        <v>-0.91</v>
+        <v>-3.14</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-2.35</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="6" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C49" s="7">
-        <v>-1.53</v>
+        <v>-1.49</v>
       </c>
       <c r="D49" s="7">
-        <v>-1.2</v>
+        <v>-3.27</v>
       </c>
       <c r="E49" s="8">
-        <v>0.33</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="7">
-        <v>5.89</v>
+        <v>-1.2</v>
       </c>
       <c r="D50" s="7">
-        <v>5.99</v>
+        <v>-2.94</v>
       </c>
       <c r="E50" s="8">
-        <v>0.1</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="7">
-        <v>-8.59</v>
+        <v>5.99</v>
       </c>
       <c r="D51" s="7">
-        <v>-8.26</v>
+        <v>3.99</v>
       </c>
       <c r="E51" s="8">
-        <v>0.33</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="7">
-        <v>5.42</v>
+        <v>-8.26</v>
       </c>
       <c r="D52" s="7">
-        <v>5.26</v>
-      </c>
-      <c r="E52" s="9">
-        <v>-0.16</v>
+        <v>-9.73</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-1.47</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="7">
-        <v>-18.86</v>
+        <v>5.26</v>
       </c>
       <c r="D53" s="7">
-        <v>-18.43</v>
+        <v>3.53</v>
       </c>
       <c r="E53" s="8">
-        <v>0.43</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="7">
-        <v>-5.82</v>
+        <v>-18.43</v>
       </c>
       <c r="D54" s="7">
-        <v>-5.53</v>
+        <v>-19.92</v>
       </c>
       <c r="E54" s="8">
-        <v>0.29</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="7">
-        <v>-22.1</v>
+        <v>-5.53</v>
       </c>
       <c r="D55" s="7">
-        <v>-22.73</v>
-      </c>
-      <c r="E55" s="9">
-        <v>-0.63</v>
+        <v>-7.59</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="7">
-        <v>-2.67</v>
+        <v>-22.73</v>
       </c>
       <c r="D56" s="7">
-        <v>-2.89</v>
-      </c>
-      <c r="E56" s="9">
-        <v>-0.22</v>
+        <v>-23.57</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="7">
-        <v>-4.51</v>
+        <v>-2.89</v>
       </c>
       <c r="D57" s="7">
-        <v>-5.01</v>
-      </c>
-      <c r="E57" s="9">
-        <v>-0.5</v>
+        <v>-4.85</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="7">
-        <v>30.77</v>
+        <v>-5.01</v>
       </c>
       <c r="D58" s="7">
-        <v>31.89</v>
+        <v>-5.43</v>
       </c>
       <c r="E58" s="8">
-        <v>1.12</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="7">
-        <v>-2.22</v>
+        <v>31.89</v>
       </c>
       <c r="D59" s="7">
-        <v>-2.76</v>
-      </c>
-      <c r="E59" s="9">
-        <v>-0.54</v>
+        <v>29.12</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-2.77</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="7">
-        <v>16.01</v>
+        <v>-2.76</v>
       </c>
       <c r="D60" s="7">
-        <v>13.38</v>
-      </c>
-      <c r="E60" s="9">
-        <v>-2.63</v>
+        <v>-4.57</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-1.81</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="7">
-        <v>21.4</v>
+        <v>13.38</v>
       </c>
       <c r="D61" s="7">
-        <v>21.41</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E61" s="8">
-        <v>0.01</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="7">
-        <v>-5.89</v>
+        <v>21.41</v>
       </c>
       <c r="D62" s="7">
-        <v>-5.41</v>
+        <v>18.55</v>
       </c>
       <c r="E62" s="8">
-        <v>0.48</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="7">
-        <v>-9.800000000000001</v>
+        <v>-5.41</v>
       </c>
       <c r="D63" s="7">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="E63" s="9">
-        <v>-0.06</v>
+        <v>-7.35</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-1.94</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="7">
-        <v>-0.61</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="D64" s="7">
-        <v>-0.54</v>
+        <v>-11.63</v>
       </c>
       <c r="E64" s="8">
-        <v>0.07000000000000001</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="6" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" s="7">
-        <v>-0.92</v>
+        <v>-0.54</v>
       </c>
       <c r="D65" s="7">
-        <v>2.08</v>
+        <v>-2.47</v>
       </c>
       <c r="E65" s="8">
-        <v>3</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="7">
-        <v>-3.44</v>
+        <v>2.08</v>
       </c>
       <c r="D66" s="7">
-        <v>-2.84</v>
+        <v>0.17</v>
       </c>
       <c r="E66" s="8">
-        <v>0.6</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="7">
-        <v>-2.07</v>
+        <v>-2.84</v>
       </c>
       <c r="D67" s="7">
-        <v>-0.66</v>
+        <v>-4.36</v>
       </c>
       <c r="E67" s="8">
-        <v>1.41</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="7">
-        <v>-5.74</v>
+        <v>-0.66</v>
       </c>
       <c r="D68" s="7">
-        <v>-5.73</v>
+        <v>-2.13</v>
       </c>
       <c r="E68" s="8">
-        <v>0.01</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="7">
-        <v>-7.41</v>
+        <v>-5.73</v>
       </c>
       <c r="D69" s="7">
-        <v>-6.49</v>
+        <v>-7.67</v>
       </c>
       <c r="E69" s="8">
-        <v>0.92</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="7">
-        <v>-6.79</v>
+        <v>-6.49</v>
       </c>
       <c r="D70" s="7">
-        <v>-5.65</v>
+        <v>-7.23</v>
       </c>
       <c r="E70" s="8">
-        <v>1.14</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="7">
-        <v>3.21</v>
+        <v>-5.65</v>
       </c>
       <c r="D71" s="7">
-        <v>4.15</v>
+        <v>-7.09</v>
       </c>
       <c r="E71" s="8">
-        <v>0.9399999999999999</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="7">
-        <v>-0.72</v>
+        <v>4.15</v>
       </c>
       <c r="D72" s="7">
-        <v>0.38</v>
-      </c>
-      <c r="E72" s="8">
-        <v>1.1</v>
+        <v>6.8</v>
+      </c>
+      <c r="E72" s="9">
+        <v>2.65</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="7">
-        <v>-5.45</v>
+        <v>0.38</v>
       </c>
       <c r="D73" s="7">
-        <v>-4.56</v>
+        <v>-1.48</v>
       </c>
       <c r="E73" s="8">
-        <v>0.89</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="7">
-        <v>2.94</v>
+        <v>-4.56</v>
       </c>
       <c r="D74" s="7">
-        <v>4.08</v>
+        <v>-6.49</v>
       </c>
       <c r="E74" s="8">
-        <v>1.14</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="7">
-        <v>4.79</v>
+        <v>4.08</v>
       </c>
       <c r="D75" s="7">
-        <v>4.32</v>
+        <v>4.12</v>
       </c>
       <c r="E75" s="9">
-        <v>-0.47</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="7">
-        <v>-4</v>
+        <v>4.32</v>
       </c>
       <c r="D76" s="7">
-        <v>-3.98</v>
+        <v>2.68</v>
       </c>
       <c r="E76" s="8">
-        <v>0.02</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="7">
-        <v>-4.23</v>
+        <v>-3.98</v>
       </c>
       <c r="D77" s="7">
-        <v>-3.03</v>
+        <v>-5.92</v>
       </c>
       <c r="E77" s="8">
-        <v>1.2</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="7">
-        <v>8.25</v>
+        <v>-3.03</v>
       </c>
       <c r="D78" s="7">
-        <v>7.04</v>
-      </c>
-      <c r="E78" s="9">
-        <v>-1.21</v>
+        <v>-5.49</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-2.46</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="7">
-        <v>4.25</v>
+        <v>7.04</v>
       </c>
       <c r="D79" s="7">
-        <v>6.17</v>
+        <v>5.67</v>
       </c>
       <c r="E79" s="8">
-        <v>1.92</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="7">
-        <v>-3.77</v>
+        <v>6.17</v>
       </c>
       <c r="D80" s="7">
-        <v>-3.3</v>
+        <v>2.57</v>
       </c>
       <c r="E80" s="8">
-        <v>0.47</v>
+        <v>-3.6</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="7">
-        <v>4.97</v>
+        <v>-3.3</v>
       </c>
       <c r="D81" s="7">
-        <v>3.51</v>
-      </c>
-      <c r="E81" s="9">
-        <v>-1.46</v>
+        <v>-4.3</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-1</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="7">
-        <v>-0.37</v>
+        <v>3.51</v>
       </c>
       <c r="D82" s="7">
-        <v>0.11</v>
+        <v>2.46</v>
       </c>
       <c r="E82" s="8">
-        <v>0.48</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="7">
-        <v>-2.45</v>
+        <v>0.11</v>
       </c>
       <c r="D83" s="7">
-        <v>-1.36</v>
+        <v>-3.03</v>
       </c>
       <c r="E83" s="8">
-        <v>1.09</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="7">
-        <v>-5.5</v>
+        <v>-1.36</v>
       </c>
       <c r="D84" s="7">
-        <v>-4.16</v>
+        <v>-3.35</v>
       </c>
       <c r="E84" s="8">
-        <v>1.34</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="6" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C85" s="7">
-        <v>-9.84</v>
+        <v>-4.16</v>
       </c>
       <c r="D85" s="7">
-        <v>-9.039999999999999</v>
+        <v>-5.2</v>
       </c>
       <c r="E85" s="8">
-        <v>0.8</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="7">
-        <v>-9.4</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="D86" s="7">
-        <v>-9.16</v>
+        <v>-10.53</v>
       </c>
       <c r="E86" s="8">
-        <v>0.24</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="7">
-        <v>-10.17</v>
+        <v>-9.16</v>
       </c>
       <c r="D87" s="7">
-        <v>-9.68</v>
+        <v>-10.82</v>
       </c>
       <c r="E87" s="8">
-        <v>0.49</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="7">
-        <v>-10.05</v>
+        <v>-9.68</v>
       </c>
       <c r="D88" s="7">
-        <v>-9.859999999999999</v>
+        <v>-10.83</v>
       </c>
       <c r="E88" s="8">
-        <v>0.19</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="7">
-        <v>-19.4</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="D89" s="7">
-        <v>-19.08</v>
+        <v>-11.66</v>
       </c>
       <c r="E89" s="8">
-        <v>0.32</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="7">
-        <v>-12.33</v>
+        <v>-19.08</v>
       </c>
       <c r="D90" s="7">
-        <v>-11.83</v>
+        <v>-20.27</v>
       </c>
       <c r="E90" s="8">
-        <v>0.5</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="7">
-        <v>-28.56</v>
+        <v>-11.83</v>
       </c>
       <c r="D91" s="7">
-        <v>-28.68</v>
-      </c>
-      <c r="E91" s="9">
-        <v>-0.12</v>
+        <v>-13.32</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-1.49</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="7">
-        <v>-5.12</v>
+        <v>-28.68</v>
       </c>
       <c r="D92" s="7">
-        <v>-4.68</v>
+        <v>-28.87</v>
       </c>
       <c r="E92" s="8">
-        <v>0.44</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="7">
-        <v>-8.41</v>
+        <v>-4.68</v>
       </c>
       <c r="D93" s="7">
-        <v>-8.279999999999999</v>
+        <v>-6.13</v>
       </c>
       <c r="E93" s="8">
-        <v>0.13</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="7">
-        <v>-4.79</v>
+        <v>-8.279999999999999</v>
       </c>
       <c r="D94" s="7">
-        <v>-4.73</v>
+        <v>-10.07</v>
       </c>
       <c r="E94" s="8">
-        <v>0.06</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="7">
-        <v>-4.93</v>
+        <v>-4.73</v>
       </c>
       <c r="D95" s="7">
-        <v>-4.6</v>
+        <v>-5.41</v>
       </c>
       <c r="E95" s="8">
-        <v>0.33</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="7">
-        <v>-11.25</v>
+        <v>-4.6</v>
       </c>
       <c r="D96" s="7">
-        <v>-11.09</v>
+        <v>-6.3</v>
       </c>
       <c r="E96" s="8">
-        <v>0.16</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="7">
-        <v>-16.28</v>
+        <v>-11.09</v>
       </c>
       <c r="D97" s="7">
-        <v>-16.05</v>
+        <v>-12.78</v>
       </c>
       <c r="E97" s="8">
-        <v>0.23</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="7">
-        <v>-0.58</v>
+        <v>-16.05</v>
       </c>
       <c r="D98" s="7">
-        <v>-0.67</v>
-      </c>
-      <c r="E98" s="9">
-        <v>-0.09</v>
+        <v>-18.76</v>
+      </c>
+      <c r="E98" s="8">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="7">
-        <v>-11.07</v>
+        <v>-0.67</v>
       </c>
       <c r="D99" s="7">
-        <v>-10.25</v>
+        <v>-1.56</v>
       </c>
       <c r="E99" s="8">
-        <v>0.82</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="7">
-        <v>-13.38</v>
+        <v>-10.25</v>
       </c>
       <c r="D100" s="7">
-        <v>-13.16</v>
+        <v>-12.16</v>
       </c>
       <c r="E100" s="8">
-        <v>0.22</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="7">
-        <v>-1.09</v>
+        <v>-13.16</v>
       </c>
       <c r="D101" s="7">
-        <v>-1.55</v>
-      </c>
-      <c r="E101" s="9">
-        <v>-0.46</v>
+        <v>-14.39</v>
+      </c>
+      <c r="E101" s="8">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="7">
-        <v>-6.37</v>
+        <v>-1.55</v>
       </c>
       <c r="D102" s="7">
-        <v>-5.97</v>
+        <v>-2.39</v>
       </c>
       <c r="E102" s="8">
-        <v>0.4</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="7">
-        <v>-4.39</v>
+        <v>-5.97</v>
       </c>
       <c r="D103" s="7">
-        <v>-4.46</v>
-      </c>
-      <c r="E103" s="9">
-        <v>-0.07000000000000001</v>
+        <v>-7.68</v>
+      </c>
+      <c r="E103" s="8">
+        <v>-1.71</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="7">
-        <v>-8.300000000000001</v>
+        <v>-4.46</v>
       </c>
       <c r="D104" s="7">
-        <v>-7.9</v>
+        <v>-6.23</v>
       </c>
       <c r="E104" s="8">
-        <v>0.4</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="6" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C105" s="7">
-        <v>26730.1</v>
+        <v>-7.9</v>
       </c>
       <c r="D105" s="7">
-        <v>26967.9</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="E105" s="8">
-        <v>237.8</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="7">
-        <v>9515.6</v>
+        <v>26967.9</v>
       </c>
       <c r="D106" s="7">
-        <v>9540.75</v>
+        <v>26525.05</v>
       </c>
       <c r="E106" s="8">
-        <v>25.15</v>
+        <v>-442.85</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="7">
-        <v>11353.45</v>
+        <v>9540.75</v>
       </c>
       <c r="D107" s="7">
-        <v>11415.4</v>
+        <v>9366.4</v>
       </c>
       <c r="E107" s="8">
-        <v>61.95</v>
+        <v>-174.35</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="7">
-        <v>37360.95</v>
+        <v>11415.4</v>
       </c>
       <c r="D108" s="7">
-        <v>37440.35</v>
+        <v>11270.1</v>
       </c>
       <c r="E108" s="8">
-        <v>79.40000000000001</v>
+        <v>-145.3</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="7">
-        <v>45759.35</v>
+        <v>37440.35</v>
       </c>
       <c r="D109" s="7">
-        <v>45941.3</v>
+        <v>36693.2</v>
       </c>
       <c r="E109" s="8">
-        <v>181.95</v>
+        <v>-747.15</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="7">
-        <v>24954.15</v>
+        <v>45941.3</v>
       </c>
       <c r="D110" s="7">
-        <v>25094.85</v>
+        <v>45264.35</v>
       </c>
       <c r="E110" s="8">
-        <v>140.7</v>
+        <v>-676.95</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="7">
-        <v>28208.85</v>
+        <v>25094.85</v>
       </c>
       <c r="D111" s="7">
-        <v>28160.9</v>
-      </c>
-      <c r="E111" s="9">
-        <v>-47.95</v>
+        <v>24671.65</v>
+      </c>
+      <c r="E111" s="8">
+        <v>-423.2</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="7">
-        <v>15809.8</v>
+        <v>28160.9</v>
       </c>
       <c r="D112" s="7">
-        <v>15881.9</v>
+        <v>28086.5</v>
       </c>
       <c r="E112" s="8">
-        <v>72.09999999999999</v>
+        <v>-74.40000000000001</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="7">
-        <v>8944.85</v>
+        <v>15881.9</v>
       </c>
       <c r="D113" s="7">
-        <v>8957.450000000001</v>
+        <v>15641.05</v>
       </c>
       <c r="E113" s="8">
-        <v>12.6</v>
+        <v>-240.85</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="7">
-        <v>1554.25</v>
+        <v>8957.450000000001</v>
       </c>
       <c r="D114" s="7">
-        <v>1550.65</v>
-      </c>
-      <c r="E114" s="9">
-        <v>-3.6</v>
+        <v>8782.5</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-174.95</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="7">
-        <v>13041.95</v>
+        <v>1550.65</v>
       </c>
       <c r="D115" s="7">
-        <v>13087.15</v>
+        <v>1539.25</v>
       </c>
       <c r="E115" s="8">
-        <v>45.2</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="7">
-        <v>9555.450000000001</v>
+        <v>13087.15</v>
       </c>
       <c r="D116" s="7">
-        <v>9572.85</v>
+        <v>12854.4</v>
       </c>
       <c r="E116" s="8">
-        <v>17.4</v>
+        <v>-232.75</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="7">
-        <v>8271.15</v>
+        <v>9572.85</v>
       </c>
       <c r="D117" s="7">
-        <v>8294.5</v>
+        <v>9390.299999999999</v>
       </c>
       <c r="E117" s="8">
-        <v>23.35</v>
+        <v>-182.55</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="7">
-        <v>27028.7</v>
+        <v>8294.5</v>
       </c>
       <c r="D118" s="7">
-        <v>27003</v>
-      </c>
-      <c r="E118" s="9">
-        <v>-25.7</v>
+        <v>8026.1</v>
+      </c>
+      <c r="E118" s="8">
+        <v>-268.4</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="7">
-        <v>861.4</v>
+        <v>27003</v>
       </c>
       <c r="D119" s="7">
-        <v>869.35</v>
+        <v>26761.65</v>
       </c>
       <c r="E119" s="8">
-        <v>7.95</v>
+        <v>-241.35</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="7">
-        <v>29539.95</v>
+        <v>869.35</v>
       </c>
       <c r="D120" s="7">
-        <v>29613.95</v>
+        <v>850.9</v>
       </c>
       <c r="E120" s="8">
-        <v>74</v>
+        <v>-18.45</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="7">
-        <v>16757.2</v>
+        <v>29613.95</v>
       </c>
       <c r="D121" s="7">
-        <v>16678.55</v>
-      </c>
-      <c r="E121" s="9">
-        <v>-78.65000000000001</v>
+        <v>29193.7</v>
+      </c>
+      <c r="E121" s="8">
+        <v>-420.25</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="7">
-        <v>9361.700000000001</v>
+        <v>16678.55</v>
       </c>
       <c r="D122" s="7">
-        <v>9401.65</v>
+        <v>16537.15</v>
       </c>
       <c r="E122" s="8">
-        <v>39.95</v>
+        <v>-141.4</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="7">
-        <v>10869.85</v>
+        <v>9401.65</v>
       </c>
       <c r="D123" s="7">
-        <v>10862.15</v>
-      </c>
-      <c r="E123" s="9">
-        <v>-7.7</v>
+        <v>9231.200000000001</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-170.45</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>3</v>
       </c>
       <c r="C124" s="7">
-        <v>26763.95</v>
+        <v>10862.15</v>
       </c>
       <c r="D124" s="7">
-        <v>26883.2</v>
+        <v>10660.6</v>
       </c>
       <c r="E124" s="8">
-        <v>119.25</v>
+        <v>-201.55</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="6" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C125" s="7">
-        <v>56</v>
+        <v>26883.2</v>
       </c>
       <c r="D125" s="7">
-        <v>62</v>
+        <v>26476.4</v>
       </c>
       <c r="E125" s="8">
-        <v>6</v>
+        <v>-406.8</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="6" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="7">
+        <v>74</v>
+      </c>
+      <c r="D126" s="7">
         <v>68</v>
       </c>
-      <c r="D126" s="7">
-        <v>56</v>
-      </c>
-      <c r="E126" s="9">
-        <v>-12</v>
+      <c r="E126" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="6" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="7">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D127" s="7">
-        <v>68</v>
-      </c>
-      <c r="E127" s="8">
-        <v>6</v>
+        <v>74</v>
+      </c>
+      <c r="E127" s="9">
+        <v>18</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="6" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C128" s="7">
-        <v>28.76</v>
+        <v>68</v>
       </c>
       <c r="D128" s="7">
-        <v>35.55</v>
+        <v>56</v>
       </c>
       <c r="E128" s="8">
-        <v>6.79</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C129" s="7">
-        <v>40.19</v>
+        <v>35.55</v>
       </c>
       <c r="D129" s="7">
-        <v>42.06</v>
+        <v>29.84</v>
       </c>
       <c r="E129" s="8">
-        <v>1.87</v>
+        <v>-5.71</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C130" s="7">
-        <v>33.99</v>
+        <v>42.06</v>
       </c>
       <c r="D130" s="7">
-        <v>38.5</v>
+        <v>34.08</v>
       </c>
       <c r="E130" s="8">
-        <v>4.51</v>
+        <v>-7.98</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C131" s="7">
-        <v>37.13</v>
+        <v>38.5</v>
       </c>
       <c r="D131" s="7">
-        <v>39.17</v>
+        <v>32.83</v>
       </c>
       <c r="E131" s="8">
-        <v>2.04</v>
+        <v>-5.67</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C132" s="7">
-        <v>42.91</v>
+        <v>39.17</v>
       </c>
       <c r="D132" s="7">
-        <v>45.33</v>
+        <v>29.48</v>
       </c>
       <c r="E132" s="8">
-        <v>2.42</v>
+        <v>-9.69</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="7">
-        <v>32.91</v>
+        <v>45.33</v>
       </c>
       <c r="D133" s="7">
-        <v>36.79</v>
+        <v>38.75</v>
       </c>
       <c r="E133" s="8">
-        <v>3.88</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="7">
-        <v>32.01</v>
+        <v>36.79</v>
       </c>
       <c r="D134" s="7">
-        <v>31.61</v>
-      </c>
-      <c r="E134" s="9">
-        <v>-0.4</v>
+        <v>30.98</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-5.81</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="7">
-        <v>38.1</v>
+        <v>31.61</v>
       </c>
       <c r="D135" s="7">
-        <v>41.5</v>
+        <v>30.97</v>
       </c>
       <c r="E135" s="8">
-        <v>3.4</v>
+        <v>-0.64</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="7">
-        <v>35.42</v>
+        <v>41.5</v>
       </c>
       <c r="D136" s="7">
-        <v>36.6</v>
+        <v>34.66</v>
       </c>
       <c r="E136" s="8">
-        <v>1.18</v>
+        <v>-6.84</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="7">
-        <v>50.08</v>
+        <v>36.6</v>
       </c>
       <c r="D137" s="7">
-        <v>49.18</v>
-      </c>
-      <c r="E137" s="9">
-        <v>-0.9</v>
+        <v>28.76</v>
+      </c>
+      <c r="E137" s="8">
+        <v>-7.84</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="7">
-        <v>49.21</v>
+        <v>49.18</v>
       </c>
       <c r="D138" s="7">
-        <v>50.4</v>
+        <v>46.35</v>
       </c>
       <c r="E138" s="8">
-        <v>1.19</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="7">
-        <v>38.15</v>
+        <v>50.4</v>
       </c>
       <c r="D139" s="7">
-        <v>40.12</v>
+        <v>44.58</v>
       </c>
       <c r="E139" s="8">
-        <v>1.97</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="7">
-        <v>41.03</v>
+        <v>40.12</v>
       </c>
       <c r="D140" s="7">
-        <v>42.75</v>
+        <v>29.53</v>
       </c>
       <c r="E140" s="8">
-        <v>1.72</v>
+        <v>-10.59</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="7">
-        <v>58.57</v>
+        <v>42.75</v>
       </c>
       <c r="D141" s="7">
-        <v>57.9</v>
-      </c>
-      <c r="E141" s="9">
-        <v>-0.67</v>
+        <v>31.4</v>
+      </c>
+      <c r="E141" s="8">
+        <v>-11.35</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="7">
-        <v>45.65</v>
+        <v>57.9</v>
       </c>
       <c r="D142" s="7">
-        <v>48.7</v>
+        <v>51.93</v>
       </c>
       <c r="E142" s="8">
-        <v>3.05</v>
+        <v>-5.97</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="7">
-        <v>30.27</v>
+        <v>48.7</v>
       </c>
       <c r="D143" s="7">
-        <v>32.84</v>
+        <v>42.71</v>
       </c>
       <c r="E143" s="8">
-        <v>2.57</v>
+        <v>-5.99</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="7">
-        <v>56.06</v>
+        <v>32.84</v>
       </c>
       <c r="D144" s="7">
-        <v>53</v>
-      </c>
-      <c r="E144" s="9">
-        <v>-3.06</v>
+        <v>26.81</v>
+      </c>
+      <c r="E144" s="8">
+        <v>-6.03</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="7">
-        <v>42.27</v>
+        <v>53</v>
       </c>
       <c r="D145" s="7">
-        <v>44.14</v>
+        <v>47.93</v>
       </c>
       <c r="E145" s="8">
-        <v>1.87</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="7">
-        <v>38.75</v>
+        <v>44.14</v>
       </c>
       <c r="D146" s="7">
-        <v>38.35</v>
-      </c>
-      <c r="E146" s="9">
-        <v>-0.4</v>
+        <v>38.43</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-5.71</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="7">
-        <v>35.63</v>
+        <v>38.35</v>
       </c>
       <c r="D147" s="7">
+        <v>29.71</v>
+      </c>
+      <c r="E147" s="8">
+        <v>-8.640000000000001</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
+      <c r="A148" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C148" s="7">
         <v>38.84</v>
       </c>
-      <c r="E147" s="8">
-        <v>3.21</v>
+      <c r="D148" s="7">
+        <v>32.83</v>
+      </c>
+      <c r="E148" s="8">
+        <v>-6.01</v>
       </c>
     </row>
   </sheetData>
@@ -5843,28 +5879,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5878,16 +5914,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="12">
-        <v>42.2</v>
+        <v>35.6</v>
       </c>
       <c r="E2" s="12">
         <v>20</v>
       </c>
       <c r="F2" s="12">
-        <v>-3.4</v>
+        <v>-4.7</v>
       </c>
       <c r="G2" s="12">
-        <v>-0.5</v>
+        <v>-2</v>
       </c>
       <c r="H2" s="12">
         <v>53.1</v>
@@ -6010,13 +6046,13 @@
         <v>48</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="G1" s="14" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I1" s="14" t="s">
         <v>39</v>
@@ -6027,42 +6063,42 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="15">
-        <v>0.2852</v>
+        <v>0.2733</v>
       </c>
       <c r="B2" s="15">
-        <v>0.2755</v>
+        <v>0.2309</v>
       </c>
       <c r="C2" s="15">
-        <v>0.2019</v>
+        <v>0.1992</v>
       </c>
       <c r="D2" s="15">
-        <v>0.1985</v>
+        <v>0.1864</v>
       </c>
       <c r="E2" s="15">
-        <v>0.1894</v>
+        <v>0.1836</v>
       </c>
       <c r="F2" s="15">
-        <v>0.1661</v>
+        <v>0.1356</v>
       </c>
       <c r="G2" s="15">
-        <v>0.138</v>
+        <v>0.1182</v>
       </c>
       <c r="H2" s="15">
-        <v>0.1229</v>
+        <v>0.1119</v>
       </c>
       <c r="I2" s="15">
-        <v>0.1126</v>
+        <v>0.1067</v>
       </c>
       <c r="J2" s="15">
-        <v>0.1123</v>
+        <v>0.1033</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="14" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>57</v>
@@ -6071,54 +6107,54 @@
         <v>43</v>
       </c>
       <c r="E3" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>42</v>
-      </c>
       <c r="H3" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="J3" s="14" t="s">
         <v>56</v>
-      </c>
-      <c r="I3" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="15">
-        <v>0.11</v>
+        <v>0.0915</v>
       </c>
       <c r="B4" s="15">
-        <v>0.09279999999999999</v>
+        <v>0.0915</v>
       </c>
       <c r="C4" s="15">
-        <v>0.06150000000000001</v>
+        <v>0.0597</v>
       </c>
       <c r="D4" s="15">
-        <v>0.06059999999999999</v>
+        <v>0.05889999999999999</v>
       </c>
       <c r="E4" s="15">
-        <v>0.04940000000000001</v>
+        <v>0.0329</v>
       </c>
       <c r="F4" s="15">
-        <v>0.0334</v>
+        <v>0.0216</v>
       </c>
       <c r="G4" s="15">
-        <v>0.0244</v>
+        <v>-0.0048</v>
       </c>
       <c r="H4" s="15">
-        <v>-0.0466</v>
+        <v>-0.0444</v>
       </c>
       <c r="I4" s="15">
-        <v>-0.0482</v>
+        <v>-0.06480000000000001</v>
       </c>
       <c r="J4" s="15">
-        <v>-0.0667</v>
+        <v>-0.104</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="115">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,70 +289,43 @@
     <t>RSI Oversold Recovery</t>
   </si>
   <si>
-    <t>26.0 → 30.1</t>
+    <t>27.4 → 35.2</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>26.0</t>
-  </si>
-  <si>
-    <t>30.1</t>
-  </si>
-  <si>
-    <t>28.2 → 33.3</t>
-  </si>
-  <si>
-    <t>28.2</t>
-  </si>
-  <si>
-    <t>33.3</t>
-  </si>
-  <si>
-    <t>28.2 → 38.5</t>
-  </si>
-  <si>
-    <t>38.5</t>
-  </si>
-  <si>
-    <t>29.5 → 32.7</t>
-  </si>
-  <si>
-    <t>29.5</t>
-  </si>
-  <si>
-    <t>32.7</t>
-  </si>
-  <si>
-    <t>22.8 → 30.7</t>
-  </si>
-  <si>
-    <t>22.8</t>
-  </si>
-  <si>
-    <t>30.7</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.4 → 51.5</t>
-  </si>
-  <si>
-    <t>48.4</t>
-  </si>
-  <si>
-    <t>51.5</t>
-  </si>
-  <si>
-    <t>23.5 → 30.9</t>
-  </si>
-  <si>
-    <t>23.5</t>
-  </si>
-  <si>
-    <t>30.9</t>
+    <t>27.4</t>
+  </si>
+  <si>
+    <t>35.2</t>
+  </si>
+  <si>
+    <t>26.7 → 35.9</t>
+  </si>
+  <si>
+    <t>26.7</t>
+  </si>
+  <si>
+    <t>35.9</t>
+  </si>
+  <si>
+    <t>28.1 → 34.1</t>
+  </si>
+  <si>
+    <t>28.1</t>
+  </si>
+  <si>
+    <t>34.1</t>
+  </si>
+  <si>
+    <t>29.0 → 40.3</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>40.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1082,10 +1055,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>25421.9</v>
+        <v>25541.95</v>
       </c>
       <c r="E2">
-        <v>0.15</v>
+        <v>0.47</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1094,43 +1067,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-14.25</v>
+        <v>-13.85</v>
       </c>
       <c r="I2">
-        <v>6.95</v>
+        <v>7.46</v>
       </c>
       <c r="J2">
-        <v>-5.73</v>
+        <v>-3.71</v>
       </c>
       <c r="K2">
-        <v>-9.15</v>
+        <v>-8.25</v>
       </c>
       <c r="L2">
-        <v>-7.06</v>
+        <v>-6.59</v>
       </c>
       <c r="M2">
-        <v>-5.87</v>
+        <v>-4.55</v>
       </c>
       <c r="N2">
-        <v>18.92</v>
+        <v>19.31</v>
       </c>
       <c r="O2">
         <v>32</v>
       </c>
       <c r="Q2">
-        <v>25959.84</v>
+        <v>25763.22</v>
       </c>
       <c r="R2">
-        <v>26925.72</v>
+        <v>26817.27</v>
       </c>
       <c r="S2">
-        <v>28035.97</v>
+        <v>28004.81</v>
       </c>
       <c r="T2">
-        <v>27067.98</v>
+        <v>27057.38</v>
       </c>
       <c r="U2">
-        <v>-6.08</v>
+        <v>-5.6</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1145,31 +1118,31 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>22.7</v>
+        <v>25.6</v>
       </c>
       <c r="AA2">
-        <v>-627.05</v>
+        <v>-652.88</v>
       </c>
       <c r="AB2">
-        <v>-480.2</v>
+        <v>-514.74</v>
       </c>
       <c r="AC2">
-        <v>-146.85</v>
+        <v>-138.14</v>
       </c>
       <c r="AD2">
-        <v>20.4</v>
+        <v>11.27</v>
       </c>
       <c r="AE2">
-        <v>32.51</v>
+        <v>20.18</v>
       </c>
       <c r="AF2">
-        <v>415.19</v>
+        <v>403.43</v>
       </c>
       <c r="AH2">
-        <v>28305.6</v>
+        <v>28276</v>
       </c>
       <c r="AI2">
-        <v>25545.83</v>
+        <v>25358.54</v>
       </c>
       <c r="AJ2">
         <v>26575.22</v>
@@ -1178,7 +1151,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>75.28</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1192,10 +1165,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9182.549999999999</v>
+        <v>9239.299999999999</v>
       </c>
       <c r="E3">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1204,43 +1177,43 @@
         <v>8890.35</v>
       </c>
       <c r="H3">
-        <v>-12.57</v>
+        <v>-12.03</v>
       </c>
       <c r="I3">
-        <v>3.29</v>
+        <v>3.93</v>
       </c>
       <c r="J3">
-        <v>-3.75</v>
+        <v>-1.36</v>
       </c>
       <c r="K3">
-        <v>-5.89</v>
+        <v>-5.24</v>
       </c>
       <c r="L3">
-        <v>-7.7</v>
+        <v>-6.75</v>
       </c>
       <c r="M3">
-        <v>1.63</v>
+        <v>2.57</v>
       </c>
       <c r="N3">
-        <v>9.31</v>
+        <v>9.76</v>
       </c>
       <c r="O3">
         <v>62</v>
       </c>
       <c r="Q3">
-        <v>9263.379999999999</v>
+        <v>9237.959999999999</v>
       </c>
       <c r="R3">
-        <v>9512.049999999999</v>
+        <v>9483.82</v>
       </c>
       <c r="S3">
-        <v>9715.950000000001</v>
+        <v>9704.09</v>
       </c>
       <c r="T3">
-        <v>9775.559999999999</v>
+        <v>9776.18</v>
       </c>
       <c r="U3">
-        <v>-6.07</v>
+        <v>-5.49</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1255,31 +1228,31 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>30.06</v>
+        <v>34.29</v>
       </c>
       <c r="AA3">
-        <v>-136.4</v>
+        <v>-138.34</v>
       </c>
       <c r="AB3">
-        <v>-102.47</v>
+        <v>-109.64</v>
       </c>
       <c r="AC3">
-        <v>-33.94</v>
+        <v>-28.7</v>
       </c>
       <c r="AD3">
-        <v>14.3</v>
+        <v>19.07</v>
       </c>
       <c r="AE3">
-        <v>20.02</v>
+        <v>16.83</v>
       </c>
       <c r="AF3">
-        <v>118.61</v>
+        <v>115.76</v>
       </c>
       <c r="AH3">
-        <v>9877.34</v>
+        <v>9841.34</v>
       </c>
       <c r="AI3">
-        <v>9146.76</v>
+        <v>9126.309999999999</v>
       </c>
       <c r="AJ3">
         <v>9501.32</v>
@@ -1288,7 +1261,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>45.28</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1302,10 +1275,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>10943.6</v>
+        <v>11074.35</v>
       </c>
       <c r="E4">
-        <v>0.74</v>
+        <v>1.19</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1314,43 +1287,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-13.41</v>
+        <v>-12.38</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>7.16</v>
       </c>
       <c r="J4">
-        <v>-4.13</v>
+        <v>-1.74</v>
       </c>
       <c r="K4">
-        <v>-6.49</v>
+        <v>-4.9</v>
       </c>
       <c r="L4">
-        <v>-7.83</v>
+        <v>-6.74</v>
       </c>
       <c r="M4">
-        <v>-11.16</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="N4">
-        <v>8.619999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="O4">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="Q4">
-        <v>11061.01</v>
+        <v>11021.86</v>
       </c>
       <c r="R4">
-        <v>11369.22</v>
+        <v>11343.05</v>
       </c>
       <c r="S4">
-        <v>11744.15</v>
+        <v>11731.53</v>
       </c>
       <c r="T4">
-        <v>11574.07</v>
+        <v>11568.74</v>
       </c>
       <c r="U4">
-        <v>-5.45</v>
+        <v>-4.27</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1365,31 +1338,31 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>27.43</v>
+        <v>35.21</v>
       </c>
       <c r="AA4">
-        <v>-197.87</v>
+        <v>-195.43</v>
       </c>
       <c r="AB4">
-        <v>-153.37</v>
+        <v>-161.78</v>
       </c>
       <c r="AC4">
-        <v>-44.5</v>
+        <v>-33.64</v>
       </c>
       <c r="AD4">
-        <v>24.78</v>
+        <v>35.34</v>
       </c>
       <c r="AE4">
-        <v>31.54</v>
+        <v>29.13</v>
       </c>
       <c r="AF4">
-        <v>125.74</v>
+        <v>126.5</v>
       </c>
       <c r="AH4">
-        <v>11792.79</v>
+        <v>11771.82</v>
       </c>
       <c r="AI4">
-        <v>10945.65</v>
+        <v>10914.28</v>
       </c>
       <c r="AJ4">
         <v>11268.15</v>
@@ -1398,7 +1371,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>60.74</v>
+        <v>59.11</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1412,10 +1385,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>36594.65</v>
+        <v>36915.75</v>
       </c>
       <c r="E5">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1424,43 +1397,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-11.9</v>
+        <v>-11.12</v>
       </c>
       <c r="I5">
-        <v>10.56</v>
+        <v>11.53</v>
       </c>
       <c r="J5">
-        <v>-2.26</v>
+        <v>0.61</v>
       </c>
       <c r="K5">
-        <v>-3.77</v>
+        <v>-3.21</v>
       </c>
       <c r="L5">
-        <v>-7.31</v>
+        <v>-5.8</v>
       </c>
       <c r="M5">
-        <v>3.06</v>
+        <v>4.71</v>
       </c>
       <c r="N5">
-        <v>8.800000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="O5">
         <v>74</v>
       </c>
       <c r="Q5">
-        <v>36564.35</v>
+        <v>36608.86</v>
       </c>
       <c r="R5">
-        <v>37452.1</v>
+        <v>37394.49</v>
       </c>
       <c r="S5">
-        <v>38102.35</v>
+        <v>38055.13</v>
       </c>
       <c r="T5">
-        <v>37673.78</v>
+        <v>37684.6</v>
       </c>
       <c r="U5">
-        <v>-2.86</v>
+        <v>-2.04</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1475,31 +1448,31 @@
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>33.27</v>
+        <v>40.29</v>
       </c>
       <c r="AA5">
-        <v>-444.46</v>
+        <v>-421.28</v>
       </c>
       <c r="AB5">
-        <v>-352.85</v>
+        <v>-366.54</v>
       </c>
       <c r="AC5">
-        <v>-91.61</v>
+        <v>-54.74</v>
       </c>
       <c r="AD5">
-        <v>17.76</v>
+        <v>36.52</v>
       </c>
       <c r="AE5">
-        <v>11.11</v>
+        <v>20.4</v>
       </c>
       <c r="AF5">
-        <v>439.58</v>
+        <v>435.09</v>
       </c>
       <c r="AH5">
-        <v>38687.61</v>
+        <v>38616.48</v>
       </c>
       <c r="AI5">
-        <v>36216.59</v>
+        <v>36172.51</v>
       </c>
       <c r="AJ5">
         <v>37638.72</v>
@@ -1508,7 +1481,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>32.16</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1522,10 +1495,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>44579.65</v>
+        <v>45205.35</v>
       </c>
       <c r="E6">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1534,43 +1507,43 @@
         <v>43789.85</v>
       </c>
       <c r="H6">
-        <v>-21.48</v>
+        <v>-20.37</v>
       </c>
       <c r="I6">
-        <v>1.8</v>
+        <v>3.23</v>
       </c>
       <c r="J6">
-        <v>-2.96</v>
+        <v>-0.13</v>
       </c>
       <c r="K6">
-        <v>-3.59</v>
+        <v>-1.63</v>
       </c>
       <c r="L6">
-        <v>-11.19</v>
+        <v>-10</v>
       </c>
       <c r="M6">
-        <v>-19.5</v>
+        <v>-17.97</v>
       </c>
       <c r="N6">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>44586.52</v>
+        <v>44574.72</v>
       </c>
       <c r="R6">
-        <v>45333.15</v>
+        <v>45298.78</v>
       </c>
       <c r="S6">
-        <v>47043.76</v>
+        <v>46972.89</v>
       </c>
       <c r="T6">
-        <v>49616.72</v>
+        <v>49569.64</v>
       </c>
       <c r="U6">
-        <v>-10.15</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1585,31 +1558,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>38.46</v>
+        <v>45.13</v>
       </c>
       <c r="AA6">
-        <v>-648.62</v>
+        <v>-590.28</v>
       </c>
       <c r="AB6">
-        <v>-603.99</v>
+        <v>-601.25</v>
       </c>
       <c r="AC6">
-        <v>-44.62</v>
+        <v>10.97</v>
       </c>
       <c r="AD6">
-        <v>40.31</v>
+        <v>55.27</v>
       </c>
       <c r="AE6">
-        <v>41.81</v>
+        <v>43.75</v>
       </c>
       <c r="AF6">
-        <v>597.04</v>
+        <v>608.8</v>
       </c>
       <c r="AH6">
-        <v>46529.63</v>
+        <v>46466.73</v>
       </c>
       <c r="AI6">
-        <v>44136.68</v>
+        <v>44130.84</v>
       </c>
       <c r="AJ6">
         <v>45688.38</v>
@@ -1618,7 +1591,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>43.93</v>
+        <v>41.24</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1632,10 +1605,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>24656.4</v>
+        <v>24946.05</v>
       </c>
       <c r="E7">
-        <v>0.41</v>
+        <v>1.17</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1644,43 +1617,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-13.37</v>
+        <v>-12.36</v>
       </c>
       <c r="I7">
-        <v>4.82</v>
+        <v>6.06</v>
       </c>
       <c r="J7">
-        <v>-1.75</v>
+        <v>1.11</v>
       </c>
       <c r="K7">
-        <v>-4.48</v>
+        <v>-3.77</v>
       </c>
       <c r="L7">
-        <v>-8.66</v>
+        <v>-7.56</v>
       </c>
       <c r="M7">
-        <v>-6.56</v>
+        <v>-4.96</v>
       </c>
       <c r="N7">
-        <v>6.07</v>
+        <v>6.38</v>
       </c>
       <c r="O7">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q7">
-        <v>24636.43</v>
+        <v>24691.31</v>
       </c>
       <c r="R7">
-        <v>25251.54</v>
+        <v>25196.29</v>
       </c>
       <c r="S7">
-        <v>25951.54</v>
+        <v>25912.39</v>
       </c>
       <c r="T7">
-        <v>26403.7</v>
+        <v>26390.62</v>
       </c>
       <c r="U7">
-        <v>-6.62</v>
+        <v>-5.47</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1695,31 +1668,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>32.67</v>
+        <v>41.03</v>
       </c>
       <c r="AA7">
-        <v>-377.38</v>
+        <v>-351.04</v>
       </c>
       <c r="AB7">
-        <v>-325.52</v>
+        <v>-330.62</v>
       </c>
       <c r="AC7">
-        <v>-51.87</v>
+        <v>-20.42</v>
       </c>
       <c r="AD7">
-        <v>20.65</v>
+        <v>41.28</v>
       </c>
       <c r="AE7">
-        <v>18.98</v>
+        <v>26.17</v>
       </c>
       <c r="AF7">
-        <v>319.41</v>
+        <v>317.94</v>
       </c>
       <c r="AH7">
-        <v>26145.27</v>
+        <v>26015.44</v>
       </c>
       <c r="AI7">
-        <v>24357.8</v>
+        <v>24377.14</v>
       </c>
       <c r="AJ7">
         <v>25420.21</v>
@@ -1728,7 +1701,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>41.46</v>
+        <v>40.57</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1742,10 +1715,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>28301.65</v>
+        <v>28136.05</v>
       </c>
       <c r="E8">
-        <v>-0.01</v>
+        <v>-0.59</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1754,43 +1727,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-28.33</v>
+        <v>-28.75</v>
       </c>
       <c r="I8">
-        <v>9.82</v>
+        <v>9.18</v>
       </c>
       <c r="J8">
-        <v>0.5</v>
+        <v>0.18</v>
       </c>
       <c r="K8">
-        <v>-9.01</v>
+        <v>-8.76</v>
       </c>
       <c r="L8">
-        <v>3.76</v>
+        <v>0.7</v>
       </c>
       <c r="M8">
-        <v>-19.12</v>
+        <v>-18.56</v>
       </c>
       <c r="N8">
-        <v>-4.46</v>
+        <v>-4.31</v>
       </c>
       <c r="O8">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="Q8">
-        <v>28013.53</v>
+        <v>28023.44</v>
       </c>
       <c r="R8">
-        <v>28806.88</v>
+        <v>28678.93</v>
       </c>
       <c r="S8">
-        <v>30074.92</v>
+        <v>30062.28</v>
       </c>
       <c r="T8">
-        <v>31364.41</v>
+        <v>31314.61</v>
       </c>
       <c r="U8">
-        <v>-9.77</v>
+        <v>-10.15</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1805,31 +1778,31 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>39.27</v>
+        <v>37.43</v>
       </c>
       <c r="AA8">
-        <v>-585.71</v>
+        <v>-564.23</v>
       </c>
       <c r="AB8">
-        <v>-550.71</v>
+        <v>-553.41</v>
       </c>
       <c r="AC8">
-        <v>-35</v>
+        <v>-10.82</v>
       </c>
       <c r="AD8">
-        <v>51.75</v>
+        <v>76.70999999999999</v>
       </c>
       <c r="AE8">
-        <v>26.64</v>
+        <v>51.71</v>
       </c>
       <c r="AF8">
-        <v>615.6</v>
+        <v>602.8099999999999</v>
       </c>
       <c r="AH8">
-        <v>30363.81</v>
+        <v>29982.47</v>
       </c>
       <c r="AI8">
-        <v>27249.96</v>
+        <v>27375.39</v>
       </c>
       <c r="AJ8">
         <v>29714.41</v>
@@ -1838,7 +1811,7 @@
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>30.35</v>
+        <v>27.41</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1852,10 +1825,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15220.55</v>
+        <v>15422.65</v>
       </c>
       <c r="E9">
-        <v>0.16</v>
+        <v>1.33</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1864,31 +1837,31 @@
         <v>15195.9</v>
       </c>
       <c r="H9">
-        <v>-8.65</v>
+        <v>-7.44</v>
       </c>
       <c r="I9">
-        <v>0.16</v>
+        <v>1.49</v>
       </c>
       <c r="J9">
-        <v>-4.16</v>
+        <v>-1.4</v>
       </c>
       <c r="K9">
-        <v>-6.45</v>
+        <v>-5.22</v>
       </c>
       <c r="L9">
-        <v>-5.62</v>
+        <v>-3.67</v>
       </c>
       <c r="N9">
-        <v>-8.699999999999999</v>
+        <v>-4.75</v>
       </c>
       <c r="Q9">
-        <v>15404.37</v>
+        <v>15360.69</v>
       </c>
       <c r="R9">
-        <v>15823.68</v>
+        <v>15783.74</v>
       </c>
       <c r="S9">
-        <v>16193.07</v>
+        <v>16184.62</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1900,31 +1873,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>26.68</v>
+        <v>35.94</v>
       </c>
       <c r="AA9">
-        <v>-241.26</v>
+        <v>-239.12</v>
       </c>
       <c r="AB9">
-        <v>-176.38</v>
+        <v>-188.93</v>
       </c>
       <c r="AC9">
-        <v>-64.88</v>
+        <v>-50.2</v>
       </c>
       <c r="AD9">
-        <v>31.76</v>
+        <v>37.83</v>
       </c>
       <c r="AE9">
-        <v>39.97</v>
+        <v>35.9</v>
       </c>
       <c r="AF9">
-        <v>180.45</v>
+        <v>183.98</v>
       </c>
       <c r="AH9">
-        <v>16460.05</v>
+        <v>16415.26</v>
       </c>
       <c r="AI9">
-        <v>15187.3</v>
+        <v>15152.22</v>
       </c>
       <c r="AJ9">
         <v>15743.94</v>
@@ -1933,7 +1906,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>57.28</v>
+        <v>56.61</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1947,10 +1920,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8692.950000000001</v>
+        <v>8797.549999999999</v>
       </c>
       <c r="E10">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1959,43 +1932,43 @@
         <v>8560.950000000001</v>
       </c>
       <c r="H10">
-        <v>-10.99</v>
+        <v>-9.91</v>
       </c>
       <c r="I10">
-        <v>1.54</v>
+        <v>2.76</v>
       </c>
       <c r="J10">
-        <v>-2.95</v>
+        <v>0.17</v>
       </c>
       <c r="K10">
-        <v>-5.64</v>
+        <v>-4.42</v>
       </c>
       <c r="L10">
-        <v>-8.69</v>
+        <v>-6.94</v>
       </c>
       <c r="M10">
-        <v>-4.98</v>
+        <v>-3.1</v>
       </c>
       <c r="N10">
-        <v>11.15</v>
+        <v>11.7</v>
       </c>
       <c r="O10">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="Q10">
-        <v>8710.6</v>
+        <v>8713.610000000001</v>
       </c>
       <c r="R10">
-        <v>8967.5</v>
+        <v>8947.49</v>
       </c>
       <c r="S10">
-        <v>9202.780000000001</v>
+        <v>9191.190000000001</v>
       </c>
       <c r="T10">
-        <v>9285.42</v>
+        <v>9282.200000000001</v>
       </c>
       <c r="U10">
-        <v>-6.38</v>
+        <v>-5.22</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -2010,31 +1983,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>30.74</v>
+        <v>38.81</v>
       </c>
       <c r="AA10">
-        <v>-143.31</v>
+        <v>-136.67</v>
       </c>
       <c r="AB10">
-        <v>-113.61</v>
+        <v>-118.23</v>
       </c>
       <c r="AC10">
-        <v>-29.7</v>
+        <v>-18.45</v>
       </c>
       <c r="AD10">
-        <v>26.18</v>
+        <v>42.54</v>
       </c>
       <c r="AE10">
-        <v>25.64</v>
+        <v>29.99</v>
       </c>
       <c r="AF10">
-        <v>99.48999999999999</v>
+        <v>100.7</v>
       </c>
       <c r="AH10">
-        <v>9319.67</v>
+        <v>9289.91</v>
       </c>
       <c r="AI10">
-        <v>8615.33</v>
+        <v>8605.07</v>
       </c>
       <c r="AJ10">
         <v>8911.82</v>
@@ -2043,7 +2016,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>64.83</v>
+        <v>62.1</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2057,10 +2030,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1560.5</v>
+        <v>1567.7</v>
       </c>
       <c r="E11">
-        <v>0.92</v>
+        <v>0.46</v>
       </c>
       <c r="F11">
         <v>1621.4</v>
@@ -2069,43 +2042,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-3.76</v>
+        <v>-3.31</v>
       </c>
       <c r="I11">
-        <v>24.51</v>
+        <v>25.08</v>
       </c>
       <c r="J11">
-        <v>0.64</v>
+        <v>1.85</v>
       </c>
       <c r="K11">
-        <v>1.72</v>
+        <v>0.45</v>
       </c>
       <c r="L11">
-        <v>4.18</v>
+        <v>5.44</v>
       </c>
       <c r="M11">
-        <v>-2.68</v>
+        <v>-1.58</v>
       </c>
       <c r="N11">
-        <v>-6.88</v>
+        <v>-6.67</v>
       </c>
       <c r="O11">
         <v>87</v>
       </c>
       <c r="Q11">
-        <v>1554.04</v>
+        <v>1559.73</v>
       </c>
       <c r="R11">
-        <v>1545.18</v>
+        <v>1545.29</v>
       </c>
       <c r="S11">
-        <v>1563.37</v>
+        <v>1564.29</v>
       </c>
       <c r="T11">
-        <v>1457.2</v>
+        <v>1457.99</v>
       </c>
       <c r="U11">
-        <v>7.09</v>
+        <v>7.52</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2120,31 +2093,31 @@
         <v>2</v>
       </c>
       <c r="Z11">
-        <v>51.5</v>
+        <v>53.06</v>
       </c>
       <c r="AA11">
-        <v>-0.38</v>
+        <v>0.77</v>
       </c>
       <c r="AB11">
-        <v>-2.5</v>
+        <v>-1.85</v>
       </c>
       <c r="AC11">
-        <v>2.12</v>
+        <v>2.62</v>
       </c>
       <c r="AD11">
-        <v>74.08</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="AE11">
-        <v>69.25</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="AF11">
-        <v>35.24</v>
+        <v>33.84</v>
       </c>
       <c r="AH11">
-        <v>1585.41</v>
+        <v>1585.78</v>
       </c>
       <c r="AI11">
-        <v>1504.95</v>
+        <v>1504.81</v>
       </c>
       <c r="AJ11">
         <v>1604.15</v>
@@ -2153,7 +2126,7 @@
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>23.37</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2167,10 +2140,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>12498</v>
+        <v>12599.75</v>
       </c>
       <c r="E12">
-        <v>0.3</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2179,43 +2152,43 @@
         <v>9888.25</v>
       </c>
       <c r="H12">
-        <v>-8.9</v>
+        <v>-8.15</v>
       </c>
       <c r="I12">
-        <v>26.39</v>
+        <v>27.42</v>
       </c>
       <c r="J12">
-        <v>-4.5</v>
+        <v>-1.98</v>
       </c>
       <c r="K12">
-        <v>-5.01</v>
+        <v>-4.37</v>
       </c>
       <c r="L12">
-        <v>-1.76</v>
+        <v>0.14</v>
       </c>
       <c r="M12">
-        <v>24.23</v>
+        <v>24.97</v>
       </c>
       <c r="N12">
-        <v>16.6</v>
+        <v>17.5</v>
       </c>
       <c r="O12">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="Q12">
-        <v>12705.61</v>
+        <v>12654.68</v>
       </c>
       <c r="R12">
-        <v>12978.18</v>
+        <v>12942.29</v>
       </c>
       <c r="S12">
-        <v>13019.6</v>
+        <v>13022.86</v>
       </c>
       <c r="T12">
-        <v>12388.12</v>
+        <v>12399.78</v>
       </c>
       <c r="U12">
-        <v>0.89</v>
+        <v>1.61</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2230,31 +2203,31 @@
         <v>2</v>
       </c>
       <c r="Z12">
-        <v>38.1</v>
+        <v>41.22</v>
       </c>
       <c r="AA12">
-        <v>-111.27</v>
+        <v>-122.13</v>
       </c>
       <c r="AB12">
-        <v>-47.58</v>
+        <v>-62.49</v>
       </c>
       <c r="AC12">
-        <v>-63.69</v>
+        <v>-59.64</v>
       </c>
       <c r="AD12">
-        <v>11.61</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="AE12">
-        <v>24.47</v>
+        <v>15.37</v>
       </c>
       <c r="AF12">
-        <v>242.25</v>
+        <v>235.66</v>
       </c>
       <c r="AH12">
-        <v>13503.45</v>
+        <v>13468.03</v>
       </c>
       <c r="AI12">
-        <v>12452.91</v>
+        <v>12416.55</v>
       </c>
       <c r="AJ12">
         <v>13232.47</v>
@@ -2263,7 +2236,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>28.87</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2277,10 +2250,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9283.549999999999</v>
+        <v>9346.450000000001</v>
       </c>
       <c r="E13">
-        <v>0.8100000000000001</v>
+        <v>0.68</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2289,43 +2262,43 @@
         <v>9208.65</v>
       </c>
       <c r="H13">
-        <v>-13.77</v>
+        <v>-13.19</v>
       </c>
       <c r="I13">
-        <v>0.8100000000000001</v>
+        <v>1.5</v>
       </c>
       <c r="J13">
-        <v>-3.02</v>
+        <v>-0.47</v>
       </c>
       <c r="K13">
-        <v>-4.25</v>
+        <v>-3.71</v>
       </c>
       <c r="L13">
-        <v>-7.43</v>
+        <v>-6.14</v>
       </c>
       <c r="M13">
-        <v>-5.55</v>
+        <v>-4.43</v>
       </c>
       <c r="N13">
-        <v>16.87</v>
+        <v>17.16</v>
       </c>
       <c r="O13">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="Q13">
-        <v>9317.32</v>
+        <v>9308.549999999999</v>
       </c>
       <c r="R13">
-        <v>9548.09</v>
+        <v>9529.9</v>
       </c>
       <c r="S13">
-        <v>9719.969999999999</v>
+        <v>9708.129999999999</v>
       </c>
       <c r="T13">
-        <v>10011.62</v>
+        <v>10010.88</v>
       </c>
       <c r="U13">
-        <v>-7.27</v>
+        <v>-6.64</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2340,31 +2313,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>30.85</v>
+        <v>36.36</v>
       </c>
       <c r="AA13">
-        <v>-117.44</v>
+        <v>-116.03</v>
       </c>
       <c r="AB13">
-        <v>-88.45999999999999</v>
+        <v>-93.98</v>
       </c>
       <c r="AC13">
-        <v>-28.98</v>
+        <v>-22.05</v>
       </c>
       <c r="AD13">
-        <v>18.12</v>
+        <v>31.96</v>
       </c>
       <c r="AE13">
-        <v>15.04</v>
+        <v>20.07</v>
       </c>
       <c r="AF13">
-        <v>112.01</v>
+        <v>109.58</v>
       </c>
       <c r="AH13">
-        <v>9866.48</v>
+        <v>9850.85</v>
       </c>
       <c r="AI13">
-        <v>9229.700000000001</v>
+        <v>9208.950000000001</v>
       </c>
       <c r="AJ13">
         <v>9548.950000000001</v>
@@ -2373,7 +2346,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>47.82</v>
+        <v>49.53</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2387,10 +2360,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8014.85</v>
+        <v>8008.4</v>
       </c>
       <c r="E14">
-        <v>0.97</v>
+        <v>-0.08</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2399,43 +2372,43 @@
         <v>7261.45</v>
       </c>
       <c r="H14">
-        <v>-18.88</v>
+        <v>-18.94</v>
       </c>
       <c r="I14">
-        <v>10.38</v>
+        <v>10.29</v>
       </c>
       <c r="J14">
-        <v>-3.37</v>
+        <v>-0.22</v>
       </c>
       <c r="K14">
-        <v>-5.84</v>
+        <v>-6.36</v>
       </c>
       <c r="L14">
-        <v>-3.83</v>
+        <v>-3.49</v>
       </c>
       <c r="M14">
-        <v>7.84</v>
+        <v>8.32</v>
       </c>
       <c r="N14">
-        <v>25.82</v>
+        <v>26.29</v>
       </c>
       <c r="O14">
         <v>81</v>
       </c>
       <c r="Q14">
-        <v>7993.52</v>
+        <v>7989.98</v>
       </c>
       <c r="R14">
-        <v>8248.5</v>
+        <v>8223.18</v>
       </c>
       <c r="S14">
-        <v>8444.01</v>
+        <v>8436.549999999999</v>
       </c>
       <c r="T14">
-        <v>8583.629999999999</v>
+        <v>8582.5</v>
       </c>
       <c r="U14">
-        <v>-6.63</v>
+        <v>-6.69</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2450,31 +2423,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>35.7</v>
+        <v>35.45</v>
       </c>
       <c r="AA14">
-        <v>-130.49</v>
+        <v>-131.21</v>
       </c>
       <c r="AB14">
-        <v>-100.61</v>
+        <v>-106.73</v>
       </c>
       <c r="AC14">
-        <v>-29.87</v>
+        <v>-24.48</v>
       </c>
       <c r="AD14">
-        <v>24.96</v>
+        <v>28.34</v>
       </c>
       <c r="AE14">
-        <v>18.2</v>
+        <v>22.34</v>
       </c>
       <c r="AF14">
-        <v>135.28</v>
+        <v>131.33</v>
       </c>
       <c r="AH14">
-        <v>8586.459999999999</v>
+        <v>8552.9</v>
       </c>
       <c r="AI14">
-        <v>7910.53</v>
+        <v>7893.45</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
@@ -2483,7 +2456,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>39.38</v>
+        <v>39.56</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2497,10 +2470,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26117.1</v>
+        <v>26549.6</v>
       </c>
       <c r="E15">
-        <v>-0.74</v>
+        <v>1.66</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2509,43 +2482,43 @@
         <v>21454.25</v>
       </c>
       <c r="H15">
-        <v>-3.93</v>
+        <v>-2.34</v>
       </c>
       <c r="I15">
-        <v>21.73</v>
+        <v>23.75</v>
       </c>
       <c r="J15">
-        <v>-3.28</v>
+        <v>-0.79</v>
       </c>
       <c r="K15">
-        <v>-2.48</v>
+        <v>-0.41</v>
       </c>
       <c r="L15">
-        <v>0.97</v>
+        <v>3.4</v>
       </c>
       <c r="M15">
-        <v>17.75</v>
+        <v>20.8</v>
       </c>
       <c r="N15">
-        <v>12.13</v>
+        <v>12.92</v>
       </c>
       <c r="O15">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="Q15">
-        <v>26512.39</v>
+        <v>26469.98</v>
       </c>
       <c r="R15">
-        <v>26655.75</v>
+        <v>26659.32</v>
       </c>
       <c r="S15">
-        <v>26572.06</v>
+        <v>26592.09</v>
       </c>
       <c r="T15">
-        <v>24176.26</v>
+        <v>24195.09</v>
       </c>
       <c r="U15">
-        <v>8.029999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="V15" t="s">
         <v>80</v>
@@ -2560,31 +2533,31 @@
         <v>3</v>
       </c>
       <c r="Z15">
-        <v>39.78</v>
+        <v>48.88</v>
       </c>
       <c r="AA15">
-        <v>-8.130000000000001</v>
+        <v>-12.36</v>
       </c>
       <c r="AB15">
-        <v>73.22</v>
+        <v>56.1</v>
       </c>
       <c r="AC15">
-        <v>-81.34</v>
+        <v>-68.45999999999999</v>
       </c>
       <c r="AD15">
-        <v>10.1</v>
+        <v>17.12</v>
       </c>
       <c r="AE15">
-        <v>30.4</v>
+        <v>20.2</v>
       </c>
       <c r="AF15">
-        <v>345.19</v>
+        <v>358.3</v>
       </c>
       <c r="AH15">
-        <v>27278.88</v>
+        <v>27278.98</v>
       </c>
       <c r="AI15">
-        <v>26032.61</v>
+        <v>26039.66</v>
       </c>
       <c r="AJ15">
         <v>27223.84</v>
@@ -2593,7 +2566,7 @@
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>28.35</v>
+        <v>28.38</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2607,10 +2580,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>839.7</v>
+        <v>837.45</v>
       </c>
       <c r="E16">
-        <v>0.5600000000000001</v>
+        <v>-0.27</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2619,43 +2592,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-13.31</v>
+        <v>-13.54</v>
       </c>
       <c r="I16">
-        <v>28.96</v>
+        <v>28.61</v>
       </c>
       <c r="J16">
-        <v>-3.41</v>
+        <v>-1.58</v>
       </c>
       <c r="K16">
-        <v>-5.98</v>
+        <v>-8.59</v>
       </c>
       <c r="L16">
-        <v>-7.41</v>
+        <v>-6.18</v>
       </c>
       <c r="M16">
-        <v>-5.72</v>
+        <v>-4.39</v>
       </c>
       <c r="N16">
-        <v>10.49</v>
+        <v>10.79</v>
       </c>
       <c r="O16">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Q16">
-        <v>841.36</v>
+        <v>838.67</v>
       </c>
       <c r="R16">
-        <v>856.2</v>
+        <v>852.6799999999999</v>
       </c>
       <c r="S16">
-        <v>884.61</v>
+        <v>882.99</v>
       </c>
       <c r="T16">
-        <v>826.92</v>
+        <v>826.74</v>
       </c>
       <c r="U16">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2670,31 +2643,31 @@
         <v>2</v>
       </c>
       <c r="Z16">
-        <v>41.81</v>
+        <v>41.16</v>
       </c>
       <c r="AA16">
-        <v>-12.29</v>
+        <v>-12.38</v>
       </c>
       <c r="AB16">
-        <v>-11.66</v>
+        <v>-11.81</v>
       </c>
       <c r="AC16">
-        <v>-0.63</v>
+        <v>-0.58</v>
       </c>
       <c r="AD16">
-        <v>70.98999999999999</v>
+        <v>66.03</v>
       </c>
       <c r="AE16">
-        <v>68.84</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="AF16">
-        <v>18.46</v>
+        <v>17.85</v>
       </c>
       <c r="AH16">
-        <v>904.67</v>
+        <v>895.2</v>
       </c>
       <c r="AI16">
-        <v>807.74</v>
+        <v>810.16</v>
       </c>
       <c r="AJ16">
         <v>877.53</v>
@@ -2703,7 +2676,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>26.34</v>
+        <v>27.48</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2717,10 +2690,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29069.15</v>
+        <v>29240.7</v>
       </c>
       <c r="E17">
-        <v>0.38</v>
+        <v>0.59</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2729,43 +2702,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-14.76</v>
+        <v>-14.25</v>
       </c>
       <c r="I17">
-        <v>2.49</v>
+        <v>3.09</v>
       </c>
       <c r="J17">
-        <v>-1.84</v>
+        <v>0.16</v>
       </c>
       <c r="K17">
-        <v>-4.77</v>
+        <v>-4.36</v>
       </c>
       <c r="L17">
-        <v>-6.97</v>
+        <v>-6.69</v>
       </c>
       <c r="M17">
-        <v>-10.65</v>
+        <v>-9.5</v>
       </c>
       <c r="N17">
-        <v>3.22</v>
+        <v>3.47</v>
       </c>
       <c r="O17">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Q17">
-        <v>29078.85</v>
+        <v>29088.25</v>
       </c>
       <c r="R17">
-        <v>29749.52</v>
+        <v>29682.78</v>
       </c>
       <c r="S17">
-        <v>30563.02</v>
+        <v>30519.04</v>
       </c>
       <c r="T17">
-        <v>31236.95</v>
+        <v>31215.05</v>
       </c>
       <c r="U17">
-        <v>-6.94</v>
+        <v>-6.32</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2780,31 +2753,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>28.12</v>
+        <v>34.15</v>
       </c>
       <c r="AA17">
-        <v>-420.17</v>
+        <v>-405.41</v>
       </c>
       <c r="AB17">
-        <v>-356.28</v>
+        <v>-366.11</v>
       </c>
       <c r="AC17">
-        <v>-63.89</v>
+        <v>-39.3</v>
       </c>
       <c r="AD17">
-        <v>8.470000000000001</v>
+        <v>29.12</v>
       </c>
       <c r="AE17">
-        <v>8.289999999999999</v>
+        <v>14.26</v>
       </c>
       <c r="AF17">
-        <v>309.83</v>
+        <v>303.64</v>
       </c>
       <c r="AH17">
-        <v>30681.42</v>
+        <v>30554.87</v>
       </c>
       <c r="AI17">
-        <v>28817.62</v>
+        <v>28810.69</v>
       </c>
       <c r="AJ17">
         <v>29796.41</v>
@@ -2813,7 +2786,7 @@
         <v>81</v>
       </c>
       <c r="AL17">
-        <v>45.69</v>
+        <v>46.23</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2827,10 +2800,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>15934.65</v>
+        <v>16101.3</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>1.05</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2839,31 +2812,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-5.94</v>
+        <v>-4.96</v>
       </c>
       <c r="I18">
-        <v>3.45</v>
+        <v>4.53</v>
       </c>
       <c r="J18">
-        <v>-4.46</v>
+        <v>-2.64</v>
       </c>
       <c r="K18">
-        <v>-4.18</v>
+        <v>-2.72</v>
       </c>
       <c r="L18">
-        <v>-3.32</v>
+        <v>-1.48</v>
       </c>
       <c r="N18">
-        <v>8.029999999999999</v>
+        <v>11.56</v>
       </c>
       <c r="Q18">
-        <v>16253.55</v>
+        <v>16166.38</v>
       </c>
       <c r="R18">
-        <v>16497.51</v>
+        <v>16482.17</v>
       </c>
       <c r="S18">
-        <v>16563.73</v>
+        <v>16561.03</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2875,40 +2848,40 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>32.45</v>
+        <v>38.95</v>
       </c>
       <c r="AA18">
-        <v>-87.68000000000001</v>
+        <v>-104.57</v>
       </c>
       <c r="AB18">
-        <v>-12.45</v>
+        <v>-30.87</v>
       </c>
       <c r="AC18">
-        <v>-75.23</v>
+        <v>-73.7</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>7.68</v>
       </c>
       <c r="AE18">
-        <v>14.69</v>
+        <v>7.62</v>
       </c>
       <c r="AF18">
-        <v>206.95</v>
+        <v>211.64</v>
       </c>
       <c r="AH18">
-        <v>16984.41</v>
+        <v>16999.32</v>
       </c>
       <c r="AI18">
-        <v>16010.6</v>
+        <v>15965.01</v>
       </c>
       <c r="AJ18">
-        <v>16620.3</v>
+        <v>16601.73</v>
       </c>
       <c r="AK18" t="s">
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>31.88</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2922,10 +2895,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9180.5</v>
+        <v>9347.25</v>
       </c>
       <c r="E19">
-        <v>0.42</v>
+        <v>1.82</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2934,31 +2907,31 @@
         <v>8995.35</v>
       </c>
       <c r="H19">
-        <v>-8.18</v>
+        <v>-6.52</v>
       </c>
       <c r="I19">
-        <v>2.06</v>
+        <v>3.91</v>
       </c>
       <c r="J19">
-        <v>-2.35</v>
+        <v>1.26</v>
       </c>
       <c r="K19">
-        <v>-4.58</v>
+        <v>-3.35</v>
       </c>
       <c r="L19">
-        <v>-4.78</v>
+        <v>-1.43</v>
       </c>
       <c r="N19">
-        <v>6.68</v>
+        <v>12.84</v>
       </c>
       <c r="Q19">
-        <v>9194.129999999999</v>
+        <v>9217.34</v>
       </c>
       <c r="R19">
-        <v>9442.719999999999</v>
+        <v>9424.639999999999</v>
       </c>
       <c r="S19">
-        <v>9548.84</v>
+        <v>9548.690000000001</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2970,31 +2943,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>39.94</v>
+        <v>47.06</v>
       </c>
       <c r="AA19">
-        <v>-117.91</v>
+        <v>-105.98</v>
       </c>
       <c r="AB19">
-        <v>-89.81</v>
+        <v>-93.04000000000001</v>
       </c>
       <c r="AC19">
-        <v>-28.1</v>
+        <v>-12.94</v>
       </c>
       <c r="AD19">
-        <v>47.28</v>
+        <v>64.78</v>
       </c>
       <c r="AE19">
-        <v>36.07</v>
+        <v>48.39</v>
       </c>
       <c r="AF19">
-        <v>168.19</v>
+        <v>170.21</v>
       </c>
       <c r="AH19">
-        <v>9993.469999999999</v>
+        <v>9962.190000000001</v>
       </c>
       <c r="AI19">
-        <v>8891.969999999999</v>
+        <v>8887.09</v>
       </c>
       <c r="AJ19">
         <v>9616.870000000001</v>
@@ -3003,7 +2976,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>34.58</v>
+        <v>33.01</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3017,10 +2990,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10510.75</v>
+        <v>10676.85</v>
       </c>
       <c r="E20">
-        <v>0.34</v>
+        <v>1.58</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3029,31 +3002,31 @@
         <v>10474.85</v>
       </c>
       <c r="H20">
-        <v>-7.55</v>
+        <v>-6.09</v>
       </c>
       <c r="I20">
-        <v>0.34</v>
+        <v>1.93</v>
       </c>
       <c r="J20">
-        <v>-3.24</v>
+        <v>0.15</v>
       </c>
       <c r="K20">
-        <v>-5.98</v>
+        <v>-4.37</v>
       </c>
       <c r="L20">
-        <v>-6.66</v>
+        <v>-5.09</v>
       </c>
       <c r="N20">
-        <v>-13.76</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="Q20">
-        <v>10565.68</v>
+        <v>10568.93</v>
       </c>
       <c r="R20">
-        <v>10867.64</v>
+        <v>10842.1</v>
       </c>
       <c r="S20">
-        <v>11059.86</v>
+        <v>11051.85</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3065,31 +3038,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>28.97</v>
+        <v>40.27</v>
       </c>
       <c r="AA20">
-        <v>-147.19</v>
+        <v>-140.19</v>
       </c>
       <c r="AB20">
-        <v>-105.14</v>
+        <v>-112.15</v>
       </c>
       <c r="AC20">
-        <v>-42.05</v>
+        <v>-28.04</v>
       </c>
       <c r="AD20">
-        <v>14.7</v>
+        <v>29.61</v>
       </c>
       <c r="AE20">
-        <v>14.2</v>
+        <v>18.5</v>
       </c>
       <c r="AF20">
-        <v>139.8</v>
+        <v>141.76</v>
       </c>
       <c r="AH20">
-        <v>11275.69</v>
+        <v>11229.22</v>
       </c>
       <c r="AI20">
-        <v>10459.59</v>
+        <v>10454.98</v>
       </c>
       <c r="AJ20">
         <v>10902.64</v>
@@ -3098,7 +3071,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>50.01</v>
+        <v>49.2</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3112,10 +3085,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>26718.15</v>
+        <v>27093.75</v>
       </c>
       <c r="E21">
-        <v>0.08</v>
+        <v>1.41</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3124,43 +3097,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-8.460000000000001</v>
+        <v>-7.17</v>
       </c>
       <c r="I21">
-        <v>10.66</v>
+        <v>12.21</v>
       </c>
       <c r="J21">
-        <v>-0.61</v>
+        <v>2.33</v>
       </c>
       <c r="K21">
-        <v>-3.22</v>
+        <v>-2.36</v>
       </c>
       <c r="L21">
-        <v>-5.75</v>
+        <v>-4.28</v>
       </c>
       <c r="M21">
-        <v>-0.4</v>
+        <v>1.14</v>
       </c>
       <c r="N21">
-        <v>6.37</v>
+        <v>6.8</v>
       </c>
       <c r="O21">
         <v>68</v>
       </c>
       <c r="Q21">
-        <v>26606.11</v>
+        <v>26729.58</v>
       </c>
       <c r="R21">
-        <v>27125.58</v>
+        <v>27089.04</v>
       </c>
       <c r="S21">
-        <v>27462.04</v>
+        <v>27433.74</v>
       </c>
       <c r="T21">
-        <v>27491.78</v>
+        <v>27483.88</v>
       </c>
       <c r="U21">
-        <v>-2.81</v>
+        <v>-1.42</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3175,31 +3148,31 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>39.69</v>
+        <v>48.98</v>
       </c>
       <c r="AA21">
-        <v>-249</v>
+        <v>-213.66</v>
       </c>
       <c r="AB21">
-        <v>-201.96</v>
+        <v>-204.3</v>
       </c>
       <c r="AC21">
-        <v>-47.05</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="AD21">
-        <v>46.75</v>
+        <v>65</v>
       </c>
       <c r="AE21">
-        <v>30.71</v>
+        <v>47.34</v>
       </c>
       <c r="AF21">
-        <v>352.34</v>
+        <v>357.09</v>
       </c>
       <c r="AH21">
-        <v>27912.58</v>
+        <v>27803.97</v>
       </c>
       <c r="AI21">
-        <v>26338.57</v>
+        <v>26374.11</v>
       </c>
       <c r="AJ21">
         <v>27249.36</v>
@@ -3208,7 +3181,7 @@
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>29.6</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -3349,7 +3322,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F157"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3389,7 +3362,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>88</v>
@@ -3409,7 +3382,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>88</v>
@@ -3429,7 +3402,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>88</v>
@@ -3441,2093 +3414,2084 @@
         <v>90</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>88</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>90</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="4" t="s">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E8" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>110</v>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-9.15</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-8.25</v>
+      </c>
+      <c r="E10" s="7">
+        <v>0.9</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="A11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-5.89</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.24</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>115</v>
+      <c r="A12" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-6.49</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-4.9</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-10.9</v>
+        <v>-3.77</v>
       </c>
       <c r="D13" s="6">
-        <v>-9.15</v>
+        <v>-3.21</v>
       </c>
       <c r="E13" s="7">
-        <v>1.75</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-5.91</v>
+        <v>-3.59</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.89</v>
+        <v>-1.63</v>
       </c>
       <c r="E14" s="7">
-        <v>0.02</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-7.8</v>
+        <v>-4.48</v>
       </c>
       <c r="D15" s="6">
-        <v>-6.49</v>
+        <v>-3.77</v>
       </c>
       <c r="E15" s="7">
-        <v>1.31</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.75</v>
+        <v>-9.01</v>
       </c>
       <c r="D16" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.02</v>
+        <v>-8.76</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.74</v>
+        <v>-6.45</v>
       </c>
       <c r="D17" s="6">
-        <v>-3.59</v>
+        <v>-5.22</v>
       </c>
       <c r="E17" s="7">
-        <v>2.15</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.57</v>
+        <v>-5.64</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.48</v>
+        <v>-4.42</v>
       </c>
       <c r="E18" s="7">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-10.13</v>
+        <v>1.72</v>
       </c>
       <c r="D19" s="6">
-        <v>-9.01</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.12</v>
+        <v>0.45</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-1.27</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-7.36</v>
+        <v>-5.01</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.45</v>
+        <v>-4.37</v>
       </c>
       <c r="E20" s="7">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-6.56</v>
+        <v>-4.25</v>
       </c>
       <c r="D21" s="6">
-        <v>-5.64</v>
+        <v>-3.71</v>
       </c>
       <c r="E21" s="7">
-        <v>0.92</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-0.97</v>
+        <v>-5.84</v>
       </c>
       <c r="D22" s="6">
-        <v>1.72</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.69</v>
+        <v>-6.36</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-0.52</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-5.53</v>
+        <v>-2.48</v>
       </c>
       <c r="D23" s="6">
-        <v>-5.01</v>
+        <v>-0.41</v>
       </c>
       <c r="E23" s="7">
-        <v>0.52</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.67</v>
+        <v>-5.98</v>
       </c>
       <c r="D24" s="6">
-        <v>-4.25</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.42</v>
+        <v>-8.59</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-2.61</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-6.68</v>
+        <v>-4.77</v>
       </c>
       <c r="D25" s="6">
-        <v>-5.84</v>
+        <v>-4.36</v>
       </c>
       <c r="E25" s="7">
-        <v>0.84</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-1.8</v>
+        <v>-4.18</v>
       </c>
       <c r="D26" s="6">
-        <v>-2.48</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.68</v>
+        <v>-2.72</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.46</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-6.32</v>
+        <v>-4.58</v>
       </c>
       <c r="D27" s="6">
-        <v>-5.98</v>
+        <v>-3.35</v>
       </c>
       <c r="E27" s="7">
-        <v>0.34</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-5.85</v>
+        <v>-5.98</v>
       </c>
       <c r="D28" s="6">
-        <v>-4.77</v>
+        <v>-4.37</v>
       </c>
       <c r="E28" s="7">
-        <v>1.08</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-3.45</v>
+        <v>-3.22</v>
       </c>
       <c r="D29" s="6">
-        <v>-4.18</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.73</v>
+        <v>-2.36</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.86</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>-5.24</v>
+        <v>-5.73</v>
       </c>
       <c r="D30" s="6">
-        <v>-4.58</v>
+        <v>-3.71</v>
       </c>
       <c r="E30" s="7">
-        <v>0.66</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-5.99</v>
+        <v>-3.75</v>
       </c>
       <c r="D31" s="6">
-        <v>-5.98</v>
+        <v>-1.36</v>
       </c>
       <c r="E31" s="7">
-        <v>0.01</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-3.84</v>
+        <v>-4.13</v>
       </c>
       <c r="D32" s="6">
-        <v>-3.22</v>
+        <v>-1.74</v>
       </c>
       <c r="E32" s="7">
-        <v>0.62</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-5.03</v>
+        <v>-2.26</v>
       </c>
       <c r="D33" s="6">
-        <v>-5.73</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.7</v>
+        <v>0.61</v>
+      </c>
+      <c r="E33" s="7">
+        <v>2.87</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>-4.05</v>
+        <v>-2.96</v>
       </c>
       <c r="D34" s="6">
-        <v>-3.75</v>
+        <v>-0.13</v>
       </c>
       <c r="E34" s="7">
-        <v>0.3</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>-4.32</v>
+        <v>-1.75</v>
       </c>
       <c r="D35" s="6">
-        <v>-4.13</v>
+        <v>1.11</v>
       </c>
       <c r="E35" s="7">
-        <v>0.19</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-2.6</v>
+        <v>0.5</v>
       </c>
       <c r="D36" s="6">
-        <v>-2.26</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.34</v>
+        <v>0.18</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-4.3</v>
+        <v>-4.16</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.96</v>
+        <v>-1.4</v>
       </c>
       <c r="E37" s="7">
-        <v>1.34</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-1.6</v>
+        <v>-2.95</v>
       </c>
       <c r="D38" s="6">
-        <v>-1.75</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.15</v>
+        <v>0.17</v>
+      </c>
+      <c r="E38" s="7">
+        <v>3.12</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>0.34</v>
+        <v>0.64</v>
       </c>
       <c r="D39" s="6">
-        <v>0.5</v>
+        <v>1.85</v>
       </c>
       <c r="E39" s="7">
-        <v>0.16</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-3.88</v>
+        <v>-4.5</v>
       </c>
       <c r="D40" s="6">
-        <v>-4.16</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-0.28</v>
+        <v>-1.98</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.52</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>-3.8</v>
+        <v>-3.02</v>
       </c>
       <c r="D41" s="6">
-        <v>-2.95</v>
+        <v>-0.47</v>
       </c>
       <c r="E41" s="7">
-        <v>0.85</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>-0.51</v>
+        <v>-3.37</v>
       </c>
       <c r="D42" s="6">
-        <v>0.64</v>
+        <v>-0.22</v>
       </c>
       <c r="E42" s="7">
-        <v>1.15</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-4.46</v>
+        <v>-3.28</v>
       </c>
       <c r="D43" s="6">
-        <v>-4.5</v>
-      </c>
-      <c r="E43" s="8">
-        <v>-0.04</v>
+        <v>-0.79</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.49</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>-3.63</v>
+        <v>-3.41</v>
       </c>
       <c r="D44" s="6">
-        <v>-3.02</v>
+        <v>-1.58</v>
       </c>
       <c r="E44" s="7">
-        <v>0.61</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>-4.03</v>
+        <v>-1.84</v>
       </c>
       <c r="D45" s="6">
-        <v>-3.37</v>
+        <v>0.16</v>
       </c>
       <c r="E45" s="7">
-        <v>0.66</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-2.65</v>
+        <v>-4.46</v>
       </c>
       <c r="D46" s="6">
-        <v>-3.28</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-0.63</v>
+        <v>-2.64</v>
+      </c>
+      <c r="E46" s="7">
+        <v>1.82</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>-3.06</v>
+        <v>-2.35</v>
       </c>
       <c r="D47" s="6">
-        <v>-3.41</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.35</v>
+        <v>1.26</v>
+      </c>
+      <c r="E47" s="7">
+        <v>3.61</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="6">
-        <v>-1.97</v>
+        <v>-3.24</v>
       </c>
       <c r="D48" s="6">
-        <v>-1.84</v>
+        <v>0.15</v>
       </c>
       <c r="E48" s="7">
-        <v>0.13</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="6">
-        <v>-3.95</v>
+        <v>-0.61</v>
       </c>
       <c r="D49" s="6">
-        <v>-4.46</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.51</v>
+        <v>2.33</v>
+      </c>
+      <c r="E49" s="7">
+        <v>2.94</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>-2.34</v>
+        <v>-5.87</v>
       </c>
       <c r="D50" s="6">
-        <v>-2.35</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.01</v>
+        <v>-4.55</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.32</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>-3.63</v>
+        <v>1.63</v>
       </c>
       <c r="D51" s="6">
-        <v>-3.24</v>
+        <v>2.57</v>
       </c>
       <c r="E51" s="7">
-        <v>0.39</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-0.25</v>
+        <v>-11.16</v>
       </c>
       <c r="D52" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.36</v>
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="E52" s="7">
+        <v>1.61</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-7.09</v>
+        <v>3.06</v>
       </c>
       <c r="D53" s="6">
-        <v>-5.87</v>
+        <v>4.71</v>
       </c>
       <c r="E53" s="7">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>0.32</v>
+        <v>-19.5</v>
       </c>
       <c r="D54" s="6">
-        <v>1.63</v>
+        <v>-17.97</v>
       </c>
       <c r="E54" s="7">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-12.35</v>
+        <v>-6.56</v>
       </c>
       <c r="D55" s="6">
-        <v>-11.16</v>
+        <v>-4.96</v>
       </c>
       <c r="E55" s="7">
-        <v>1.19</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>1.57</v>
+        <v>-19.12</v>
       </c>
       <c r="D56" s="6">
-        <v>3.06</v>
+        <v>-18.56</v>
       </c>
       <c r="E56" s="7">
-        <v>1.49</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>-20.79</v>
+        <v>-4.98</v>
       </c>
       <c r="D57" s="6">
-        <v>-19.5</v>
+        <v>-3.1</v>
       </c>
       <c r="E57" s="7">
-        <v>1.29</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>-7.54</v>
+        <v>-2.68</v>
       </c>
       <c r="D58" s="6">
-        <v>-6.56</v>
+        <v>-1.58</v>
       </c>
       <c r="E58" s="7">
-        <v>0.98</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>-19.7</v>
+        <v>24.23</v>
       </c>
       <c r="D59" s="6">
-        <v>-19.12</v>
+        <v>24.97</v>
       </c>
       <c r="E59" s="7">
-        <v>0.58</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>-6.39</v>
+        <v>-5.55</v>
       </c>
       <c r="D60" s="6">
-        <v>-4.98</v>
+        <v>-4.43</v>
       </c>
       <c r="E60" s="7">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>-4.35</v>
+        <v>7.84</v>
       </c>
       <c r="D61" s="6">
-        <v>-2.68</v>
+        <v>8.32</v>
       </c>
       <c r="E61" s="7">
-        <v>1.67</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>23.02</v>
+        <v>17.75</v>
       </c>
       <c r="D62" s="6">
-        <v>24.23</v>
+        <v>20.8</v>
       </c>
       <c r="E62" s="7">
-        <v>1.21</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>-6.64</v>
+        <v>-5.72</v>
       </c>
       <c r="D63" s="6">
-        <v>-5.55</v>
+        <v>-4.39</v>
       </c>
       <c r="E63" s="7">
-        <v>1.09</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="6">
-        <v>6.53</v>
+        <v>-10.65</v>
       </c>
       <c r="D64" s="6">
-        <v>7.84</v>
+        <v>-9.5</v>
       </c>
       <c r="E64" s="7">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="6">
-        <v>17.99</v>
+        <v>-0.4</v>
       </c>
       <c r="D65" s="6">
-        <v>17.75</v>
-      </c>
-      <c r="E65" s="8">
-        <v>-0.24</v>
+        <v>1.14</v>
+      </c>
+      <c r="E65" s="7">
+        <v>1.54</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-8.58</v>
+        <v>-7.06</v>
       </c>
       <c r="D66" s="6">
-        <v>-5.72</v>
+        <v>-6.59</v>
       </c>
       <c r="E66" s="7">
-        <v>2.86</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-11.49</v>
+        <v>-7.7</v>
       </c>
       <c r="D67" s="6">
-        <v>-10.65</v>
+        <v>-6.75</v>
       </c>
       <c r="E67" s="7">
-        <v>0.84</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-1.33</v>
+        <v>-7.83</v>
       </c>
       <c r="D68" s="6">
-        <v>-0.4</v>
+        <v>-6.74</v>
       </c>
       <c r="E68" s="7">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-5.94</v>
+        <v>-7.31</v>
       </c>
       <c r="D69" s="6">
-        <v>-7.06</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-1.12</v>
+        <v>-5.8</v>
+      </c>
+      <c r="E69" s="7">
+        <v>1.51</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-7.68</v>
+        <v>-11.19</v>
       </c>
       <c r="D70" s="6">
-        <v>-7.7</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-0.02</v>
+        <v>-10</v>
+      </c>
+      <c r="E70" s="7">
+        <v>1.19</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-7.91</v>
+        <v>-8.66</v>
       </c>
       <c r="D71" s="6">
-        <v>-7.83</v>
+        <v>-7.56</v>
       </c>
       <c r="E71" s="7">
-        <v>0.08</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-7.12</v>
+        <v>3.76</v>
       </c>
       <c r="D72" s="6">
-        <v>-7.31</v>
+        <v>0.7</v>
       </c>
       <c r="E72" s="8">
-        <v>-0.19</v>
+        <v>-3.06</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>-12.59</v>
+        <v>-5.62</v>
       </c>
       <c r="D73" s="6">
-        <v>-11.19</v>
+        <v>-3.67</v>
       </c>
       <c r="E73" s="7">
-        <v>1.4</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-8.630000000000001</v>
+        <v>-8.69</v>
       </c>
       <c r="D74" s="6">
-        <v>-8.66</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-0.03</v>
+        <v>-6.94</v>
+      </c>
+      <c r="E74" s="7">
+        <v>1.75</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>3.15</v>
+        <v>4.18</v>
       </c>
       <c r="D75" s="6">
-        <v>3.76</v>
+        <v>5.44</v>
       </c>
       <c r="E75" s="7">
-        <v>0.61</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-4.83</v>
+        <v>-1.76</v>
       </c>
       <c r="D76" s="6">
-        <v>-5.62</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.79</v>
+        <v>0.14</v>
+      </c>
+      <c r="E76" s="7">
+        <v>1.9</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>-9.17</v>
+        <v>-7.43</v>
       </c>
       <c r="D77" s="6">
-        <v>-8.69</v>
+        <v>-6.14</v>
       </c>
       <c r="E77" s="7">
-        <v>0.48</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>2.25</v>
+        <v>-3.83</v>
       </c>
       <c r="D78" s="6">
-        <v>4.18</v>
+        <v>-3.49</v>
       </c>
       <c r="E78" s="7">
-        <v>1.93</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-1.09</v>
+        <v>0.97</v>
       </c>
       <c r="D79" s="6">
-        <v>-1.76</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.67</v>
+        <v>3.4</v>
+      </c>
+      <c r="E79" s="7">
+        <v>2.43</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-8.02</v>
+        <v>-7.41</v>
       </c>
       <c r="D80" s="6">
-        <v>-7.43</v>
+        <v>-6.18</v>
       </c>
       <c r="E80" s="7">
-        <v>0.59</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-5.59</v>
+        <v>-6.97</v>
       </c>
       <c r="D81" s="6">
-        <v>-3.83</v>
+        <v>-6.69</v>
       </c>
       <c r="E81" s="7">
-        <v>1.76</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>2.2</v>
+        <v>-3.32</v>
       </c>
       <c r="D82" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="E82" s="8">
-        <v>-1.23</v>
+        <v>-1.48</v>
+      </c>
+      <c r="E82" s="7">
+        <v>1.84</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-6.26</v>
+        <v>-4.78</v>
       </c>
       <c r="D83" s="6">
-        <v>-7.41</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-1.15</v>
+        <v>-1.43</v>
+      </c>
+      <c r="E83" s="7">
+        <v>3.35</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="6">
-        <v>-6.82</v>
+        <v>-6.66</v>
       </c>
       <c r="D84" s="6">
-        <v>-6.97</v>
-      </c>
-      <c r="E84" s="8">
-        <v>-0.15</v>
+        <v>-5.09</v>
+      </c>
+      <c r="E84" s="7">
+        <v>1.57</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C85" s="6">
-        <v>-2.1</v>
+        <v>-5.75</v>
       </c>
       <c r="D85" s="6">
-        <v>-3.32</v>
-      </c>
-      <c r="E85" s="8">
-        <v>-1.22</v>
+        <v>-4.28</v>
+      </c>
+      <c r="E85" s="7">
+        <v>1.47</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C86" s="6">
-        <v>-4.51</v>
+        <v>-14.25</v>
       </c>
       <c r="D86" s="6">
-        <v>-4.78</v>
-      </c>
-      <c r="E86" s="8">
-        <v>-0.27</v>
+        <v>-13.85</v>
+      </c>
+      <c r="E86" s="7">
+        <v>0.4</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-5.94</v>
+        <v>-12.57</v>
       </c>
       <c r="D87" s="6">
-        <v>-6.66</v>
-      </c>
-      <c r="E87" s="8">
-        <v>-0.72</v>
+        <v>-12.03</v>
+      </c>
+      <c r="E87" s="7">
+        <v>0.54</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-5.38</v>
+        <v>-13.41</v>
       </c>
       <c r="D88" s="6">
-        <v>-5.75</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-0.37</v>
+        <v>-12.38</v>
+      </c>
+      <c r="E88" s="7">
+        <v>1.03</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-14.38</v>
+        <v>-11.9</v>
       </c>
       <c r="D89" s="6">
-        <v>-14.25</v>
+        <v>-11.12</v>
       </c>
       <c r="E89" s="7">
-        <v>0.13</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-13.07</v>
+        <v>-21.48</v>
       </c>
       <c r="D90" s="6">
-        <v>-12.57</v>
+        <v>-20.37</v>
       </c>
       <c r="E90" s="7">
-        <v>0.5</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-14.05</v>
+        <v>-13.37</v>
       </c>
       <c r="D91" s="6">
-        <v>-13.41</v>
+        <v>-12.36</v>
       </c>
       <c r="E91" s="7">
-        <v>0.64</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-12.39</v>
+        <v>-28.33</v>
       </c>
       <c r="D92" s="6">
-        <v>-11.9</v>
-      </c>
-      <c r="E92" s="7">
-        <v>0.49</v>
+        <v>-28.75</v>
+      </c>
+      <c r="E92" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-22.87</v>
+        <v>-8.65</v>
       </c>
       <c r="D93" s="6">
-        <v>-21.48</v>
+        <v>-7.44</v>
       </c>
       <c r="E93" s="7">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-13.73</v>
+        <v>-10.99</v>
       </c>
       <c r="D94" s="6">
-        <v>-13.37</v>
+        <v>-9.91</v>
       </c>
       <c r="E94" s="7">
-        <v>0.36</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-28.32</v>
+        <v>-3.76</v>
       </c>
       <c r="D95" s="6">
-        <v>-28.33</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-0.01</v>
+        <v>-3.31</v>
+      </c>
+      <c r="E95" s="7">
+        <v>0.45</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-8.800000000000001</v>
+        <v>-8.9</v>
       </c>
       <c r="D96" s="6">
-        <v>-8.65</v>
+        <v>-8.15</v>
       </c>
       <c r="E96" s="7">
-        <v>0.15</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-11.88</v>
+        <v>-13.77</v>
       </c>
       <c r="D97" s="6">
-        <v>-10.99</v>
+        <v>-13.19</v>
       </c>
       <c r="E97" s="7">
-        <v>0.89</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-4.63</v>
+        <v>-18.88</v>
       </c>
       <c r="D98" s="6">
-        <v>-3.76</v>
-      </c>
-      <c r="E98" s="7">
-        <v>0.87</v>
+        <v>-18.94</v>
+      </c>
+      <c r="E98" s="8">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-9.17</v>
+        <v>-3.93</v>
       </c>
       <c r="D99" s="6">
-        <v>-8.9</v>
+        <v>-2.34</v>
       </c>
       <c r="E99" s="7">
-        <v>0.27</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-14.47</v>
+        <v>-13.31</v>
       </c>
       <c r="D100" s="6">
-        <v>-13.77</v>
-      </c>
-      <c r="E100" s="7">
-        <v>0.7</v>
+        <v>-13.54</v>
+      </c>
+      <c r="E100" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-19.66</v>
+        <v>-14.76</v>
       </c>
       <c r="D101" s="6">
-        <v>-18.88</v>
+        <v>-14.25</v>
       </c>
       <c r="E101" s="7">
-        <v>0.78</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-3.22</v>
+        <v>-5.94</v>
       </c>
       <c r="D102" s="6">
-        <v>-3.93</v>
-      </c>
-      <c r="E102" s="8">
-        <v>-0.71</v>
+        <v>-4.96</v>
+      </c>
+      <c r="E102" s="7">
+        <v>0.98</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="6">
-        <v>-13.8</v>
+        <v>-8.18</v>
       </c>
       <c r="D103" s="6">
-        <v>-13.31</v>
+        <v>-6.52</v>
       </c>
       <c r="E103" s="7">
-        <v>0.49</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="6">
-        <v>-15.08</v>
+        <v>-7.55</v>
       </c>
       <c r="D104" s="6">
-        <v>-14.76</v>
+        <v>-6.09</v>
       </c>
       <c r="E104" s="7">
-        <v>0.32</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C105" s="6">
-        <v>-4.99</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="D105" s="6">
-        <v>-5.94</v>
-      </c>
-      <c r="E105" s="8">
-        <v>-0.95</v>
+        <v>-7.17</v>
+      </c>
+      <c r="E105" s="7">
+        <v>1.29</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>-8.56</v>
+        <v>25421.9</v>
       </c>
       <c r="D106" s="6">
-        <v>-8.18</v>
+        <v>25541.95</v>
       </c>
       <c r="E106" s="7">
-        <v>0.38</v>
+        <v>120.05</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>-7.87</v>
+        <v>9182.549999999999</v>
       </c>
       <c r="D107" s="6">
-        <v>-7.55</v>
+        <v>9239.299999999999</v>
       </c>
       <c r="E107" s="7">
-        <v>0.32</v>
+        <v>56.75</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>-8.529999999999999</v>
+        <v>10943.6</v>
       </c>
       <c r="D108" s="6">
-        <v>-8.460000000000001</v>
+        <v>11074.35</v>
       </c>
       <c r="E108" s="7">
-        <v>0.07000000000000001</v>
+        <v>130.75</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>25384.95</v>
+        <v>36594.65</v>
       </c>
       <c r="D109" s="6">
-        <v>25421.9</v>
+        <v>36915.75</v>
       </c>
       <c r="E109" s="7">
-        <v>36.95</v>
+        <v>321.1</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>9130.25</v>
+        <v>44579.65</v>
       </c>
       <c r="D110" s="6">
-        <v>9182.549999999999</v>
+        <v>45205.35</v>
       </c>
       <c r="E110" s="7">
-        <v>52.3</v>
+        <v>625.7</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>10862.95</v>
+        <v>24656.4</v>
       </c>
       <c r="D111" s="6">
-        <v>10943.6</v>
+        <v>24946.05</v>
       </c>
       <c r="E111" s="7">
-        <v>80.65000000000001</v>
+        <v>289.65</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>36388.15</v>
+        <v>28301.65</v>
       </c>
       <c r="D112" s="6">
-        <v>36594.65</v>
-      </c>
-      <c r="E112" s="7">
-        <v>206.5</v>
+        <v>28136.05</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-165.6</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>43789.85</v>
+        <v>15220.55</v>
       </c>
       <c r="D113" s="6">
-        <v>44579.65</v>
+        <v>15422.65</v>
       </c>
       <c r="E113" s="7">
-        <v>789.8</v>
+        <v>202.1</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>24556.1</v>
+        <v>8692.950000000001</v>
       </c>
       <c r="D114" s="6">
-        <v>24656.4</v>
+        <v>8797.549999999999</v>
       </c>
       <c r="E114" s="7">
-        <v>100.3</v>
+        <v>104.6</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>28304.7</v>
+        <v>1560.5</v>
       </c>
       <c r="D115" s="6">
-        <v>28301.65</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-3.05</v>
+        <v>1567.7</v>
+      </c>
+      <c r="E115" s="7">
+        <v>7.2</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>15195.9</v>
+        <v>12498</v>
       </c>
       <c r="D116" s="6">
-        <v>15220.55</v>
+        <v>12599.75</v>
       </c>
       <c r="E116" s="7">
-        <v>24.65</v>
+        <v>101.75</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>8605.15</v>
+        <v>9283.549999999999</v>
       </c>
       <c r="D117" s="6">
-        <v>8692.950000000001</v>
+        <v>9346.450000000001</v>
       </c>
       <c r="E117" s="7">
-        <v>87.8</v>
+        <v>62.9</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>1546.3</v>
+        <v>8014.85</v>
       </c>
       <c r="D118" s="6">
-        <v>1560.5</v>
-      </c>
-      <c r="E118" s="7">
-        <v>14.2</v>
+        <v>8008.4</v>
+      </c>
+      <c r="E118" s="8">
+        <v>-6.45</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>12460.7</v>
+        <v>26117.1</v>
       </c>
       <c r="D119" s="6">
-        <v>12498</v>
+        <v>26549.6</v>
       </c>
       <c r="E119" s="7">
-        <v>37.3</v>
+        <v>432.5</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>9208.65</v>
+        <v>839.7</v>
       </c>
       <c r="D120" s="6">
-        <v>9283.549999999999</v>
-      </c>
-      <c r="E120" s="7">
-        <v>74.90000000000001</v>
+        <v>837.45</v>
+      </c>
+      <c r="E120" s="8">
+        <v>-2.25</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>7937.8</v>
+        <v>29069.15</v>
       </c>
       <c r="D121" s="6">
-        <v>8014.85</v>
+        <v>29240.7</v>
       </c>
       <c r="E121" s="7">
-        <v>77.05</v>
+        <v>171.55</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>26311.55</v>
+        <v>15934.65</v>
       </c>
       <c r="D122" s="6">
-        <v>26117.1</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-194.45</v>
+        <v>16101.3</v>
+      </c>
+      <c r="E122" s="7">
+        <v>166.65</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="6">
-        <v>835</v>
+        <v>9180.5</v>
       </c>
       <c r="D123" s="6">
-        <v>839.7</v>
+        <v>9347.25</v>
       </c>
       <c r="E123" s="7">
-        <v>4.7</v>
+        <v>166.75</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C124" s="6">
-        <v>28957.9</v>
+        <v>10510.75</v>
       </c>
       <c r="D124" s="6">
-        <v>29069.15</v>
+        <v>10676.85</v>
       </c>
       <c r="E124" s="7">
-        <v>111.25</v>
+        <v>166.1</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C125" s="6">
-        <v>16095.55</v>
+        <v>26718.15</v>
       </c>
       <c r="D125" s="6">
-        <v>15934.65</v>
-      </c>
-      <c r="E125" s="8">
-        <v>-160.9</v>
+        <v>27093.75</v>
+      </c>
+      <c r="E125" s="7">
+        <v>375.6</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C126" s="6">
-        <v>9142.549999999999</v>
+        <v>13</v>
       </c>
       <c r="D126" s="6">
-        <v>9180.5</v>
+        <v>19</v>
       </c>
       <c r="E126" s="7">
-        <v>37.95</v>
+        <v>6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>10474.85</v>
+        <v>38</v>
       </c>
       <c r="D127" s="6">
-        <v>10510.75</v>
+        <v>44</v>
       </c>
       <c r="E127" s="7">
-        <v>35.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>26697.25</v>
+        <v>26</v>
       </c>
       <c r="D128" s="6">
-        <v>26718.15</v>
-      </c>
-      <c r="E128" s="7">
-        <v>20.9</v>
+        <v>13</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-13</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
@@ -5536,58 +5500,58 @@
         <v>44</v>
       </c>
       <c r="D129" s="6">
-        <v>32</v>
-      </c>
-      <c r="E129" s="8">
-        <v>-12</v>
+        <v>56</v>
+      </c>
+      <c r="E129" s="7">
+        <v>12</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C130" s="6">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D130" s="6">
-        <v>38</v>
-      </c>
-      <c r="E130" s="7">
-        <v>6</v>
+        <v>93</v>
+      </c>
+      <c r="E130" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="6">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="D131" s="6">
-        <v>26</v>
-      </c>
-      <c r="E131" s="7">
-        <v>7</v>
+        <v>50</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C132" s="6">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="D132" s="6">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="E132" s="7">
         <v>6</v>
@@ -5595,433 +5559,382 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C133" s="6">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="D133" s="6">
-        <v>87</v>
-      </c>
-      <c r="E133" s="7">
-        <v>6</v>
+        <v>38</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-12</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C134" s="6">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="D134" s="6">
-        <v>99</v>
+        <v>26</v>
       </c>
       <c r="E134" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>87</v>
+        <v>22.7</v>
       </c>
       <c r="D135" s="6">
-        <v>81</v>
-      </c>
-      <c r="E135" s="8">
-        <v>-6</v>
+        <v>25.6</v>
+      </c>
+      <c r="E135" s="7">
+        <v>2.9</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>99</v>
+        <v>30.06</v>
       </c>
       <c r="D136" s="6">
-        <v>93</v>
-      </c>
-      <c r="E136" s="8">
-        <v>-6</v>
+        <v>34.29</v>
+      </c>
+      <c r="E136" s="7">
+        <v>4.23</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>26</v>
+        <v>27.43</v>
       </c>
       <c r="D137" s="6">
-        <v>19</v>
-      </c>
-      <c r="E137" s="8">
-        <v>-7</v>
+        <v>35.21</v>
+      </c>
+      <c r="E137" s="7">
+        <v>7.78</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>21.82</v>
+        <v>33.27</v>
       </c>
       <c r="D138" s="6">
-        <v>22.7</v>
+        <v>40.29</v>
       </c>
       <c r="E138" s="7">
-        <v>0.88</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>25.97</v>
+        <v>38.46</v>
       </c>
       <c r="D139" s="6">
-        <v>30.06</v>
+        <v>45.13</v>
       </c>
       <c r="E139" s="7">
-        <v>4.09</v>
+        <v>6.67</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>22.07</v>
+        <v>32.67</v>
       </c>
       <c r="D140" s="6">
-        <v>27.43</v>
+        <v>41.03</v>
       </c>
       <c r="E140" s="7">
-        <v>5.36</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>28.22</v>
+        <v>39.27</v>
       </c>
       <c r="D141" s="6">
-        <v>33.27</v>
-      </c>
-      <c r="E141" s="7">
-        <v>5.05</v>
+        <v>37.43</v>
+      </c>
+      <c r="E141" s="8">
+        <v>-1.84</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>28.25</v>
+        <v>26.68</v>
       </c>
       <c r="D142" s="6">
-        <v>38.46</v>
+        <v>35.94</v>
       </c>
       <c r="E142" s="7">
-        <v>10.21</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>29.46</v>
+        <v>30.74</v>
       </c>
       <c r="D143" s="6">
-        <v>32.67</v>
+        <v>38.81</v>
       </c>
       <c r="E143" s="7">
-        <v>3.21</v>
+        <v>8.07</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>39.3</v>
+        <v>51.5</v>
       </c>
       <c r="D144" s="6">
-        <v>39.27</v>
-      </c>
-      <c r="E144" s="8">
-        <v>-0.03</v>
+        <v>53.06</v>
+      </c>
+      <c r="E144" s="7">
+        <v>1.56</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>25.45</v>
+        <v>38.1</v>
       </c>
       <c r="D145" s="6">
-        <v>26.68</v>
+        <v>41.22</v>
       </c>
       <c r="E145" s="7">
-        <v>1.23</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>22.8</v>
+        <v>30.85</v>
       </c>
       <c r="D146" s="6">
-        <v>30.74</v>
+        <v>36.36</v>
       </c>
       <c r="E146" s="7">
-        <v>7.94</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>48.35</v>
+        <v>35.7</v>
       </c>
       <c r="D147" s="6">
-        <v>51.5</v>
-      </c>
-      <c r="E147" s="7">
-        <v>3.15</v>
+        <v>35.45</v>
+      </c>
+      <c r="E147" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>36.96</v>
+        <v>39.78</v>
       </c>
       <c r="D148" s="6">
-        <v>38.1</v>
+        <v>48.88</v>
       </c>
       <c r="E148" s="7">
-        <v>1.14</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>23.53</v>
+        <v>41.81</v>
       </c>
       <c r="D149" s="6">
-        <v>30.85</v>
-      </c>
-      <c r="E149" s="7">
-        <v>7.32</v>
+        <v>41.16</v>
+      </c>
+      <c r="E149" s="8">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>30.22</v>
+        <v>28.12</v>
       </c>
       <c r="D150" s="6">
-        <v>35.7</v>
+        <v>34.15</v>
       </c>
       <c r="E150" s="7">
-        <v>5.48</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>42.98</v>
+        <v>32.45</v>
       </c>
       <c r="D151" s="6">
-        <v>39.78</v>
-      </c>
-      <c r="E151" s="8">
-        <v>-3.2</v>
+        <v>38.95</v>
+      </c>
+      <c r="E151" s="7">
+        <v>6.5</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C152" s="6">
-        <v>39.97</v>
+        <v>39.94</v>
       </c>
       <c r="D152" s="6">
-        <v>41.81</v>
+        <v>47.06</v>
       </c>
       <c r="E152" s="7">
-        <v>1.84</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C153" s="6">
-        <v>23.92</v>
+        <v>28.97</v>
       </c>
       <c r="D153" s="6">
-        <v>28.12</v>
+        <v>40.27</v>
       </c>
       <c r="E153" s="7">
-        <v>4.2</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C154" s="6">
-        <v>35.88</v>
+        <v>39.69</v>
       </c>
       <c r="D154" s="6">
-        <v>32.45</v>
-      </c>
-      <c r="E154" s="8">
-        <v>-3.43</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C155" s="6">
-        <v>38.18</v>
-      </c>
-      <c r="D155" s="6">
-        <v>39.94</v>
-      </c>
-      <c r="E155" s="7">
-        <v>1.76</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C156" s="6">
-        <v>26.17</v>
-      </c>
-      <c r="D156" s="6">
-        <v>28.97</v>
-      </c>
-      <c r="E156" s="7">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
-      <c r="A157" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C157" s="6">
-        <v>39.12</v>
-      </c>
-      <c r="D157" s="6">
-        <v>39.69</v>
-      </c>
-      <c r="E157" s="7">
-        <v>0.57</v>
+        <v>48.98</v>
+      </c>
+      <c r="E154" s="7">
+        <v>9.289999999999999</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6045,28 +5958,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6080,16 +5993,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>34.4</v>
+        <v>40</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-5</v>
+        <v>-4.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-5.2</v>
+        <v>-4</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -6203,68 +6116,68 @@
         <v>38</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>49</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>51</v>
       </c>
       <c r="F1" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="J1" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2582</v>
+        <v>0.2629</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1892</v>
+        <v>0.1931</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1687</v>
+        <v>0.175</v>
       </c>
       <c r="D2" s="14">
-        <v>0.166</v>
+        <v>0.1716</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1213</v>
+        <v>0.1292</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1115</v>
+        <v>0.1284</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1049</v>
+        <v>0.117</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0931</v>
+        <v>0.1156</v>
       </c>
       <c r="I2" s="14">
-        <v>0.08800000000000001</v>
+        <v>0.1079</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0862</v>
+        <v>0.09759999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>57</v>
@@ -6282,10 +6195,10 @@
         <v>44</v>
       </c>
       <c r="H3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="I3" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="J3" s="13" t="s">
         <v>56</v>
@@ -6293,34 +6206,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0803</v>
+        <v>0.091</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0668</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="C4" s="14">
-        <v>0.06370000000000001</v>
+        <v>0.068</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0607</v>
+        <v>0.0638</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0322</v>
+        <v>0.0347</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0197</v>
+        <v>0.0239</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0446</v>
+        <v>-0.0431</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0688</v>
+        <v>-0.0475</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.08699999999999999</v>
+        <v>-0.0667</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.1376</v>
+        <v>-0.09279999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="117">
   <si>
     <t>Symbol</t>
   </si>
@@ -283,28 +283,55 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>26.9 → 35.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>26.9</t>
+  </si>
+  <si>
+    <t>35.1</t>
+  </si>
+  <si>
+    <t>28.3 → 33.1</t>
+  </si>
+  <si>
+    <t>28.3</t>
+  </si>
+  <si>
+    <t>33.1</t>
+  </si>
+  <si>
+    <t>29.3 → 33.1</t>
+  </si>
+  <si>
+    <t>29.3</t>
+  </si>
+  <si>
+    <t>25.4 → 38.5</t>
+  </si>
+  <si>
+    <t>25.4</t>
+  </si>
+  <si>
+    <t>38.5</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>55.4 → 45.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>55.4</t>
-  </si>
-  <si>
-    <t>45.5</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>44.3 → 52.0</t>
+  </si>
+  <si>
+    <t>44.3</t>
+  </si>
+  <si>
+    <t>52.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -390,14 +417,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -430,13 +457,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1034,10 +1061,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>24512.7</v>
+        <v>24859.9</v>
       </c>
       <c r="E2">
-        <v>-2.49</v>
+        <v>1.42</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1046,43 +1073,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-17.32</v>
+        <v>-16.15</v>
       </c>
       <c r="I2">
-        <v>3.13</v>
+        <v>4.59</v>
       </c>
       <c r="J2">
-        <v>-6.77</v>
+        <v>-2.07</v>
       </c>
       <c r="K2">
-        <v>-11.5</v>
+        <v>-10.5</v>
       </c>
       <c r="L2">
-        <v>-8.109999999999999</v>
+        <v>-7.45</v>
       </c>
       <c r="M2">
-        <v>-7.28</v>
+        <v>-6.34</v>
       </c>
       <c r="N2">
-        <v>17.22</v>
+        <v>16.95</v>
       </c>
       <c r="O2">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q2">
-        <v>25200.08</v>
+        <v>25095.07</v>
       </c>
       <c r="R2">
-        <v>26526.14</v>
+        <v>26386.47</v>
       </c>
       <c r="S2">
-        <v>27913.86</v>
+        <v>27869.06</v>
       </c>
       <c r="T2">
-        <v>27028.7</v>
+        <v>27015.29</v>
       </c>
       <c r="U2">
-        <v>-9.31</v>
+        <v>-7.98</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1097,40 +1124,40 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>18.78</v>
+        <v>26.13</v>
       </c>
       <c r="AA2">
-        <v>-775.05</v>
+        <v>-799.01</v>
       </c>
       <c r="AB2">
-        <v>-596.09</v>
+        <v>-636.6799999999999</v>
       </c>
       <c r="AC2">
-        <v>-178.95</v>
+        <v>-162.34</v>
       </c>
       <c r="AD2">
-        <v>10.89</v>
+        <v>16.34</v>
       </c>
       <c r="AE2">
-        <v>11.72</v>
+        <v>13.41</v>
       </c>
       <c r="AF2">
-        <v>424.08</v>
+        <v>430.89</v>
       </c>
       <c r="AH2">
-        <v>28294.01</v>
+        <v>28219.56</v>
       </c>
       <c r="AI2">
-        <v>24758.28</v>
+        <v>24553.38</v>
       </c>
       <c r="AJ2">
-        <v>26086.21</v>
+        <v>26008.9</v>
       </c>
       <c r="AK2" t="s">
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>79.04000000000001</v>
+        <v>80.47</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1144,10 +1171,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>8851.4</v>
+        <v>8923.4</v>
       </c>
       <c r="E3">
-        <v>-2.81</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1156,43 +1183,43 @@
         <v>8851.4</v>
       </c>
       <c r="H3">
-        <v>-15.73</v>
+        <v>-15.04</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J3">
-        <v>-4.93</v>
+        <v>-2.27</v>
       </c>
       <c r="K3">
-        <v>-8.77</v>
+        <v>-7.78</v>
       </c>
       <c r="L3">
-        <v>-9.44</v>
+        <v>-9.789999999999999</v>
       </c>
       <c r="M3">
-        <v>-1.12</v>
+        <v>-0.7</v>
       </c>
       <c r="N3">
-        <v>8.66</v>
+        <v>8.59</v>
       </c>
       <c r="O3">
         <v>56</v>
       </c>
       <c r="Q3">
-        <v>9102.15</v>
+        <v>9060.780000000001</v>
       </c>
       <c r="R3">
-        <v>9412.84</v>
+        <v>9372.08</v>
       </c>
       <c r="S3">
-        <v>9669.98</v>
+        <v>9651.809999999999</v>
       </c>
       <c r="T3">
-        <v>9773.27</v>
+        <v>9771.91</v>
       </c>
       <c r="U3">
-        <v>-9.43</v>
+        <v>-8.68</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1207,40 +1234,40 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>23.35</v>
+        <v>28.06</v>
       </c>
       <c r="AA3">
-        <v>-175.75</v>
+        <v>-189.09</v>
       </c>
       <c r="AB3">
-        <v>-129.13</v>
+        <v>-141.12</v>
       </c>
       <c r="AC3">
-        <v>-46.62</v>
+        <v>-47.97</v>
       </c>
       <c r="AD3">
-        <v>18.63</v>
+        <v>12.29</v>
       </c>
       <c r="AE3">
-        <v>20.87</v>
+        <v>18.61</v>
       </c>
       <c r="AF3">
-        <v>128.51</v>
+        <v>126.99</v>
       </c>
       <c r="AH3">
-        <v>9863.209999999999</v>
+        <v>9845.299999999999</v>
       </c>
       <c r="AI3">
-        <v>8962.469999999999</v>
+        <v>8898.870000000001</v>
       </c>
       <c r="AJ3">
-        <v>9359.57</v>
+        <v>9261.98</v>
       </c>
       <c r="AK3" t="s">
         <v>80</v>
       </c>
       <c r="AL3">
-        <v>56.44</v>
+        <v>60.22</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1254,10 +1281,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>10741.2</v>
+        <v>10903.45</v>
       </c>
       <c r="E4">
-        <v>-2.15</v>
+        <v>1.51</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1266,43 +1293,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-15.02</v>
+        <v>-13.73</v>
       </c>
       <c r="I4">
-        <v>3.94</v>
+        <v>5.51</v>
       </c>
       <c r="J4">
-        <v>-2.99</v>
+        <v>0.37</v>
       </c>
       <c r="K4">
-        <v>-7.09</v>
+        <v>-5.76</v>
       </c>
       <c r="L4">
-        <v>-8.199999999999999</v>
+        <v>-7.11</v>
       </c>
       <c r="M4">
-        <v>-11.29</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="N4">
-        <v>8.08</v>
+        <v>8.19</v>
       </c>
       <c r="O4">
         <v>19</v>
       </c>
       <c r="Q4">
-        <v>10919.75</v>
+        <v>10927.85</v>
       </c>
       <c r="R4">
-        <v>11272.44</v>
+        <v>11241.03</v>
       </c>
       <c r="S4">
-        <v>11697.69</v>
+        <v>11681.66</v>
       </c>
       <c r="T4">
-        <v>11555.24</v>
+        <v>11548.8</v>
       </c>
       <c r="U4">
-        <v>-7.04</v>
+        <v>-5.59</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1317,31 +1344,31 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>26.88</v>
+        <v>35.11</v>
       </c>
       <c r="AA4">
-        <v>-218.45</v>
+        <v>-218.19</v>
       </c>
       <c r="AB4">
-        <v>-179.08</v>
+        <v>-186.91</v>
       </c>
       <c r="AC4">
-        <v>-39.36</v>
+        <v>-31.29</v>
       </c>
       <c r="AD4">
-        <v>44.8</v>
+        <v>44.64</v>
       </c>
       <c r="AE4">
-        <v>42.8</v>
+        <v>45.9</v>
       </c>
       <c r="AF4">
-        <v>135.29</v>
+        <v>139.8</v>
       </c>
       <c r="AH4">
-        <v>11769.04</v>
+        <v>11747.96</v>
       </c>
       <c r="AI4">
-        <v>10775.84</v>
+        <v>10734.1</v>
       </c>
       <c r="AJ4">
         <v>11255.06</v>
@@ -1350,7 +1377,7 @@
         <v>80</v>
       </c>
       <c r="AL4">
-        <v>58.65</v>
+        <v>59.47</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1364,10 +1391,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>35649.3</v>
+        <v>35786.5</v>
       </c>
       <c r="E5">
-        <v>-2.82</v>
+        <v>0.38</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1376,43 +1403,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-14.17</v>
+        <v>-13.84</v>
       </c>
       <c r="I5">
-        <v>7.71</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="J5">
-        <v>-2.69</v>
+        <v>-1.65</v>
       </c>
       <c r="K5">
-        <v>-6.12</v>
+        <v>-6.06</v>
       </c>
       <c r="L5">
-        <v>-8.210000000000001</v>
+        <v>-8.81</v>
       </c>
       <c r="M5">
-        <v>1.65</v>
+        <v>2.25</v>
       </c>
       <c r="N5">
-        <v>8.32</v>
+        <v>8.18</v>
       </c>
       <c r="O5">
         <v>68</v>
       </c>
       <c r="Q5">
-        <v>36446.26</v>
+        <v>36325.93</v>
       </c>
       <c r="R5">
-        <v>37207.79</v>
+        <v>37080.43</v>
       </c>
       <c r="S5">
-        <v>37930.7</v>
+        <v>37860.89</v>
       </c>
       <c r="T5">
-        <v>37695.92</v>
+        <v>37701.01</v>
       </c>
       <c r="U5">
-        <v>-5.43</v>
+        <v>-5.08</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1427,40 +1454,40 @@
         <v>1</v>
       </c>
       <c r="Z5">
-        <v>27.31</v>
+        <v>29.98</v>
       </c>
       <c r="AA5">
-        <v>-491.13</v>
+        <v>-532.78</v>
       </c>
       <c r="AB5">
-        <v>-399.51</v>
+        <v>-426.16</v>
       </c>
       <c r="AC5">
-        <v>-91.62</v>
+        <v>-106.62</v>
       </c>
       <c r="AD5">
-        <v>42.99</v>
+        <v>23.6</v>
       </c>
       <c r="AE5">
-        <v>44.46</v>
+        <v>40.16</v>
       </c>
       <c r="AF5">
-        <v>475.2</v>
+        <v>481.74</v>
       </c>
       <c r="AH5">
-        <v>38593.68</v>
+        <v>38498.47</v>
       </c>
       <c r="AI5">
-        <v>35821.89</v>
+        <v>35662.39</v>
       </c>
       <c r="AJ5">
-        <v>37562.57</v>
+        <v>37083.58</v>
       </c>
       <c r="AK5" t="s">
         <v>80</v>
       </c>
       <c r="AL5">
-        <v>37.19</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1474,10 +1501,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>43898.05</v>
+        <v>44864.25</v>
       </c>
       <c r="E6">
-        <v>-2.02</v>
+        <v>2.2</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1486,43 +1513,43 @@
         <v>43789.85</v>
       </c>
       <c r="H6">
-        <v>-22.68</v>
+        <v>-20.98</v>
       </c>
       <c r="I6">
-        <v>0.25</v>
+        <v>2.45</v>
       </c>
       <c r="J6">
-        <v>-1.37</v>
+        <v>2.45</v>
       </c>
       <c r="K6">
-        <v>-3.72</v>
+        <v>-1.94</v>
       </c>
       <c r="L6">
-        <v>-11.05</v>
+        <v>-9.02</v>
       </c>
       <c r="M6">
-        <v>-20.11</v>
+        <v>-18</v>
       </c>
       <c r="N6">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>44454.75</v>
+        <v>44669.63</v>
       </c>
       <c r="R6">
-        <v>45166.63</v>
+        <v>45144.38</v>
       </c>
       <c r="S6">
-        <v>46796.92</v>
+        <v>46719.23</v>
       </c>
       <c r="T6">
-        <v>49466.34</v>
+        <v>49416.35</v>
       </c>
       <c r="U6">
-        <v>-11.26</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1537,31 +1564,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>35.91</v>
+        <v>45.04</v>
       </c>
       <c r="AA6">
-        <v>-619.85</v>
+        <v>-574.67</v>
       </c>
       <c r="AB6">
-        <v>-599.99</v>
+        <v>-594.92</v>
       </c>
       <c r="AC6">
-        <v>-19.86</v>
+        <v>20.26</v>
       </c>
       <c r="AD6">
-        <v>63.37</v>
+        <v>63.24</v>
       </c>
       <c r="AE6">
-        <v>63.22</v>
+        <v>65.88</v>
       </c>
       <c r="AF6">
-        <v>646.62</v>
+        <v>680.48</v>
       </c>
       <c r="AH6">
-        <v>46468.5</v>
+        <v>46451.18</v>
       </c>
       <c r="AI6">
-        <v>43864.76</v>
+        <v>43837.57</v>
       </c>
       <c r="AJ6">
         <v>45688.38</v>
@@ -1570,7 +1597,7 @@
         <v>80</v>
       </c>
       <c r="AL6">
-        <v>40.05</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1584,10 +1611,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>24640.45</v>
+        <v>24968.5</v>
       </c>
       <c r="E7">
-        <v>-1.11</v>
+        <v>1.33</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1596,22 +1623,22 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-13.43</v>
+        <v>-12.28</v>
       </c>
       <c r="I7">
-        <v>4.76</v>
+        <v>6.15</v>
       </c>
       <c r="J7">
-        <v>-0.04</v>
+        <v>1.68</v>
       </c>
       <c r="K7">
-        <v>-4.99</v>
+        <v>-2.83</v>
       </c>
       <c r="L7">
-        <v>-6.96</v>
+        <v>-6.94</v>
       </c>
       <c r="M7">
-        <v>-5.25</v>
+        <v>-4.05</v>
       </c>
       <c r="N7">
         <v>6.16</v>
@@ -1620,19 +1647,19 @@
         <v>62</v>
       </c>
       <c r="Q7">
-        <v>24743.08</v>
+        <v>24825.56</v>
       </c>
       <c r="R7">
-        <v>25092.57</v>
+        <v>25072.16</v>
       </c>
       <c r="S7">
-        <v>25827.4</v>
+        <v>25788.7</v>
       </c>
       <c r="T7">
-        <v>26362.03</v>
+        <v>26349.94</v>
       </c>
       <c r="U7">
-        <v>-6.53</v>
+        <v>-5.24</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1647,31 +1674,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>35.65</v>
+        <v>44.17</v>
       </c>
       <c r="AA7">
-        <v>-329.58</v>
+        <v>-300.29</v>
       </c>
       <c r="AB7">
-        <v>-330.11</v>
+        <v>-324.15</v>
       </c>
       <c r="AC7">
-        <v>0.54</v>
+        <v>23.86</v>
       </c>
       <c r="AD7">
-        <v>67.28</v>
+        <v>73.56</v>
       </c>
       <c r="AE7">
-        <v>57.27</v>
+        <v>68.03</v>
       </c>
       <c r="AF7">
-        <v>316.34</v>
+        <v>322.77</v>
       </c>
       <c r="AH7">
-        <v>25827.22</v>
+        <v>25796.16</v>
       </c>
       <c r="AI7">
-        <v>24357.93</v>
+        <v>24348.16</v>
       </c>
       <c r="AJ7">
         <v>25420.21</v>
@@ -1680,7 +1707,7 @@
         <v>80</v>
       </c>
       <c r="AL7">
-        <v>38.88</v>
+        <v>36.33</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1694,10 +1721,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>27736.6</v>
+        <v>28574.9</v>
       </c>
       <c r="E8">
-        <v>-0.08</v>
+        <v>3.02</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1706,43 +1733,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-29.76</v>
+        <v>-27.64</v>
       </c>
       <c r="I8">
-        <v>7.63</v>
+        <v>10.89</v>
       </c>
       <c r="J8">
-        <v>0.11</v>
+        <v>0.95</v>
       </c>
       <c r="K8">
-        <v>-7.53</v>
+        <v>-4.38</v>
       </c>
       <c r="L8">
-        <v>0.97</v>
+        <v>2.02</v>
       </c>
       <c r="M8">
-        <v>-17.68</v>
+        <v>-15.09</v>
       </c>
       <c r="N8">
-        <v>-5.29</v>
+        <v>-4.08</v>
       </c>
       <c r="O8">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="Q8">
-        <v>28047.36</v>
+        <v>28101.4</v>
       </c>
       <c r="R8">
-        <v>28459.72</v>
+        <v>28442.77</v>
       </c>
       <c r="S8">
-        <v>29974.96</v>
+        <v>29924</v>
       </c>
       <c r="T8">
-        <v>31208.78</v>
+        <v>31161.34</v>
       </c>
       <c r="U8">
-        <v>-11.13</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1757,31 +1784,31 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>33.35</v>
+        <v>47.27</v>
       </c>
       <c r="AA8">
-        <v>-571.75</v>
+        <v>-498.84</v>
       </c>
       <c r="AB8">
-        <v>-559.92</v>
+        <v>-547.7</v>
       </c>
       <c r="AC8">
-        <v>-11.83</v>
+        <v>48.87</v>
       </c>
       <c r="AD8">
-        <v>59</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="AE8">
-        <v>67.79000000000001</v>
+        <v>64.17</v>
       </c>
       <c r="AF8">
-        <v>599.22</v>
+        <v>630.71</v>
       </c>
       <c r="AH8">
-        <v>29551.62</v>
+        <v>29515.33</v>
       </c>
       <c r="AI8">
-        <v>27367.81</v>
+        <v>27370.2</v>
       </c>
       <c r="AJ8">
         <v>29681.62</v>
@@ -1790,7 +1817,7 @@
         <v>80</v>
       </c>
       <c r="AL8">
-        <v>22.8</v>
+        <v>22.57</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1804,10 +1831,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>14845.15</v>
+        <v>14953.05</v>
       </c>
       <c r="E9">
-        <v>-2.61</v>
+        <v>0.73</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1816,31 +1843,31 @@
         <v>14845.15</v>
       </c>
       <c r="H9">
-        <v>-10.91</v>
+        <v>-10.26</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="J9">
-        <v>-3.94</v>
+        <v>-1.6</v>
       </c>
       <c r="K9">
-        <v>-8.289999999999999</v>
+        <v>-7.97</v>
       </c>
       <c r="L9">
-        <v>-6</v>
+        <v>-6.19</v>
       </c>
       <c r="N9">
-        <v>-15.3</v>
+        <v>-13.27</v>
       </c>
       <c r="Q9">
-        <v>15185.51</v>
+        <v>15136.94</v>
       </c>
       <c r="R9">
-        <v>15666.41</v>
+        <v>15603.55</v>
       </c>
       <c r="S9">
-        <v>16147.28</v>
+        <v>16125.24</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1852,40 +1879,40 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>25.5</v>
+        <v>29.7</v>
       </c>
       <c r="AA9">
-        <v>-285.72</v>
+        <v>-302.61</v>
       </c>
       <c r="AB9">
-        <v>-217.9</v>
+        <v>-234.84</v>
       </c>
       <c r="AC9">
-        <v>-67.81999999999999</v>
+        <v>-67.76000000000001</v>
       </c>
       <c r="AD9">
-        <v>31.67</v>
+        <v>18.5</v>
       </c>
       <c r="AE9">
-        <v>36.87</v>
+        <v>30.43</v>
       </c>
       <c r="AF9">
-        <v>201.39</v>
+        <v>204.5</v>
       </c>
       <c r="AH9">
-        <v>16379.27</v>
+        <v>16335.96</v>
       </c>
       <c r="AI9">
-        <v>14953.55</v>
+        <v>14871.14</v>
       </c>
       <c r="AJ9">
-        <v>15644.71</v>
+        <v>15490.29</v>
       </c>
       <c r="AK9" t="s">
         <v>80</v>
       </c>
       <c r="AL9">
-        <v>57.77</v>
+        <v>59.65</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1899,10 +1926,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8503.6</v>
+        <v>8574.450000000001</v>
       </c>
       <c r="E10">
-        <v>-2.58</v>
+        <v>0.83</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1911,43 +1938,43 @@
         <v>8503.6</v>
       </c>
       <c r="H10">
-        <v>-12.92</v>
+        <v>-12.2</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>0.83</v>
       </c>
       <c r="J10">
-        <v>-2.64</v>
+        <v>-0.36</v>
       </c>
       <c r="K10">
-        <v>-7.46</v>
+        <v>-6.23</v>
       </c>
       <c r="L10">
-        <v>-8.82</v>
+        <v>-9.07</v>
       </c>
       <c r="M10">
-        <v>-6.06</v>
+        <v>-4.8</v>
       </c>
       <c r="N10">
-        <v>10.67</v>
+        <v>10.76</v>
       </c>
       <c r="O10">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Q10">
-        <v>8665.549999999999</v>
+        <v>8659.41</v>
       </c>
       <c r="R10">
-        <v>8892.459999999999</v>
+        <v>8865.209999999999</v>
       </c>
       <c r="S10">
-        <v>9160.73</v>
+        <v>9144.68</v>
       </c>
       <c r="T10">
-        <v>9272.860000000001</v>
+        <v>9268.190000000001</v>
       </c>
       <c r="U10">
-        <v>-8.300000000000001</v>
+        <v>-7.49</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1962,40 +1989,40 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>28.26</v>
+        <v>33.06</v>
       </c>
       <c r="AA10">
-        <v>-150.84</v>
+        <v>-155.54</v>
       </c>
       <c r="AB10">
-        <v>-127.5</v>
+        <v>-133.11</v>
       </c>
       <c r="AC10">
-        <v>-23.34</v>
+        <v>-22.44</v>
       </c>
       <c r="AD10">
-        <v>53.62</v>
+        <v>44</v>
       </c>
       <c r="AE10">
-        <v>51.85</v>
+        <v>52.33</v>
       </c>
       <c r="AF10">
-        <v>110.75</v>
+        <v>110.71</v>
       </c>
       <c r="AH10">
-        <v>9260.83</v>
+        <v>9243.370000000001</v>
       </c>
       <c r="AI10">
-        <v>8524.09</v>
+        <v>8487.040000000001</v>
       </c>
       <c r="AJ10">
-        <v>8911.82</v>
+        <v>8874.16</v>
       </c>
       <c r="AK10" t="s">
         <v>80</v>
       </c>
       <c r="AL10">
-        <v>60.63</v>
+        <v>61.39</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2009,10 +2036,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1534.5</v>
+        <v>1553.3</v>
       </c>
       <c r="E11">
-        <v>-2.79</v>
+        <v>1.23</v>
       </c>
       <c r="F11">
         <v>1621.4</v>
@@ -2021,43 +2048,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-5.36</v>
+        <v>-4.2</v>
       </c>
       <c r="I11">
-        <v>22.43</v>
+        <v>23.93</v>
       </c>
       <c r="J11">
-        <v>-3.08</v>
+        <v>0.45</v>
       </c>
       <c r="K11">
-        <v>0.91</v>
+        <v>0.82</v>
       </c>
       <c r="L11">
-        <v>3.49</v>
+        <v>4.65</v>
       </c>
       <c r="M11">
-        <v>-1.77</v>
+        <v>0.67</v>
       </c>
       <c r="N11">
-        <v>-7.4</v>
+        <v>-7.44</v>
       </c>
       <c r="O11">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="Q11">
-        <v>1557.5</v>
+        <v>1558.9</v>
       </c>
       <c r="R11">
-        <v>1547.88</v>
+        <v>1549.22</v>
       </c>
       <c r="S11">
-        <v>1565.7</v>
+        <v>1566.33</v>
       </c>
       <c r="T11">
-        <v>1459.33</v>
+        <v>1459.92</v>
       </c>
       <c r="U11">
-        <v>5.15</v>
+        <v>6.4</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2072,31 +2099,31 @@
         <v>2</v>
       </c>
       <c r="Z11">
-        <v>45.51</v>
+        <v>49.64</v>
       </c>
       <c r="AA11">
-        <v>0.36</v>
+        <v>0.16</v>
       </c>
       <c r="AB11">
-        <v>-0.71</v>
+        <v>-0.54</v>
       </c>
       <c r="AC11">
-        <v>1.07</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AD11">
-        <v>52.13</v>
+        <v>39.32</v>
       </c>
       <c r="AE11">
-        <v>64.2</v>
+        <v>55.57</v>
       </c>
       <c r="AF11">
-        <v>34.95</v>
+        <v>34.49</v>
       </c>
       <c r="AH11">
-        <v>1589.53</v>
+        <v>1589.68</v>
       </c>
       <c r="AI11">
-        <v>1506.23</v>
+        <v>1508.76</v>
       </c>
       <c r="AJ11">
         <v>1604.15</v>
@@ -2105,7 +2132,7 @@
         <v>80</v>
       </c>
       <c r="AL11">
-        <v>19.89</v>
+        <v>18.28</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2119,10 +2146,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>11870.05</v>
+        <v>12000.75</v>
       </c>
       <c r="E12">
-        <v>-3.55</v>
+        <v>1.1</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2131,43 +2158,43 @@
         <v>10017.9</v>
       </c>
       <c r="H12">
-        <v>-13.47</v>
+        <v>-12.52</v>
       </c>
       <c r="I12">
-        <v>18.49</v>
+        <v>19.79</v>
       </c>
       <c r="J12">
-        <v>-6.98</v>
+        <v>-3.69</v>
       </c>
       <c r="K12">
-        <v>-9.75</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="L12">
-        <v>-5.06</v>
+        <v>-5.42</v>
       </c>
       <c r="M12">
-        <v>19.62</v>
+        <v>19.55</v>
       </c>
       <c r="N12">
-        <v>15.88</v>
+        <v>15.81</v>
       </c>
       <c r="O12">
         <v>93</v>
       </c>
       <c r="Q12">
-        <v>12347.04</v>
+        <v>12255.05</v>
       </c>
       <c r="R12">
-        <v>12835.69</v>
+        <v>12766.16</v>
       </c>
       <c r="S12">
-        <v>13008.91</v>
+        <v>13000.19</v>
       </c>
       <c r="T12">
-        <v>12415.22</v>
+        <v>12422.9</v>
       </c>
       <c r="U12">
-        <v>-4.39</v>
+        <v>-3.4</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2182,40 +2209,40 @@
         <v>1</v>
       </c>
       <c r="Z12">
-        <v>29.28</v>
+        <v>33.13</v>
       </c>
       <c r="AA12">
-        <v>-209.6</v>
+        <v>-241.43</v>
       </c>
       <c r="AB12">
-        <v>-106.33</v>
+        <v>-133.35</v>
       </c>
       <c r="AC12">
-        <v>-103.27</v>
+        <v>-108.08</v>
       </c>
       <c r="AD12">
-        <v>7.28</v>
+        <v>4.71</v>
       </c>
       <c r="AE12">
-        <v>8.58</v>
+        <v>7.07</v>
       </c>
       <c r="AF12">
-        <v>255.46</v>
+        <v>252.68</v>
       </c>
       <c r="AH12">
-        <v>13568.28</v>
+        <v>13539.51</v>
       </c>
       <c r="AI12">
-        <v>12103.09</v>
+        <v>11992.8</v>
       </c>
       <c r="AJ12">
-        <v>12850.7</v>
+        <v>12689.95</v>
       </c>
       <c r="AK12" t="s">
         <v>80</v>
       </c>
       <c r="AL12">
-        <v>42.19</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2229,10 +2256,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9010.450000000001</v>
+        <v>9077.75</v>
       </c>
       <c r="E13">
-        <v>-2.4</v>
+        <v>0.75</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2241,43 +2268,43 @@
         <v>9010.450000000001</v>
       </c>
       <c r="H13">
-        <v>-16.31</v>
+        <v>-15.68</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="J13">
-        <v>-3.74</v>
+        <v>-1.42</v>
       </c>
       <c r="K13">
-        <v>-6.92</v>
+        <v>-6.51</v>
       </c>
       <c r="L13">
-        <v>-8.109999999999999</v>
+        <v>-8.41</v>
       </c>
       <c r="M13">
-        <v>-7.8</v>
+        <v>-7.38</v>
       </c>
       <c r="N13">
-        <v>16.41</v>
+        <v>16.19</v>
       </c>
       <c r="O13">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="Q13">
-        <v>9216.290000000001</v>
+        <v>9190.110000000001</v>
       </c>
       <c r="R13">
-        <v>9472.57</v>
+        <v>9439.6</v>
       </c>
       <c r="S13">
-        <v>9675.440000000001</v>
+        <v>9658.23</v>
       </c>
       <c r="T13">
-        <v>10006.43</v>
+        <v>10004.41</v>
       </c>
       <c r="U13">
-        <v>-9.949999999999999</v>
+        <v>-9.26</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2292,40 +2319,40 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>24.54</v>
+        <v>29.6</v>
       </c>
       <c r="AA13">
-        <v>-144.23</v>
+        <v>-154.09</v>
       </c>
       <c r="AB13">
-        <v>-108.62</v>
+        <v>-117.72</v>
       </c>
       <c r="AC13">
-        <v>-35.61</v>
+        <v>-36.37</v>
       </c>
       <c r="AD13">
-        <v>34.54</v>
+        <v>23.82</v>
       </c>
       <c r="AE13">
-        <v>37.02</v>
+        <v>34.3</v>
       </c>
       <c r="AF13">
-        <v>120.09</v>
+        <v>120.78</v>
       </c>
       <c r="AH13">
-        <v>9863.84</v>
+        <v>9847.75</v>
       </c>
       <c r="AI13">
-        <v>9081.299999999999</v>
+        <v>9031.450000000001</v>
       </c>
       <c r="AJ13">
-        <v>9473.25</v>
+        <v>9403.969999999999</v>
       </c>
       <c r="AK13" t="s">
         <v>80</v>
       </c>
       <c r="AL13">
-        <v>55.13</v>
+        <v>58.27</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2339,10 +2366,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>7995.95</v>
+        <v>8126.35</v>
       </c>
       <c r="E14">
-        <v>-1.15</v>
+        <v>1.63</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2351,43 +2378,43 @@
         <v>7499.2</v>
       </c>
       <c r="H14">
-        <v>-19.07</v>
+        <v>-17.75</v>
       </c>
       <c r="I14">
-        <v>6.62</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="J14">
-        <v>-0.25</v>
+        <v>2.38</v>
       </c>
       <c r="K14">
-        <v>-5.09</v>
+        <v>-3.4</v>
       </c>
       <c r="L14">
-        <v>-2.53</v>
+        <v>-3.85</v>
       </c>
       <c r="M14">
-        <v>8.19</v>
+        <v>7.97</v>
       </c>
       <c r="N14">
-        <v>25.68</v>
+        <v>25.93</v>
       </c>
       <c r="O14">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="Q14">
-        <v>8009.14</v>
+        <v>8046.85</v>
       </c>
       <c r="R14">
-        <v>8185.56</v>
+        <v>8173.42</v>
       </c>
       <c r="S14">
-        <v>8422.969999999999</v>
+        <v>8417.860000000001</v>
       </c>
       <c r="T14">
-        <v>8580.25</v>
+        <v>8579.82</v>
       </c>
       <c r="U14">
-        <v>-6.81</v>
+        <v>-5.29</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2402,31 +2429,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>37.04</v>
+        <v>45.09</v>
       </c>
       <c r="AA14">
-        <v>-124.12</v>
+        <v>-112.49</v>
       </c>
       <c r="AB14">
-        <v>-112.95</v>
+        <v>-112.86</v>
       </c>
       <c r="AC14">
-        <v>-11.17</v>
+        <v>0.37</v>
       </c>
       <c r="AD14">
-        <v>49.13</v>
+        <v>68.56</v>
       </c>
       <c r="AE14">
-        <v>41.78</v>
+        <v>55.19</v>
       </c>
       <c r="AF14">
-        <v>137.64</v>
+        <v>138.24</v>
       </c>
       <c r="AH14">
-        <v>8503.93</v>
+        <v>8480.620000000001</v>
       </c>
       <c r="AI14">
-        <v>7867.19</v>
+        <v>7866.21</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
@@ -2435,7 +2462,7 @@
         <v>80</v>
       </c>
       <c r="AL14">
-        <v>34.01</v>
+        <v>31.49</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2449,55 +2476,55 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>25823.25</v>
+        <v>25962.05</v>
       </c>
       <c r="E15">
-        <v>-2.32</v>
+        <v>0.54</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
       </c>
       <c r="G15">
-        <v>21454.25</v>
+        <v>21549.55</v>
       </c>
       <c r="H15">
-        <v>-5.01</v>
+        <v>-4.5</v>
       </c>
       <c r="I15">
-        <v>20.36</v>
+        <v>20.48</v>
       </c>
       <c r="J15">
-        <v>-2.33</v>
+        <v>-1.33</v>
       </c>
       <c r="K15">
-        <v>-3.19</v>
+        <v>-3.42</v>
       </c>
       <c r="L15">
-        <v>0.65</v>
+        <v>1.12</v>
       </c>
       <c r="M15">
-        <v>20.25</v>
+        <v>21.01</v>
       </c>
       <c r="N15">
-        <v>12.21</v>
+        <v>12.19</v>
       </c>
       <c r="O15">
         <v>99</v>
       </c>
       <c r="Q15">
-        <v>26247.61</v>
+        <v>26177.71</v>
       </c>
       <c r="R15">
-        <v>26594.5</v>
+        <v>26558.01</v>
       </c>
       <c r="S15">
-        <v>26598.39</v>
+        <v>26590.16</v>
       </c>
       <c r="T15">
-        <v>24228.75</v>
+        <v>24245.6</v>
       </c>
       <c r="U15">
-        <v>6.58</v>
+        <v>7.08</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2512,40 +2539,40 @@
         <v>2</v>
       </c>
       <c r="Z15">
-        <v>37.86</v>
+        <v>40.65</v>
       </c>
       <c r="AA15">
-        <v>-82.73999999999999</v>
+        <v>-116.32</v>
       </c>
       <c r="AB15">
-        <v>15.43</v>
+        <v>-10.92</v>
       </c>
       <c r="AC15">
-        <v>-98.17</v>
+        <v>-105.4</v>
       </c>
       <c r="AD15">
-        <v>24.61</v>
+        <v>14.68</v>
       </c>
       <c r="AE15">
-        <v>22.11</v>
+        <v>21.3</v>
       </c>
       <c r="AF15">
-        <v>381.52</v>
+        <v>381.24</v>
       </c>
       <c r="AH15">
-        <v>27311.09</v>
+        <v>27326.2</v>
       </c>
       <c r="AI15">
-        <v>25877.9</v>
+        <v>25789.82</v>
       </c>
       <c r="AJ15">
-        <v>27223.84</v>
+        <v>26990.16</v>
       </c>
       <c r="AK15" t="s">
         <v>80</v>
       </c>
       <c r="AL15">
-        <v>29.7</v>
+        <v>32.57</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2559,10 +2586,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>796.6</v>
+        <v>803.95</v>
       </c>
       <c r="E16">
-        <v>-3.16</v>
+        <v>0.92</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2571,43 +2598,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-17.76</v>
+        <v>-17</v>
       </c>
       <c r="I16">
-        <v>22.34</v>
+        <v>23.47</v>
       </c>
       <c r="J16">
-        <v>-5.99</v>
+        <v>-3.72</v>
       </c>
       <c r="K16">
-        <v>-10.75</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L16">
-        <v>-12.17</v>
+        <v>-14.35</v>
       </c>
       <c r="M16">
-        <v>-8.93</v>
+        <v>-7.34</v>
       </c>
       <c r="N16">
-        <v>8.869999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O16">
         <v>13</v>
       </c>
       <c r="Q16">
-        <v>826.27</v>
+        <v>820.0599999999999</v>
       </c>
       <c r="R16">
-        <v>844.41</v>
+        <v>841</v>
       </c>
       <c r="S16">
-        <v>878.62</v>
+        <v>876.33</v>
       </c>
       <c r="T16">
-        <v>825.97</v>
+        <v>825.62</v>
       </c>
       <c r="U16">
-        <v>-3.56</v>
+        <v>-2.62</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2622,40 +2649,40 @@
         <v>1</v>
       </c>
       <c r="Z16">
-        <v>31.18</v>
+        <v>34.35</v>
       </c>
       <c r="AA16">
-        <v>-16.29</v>
+        <v>-17.71</v>
       </c>
       <c r="AB16">
-        <v>-12.97</v>
+        <v>-13.92</v>
       </c>
       <c r="AC16">
-        <v>-3.32</v>
+        <v>-3.79</v>
       </c>
       <c r="AD16">
-        <v>27.93</v>
+        <v>13</v>
       </c>
       <c r="AE16">
-        <v>48.57</v>
+        <v>30.89</v>
       </c>
       <c r="AF16">
-        <v>18.29</v>
+        <v>17.96</v>
       </c>
       <c r="AH16">
-        <v>885.8</v>
+        <v>883.97</v>
       </c>
       <c r="AI16">
-        <v>803.03</v>
+        <v>798.04</v>
       </c>
       <c r="AJ16">
-        <v>864.46</v>
+        <v>855.3200000000001</v>
       </c>
       <c r="AK16" t="s">
         <v>80</v>
       </c>
       <c r="AL16">
-        <v>34.9</v>
+        <v>39.11</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2669,10 +2696,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>28623.75</v>
+        <v>29090.7</v>
       </c>
       <c r="E17">
-        <v>-1.5</v>
+        <v>1.63</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2681,43 +2708,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-16.06</v>
+        <v>-14.69</v>
       </c>
       <c r="I17">
-        <v>0.92</v>
+        <v>2.56</v>
       </c>
       <c r="J17">
-        <v>-1.34</v>
+        <v>0.46</v>
       </c>
       <c r="K17">
-        <v>-5.91</v>
+        <v>-3.63</v>
       </c>
       <c r="L17">
-        <v>-7.25</v>
+        <v>-6.67</v>
       </c>
       <c r="M17">
-        <v>-10.25</v>
+        <v>-8.67</v>
       </c>
       <c r="N17">
-        <v>2.84</v>
+        <v>3.17</v>
       </c>
       <c r="O17">
         <v>38</v>
       </c>
       <c r="Q17">
-        <v>28990.1</v>
+        <v>29016.66</v>
       </c>
       <c r="R17">
-        <v>29536.42</v>
+        <v>29500.11</v>
       </c>
       <c r="S17">
-        <v>30415.12</v>
+        <v>30368.14</v>
       </c>
       <c r="T17">
-        <v>31165.65</v>
+        <v>31143.5</v>
       </c>
       <c r="U17">
-        <v>-8.16</v>
+        <v>-6.59</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2732,31 +2759,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>25.44</v>
+        <v>38.5</v>
       </c>
       <c r="AA17">
-        <v>-432.51</v>
+        <v>-412.9</v>
       </c>
       <c r="AB17">
-        <v>-385.41</v>
+        <v>-390.9</v>
       </c>
       <c r="AC17">
-        <v>-47.11</v>
+        <v>-21.99</v>
       </c>
       <c r="AD17">
-        <v>38.32</v>
+        <v>47.11</v>
       </c>
       <c r="AE17">
-        <v>37.06</v>
+        <v>43.06</v>
       </c>
       <c r="AF17">
-        <v>319.23</v>
+        <v>335.84</v>
       </c>
       <c r="AH17">
-        <v>30441.72</v>
+        <v>30416.23</v>
       </c>
       <c r="AI17">
-        <v>28631.13</v>
+        <v>28583.99</v>
       </c>
       <c r="AJ17">
         <v>29780.35</v>
@@ -2765,7 +2792,7 @@
         <v>80</v>
       </c>
       <c r="AL17">
-        <v>49.62</v>
+        <v>50.84</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2779,10 +2806,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>15684.65</v>
+        <v>15855.55</v>
       </c>
       <c r="E18">
-        <v>-2.33</v>
+        <v>1.09</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2791,31 +2818,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-7.42</v>
+        <v>-6.41</v>
       </c>
       <c r="I18">
-        <v>1.83</v>
+        <v>2.94</v>
       </c>
       <c r="J18">
-        <v>-2.81</v>
+        <v>-1.49</v>
       </c>
       <c r="K18">
-        <v>-5.06</v>
+        <v>-4.63</v>
       </c>
       <c r="L18">
-        <v>-3.82</v>
+        <v>-2.95</v>
       </c>
       <c r="N18">
-        <v>2.67</v>
+        <v>6.12</v>
       </c>
       <c r="Q18">
-        <v>15975.06</v>
+        <v>15927.06</v>
       </c>
       <c r="R18">
-        <v>16412.11</v>
+        <v>16375.83</v>
       </c>
       <c r="S18">
-        <v>16536.5</v>
+        <v>16519.69</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2827,40 +2854,40 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>30.5</v>
+        <v>36.62</v>
       </c>
       <c r="AA18">
-        <v>-160.56</v>
+        <v>-176.89</v>
       </c>
       <c r="AB18">
-        <v>-71.06999999999999</v>
+        <v>-92.23</v>
       </c>
       <c r="AC18">
-        <v>-89.48999999999999</v>
+        <v>-84.66</v>
       </c>
       <c r="AD18">
-        <v>14.19</v>
+        <v>13.27</v>
       </c>
       <c r="AE18">
-        <v>12.02</v>
+        <v>13.88</v>
       </c>
       <c r="AF18">
-        <v>222.85</v>
+        <v>224.12</v>
       </c>
       <c r="AH18">
-        <v>17055.37</v>
+        <v>17059.53</v>
       </c>
       <c r="AI18">
-        <v>15768.85</v>
+        <v>15692.14</v>
       </c>
       <c r="AJ18">
-        <v>16531.89</v>
+        <v>16454.47</v>
       </c>
       <c r="AK18" t="s">
         <v>80</v>
       </c>
       <c r="AL18">
-        <v>43.27</v>
+        <v>47.08</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2874,10 +2901,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>8961.25</v>
+        <v>9006.65</v>
       </c>
       <c r="E19">
-        <v>-2.76</v>
+        <v>0.51</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2886,31 +2913,31 @@
         <v>8961.25</v>
       </c>
       <c r="H19">
-        <v>-10.38</v>
+        <v>-9.92</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="J19">
-        <v>-3.4</v>
+        <v>-1.49</v>
       </c>
       <c r="K19">
-        <v>-8.130000000000001</v>
+        <v>-9.92</v>
       </c>
       <c r="L19">
-        <v>-3.74</v>
+        <v>-5.05</v>
       </c>
       <c r="N19">
-        <v>-1.17</v>
+        <v>0.39</v>
       </c>
       <c r="Q19">
-        <v>9169.379999999999</v>
+        <v>9142.200000000001</v>
       </c>
       <c r="R19">
-        <v>9345.809999999999</v>
+        <v>9301.530000000001</v>
       </c>
       <c r="S19">
-        <v>9539.51</v>
+        <v>9535.219999999999</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2922,40 +2949,40 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>35.91</v>
+        <v>37.82</v>
       </c>
       <c r="AA19">
-        <v>-124.99</v>
+        <v>-134.86</v>
       </c>
       <c r="AB19">
-        <v>-101.5</v>
+        <v>-108.17</v>
       </c>
       <c r="AC19">
-        <v>-23.49</v>
+        <v>-26.69</v>
       </c>
       <c r="AD19">
-        <v>54.36</v>
+        <v>27.1</v>
       </c>
       <c r="AE19">
-        <v>64.18000000000001</v>
+        <v>51.62</v>
       </c>
       <c r="AF19">
-        <v>176.97</v>
+        <v>176.59</v>
       </c>
       <c r="AH19">
-        <v>9820.07</v>
+        <v>9723.51</v>
       </c>
       <c r="AI19">
-        <v>8871.540000000001</v>
+        <v>8879.559999999999</v>
       </c>
       <c r="AJ19">
-        <v>9603</v>
+        <v>9494.469999999999</v>
       </c>
       <c r="AK19" t="s">
         <v>80</v>
       </c>
       <c r="AL19">
-        <v>33.86</v>
+        <v>36.24</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2969,43 +2996,43 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10354.65</v>
+        <v>10345.3</v>
       </c>
       <c r="E20">
-        <v>-2.52</v>
+        <v>-0.09</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
       </c>
       <c r="G20">
-        <v>10354.65</v>
+        <v>10345.3</v>
       </c>
       <c r="H20">
-        <v>-8.92</v>
+        <v>-9</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>-2.45</v>
+        <v>-1.24</v>
       </c>
       <c r="K20">
-        <v>-6.87</v>
+        <v>-6.33</v>
       </c>
       <c r="L20">
-        <v>-6.15</v>
+        <v>-7.44</v>
       </c>
       <c r="N20">
-        <v>-17.35</v>
+        <v>-17.45</v>
       </c>
       <c r="Q20">
-        <v>10527.98</v>
+        <v>10502.07</v>
       </c>
       <c r="R20">
-        <v>10782.79</v>
+        <v>10748.61</v>
       </c>
       <c r="S20">
-        <v>11028.46</v>
+        <v>11013.84</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3017,40 +3044,40 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>29.75</v>
+        <v>29.51</v>
       </c>
       <c r="AA20">
-        <v>-155.07</v>
+        <v>-167.88</v>
       </c>
       <c r="AB20">
-        <v>-124.78</v>
+        <v>-133.4</v>
       </c>
       <c r="AC20">
-        <v>-30.29</v>
+        <v>-34.48</v>
       </c>
       <c r="AD20">
-        <v>48.16</v>
+        <v>30.68</v>
       </c>
       <c r="AE20">
-        <v>41.89</v>
+        <v>42.25</v>
       </c>
       <c r="AF20">
-        <v>149.92</v>
+        <v>147.07</v>
       </c>
       <c r="AH20">
-        <v>11195.62</v>
+        <v>11187.97</v>
       </c>
       <c r="AI20">
-        <v>10369.96</v>
+        <v>10309.24</v>
       </c>
       <c r="AJ20">
-        <v>10902.64</v>
+        <v>10782.9</v>
       </c>
       <c r="AK20" t="s">
         <v>80</v>
       </c>
       <c r="AL20">
-        <v>50.67</v>
+        <v>52.85</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3064,10 +3091,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>26869.1</v>
+        <v>27222.55</v>
       </c>
       <c r="E21">
-        <v>-0.91</v>
+        <v>1.32</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3076,43 +3103,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-7.94</v>
+        <v>-6.73</v>
       </c>
       <c r="I21">
-        <v>11.28</v>
+        <v>12.75</v>
       </c>
       <c r="J21">
-        <v>0.65</v>
+        <v>1.97</v>
       </c>
       <c r="K21">
-        <v>-3.16</v>
+        <v>-0.92</v>
       </c>
       <c r="L21">
-        <v>-3.22</v>
+        <v>-3.07</v>
       </c>
       <c r="M21">
-        <v>1.73</v>
+        <v>2.87</v>
       </c>
       <c r="N21">
-        <v>6.34</v>
+        <v>6.42</v>
       </c>
       <c r="O21">
         <v>74</v>
       </c>
       <c r="Q21">
-        <v>26898.83</v>
+        <v>27003.89</v>
       </c>
       <c r="R21">
-        <v>27027.27</v>
+        <v>27027.68</v>
       </c>
       <c r="S21">
-        <v>27373.1</v>
+        <v>27347.38</v>
       </c>
       <c r="T21">
-        <v>27465.7</v>
+        <v>27459.49</v>
       </c>
       <c r="U21">
-        <v>-2.17</v>
+        <v>-0.86</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3127,31 +3154,31 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>44.32</v>
+        <v>52.02</v>
       </c>
       <c r="AA21">
-        <v>-174.4</v>
+        <v>-138.45</v>
       </c>
       <c r="AB21">
-        <v>-194.71</v>
+        <v>-183.46</v>
       </c>
       <c r="AC21">
-        <v>20.31</v>
+        <v>45.01</v>
       </c>
       <c r="AD21">
         <v>89.95</v>
       </c>
       <c r="AE21">
-        <v>79.36</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="AF21">
-        <v>358.08</v>
+        <v>365.61</v>
       </c>
       <c r="AH21">
-        <v>27646.37</v>
+        <v>27647.32</v>
       </c>
       <c r="AI21">
-        <v>26408.16</v>
+        <v>26408.04</v>
       </c>
       <c r="AJ21">
         <v>27249.36</v>
@@ -3160,7 +3187,7 @@
         <v>80</v>
       </c>
       <c r="AL21">
-        <v>21.21</v>
+        <v>21.17</v>
       </c>
     </row>
   </sheetData>
@@ -3301,7 +3328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3341,7 +3368,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>87</v>
@@ -3361,10 +3388,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>92</v>
@@ -3376,2076 +3403,2082 @@
         <v>93</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>89</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>79</v>
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-9.279999999999999</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-11.5</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-7.11</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-8.77</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.66</v>
+      <c r="B10" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.35</v>
+        <v>-11.5</v>
       </c>
       <c r="D11" s="6">
-        <v>-7.09</v>
+        <v>-10.5</v>
       </c>
       <c r="E11" s="7">
-        <v>-1.74</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-3.64</v>
+        <v>-8.77</v>
       </c>
       <c r="D12" s="6">
-        <v>-6.12</v>
+        <v>-7.78</v>
       </c>
       <c r="E12" s="7">
-        <v>-2.48</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.38</v>
+        <v>-7.09</v>
       </c>
       <c r="D13" s="6">
-        <v>-3.72</v>
+        <v>-5.76</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.34</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-4.36</v>
+        <v>-6.12</v>
       </c>
       <c r="D14" s="6">
-        <v>-4.99</v>
+        <v>-6.06</v>
       </c>
       <c r="E14" s="7">
-        <v>-0.63</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-9.57</v>
+        <v>-3.72</v>
       </c>
       <c r="D15" s="6">
-        <v>-7.53</v>
-      </c>
-      <c r="E15" s="8">
-        <v>2.04</v>
+        <v>-1.94</v>
+      </c>
+      <c r="E15" s="7">
+        <v>1.78</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-6.03</v>
+        <v>-4.99</v>
       </c>
       <c r="D16" s="6">
-        <v>-8.289999999999999</v>
+        <v>-2.83</v>
       </c>
       <c r="E16" s="7">
-        <v>-2.26</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.1</v>
+        <v>-7.53</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.46</v>
+        <v>-4.38</v>
       </c>
       <c r="E17" s="7">
-        <v>-2.36</v>
+        <v>3.15</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>0.83</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="D18" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.08</v>
+        <v>-7.97</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-7.59</v>
+        <v>-7.46</v>
       </c>
       <c r="D19" s="6">
-        <v>-9.75</v>
+        <v>-6.23</v>
       </c>
       <c r="E19" s="7">
-        <v>-2.16</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-4.92</v>
+        <v>0.91</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.92</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-2</v>
+        <v>0.82</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-5</v>
+        <v>-9.75</v>
       </c>
       <c r="D21" s="6">
-        <v>-5.09</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.09</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-0.16</v>
+        <v>-6.92</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.19</v>
+        <v>-6.51</v>
       </c>
       <c r="E22" s="7">
-        <v>-3.03</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-9.4</v>
+        <v>-5.09</v>
       </c>
       <c r="D23" s="6">
-        <v>-10.75</v>
+        <v>-3.4</v>
       </c>
       <c r="E23" s="7">
-        <v>-1.35</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-4.96</v>
+        <v>-3.19</v>
       </c>
       <c r="D24" s="6">
-        <v>-5.91</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.95</v>
+        <v>-3.42</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-2.13</v>
+        <v>-10.75</v>
       </c>
       <c r="D25" s="6">
-        <v>-5.06</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="E25" s="7">
-        <v>-2.93</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-5.08</v>
+        <v>-5.91</v>
       </c>
       <c r="D26" s="6">
-        <v>-8.130000000000001</v>
+        <v>-3.63</v>
       </c>
       <c r="E26" s="7">
-        <v>-3.05</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-5.05</v>
+        <v>-5.06</v>
       </c>
       <c r="D27" s="6">
-        <v>-6.87</v>
+        <v>-4.63</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.82</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-2.55</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.16</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-0.61</v>
+        <v>-9.92</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-1.79</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-3.95</v>
+        <v>-6.87</v>
       </c>
       <c r="D29" s="6">
-        <v>-6.77</v>
+        <v>-6.33</v>
       </c>
       <c r="E29" s="7">
-        <v>-2.82</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-2.36</v>
+        <v>-3.16</v>
       </c>
       <c r="D30" s="6">
-        <v>-4.93</v>
+        <v>-0.92</v>
       </c>
       <c r="E30" s="7">
-        <v>-2.57</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-1.61</v>
+        <v>-6.77</v>
       </c>
       <c r="D31" s="6">
-        <v>-2.99</v>
+        <v>-2.07</v>
       </c>
       <c r="E31" s="7">
-        <v>-1.38</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>0.48</v>
+        <v>-4.93</v>
       </c>
       <c r="D32" s="6">
-        <v>-2.69</v>
+        <v>-2.27</v>
       </c>
       <c r="E32" s="7">
-        <v>-3.17</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>0.02</v>
+        <v>-2.99</v>
       </c>
       <c r="D33" s="6">
-        <v>-1.37</v>
+        <v>0.37</v>
       </c>
       <c r="E33" s="7">
-        <v>-1.39</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>1.09</v>
+        <v>-2.69</v>
       </c>
       <c r="D34" s="6">
-        <v>-0.04</v>
+        <v>-1.65</v>
       </c>
       <c r="E34" s="7">
-        <v>-1.13</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>0.32</v>
+        <v>-1.37</v>
       </c>
       <c r="D35" s="6">
-        <v>0.11</v>
+        <v>2.45</v>
       </c>
       <c r="E35" s="7">
-        <v>-0.21</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.72</v>
+        <v>-0.04</v>
       </c>
       <c r="D36" s="6">
-        <v>-3.94</v>
+        <v>1.68</v>
       </c>
       <c r="E36" s="7">
-        <v>-2.22</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-0.11</v>
+        <v>0.11</v>
       </c>
       <c r="D37" s="6">
-        <v>-2.64</v>
+        <v>0.95</v>
       </c>
       <c r="E37" s="7">
-        <v>-2.53</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>2.44</v>
+        <v>-3.94</v>
       </c>
       <c r="D38" s="6">
-        <v>-3.08</v>
+        <v>-1.6</v>
       </c>
       <c r="E38" s="7">
-        <v>-5.52</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>-5</v>
+        <v>-2.64</v>
       </c>
       <c r="D39" s="6">
-        <v>-6.98</v>
+        <v>-0.36</v>
       </c>
       <c r="E39" s="7">
-        <v>-1.98</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-1.19</v>
+        <v>-3.08</v>
       </c>
       <c r="D40" s="6">
-        <v>-3.74</v>
+        <v>0.45</v>
       </c>
       <c r="E40" s="7">
-        <v>-2.55</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>1.45</v>
+        <v>-6.98</v>
       </c>
       <c r="D41" s="6">
-        <v>-0.25</v>
+        <v>-3.69</v>
       </c>
       <c r="E41" s="7">
-        <v>-1.7</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>-1.85</v>
+        <v>-3.74</v>
       </c>
       <c r="D42" s="6">
-        <v>-2.33</v>
+        <v>-1.42</v>
       </c>
       <c r="E42" s="7">
-        <v>-0.48</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-1.35</v>
+        <v>-0.25</v>
       </c>
       <c r="D43" s="6">
-        <v>-5.99</v>
+        <v>2.38</v>
       </c>
       <c r="E43" s="7">
-        <v>-4.64</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>-0.34</v>
+        <v>-2.33</v>
       </c>
       <c r="D44" s="6">
-        <v>-1.34</v>
+        <v>-1.33</v>
       </c>
       <c r="E44" s="7">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>-3.04</v>
+        <v>-5.99</v>
       </c>
       <c r="D45" s="6">
-        <v>-2.81</v>
-      </c>
-      <c r="E45" s="8">
-        <v>0.23</v>
+        <v>-3.72</v>
+      </c>
+      <c r="E45" s="7">
+        <v>2.27</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>0.83</v>
+        <v>-1.34</v>
       </c>
       <c r="D46" s="6">
-        <v>-3.4</v>
+        <v>0.46</v>
       </c>
       <c r="E46" s="7">
-        <v>-4.23</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>0.52</v>
+        <v>-2.81</v>
       </c>
       <c r="D47" s="6">
-        <v>-2.45</v>
+        <v>-1.49</v>
       </c>
       <c r="E47" s="7">
-        <v>-2.97</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="6">
-        <v>2.54</v>
+        <v>-3.4</v>
       </c>
       <c r="D48" s="6">
-        <v>0.65</v>
+        <v>-1.49</v>
       </c>
       <c r="E48" s="7">
-        <v>-1.89</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C49" s="6">
-        <v>-5.08</v>
+        <v>-2.45</v>
       </c>
       <c r="D49" s="6">
-        <v>-7.28</v>
+        <v>-1.24</v>
       </c>
       <c r="E49" s="7">
-        <v>-2.2</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" s="6">
-        <v>2.44</v>
+        <v>0.65</v>
       </c>
       <c r="D50" s="6">
-        <v>-1.12</v>
+        <v>1.97</v>
       </c>
       <c r="E50" s="7">
-        <v>-3.56</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>-9.130000000000001</v>
+        <v>-7.28</v>
       </c>
       <c r="D51" s="6">
-        <v>-11.29</v>
+        <v>-6.34</v>
       </c>
       <c r="E51" s="7">
-        <v>-2.16</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>5.32</v>
+        <v>-1.12</v>
       </c>
       <c r="D52" s="6">
-        <v>1.65</v>
+        <v>-0.7</v>
       </c>
       <c r="E52" s="7">
-        <v>-3.67</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-18.32</v>
+        <v>-11.29</v>
       </c>
       <c r="D53" s="6">
-        <v>-20.11</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="E53" s="7">
-        <v>-1.79</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-4.11</v>
+        <v>1.65</v>
       </c>
       <c r="D54" s="6">
-        <v>-5.25</v>
+        <v>2.25</v>
       </c>
       <c r="E54" s="7">
-        <v>-1.14</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-17.64</v>
+        <v>-20.11</v>
       </c>
       <c r="D55" s="6">
-        <v>-17.68</v>
+        <v>-18</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.04</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-3.44</v>
+        <v>-5.25</v>
       </c>
       <c r="D56" s="6">
-        <v>-6.06</v>
+        <v>-4.05</v>
       </c>
       <c r="E56" s="7">
-        <v>-2.62</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>0.19</v>
+        <v>-17.68</v>
       </c>
       <c r="D57" s="6">
-        <v>-1.77</v>
+        <v>-15.09</v>
       </c>
       <c r="E57" s="7">
-        <v>-1.96</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>24.46</v>
+        <v>-6.06</v>
       </c>
       <c r="D58" s="6">
-        <v>19.62</v>
+        <v>-4.8</v>
       </c>
       <c r="E58" s="7">
-        <v>-4.84</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>-4.42</v>
+        <v>-1.77</v>
       </c>
       <c r="D59" s="6">
-        <v>-7.8</v>
+        <v>0.67</v>
       </c>
       <c r="E59" s="7">
-        <v>-3.38</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>11.39</v>
+        <v>19.62</v>
       </c>
       <c r="D60" s="6">
-        <v>8.19</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-3.2</v>
+        <v>19.55</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>22.92</v>
+        <v>-7.8</v>
       </c>
       <c r="D61" s="6">
-        <v>20.25</v>
+        <v>-7.38</v>
       </c>
       <c r="E61" s="7">
-        <v>-2.67</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>-5.14</v>
+        <v>8.19</v>
       </c>
       <c r="D62" s="6">
-        <v>-8.93</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-3.79</v>
+        <v>7.97</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>-8.859999999999999</v>
+        <v>20.25</v>
       </c>
       <c r="D63" s="6">
-        <v>-10.25</v>
+        <v>21.01</v>
       </c>
       <c r="E63" s="7">
-        <v>-1.39</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="6">
-        <v>2.37</v>
+        <v>-8.93</v>
       </c>
       <c r="D64" s="6">
-        <v>1.73</v>
+        <v>-7.34</v>
       </c>
       <c r="E64" s="7">
-        <v>-0.64</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" s="6">
-        <v>-5.96</v>
+        <v>-10.25</v>
       </c>
       <c r="D65" s="6">
-        <v>-8.109999999999999</v>
+        <v>-8.67</v>
       </c>
       <c r="E65" s="7">
-        <v>-2.15</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="6">
-        <v>-6.7</v>
+        <v>1.73</v>
       </c>
       <c r="D66" s="6">
-        <v>-9.44</v>
+        <v>2.87</v>
       </c>
       <c r="E66" s="7">
-        <v>-2.74</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-5.61</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="D67" s="6">
-        <v>-8.199999999999999</v>
+        <v>-7.45</v>
       </c>
       <c r="E67" s="7">
-        <v>-2.59</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-5.2</v>
+        <v>-9.44</v>
       </c>
       <c r="D68" s="6">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="E68" s="7">
-        <v>-3.01</v>
+        <v>-9.789999999999999</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-8.529999999999999</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="D69" s="6">
-        <v>-11.05</v>
+        <v>-7.11</v>
       </c>
       <c r="E69" s="7">
-        <v>-2.52</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-5.35</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="D70" s="6">
-        <v>-6.96</v>
-      </c>
-      <c r="E70" s="7">
-        <v>-1.61</v>
+        <v>-8.81</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>0.74</v>
+        <v>-11.05</v>
       </c>
       <c r="D71" s="6">
-        <v>0.97</v>
-      </c>
-      <c r="E71" s="8">
-        <v>0.23</v>
+        <v>-9.02</v>
+      </c>
+      <c r="E71" s="7">
+        <v>2.03</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-3.16</v>
+        <v>-6.96</v>
       </c>
       <c r="D72" s="6">
-        <v>-6</v>
+        <v>-6.94</v>
       </c>
       <c r="E72" s="7">
-        <v>-2.84</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>-5.64</v>
+        <v>0.97</v>
       </c>
       <c r="D73" s="6">
-        <v>-8.82</v>
+        <v>2.02</v>
       </c>
       <c r="E73" s="7">
-        <v>-3.18</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>8.68</v>
+        <v>-6</v>
       </c>
       <c r="D74" s="6">
-        <v>3.49</v>
-      </c>
-      <c r="E74" s="7">
-        <v>-5.19</v>
+        <v>-6.19</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-1.3</v>
+        <v>-8.82</v>
       </c>
       <c r="D75" s="6">
-        <v>-5.06</v>
-      </c>
-      <c r="E75" s="7">
-        <v>-3.76</v>
+        <v>-9.07</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-5.83</v>
+        <v>3.49</v>
       </c>
       <c r="D76" s="6">
-        <v>-8.109999999999999</v>
+        <v>4.65</v>
       </c>
       <c r="E76" s="7">
-        <v>-2.28</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>0.2</v>
+        <v>-5.06</v>
       </c>
       <c r="D77" s="6">
-        <v>-2.53</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-2.73</v>
+        <v>-5.42</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>3.96</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="D78" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-3.31</v>
+        <v>-8.41</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-6.09</v>
+        <v>-2.53</v>
       </c>
       <c r="D79" s="6">
-        <v>-12.17</v>
-      </c>
-      <c r="E79" s="7">
-        <v>-6.08</v>
+        <v>-3.85</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-1.32</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-5.28</v>
+        <v>0.65</v>
       </c>
       <c r="D80" s="6">
-        <v>-7.25</v>
+        <v>1.12</v>
       </c>
       <c r="E80" s="7">
-        <v>-1.97</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-0.54</v>
+        <v>-12.17</v>
       </c>
       <c r="D81" s="6">
-        <v>-3.82</v>
-      </c>
-      <c r="E81" s="7">
-        <v>-3.28</v>
+        <v>-14.35</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-2.18</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-1.17</v>
+        <v>-7.25</v>
       </c>
       <c r="D82" s="6">
-        <v>-3.74</v>
+        <v>-6.67</v>
       </c>
       <c r="E82" s="7">
-        <v>-2.57</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-3.42</v>
+        <v>-3.82</v>
       </c>
       <c r="D83" s="6">
-        <v>-6.15</v>
+        <v>-2.95</v>
       </c>
       <c r="E83" s="7">
-        <v>-2.73</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="6">
-        <v>-1.72</v>
+        <v>-3.74</v>
       </c>
       <c r="D84" s="6">
-        <v>-3.22</v>
-      </c>
-      <c r="E84" s="7">
-        <v>-1.5</v>
+        <v>-5.05</v>
+      </c>
+      <c r="E84" s="8">
+        <v>-1.31</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C85" s="6">
-        <v>-15.21</v>
+        <v>-6.15</v>
       </c>
       <c r="D85" s="6">
-        <v>-17.32</v>
-      </c>
-      <c r="E85" s="7">
-        <v>-2.11</v>
+        <v>-7.44</v>
+      </c>
+      <c r="E85" s="8">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C86" s="6">
-        <v>-13.29</v>
+        <v>-3.22</v>
       </c>
       <c r="D86" s="6">
-        <v>-15.73</v>
+        <v>-3.07</v>
       </c>
       <c r="E86" s="7">
-        <v>-2.44</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-13.15</v>
+        <v>-17.32</v>
       </c>
       <c r="D87" s="6">
-        <v>-15.02</v>
+        <v>-16.15</v>
       </c>
       <c r="E87" s="7">
-        <v>-1.87</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-11.68</v>
+        <v>-15.73</v>
       </c>
       <c r="D88" s="6">
-        <v>-14.17</v>
+        <v>-15.04</v>
       </c>
       <c r="E88" s="7">
-        <v>-2.49</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-21.09</v>
+        <v>-15.02</v>
       </c>
       <c r="D89" s="6">
-        <v>-22.68</v>
+        <v>-13.73</v>
       </c>
       <c r="E89" s="7">
-        <v>-1.59</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-12.46</v>
+        <v>-14.17</v>
       </c>
       <c r="D90" s="6">
-        <v>-13.43</v>
+        <v>-13.84</v>
       </c>
       <c r="E90" s="7">
-        <v>-0.97</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-29.71</v>
+        <v>-22.68</v>
       </c>
       <c r="D91" s="6">
-        <v>-29.76</v>
+        <v>-20.98</v>
       </c>
       <c r="E91" s="7">
-        <v>-0.05</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-8.52</v>
+        <v>-13.43</v>
       </c>
       <c r="D92" s="6">
-        <v>-10.91</v>
+        <v>-12.28</v>
       </c>
       <c r="E92" s="7">
-        <v>-2.39</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-10.62</v>
+        <v>-29.76</v>
       </c>
       <c r="D93" s="6">
-        <v>-12.92</v>
+        <v>-27.64</v>
       </c>
       <c r="E93" s="7">
-        <v>-2.3</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-2.65</v>
+        <v>-10.91</v>
       </c>
       <c r="D94" s="6">
-        <v>-5.36</v>
+        <v>-10.26</v>
       </c>
       <c r="E94" s="7">
-        <v>-2.71</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-10.29</v>
+        <v>-12.92</v>
       </c>
       <c r="D95" s="6">
-        <v>-13.47</v>
+        <v>-12.2</v>
       </c>
       <c r="E95" s="7">
-        <v>-3.18</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-14.25</v>
+        <v>-5.36</v>
       </c>
       <c r="D96" s="6">
-        <v>-16.31</v>
+        <v>-4.2</v>
       </c>
       <c r="E96" s="7">
-        <v>-2.06</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-18.13</v>
+        <v>-13.47</v>
       </c>
       <c r="D97" s="6">
-        <v>-19.07</v>
+        <v>-12.52</v>
       </c>
       <c r="E97" s="7">
-        <v>-0.9399999999999999</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-2.76</v>
+        <v>-16.31</v>
       </c>
       <c r="D98" s="6">
-        <v>-5.01</v>
+        <v>-15.68</v>
       </c>
       <c r="E98" s="7">
-        <v>-2.25</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-15.08</v>
+        <v>-19.07</v>
       </c>
       <c r="D99" s="6">
-        <v>-17.76</v>
+        <v>-17.75</v>
       </c>
       <c r="E99" s="7">
-        <v>-2.68</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-14.79</v>
+        <v>-5.01</v>
       </c>
       <c r="D100" s="6">
-        <v>-16.06</v>
+        <v>-4.5</v>
       </c>
       <c r="E100" s="7">
-        <v>-1.27</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-5.21</v>
+        <v>-17.76</v>
       </c>
       <c r="D101" s="6">
-        <v>-7.42</v>
+        <v>-17</v>
       </c>
       <c r="E101" s="7">
-        <v>-2.21</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-7.83</v>
+        <v>-16.06</v>
       </c>
       <c r="D102" s="6">
-        <v>-10.38</v>
+        <v>-14.69</v>
       </c>
       <c r="E102" s="7">
-        <v>-2.55</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="6">
-        <v>-6.56</v>
+        <v>-7.42</v>
       </c>
       <c r="D103" s="6">
-        <v>-8.92</v>
+        <v>-6.41</v>
       </c>
       <c r="E103" s="7">
-        <v>-2.36</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="6">
-        <v>-7.1</v>
+        <v>-10.38</v>
       </c>
       <c r="D104" s="6">
-        <v>-7.94</v>
+        <v>-9.92</v>
       </c>
       <c r="E104" s="7">
-        <v>-0.84</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C105" s="6">
-        <v>25138.9</v>
+        <v>-8.92</v>
       </c>
       <c r="D105" s="6">
-        <v>24512.7</v>
-      </c>
-      <c r="E105" s="7">
-        <v>-626.2</v>
+        <v>-9</v>
+      </c>
+      <c r="E105" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C106" s="6">
-        <v>9107.25</v>
+        <v>-7.94</v>
       </c>
       <c r="D106" s="6">
-        <v>8851.4</v>
+        <v>-6.73</v>
       </c>
       <c r="E106" s="7">
-        <v>-255.85</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>10976.65</v>
+        <v>24512.7</v>
       </c>
       <c r="D107" s="6">
-        <v>10741.2</v>
+        <v>24859.9</v>
       </c>
       <c r="E107" s="7">
-        <v>-235.45</v>
+        <v>347.2</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>36683.45</v>
+        <v>8851.4</v>
       </c>
       <c r="D108" s="6">
-        <v>35649.3</v>
+        <v>8923.4</v>
       </c>
       <c r="E108" s="7">
-        <v>-1034.15</v>
+        <v>72</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>44800.85</v>
+        <v>10741.2</v>
       </c>
       <c r="D109" s="6">
-        <v>43898.05</v>
+        <v>10903.45</v>
       </c>
       <c r="E109" s="7">
-        <v>-902.8</v>
+        <v>162.25</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>24916.4</v>
+        <v>35649.3</v>
       </c>
       <c r="D110" s="6">
-        <v>24640.45</v>
+        <v>35786.5</v>
       </c>
       <c r="E110" s="7">
-        <v>-275.95</v>
+        <v>137.2</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>27757.8</v>
+        <v>43898.05</v>
       </c>
       <c r="D111" s="6">
-        <v>27736.6</v>
+        <v>44864.25</v>
       </c>
       <c r="E111" s="7">
-        <v>-21.2</v>
+        <v>966.2</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>15243.3</v>
+        <v>24640.45</v>
       </c>
       <c r="D112" s="6">
-        <v>14845.15</v>
+        <v>24968.5</v>
       </c>
       <c r="E112" s="7">
-        <v>-398.15</v>
+        <v>328.05</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>8728.5</v>
+        <v>27736.6</v>
       </c>
       <c r="D113" s="6">
-        <v>8503.6</v>
+        <v>28574.9</v>
       </c>
       <c r="E113" s="7">
-        <v>-224.9</v>
+        <v>838.3</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>1578.5</v>
+        <v>14845.15</v>
       </c>
       <c r="D114" s="6">
-        <v>1534.5</v>
+        <v>14953.05</v>
       </c>
       <c r="E114" s="7">
-        <v>-44</v>
+        <v>107.9</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>12306.7</v>
+        <v>8503.6</v>
       </c>
       <c r="D115" s="6">
-        <v>11870.05</v>
+        <v>8574.450000000001</v>
       </c>
       <c r="E115" s="7">
-        <v>-436.65</v>
+        <v>70.84999999999999</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>9232.35</v>
+        <v>1534.5</v>
       </c>
       <c r="D116" s="6">
-        <v>9010.450000000001</v>
+        <v>1553.3</v>
       </c>
       <c r="E116" s="7">
-        <v>-221.9</v>
+        <v>18.8</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>8088.7</v>
+        <v>11870.05</v>
       </c>
       <c r="D117" s="6">
-        <v>7995.95</v>
+        <v>12000.75</v>
       </c>
       <c r="E117" s="7">
-        <v>-92.75</v>
+        <v>130.7</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>26436.55</v>
+        <v>9010.450000000001</v>
       </c>
       <c r="D118" s="6">
-        <v>25823.25</v>
+        <v>9077.75</v>
       </c>
       <c r="E118" s="7">
-        <v>-613.3</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>822.6</v>
+        <v>7995.95</v>
       </c>
       <c r="D119" s="6">
-        <v>796.6</v>
+        <v>8126.35</v>
       </c>
       <c r="E119" s="7">
-        <v>-26</v>
+        <v>130.4</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>29059</v>
+        <v>25823.25</v>
       </c>
       <c r="D120" s="6">
-        <v>28623.75</v>
+        <v>25962.05</v>
       </c>
       <c r="E120" s="7">
-        <v>-435.25</v>
+        <v>138.8</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>16059.15</v>
+        <v>796.6</v>
       </c>
       <c r="D121" s="6">
-        <v>15684.65</v>
+        <v>803.95</v>
       </c>
       <c r="E121" s="7">
-        <v>-374.5</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>9215.35</v>
+        <v>28623.75</v>
       </c>
       <c r="D122" s="6">
-        <v>8961.25</v>
+        <v>29090.7</v>
       </c>
       <c r="E122" s="7">
-        <v>-254.1</v>
+        <v>466.95</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="6">
-        <v>10622.8</v>
+        <v>15684.65</v>
       </c>
       <c r="D123" s="6">
-        <v>10354.65</v>
+        <v>15855.55</v>
       </c>
       <c r="E123" s="7">
-        <v>-268.15</v>
+        <v>170.9</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C124" s="6">
-        <v>27115.9</v>
+        <v>8961.25</v>
       </c>
       <c r="D124" s="6">
-        <v>26869.1</v>
+        <v>9006.65</v>
       </c>
       <c r="E124" s="7">
-        <v>-246.8</v>
+        <v>45.4</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C125" s="6">
-        <v>38</v>
+        <v>10354.65</v>
       </c>
       <c r="D125" s="6">
-        <v>26</v>
-      </c>
-      <c r="E125" s="7">
-        <v>-12</v>
+        <v>10345.3</v>
+      </c>
+      <c r="E125" s="8">
+        <v>-9.35</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C126" s="6">
-        <v>62</v>
+        <v>26869.1</v>
       </c>
       <c r="D126" s="6">
-        <v>56</v>
+        <v>27222.55</v>
       </c>
       <c r="E126" s="7">
-        <v>-6</v>
+        <v>353.45</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="D127" s="6">
-        <v>62</v>
-      </c>
-      <c r="E127" s="8">
-        <v>12</v>
+        <v>32</v>
+      </c>
+      <c r="E127" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -5456,13 +5489,13 @@
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="D128" s="6">
-        <v>32</v>
-      </c>
-      <c r="E128" s="8">
-        <v>19</v>
+        <v>50</v>
+      </c>
+      <c r="E128" s="7">
+        <v>18</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -5473,12 +5506,12 @@
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D129" s="6">
-        <v>50</v>
-      </c>
-      <c r="E129" s="7">
+        <v>44</v>
+      </c>
+      <c r="E129" s="8">
         <v>-6</v>
       </c>
     </row>
@@ -5490,410 +5523,393 @@
         <v>14</v>
       </c>
       <c r="C130" s="6">
+        <v>81</v>
+      </c>
+      <c r="D130" s="6">
         <v>87</v>
       </c>
-      <c r="D130" s="6">
-        <v>81</v>
-      </c>
       <c r="E130" s="7">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="6">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="D131" s="6">
-        <v>87</v>
+        <v>26</v>
       </c>
       <c r="E131" s="8">
-        <v>6</v>
+        <v>-18</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C132" s="6">
-        <v>32</v>
+        <v>87</v>
       </c>
       <c r="D132" s="6">
-        <v>13</v>
-      </c>
-      <c r="E132" s="7">
-        <v>-19</v>
+        <v>81</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C133" s="6">
-        <v>26</v>
+        <v>18.78</v>
       </c>
       <c r="D133" s="6">
-        <v>38</v>
-      </c>
-      <c r="E133" s="8">
-        <v>12</v>
+        <v>26.13</v>
+      </c>
+      <c r="E133" s="7">
+        <v>7.35</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="6">
-        <v>22.54</v>
+        <v>23.35</v>
       </c>
       <c r="D134" s="6">
-        <v>18.78</v>
+        <v>28.06</v>
       </c>
       <c r="E134" s="7">
-        <v>-3.76</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>29.77</v>
+        <v>26.88</v>
       </c>
       <c r="D135" s="6">
-        <v>23.35</v>
+        <v>35.11</v>
       </c>
       <c r="E135" s="7">
-        <v>-6.42</v>
+        <v>8.23</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>32.41</v>
+        <v>27.31</v>
       </c>
       <c r="D136" s="6">
-        <v>26.88</v>
+        <v>29.98</v>
       </c>
       <c r="E136" s="7">
-        <v>-5.53</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>37.24</v>
+        <v>35.91</v>
       </c>
       <c r="D137" s="6">
-        <v>27.31</v>
+        <v>45.04</v>
       </c>
       <c r="E137" s="7">
-        <v>-9.93</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>41.96</v>
+        <v>35.65</v>
       </c>
       <c r="D138" s="6">
-        <v>35.91</v>
+        <v>44.17</v>
       </c>
       <c r="E138" s="7">
-        <v>-6.05</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>40.48</v>
+        <v>33.35</v>
       </c>
       <c r="D139" s="6">
-        <v>35.65</v>
+        <v>47.27</v>
       </c>
       <c r="E139" s="7">
-        <v>-4.83</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>33.56</v>
+        <v>25.5</v>
       </c>
       <c r="D140" s="6">
-        <v>33.35</v>
+        <v>29.7</v>
       </c>
       <c r="E140" s="7">
-        <v>-0.21</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>32.07</v>
+        <v>28.26</v>
       </c>
       <c r="D141" s="6">
-        <v>25.5</v>
+        <v>33.06</v>
       </c>
       <c r="E141" s="7">
-        <v>-6.57</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>35.84</v>
+        <v>45.51</v>
       </c>
       <c r="D142" s="6">
-        <v>28.26</v>
+        <v>49.64</v>
       </c>
       <c r="E142" s="7">
-        <v>-7.58</v>
+        <v>4.13</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>55.37</v>
+        <v>29.28</v>
       </c>
       <c r="D143" s="6">
-        <v>45.51</v>
+        <v>33.13</v>
       </c>
       <c r="E143" s="7">
-        <v>-9.859999999999999</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>35.64</v>
+        <v>24.54</v>
       </c>
       <c r="D144" s="6">
-        <v>29.28</v>
+        <v>29.6</v>
       </c>
       <c r="E144" s="7">
-        <v>-6.36</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>31.46</v>
+        <v>37.04</v>
       </c>
       <c r="D145" s="6">
-        <v>24.54</v>
+        <v>45.09</v>
       </c>
       <c r="E145" s="7">
-        <v>-6.92</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>41.01</v>
+        <v>37.86</v>
       </c>
       <c r="D146" s="6">
-        <v>37.04</v>
+        <v>40.65</v>
       </c>
       <c r="E146" s="7">
-        <v>-3.97</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>46.89</v>
+        <v>31.18</v>
       </c>
       <c r="D147" s="6">
-        <v>37.86</v>
+        <v>34.35</v>
       </c>
       <c r="E147" s="7">
-        <v>-9.029999999999999</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>37.05</v>
+        <v>25.44</v>
       </c>
       <c r="D148" s="6">
-        <v>31.18</v>
+        <v>38.5</v>
       </c>
       <c r="E148" s="7">
-        <v>-5.87</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>31.17</v>
+        <v>30.5</v>
       </c>
       <c r="D149" s="6">
-        <v>25.44</v>
+        <v>36.62</v>
       </c>
       <c r="E149" s="7">
-        <v>-5.73</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>37.96</v>
+        <v>35.91</v>
       </c>
       <c r="D150" s="6">
-        <v>30.5</v>
+        <v>37.82</v>
       </c>
       <c r="E150" s="7">
-        <v>-7.46</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>42.74</v>
+        <v>29.75</v>
       </c>
       <c r="D151" s="6">
-        <v>35.91</v>
-      </c>
-      <c r="E151" s="7">
-        <v>-6.83</v>
+        <v>29.51</v>
+      </c>
+      <c r="E151" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C152" s="6">
-        <v>38.14</v>
+        <v>44.32</v>
       </c>
       <c r="D152" s="6">
-        <v>29.75</v>
+        <v>52.02</v>
       </c>
       <c r="E152" s="7">
-        <v>-8.390000000000001</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C153" s="6">
-        <v>49.47</v>
-      </c>
-      <c r="D153" s="6">
-        <v>44.32</v>
-      </c>
-      <c r="E153" s="7">
-        <v>-5.15</v>
+        <v>7.7</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5917,28 +5933,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5952,13 +5968,13 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>31.3</v>
+        <v>37.3</v>
       </c>
       <c r="E2" s="11">
         <v>10</v>
       </c>
       <c r="F2" s="11">
-        <v>-6.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G2" s="11">
         <v>-5.7</v>
@@ -6093,42 +6109,42 @@
         <v>39</v>
       </c>
       <c r="I1" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2568</v>
+        <v>0.2593</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1722</v>
+        <v>0.1695</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1641</v>
+        <v>0.1619</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1588</v>
+        <v>0.1581</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1221</v>
+        <v>0.1219</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1067</v>
+        <v>0.1076</v>
       </c>
       <c r="G2" s="14">
-        <v>0.08869999999999999</v>
+        <v>0.08710000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0866</v>
+        <v>0.0859</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0832</v>
+        <v>0.0819</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0808</v>
+        <v>0.0818</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6139,10 +6155,10 @@
         <v>43</v>
       </c>
       <c r="C3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="E3" s="13" t="s">
         <v>42</v>
@@ -6165,34 +6181,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0634</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="B4" s="14">
         <v>0.0616</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0284</v>
+        <v>0.0612</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0267</v>
+        <v>0.0317</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0188</v>
+        <v>0.0216</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.0117</v>
+        <v>0.0039</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0529</v>
+        <v>-0.0408</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.07400000000000001</v>
+        <v>-0.07440000000000001</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.153</v>
+        <v>-0.1327</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.1735</v>
+        <v>-0.1745</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="110">
   <si>
     <t>Symbol</t>
   </si>
@@ -286,58 +286,31 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>26.9 → 32.0</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>26.9</t>
-  </si>
-  <si>
-    <t>32.0</t>
-  </si>
-  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>42.3 → 50.4</t>
-  </si>
-  <si>
-    <t>42.3</t>
+    <t>50.4 → 45.1</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.4</t>
   </si>
   <si>
-    <t>44.6 → 60.5</t>
-  </si>
-  <si>
-    <t>44.6</t>
-  </si>
-  <si>
-    <t>60.5</t>
-  </si>
-  <si>
-    <t>28.3 → 31.6</t>
-  </si>
-  <si>
-    <t>28.3</t>
-  </si>
-  <si>
-    <t>31.6</t>
-  </si>
-  <si>
-    <t>49.9 → 54.0</t>
-  </si>
-  <si>
-    <t>49.9</t>
-  </si>
-  <si>
-    <t>54.0</t>
+    <t>45.1</t>
+  </si>
+  <si>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -423,14 +396,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -463,13 +436,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1067,10 +1040,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>25391.85</v>
+        <v>25156.75</v>
       </c>
       <c r="E2">
-        <v>1.23</v>
+        <v>-0.93</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1079,43 +1052,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-14.36</v>
+        <v>-15.15</v>
       </c>
       <c r="I2">
-        <v>6.82</v>
+        <v>5.84</v>
       </c>
       <c r="J2">
-        <v>-0.59</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K2">
-        <v>-7.8</v>
+        <v>-7.87</v>
       </c>
       <c r="L2">
-        <v>-4.35</v>
+        <v>-5.59</v>
       </c>
       <c r="M2">
-        <v>-5.09</v>
+        <v>-6.33</v>
       </c>
       <c r="N2">
-        <v>16.43</v>
+        <v>16.35</v>
       </c>
       <c r="O2">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="Q2">
-        <v>24997.55</v>
+        <v>25001.12</v>
       </c>
       <c r="R2">
-        <v>26168.01</v>
+        <v>26088.02</v>
       </c>
       <c r="S2">
-        <v>27738.12</v>
+        <v>27657.88</v>
       </c>
       <c r="T2">
-        <v>26993.61</v>
+        <v>26981.11</v>
       </c>
       <c r="U2">
-        <v>-5.93</v>
+        <v>-6.76</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1130,31 +1103,31 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>36.09</v>
+        <v>33.85</v>
       </c>
       <c r="AA2">
-        <v>-750.79</v>
+        <v>-729.66</v>
       </c>
       <c r="AB2">
-        <v>-684.16</v>
+        <v>-693.26</v>
       </c>
       <c r="AC2">
-        <v>-66.63</v>
+        <v>-36.4</v>
       </c>
       <c r="AD2">
-        <v>71.23999999999999</v>
+        <v>85.66</v>
       </c>
       <c r="AE2">
-        <v>41.83</v>
+        <v>64.94</v>
       </c>
       <c r="AF2">
-        <v>440.3</v>
+        <v>431.54</v>
       </c>
       <c r="AH2">
-        <v>27975.34</v>
+        <v>27927.01</v>
       </c>
       <c r="AI2">
-        <v>24360.68</v>
+        <v>24249.03</v>
       </c>
       <c r="AJ2">
         <v>26008.9</v>
@@ -1163,7 +1136,7 @@
         <v>80</v>
       </c>
       <c r="AL2">
-        <v>75.78</v>
+        <v>73.52</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1177,10 +1150,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>8955.450000000001</v>
+        <v>9011.299999999999</v>
       </c>
       <c r="E3">
-        <v>0.9</v>
+        <v>0.62</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1189,43 +1162,43 @@
         <v>8851.4</v>
       </c>
       <c r="H3">
-        <v>-14.74</v>
+        <v>-14.2</v>
       </c>
       <c r="I3">
-        <v>1.18</v>
+        <v>1.81</v>
       </c>
       <c r="J3">
-        <v>-3.07</v>
+        <v>-1.05</v>
       </c>
       <c r="K3">
-        <v>-7.77</v>
+        <v>-5.93</v>
       </c>
       <c r="L3">
-        <v>-9.19</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="M3">
-        <v>-1.38</v>
+        <v>-0.92</v>
       </c>
       <c r="N3">
-        <v>8.32</v>
+        <v>8.24</v>
       </c>
       <c r="O3">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="Q3">
-        <v>8942.6</v>
+        <v>8923.41</v>
       </c>
       <c r="R3">
-        <v>9299.139999999999</v>
+        <v>9279.33</v>
       </c>
       <c r="S3">
-        <v>9614.68</v>
+        <v>9594.84</v>
       </c>
       <c r="T3">
-        <v>9769.24</v>
+        <v>9768.18</v>
       </c>
       <c r="U3">
-        <v>-8.33</v>
+        <v>-7.75</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1240,31 +1213,31 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>32.02</v>
+        <v>35.43</v>
       </c>
       <c r="AA3">
-        <v>-202.05</v>
+        <v>-195.94</v>
       </c>
       <c r="AB3">
-        <v>-162.92</v>
+        <v>-169.53</v>
       </c>
       <c r="AC3">
-        <v>-39.12</v>
+        <v>-26.41</v>
       </c>
       <c r="AD3">
-        <v>23.17</v>
+        <v>38.24</v>
       </c>
       <c r="AE3">
-        <v>15.58</v>
+        <v>24.23</v>
       </c>
       <c r="AF3">
-        <v>128.93</v>
+        <v>129.55</v>
       </c>
       <c r="AH3">
-        <v>9805.98</v>
+        <v>9799.129999999999</v>
       </c>
       <c r="AI3">
-        <v>8792.309999999999</v>
+        <v>8759.530000000001</v>
       </c>
       <c r="AJ3">
         <v>9261.98</v>
@@ -1273,7 +1246,7 @@
         <v>80</v>
       </c>
       <c r="AL3">
-        <v>61.04</v>
+        <v>58.08</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1287,10 +1260,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>10948.6</v>
+        <v>10910</v>
       </c>
       <c r="E4">
-        <v>1.16</v>
+        <v>-0.35</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1299,43 +1272,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-13.37</v>
+        <v>-13.68</v>
       </c>
       <c r="I4">
-        <v>5.94</v>
+        <v>5.57</v>
       </c>
       <c r="J4">
-        <v>-1.14</v>
+        <v>-0.61</v>
       </c>
       <c r="K4">
-        <v>-4.92</v>
+        <v>-4.8</v>
       </c>
       <c r="L4">
-        <v>-5.71</v>
+        <v>-6.23</v>
       </c>
       <c r="M4">
-        <v>-9.84</v>
+        <v>-10.65</v>
       </c>
       <c r="N4">
-        <v>7.78</v>
+        <v>7.62</v>
       </c>
       <c r="O4">
         <v>13</v>
       </c>
       <c r="Q4">
-        <v>10878.63</v>
+        <v>10865.3</v>
       </c>
       <c r="R4">
-        <v>11180.86</v>
+        <v>11162.22</v>
       </c>
       <c r="S4">
-        <v>11633.78</v>
+        <v>11606.8</v>
       </c>
       <c r="T4">
-        <v>11536.45</v>
+        <v>11530.05</v>
       </c>
       <c r="U4">
-        <v>-5.1</v>
+        <v>-5.38</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1350,31 +1323,31 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>38.93</v>
+        <v>37.84</v>
       </c>
       <c r="AA4">
-        <v>-212.28</v>
+        <v>-205.41</v>
       </c>
       <c r="AB4">
-        <v>-197.58</v>
+        <v>-199.15</v>
       </c>
       <c r="AC4">
-        <v>-14.7</v>
+        <v>-6.26</v>
       </c>
       <c r="AD4">
-        <v>64.84999999999999</v>
+        <v>75.38</v>
       </c>
       <c r="AE4">
-        <v>51.75</v>
+        <v>62</v>
       </c>
       <c r="AF4">
-        <v>145.54</v>
+        <v>141.38</v>
       </c>
       <c r="AH4">
-        <v>11701</v>
+        <v>11693.58</v>
       </c>
       <c r="AI4">
-        <v>10660.71</v>
+        <v>10630.85</v>
       </c>
       <c r="AJ4">
         <v>11255.06</v>
@@ -1383,7 +1356,7 @@
         <v>80</v>
       </c>
       <c r="AL4">
-        <v>58.94</v>
+        <v>57.95</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1397,10 +1370,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>35975.9</v>
+        <v>36503.5</v>
       </c>
       <c r="E5">
-        <v>0.33</v>
+        <v>1.47</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1409,82 +1382,82 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-13.39</v>
+        <v>-12.12</v>
       </c>
       <c r="I5">
-        <v>8.69</v>
+        <v>10.29</v>
       </c>
       <c r="J5">
-        <v>-2.55</v>
+        <v>-0.49</v>
       </c>
       <c r="K5">
-        <v>-5.88</v>
+        <v>-3.77</v>
       </c>
       <c r="L5">
-        <v>-8.23</v>
+        <v>-7.31</v>
       </c>
       <c r="M5">
-        <v>1.7</v>
+        <v>3.21</v>
       </c>
       <c r="N5">
-        <v>7.9</v>
+        <v>8.07</v>
       </c>
       <c r="O5">
         <v>62</v>
       </c>
       <c r="Q5">
-        <v>35990.46</v>
+        <v>35954.47</v>
       </c>
       <c r="R5">
-        <v>36864.15</v>
+        <v>36831.93</v>
       </c>
       <c r="S5">
-        <v>37756.69</v>
+        <v>37708.02</v>
       </c>
       <c r="T5">
-        <v>37714.16</v>
+        <v>37722.7</v>
       </c>
       <c r="U5">
-        <v>-4.61</v>
+        <v>-3.23</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
       </c>
       <c r="W5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="s">
         <v>79</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>33.76</v>
+        <v>43.23</v>
       </c>
       <c r="AA5">
-        <v>-554.3099999999999</v>
+        <v>-506.39</v>
       </c>
       <c r="AB5">
-        <v>-472.2</v>
+        <v>-479.04</v>
       </c>
       <c r="AC5">
-        <v>-82.12</v>
+        <v>-27.35</v>
       </c>
       <c r="AD5">
-        <v>26.05</v>
+        <v>54.33</v>
       </c>
       <c r="AE5">
-        <v>20.94</v>
+        <v>31.18</v>
       </c>
       <c r="AF5">
-        <v>479.12</v>
+        <v>494.39</v>
       </c>
       <c r="AH5">
-        <v>38263.05</v>
+        <v>38232.99</v>
       </c>
       <c r="AI5">
-        <v>35465.26</v>
+        <v>35430.87</v>
       </c>
       <c r="AJ5">
         <v>37083.58</v>
@@ -1493,7 +1466,7 @@
         <v>80</v>
       </c>
       <c r="AL5">
-        <v>43.87</v>
+        <v>40.67</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1507,10 +1480,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>44731.15</v>
+        <v>45271.7</v>
       </c>
       <c r="E6">
-        <v>1.4</v>
+        <v>1.21</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1519,43 +1492,43 @@
         <v>43789.85</v>
       </c>
       <c r="H6">
-        <v>-21.21</v>
+        <v>-20.26</v>
       </c>
       <c r="I6">
-        <v>2.15</v>
+        <v>3.38</v>
       </c>
       <c r="J6">
-        <v>-1.05</v>
+        <v>1.05</v>
       </c>
       <c r="K6">
-        <v>-1.01</v>
+        <v>0.48</v>
       </c>
       <c r="L6">
-        <v>-7.82</v>
+        <v>-6.24</v>
       </c>
       <c r="M6">
-        <v>-18.92</v>
+        <v>-17.77</v>
       </c>
       <c r="N6">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>44481.54</v>
+        <v>44575.71</v>
       </c>
       <c r="R6">
-        <v>45074.64</v>
+        <v>45096.73</v>
       </c>
       <c r="S6">
-        <v>46520.86</v>
+        <v>46426.98</v>
       </c>
       <c r="T6">
-        <v>49314.82</v>
+        <v>49267.27</v>
       </c>
       <c r="U6">
-        <v>-9.289999999999999</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1570,31 +1543,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>45.4</v>
+        <v>49.5</v>
       </c>
       <c r="AA6">
-        <v>-550.65</v>
+        <v>-468.37</v>
       </c>
       <c r="AB6">
-        <v>-585.7</v>
+        <v>-562.23</v>
       </c>
       <c r="AC6">
-        <v>35.05</v>
+        <v>93.87</v>
       </c>
       <c r="AD6">
-        <v>76.11</v>
+        <v>81.62</v>
       </c>
       <c r="AE6">
-        <v>66.58</v>
+        <v>72.70999999999999</v>
       </c>
       <c r="AF6">
-        <v>708.41</v>
+        <v>701.16</v>
       </c>
       <c r="AH6">
-        <v>46469.23</v>
+        <v>46489</v>
       </c>
       <c r="AI6">
-        <v>43680.04</v>
+        <v>43704.45</v>
       </c>
       <c r="AJ6">
         <v>45688.38</v>
@@ -1603,7 +1576,7 @@
         <v>80</v>
       </c>
       <c r="AL6">
-        <v>40.64</v>
+        <v>36.26</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1617,10 +1590,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25228.55</v>
+        <v>24948.7</v>
       </c>
       <c r="E7">
-        <v>1.46</v>
+        <v>-1.11</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1629,43 +1602,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-11.36</v>
+        <v>-12.35</v>
       </c>
       <c r="I7">
-        <v>7.26</v>
+        <v>6.07</v>
       </c>
       <c r="J7">
-        <v>1.13</v>
+        <v>0.13</v>
       </c>
       <c r="K7">
-        <v>-1.14</v>
+        <v>-2.34</v>
       </c>
       <c r="L7">
-        <v>-4.93</v>
+        <v>-6.54</v>
       </c>
       <c r="M7">
-        <v>-4.53</v>
+        <v>-6.6</v>
       </c>
       <c r="N7">
-        <v>6.23</v>
+        <v>5.66</v>
       </c>
       <c r="O7">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="Q7">
-        <v>24924.05</v>
+        <v>24930.51</v>
       </c>
       <c r="R7">
-        <v>25023.62</v>
+        <v>25017.22</v>
       </c>
       <c r="S7">
-        <v>25733.69</v>
+        <v>25692.98</v>
       </c>
       <c r="T7">
-        <v>26327.82</v>
+        <v>26315.67</v>
       </c>
       <c r="U7">
-        <v>-4.18</v>
+        <v>-5.19</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1680,31 +1653,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>50.35</v>
+        <v>45.11</v>
       </c>
       <c r="AA7">
-        <v>-235.69</v>
+        <v>-218.99</v>
       </c>
       <c r="AB7">
-        <v>-299.73</v>
+        <v>-283.58</v>
       </c>
       <c r="AC7">
-        <v>64.03</v>
+        <v>64.59</v>
       </c>
       <c r="AD7">
-        <v>95.75</v>
+        <v>87.38</v>
       </c>
       <c r="AE7">
-        <v>82.06999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="AF7">
-        <v>335.81</v>
+        <v>336.34</v>
       </c>
       <c r="AH7">
-        <v>25686.11</v>
+        <v>25680.03</v>
       </c>
       <c r="AI7">
-        <v>24361.13</v>
+        <v>24354.41</v>
       </c>
       <c r="AJ7">
         <v>25420.21</v>
@@ -1713,7 +1686,7 @@
         <v>80</v>
       </c>
       <c r="AL7">
-        <v>29.63</v>
+        <v>26.33</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1727,10 +1700,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>29830.1</v>
+        <v>30171</v>
       </c>
       <c r="E8">
-        <v>5.22</v>
+        <v>1.14</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1739,43 +1712,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-24.46</v>
+        <v>-23.59</v>
       </c>
       <c r="I8">
-        <v>15.76</v>
+        <v>17.08</v>
       </c>
       <c r="J8">
-        <v>6.02</v>
+        <v>8.69</v>
       </c>
       <c r="K8">
-        <v>3.25</v>
+        <v>4.32</v>
       </c>
       <c r="L8">
-        <v>3.85</v>
+        <v>5.74</v>
       </c>
       <c r="M8">
-        <v>-12.13</v>
+        <v>-13.11</v>
       </c>
       <c r="N8">
-        <v>-3.3</v>
+        <v>-3.33</v>
       </c>
       <c r="O8">
         <v>68</v>
       </c>
       <c r="Q8">
-        <v>28449.8</v>
+        <v>28932.44</v>
       </c>
       <c r="R8">
-        <v>28461.13</v>
+        <v>28491.92</v>
       </c>
       <c r="S8">
-        <v>29849.53</v>
+        <v>29818.64</v>
       </c>
       <c r="T8">
-        <v>31068.21</v>
+        <v>31025.61</v>
       </c>
       <c r="U8">
-        <v>-3.99</v>
+        <v>-2.75</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1790,40 +1763,40 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>60.51</v>
+        <v>63.13</v>
       </c>
       <c r="AA8">
-        <v>-295.59</v>
+        <v>-140.92</v>
       </c>
       <c r="AB8">
-        <v>-482.29</v>
+        <v>-414.01</v>
       </c>
       <c r="AC8">
-        <v>186.7</v>
+        <v>273.1</v>
       </c>
       <c r="AD8">
         <v>95.44</v>
       </c>
       <c r="AE8">
-        <v>79.94</v>
+        <v>89.81</v>
       </c>
       <c r="AF8">
-        <v>689.95</v>
+        <v>679.74</v>
       </c>
       <c r="AH8">
-        <v>29671.7</v>
+        <v>29842.82</v>
       </c>
       <c r="AI8">
-        <v>27250.56</v>
+        <v>27141.01</v>
       </c>
       <c r="AJ8">
-        <v>27154.42</v>
+        <v>28089.09</v>
       </c>
       <c r="AK8" t="s">
         <v>81</v>
       </c>
       <c r="AL8">
-        <v>26.95</v>
+        <v>31.89</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1837,10 +1810,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15149.7</v>
+        <v>15083.55</v>
       </c>
       <c r="E9">
-        <v>0.72</v>
+        <v>-0.44</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1849,31 +1822,31 @@
         <v>14845.15</v>
       </c>
       <c r="H9">
-        <v>-9.08</v>
+        <v>-9.48</v>
       </c>
       <c r="I9">
-        <v>2.05</v>
+        <v>1.61</v>
       </c>
       <c r="J9">
-        <v>-1.77</v>
+        <v>-1.05</v>
       </c>
       <c r="K9">
-        <v>-5.99</v>
+        <v>-5.54</v>
       </c>
       <c r="L9">
-        <v>-4.42</v>
+        <v>-5.21</v>
       </c>
       <c r="N9">
-        <v>-9.42</v>
+        <v>-10.51</v>
       </c>
       <c r="Q9">
-        <v>15046.54</v>
+        <v>15014.59</v>
       </c>
       <c r="R9">
-        <v>15508.96</v>
+        <v>15483.9</v>
       </c>
       <c r="S9">
-        <v>16079.77</v>
+        <v>16051.01</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1885,31 +1858,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>36.98</v>
+        <v>35.6</v>
       </c>
       <c r="AA9">
-        <v>-295.35</v>
+        <v>-289.44</v>
       </c>
       <c r="AB9">
-        <v>-258.22</v>
+        <v>-264.47</v>
       </c>
       <c r="AC9">
-        <v>-37.13</v>
+        <v>-24.98</v>
       </c>
       <c r="AD9">
-        <v>39.61</v>
+        <v>53.48</v>
       </c>
       <c r="AE9">
-        <v>26.08</v>
+        <v>37.74</v>
       </c>
       <c r="AF9">
-        <v>205.76</v>
+        <v>199.53</v>
       </c>
       <c r="AH9">
-        <v>16233.88</v>
+        <v>16232.08</v>
       </c>
       <c r="AI9">
-        <v>14784.03</v>
+        <v>14735.72</v>
       </c>
       <c r="AJ9">
         <v>15490.29</v>
@@ -1918,7 +1891,7 @@
         <v>80</v>
       </c>
       <c r="AL9">
-        <v>57.72</v>
+        <v>57.15</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1932,10 +1905,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8578.5</v>
+        <v>8580.299999999999</v>
       </c>
       <c r="E10">
-        <v>0.93</v>
+        <v>0.02</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1944,43 +1917,43 @@
         <v>8499.65</v>
       </c>
       <c r="H10">
-        <v>-12.16</v>
+        <v>-12.14</v>
       </c>
       <c r="I10">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="J10">
-        <v>-2.49</v>
+        <v>-1.7</v>
       </c>
       <c r="K10">
-        <v>-6.08</v>
+        <v>-5.47</v>
       </c>
       <c r="L10">
-        <v>-8.26</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="M10">
-        <v>-5.45</v>
+        <v>-5.87</v>
       </c>
       <c r="N10">
-        <v>10.47</v>
+        <v>10.24</v>
       </c>
       <c r="O10">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Q10">
-        <v>8576.940000000001</v>
+        <v>8547.299999999999</v>
       </c>
       <c r="R10">
-        <v>8808.58</v>
+        <v>8792.059999999999</v>
       </c>
       <c r="S10">
-        <v>9111.15</v>
+        <v>9092.6</v>
       </c>
       <c r="T10">
-        <v>9258.780000000001</v>
+        <v>9253.9</v>
       </c>
       <c r="U10">
-        <v>-7.35</v>
+        <v>-7.28</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1995,31 +1968,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>35.88</v>
+        <v>35.99</v>
       </c>
       <c r="AA10">
-        <v>-161.45</v>
+        <v>-157.92</v>
       </c>
       <c r="AB10">
-        <v>-143.63</v>
+        <v>-146.49</v>
       </c>
       <c r="AC10">
-        <v>-17.82</v>
+        <v>-11.43</v>
       </c>
       <c r="AD10">
-        <v>47.82</v>
+        <v>59.58</v>
       </c>
       <c r="AE10">
-        <v>42.66</v>
+        <v>47.86</v>
       </c>
       <c r="AF10">
-        <v>116.69</v>
+        <v>115.61</v>
       </c>
       <c r="AH10">
-        <v>9196.32</v>
+        <v>9189.51</v>
       </c>
       <c r="AI10">
-        <v>8420.84</v>
+        <v>8394.610000000001</v>
       </c>
       <c r="AJ10">
         <v>8855.59</v>
@@ -2028,7 +2001,7 @@
         <v>80</v>
       </c>
       <c r="AL10">
-        <v>59.42</v>
+        <v>56.54</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2042,13 +2015,13 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1631.7</v>
+        <v>1641.35</v>
       </c>
       <c r="E11">
-        <v>0.42</v>
+        <v>0.59</v>
       </c>
       <c r="F11">
-        <v>1631.7</v>
+        <v>1641.35</v>
       </c>
       <c r="G11">
         <v>1253.35</v>
@@ -2057,40 +2030,40 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>30.19</v>
+        <v>30.96</v>
       </c>
       <c r="J11">
-        <v>4.08</v>
+        <v>3.98</v>
       </c>
       <c r="K11">
-        <v>6.31</v>
+        <v>6.78</v>
       </c>
       <c r="L11">
-        <v>8.02</v>
+        <v>9.15</v>
       </c>
       <c r="M11">
-        <v>1.67</v>
+        <v>3.2</v>
       </c>
       <c r="N11">
-        <v>-6.84</v>
+        <v>-6.93</v>
       </c>
       <c r="O11">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="Q11">
-        <v>1584.56</v>
+        <v>1597.13</v>
       </c>
       <c r="R11">
-        <v>1558.45</v>
+        <v>1565.32</v>
       </c>
       <c r="S11">
-        <v>1567.38</v>
+        <v>1568.84</v>
       </c>
       <c r="T11">
-        <v>1462.18</v>
+        <v>1463.41</v>
       </c>
       <c r="U11">
-        <v>11.59</v>
+        <v>12.16</v>
       </c>
       <c r="V11" t="s">
         <v>79</v>
@@ -2105,40 +2078,40 @@
         <v>2</v>
       </c>
       <c r="Z11">
-        <v>62.48</v>
+        <v>63.79</v>
       </c>
       <c r="AA11">
-        <v>10.53</v>
+        <v>14.96</v>
       </c>
       <c r="AB11">
-        <v>2.68</v>
+        <v>5.13</v>
       </c>
       <c r="AC11">
-        <v>7.86</v>
+        <v>9.83</v>
       </c>
       <c r="AD11">
-        <v>78.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="AE11">
-        <v>54.21</v>
+        <v>74.44</v>
       </c>
       <c r="AF11">
-        <v>37.73</v>
+        <v>36.45</v>
       </c>
       <c r="AH11">
-        <v>1620.41</v>
+        <v>1632.11</v>
       </c>
       <c r="AI11">
-        <v>1496.49</v>
+        <v>1498.53</v>
       </c>
       <c r="AJ11">
-        <v>1505.62</v>
+        <v>1526.96</v>
       </c>
       <c r="AK11" t="s">
         <v>81</v>
       </c>
       <c r="AL11">
-        <v>23.01</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2152,10 +2125,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>12088.25</v>
+        <v>12006.75</v>
       </c>
       <c r="E12">
-        <v>1.15</v>
+        <v>-0.67</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2164,43 +2137,43 @@
         <v>10017.9</v>
       </c>
       <c r="H12">
-        <v>-11.88</v>
+        <v>-12.48</v>
       </c>
       <c r="I12">
-        <v>20.67</v>
+        <v>19.85</v>
       </c>
       <c r="J12">
-        <v>-4.06</v>
+        <v>-2.44</v>
       </c>
       <c r="K12">
-        <v>-9.140000000000001</v>
+        <v>-7.63</v>
       </c>
       <c r="L12">
-        <v>-4.65</v>
+        <v>-4.23</v>
       </c>
       <c r="M12">
-        <v>17.62</v>
+        <v>17.88</v>
       </c>
       <c r="N12">
-        <v>15.37</v>
+        <v>14.81</v>
       </c>
       <c r="O12">
         <v>87</v>
       </c>
       <c r="Q12">
-        <v>12043.38</v>
+        <v>11983.39</v>
       </c>
       <c r="R12">
-        <v>12652.93</v>
+        <v>12619.81</v>
       </c>
       <c r="S12">
-        <v>12972.56</v>
+        <v>12954.4</v>
       </c>
       <c r="T12">
-        <v>12438.07</v>
+        <v>12445.49</v>
       </c>
       <c r="U12">
-        <v>-2.81</v>
+        <v>-3.53</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2215,31 +2188,31 @@
         <v>1</v>
       </c>
       <c r="Z12">
-        <v>36.52</v>
+        <v>35.15</v>
       </c>
       <c r="AA12">
-        <v>-274.07</v>
+        <v>-282.54</v>
       </c>
       <c r="AB12">
-        <v>-182.97</v>
+        <v>-202.88</v>
       </c>
       <c r="AC12">
-        <v>-91.09999999999999</v>
+        <v>-79.65000000000001</v>
       </c>
       <c r="AD12">
-        <v>17.4</v>
+        <v>21.95</v>
       </c>
       <c r="AE12">
-        <v>10.22</v>
+        <v>15.97</v>
       </c>
       <c r="AF12">
-        <v>248.56</v>
+        <v>239.25</v>
       </c>
       <c r="AH12">
-        <v>13494.44</v>
+        <v>13509.4</v>
       </c>
       <c r="AI12">
-        <v>11811.41</v>
+        <v>11730.21</v>
       </c>
       <c r="AJ12">
         <v>12689.95</v>
@@ -2248,7 +2221,7 @@
         <v>80</v>
       </c>
       <c r="AL12">
-        <v>49.69</v>
+        <v>50.89</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2262,10 +2235,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9196.6</v>
+        <v>9280.799999999999</v>
       </c>
       <c r="E13">
-        <v>1.08</v>
+        <v>0.92</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2274,43 +2247,43 @@
         <v>9010.450000000001</v>
       </c>
       <c r="H13">
-        <v>-14.58</v>
+        <v>-13.8</v>
       </c>
       <c r="I13">
-        <v>2.07</v>
+        <v>3</v>
       </c>
       <c r="J13">
-        <v>-1.6</v>
+        <v>0.52</v>
       </c>
       <c r="K13">
-        <v>-5.68</v>
+        <v>-4.21</v>
       </c>
       <c r="L13">
-        <v>-7.32</v>
+        <v>-6.39</v>
       </c>
       <c r="M13">
-        <v>-7.36</v>
+        <v>-6.44</v>
       </c>
       <c r="N13">
-        <v>16.32</v>
+        <v>16.17</v>
       </c>
       <c r="O13">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="Q13">
-        <v>9123.15</v>
+        <v>9132.84</v>
       </c>
       <c r="R13">
-        <v>9382.42</v>
+        <v>9373.110000000001</v>
       </c>
       <c r="S13">
-        <v>9627.43</v>
+        <v>9612.940000000001</v>
       </c>
       <c r="T13">
-        <v>10001.36</v>
+        <v>10000.09</v>
       </c>
       <c r="U13">
-        <v>-8.050000000000001</v>
+        <v>-7.19</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2325,31 +2298,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>38.01</v>
+        <v>43.24</v>
       </c>
       <c r="AA13">
-        <v>-152.14</v>
+        <v>-138.8</v>
       </c>
       <c r="AB13">
-        <v>-131.11</v>
+        <v>-132.65</v>
       </c>
       <c r="AC13">
-        <v>-21.03</v>
+        <v>-6.15</v>
       </c>
       <c r="AD13">
-        <v>44.66</v>
+        <v>68.36</v>
       </c>
       <c r="AE13">
-        <v>30.59</v>
+        <v>45.44</v>
       </c>
       <c r="AF13">
-        <v>122.49</v>
+        <v>121.37</v>
       </c>
       <c r="AH13">
-        <v>9777.860000000001</v>
+        <v>9768.940000000001</v>
       </c>
       <c r="AI13">
-        <v>8986.98</v>
+        <v>8977.290000000001</v>
       </c>
       <c r="AJ13">
         <v>9403.969999999999</v>
@@ -2358,7 +2331,7 @@
         <v>80</v>
       </c>
       <c r="AL13">
-        <v>58.71</v>
+        <v>55.4</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2372,10 +2345,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8146.55</v>
+        <v>8167.55</v>
       </c>
       <c r="E14">
-        <v>1.44</v>
+        <v>0.26</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2384,43 +2357,43 @@
         <v>7523.45</v>
       </c>
       <c r="H14">
-        <v>-17.54</v>
+        <v>-17.33</v>
       </c>
       <c r="I14">
-        <v>8.279999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="J14">
-        <v>1.73</v>
+        <v>0.97</v>
       </c>
       <c r="K14">
-        <v>-3.04</v>
+        <v>-2.18</v>
       </c>
       <c r="L14">
-        <v>-1.94</v>
+        <v>-2.61</v>
       </c>
       <c r="M14">
-        <v>7.43</v>
+        <v>7.25</v>
       </c>
       <c r="N14">
-        <v>25</v>
+        <v>24.63</v>
       </c>
       <c r="O14">
         <v>81</v>
       </c>
       <c r="Q14">
-        <v>8077.64</v>
+        <v>8093.41</v>
       </c>
       <c r="R14">
-        <v>8144.69</v>
+        <v>8145.14</v>
       </c>
       <c r="S14">
-        <v>8407.51</v>
+        <v>8401.129999999999</v>
       </c>
       <c r="T14">
-        <v>8577.49</v>
+        <v>8576.540000000001</v>
       </c>
       <c r="U14">
-        <v>-5.02</v>
+        <v>-4.77</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2435,31 +2408,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>47.26</v>
+        <v>48.34</v>
       </c>
       <c r="AA14">
-        <v>-97.08</v>
+        <v>-84.38</v>
       </c>
       <c r="AB14">
-        <v>-109.2</v>
+        <v>-104.24</v>
       </c>
       <c r="AC14">
-        <v>12.13</v>
+        <v>19.86</v>
       </c>
       <c r="AD14">
-        <v>86.98999999999999</v>
+        <v>89.33</v>
       </c>
       <c r="AE14">
-        <v>74.66</v>
+        <v>81.59</v>
       </c>
       <c r="AF14">
-        <v>140.64</v>
+        <v>141.7</v>
       </c>
       <c r="AH14">
-        <v>8423.620000000001</v>
+        <v>8424.200000000001</v>
       </c>
       <c r="AI14">
-        <v>7865.76</v>
+        <v>7866.08</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
@@ -2468,7 +2441,7 @@
         <v>80</v>
       </c>
       <c r="AL14">
-        <v>25.72</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2482,10 +2455,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26075</v>
+        <v>25736.95</v>
       </c>
       <c r="E15">
-        <v>-0.01</v>
+        <v>-1.3</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2494,43 +2467,43 @@
         <v>21549.55</v>
       </c>
       <c r="H15">
-        <v>-4.09</v>
+        <v>-5.33</v>
       </c>
       <c r="I15">
-        <v>21</v>
+        <v>19.43</v>
       </c>
       <c r="J15">
-        <v>-1.79</v>
+        <v>-2.65</v>
       </c>
       <c r="K15">
-        <v>-1.81</v>
+        <v>-3</v>
       </c>
       <c r="L15">
-        <v>0.65</v>
+        <v>-1.03</v>
       </c>
       <c r="M15">
-        <v>19.85</v>
+        <v>18.17</v>
       </c>
       <c r="N15">
-        <v>12.18</v>
+        <v>11.81</v>
       </c>
       <c r="O15">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="Q15">
-        <v>26075.14</v>
+        <v>25935.22</v>
       </c>
       <c r="R15">
-        <v>26511.29</v>
+        <v>26488.71</v>
       </c>
       <c r="S15">
-        <v>26575.62</v>
+        <v>26557.11</v>
       </c>
       <c r="T15">
-        <v>24280.52</v>
+        <v>24295.45</v>
       </c>
       <c r="U15">
-        <v>7.39</v>
+        <v>5.93</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2545,40 +2518,40 @@
         <v>2</v>
       </c>
       <c r="Z15">
-        <v>42.9</v>
+        <v>37.94</v>
       </c>
       <c r="AA15">
-        <v>-143.06</v>
+        <v>-177.08</v>
       </c>
       <c r="AB15">
-        <v>-56.72</v>
+        <v>-80.79000000000001</v>
       </c>
       <c r="AC15">
-        <v>-86.34</v>
+        <v>-96.29000000000001</v>
       </c>
       <c r="AD15">
-        <v>18.05</v>
+        <v>14.29</v>
       </c>
       <c r="AE15">
-        <v>14.58</v>
+        <v>14.45</v>
       </c>
       <c r="AF15">
-        <v>366.09</v>
+        <v>373.8</v>
       </c>
       <c r="AH15">
-        <v>27334.84</v>
+        <v>27372.1</v>
       </c>
       <c r="AI15">
-        <v>25687.74</v>
+        <v>25605.33</v>
       </c>
       <c r="AJ15">
-        <v>26990.16</v>
+        <v>26953.21</v>
       </c>
       <c r="AK15" t="s">
         <v>80</v>
       </c>
       <c r="AL15">
-        <v>35.53</v>
+        <v>37.95</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2592,10 +2565,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>829.95</v>
+        <v>822.8</v>
       </c>
       <c r="E16">
-        <v>2.46</v>
+        <v>-0.86</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2604,43 +2577,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-14.32</v>
+        <v>-15.06</v>
       </c>
       <c r="I16">
-        <v>27.46</v>
+        <v>26.36</v>
       </c>
       <c r="J16">
-        <v>-0.9</v>
+        <v>0.02</v>
       </c>
       <c r="K16">
-        <v>-4.83</v>
+        <v>-3.03</v>
       </c>
       <c r="L16">
-        <v>-9.66</v>
+        <v>-10.09</v>
       </c>
       <c r="M16">
-        <v>-5.27</v>
+        <v>-6.72</v>
       </c>
       <c r="N16">
-        <v>9.279999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="O16">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="Q16">
-        <v>812.63</v>
+        <v>812.67</v>
       </c>
       <c r="R16">
-        <v>836.97</v>
+        <v>837.4</v>
       </c>
       <c r="S16">
-        <v>873.11</v>
+        <v>871.3</v>
       </c>
       <c r="T16">
-        <v>825.13</v>
+        <v>824.8200000000001</v>
       </c>
       <c r="U16">
-        <v>0.58</v>
+        <v>-0.24</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2652,34 +2625,34 @@
         <v>79</v>
       </c>
       <c r="Y16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z16">
-        <v>44.63</v>
+        <v>42.62</v>
       </c>
       <c r="AA16">
-        <v>-16.67</v>
+        <v>-15.9</v>
       </c>
       <c r="AB16">
-        <v>-15.14</v>
+        <v>-15.3</v>
       </c>
       <c r="AC16">
-        <v>-1.52</v>
+        <v>-0.61</v>
       </c>
       <c r="AD16">
-        <v>42.05</v>
+        <v>57.85</v>
       </c>
       <c r="AE16">
-        <v>23.94</v>
+        <v>38.9</v>
       </c>
       <c r="AF16">
-        <v>17.83</v>
+        <v>17.54</v>
       </c>
       <c r="AH16">
-        <v>879.29</v>
+        <v>878.91</v>
       </c>
       <c r="AI16">
-        <v>794.66</v>
+        <v>795.89</v>
       </c>
       <c r="AJ16">
         <v>855.3200000000001</v>
@@ -2688,7 +2661,7 @@
         <v>80</v>
       </c>
       <c r="AL16">
-        <v>37.24</v>
+        <v>33.35</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2702,10 +2675,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29443</v>
+        <v>29455.4</v>
       </c>
       <c r="E17">
-        <v>2.08</v>
+        <v>0.04</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2714,43 +2687,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-13.66</v>
+        <v>-13.62</v>
       </c>
       <c r="I17">
-        <v>3.81</v>
+        <v>3.85</v>
       </c>
       <c r="J17">
-        <v>0.6899999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="K17">
-        <v>-1.65</v>
+        <v>-1.71</v>
       </c>
       <c r="L17">
-        <v>-5.19</v>
+        <v>-5.44</v>
       </c>
       <c r="M17">
-        <v>-8.69</v>
+        <v>-9.69</v>
       </c>
       <c r="N17">
-        <v>3.27</v>
+        <v>3.02</v>
       </c>
       <c r="O17">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Q17">
-        <v>29011.88</v>
+        <v>29091.16</v>
       </c>
       <c r="R17">
-        <v>29419.11</v>
+        <v>29405.44</v>
       </c>
       <c r="S17">
-        <v>30284.78</v>
+        <v>30238.4</v>
       </c>
       <c r="T17">
-        <v>31100.22</v>
+        <v>31079.18</v>
       </c>
       <c r="U17">
-        <v>-5.33</v>
+        <v>-5.22</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2765,31 +2738,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>47.47</v>
+        <v>47.69</v>
       </c>
       <c r="AA17">
-        <v>-359.77</v>
+        <v>-313.3</v>
       </c>
       <c r="AB17">
-        <v>-388.15</v>
+        <v>-373.18</v>
       </c>
       <c r="AC17">
-        <v>28.38</v>
+        <v>59.87</v>
       </c>
       <c r="AD17">
-        <v>85.12</v>
+        <v>89.02</v>
       </c>
       <c r="AE17">
-        <v>62.36</v>
+        <v>76.33</v>
       </c>
       <c r="AF17">
-        <v>363.96</v>
+        <v>355.5</v>
       </c>
       <c r="AH17">
-        <v>30322.88</v>
+        <v>30297.67</v>
       </c>
       <c r="AI17">
-        <v>28515.35</v>
+        <v>28513.2</v>
       </c>
       <c r="AJ17">
         <v>29780.35</v>
@@ -2798,7 +2771,7 @@
         <v>80</v>
       </c>
       <c r="AL17">
-        <v>47.24</v>
+        <v>42.11</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2812,10 +2785,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>15860.65</v>
+        <v>15663</v>
       </c>
       <c r="E18">
-        <v>0.08</v>
+        <v>-1.25</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2824,31 +2797,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-6.38</v>
+        <v>-7.55</v>
       </c>
       <c r="I18">
-        <v>2.97</v>
+        <v>1.69</v>
       </c>
       <c r="J18">
-        <v>-1.49</v>
+        <v>-2.47</v>
       </c>
       <c r="K18">
-        <v>-3.98</v>
+        <v>-5.03</v>
       </c>
       <c r="L18">
-        <v>-3.53</v>
+        <v>-5.12</v>
       </c>
       <c r="N18">
-        <v>6.02</v>
+        <v>2.12</v>
       </c>
       <c r="Q18">
-        <v>15861.54</v>
+        <v>15782.31</v>
       </c>
       <c r="R18">
-        <v>16310.71</v>
+        <v>16278.91</v>
       </c>
       <c r="S18">
-        <v>16484.75</v>
+        <v>16462.34</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2860,40 +2833,40 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>36.95</v>
+        <v>32.82</v>
       </c>
       <c r="AA18">
-        <v>-194.05</v>
+        <v>-212.12</v>
       </c>
       <c r="AB18">
-        <v>-127.97</v>
+        <v>-144.8</v>
       </c>
       <c r="AC18">
-        <v>-66.09</v>
+        <v>-67.31999999999999</v>
       </c>
       <c r="AD18">
-        <v>20.47</v>
+        <v>16.74</v>
       </c>
       <c r="AE18">
-        <v>15.7</v>
+        <v>16.85</v>
       </c>
       <c r="AF18">
-        <v>217.19</v>
+        <v>221.89</v>
       </c>
       <c r="AH18">
-        <v>17057.06</v>
+        <v>17079.59</v>
       </c>
       <c r="AI18">
-        <v>15564.36</v>
+        <v>15478.24</v>
       </c>
       <c r="AJ18">
-        <v>16426.2</v>
+        <v>16384.12</v>
       </c>
       <c r="AK18" t="s">
         <v>80</v>
       </c>
       <c r="AL18">
-        <v>51.23</v>
+        <v>53.81</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2907,10 +2880,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9250.5</v>
+        <v>9294.1</v>
       </c>
       <c r="E19">
-        <v>1.41</v>
+        <v>0.47</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2919,31 +2892,31 @@
         <v>8961.25</v>
       </c>
       <c r="H19">
-        <v>-7.48</v>
+        <v>-7.05</v>
       </c>
       <c r="I19">
-        <v>3.23</v>
+        <v>3.71</v>
       </c>
       <c r="J19">
-        <v>-1.04</v>
+        <v>0.85</v>
       </c>
       <c r="K19">
-        <v>-5.57</v>
+        <v>-4.42</v>
       </c>
       <c r="L19">
-        <v>-0.8</v>
+        <v>-0.4</v>
       </c>
       <c r="N19">
-        <v>8.66</v>
+        <v>10.1</v>
       </c>
       <c r="Q19">
-        <v>9111.17</v>
+        <v>9126.92</v>
       </c>
       <c r="R19">
-        <v>9244.190000000001</v>
+        <v>9251.68</v>
       </c>
       <c r="S19">
-        <v>9532.280000000001</v>
+        <v>9529.4</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2955,31 +2928,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>47.29</v>
+        <v>48.84</v>
       </c>
       <c r="AA19">
-        <v>-117.74</v>
+        <v>-101.87</v>
       </c>
       <c r="AB19">
-        <v>-113.88</v>
+        <v>-111.47</v>
       </c>
       <c r="AC19">
-        <v>-3.87</v>
+        <v>9.6</v>
       </c>
       <c r="AD19">
-        <v>59.35</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="AE19">
-        <v>37.63</v>
+        <v>57.47</v>
       </c>
       <c r="AF19">
-        <v>178.77</v>
+        <v>172.3</v>
       </c>
       <c r="AH19">
-        <v>9531.559999999999</v>
+        <v>9535.870000000001</v>
       </c>
       <c r="AI19">
-        <v>8956.809999999999</v>
+        <v>8967.49</v>
       </c>
       <c r="AJ19">
         <v>9494.469999999999</v>
@@ -2988,7 +2961,7 @@
         <v>80</v>
       </c>
       <c r="AL19">
-        <v>32.34</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3002,10 +2975,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10349.6</v>
+        <v>10456.75</v>
       </c>
       <c r="E20">
-        <v>0.49</v>
+        <v>1.04</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3014,31 +2987,31 @@
         <v>10299.4</v>
       </c>
       <c r="H20">
-        <v>-8.970000000000001</v>
+        <v>-8.02</v>
       </c>
       <c r="I20">
-        <v>0.49</v>
+        <v>1.53</v>
       </c>
       <c r="J20">
-        <v>-3.07</v>
+        <v>-1.56</v>
       </c>
       <c r="K20">
-        <v>-6.17</v>
+        <v>-4.39</v>
       </c>
       <c r="L20">
-        <v>-6.78</v>
+        <v>-6.46</v>
       </c>
       <c r="N20">
-        <v>-16.83</v>
+        <v>-14.14</v>
       </c>
       <c r="Q20">
-        <v>10394.35</v>
+        <v>10361.14</v>
       </c>
       <c r="R20">
-        <v>10682.71</v>
+        <v>10665.73</v>
       </c>
       <c r="S20">
-        <v>10979.32</v>
+        <v>10961.3</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3050,31 +3023,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>31.63</v>
+        <v>38.25</v>
       </c>
       <c r="AA20">
-        <v>-182.84</v>
+        <v>-174.7</v>
       </c>
       <c r="AB20">
-        <v>-150.69</v>
+        <v>-155.49</v>
       </c>
       <c r="AC20">
-        <v>-32.15</v>
+        <v>-19.21</v>
       </c>
       <c r="AD20">
-        <v>17.72</v>
+        <v>40.84</v>
       </c>
       <c r="AE20">
-        <v>21.02</v>
+        <v>24.41</v>
       </c>
       <c r="AF20">
-        <v>143.34</v>
+        <v>146.44</v>
       </c>
       <c r="AH20">
-        <v>11158.77</v>
+        <v>11148.89</v>
       </c>
       <c r="AI20">
-        <v>10206.66</v>
+        <v>10182.57</v>
       </c>
       <c r="AJ20">
         <v>10732.68</v>
@@ -3083,7 +3056,7 @@
         <v>80</v>
       </c>
       <c r="AL20">
-        <v>53.49</v>
+        <v>49.21</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3097,10 +3070,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27324.35</v>
+        <v>27166.8</v>
       </c>
       <c r="E21">
-        <v>0.74</v>
+        <v>-0.58</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3109,43 +3082,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6.38</v>
+        <v>-6.92</v>
       </c>
       <c r="I21">
-        <v>13.17</v>
+        <v>12.52</v>
       </c>
       <c r="J21">
-        <v>0.85</v>
+        <v>0.19</v>
       </c>
       <c r="K21">
-        <v>0.07000000000000001</v>
+        <v>-0.98</v>
       </c>
       <c r="L21">
-        <v>-2.12</v>
+        <v>-2.98</v>
       </c>
       <c r="M21">
-        <v>0.61</v>
+        <v>-1.18</v>
       </c>
       <c r="N21">
-        <v>6.32</v>
+        <v>5.84</v>
       </c>
       <c r="O21">
         <v>74</v>
       </c>
       <c r="Q21">
-        <v>27130.96</v>
+        <v>27141.14</v>
       </c>
       <c r="R21">
-        <v>27012.95</v>
+        <v>27017.8</v>
       </c>
       <c r="S21">
-        <v>27335.57</v>
+        <v>27318.01</v>
       </c>
       <c r="T21">
-        <v>27448.37</v>
+        <v>27442.15</v>
       </c>
       <c r="U21">
-        <v>-0.45</v>
+        <v>-1</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3160,40 +3133,40 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>53.97</v>
+        <v>50.53</v>
       </c>
       <c r="AA21">
-        <v>-82.17</v>
+        <v>-66.79000000000001</v>
       </c>
       <c r="AB21">
-        <v>-152.51</v>
+        <v>-135.37</v>
       </c>
       <c r="AC21">
-        <v>70.34</v>
+        <v>68.58</v>
       </c>
       <c r="AD21">
-        <v>96.44</v>
+        <v>91.14</v>
       </c>
       <c r="AE21">
-        <v>90.93000000000001</v>
+        <v>91.31999999999999</v>
       </c>
       <c r="AF21">
-        <v>363.61</v>
+        <v>358.19</v>
       </c>
       <c r="AH21">
-        <v>27606.31</v>
+        <v>27614.69</v>
       </c>
       <c r="AI21">
-        <v>26419.58</v>
+        <v>26420.9</v>
       </c>
       <c r="AJ21">
-        <v>26094.07</v>
+        <v>26197.52</v>
       </c>
       <c r="AK21" t="s">
         <v>81</v>
       </c>
       <c r="AL21">
-        <v>22.09</v>
+        <v>23.13</v>
       </c>
     </row>
   </sheetData>
@@ -3334,7 +3307,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F153"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3374,7 +3347,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>88</v>
@@ -3394,7 +3367,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>93</v>
@@ -3403,2042 +3376,2033 @@
         <v>94</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>105</v>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-7.8</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-7.87</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-7.77</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-5.93</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.84</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>110</v>
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-4.92</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-4.8</v>
+      </c>
+      <c r="E10" s="8">
+        <v>0.12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-9.289999999999999</v>
+        <v>-5.88</v>
       </c>
       <c r="D11" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.49</v>
+        <v>-3.77</v>
+      </c>
+      <c r="E11" s="8">
+        <v>2.11</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-8.859999999999999</v>
+        <v>-1.01</v>
       </c>
       <c r="D12" s="6">
-        <v>-7.77</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.09</v>
+        <v>0.48</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.49</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-6.14</v>
+        <v>-1.14</v>
       </c>
       <c r="D13" s="6">
-        <v>-4.92</v>
+        <v>-2.34</v>
       </c>
       <c r="E13" s="7">
-        <v>1.22</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.46</v>
+        <v>3.25</v>
       </c>
       <c r="D14" s="6">
-        <v>-5.88</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.58</v>
+        <v>4.32</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.07</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.64</v>
+        <v>-5.99</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.01</v>
-      </c>
-      <c r="E15" s="7">
-        <v>1.63</v>
+        <v>-5.54</v>
+      </c>
+      <c r="E15" s="8">
+        <v>0.45</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.01</v>
+        <v>-6.08</v>
       </c>
       <c r="D16" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.87</v>
+        <v>-5.47</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.61</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.95</v>
+        <v>6.31</v>
       </c>
       <c r="D17" s="6">
-        <v>3.25</v>
-      </c>
-      <c r="E17" s="7">
-        <v>5.2</v>
+        <v>6.78</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.47</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-7.21</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="D18" s="6">
-        <v>-5.99</v>
-      </c>
-      <c r="E18" s="7">
-        <v>1.22</v>
+        <v>-7.63</v>
+      </c>
+      <c r="E18" s="8">
+        <v>1.51</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-6.8</v>
+        <v>-5.68</v>
       </c>
       <c r="D19" s="6">
-        <v>-6.08</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.72</v>
+        <v>-4.21</v>
+      </c>
+      <c r="E19" s="8">
+        <v>1.47</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>6.44</v>
+        <v>-3.04</v>
       </c>
       <c r="D20" s="6">
-        <v>6.31</v>
+        <v>-2.18</v>
       </c>
       <c r="E20" s="8">
-        <v>-0.13</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-10.76</v>
+        <v>-1.81</v>
       </c>
       <c r="D21" s="6">
-        <v>-9.140000000000001</v>
+        <v>-3</v>
       </c>
       <c r="E21" s="7">
-        <v>1.62</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-6.56</v>
+        <v>-4.83</v>
       </c>
       <c r="D22" s="6">
-        <v>-5.68</v>
-      </c>
-      <c r="E22" s="7">
-        <v>0.88</v>
+        <v>-3.03</v>
+      </c>
+      <c r="E22" s="8">
+        <v>1.8</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-4.05</v>
+        <v>-1.65</v>
       </c>
       <c r="D23" s="6">
-        <v>-3.04</v>
+        <v>-1.71</v>
       </c>
       <c r="E23" s="7">
-        <v>1.01</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-2.3</v>
+        <v>-3.98</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.81</v>
+        <v>-5.03</v>
       </c>
       <c r="E24" s="7">
-        <v>0.49</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-7.13</v>
+        <v>-5.57</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.83</v>
-      </c>
-      <c r="E25" s="7">
-        <v>2.3</v>
+        <v>-4.42</v>
+      </c>
+      <c r="E25" s="8">
+        <v>1.15</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-3.27</v>
+        <v>-6.17</v>
       </c>
       <c r="D26" s="6">
-        <v>-1.65</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.62</v>
+        <v>-4.39</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.78</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-4.42</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D27" s="6">
-        <v>-3.98</v>
+        <v>-0.98</v>
       </c>
       <c r="E27" s="7">
-        <v>0.44</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>-7.78</v>
+        <v>-0.59</v>
       </c>
       <c r="D28" s="6">
-        <v>-5.57</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.21</v>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.66</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-6.62</v>
+        <v>-3.07</v>
       </c>
       <c r="D29" s="6">
-        <v>-6.17</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.45</v>
+        <v>-1.05</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2.02</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>-0.34</v>
+        <v>-1.14</v>
       </c>
       <c r="D30" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.41</v>
+        <v>-0.61</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.53</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-1.33</v>
+        <v>-2.55</v>
       </c>
       <c r="D31" s="6">
-        <v>-0.59</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.74</v>
+        <v>-0.49</v>
+      </c>
+      <c r="E31" s="8">
+        <v>2.06</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-3.34</v>
+        <v>-1.05</v>
       </c>
       <c r="D32" s="6">
-        <v>-3.07</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.27</v>
+        <v>1.05</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2.1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-1.1</v>
+        <v>1.13</v>
       </c>
       <c r="D33" s="6">
-        <v>-1.14</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.04</v>
+        <v>0.13</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.02</v>
+        <v>6.02</v>
       </c>
       <c r="D34" s="6">
-        <v>-2.55</v>
+        <v>8.69</v>
       </c>
       <c r="E34" s="8">
-        <v>-0.53</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>0.85</v>
+        <v>-1.77</v>
       </c>
       <c r="D35" s="6">
-        <v>1.13</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.28</v>
+        <v>-1.05</v>
+      </c>
+      <c r="E35" s="8">
+        <v>0.72</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>0.17</v>
+        <v>-2.49</v>
       </c>
       <c r="D36" s="6">
-        <v>6.02</v>
-      </c>
-      <c r="E36" s="7">
-        <v>5.85</v>
+        <v>-1.7</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.79</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.18</v>
+        <v>4.08</v>
       </c>
       <c r="D37" s="6">
-        <v>-1.77</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.59</v>
+        <v>3.98</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-2.22</v>
+        <v>-4.06</v>
       </c>
       <c r="D38" s="6">
-        <v>-2.49</v>
+        <v>-2.44</v>
       </c>
       <c r="E38" s="8">
-        <v>-0.27</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>4.12</v>
+        <v>-1.6</v>
       </c>
       <c r="D39" s="6">
-        <v>4.08</v>
+        <v>0.52</v>
       </c>
       <c r="E39" s="8">
-        <v>-0.04</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-4.38</v>
+        <v>1.73</v>
       </c>
       <c r="D40" s="6">
-        <v>-4.06</v>
+        <v>0.97</v>
       </c>
       <c r="E40" s="7">
-        <v>0.32</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>-1.99</v>
+        <v>-1.79</v>
       </c>
       <c r="D41" s="6">
-        <v>-1.6</v>
+        <v>-2.65</v>
       </c>
       <c r="E41" s="7">
-        <v>0.39</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>0.2</v>
+        <v>-0.9</v>
       </c>
       <c r="D42" s="6">
-        <v>1.73</v>
-      </c>
-      <c r="E42" s="7">
-        <v>1.53</v>
+        <v>0.02</v>
+      </c>
+      <c r="E42" s="8">
+        <v>0.92</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-0.15</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D43" s="6">
-        <v>-1.79</v>
+        <v>1.36</v>
       </c>
       <c r="E43" s="8">
-        <v>-1.64</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>-3.53</v>
+        <v>-1.49</v>
       </c>
       <c r="D44" s="6">
-        <v>-0.9</v>
+        <v>-2.47</v>
       </c>
       <c r="E44" s="7">
-        <v>2.63</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>-0.78</v>
+        <v>-1.04</v>
       </c>
       <c r="D45" s="6">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E45" s="7">
-        <v>1.47</v>
+        <v>0.85</v>
+      </c>
+      <c r="E45" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-0.55</v>
+        <v>-3.07</v>
       </c>
       <c r="D46" s="6">
-        <v>-1.49</v>
+        <v>-1.56</v>
       </c>
       <c r="E46" s="8">
-        <v>-0.9399999999999999</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>-0.64</v>
+        <v>0.85</v>
       </c>
       <c r="D47" s="6">
-        <v>-1.04</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-0.4</v>
+        <v>0.19</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48" s="6">
-        <v>-2.01</v>
+        <v>-5.09</v>
       </c>
       <c r="D48" s="6">
-        <v>-3.07</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-1.06</v>
+        <v>-6.33</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-1.24</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" s="6">
-        <v>1.51</v>
+        <v>-1.38</v>
       </c>
       <c r="D49" s="6">
-        <v>0.85</v>
+        <v>-0.92</v>
       </c>
       <c r="E49" s="8">
-        <v>-0.66</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>-6.29</v>
+        <v>-9.84</v>
       </c>
       <c r="D50" s="6">
-        <v>-5.09</v>
+        <v>-10.65</v>
       </c>
       <c r="E50" s="7">
-        <v>1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>-1.67</v>
+        <v>1.7</v>
       </c>
       <c r="D51" s="6">
-        <v>-1.38</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.29</v>
+        <v>3.21</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1.51</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-10.79</v>
+        <v>-18.92</v>
       </c>
       <c r="D52" s="6">
-        <v>-9.84</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.95</v>
+        <v>-17.77</v>
+      </c>
+      <c r="E52" s="8">
+        <v>1.15</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>1.92</v>
+        <v>-4.53</v>
       </c>
       <c r="D53" s="6">
-        <v>1.7</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-0.22</v>
+        <v>-6.6</v>
+      </c>
+      <c r="E53" s="7">
+        <v>-2.07</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-19.95</v>
+        <v>-12.13</v>
       </c>
       <c r="D54" s="6">
-        <v>-18.92</v>
+        <v>-13.11</v>
       </c>
       <c r="E54" s="7">
-        <v>1.03</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-5.75</v>
+        <v>-5.45</v>
       </c>
       <c r="D55" s="6">
-        <v>-4.53</v>
+        <v>-5.87</v>
       </c>
       <c r="E55" s="7">
-        <v>1.22</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-16.39</v>
+        <v>1.67</v>
       </c>
       <c r="D56" s="6">
-        <v>-12.13</v>
-      </c>
-      <c r="E56" s="7">
-        <v>4.26</v>
+        <v>3.2</v>
+      </c>
+      <c r="E56" s="8">
+        <v>1.53</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>-5.8</v>
+        <v>17.62</v>
       </c>
       <c r="D57" s="6">
-        <v>-5.45</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.35</v>
+        <v>17.88</v>
+      </c>
+      <c r="E57" s="8">
+        <v>0.26</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>1.28</v>
+        <v>-7.36</v>
       </c>
       <c r="D58" s="6">
-        <v>1.67</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0.39</v>
+        <v>-6.44</v>
+      </c>
+      <c r="E58" s="8">
+        <v>0.92</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>18.41</v>
+        <v>7.43</v>
       </c>
       <c r="D59" s="6">
-        <v>17.62</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-0.79</v>
+        <v>7.25</v>
+      </c>
+      <c r="E59" s="7">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>-7.42</v>
+        <v>19.85</v>
       </c>
       <c r="D60" s="6">
-        <v>-7.36</v>
+        <v>18.17</v>
       </c>
       <c r="E60" s="7">
-        <v>0.06</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>7.09</v>
+        <v>-5.27</v>
       </c>
       <c r="D61" s="6">
-        <v>7.43</v>
+        <v>-6.72</v>
       </c>
       <c r="E61" s="7">
-        <v>0.34</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>19.99</v>
+        <v>-8.69</v>
       </c>
       <c r="D62" s="6">
-        <v>19.85</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.14</v>
+        <v>-9.69</v>
+      </c>
+      <c r="E62" s="7">
+        <v>-1</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>-7.65</v>
+        <v>0.61</v>
       </c>
       <c r="D63" s="6">
-        <v>-5.27</v>
+        <v>-1.18</v>
       </c>
       <c r="E63" s="7">
-        <v>2.38</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-10.33</v>
+        <v>-4.35</v>
       </c>
       <c r="D64" s="6">
-        <v>-8.69</v>
+        <v>-5.59</v>
       </c>
       <c r="E64" s="7">
-        <v>1.64</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>0.51</v>
+        <v>-9.19</v>
       </c>
       <c r="D65" s="6">
-        <v>0.61</v>
-      </c>
-      <c r="E65" s="7">
-        <v>0.1</v>
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="E65" s="8">
+        <v>0.9</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-7.03</v>
+        <v>-5.71</v>
       </c>
       <c r="D66" s="6">
-        <v>-4.35</v>
+        <v>-6.23</v>
       </c>
       <c r="E66" s="7">
-        <v>2.68</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-9.82</v>
+        <v>-8.23</v>
       </c>
       <c r="D67" s="6">
-        <v>-9.19</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0.63</v>
+        <v>-7.31</v>
+      </c>
+      <c r="E67" s="8">
+        <v>0.92</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-7.23</v>
+        <v>-7.82</v>
       </c>
       <c r="D68" s="6">
-        <v>-5.71</v>
-      </c>
-      <c r="E68" s="7">
-        <v>1.52</v>
+        <v>-6.24</v>
+      </c>
+      <c r="E68" s="8">
+        <v>1.58</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-8.58</v>
+        <v>-4.93</v>
       </c>
       <c r="D69" s="6">
-        <v>-8.23</v>
+        <v>-6.54</v>
       </c>
       <c r="E69" s="7">
-        <v>0.35</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-9.619999999999999</v>
+        <v>3.85</v>
       </c>
       <c r="D70" s="6">
-        <v>-7.82</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.8</v>
+        <v>5.74</v>
+      </c>
+      <c r="E70" s="8">
+        <v>1.89</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-7.34</v>
+        <v>-4.42</v>
       </c>
       <c r="D71" s="6">
-        <v>-4.93</v>
+        <v>-5.21</v>
       </c>
       <c r="E71" s="7">
-        <v>2.41</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-2.3</v>
+        <v>-8.26</v>
       </c>
       <c r="D72" s="6">
-        <v>3.85</v>
-      </c>
-      <c r="E72" s="7">
-        <v>6.15</v>
+        <v>-8.109999999999999</v>
+      </c>
+      <c r="E72" s="8">
+        <v>0.15</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>-5.4</v>
+        <v>8.02</v>
       </c>
       <c r="D73" s="6">
-        <v>-4.42</v>
-      </c>
-      <c r="E73" s="7">
-        <v>0.98</v>
+        <v>9.15</v>
+      </c>
+      <c r="E73" s="8">
+        <v>1.13</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-9.4</v>
+        <v>-4.65</v>
       </c>
       <c r="D74" s="6">
-        <v>-8.26</v>
-      </c>
-      <c r="E74" s="7">
-        <v>1.14</v>
+        <v>-4.23</v>
+      </c>
+      <c r="E74" s="8">
+        <v>0.42</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>7.23</v>
+        <v>-7.32</v>
       </c>
       <c r="D75" s="6">
-        <v>8.02</v>
-      </c>
-      <c r="E75" s="7">
-        <v>0.79</v>
+        <v>-6.39</v>
+      </c>
+      <c r="E75" s="8">
+        <v>0.93</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-5.16</v>
+        <v>-1.94</v>
       </c>
       <c r="D76" s="6">
-        <v>-4.65</v>
+        <v>-2.61</v>
       </c>
       <c r="E76" s="7">
-        <v>0.51</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>-8.630000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="D77" s="6">
-        <v>-7.32</v>
+        <v>-1.03</v>
       </c>
       <c r="E77" s="7">
-        <v>1.31</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>-5.08</v>
+        <v>-9.66</v>
       </c>
       <c r="D78" s="6">
-        <v>-1.94</v>
+        <v>-10.09</v>
       </c>
       <c r="E78" s="7">
-        <v>3.14</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>1.7</v>
+        <v>-5.19</v>
       </c>
       <c r="D79" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-1.05</v>
+        <v>-5.44</v>
+      </c>
+      <c r="E79" s="7">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-13.56</v>
+        <v>-3.53</v>
       </c>
       <c r="D80" s="6">
-        <v>-9.66</v>
+        <v>-5.12</v>
       </c>
       <c r="E80" s="7">
-        <v>3.9</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-7.77</v>
+        <v>-0.8</v>
       </c>
       <c r="D81" s="6">
-        <v>-5.19</v>
-      </c>
-      <c r="E81" s="7">
-        <v>2.58</v>
+        <v>-0.4</v>
+      </c>
+      <c r="E81" s="8">
+        <v>0.4</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-2.75</v>
+        <v>-6.78</v>
       </c>
       <c r="D82" s="6">
-        <v>-3.53</v>
+        <v>-6.46</v>
       </c>
       <c r="E82" s="8">
-        <v>-0.78</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-3.1</v>
+        <v>-2.12</v>
       </c>
       <c r="D83" s="6">
-        <v>-0.8</v>
+        <v>-2.98</v>
       </c>
       <c r="E83" s="7">
-        <v>2.3</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C84" s="6">
-        <v>-7.85</v>
+        <v>-14.36</v>
       </c>
       <c r="D84" s="6">
-        <v>-6.78</v>
+        <v>-15.15</v>
       </c>
       <c r="E84" s="7">
-        <v>1.07</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C85" s="6">
-        <v>-3.66</v>
+        <v>-14.74</v>
       </c>
       <c r="D85" s="6">
-        <v>-2.12</v>
-      </c>
-      <c r="E85" s="7">
-        <v>1.54</v>
+        <v>-14.2</v>
+      </c>
+      <c r="E85" s="8">
+        <v>0.54</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="6">
-        <v>-15.39</v>
+        <v>-13.37</v>
       </c>
       <c r="D86" s="6">
-        <v>-14.36</v>
+        <v>-13.68</v>
       </c>
       <c r="E86" s="7">
-        <v>1.03</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-15.5</v>
+        <v>-13.39</v>
       </c>
       <c r="D87" s="6">
-        <v>-14.74</v>
-      </c>
-      <c r="E87" s="7">
-        <v>0.76</v>
+        <v>-12.12</v>
+      </c>
+      <c r="E87" s="8">
+        <v>1.27</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-14.37</v>
+        <v>-21.21</v>
       </c>
       <c r="D88" s="6">
-        <v>-13.37</v>
-      </c>
-      <c r="E88" s="7">
-        <v>1</v>
+        <v>-20.26</v>
+      </c>
+      <c r="E88" s="8">
+        <v>0.95</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-13.67</v>
+        <v>-11.36</v>
       </c>
       <c r="D89" s="6">
-        <v>-13.39</v>
+        <v>-12.35</v>
       </c>
       <c r="E89" s="7">
-        <v>0.28</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-22.3</v>
+        <v>-24.46</v>
       </c>
       <c r="D90" s="6">
-        <v>-21.21</v>
-      </c>
-      <c r="E90" s="7">
-        <v>1.09</v>
+        <v>-23.59</v>
+      </c>
+      <c r="E90" s="8">
+        <v>0.87</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-12.64</v>
+        <v>-9.08</v>
       </c>
       <c r="D91" s="6">
-        <v>-11.36</v>
+        <v>-9.48</v>
       </c>
       <c r="E91" s="7">
-        <v>1.28</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-28.21</v>
+        <v>-12.16</v>
       </c>
       <c r="D92" s="6">
-        <v>-24.46</v>
-      </c>
-      <c r="E92" s="7">
-        <v>3.75</v>
+        <v>-12.14</v>
+      </c>
+      <c r="E92" s="8">
+        <v>0.02</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-9.73</v>
+        <v>-11.88</v>
       </c>
       <c r="D93" s="6">
-        <v>-9.08</v>
+        <v>-12.48</v>
       </c>
       <c r="E93" s="7">
-        <v>0.65</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-12.96</v>
+        <v>-14.58</v>
       </c>
       <c r="D94" s="6">
-        <v>-12.16</v>
-      </c>
-      <c r="E94" s="7">
-        <v>0.8</v>
+        <v>-13.8</v>
+      </c>
+      <c r="E94" s="8">
+        <v>0.78</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-12.88</v>
+        <v>-17.54</v>
       </c>
       <c r="D95" s="6">
-        <v>-11.88</v>
-      </c>
-      <c r="E95" s="7">
-        <v>1</v>
+        <v>-17.33</v>
+      </c>
+      <c r="E95" s="8">
+        <v>0.21</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-15.49</v>
+        <v>-4.09</v>
       </c>
       <c r="D96" s="6">
-        <v>-14.58</v>
+        <v>-5.33</v>
       </c>
       <c r="E96" s="7">
-        <v>0.91</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-18.72</v>
+        <v>-14.32</v>
       </c>
       <c r="D97" s="6">
-        <v>-17.54</v>
+        <v>-15.06</v>
       </c>
       <c r="E97" s="7">
-        <v>1.18</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-4.07</v>
+        <v>-13.66</v>
       </c>
       <c r="D98" s="6">
-        <v>-4.09</v>
+        <v>-13.62</v>
       </c>
       <c r="E98" s="8">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-16.37</v>
+        <v>-6.38</v>
       </c>
       <c r="D99" s="6">
-        <v>-14.32</v>
+        <v>-7.55</v>
       </c>
       <c r="E99" s="7">
-        <v>2.05</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-15.42</v>
+        <v>-7.48</v>
       </c>
       <c r="D100" s="6">
-        <v>-13.66</v>
-      </c>
-      <c r="E100" s="7">
-        <v>1.76</v>
+        <v>-7.05</v>
+      </c>
+      <c r="E100" s="8">
+        <v>0.43</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-6.46</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="D101" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="E101" s="7">
-        <v>0.08</v>
+        <v>-8.02</v>
+      </c>
+      <c r="E101" s="8">
+        <v>0.95</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-8.77</v>
+        <v>-6.38</v>
       </c>
       <c r="D102" s="6">
-        <v>-7.48</v>
+        <v>-6.92</v>
       </c>
       <c r="E102" s="7">
-        <v>1.29</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C103" s="6">
-        <v>-9.41</v>
+        <v>25391.85</v>
       </c>
       <c r="D103" s="6">
-        <v>-8.970000000000001</v>
+        <v>25156.75</v>
       </c>
       <c r="E103" s="7">
-        <v>0.44</v>
+        <v>-235.1</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C104" s="6">
-        <v>-7.08</v>
+        <v>8955.450000000001</v>
       </c>
       <c r="D104" s="6">
-        <v>-6.38</v>
-      </c>
-      <c r="E104" s="7">
-        <v>0.7</v>
+        <v>9011.299999999999</v>
+      </c>
+      <c r="E104" s="8">
+        <v>55.85</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C105" s="6">
-        <v>25084.4</v>
+        <v>10948.6</v>
       </c>
       <c r="D105" s="6">
-        <v>25391.85</v>
+        <v>10910</v>
       </c>
       <c r="E105" s="7">
-        <v>307.45</v>
+        <v>-38.6</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>8875.5</v>
+        <v>35975.9</v>
       </c>
       <c r="D106" s="6">
-        <v>8955.450000000001</v>
-      </c>
-      <c r="E106" s="7">
-        <v>79.95</v>
+        <v>36503.5</v>
+      </c>
+      <c r="E106" s="8">
+        <v>527.6</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>10823.25</v>
+        <v>44731.15</v>
       </c>
       <c r="D107" s="6">
-        <v>10948.6</v>
-      </c>
-      <c r="E107" s="7">
-        <v>125.35</v>
+        <v>45271.7</v>
+      </c>
+      <c r="E107" s="8">
+        <v>540.55</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>35857.15</v>
+        <v>25228.55</v>
       </c>
       <c r="D108" s="6">
-        <v>35975.9</v>
+        <v>24948.7</v>
       </c>
       <c r="E108" s="7">
-        <v>118.75</v>
+        <v>-279.85</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>44113.4</v>
+        <v>29830.1</v>
       </c>
       <c r="D109" s="6">
-        <v>44731.15</v>
-      </c>
-      <c r="E109" s="7">
-        <v>617.75</v>
+        <v>30171</v>
+      </c>
+      <c r="E109" s="8">
+        <v>340.9</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>24866.35</v>
+        <v>15149.7</v>
       </c>
       <c r="D110" s="6">
-        <v>25228.55</v>
+        <v>15083.55</v>
       </c>
       <c r="E110" s="7">
-        <v>362.2</v>
+        <v>-66.15000000000001</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>28349.6</v>
+        <v>8578.5</v>
       </c>
       <c r="D111" s="6">
-        <v>29830.1</v>
-      </c>
-      <c r="E111" s="7">
-        <v>1480.5</v>
+        <v>8580.299999999999</v>
+      </c>
+      <c r="E111" s="8">
+        <v>1.8</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>15041.5</v>
+        <v>1631.7</v>
       </c>
       <c r="D112" s="6">
-        <v>15149.7</v>
-      </c>
-      <c r="E112" s="7">
-        <v>108.2</v>
+        <v>1641.35</v>
+      </c>
+      <c r="E112" s="8">
+        <v>9.65</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>8499.65</v>
+        <v>12088.25</v>
       </c>
       <c r="D113" s="6">
-        <v>8578.5</v>
+        <v>12006.75</v>
       </c>
       <c r="E113" s="7">
-        <v>78.84999999999999</v>
+        <v>-81.5</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>1624.8</v>
+        <v>9196.6</v>
       </c>
       <c r="D114" s="6">
-        <v>1631.7</v>
-      </c>
-      <c r="E114" s="7">
-        <v>6.9</v>
+        <v>9280.799999999999</v>
+      </c>
+      <c r="E114" s="8">
+        <v>84.2</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>11951.15</v>
+        <v>8146.55</v>
       </c>
       <c r="D115" s="6">
-        <v>12088.25</v>
-      </c>
-      <c r="E115" s="7">
-        <v>137.1</v>
+        <v>8167.55</v>
+      </c>
+      <c r="E115" s="8">
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>9098.6</v>
+        <v>26075</v>
       </c>
       <c r="D116" s="6">
-        <v>9196.6</v>
+        <v>25736.95</v>
       </c>
       <c r="E116" s="7">
-        <v>98</v>
+        <v>-338.05</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>8030.65</v>
+        <v>829.95</v>
       </c>
       <c r="D117" s="6">
-        <v>8146.55</v>
+        <v>822.8</v>
       </c>
       <c r="E117" s="7">
-        <v>115.9</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>26078.85</v>
+        <v>29443</v>
       </c>
       <c r="D118" s="6">
-        <v>26075</v>
+        <v>29455.4</v>
       </c>
       <c r="E118" s="8">
-        <v>-3.85</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>810.05</v>
+        <v>15860.65</v>
       </c>
       <c r="D119" s="6">
-        <v>829.95</v>
+        <v>15663</v>
       </c>
       <c r="E119" s="7">
-        <v>19.9</v>
+        <v>-197.65</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>28842.95</v>
+        <v>9250.5</v>
       </c>
       <c r="D120" s="6">
-        <v>29443</v>
-      </c>
-      <c r="E120" s="7">
-        <v>600.05</v>
+        <v>9294.1</v>
+      </c>
+      <c r="E120" s="8">
+        <v>43.6</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>15847.7</v>
+        <v>10349.6</v>
       </c>
       <c r="D121" s="6">
-        <v>15860.65</v>
-      </c>
-      <c r="E121" s="7">
-        <v>12.95</v>
+        <v>10456.75</v>
+      </c>
+      <c r="E121" s="8">
+        <v>107.15</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>9122.1</v>
+        <v>27324.35</v>
       </c>
       <c r="D122" s="6">
-        <v>9250.5</v>
+        <v>27166.8</v>
       </c>
       <c r="E122" s="7">
-        <v>128.4</v>
+        <v>-157.55</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C123" s="6">
-        <v>10299.4</v>
+        <v>50</v>
       </c>
       <c r="D123" s="6">
-        <v>10349.6</v>
+        <v>38</v>
       </c>
       <c r="E123" s="7">
-        <v>50.2</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C124" s="6">
-        <v>27122.9</v>
+        <v>44</v>
       </c>
       <c r="D124" s="6">
-        <v>27324.35</v>
-      </c>
-      <c r="E124" s="7">
-        <v>201.45</v>
+        <v>56</v>
+      </c>
+      <c r="E124" s="8">
+        <v>12</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>14</v>
@@ -5447,100 +5411,100 @@
         <v>56</v>
       </c>
       <c r="D125" s="6">
-        <v>44</v>
-      </c>
-      <c r="E125" s="8">
-        <v>-12</v>
+        <v>50</v>
+      </c>
+      <c r="E125" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="6">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D126" s="6">
-        <v>13</v>
-      </c>
-      <c r="E126" s="8">
+        <v>26</v>
+      </c>
+      <c r="E126" s="7">
         <v>-6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="D127" s="6">
-        <v>62</v>
+        <v>99</v>
       </c>
       <c r="E127" s="8">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="D128" s="6">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E128" s="8">
-        <v>-6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="D129" s="6">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="E129" s="7">
-        <v>36</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C130" s="6">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D130" s="6">
-        <v>32</v>
-      </c>
-      <c r="E130" s="8">
-        <v>-12</v>
+        <v>19</v>
+      </c>
+      <c r="E130" s="7">
+        <v>-7</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
@@ -5549,390 +5513,356 @@
         <v>38</v>
       </c>
       <c r="D131" s="6">
-        <v>19</v>
-      </c>
-      <c r="E131" s="8">
-        <v>-19</v>
+        <v>32</v>
+      </c>
+      <c r="E131" s="7">
+        <v>-6</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C132" s="6">
-        <v>13</v>
+        <v>36.09</v>
       </c>
       <c r="D132" s="6">
-        <v>26</v>
+        <v>33.85</v>
       </c>
       <c r="E132" s="7">
-        <v>13</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C133" s="6">
-        <v>26</v>
+        <v>32.02</v>
       </c>
       <c r="D133" s="6">
-        <v>38</v>
-      </c>
-      <c r="E133" s="7">
-        <v>12</v>
+        <v>35.43</v>
+      </c>
+      <c r="E133" s="8">
+        <v>3.41</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="6">
-        <v>30.51</v>
+        <v>38.93</v>
       </c>
       <c r="D134" s="6">
-        <v>36.09</v>
+        <v>37.84</v>
       </c>
       <c r="E134" s="7">
-        <v>5.58</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>26.87</v>
+        <v>33.76</v>
       </c>
       <c r="D135" s="6">
-        <v>32.02</v>
-      </c>
-      <c r="E135" s="7">
-        <v>5.15</v>
+        <v>43.23</v>
+      </c>
+      <c r="E135" s="8">
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>33.12</v>
+        <v>45.4</v>
       </c>
       <c r="D136" s="6">
-        <v>38.93</v>
-      </c>
-      <c r="E136" s="7">
-        <v>5.81</v>
+        <v>49.5</v>
+      </c>
+      <c r="E136" s="8">
+        <v>4.1</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>31.37</v>
+        <v>50.35</v>
       </c>
       <c r="D137" s="6">
-        <v>33.76</v>
+        <v>45.11</v>
       </c>
       <c r="E137" s="7">
-        <v>2.39</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>40.24</v>
+        <v>60.51</v>
       </c>
       <c r="D138" s="6">
-        <v>45.4</v>
-      </c>
-      <c r="E138" s="7">
-        <v>5.16</v>
+        <v>63.13</v>
+      </c>
+      <c r="E138" s="8">
+        <v>2.62</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>42.29</v>
+        <v>36.98</v>
       </c>
       <c r="D139" s="6">
-        <v>50.35</v>
+        <v>35.6</v>
       </c>
       <c r="E139" s="7">
-        <v>8.06</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>44.58</v>
+        <v>35.88</v>
       </c>
       <c r="D140" s="6">
-        <v>60.51</v>
-      </c>
-      <c r="E140" s="7">
-        <v>15.93</v>
+        <v>35.99</v>
+      </c>
+      <c r="E140" s="8">
+        <v>0.11</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>33.04</v>
+        <v>62.48</v>
       </c>
       <c r="D141" s="6">
-        <v>36.98</v>
-      </c>
-      <c r="E141" s="7">
-        <v>3.94</v>
+        <v>63.79</v>
+      </c>
+      <c r="E141" s="8">
+        <v>1.31</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>30.72</v>
+        <v>36.52</v>
       </c>
       <c r="D142" s="6">
-        <v>35.88</v>
+        <v>35.15</v>
       </c>
       <c r="E142" s="7">
-        <v>5.16</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>61.56</v>
+        <v>38.01</v>
       </c>
       <c r="D143" s="6">
-        <v>62.48</v>
-      </c>
-      <c r="E143" s="7">
-        <v>0.92</v>
+        <v>43.24</v>
+      </c>
+      <c r="E143" s="8">
+        <v>5.23</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>32.41</v>
+        <v>47.26</v>
       </c>
       <c r="D144" s="6">
-        <v>36.52</v>
-      </c>
-      <c r="E144" s="7">
-        <v>4.11</v>
+        <v>48.34</v>
+      </c>
+      <c r="E144" s="8">
+        <v>1.08</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>31.14</v>
+        <v>42.9</v>
       </c>
       <c r="D145" s="6">
-        <v>38.01</v>
+        <v>37.94</v>
       </c>
       <c r="E145" s="7">
-        <v>6.87</v>
+        <v>-4.96</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>40.95</v>
+        <v>44.63</v>
       </c>
       <c r="D146" s="6">
-        <v>47.26</v>
+        <v>42.62</v>
       </c>
       <c r="E146" s="7">
-        <v>6.31</v>
+        <v>-2.01</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>42.96</v>
+        <v>47.47</v>
       </c>
       <c r="D147" s="6">
-        <v>42.9</v>
+        <v>47.69</v>
       </c>
       <c r="E147" s="8">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>36.94</v>
+        <v>36.95</v>
       </c>
       <c r="D148" s="6">
-        <v>44.63</v>
+        <v>32.82</v>
       </c>
       <c r="E148" s="7">
-        <v>7.69</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>35</v>
+        <v>47.29</v>
       </c>
       <c r="D149" s="6">
-        <v>47.47</v>
-      </c>
-      <c r="E149" s="7">
-        <v>12.47</v>
+        <v>48.84</v>
+      </c>
+      <c r="E149" s="8">
+        <v>1.55</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>36.46</v>
+        <v>31.63</v>
       </c>
       <c r="D150" s="6">
-        <v>36.95</v>
-      </c>
-      <c r="E150" s="7">
-        <v>0.49</v>
+        <v>38.25</v>
+      </c>
+      <c r="E150" s="8">
+        <v>6.62</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>42.52</v>
+        <v>53.97</v>
       </c>
       <c r="D151" s="6">
-        <v>47.29</v>
+        <v>50.53</v>
       </c>
       <c r="E151" s="7">
-        <v>4.77</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C152" s="6">
-        <v>28.28</v>
-      </c>
-      <c r="D152" s="6">
-        <v>31.63</v>
-      </c>
-      <c r="E152" s="7">
-        <v>3.35</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C153" s="6">
-        <v>49.93</v>
-      </c>
-      <c r="D153" s="6">
-        <v>53.97</v>
-      </c>
-      <c r="E153" s="7">
-        <v>4.04</v>
+        <v>-3.44</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5956,28 +5886,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5985,22 +5915,22 @@
         <v>78</v>
       </c>
       <c r="B2" s="11">
-        <v>39.24</v>
+        <v>35.24</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>43</v>
+        <v>43.4</v>
       </c>
       <c r="E2" s="11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.6</v>
+        <v>-3</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.1</v>
+        <v>-4.2</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -6126,10 +6056,10 @@
         <v>46</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>52</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>39</v>
@@ -6140,34 +6070,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.25</v>
+        <v>0.2463</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1643</v>
+        <v>0.1635</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1632</v>
+        <v>0.1617</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1537</v>
+        <v>0.1481</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1218</v>
+        <v>0.1181</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1047</v>
+        <v>0.1024</v>
       </c>
       <c r="G2" s="14">
-        <v>0.09279999999999999</v>
+        <v>0.101</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0866</v>
+        <v>0.0882</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0832</v>
+        <v>0.0824</v>
       </c>
       <c r="J2" s="14">
-        <v>0.079</v>
+        <v>0.08070000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6181,10 +6111,10 @@
         <v>43</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>42</v>
@@ -6204,34 +6134,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.07780000000000001</v>
+        <v>0.0762</v>
       </c>
       <c r="B4" s="14">
-        <v>0.06320000000000001</v>
+        <v>0.0584</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0623</v>
+        <v>0.0566</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0602</v>
+        <v>0.0302</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0327</v>
+        <v>0.0212</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0168</v>
+        <v>0.0182</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.033</v>
+        <v>-0.0333</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0684</v>
+        <v>-0.0693</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.09420000000000001</v>
+        <v>-0.1051</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.1683</v>
+        <v>-0.1414</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="112">
   <si>
     <t>Symbol</t>
   </si>
@@ -262,6 +262,9 @@
     <t>No</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>DOWN</t>
   </si>
   <si>
@@ -289,28 +292,31 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>50.4 → 45.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>50.4</t>
+    <t>45.1 → 52.9</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
   </si>
   <si>
     <t>45.1</t>
   </si>
   <si>
-    <t>50 DMA &gt; 200 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 DEATH CROSS</t>
-  </si>
-  <si>
-    <t>Yes</t>
+    <t>52.9</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>47.7 → 56.4</t>
+  </si>
+  <si>
+    <t>47.7</t>
+  </si>
+  <si>
+    <t>56.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -396,14 +402,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -436,13 +442,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1040,10 +1046,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>25156.75</v>
+        <v>25576.4</v>
       </c>
       <c r="E2">
-        <v>-0.93</v>
+        <v>1.67</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1052,43 +1058,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-15.15</v>
+        <v>-13.73</v>
       </c>
       <c r="I2">
-        <v>5.84</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>0.07000000000000001</v>
+        <v>4.34</v>
       </c>
       <c r="K2">
-        <v>-7.87</v>
+        <v>-4.41</v>
       </c>
       <c r="L2">
-        <v>-5.59</v>
+        <v>-4.45</v>
       </c>
       <c r="M2">
-        <v>-6.33</v>
+        <v>-5.04</v>
       </c>
       <c r="N2">
-        <v>16.35</v>
+        <v>16.74</v>
       </c>
       <c r="O2">
         <v>38</v>
       </c>
       <c r="Q2">
-        <v>25001.12</v>
+        <v>25213.86</v>
       </c>
       <c r="R2">
-        <v>26088.02</v>
+        <v>26022.16</v>
       </c>
       <c r="S2">
-        <v>27657.88</v>
+        <v>27588.58</v>
       </c>
       <c r="T2">
-        <v>26981.11</v>
+        <v>26969.56</v>
       </c>
       <c r="U2">
-        <v>-6.76</v>
+        <v>-5.17</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1103,40 +1109,40 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>33.85</v>
+        <v>40.91</v>
       </c>
       <c r="AA2">
-        <v>-729.66</v>
+        <v>-671.3099999999999</v>
       </c>
       <c r="AB2">
-        <v>-693.26</v>
+        <v>-688.87</v>
       </c>
       <c r="AC2">
-        <v>-36.4</v>
+        <v>17.56</v>
       </c>
       <c r="AD2">
-        <v>85.66</v>
+        <v>95.69</v>
       </c>
       <c r="AE2">
-        <v>64.94</v>
+        <v>84.19</v>
       </c>
       <c r="AF2">
-        <v>431.54</v>
+        <v>437.18</v>
       </c>
       <c r="AH2">
-        <v>27927.01</v>
+        <v>27833.81</v>
       </c>
       <c r="AI2">
-        <v>24249.03</v>
+        <v>24210.51</v>
       </c>
       <c r="AJ2">
         <v>26008.9</v>
       </c>
       <c r="AK2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL2">
-        <v>73.52</v>
+        <v>68.68000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1150,10 +1156,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9011.299999999999</v>
+        <v>9069.450000000001</v>
       </c>
       <c r="E3">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1162,43 +1168,43 @@
         <v>8851.4</v>
       </c>
       <c r="H3">
-        <v>-14.2</v>
+        <v>-13.65</v>
       </c>
       <c r="I3">
-        <v>1.81</v>
+        <v>2.46</v>
       </c>
       <c r="J3">
-        <v>-1.05</v>
+        <v>2.46</v>
       </c>
       <c r="K3">
-        <v>-5.93</v>
+        <v>-3.59</v>
       </c>
       <c r="L3">
-        <v>-8.289999999999999</v>
+        <v>-7.62</v>
       </c>
       <c r="M3">
-        <v>-0.92</v>
+        <v>-0.31</v>
       </c>
       <c r="N3">
-        <v>8.24</v>
+        <v>7.96</v>
       </c>
       <c r="O3">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="Q3">
-        <v>8923.41</v>
+        <v>8967.02</v>
       </c>
       <c r="R3">
-        <v>9279.33</v>
+        <v>9260.700000000001</v>
       </c>
       <c r="S3">
-        <v>9594.84</v>
+        <v>9577.66</v>
       </c>
       <c r="T3">
-        <v>9768.18</v>
+        <v>9767.09</v>
       </c>
       <c r="U3">
-        <v>-7.75</v>
+        <v>-7.14</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1213,40 +1219,40 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>35.43</v>
+        <v>38.88</v>
       </c>
       <c r="AA3">
-        <v>-195.94</v>
+        <v>-184.28</v>
       </c>
       <c r="AB3">
-        <v>-169.53</v>
+        <v>-172.48</v>
       </c>
       <c r="AC3">
-        <v>-26.41</v>
+        <v>-11.8</v>
       </c>
       <c r="AD3">
-        <v>38.24</v>
+        <v>61.06</v>
       </c>
       <c r="AE3">
-        <v>24.23</v>
+        <v>40.82</v>
       </c>
       <c r="AF3">
-        <v>129.55</v>
+        <v>130.7</v>
       </c>
       <c r="AH3">
-        <v>9799.129999999999</v>
+        <v>9782.639999999999</v>
       </c>
       <c r="AI3">
-        <v>8759.530000000001</v>
+        <v>8738.75</v>
       </c>
       <c r="AJ3">
         <v>9261.98</v>
       </c>
       <c r="AK3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL3">
-        <v>58.08</v>
+        <v>53.3</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1260,10 +1266,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>10910</v>
+        <v>11005.25</v>
       </c>
       <c r="E4">
-        <v>-0.35</v>
+        <v>0.87</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1272,43 +1278,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-13.68</v>
+        <v>-12.93</v>
       </c>
       <c r="I4">
-        <v>5.57</v>
+        <v>6.49</v>
       </c>
       <c r="J4">
-        <v>-0.61</v>
+        <v>2.46</v>
       </c>
       <c r="K4">
-        <v>-4.8</v>
+        <v>-2.46</v>
       </c>
       <c r="L4">
-        <v>-6.23</v>
+        <v>-5.62</v>
       </c>
       <c r="M4">
-        <v>-10.65</v>
+        <v>-9.98</v>
       </c>
       <c r="N4">
-        <v>7.62</v>
+        <v>7.93</v>
       </c>
       <c r="O4">
         <v>13</v>
       </c>
       <c r="Q4">
-        <v>10865.3</v>
+        <v>10918.11</v>
       </c>
       <c r="R4">
-        <v>11162.22</v>
+        <v>11144.4</v>
       </c>
       <c r="S4">
-        <v>11606.8</v>
+        <v>11582.72</v>
       </c>
       <c r="T4">
-        <v>11530.05</v>
+        <v>11523.66</v>
       </c>
       <c r="U4">
-        <v>-5.38</v>
+        <v>-4.5</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1323,40 +1329,40 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>37.84</v>
+        <v>42.15</v>
       </c>
       <c r="AA4">
-        <v>-205.41</v>
+        <v>-190.08</v>
       </c>
       <c r="AB4">
-        <v>-199.15</v>
+        <v>-197.33</v>
       </c>
       <c r="AC4">
-        <v>-6.26</v>
+        <v>7.25</v>
       </c>
       <c r="AD4">
-        <v>75.38</v>
+        <v>91.22</v>
       </c>
       <c r="AE4">
-        <v>62</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="AF4">
-        <v>141.38</v>
+        <v>142.45</v>
       </c>
       <c r="AH4">
-        <v>11693.58</v>
+        <v>11671.49</v>
       </c>
       <c r="AI4">
-        <v>10630.85</v>
+        <v>10617.3</v>
       </c>
       <c r="AJ4">
         <v>11255.06</v>
       </c>
       <c r="AK4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL4">
-        <v>57.95</v>
+        <v>53.73</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1370,10 +1376,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>36503.5</v>
+        <v>36213.7</v>
       </c>
       <c r="E5">
-        <v>1.47</v>
+        <v>-0.79</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1382,43 +1388,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-12.12</v>
+        <v>-12.81</v>
       </c>
       <c r="I5">
-        <v>10.29</v>
+        <v>9.41</v>
       </c>
       <c r="J5">
-        <v>-0.49</v>
+        <v>1.58</v>
       </c>
       <c r="K5">
-        <v>-3.77</v>
+        <v>-2.51</v>
       </c>
       <c r="L5">
-        <v>-7.31</v>
+        <v>-7.96</v>
       </c>
       <c r="M5">
-        <v>3.21</v>
+        <v>2.1</v>
       </c>
       <c r="N5">
-        <v>8.07</v>
+        <v>7.58</v>
       </c>
       <c r="O5">
         <v>62</v>
       </c>
       <c r="Q5">
-        <v>35954.47</v>
+        <v>36067.35</v>
       </c>
       <c r="R5">
-        <v>36831.93</v>
+        <v>36783.44</v>
       </c>
       <c r="S5">
-        <v>37708.02</v>
+        <v>37655.96</v>
       </c>
       <c r="T5">
-        <v>37722.7</v>
+        <v>37728.64</v>
       </c>
       <c r="U5">
-        <v>-3.23</v>
+        <v>-4.02</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1433,40 +1439,40 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>43.23</v>
+        <v>39.86</v>
       </c>
       <c r="AA5">
-        <v>-506.39</v>
+        <v>-486.19</v>
       </c>
       <c r="AB5">
-        <v>-479.04</v>
+        <v>-480.47</v>
       </c>
       <c r="AC5">
-        <v>-27.35</v>
+        <v>-5.72</v>
       </c>
       <c r="AD5">
-        <v>54.33</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="AE5">
-        <v>31.18</v>
+        <v>50.96</v>
       </c>
       <c r="AF5">
-        <v>494.39</v>
+        <v>493.38</v>
       </c>
       <c r="AH5">
-        <v>38232.99</v>
+        <v>38200.32</v>
       </c>
       <c r="AI5">
-        <v>35430.87</v>
+        <v>35366.57</v>
       </c>
       <c r="AJ5">
         <v>37083.58</v>
       </c>
       <c r="AK5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL5">
-        <v>40.67</v>
+        <v>37.89</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1480,10 +1486,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>45271.7</v>
+        <v>44791.65</v>
       </c>
       <c r="E6">
-        <v>1.21</v>
+        <v>-1.06</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1492,43 +1498,43 @@
         <v>43789.85</v>
       </c>
       <c r="H6">
-        <v>-20.26</v>
+        <v>-21.1</v>
       </c>
       <c r="I6">
-        <v>3.38</v>
+        <v>2.29</v>
       </c>
       <c r="J6">
-        <v>1.05</v>
+        <v>2.04</v>
       </c>
       <c r="K6">
-        <v>0.48</v>
+        <v>-0.09</v>
       </c>
       <c r="L6">
-        <v>-6.24</v>
+        <v>-7.47</v>
       </c>
       <c r="M6">
-        <v>-17.77</v>
+        <v>-18.21</v>
       </c>
       <c r="N6">
-        <v>1.82</v>
+        <v>1.51</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>44575.71</v>
+        <v>44754.43</v>
       </c>
       <c r="R6">
-        <v>45096.73</v>
+        <v>45058.36</v>
       </c>
       <c r="S6">
-        <v>46426.98</v>
+        <v>46332.27</v>
       </c>
       <c r="T6">
-        <v>49267.27</v>
+        <v>49215.92</v>
       </c>
       <c r="U6">
-        <v>-8.109999999999999</v>
+        <v>-8.99</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1543,40 +1549,40 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>49.5</v>
+        <v>46.18</v>
       </c>
       <c r="AA6">
-        <v>-468.37</v>
+        <v>-436.86</v>
       </c>
       <c r="AB6">
-        <v>-562.23</v>
+        <v>-537.16</v>
       </c>
       <c r="AC6">
-        <v>93.87</v>
+        <v>100.3</v>
       </c>
       <c r="AD6">
-        <v>81.62</v>
+        <v>89.87</v>
       </c>
       <c r="AE6">
-        <v>72.70999999999999</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="AF6">
-        <v>701.16</v>
+        <v>721.9</v>
       </c>
       <c r="AH6">
-        <v>46489</v>
+        <v>46439.24</v>
       </c>
       <c r="AI6">
-        <v>43704.45</v>
+        <v>43677.48</v>
       </c>
       <c r="AJ6">
         <v>45688.38</v>
       </c>
       <c r="AK6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL6">
-        <v>36.26</v>
+        <v>32.86</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1590,10 +1596,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>24948.7</v>
+        <v>25364.2</v>
       </c>
       <c r="E7">
-        <v>-1.11</v>
+        <v>1.67</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1602,43 +1608,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-12.35</v>
+        <v>-10.89</v>
       </c>
       <c r="I7">
-        <v>6.07</v>
+        <v>7.83</v>
       </c>
       <c r="J7">
-        <v>0.13</v>
+        <v>2.94</v>
       </c>
       <c r="K7">
-        <v>-2.34</v>
+        <v>1.15</v>
       </c>
       <c r="L7">
-        <v>-6.54</v>
+        <v>-4.49</v>
       </c>
       <c r="M7">
-        <v>-6.6</v>
+        <v>-5.28</v>
       </c>
       <c r="N7">
-        <v>5.66</v>
+        <v>5.92</v>
       </c>
       <c r="O7">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Q7">
-        <v>24930.51</v>
+        <v>25075.26</v>
       </c>
       <c r="R7">
-        <v>25017.22</v>
+        <v>25022.31</v>
       </c>
       <c r="S7">
-        <v>25692.98</v>
+        <v>25663.37</v>
       </c>
       <c r="T7">
-        <v>26315.67</v>
+        <v>26305.1</v>
       </c>
       <c r="U7">
-        <v>-5.19</v>
+        <v>-3.58</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1653,40 +1659,40 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>45.11</v>
+        <v>52.94</v>
       </c>
       <c r="AA7">
-        <v>-218.99</v>
+        <v>-170.26</v>
       </c>
       <c r="AB7">
-        <v>-283.58</v>
+        <v>-260.92</v>
       </c>
       <c r="AC7">
-        <v>64.59</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="AD7">
-        <v>87.38</v>
+        <v>91.64</v>
       </c>
       <c r="AE7">
-        <v>86.67</v>
+        <v>91.59</v>
       </c>
       <c r="AF7">
-        <v>336.34</v>
+        <v>346.09</v>
       </c>
       <c r="AH7">
-        <v>25680.03</v>
+        <v>25694.54</v>
       </c>
       <c r="AI7">
-        <v>24354.41</v>
+        <v>24350.08</v>
       </c>
       <c r="AJ7">
         <v>25420.21</v>
       </c>
       <c r="AK7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL7">
-        <v>26.33</v>
+        <v>26.01</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1700,10 +1706,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>30171</v>
+        <v>30719.8</v>
       </c>
       <c r="E8">
-        <v>1.14</v>
+        <v>1.82</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1712,43 +1718,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-23.59</v>
+        <v>-22.2</v>
       </c>
       <c r="I8">
-        <v>17.08</v>
+        <v>19.21</v>
       </c>
       <c r="J8">
-        <v>8.69</v>
+        <v>10.76</v>
       </c>
       <c r="K8">
-        <v>4.32</v>
+        <v>3.94</v>
       </c>
       <c r="L8">
-        <v>5.74</v>
+        <v>6.95</v>
       </c>
       <c r="M8">
-        <v>-13.11</v>
+        <v>-11.49</v>
       </c>
       <c r="N8">
-        <v>-3.33</v>
+        <v>-3.29</v>
       </c>
       <c r="O8">
         <v>68</v>
       </c>
       <c r="Q8">
-        <v>28932.44</v>
+        <v>29529.08</v>
       </c>
       <c r="R8">
-        <v>28491.92</v>
+        <v>28573.52</v>
       </c>
       <c r="S8">
-        <v>29818.64</v>
+        <v>29803.95</v>
       </c>
       <c r="T8">
-        <v>31025.61</v>
+        <v>30981.77</v>
       </c>
       <c r="U8">
-        <v>-2.75</v>
+        <v>-0.85</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1763,40 +1769,40 @@
         <v>0</v>
       </c>
       <c r="Z8">
-        <v>63.13</v>
+        <v>66.95</v>
       </c>
       <c r="AA8">
-        <v>-140.92</v>
+        <v>25.65</v>
       </c>
       <c r="AB8">
-        <v>-414.01</v>
+        <v>-326.08</v>
       </c>
       <c r="AC8">
-        <v>273.1</v>
+        <v>351.73</v>
       </c>
       <c r="AD8">
-        <v>95.44</v>
+        <v>100</v>
       </c>
       <c r="AE8">
-        <v>89.81</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="AF8">
-        <v>679.74</v>
+        <v>693.13</v>
       </c>
       <c r="AH8">
-        <v>29842.82</v>
+        <v>30236.99</v>
       </c>
       <c r="AI8">
-        <v>27141.01</v>
+        <v>26910.05</v>
       </c>
       <c r="AJ8">
-        <v>28089.09</v>
+        <v>28684.46</v>
       </c>
       <c r="AK8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL8">
-        <v>31.89</v>
+        <v>37.24</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1810,10 +1816,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15083.55</v>
+        <v>15121.1</v>
       </c>
       <c r="E9">
-        <v>-0.44</v>
+        <v>0.25</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1822,31 +1828,31 @@
         <v>14845.15</v>
       </c>
       <c r="H9">
-        <v>-9.48</v>
+        <v>-9.25</v>
       </c>
       <c r="I9">
-        <v>1.61</v>
+        <v>1.86</v>
       </c>
       <c r="J9">
-        <v>-1.05</v>
+        <v>1.86</v>
       </c>
       <c r="K9">
-        <v>-5.54</v>
+        <v>-2.97</v>
       </c>
       <c r="L9">
-        <v>-5.21</v>
+        <v>-5.22</v>
       </c>
       <c r="N9">
-        <v>-10.51</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="Q9">
-        <v>15014.59</v>
+        <v>15069.78</v>
       </c>
       <c r="R9">
-        <v>15483.9</v>
+        <v>15459.16</v>
       </c>
       <c r="S9">
-        <v>16051.01</v>
+        <v>16023.51</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1858,40 +1864,40 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>35.6</v>
+        <v>37.03</v>
       </c>
       <c r="AA9">
-        <v>-289.44</v>
+        <v>-278.52</v>
       </c>
       <c r="AB9">
-        <v>-264.47</v>
+        <v>-267.28</v>
       </c>
       <c r="AC9">
-        <v>-24.98</v>
+        <v>-11.24</v>
       </c>
       <c r="AD9">
-        <v>53.48</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="AE9">
-        <v>37.74</v>
+        <v>52.59</v>
       </c>
       <c r="AF9">
-        <v>199.53</v>
+        <v>198.67</v>
       </c>
       <c r="AH9">
-        <v>16232.08</v>
+        <v>16221.55</v>
       </c>
       <c r="AI9">
-        <v>14735.72</v>
+        <v>14696.77</v>
       </c>
       <c r="AJ9">
         <v>15490.29</v>
       </c>
       <c r="AK9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL9">
-        <v>57.15</v>
+        <v>57.06</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1905,10 +1911,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8580.299999999999</v>
+        <v>8685.9</v>
       </c>
       <c r="E10">
-        <v>0.02</v>
+        <v>1.23</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1917,43 +1923,43 @@
         <v>8499.65</v>
       </c>
       <c r="H10">
-        <v>-12.14</v>
+        <v>-11.06</v>
       </c>
       <c r="I10">
-        <v>0.95</v>
+        <v>2.19</v>
       </c>
       <c r="J10">
-        <v>-1.7</v>
+        <v>2.14</v>
       </c>
       <c r="K10">
-        <v>-5.47</v>
+        <v>-2.52</v>
       </c>
       <c r="L10">
-        <v>-8.109999999999999</v>
+        <v>-6.92</v>
       </c>
       <c r="M10">
-        <v>-5.87</v>
+        <v>-5.07</v>
       </c>
       <c r="N10">
-        <v>10.24</v>
+        <v>10.42</v>
       </c>
       <c r="O10">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="Q10">
-        <v>8547.299999999999</v>
+        <v>8583.76</v>
       </c>
       <c r="R10">
-        <v>8792.059999999999</v>
+        <v>8780.92</v>
       </c>
       <c r="S10">
-        <v>9092.6</v>
+        <v>9077.93</v>
       </c>
       <c r="T10">
-        <v>9253.9</v>
+        <v>9249.17</v>
       </c>
       <c r="U10">
-        <v>-7.28</v>
+        <v>-6.09</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1968,40 +1974,40 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>35.99</v>
+        <v>42.61</v>
       </c>
       <c r="AA10">
-        <v>-157.92</v>
+        <v>-144.93</v>
       </c>
       <c r="AB10">
-        <v>-146.49</v>
+        <v>-146.17</v>
       </c>
       <c r="AC10">
-        <v>-11.43</v>
+        <v>1.25</v>
       </c>
       <c r="AD10">
-        <v>59.58</v>
+        <v>80.8</v>
       </c>
       <c r="AE10">
-        <v>47.86</v>
+        <v>62.73</v>
       </c>
       <c r="AF10">
-        <v>115.61</v>
+        <v>119.09</v>
       </c>
       <c r="AH10">
-        <v>9189.51</v>
+        <v>9177.09</v>
       </c>
       <c r="AI10">
-        <v>8394.610000000001</v>
+        <v>8384.75</v>
       </c>
       <c r="AJ10">
         <v>8855.59</v>
       </c>
       <c r="AK10" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL10">
-        <v>56.54</v>
+        <v>50.49</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2015,10 +2021,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1641.35</v>
+        <v>1617.2</v>
       </c>
       <c r="E11">
-        <v>0.59</v>
+        <v>-1.47</v>
       </c>
       <c r="F11">
         <v>1641.35</v>
@@ -2027,91 +2033,91 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>-1.47</v>
       </c>
       <c r="I11">
-        <v>30.96</v>
+        <v>29.03</v>
       </c>
       <c r="J11">
-        <v>3.98</v>
+        <v>5.39</v>
       </c>
       <c r="K11">
-        <v>6.78</v>
+        <v>7.53</v>
       </c>
       <c r="L11">
-        <v>9.15</v>
+        <v>6.3</v>
       </c>
       <c r="M11">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="N11">
-        <v>-6.93</v>
+        <v>-7.09</v>
       </c>
       <c r="O11">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="Q11">
-        <v>1597.13</v>
+        <v>1613.67</v>
       </c>
       <c r="R11">
-        <v>1565.32</v>
+        <v>1570.43</v>
       </c>
       <c r="S11">
-        <v>1568.84</v>
+        <v>1569.17</v>
       </c>
       <c r="T11">
-        <v>1463.41</v>
+        <v>1464.49</v>
       </c>
       <c r="U11">
-        <v>12.16</v>
+        <v>10.43</v>
       </c>
       <c r="V11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
       </c>
       <c r="X11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Y11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z11">
-        <v>63.79</v>
+        <v>58.31</v>
       </c>
       <c r="AA11">
-        <v>14.96</v>
+        <v>16.34</v>
       </c>
       <c r="AB11">
-        <v>5.13</v>
+        <v>7.37</v>
       </c>
       <c r="AC11">
-        <v>9.83</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="AD11">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AE11">
-        <v>74.44</v>
+        <v>89.44</v>
       </c>
       <c r="AF11">
-        <v>36.45</v>
+        <v>35.96</v>
       </c>
       <c r="AH11">
-        <v>1632.11</v>
+        <v>1636.65</v>
       </c>
       <c r="AI11">
-        <v>1498.53</v>
+        <v>1504.2</v>
       </c>
       <c r="AJ11">
         <v>1526.96</v>
       </c>
       <c r="AK11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL11">
-        <v>25.49</v>
+        <v>25.79</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2125,10 +2131,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>12006.75</v>
+        <v>12018.5</v>
       </c>
       <c r="E12">
-        <v>-0.67</v>
+        <v>0.1</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2137,43 +2143,43 @@
         <v>10017.9</v>
       </c>
       <c r="H12">
-        <v>-12.48</v>
+        <v>-12.39</v>
       </c>
       <c r="I12">
-        <v>19.85</v>
+        <v>19.97</v>
       </c>
       <c r="J12">
-        <v>-2.44</v>
+        <v>1.25</v>
       </c>
       <c r="K12">
-        <v>-7.63</v>
+        <v>-5.14</v>
       </c>
       <c r="L12">
-        <v>-4.23</v>
+        <v>-3.82</v>
       </c>
       <c r="M12">
-        <v>17.88</v>
+        <v>18.33</v>
       </c>
       <c r="N12">
-        <v>14.81</v>
+        <v>13.99</v>
       </c>
       <c r="O12">
         <v>87</v>
       </c>
       <c r="Q12">
-        <v>11983.39</v>
+        <v>12013.08</v>
       </c>
       <c r="R12">
-        <v>12619.81</v>
+        <v>12583.78</v>
       </c>
       <c r="S12">
-        <v>12954.4</v>
+        <v>12934.13</v>
       </c>
       <c r="T12">
-        <v>12445.49</v>
+        <v>12452.24</v>
       </c>
       <c r="U12">
-        <v>-3.53</v>
+        <v>-3.48</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2188,40 +2194,40 @@
         <v>1</v>
       </c>
       <c r="Z12">
-        <v>35.15</v>
+        <v>35.52</v>
       </c>
       <c r="AA12">
-        <v>-282.54</v>
+        <v>-285.02</v>
       </c>
       <c r="AB12">
-        <v>-202.88</v>
+        <v>-219.31</v>
       </c>
       <c r="AC12">
-        <v>-79.65000000000001</v>
+        <v>-65.70999999999999</v>
       </c>
       <c r="AD12">
-        <v>21.95</v>
+        <v>27.98</v>
       </c>
       <c r="AE12">
-        <v>15.97</v>
+        <v>22.45</v>
       </c>
       <c r="AF12">
-        <v>239.25</v>
+        <v>237.08</v>
       </c>
       <c r="AH12">
-        <v>13509.4</v>
+        <v>13510.62</v>
       </c>
       <c r="AI12">
-        <v>11730.21</v>
+        <v>11656.93</v>
       </c>
       <c r="AJ12">
-        <v>12689.95</v>
+        <v>12667.92</v>
       </c>
       <c r="AK12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL12">
-        <v>50.89</v>
+        <v>52.71</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2235,10 +2241,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9280.799999999999</v>
+        <v>9257.15</v>
       </c>
       <c r="E13">
-        <v>0.92</v>
+        <v>-0.25</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2247,43 +2253,43 @@
         <v>9010.450000000001</v>
       </c>
       <c r="H13">
-        <v>-13.8</v>
+        <v>-14.02</v>
       </c>
       <c r="I13">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="J13">
-        <v>0.52</v>
+        <v>2.74</v>
       </c>
       <c r="K13">
-        <v>-4.21</v>
+        <v>-2.22</v>
       </c>
       <c r="L13">
-        <v>-6.39</v>
+        <v>-6.6</v>
       </c>
       <c r="M13">
-        <v>-6.44</v>
+        <v>-6.77</v>
       </c>
       <c r="N13">
-        <v>16.17</v>
+        <v>15.74</v>
       </c>
       <c r="O13">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="Q13">
-        <v>9132.84</v>
+        <v>9182.18</v>
       </c>
       <c r="R13">
-        <v>9373.110000000001</v>
+        <v>9361.23</v>
       </c>
       <c r="S13">
-        <v>9612.940000000001</v>
+        <v>9599.32</v>
       </c>
       <c r="T13">
-        <v>10000.09</v>
+        <v>9998.18</v>
       </c>
       <c r="U13">
-        <v>-7.19</v>
+        <v>-7.41</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2298,40 +2304,40 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>43.24</v>
+        <v>42.17</v>
       </c>
       <c r="AA13">
-        <v>-138.8</v>
+        <v>-128.64</v>
       </c>
       <c r="AB13">
-        <v>-132.65</v>
+        <v>-131.85</v>
       </c>
       <c r="AC13">
-        <v>-6.15</v>
+        <v>3.2</v>
       </c>
       <c r="AD13">
-        <v>68.36</v>
+        <v>87.8</v>
       </c>
       <c r="AE13">
-        <v>45.44</v>
+        <v>66.94</v>
       </c>
       <c r="AF13">
-        <v>121.37</v>
+        <v>120</v>
       </c>
       <c r="AH13">
-        <v>9768.940000000001</v>
+        <v>9755.950000000001</v>
       </c>
       <c r="AI13">
-        <v>8977.290000000001</v>
+        <v>8966.52</v>
       </c>
       <c r="AJ13">
         <v>9403.969999999999</v>
       </c>
       <c r="AK13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL13">
-        <v>55.4</v>
+        <v>52.13</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2345,10 +2351,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8167.55</v>
+        <v>8041.2</v>
       </c>
       <c r="E14">
-        <v>0.26</v>
+        <v>-1.55</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2357,43 +2363,43 @@
         <v>7523.45</v>
       </c>
       <c r="H14">
-        <v>-17.33</v>
+        <v>-18.61</v>
       </c>
       <c r="I14">
-        <v>8.56</v>
+        <v>6.88</v>
       </c>
       <c r="J14">
-        <v>0.97</v>
+        <v>0.57</v>
       </c>
       <c r="K14">
-        <v>-2.18</v>
+        <v>-1.44</v>
       </c>
       <c r="L14">
-        <v>-2.61</v>
+        <v>-3.67</v>
       </c>
       <c r="M14">
-        <v>7.25</v>
+        <v>6.03</v>
       </c>
       <c r="N14">
-        <v>24.63</v>
+        <v>23.32</v>
       </c>
       <c r="O14">
         <v>81</v>
       </c>
       <c r="Q14">
-        <v>8093.41</v>
+        <v>8102.46</v>
       </c>
       <c r="R14">
-        <v>8145.14</v>
+        <v>8133.41</v>
       </c>
       <c r="S14">
-        <v>8401.129999999999</v>
+        <v>8392.35</v>
       </c>
       <c r="T14">
-        <v>8576.540000000001</v>
+        <v>8574.860000000001</v>
       </c>
       <c r="U14">
-        <v>-4.77</v>
+        <v>-6.22</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2408,40 +2414,40 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>48.34</v>
+        <v>42.69</v>
       </c>
       <c r="AA14">
-        <v>-84.38</v>
+        <v>-83.55</v>
       </c>
       <c r="AB14">
-        <v>-104.24</v>
+        <v>-100.1</v>
       </c>
       <c r="AC14">
-        <v>19.86</v>
+        <v>16.55</v>
       </c>
       <c r="AD14">
-        <v>89.33</v>
+        <v>89.89</v>
       </c>
       <c r="AE14">
-        <v>81.59</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="AF14">
-        <v>141.7</v>
+        <v>146.8</v>
       </c>
       <c r="AH14">
-        <v>8424.200000000001</v>
+        <v>8409.030000000001</v>
       </c>
       <c r="AI14">
-        <v>7866.08</v>
+        <v>7857.78</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
       </c>
       <c r="AK14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL14">
-        <v>24.02</v>
+        <v>22.85</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2455,10 +2461,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>25736.95</v>
+        <v>25817.8</v>
       </c>
       <c r="E15">
-        <v>-1.3</v>
+        <v>0.31</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2467,43 +2473,43 @@
         <v>21549.55</v>
       </c>
       <c r="H15">
-        <v>-5.33</v>
+        <v>-5.03</v>
       </c>
       <c r="I15">
-        <v>19.43</v>
+        <v>19.81</v>
       </c>
       <c r="J15">
-        <v>-2.65</v>
+        <v>-0.02</v>
       </c>
       <c r="K15">
-        <v>-3</v>
+        <v>-1.42</v>
       </c>
       <c r="L15">
-        <v>-1.03</v>
+        <v>-0.73</v>
       </c>
       <c r="M15">
-        <v>18.17</v>
+        <v>18.02</v>
       </c>
       <c r="N15">
-        <v>11.81</v>
+        <v>12.1</v>
       </c>
       <c r="O15">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="Q15">
-        <v>25935.22</v>
+        <v>25934.13</v>
       </c>
       <c r="R15">
-        <v>26488.71</v>
+        <v>26472.3</v>
       </c>
       <c r="S15">
-        <v>26557.11</v>
+        <v>26541.51</v>
       </c>
       <c r="T15">
-        <v>24295.45</v>
+        <v>24309.9</v>
       </c>
       <c r="U15">
-        <v>5.93</v>
+        <v>6.2</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2518,40 +2524,40 @@
         <v>2</v>
       </c>
       <c r="Z15">
-        <v>37.94</v>
+        <v>39.74</v>
       </c>
       <c r="AA15">
-        <v>-177.08</v>
+        <v>-195.26</v>
       </c>
       <c r="AB15">
-        <v>-80.79000000000001</v>
+        <v>-103.68</v>
       </c>
       <c r="AC15">
-        <v>-96.29000000000001</v>
+        <v>-91.56999999999999</v>
       </c>
       <c r="AD15">
-        <v>14.29</v>
+        <v>10.28</v>
       </c>
       <c r="AE15">
-        <v>14.45</v>
+        <v>14.21</v>
       </c>
       <c r="AF15">
-        <v>373.8</v>
+        <v>372.24</v>
       </c>
       <c r="AH15">
-        <v>27372.1</v>
+        <v>27393.87</v>
       </c>
       <c r="AI15">
-        <v>25605.33</v>
+        <v>25550.72</v>
       </c>
       <c r="AJ15">
-        <v>26953.21</v>
+        <v>26891.71</v>
       </c>
       <c r="AK15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL15">
-        <v>37.95</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2565,10 +2571,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>822.8</v>
+        <v>828.7</v>
       </c>
       <c r="E16">
-        <v>-0.86</v>
+        <v>0.72</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2577,43 +2583,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-15.06</v>
+        <v>-14.45</v>
       </c>
       <c r="I16">
-        <v>26.36</v>
+        <v>27.27</v>
       </c>
       <c r="J16">
-        <v>0.02</v>
+        <v>4.03</v>
       </c>
       <c r="K16">
-        <v>-3.03</v>
+        <v>1.77</v>
       </c>
       <c r="L16">
-        <v>-10.09</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="M16">
-        <v>-6.72</v>
+        <v>-7.07</v>
       </c>
       <c r="N16">
-        <v>8.82</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="O16">
         <v>19</v>
       </c>
       <c r="Q16">
-        <v>812.67</v>
+        <v>819.09</v>
       </c>
       <c r="R16">
-        <v>837.4</v>
+        <v>837.72</v>
       </c>
       <c r="S16">
-        <v>871.3</v>
+        <v>870.05</v>
       </c>
       <c r="T16">
-        <v>824.8200000000001</v>
+        <v>824.54</v>
       </c>
       <c r="U16">
-        <v>-0.24</v>
+        <v>0.5</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2625,43 +2631,43 @@
         <v>79</v>
       </c>
       <c r="Y16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z16">
-        <v>42.62</v>
+        <v>44.82</v>
       </c>
       <c r="AA16">
-        <v>-15.9</v>
+        <v>-14.65</v>
       </c>
       <c r="AB16">
-        <v>-15.3</v>
+        <v>-15.17</v>
       </c>
       <c r="AC16">
-        <v>-0.61</v>
+        <v>0.52</v>
       </c>
       <c r="AD16">
-        <v>57.85</v>
+        <v>72.98</v>
       </c>
       <c r="AE16">
-        <v>38.9</v>
+        <v>57.63</v>
       </c>
       <c r="AF16">
-        <v>17.54</v>
+        <v>17.41</v>
       </c>
       <c r="AH16">
-        <v>878.91</v>
+        <v>878.84</v>
       </c>
       <c r="AI16">
-        <v>795.89</v>
+        <v>796.6</v>
       </c>
       <c r="AJ16">
         <v>855.3200000000001</v>
       </c>
       <c r="AK16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL16">
-        <v>33.35</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2675,10 +2681,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29455.4</v>
+        <v>29995.85</v>
       </c>
       <c r="E17">
-        <v>0.04</v>
+        <v>1.83</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2687,43 +2693,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-13.62</v>
+        <v>-12.04</v>
       </c>
       <c r="I17">
-        <v>3.85</v>
+        <v>5.75</v>
       </c>
       <c r="J17">
-        <v>1.36</v>
+        <v>4.79</v>
       </c>
       <c r="K17">
-        <v>-1.71</v>
+        <v>0.9</v>
       </c>
       <c r="L17">
-        <v>-5.44</v>
+        <v>-3.54</v>
       </c>
       <c r="M17">
-        <v>-9.69</v>
+        <v>-8.23</v>
       </c>
       <c r="N17">
-        <v>3.02</v>
+        <v>3.24</v>
       </c>
       <c r="O17">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="Q17">
-        <v>29091.16</v>
+        <v>29365.58</v>
       </c>
       <c r="R17">
-        <v>29405.44</v>
+        <v>29415.11</v>
       </c>
       <c r="S17">
-        <v>30238.4</v>
+        <v>30206.15</v>
       </c>
       <c r="T17">
-        <v>31079.18</v>
+        <v>31059.32</v>
       </c>
       <c r="U17">
-        <v>-5.22</v>
+        <v>-3.42</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2738,40 +2744,40 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>47.69</v>
+        <v>56.39</v>
       </c>
       <c r="AA17">
-        <v>-313.3</v>
+        <v>-230.21</v>
       </c>
       <c r="AB17">
-        <v>-373.18</v>
+        <v>-344.59</v>
       </c>
       <c r="AC17">
-        <v>59.87</v>
+        <v>114.37</v>
       </c>
       <c r="AD17">
-        <v>89.02</v>
+        <v>100</v>
       </c>
       <c r="AE17">
-        <v>76.33</v>
+        <v>91.38</v>
       </c>
       <c r="AF17">
-        <v>355.5</v>
+        <v>373.01</v>
       </c>
       <c r="AH17">
-        <v>30297.67</v>
+        <v>30329.4</v>
       </c>
       <c r="AI17">
-        <v>28513.2</v>
+        <v>28500.83</v>
       </c>
       <c r="AJ17">
-        <v>29780.35</v>
+        <v>28688.71</v>
       </c>
       <c r="AK17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AL17">
-        <v>42.11</v>
+        <v>39.94</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2785,10 +2791,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>15663</v>
+        <v>15724.4</v>
       </c>
       <c r="E18">
-        <v>-1.25</v>
+        <v>0.39</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2797,31 +2803,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-7.55</v>
+        <v>-7.18</v>
       </c>
       <c r="I18">
-        <v>1.69</v>
+        <v>2.09</v>
       </c>
       <c r="J18">
-        <v>-2.47</v>
+        <v>0.25</v>
       </c>
       <c r="K18">
-        <v>-5.03</v>
+        <v>-3.53</v>
       </c>
       <c r="L18">
-        <v>-5.12</v>
+        <v>-4.66</v>
       </c>
       <c r="N18">
-        <v>2.12</v>
+        <v>3.28</v>
       </c>
       <c r="Q18">
-        <v>15782.31</v>
+        <v>15790.26</v>
       </c>
       <c r="R18">
-        <v>16278.91</v>
+        <v>16251.4</v>
       </c>
       <c r="S18">
-        <v>16462.34</v>
+        <v>16441.9</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2833,40 +2839,40 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>32.82</v>
+        <v>35.24</v>
       </c>
       <c r="AA18">
-        <v>-212.12</v>
+        <v>-218.95</v>
       </c>
       <c r="AB18">
-        <v>-144.8</v>
+        <v>-159.63</v>
       </c>
       <c r="AC18">
-        <v>-67.31999999999999</v>
+        <v>-59.33</v>
       </c>
       <c r="AD18">
-        <v>16.74</v>
+        <v>17.17</v>
       </c>
       <c r="AE18">
-        <v>16.85</v>
+        <v>18.13</v>
       </c>
       <c r="AF18">
-        <v>221.89</v>
+        <v>222.43</v>
       </c>
       <c r="AH18">
-        <v>17079.59</v>
+        <v>17089.62</v>
       </c>
       <c r="AI18">
-        <v>15478.24</v>
+        <v>15413.18</v>
       </c>
       <c r="AJ18">
-        <v>16384.12</v>
+        <v>16367.05</v>
       </c>
       <c r="AK18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL18">
-        <v>53.81</v>
+        <v>56.04</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2880,10 +2886,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9294.1</v>
+        <v>9196.25</v>
       </c>
       <c r="E19">
-        <v>0.47</v>
+        <v>-1.05</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2892,31 +2898,31 @@
         <v>8961.25</v>
       </c>
       <c r="H19">
-        <v>-7.05</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="I19">
-        <v>3.71</v>
+        <v>2.62</v>
       </c>
       <c r="J19">
-        <v>0.85</v>
+        <v>2.62</v>
       </c>
       <c r="K19">
-        <v>-4.42</v>
+        <v>0.57</v>
       </c>
       <c r="L19">
-        <v>-0.4</v>
+        <v>-0.97</v>
       </c>
       <c r="N19">
-        <v>10.1</v>
+        <v>6.67</v>
       </c>
       <c r="Q19">
-        <v>9126.92</v>
+        <v>9173.92</v>
       </c>
       <c r="R19">
-        <v>9251.68</v>
+        <v>9255.040000000001</v>
       </c>
       <c r="S19">
-        <v>9529.4</v>
+        <v>9524.93</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2928,40 +2934,40 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>48.84</v>
+        <v>45.6</v>
       </c>
       <c r="AA19">
-        <v>-101.87</v>
+        <v>-96.08</v>
       </c>
       <c r="AB19">
-        <v>-111.47</v>
+        <v>-108.4</v>
       </c>
       <c r="AC19">
-        <v>9.6</v>
+        <v>12.31</v>
       </c>
       <c r="AD19">
-        <v>86.59999999999999</v>
+        <v>91.73</v>
       </c>
       <c r="AE19">
-        <v>57.47</v>
+        <v>79.23</v>
       </c>
       <c r="AF19">
-        <v>172.3</v>
+        <v>169.45</v>
       </c>
       <c r="AH19">
-        <v>9535.870000000001</v>
+        <v>9534.68</v>
       </c>
       <c r="AI19">
-        <v>8967.49</v>
+        <v>8975.4</v>
       </c>
       <c r="AJ19">
         <v>9494.469999999999</v>
       </c>
       <c r="AK19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL19">
-        <v>28.44</v>
+        <v>26.44</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2975,10 +2981,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10456.75</v>
+        <v>10604.6</v>
       </c>
       <c r="E20">
-        <v>1.04</v>
+        <v>1.41</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -2987,31 +2993,31 @@
         <v>10299.4</v>
       </c>
       <c r="H20">
-        <v>-8.02</v>
+        <v>-6.72</v>
       </c>
       <c r="I20">
-        <v>1.53</v>
+        <v>2.96</v>
       </c>
       <c r="J20">
-        <v>-1.56</v>
+        <v>2.41</v>
       </c>
       <c r="K20">
-        <v>-4.39</v>
+        <v>-1.78</v>
       </c>
       <c r="L20">
-        <v>-6.46</v>
+        <v>-5.22</v>
       </c>
       <c r="N20">
-        <v>-14.14</v>
+        <v>-10.44</v>
       </c>
       <c r="Q20">
-        <v>10361.14</v>
+        <v>10411.13</v>
       </c>
       <c r="R20">
-        <v>10665.73</v>
+        <v>10652.34</v>
       </c>
       <c r="S20">
-        <v>10961.3</v>
+        <v>10948.87</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3023,40 +3029,40 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>38.25</v>
+        <v>46.01</v>
       </c>
       <c r="AA20">
-        <v>-174.7</v>
+        <v>-154.54</v>
       </c>
       <c r="AB20">
-        <v>-155.49</v>
+        <v>-155.3</v>
       </c>
       <c r="AC20">
-        <v>-19.21</v>
+        <v>0.76</v>
       </c>
       <c r="AD20">
-        <v>40.84</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="AE20">
-        <v>24.41</v>
+        <v>43.1</v>
       </c>
       <c r="AF20">
-        <v>146.44</v>
+        <v>152.73</v>
       </c>
       <c r="AH20">
-        <v>11148.89</v>
+        <v>11126.13</v>
       </c>
       <c r="AI20">
-        <v>10182.57</v>
+        <v>10178.55</v>
       </c>
       <c r="AJ20">
         <v>10732.68</v>
       </c>
       <c r="AK20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AL20">
-        <v>49.21</v>
+        <v>43.18</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3070,10 +3076,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27166.8</v>
+        <v>27679.3</v>
       </c>
       <c r="E21">
-        <v>-0.58</v>
+        <v>1.89</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3082,43 +3088,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-6.92</v>
+        <v>-5.17</v>
       </c>
       <c r="I21">
-        <v>12.52</v>
+        <v>14.64</v>
       </c>
       <c r="J21">
-        <v>0.19</v>
+        <v>3.02</v>
       </c>
       <c r="K21">
-        <v>-0.98</v>
+        <v>2.25</v>
       </c>
       <c r="L21">
-        <v>-2.98</v>
+        <v>-0.85</v>
       </c>
       <c r="M21">
-        <v>-1.18</v>
+        <v>0.66</v>
       </c>
       <c r="N21">
-        <v>5.84</v>
+        <v>6.07</v>
       </c>
       <c r="O21">
         <v>74</v>
       </c>
       <c r="Q21">
-        <v>27141.14</v>
+        <v>27303.18</v>
       </c>
       <c r="R21">
-        <v>27017.8</v>
+        <v>27037.55</v>
       </c>
       <c r="S21">
-        <v>27318.01</v>
+        <v>27314.38</v>
       </c>
       <c r="T21">
-        <v>27442.15</v>
+        <v>27437.99</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>0.88</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3130,43 +3136,43 @@
         <v>79</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21">
-        <v>50.53</v>
+        <v>59.55</v>
       </c>
       <c r="AA21">
-        <v>-66.79000000000001</v>
+        <v>-13.09</v>
       </c>
       <c r="AB21">
-        <v>-135.37</v>
+        <v>-110.91</v>
       </c>
       <c r="AC21">
-        <v>68.58</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="AD21">
-        <v>91.14</v>
+        <v>94.7</v>
       </c>
       <c r="AE21">
-        <v>91.31999999999999</v>
+        <v>94.09</v>
       </c>
       <c r="AF21">
-        <v>358.19</v>
+        <v>375.17</v>
       </c>
       <c r="AH21">
-        <v>27614.69</v>
+        <v>27694.68</v>
       </c>
       <c r="AI21">
-        <v>26420.9</v>
+        <v>26380.42</v>
       </c>
       <c r="AJ21">
-        <v>26197.52</v>
+        <v>26361.32</v>
       </c>
       <c r="AK21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL21">
-        <v>23.13</v>
+        <v>26.94</v>
       </c>
     </row>
   </sheetData>
@@ -3307,7 +3313,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3317,7 +3323,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3330,19 +3336,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3350,733 +3356,739 @@
         <v>43</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>93</v>
+        <v>23</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="C5" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="D6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="F6" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-7.8</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-7.87</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-7.77</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-5.93</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.84</v>
+      <c r="D9" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.92</v>
+        <v>-7.87</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.8</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.12</v>
+        <v>-4.41</v>
+      </c>
+      <c r="E10" s="7">
+        <v>3.46</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.88</v>
+        <v>-5.93</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.77</v>
-      </c>
-      <c r="E11" s="8">
-        <v>2.11</v>
+        <v>-3.59</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2.34</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-1.01</v>
+        <v>-4.8</v>
       </c>
       <c r="D12" s="6">
-        <v>0.48</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.49</v>
+        <v>-2.46</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.34</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.14</v>
+        <v>-3.77</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.34</v>
+        <v>-2.51</v>
       </c>
       <c r="E13" s="7">
-        <v>-1.2</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>3.25</v>
+        <v>0.48</v>
       </c>
       <c r="D14" s="6">
-        <v>4.32</v>
+        <v>-0.09</v>
       </c>
       <c r="E14" s="8">
-        <v>1.07</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.99</v>
+        <v>-2.34</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.54</v>
-      </c>
-      <c r="E15" s="8">
-        <v>0.45</v>
+        <v>1.15</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.49</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-6.08</v>
+        <v>4.32</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.47</v>
+        <v>3.94</v>
       </c>
       <c r="E16" s="8">
-        <v>0.61</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>6.31</v>
+        <v>-5.54</v>
       </c>
       <c r="D17" s="6">
-        <v>6.78</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.47</v>
+        <v>-2.97</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.57</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-9.140000000000001</v>
+        <v>-5.47</v>
       </c>
       <c r="D18" s="6">
-        <v>-7.63</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.51</v>
+        <v>-2.52</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.95</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-5.68</v>
+        <v>6.78</v>
       </c>
       <c r="D19" s="6">
-        <v>-4.21</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.47</v>
+        <v>7.53</v>
+      </c>
+      <c r="E19" s="7">
+        <v>0.75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.04</v>
+        <v>-7.63</v>
       </c>
       <c r="D20" s="6">
-        <v>-2.18</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.86</v>
+        <v>-5.14</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.49</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.81</v>
+        <v>-4.21</v>
       </c>
       <c r="D21" s="6">
-        <v>-3</v>
+        <v>-2.22</v>
       </c>
       <c r="E21" s="7">
-        <v>-1.19</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-4.83</v>
+        <v>-2.18</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.03</v>
-      </c>
-      <c r="E22" s="8">
-        <v>1.8</v>
+        <v>-1.44</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.74</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.65</v>
+        <v>-3</v>
       </c>
       <c r="D23" s="6">
-        <v>-1.71</v>
+        <v>-1.42</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.06</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.98</v>
+        <v>-3.03</v>
       </c>
       <c r="D24" s="6">
-        <v>-5.03</v>
+        <v>1.77</v>
       </c>
       <c r="E24" s="7">
-        <v>-1.05</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-5.57</v>
+        <v>-1.71</v>
       </c>
       <c r="D25" s="6">
-        <v>-4.42</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.15</v>
+        <v>0.9</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.61</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-6.17</v>
+        <v>-5.03</v>
       </c>
       <c r="D26" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.78</v>
+        <v>-3.53</v>
+      </c>
+      <c r="E26" s="7">
+        <v>1.5</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>0.07000000000000001</v>
+        <v>-4.42</v>
       </c>
       <c r="D27" s="6">
-        <v>-0.98</v>
+        <v>0.57</v>
       </c>
       <c r="E27" s="7">
-        <v>-1.05</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-0.59</v>
+        <v>-4.39</v>
       </c>
       <c r="D28" s="6">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.66</v>
+        <v>-1.78</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-3.07</v>
+        <v>-0.98</v>
       </c>
       <c r="D29" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="E29" s="8">
-        <v>2.02</v>
+        <v>2.25</v>
+      </c>
+      <c r="E29" s="7">
+        <v>3.23</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>-1.14</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="D30" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.53</v>
+        <v>4.34</v>
+      </c>
+      <c r="E30" s="7">
+        <v>4.27</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-2.55</v>
+        <v>-1.05</v>
       </c>
       <c r="D31" s="6">
-        <v>-0.49</v>
-      </c>
-      <c r="E31" s="8">
-        <v>2.06</v>
+        <v>2.46</v>
+      </c>
+      <c r="E31" s="7">
+        <v>3.51</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-1.05</v>
+        <v>-0.61</v>
       </c>
       <c r="D32" s="6">
-        <v>1.05</v>
-      </c>
-      <c r="E32" s="8">
-        <v>2.1</v>
+        <v>2.46</v>
+      </c>
+      <c r="E32" s="7">
+        <v>3.07</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>1.13</v>
+        <v>-0.49</v>
       </c>
       <c r="D33" s="6">
-        <v>0.13</v>
+        <v>1.58</v>
       </c>
       <c r="E33" s="7">
-        <v>-1</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>6.02</v>
+        <v>1.05</v>
       </c>
       <c r="D34" s="6">
-        <v>8.69</v>
-      </c>
-      <c r="E34" s="8">
-        <v>2.67</v>
+        <v>2.04</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.99</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.77</v>
+        <v>0.13</v>
       </c>
       <c r="D35" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="E35" s="8">
-        <v>0.72</v>
+        <v>2.94</v>
+      </c>
+      <c r="E35" s="7">
+        <v>2.81</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-2.49</v>
+        <v>8.69</v>
       </c>
       <c r="D36" s="6">
-        <v>-1.7</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.79</v>
+        <v>10.76</v>
+      </c>
+      <c r="E36" s="7">
+        <v>2.07</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>4.08</v>
+        <v>-1.05</v>
       </c>
       <c r="D37" s="6">
-        <v>3.98</v>
+        <v>1.86</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.1</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-4.06</v>
+        <v>-1.7</v>
       </c>
       <c r="D38" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.62</v>
+        <v>2.14</v>
+      </c>
+      <c r="E38" s="7">
+        <v>3.84</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>-1.6</v>
+        <v>3.98</v>
       </c>
       <c r="D39" s="6">
-        <v>0.52</v>
-      </c>
-      <c r="E39" s="8">
-        <v>2.12</v>
+        <v>5.39</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.41</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>1.73</v>
+        <v>-2.44</v>
       </c>
       <c r="D40" s="6">
-        <v>0.97</v>
+        <v>1.25</v>
       </c>
       <c r="E40" s="7">
-        <v>-0.76</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>-1.79</v>
+        <v>0.52</v>
       </c>
       <c r="D41" s="6">
-        <v>-2.65</v>
+        <v>2.74</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.86</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>-0.9</v>
+        <v>0.97</v>
       </c>
       <c r="D42" s="6">
-        <v>0.02</v>
+        <v>0.57</v>
       </c>
       <c r="E42" s="8">
-        <v>0.92</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>0.6899999999999999</v>
+        <v>-2.65</v>
       </c>
       <c r="D43" s="6">
-        <v>1.36</v>
-      </c>
-      <c r="E43" s="8">
-        <v>0.67</v>
+        <v>-0.02</v>
+      </c>
+      <c r="E43" s="7">
+        <v>2.63</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>-1.49</v>
+        <v>0.02</v>
       </c>
       <c r="D44" s="6">
-        <v>-2.47</v>
+        <v>4.03</v>
       </c>
       <c r="E44" s="7">
-        <v>-0.98</v>
+        <v>4.01</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>-1.04</v>
+        <v>1.36</v>
       </c>
       <c r="D45" s="6">
-        <v>0.85</v>
-      </c>
-      <c r="E45" s="8">
-        <v>1.89</v>
+        <v>4.79</v>
+      </c>
+      <c r="E45" s="7">
+        <v>3.43</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-3.07</v>
+        <v>-2.47</v>
       </c>
       <c r="D46" s="6">
-        <v>-1.56</v>
-      </c>
-      <c r="E46" s="8">
-        <v>1.51</v>
+        <v>0.25</v>
+      </c>
+      <c r="E46" s="7">
+        <v>2.72</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>9</v>
@@ -4085,1392 +4097,1392 @@
         <v>0.85</v>
       </c>
       <c r="D47" s="6">
-        <v>0.19</v>
+        <v>2.62</v>
       </c>
       <c r="E47" s="7">
-        <v>-0.66</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C48" s="6">
-        <v>-5.09</v>
+        <v>-1.56</v>
       </c>
       <c r="D48" s="6">
-        <v>-6.33</v>
+        <v>2.41</v>
       </c>
       <c r="E48" s="7">
-        <v>-1.24</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C49" s="6">
-        <v>-1.38</v>
+        <v>0.19</v>
       </c>
       <c r="D49" s="6">
-        <v>-0.92</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.46</v>
+        <v>3.02</v>
+      </c>
+      <c r="E49" s="7">
+        <v>2.83</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>-9.84</v>
+        <v>-6.33</v>
       </c>
       <c r="D50" s="6">
-        <v>-10.65</v>
+        <v>-5.04</v>
       </c>
       <c r="E50" s="7">
-        <v>-0.8100000000000001</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>1.7</v>
+        <v>-0.92</v>
       </c>
       <c r="D51" s="6">
-        <v>3.21</v>
-      </c>
-      <c r="E51" s="8">
-        <v>1.51</v>
+        <v>-0.31</v>
+      </c>
+      <c r="E51" s="7">
+        <v>0.61</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-18.92</v>
+        <v>-10.65</v>
       </c>
       <c r="D52" s="6">
-        <v>-17.77</v>
-      </c>
-      <c r="E52" s="8">
-        <v>1.15</v>
+        <v>-9.98</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.67</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-4.53</v>
+        <v>3.21</v>
       </c>
       <c r="D53" s="6">
-        <v>-6.6</v>
-      </c>
-      <c r="E53" s="7">
-        <v>-2.07</v>
+        <v>2.1</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-12.13</v>
+        <v>-17.77</v>
       </c>
       <c r="D54" s="6">
-        <v>-13.11</v>
-      </c>
-      <c r="E54" s="7">
-        <v>-0.98</v>
+        <v>-18.21</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.44</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-5.45</v>
+        <v>-6.6</v>
       </c>
       <c r="D55" s="6">
-        <v>-5.87</v>
+        <v>-5.28</v>
       </c>
       <c r="E55" s="7">
-        <v>-0.42</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>1.67</v>
+        <v>-13.11</v>
       </c>
       <c r="D56" s="6">
-        <v>3.2</v>
-      </c>
-      <c r="E56" s="8">
-        <v>1.53</v>
+        <v>-11.49</v>
+      </c>
+      <c r="E56" s="7">
+        <v>1.62</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>17.62</v>
+        <v>-5.87</v>
       </c>
       <c r="D57" s="6">
-        <v>17.88</v>
-      </c>
-      <c r="E57" s="8">
-        <v>0.26</v>
+        <v>-5.07</v>
+      </c>
+      <c r="E57" s="7">
+        <v>0.8</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>-7.36</v>
+        <v>3.2</v>
       </c>
       <c r="D58" s="6">
-        <v>-6.44</v>
+        <v>2.15</v>
       </c>
       <c r="E58" s="8">
-        <v>0.92</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>7.43</v>
+        <v>17.88</v>
       </c>
       <c r="D59" s="6">
-        <v>7.25</v>
+        <v>18.33</v>
       </c>
       <c r="E59" s="7">
-        <v>-0.18</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>19.85</v>
+        <v>-6.44</v>
       </c>
       <c r="D60" s="6">
-        <v>18.17</v>
-      </c>
-      <c r="E60" s="7">
-        <v>-1.68</v>
+        <v>-6.77</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.33</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>-5.27</v>
+        <v>7.25</v>
       </c>
       <c r="D61" s="6">
-        <v>-6.72</v>
-      </c>
-      <c r="E61" s="7">
-        <v>-1.45</v>
+        <v>6.03</v>
+      </c>
+      <c r="E61" s="8">
+        <v>-1.22</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>-8.69</v>
+        <v>18.17</v>
       </c>
       <c r="D62" s="6">
-        <v>-9.69</v>
-      </c>
-      <c r="E62" s="7">
-        <v>-1</v>
+        <v>18.02</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>0.61</v>
+        <v>-6.72</v>
       </c>
       <c r="D63" s="6">
-        <v>-1.18</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-1.79</v>
+        <v>-7.07</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" s="6">
-        <v>-4.35</v>
+        <v>-9.69</v>
       </c>
       <c r="D64" s="6">
-        <v>-5.59</v>
+        <v>-8.23</v>
       </c>
       <c r="E64" s="7">
-        <v>-1.24</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" s="6">
-        <v>-9.19</v>
+        <v>-1.18</v>
       </c>
       <c r="D65" s="6">
-        <v>-8.289999999999999</v>
-      </c>
-      <c r="E65" s="8">
-        <v>0.9</v>
+        <v>0.66</v>
+      </c>
+      <c r="E65" s="7">
+        <v>1.84</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-5.71</v>
+        <v>-5.59</v>
       </c>
       <c r="D66" s="6">
-        <v>-6.23</v>
+        <v>-4.45</v>
       </c>
       <c r="E66" s="7">
-        <v>-0.52</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-8.23</v>
+        <v>-8.289999999999999</v>
       </c>
       <c r="D67" s="6">
-        <v>-7.31</v>
-      </c>
-      <c r="E67" s="8">
-        <v>0.92</v>
+        <v>-7.62</v>
+      </c>
+      <c r="E67" s="7">
+        <v>0.67</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-7.82</v>
+        <v>-6.23</v>
       </c>
       <c r="D68" s="6">
-        <v>-6.24</v>
-      </c>
-      <c r="E68" s="8">
-        <v>1.58</v>
+        <v>-5.62</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.61</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-4.93</v>
+        <v>-7.31</v>
       </c>
       <c r="D69" s="6">
-        <v>-6.54</v>
-      </c>
-      <c r="E69" s="7">
-        <v>-1.61</v>
+        <v>-7.96</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-0.65</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>3.85</v>
+        <v>-6.24</v>
       </c>
       <c r="D70" s="6">
-        <v>5.74</v>
+        <v>-7.47</v>
       </c>
       <c r="E70" s="8">
-        <v>1.89</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-4.42</v>
+        <v>-6.54</v>
       </c>
       <c r="D71" s="6">
-        <v>-5.21</v>
+        <v>-4.49</v>
       </c>
       <c r="E71" s="7">
-        <v>-0.79</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-8.26</v>
+        <v>5.74</v>
       </c>
       <c r="D72" s="6">
-        <v>-8.109999999999999</v>
-      </c>
-      <c r="E72" s="8">
-        <v>0.15</v>
+        <v>6.95</v>
+      </c>
+      <c r="E72" s="7">
+        <v>1.21</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>8.02</v>
+        <v>-5.21</v>
       </c>
       <c r="D73" s="6">
-        <v>9.15</v>
+        <v>-5.22</v>
       </c>
       <c r="E73" s="8">
-        <v>1.13</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-4.65</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="D74" s="6">
-        <v>-4.23</v>
-      </c>
-      <c r="E74" s="8">
-        <v>0.42</v>
+        <v>-6.92</v>
+      </c>
+      <c r="E74" s="7">
+        <v>1.19</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-7.32</v>
+        <v>9.15</v>
       </c>
       <c r="D75" s="6">
-        <v>-6.39</v>
+        <v>6.3</v>
       </c>
       <c r="E75" s="8">
-        <v>0.93</v>
+        <v>-2.85</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-1.94</v>
+        <v>-4.23</v>
       </c>
       <c r="D76" s="6">
-        <v>-2.61</v>
+        <v>-3.82</v>
       </c>
       <c r="E76" s="7">
-        <v>-0.67</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>0.65</v>
+        <v>-6.39</v>
       </c>
       <c r="D77" s="6">
-        <v>-1.03</v>
-      </c>
-      <c r="E77" s="7">
-        <v>-1.68</v>
+        <v>-6.6</v>
+      </c>
+      <c r="E77" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>-9.66</v>
+        <v>-2.61</v>
       </c>
       <c r="D78" s="6">
-        <v>-10.09</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-0.43</v>
+        <v>-3.67</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-1.06</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-5.19</v>
+        <v>-1.03</v>
       </c>
       <c r="D79" s="6">
-        <v>-5.44</v>
+        <v>-0.73</v>
       </c>
       <c r="E79" s="7">
-        <v>-0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-3.53</v>
+        <v>-10.09</v>
       </c>
       <c r="D80" s="6">
-        <v>-5.12</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="E80" s="7">
-        <v>-1.59</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-0.8</v>
+        <v>-5.44</v>
       </c>
       <c r="D81" s="6">
-        <v>-0.4</v>
-      </c>
-      <c r="E81" s="8">
-        <v>0.4</v>
+        <v>-3.54</v>
+      </c>
+      <c r="E81" s="7">
+        <v>1.9</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-6.78</v>
+        <v>-5.12</v>
       </c>
       <c r="D82" s="6">
-        <v>-6.46</v>
-      </c>
-      <c r="E82" s="8">
-        <v>0.32</v>
+        <v>-4.66</v>
+      </c>
+      <c r="E82" s="7">
+        <v>0.46</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-2.12</v>
+        <v>-0.4</v>
       </c>
       <c r="D83" s="6">
-        <v>-2.98</v>
-      </c>
-      <c r="E83" s="7">
-        <v>-0.86</v>
+        <v>-0.97</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C84" s="6">
-        <v>-14.36</v>
+        <v>-6.46</v>
       </c>
       <c r="D84" s="6">
-        <v>-15.15</v>
+        <v>-5.22</v>
       </c>
       <c r="E84" s="7">
-        <v>-0.79</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C85" s="6">
-        <v>-14.74</v>
+        <v>-2.98</v>
       </c>
       <c r="D85" s="6">
-        <v>-14.2</v>
-      </c>
-      <c r="E85" s="8">
-        <v>0.54</v>
+        <v>-0.85</v>
+      </c>
+      <c r="E85" s="7">
+        <v>2.13</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="6">
-        <v>-13.37</v>
+        <v>-15.15</v>
       </c>
       <c r="D86" s="6">
-        <v>-13.68</v>
+        <v>-13.73</v>
       </c>
       <c r="E86" s="7">
-        <v>-0.31</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-13.39</v>
+        <v>-14.2</v>
       </c>
       <c r="D87" s="6">
-        <v>-12.12</v>
-      </c>
-      <c r="E87" s="8">
-        <v>1.27</v>
+        <v>-13.65</v>
+      </c>
+      <c r="E87" s="7">
+        <v>0.55</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-21.21</v>
+        <v>-13.68</v>
       </c>
       <c r="D88" s="6">
-        <v>-20.26</v>
-      </c>
-      <c r="E88" s="8">
-        <v>0.95</v>
+        <v>-12.93</v>
+      </c>
+      <c r="E88" s="7">
+        <v>0.75</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-11.36</v>
+        <v>-12.12</v>
       </c>
       <c r="D89" s="6">
-        <v>-12.35</v>
-      </c>
-      <c r="E89" s="7">
-        <v>-0.99</v>
+        <v>-12.81</v>
+      </c>
+      <c r="E89" s="8">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-24.46</v>
+        <v>-20.26</v>
       </c>
       <c r="D90" s="6">
-        <v>-23.59</v>
+        <v>-21.1</v>
       </c>
       <c r="E90" s="8">
-        <v>0.87</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-9.08</v>
+        <v>-12.35</v>
       </c>
       <c r="D91" s="6">
-        <v>-9.48</v>
+        <v>-10.89</v>
       </c>
       <c r="E91" s="7">
-        <v>-0.4</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-12.16</v>
+        <v>-23.59</v>
       </c>
       <c r="D92" s="6">
-        <v>-12.14</v>
-      </c>
-      <c r="E92" s="8">
-        <v>0.02</v>
+        <v>-22.2</v>
+      </c>
+      <c r="E92" s="7">
+        <v>1.39</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-11.88</v>
+        <v>-9.48</v>
       </c>
       <c r="D93" s="6">
-        <v>-12.48</v>
+        <v>-9.25</v>
       </c>
       <c r="E93" s="7">
-        <v>-0.6</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-14.58</v>
+        <v>-12.14</v>
       </c>
       <c r="D94" s="6">
-        <v>-13.8</v>
-      </c>
-      <c r="E94" s="8">
-        <v>0.78</v>
+        <v>-11.06</v>
+      </c>
+      <c r="E94" s="7">
+        <v>1.08</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-17.54</v>
+        <v>0</v>
       </c>
       <c r="D95" s="6">
-        <v>-17.33</v>
+        <v>-1.47</v>
       </c>
       <c r="E95" s="8">
-        <v>0.21</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-4.09</v>
+        <v>-12.48</v>
       </c>
       <c r="D96" s="6">
-        <v>-5.33</v>
+        <v>-12.39</v>
       </c>
       <c r="E96" s="7">
-        <v>-1.24</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-14.32</v>
+        <v>-13.8</v>
       </c>
       <c r="D97" s="6">
-        <v>-15.06</v>
-      </c>
-      <c r="E97" s="7">
-        <v>-0.74</v>
+        <v>-14.02</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-13.66</v>
+        <v>-17.33</v>
       </c>
       <c r="D98" s="6">
-        <v>-13.62</v>
+        <v>-18.61</v>
       </c>
       <c r="E98" s="8">
-        <v>0.04</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-6.38</v>
+        <v>-5.33</v>
       </c>
       <c r="D99" s="6">
-        <v>-7.55</v>
+        <v>-5.03</v>
       </c>
       <c r="E99" s="7">
-        <v>-1.17</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-7.48</v>
+        <v>-15.06</v>
       </c>
       <c r="D100" s="6">
-        <v>-7.05</v>
-      </c>
-      <c r="E100" s="8">
-        <v>0.43</v>
+        <v>-14.45</v>
+      </c>
+      <c r="E100" s="7">
+        <v>0.61</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-8.970000000000001</v>
+        <v>-13.62</v>
       </c>
       <c r="D101" s="6">
-        <v>-8.02</v>
-      </c>
-      <c r="E101" s="8">
-        <v>0.95</v>
+        <v>-12.04</v>
+      </c>
+      <c r="E101" s="7">
+        <v>1.58</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-6.38</v>
+        <v>-7.55</v>
       </c>
       <c r="D102" s="6">
-        <v>-6.92</v>
+        <v>-7.18</v>
       </c>
       <c r="E102" s="7">
-        <v>-0.54</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C103" s="6">
-        <v>25391.85</v>
+        <v>-7.05</v>
       </c>
       <c r="D103" s="6">
-        <v>25156.75</v>
-      </c>
-      <c r="E103" s="7">
-        <v>-235.1</v>
+        <v>-8.029999999999999</v>
+      </c>
+      <c r="E103" s="8">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C104" s="6">
-        <v>8955.450000000001</v>
+        <v>-8.02</v>
       </c>
       <c r="D104" s="6">
-        <v>9011.299999999999</v>
-      </c>
-      <c r="E104" s="8">
-        <v>55.85</v>
+        <v>-6.72</v>
+      </c>
+      <c r="E104" s="7">
+        <v>1.3</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C105" s="6">
-        <v>10948.6</v>
+        <v>-6.92</v>
       </c>
       <c r="D105" s="6">
-        <v>10910</v>
+        <v>-5.17</v>
       </c>
       <c r="E105" s="7">
-        <v>-38.6</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>35975.9</v>
+        <v>25156.75</v>
       </c>
       <c r="D106" s="6">
-        <v>36503.5</v>
-      </c>
-      <c r="E106" s="8">
-        <v>527.6</v>
+        <v>25576.4</v>
+      </c>
+      <c r="E106" s="7">
+        <v>419.65</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>44731.15</v>
+        <v>9011.299999999999</v>
       </c>
       <c r="D107" s="6">
-        <v>45271.7</v>
-      </c>
-      <c r="E107" s="8">
-        <v>540.55</v>
+        <v>9069.450000000001</v>
+      </c>
+      <c r="E107" s="7">
+        <v>58.15</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>25228.55</v>
+        <v>10910</v>
       </c>
       <c r="D108" s="6">
-        <v>24948.7</v>
+        <v>11005.25</v>
       </c>
       <c r="E108" s="7">
-        <v>-279.85</v>
+        <v>95.25</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>29830.1</v>
+        <v>36503.5</v>
       </c>
       <c r="D109" s="6">
-        <v>30171</v>
+        <v>36213.7</v>
       </c>
       <c r="E109" s="8">
-        <v>340.9</v>
+        <v>-289.8</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>15149.7</v>
+        <v>45271.7</v>
       </c>
       <c r="D110" s="6">
-        <v>15083.55</v>
-      </c>
-      <c r="E110" s="7">
-        <v>-66.15000000000001</v>
+        <v>44791.65</v>
+      </c>
+      <c r="E110" s="8">
+        <v>-480.05</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>8578.5</v>
+        <v>24948.7</v>
       </c>
       <c r="D111" s="6">
-        <v>8580.299999999999</v>
-      </c>
-      <c r="E111" s="8">
-        <v>1.8</v>
+        <v>25364.2</v>
+      </c>
+      <c r="E111" s="7">
+        <v>415.5</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>1631.7</v>
+        <v>30171</v>
       </c>
       <c r="D112" s="6">
-        <v>1641.35</v>
-      </c>
-      <c r="E112" s="8">
-        <v>9.65</v>
+        <v>30719.8</v>
+      </c>
+      <c r="E112" s="7">
+        <v>548.8</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>12088.25</v>
+        <v>15083.55</v>
       </c>
       <c r="D113" s="6">
-        <v>12006.75</v>
+        <v>15121.1</v>
       </c>
       <c r="E113" s="7">
-        <v>-81.5</v>
+        <v>37.55</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>9196.6</v>
+        <v>8580.299999999999</v>
       </c>
       <c r="D114" s="6">
-        <v>9280.799999999999</v>
-      </c>
-      <c r="E114" s="8">
-        <v>84.2</v>
+        <v>8685.9</v>
+      </c>
+      <c r="E114" s="7">
+        <v>105.6</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>8146.55</v>
+        <v>1641.35</v>
       </c>
       <c r="D115" s="6">
-        <v>8167.55</v>
+        <v>1617.2</v>
       </c>
       <c r="E115" s="8">
-        <v>21</v>
+        <v>-24.15</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>26075</v>
+        <v>12006.75</v>
       </c>
       <c r="D116" s="6">
-        <v>25736.95</v>
+        <v>12018.5</v>
       </c>
       <c r="E116" s="7">
-        <v>-338.05</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>829.95</v>
+        <v>9280.799999999999</v>
       </c>
       <c r="D117" s="6">
-        <v>822.8</v>
-      </c>
-      <c r="E117" s="7">
-        <v>-7.15</v>
+        <v>9257.15</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-23.65</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>29443</v>
+        <v>8167.55</v>
       </c>
       <c r="D118" s="6">
-        <v>29455.4</v>
+        <v>8041.2</v>
       </c>
       <c r="E118" s="8">
-        <v>12.4</v>
+        <v>-126.35</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>15860.65</v>
+        <v>25736.95</v>
       </c>
       <c r="D119" s="6">
-        <v>15663</v>
+        <v>25817.8</v>
       </c>
       <c r="E119" s="7">
-        <v>-197.65</v>
+        <v>80.84999999999999</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>9250.5</v>
+        <v>822.8</v>
       </c>
       <c r="D120" s="6">
-        <v>9294.1</v>
-      </c>
-      <c r="E120" s="8">
-        <v>43.6</v>
+        <v>828.7</v>
+      </c>
+      <c r="E120" s="7">
+        <v>5.9</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>10349.6</v>
+        <v>29455.4</v>
       </c>
       <c r="D121" s="6">
-        <v>10456.75</v>
-      </c>
-      <c r="E121" s="8">
-        <v>107.15</v>
+        <v>29995.85</v>
+      </c>
+      <c r="E121" s="7">
+        <v>540.45</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>27324.35</v>
+        <v>15663</v>
       </c>
       <c r="D122" s="6">
-        <v>27166.8</v>
+        <v>15724.4</v>
       </c>
       <c r="E122" s="7">
-        <v>-157.55</v>
+        <v>61.4</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C123" s="6">
-        <v>50</v>
+        <v>9294.1</v>
       </c>
       <c r="D123" s="6">
-        <v>38</v>
-      </c>
-      <c r="E123" s="7">
-        <v>-12</v>
+        <v>9196.25</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-97.84999999999999</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C124" s="6">
-        <v>44</v>
+        <v>10456.75</v>
       </c>
       <c r="D124" s="6">
-        <v>56</v>
-      </c>
-      <c r="E124" s="8">
-        <v>12</v>
+        <v>10604.6</v>
+      </c>
+      <c r="E124" s="7">
+        <v>147.85</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C125" s="6">
-        <v>56</v>
+        <v>27166.8</v>
       </c>
       <c r="D125" s="6">
-        <v>50</v>
+        <v>27679.3</v>
       </c>
       <c r="E125" s="7">
-        <v>-6</v>
+        <v>512.5</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="6">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="D126" s="6">
-        <v>26</v>
-      </c>
-      <c r="E126" s="7">
+        <v>50</v>
+      </c>
+      <c r="E126" s="8">
         <v>-6</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="D127" s="6">
-        <v>99</v>
-      </c>
-      <c r="E127" s="8">
+        <v>56</v>
+      </c>
+      <c r="E127" s="7">
         <v>6</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="D128" s="6">
-        <v>44</v>
-      </c>
-      <c r="E128" s="8">
-        <v>25</v>
+        <v>32</v>
+      </c>
+      <c r="E128" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
@@ -5481,388 +5493,405 @@
       <c r="D129" s="6">
         <v>93</v>
       </c>
-      <c r="E129" s="7">
+      <c r="E129" s="8">
         <v>-6</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C130" s="6">
+        <v>44</v>
+      </c>
+      <c r="D130" s="6">
         <v>26</v>
       </c>
-      <c r="D130" s="6">
-        <v>19</v>
-      </c>
-      <c r="E130" s="7">
-        <v>-7</v>
+      <c r="E130" s="8">
+        <v>-18</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="6">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="D131" s="6">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="E131" s="7">
-        <v>-6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C132" s="6">
-        <v>36.09</v>
+        <v>32</v>
       </c>
       <c r="D132" s="6">
-        <v>33.85</v>
+        <v>44</v>
       </c>
       <c r="E132" s="7">
-        <v>-2.24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="6">
-        <v>32.02</v>
+        <v>33.85</v>
       </c>
       <c r="D133" s="6">
-        <v>35.43</v>
-      </c>
-      <c r="E133" s="8">
-        <v>3.41</v>
+        <v>40.91</v>
+      </c>
+      <c r="E133" s="7">
+        <v>7.06</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="6">
-        <v>38.93</v>
+        <v>35.43</v>
       </c>
       <c r="D134" s="6">
-        <v>37.84</v>
+        <v>38.88</v>
       </c>
       <c r="E134" s="7">
-        <v>-1.09</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>33.76</v>
+        <v>37.84</v>
       </c>
       <c r="D135" s="6">
-        <v>43.23</v>
-      </c>
-      <c r="E135" s="8">
-        <v>9.470000000000001</v>
+        <v>42.15</v>
+      </c>
+      <c r="E135" s="7">
+        <v>4.31</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>45.4</v>
+        <v>43.23</v>
       </c>
       <c r="D136" s="6">
-        <v>49.5</v>
+        <v>39.86</v>
       </c>
       <c r="E136" s="8">
-        <v>4.1</v>
+        <v>-3.37</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>50.35</v>
+        <v>49.5</v>
       </c>
       <c r="D137" s="6">
-        <v>45.11</v>
-      </c>
-      <c r="E137" s="7">
-        <v>-5.24</v>
+        <v>46.18</v>
+      </c>
+      <c r="E137" s="8">
+        <v>-3.32</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>60.51</v>
+        <v>45.11</v>
       </c>
       <c r="D138" s="6">
-        <v>63.13</v>
-      </c>
-      <c r="E138" s="8">
-        <v>2.62</v>
+        <v>52.94</v>
+      </c>
+      <c r="E138" s="7">
+        <v>7.83</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>36.98</v>
+        <v>63.13</v>
       </c>
       <c r="D139" s="6">
-        <v>35.6</v>
+        <v>66.95</v>
       </c>
       <c r="E139" s="7">
-        <v>-1.38</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>35.88</v>
+        <v>35.6</v>
       </c>
       <c r="D140" s="6">
-        <v>35.99</v>
-      </c>
-      <c r="E140" s="8">
-        <v>0.11</v>
+        <v>37.03</v>
+      </c>
+      <c r="E140" s="7">
+        <v>1.43</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>62.48</v>
+        <v>35.99</v>
       </c>
       <c r="D141" s="6">
-        <v>63.79</v>
-      </c>
-      <c r="E141" s="8">
-        <v>1.31</v>
+        <v>42.61</v>
+      </c>
+      <c r="E141" s="7">
+        <v>6.62</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>36.52</v>
+        <v>63.79</v>
       </c>
       <c r="D142" s="6">
-        <v>35.15</v>
-      </c>
-      <c r="E142" s="7">
-        <v>-1.37</v>
+        <v>58.31</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-5.48</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>38.01</v>
+        <v>35.15</v>
       </c>
       <c r="D143" s="6">
-        <v>43.24</v>
-      </c>
-      <c r="E143" s="8">
-        <v>5.23</v>
+        <v>35.52</v>
+      </c>
+      <c r="E143" s="7">
+        <v>0.37</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>47.26</v>
+        <v>43.24</v>
       </c>
       <c r="D144" s="6">
-        <v>48.34</v>
+        <v>42.17</v>
       </c>
       <c r="E144" s="8">
-        <v>1.08</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>42.9</v>
+        <v>48.34</v>
       </c>
       <c r="D145" s="6">
-        <v>37.94</v>
-      </c>
-      <c r="E145" s="7">
-        <v>-4.96</v>
+        <v>42.69</v>
+      </c>
+      <c r="E145" s="8">
+        <v>-5.65</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>44.63</v>
+        <v>37.94</v>
       </c>
       <c r="D146" s="6">
-        <v>42.62</v>
+        <v>39.74</v>
       </c>
       <c r="E146" s="7">
-        <v>-2.01</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>47.47</v>
+        <v>42.62</v>
       </c>
       <c r="D147" s="6">
-        <v>47.69</v>
-      </c>
-      <c r="E147" s="8">
-        <v>0.22</v>
+        <v>44.82</v>
+      </c>
+      <c r="E147" s="7">
+        <v>2.2</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>36.95</v>
+        <v>47.69</v>
       </c>
       <c r="D148" s="6">
-        <v>32.82</v>
+        <v>56.39</v>
       </c>
       <c r="E148" s="7">
-        <v>-4.13</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>47.29</v>
+        <v>32.82</v>
       </c>
       <c r="D149" s="6">
-        <v>48.84</v>
-      </c>
-      <c r="E149" s="8">
-        <v>1.55</v>
+        <v>35.24</v>
+      </c>
+      <c r="E149" s="7">
+        <v>2.42</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>31.63</v>
+        <v>48.84</v>
       </c>
       <c r="D150" s="6">
-        <v>38.25</v>
+        <v>45.6</v>
       </c>
       <c r="E150" s="8">
-        <v>6.62</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>53.97</v>
+        <v>38.25</v>
       </c>
       <c r="D151" s="6">
+        <v>46.01</v>
+      </c>
+      <c r="E151" s="7">
+        <v>7.76</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
+      <c r="A152" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C152" s="6">
         <v>50.53</v>
       </c>
-      <c r="E151" s="7">
-        <v>-3.44</v>
+      <c r="D152" s="6">
+        <v>59.55</v>
+      </c>
+      <c r="E152" s="7">
+        <v>9.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A8:E8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5886,28 +5915,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5915,22 +5944,22 @@
         <v>78</v>
       </c>
       <c r="B2" s="11">
-        <v>35.24</v>
+        <v>39.24</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>43.4</v>
+        <v>45.7</v>
       </c>
       <c r="E2" s="11">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-3</v>
+        <v>-0.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.2</v>
+        <v>-3.8</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -6056,13 +6085,13 @@
         <v>46</v>
       </c>
       <c r="G1" s="13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="I1" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>41</v>
@@ -6070,39 +6099,39 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2463</v>
+        <v>0.2332</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1635</v>
+        <v>0.1674</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1617</v>
+        <v>0.1574</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1481</v>
+        <v>0.1399</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1181</v>
+        <v>0.121</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1024</v>
+        <v>0.1042</v>
       </c>
       <c r="G2" s="14">
-        <v>0.101</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0882</v>
+        <v>0.0796</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0824</v>
+        <v>0.0793</v>
       </c>
       <c r="J2" s="14">
-        <v>0.08070000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>57</v>
@@ -6111,10 +6140,10 @@
         <v>43</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>53</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>42</v>
@@ -6134,34 +6163,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0762</v>
+        <v>0.0667</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0584</v>
+        <v>0.0607</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0566</v>
+        <v>0.0592</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0302</v>
+        <v>0.0328</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0212</v>
+        <v>0.03240000000000001</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0182</v>
+        <v>0.0151</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0333</v>
+        <v>-0.0329</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0693</v>
+        <v>-0.0709</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1051</v>
+        <v>-0.0978</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.1414</v>
+        <v>-0.1044</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="107">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,34 +289,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.1 → 52.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.1</t>
-  </si>
-  <si>
-    <t>52.9</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>47.7 → 56.4</t>
-  </si>
-  <si>
-    <t>47.7</t>
-  </si>
-  <si>
-    <t>56.4</t>
+    <t>RSI Overbought Entry</t>
+  </si>
+  <si>
+    <t>67.0 → 73.4</t>
+  </si>
+  <si>
+    <t>⚠️ CAUTION</t>
+  </si>
+  <si>
+    <t>67.0</t>
+  </si>
+  <si>
+    <t>73.4</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -368,7 +353,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,6 +387,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -415,7 +407,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,6 +429,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -528,12 +526,12 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -542,7 +540,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1046,10 +1044,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>25576.4</v>
+        <v>25768.5</v>
       </c>
       <c r="E2">
-        <v>1.67</v>
+        <v>0.75</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1058,43 +1056,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-13.73</v>
+        <v>-13.08</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>8.41</v>
       </c>
       <c r="J2">
-        <v>4.34</v>
+        <v>3.65</v>
       </c>
       <c r="K2">
-        <v>-4.41</v>
+        <v>-4.18</v>
       </c>
       <c r="L2">
-        <v>-4.45</v>
+        <v>-4.91</v>
       </c>
       <c r="M2">
-        <v>-5.04</v>
+        <v>-2.84</v>
       </c>
       <c r="N2">
-        <v>16.74</v>
+        <v>16.9</v>
       </c>
       <c r="O2">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="Q2">
-        <v>25213.86</v>
+        <v>25395.58</v>
       </c>
       <c r="R2">
-        <v>26022.16</v>
+        <v>25952.62</v>
       </c>
       <c r="S2">
-        <v>27588.58</v>
+        <v>27515.72</v>
       </c>
       <c r="T2">
-        <v>26969.56</v>
+        <v>26958.95</v>
       </c>
       <c r="U2">
-        <v>-5.17</v>
+        <v>-4.42</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1109,31 +1107,31 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>40.91</v>
+        <v>43.86</v>
       </c>
       <c r="AA2">
-        <v>-671.3099999999999</v>
+        <v>-602.62</v>
       </c>
       <c r="AB2">
-        <v>-688.87</v>
+        <v>-671.62</v>
       </c>
       <c r="AC2">
-        <v>17.56</v>
+        <v>69</v>
       </c>
       <c r="AD2">
         <v>95.69</v>
       </c>
       <c r="AE2">
-        <v>84.19</v>
+        <v>92.34</v>
       </c>
       <c r="AF2">
-        <v>437.18</v>
+        <v>433.12</v>
       </c>
       <c r="AH2">
-        <v>27833.81</v>
+        <v>27685.57</v>
       </c>
       <c r="AI2">
-        <v>24210.51</v>
+        <v>24219.68</v>
       </c>
       <c r="AJ2">
         <v>26008.9</v>
@@ -1142,7 +1140,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>68.68000000000001</v>
+        <v>62.32</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1156,10 +1154,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>9069.450000000001</v>
+        <v>9099.5</v>
       </c>
       <c r="E3">
-        <v>0.65</v>
+        <v>0.33</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1168,43 +1166,43 @@
         <v>8851.4</v>
       </c>
       <c r="H3">
-        <v>-13.65</v>
+        <v>-13.36</v>
       </c>
       <c r="I3">
-        <v>2.46</v>
+        <v>2.8</v>
       </c>
       <c r="J3">
-        <v>2.46</v>
+        <v>1.97</v>
       </c>
       <c r="K3">
-        <v>-3.59</v>
+        <v>-3.63</v>
       </c>
       <c r="L3">
-        <v>-7.62</v>
+        <v>-7.45</v>
       </c>
       <c r="M3">
-        <v>-0.31</v>
+        <v>0.8</v>
       </c>
       <c r="N3">
-        <v>7.96</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="Q3">
-        <v>8967.02</v>
+        <v>9002.24</v>
       </c>
       <c r="R3">
-        <v>9260.700000000001</v>
+        <v>9240.59</v>
       </c>
       <c r="S3">
-        <v>9577.66</v>
+        <v>9559.57</v>
       </c>
       <c r="T3">
-        <v>9767.09</v>
+        <v>9765.889999999999</v>
       </c>
       <c r="U3">
-        <v>-7.14</v>
+        <v>-6.82</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1219,31 +1217,31 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>38.88</v>
+        <v>40.64</v>
       </c>
       <c r="AA3">
-        <v>-184.28</v>
+        <v>-170.65</v>
       </c>
       <c r="AB3">
-        <v>-172.48</v>
+        <v>-172.11</v>
       </c>
       <c r="AC3">
-        <v>-11.8</v>
+        <v>1.46</v>
       </c>
       <c r="AD3">
-        <v>61.06</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="AE3">
-        <v>40.82</v>
+        <v>60.6</v>
       </c>
       <c r="AF3">
-        <v>130.7</v>
+        <v>130.68</v>
       </c>
       <c r="AH3">
-        <v>9782.639999999999</v>
+        <v>9754.389999999999</v>
       </c>
       <c r="AI3">
-        <v>8738.75</v>
+        <v>8726.799999999999</v>
       </c>
       <c r="AJ3">
         <v>9261.98</v>
@@ -1252,7 +1250,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>53.3</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1266,10 +1264,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11005.25</v>
+        <v>11054.65</v>
       </c>
       <c r="E4">
-        <v>0.87</v>
+        <v>0.45</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1278,43 +1276,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-12.93</v>
+        <v>-12.54</v>
       </c>
       <c r="I4">
-        <v>6.49</v>
+        <v>6.97</v>
       </c>
       <c r="J4">
-        <v>2.46</v>
+        <v>1.39</v>
       </c>
       <c r="K4">
-        <v>-2.46</v>
+        <v>-2.7</v>
       </c>
       <c r="L4">
-        <v>-5.62</v>
+        <v>-5.56</v>
       </c>
       <c r="M4">
-        <v>-9.98</v>
+        <v>-9.27</v>
       </c>
       <c r="N4">
-        <v>7.93</v>
+        <v>8.02</v>
       </c>
       <c r="O4">
         <v>13</v>
       </c>
       <c r="Q4">
-        <v>10918.11</v>
+        <v>10948.35</v>
       </c>
       <c r="R4">
-        <v>11144.4</v>
+        <v>11125.73</v>
       </c>
       <c r="S4">
-        <v>11582.72</v>
+        <v>11559.36</v>
       </c>
       <c r="T4">
-        <v>11523.66</v>
+        <v>11517.52</v>
       </c>
       <c r="U4">
-        <v>-4.5</v>
+        <v>-4.02</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1329,31 +1327,31 @@
         <v>1</v>
       </c>
       <c r="Z4">
-        <v>42.15</v>
+        <v>44.3</v>
       </c>
       <c r="AA4">
-        <v>-190.08</v>
+        <v>-171.96</v>
       </c>
       <c r="AB4">
-        <v>-197.33</v>
+        <v>-192.26</v>
       </c>
       <c r="AC4">
-        <v>7.25</v>
+        <v>20.29</v>
       </c>
       <c r="AD4">
-        <v>91.22</v>
+        <v>97.84</v>
       </c>
       <c r="AE4">
-        <v>77.15000000000001</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="AF4">
-        <v>142.45</v>
+        <v>139.5</v>
       </c>
       <c r="AH4">
-        <v>11671.49</v>
+        <v>11636.73</v>
       </c>
       <c r="AI4">
-        <v>10617.3</v>
+        <v>10614.73</v>
       </c>
       <c r="AJ4">
         <v>11255.06</v>
@@ -1362,7 +1360,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>53.73</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1376,10 +1374,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>36213.7</v>
+        <v>36190.85</v>
       </c>
       <c r="E5">
-        <v>-0.79</v>
+        <v>-0.06</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1388,43 +1386,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-12.81</v>
+        <v>-12.87</v>
       </c>
       <c r="I5">
-        <v>9.41</v>
+        <v>9.34</v>
       </c>
       <c r="J5">
-        <v>1.58</v>
+        <v>1.13</v>
       </c>
       <c r="K5">
-        <v>-2.51</v>
+        <v>-2.67</v>
       </c>
       <c r="L5">
-        <v>-7.96</v>
+        <v>-7.86</v>
       </c>
       <c r="M5">
-        <v>2.1</v>
+        <v>3.15</v>
       </c>
       <c r="N5">
-        <v>7.58</v>
+        <v>7.56</v>
       </c>
       <c r="O5">
         <v>62</v>
       </c>
       <c r="Q5">
-        <v>36067.35</v>
+        <v>36148.22</v>
       </c>
       <c r="R5">
-        <v>36783.44</v>
+        <v>36723.9</v>
       </c>
       <c r="S5">
-        <v>37655.96</v>
+        <v>37603.18</v>
       </c>
       <c r="T5">
-        <v>37728.64</v>
+        <v>37733.52</v>
       </c>
       <c r="U5">
-        <v>-4.02</v>
+        <v>-4.09</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1439,31 +1437,31 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>39.86</v>
+        <v>39.6</v>
       </c>
       <c r="AA5">
-        <v>-486.19</v>
+        <v>-466.64</v>
       </c>
       <c r="AB5">
-        <v>-480.47</v>
+        <v>-477.7</v>
       </c>
       <c r="AC5">
-        <v>-5.72</v>
+        <v>11.06</v>
       </c>
       <c r="AD5">
-        <v>72.48999999999999</v>
+        <v>85.34</v>
       </c>
       <c r="AE5">
-        <v>50.96</v>
+        <v>70.72</v>
       </c>
       <c r="AF5">
-        <v>493.38</v>
+        <v>497.73</v>
       </c>
       <c r="AH5">
-        <v>38200.32</v>
+        <v>38134.99</v>
       </c>
       <c r="AI5">
-        <v>35366.57</v>
+        <v>35312.81</v>
       </c>
       <c r="AJ5">
         <v>37083.58</v>
@@ -1472,7 +1470,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>37.89</v>
+        <v>36.52</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1486,10 +1484,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>44791.65</v>
+        <v>44616.15</v>
       </c>
       <c r="E6">
-        <v>-1.06</v>
+        <v>-0.39</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1498,43 +1496,43 @@
         <v>43789.85</v>
       </c>
       <c r="H6">
-        <v>-21.1</v>
+        <v>-21.41</v>
       </c>
       <c r="I6">
-        <v>2.29</v>
+        <v>1.89</v>
       </c>
       <c r="J6">
-        <v>2.04</v>
+        <v>-0.55</v>
       </c>
       <c r="K6">
-        <v>-0.09</v>
+        <v>-2.07</v>
       </c>
       <c r="L6">
-        <v>-7.47</v>
+        <v>-8.48</v>
       </c>
       <c r="M6">
-        <v>-18.21</v>
+        <v>-18.12</v>
       </c>
       <c r="N6">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="O6">
         <v>7</v>
       </c>
       <c r="Q6">
-        <v>44754.43</v>
+        <v>44704.81</v>
       </c>
       <c r="R6">
-        <v>45058.36</v>
+        <v>45010.53</v>
       </c>
       <c r="S6">
-        <v>46332.27</v>
+        <v>46236.92</v>
       </c>
       <c r="T6">
-        <v>49215.92</v>
+        <v>49162.25</v>
       </c>
       <c r="U6">
-        <v>-8.99</v>
+        <v>-9.25</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1549,31 +1547,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>46.18</v>
+        <v>45</v>
       </c>
       <c r="AA6">
-        <v>-436.86</v>
+        <v>-421.2</v>
       </c>
       <c r="AB6">
-        <v>-537.16</v>
+        <v>-513.97</v>
       </c>
       <c r="AC6">
-        <v>100.3</v>
+        <v>92.77</v>
       </c>
       <c r="AD6">
-        <v>89.87</v>
+        <v>87.72</v>
       </c>
       <c r="AE6">
-        <v>82.54000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="AF6">
-        <v>721.9</v>
+        <v>705.92</v>
       </c>
       <c r="AH6">
-        <v>46439.24</v>
+        <v>46382.63</v>
       </c>
       <c r="AI6">
-        <v>43677.48</v>
+        <v>43638.43</v>
       </c>
       <c r="AJ6">
         <v>45688.38</v>
@@ -1582,7 +1580,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>32.86</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1596,10 +1594,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>25364.2</v>
+        <v>25387.1</v>
       </c>
       <c r="E7">
-        <v>1.67</v>
+        <v>0.09</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1608,43 +1606,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-10.89</v>
+        <v>-10.81</v>
       </c>
       <c r="I7">
-        <v>7.83</v>
+        <v>7.93</v>
       </c>
       <c r="J7">
-        <v>2.94</v>
+        <v>1.68</v>
       </c>
       <c r="K7">
-        <v>1.15</v>
+        <v>0.49</v>
       </c>
       <c r="L7">
-        <v>-4.49</v>
+        <v>-5.64</v>
       </c>
       <c r="M7">
-        <v>-5.28</v>
+        <v>-4.76</v>
       </c>
       <c r="N7">
-        <v>5.92</v>
+        <v>5.94</v>
       </c>
       <c r="O7">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="Q7">
-        <v>25075.26</v>
+        <v>25158.98</v>
       </c>
       <c r="R7">
-        <v>25022.31</v>
+        <v>25025.75</v>
       </c>
       <c r="S7">
-        <v>25663.37</v>
+        <v>25634.23</v>
       </c>
       <c r="T7">
-        <v>26305.1</v>
+        <v>26294.11</v>
       </c>
       <c r="U7">
-        <v>-3.58</v>
+        <v>-3.45</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1659,31 +1657,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>52.94</v>
+        <v>53.34</v>
       </c>
       <c r="AA7">
-        <v>-170.26</v>
+        <v>-128.32</v>
       </c>
       <c r="AB7">
-        <v>-260.92</v>
+        <v>-234.4</v>
       </c>
       <c r="AC7">
-        <v>90.65000000000001</v>
+        <v>106.08</v>
       </c>
       <c r="AD7">
         <v>91.64</v>
       </c>
       <c r="AE7">
-        <v>91.59</v>
+        <v>90.22</v>
       </c>
       <c r="AF7">
-        <v>346.09</v>
+        <v>342.14</v>
       </c>
       <c r="AH7">
-        <v>25694.54</v>
+        <v>25705.02</v>
       </c>
       <c r="AI7">
-        <v>24350.08</v>
+        <v>24346.48</v>
       </c>
       <c r="AJ7">
         <v>25420.21</v>
@@ -1692,7 +1690,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>26.01</v>
+        <v>26.02</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1706,10 +1704,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>30719.8</v>
+        <v>31924.1</v>
       </c>
       <c r="E8">
-        <v>1.82</v>
+        <v>3.92</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1718,43 +1716,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-22.2</v>
+        <v>-19.15</v>
       </c>
       <c r="I8">
-        <v>19.21</v>
+        <v>23.88</v>
       </c>
       <c r="J8">
-        <v>10.76</v>
+        <v>11.72</v>
       </c>
       <c r="K8">
-        <v>3.94</v>
+        <v>9.75</v>
       </c>
       <c r="L8">
-        <v>6.95</v>
+        <v>9.23</v>
       </c>
       <c r="M8">
-        <v>-11.49</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="N8">
-        <v>-3.29</v>
+        <v>-2.54</v>
       </c>
       <c r="O8">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="Q8">
-        <v>29529.08</v>
+        <v>30198.92</v>
       </c>
       <c r="R8">
-        <v>28573.52</v>
+        <v>28711.95</v>
       </c>
       <c r="S8">
-        <v>29803.95</v>
+        <v>29814.35</v>
       </c>
       <c r="T8">
-        <v>30981.77</v>
+        <v>30945.52</v>
       </c>
       <c r="U8">
-        <v>-0.85</v>
+        <v>3.16</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1766,43 +1764,43 @@
         <v>79</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8">
-        <v>66.95</v>
+        <v>73.44</v>
       </c>
       <c r="AA8">
-        <v>25.65</v>
+        <v>251.93</v>
       </c>
       <c r="AB8">
-        <v>-326.08</v>
+        <v>-210.48</v>
       </c>
       <c r="AC8">
-        <v>351.73</v>
+        <v>462.41</v>
       </c>
       <c r="AD8">
         <v>100</v>
       </c>
       <c r="AE8">
-        <v>96.95999999999999</v>
+        <v>98.48</v>
       </c>
       <c r="AF8">
-        <v>693.13</v>
+        <v>736.1799999999999</v>
       </c>
       <c r="AH8">
-        <v>30236.99</v>
+        <v>30943.22</v>
       </c>
       <c r="AI8">
-        <v>26910.05</v>
+        <v>26480.68</v>
       </c>
       <c r="AJ8">
-        <v>28684.46</v>
+        <v>29251.33</v>
       </c>
       <c r="AK8" t="s">
         <v>82</v>
       </c>
       <c r="AL8">
-        <v>37.24</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1816,10 +1814,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>15121.1</v>
+        <v>15174.1</v>
       </c>
       <c r="E9">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1828,31 +1826,31 @@
         <v>14845.15</v>
       </c>
       <c r="H9">
-        <v>-9.25</v>
+        <v>-8.93</v>
       </c>
       <c r="I9">
-        <v>1.86</v>
+        <v>2.22</v>
       </c>
       <c r="J9">
-        <v>1.86</v>
+        <v>1.48</v>
       </c>
       <c r="K9">
-        <v>-2.97</v>
+        <v>-2.83</v>
       </c>
       <c r="L9">
-        <v>-5.22</v>
+        <v>-4.72</v>
       </c>
       <c r="N9">
-        <v>-9.779999999999999</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="Q9">
-        <v>15069.78</v>
+        <v>15113.99</v>
       </c>
       <c r="R9">
-        <v>15459.16</v>
+        <v>15426.53</v>
       </c>
       <c r="S9">
-        <v>16023.51</v>
+        <v>15995.16</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1864,31 +1862,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>37.03</v>
+        <v>39.1</v>
       </c>
       <c r="AA9">
-        <v>-278.52</v>
+        <v>-262.56</v>
       </c>
       <c r="AB9">
-        <v>-267.28</v>
+        <v>-266.33</v>
       </c>
       <c r="AC9">
-        <v>-11.24</v>
+        <v>3.77</v>
       </c>
       <c r="AD9">
-        <v>64.68000000000001</v>
+        <v>78.47</v>
       </c>
       <c r="AE9">
-        <v>52.59</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="AF9">
-        <v>198.67</v>
+        <v>197.17</v>
       </c>
       <c r="AH9">
-        <v>16221.55</v>
+        <v>16178.48</v>
       </c>
       <c r="AI9">
-        <v>14696.77</v>
+        <v>14674.58</v>
       </c>
       <c r="AJ9">
         <v>15490.29</v>
@@ -1897,7 +1895,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>57.06</v>
+        <v>55.86</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1911,10 +1909,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8685.9</v>
+        <v>8725.6</v>
       </c>
       <c r="E10">
-        <v>1.23</v>
+        <v>0.46</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1923,43 +1921,43 @@
         <v>8499.65</v>
       </c>
       <c r="H10">
-        <v>-11.06</v>
+        <v>-10.65</v>
       </c>
       <c r="I10">
-        <v>2.19</v>
+        <v>2.66</v>
       </c>
       <c r="J10">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="K10">
-        <v>-2.52</v>
+        <v>-2.06</v>
       </c>
       <c r="L10">
-        <v>-6.92</v>
+        <v>-6.95</v>
       </c>
       <c r="M10">
-        <v>-5.07</v>
+        <v>-4.03</v>
       </c>
       <c r="N10">
-        <v>10.42</v>
+        <v>10.52</v>
       </c>
       <c r="O10">
         <v>32</v>
       </c>
       <c r="Q10">
-        <v>8583.76</v>
+        <v>8613.99</v>
       </c>
       <c r="R10">
-        <v>8780.92</v>
+        <v>8768.74</v>
       </c>
       <c r="S10">
-        <v>9077.93</v>
+        <v>9063.389999999999</v>
       </c>
       <c r="T10">
-        <v>9249.17</v>
+        <v>9244.719999999999</v>
       </c>
       <c r="U10">
-        <v>-6.09</v>
+        <v>-5.62</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1974,31 +1972,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>42.61</v>
+        <v>44.92</v>
       </c>
       <c r="AA10">
-        <v>-144.93</v>
+        <v>-129.93</v>
       </c>
       <c r="AB10">
-        <v>-146.17</v>
+        <v>-142.93</v>
       </c>
       <c r="AC10">
-        <v>1.25</v>
+        <v>12.99</v>
       </c>
       <c r="AD10">
-        <v>80.8</v>
+        <v>94.13</v>
       </c>
       <c r="AE10">
-        <v>62.73</v>
+        <v>78.17</v>
       </c>
       <c r="AF10">
-        <v>119.09</v>
+        <v>118.58</v>
       </c>
       <c r="AH10">
-        <v>9177.09</v>
+        <v>9155.389999999999</v>
       </c>
       <c r="AI10">
-        <v>8384.75</v>
+        <v>8382.08</v>
       </c>
       <c r="AJ10">
         <v>8855.59</v>
@@ -2007,7 +2005,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>50.49</v>
+        <v>44.59</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2021,55 +2019,55 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1617.2</v>
+        <v>1648.25</v>
       </c>
       <c r="E11">
-        <v>-1.47</v>
+        <v>1.92</v>
       </c>
       <c r="F11">
-        <v>1641.35</v>
+        <v>1648.25</v>
       </c>
       <c r="G11">
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-1.47</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>29.03</v>
+        <v>31.51</v>
       </c>
       <c r="J11">
-        <v>5.39</v>
+        <v>6.11</v>
       </c>
       <c r="K11">
-        <v>7.53</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L11">
-        <v>6.3</v>
+        <v>8.33</v>
       </c>
       <c r="M11">
-        <v>2.15</v>
+        <v>5.93</v>
       </c>
       <c r="N11">
-        <v>-7.09</v>
+        <v>-6.73</v>
       </c>
       <c r="O11">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="Q11">
-        <v>1613.67</v>
+        <v>1632.66</v>
       </c>
       <c r="R11">
-        <v>1570.43</v>
+        <v>1576.18</v>
       </c>
       <c r="S11">
-        <v>1569.17</v>
+        <v>1570.63</v>
       </c>
       <c r="T11">
-        <v>1464.49</v>
+        <v>1465.66</v>
       </c>
       <c r="U11">
-        <v>10.43</v>
+        <v>12.46</v>
       </c>
       <c r="V11" t="s">
         <v>80</v>
@@ -2084,40 +2082,40 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>58.31</v>
+        <v>62.74</v>
       </c>
       <c r="AA11">
-        <v>16.34</v>
+        <v>19.71</v>
       </c>
       <c r="AB11">
-        <v>7.37</v>
+        <v>9.84</v>
       </c>
       <c r="AC11">
-        <v>8.970000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AD11">
-        <v>90</v>
+        <v>88.08</v>
       </c>
       <c r="AE11">
-        <v>89.44</v>
+        <v>92.69</v>
       </c>
       <c r="AF11">
-        <v>35.96</v>
+        <v>35.85</v>
       </c>
       <c r="AH11">
-        <v>1636.65</v>
+        <v>1648.49</v>
       </c>
       <c r="AI11">
-        <v>1504.2</v>
+        <v>1503.87</v>
       </c>
       <c r="AJ11">
-        <v>1526.96</v>
+        <v>1528.14</v>
       </c>
       <c r="AK11" t="s">
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>25.79</v>
+        <v>26.73</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2131,10 +2129,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>12018.5</v>
+        <v>12133.2</v>
       </c>
       <c r="E12">
-        <v>0.1</v>
+        <v>0.95</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2143,43 +2141,43 @@
         <v>10017.9</v>
       </c>
       <c r="H12">
-        <v>-12.39</v>
+        <v>-11.55</v>
       </c>
       <c r="I12">
-        <v>19.97</v>
+        <v>21.12</v>
       </c>
       <c r="J12">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="K12">
-        <v>-5.14</v>
+        <v>-4.76</v>
       </c>
       <c r="L12">
-        <v>-3.82</v>
+        <v>-2.44</v>
       </c>
       <c r="M12">
-        <v>18.33</v>
+        <v>19.7</v>
       </c>
       <c r="N12">
-        <v>13.99</v>
+        <v>14.19</v>
       </c>
       <c r="O12">
         <v>87</v>
       </c>
       <c r="Q12">
-        <v>12013.08</v>
+        <v>12039.57</v>
       </c>
       <c r="R12">
-        <v>12583.78</v>
+        <v>12547.51</v>
       </c>
       <c r="S12">
-        <v>12934.13</v>
+        <v>12911.67</v>
       </c>
       <c r="T12">
-        <v>12452.24</v>
+        <v>12459.27</v>
       </c>
       <c r="U12">
-        <v>-3.48</v>
+        <v>-2.62</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2194,31 +2192,31 @@
         <v>1</v>
       </c>
       <c r="Z12">
-        <v>35.52</v>
+        <v>39.22</v>
       </c>
       <c r="AA12">
-        <v>-285.02</v>
+        <v>-274.56</v>
       </c>
       <c r="AB12">
-        <v>-219.31</v>
+        <v>-230.36</v>
       </c>
       <c r="AC12">
-        <v>-65.70999999999999</v>
+        <v>-44.2</v>
       </c>
       <c r="AD12">
-        <v>27.98</v>
+        <v>37.41</v>
       </c>
       <c r="AE12">
-        <v>22.45</v>
+        <v>29.11</v>
       </c>
       <c r="AF12">
-        <v>237.08</v>
+        <v>234.63</v>
       </c>
       <c r="AH12">
-        <v>13510.62</v>
+        <v>13485.79</v>
       </c>
       <c r="AI12">
-        <v>11656.93</v>
+        <v>11609.24</v>
       </c>
       <c r="AJ12">
         <v>12667.92</v>
@@ -2227,7 +2225,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>52.71</v>
+        <v>50.91</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2241,10 +2239,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9257.15</v>
+        <v>9247.299999999999</v>
       </c>
       <c r="E13">
-        <v>-0.25</v>
+        <v>-0.11</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2253,43 +2251,43 @@
         <v>9010.450000000001</v>
       </c>
       <c r="H13">
-        <v>-14.02</v>
+        <v>-14.11</v>
       </c>
       <c r="I13">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="J13">
-        <v>2.74</v>
+        <v>1.87</v>
       </c>
       <c r="K13">
-        <v>-2.22</v>
+        <v>-2.61</v>
       </c>
       <c r="L13">
-        <v>-6.6</v>
+        <v>-6.96</v>
       </c>
       <c r="M13">
-        <v>-6.77</v>
+        <v>-5.82</v>
       </c>
       <c r="N13">
-        <v>15.74</v>
+        <v>15.71</v>
       </c>
       <c r="O13">
         <v>26</v>
       </c>
       <c r="Q13">
-        <v>9182.18</v>
+        <v>9216.09</v>
       </c>
       <c r="R13">
-        <v>9361.23</v>
+        <v>9345.879999999999</v>
       </c>
       <c r="S13">
-        <v>9599.32</v>
+        <v>9585.24</v>
       </c>
       <c r="T13">
-        <v>9998.18</v>
+        <v>9995.73</v>
       </c>
       <c r="U13">
-        <v>-7.41</v>
+        <v>-7.49</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2304,31 +2302,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>42.17</v>
+        <v>41.7</v>
       </c>
       <c r="AA13">
-        <v>-128.64</v>
+        <v>-120.01</v>
       </c>
       <c r="AB13">
-        <v>-131.85</v>
+        <v>-129.48</v>
       </c>
       <c r="AC13">
-        <v>3.2</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="AD13">
-        <v>87.8</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="AE13">
-        <v>66.94</v>
+        <v>83.91</v>
       </c>
       <c r="AF13">
-        <v>120</v>
+        <v>119.24</v>
       </c>
       <c r="AH13">
-        <v>9755.950000000001</v>
+        <v>9732.780000000001</v>
       </c>
       <c r="AI13">
-        <v>8966.52</v>
+        <v>8958.98</v>
       </c>
       <c r="AJ13">
         <v>9403.969999999999</v>
@@ -2337,7 +2335,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>52.13</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2351,55 +2349,55 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8041.2</v>
+        <v>8094.95</v>
       </c>
       <c r="E14">
-        <v>-1.55</v>
+        <v>0.67</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
       </c>
       <c r="G14">
-        <v>7523.45</v>
+        <v>7569.3</v>
       </c>
       <c r="H14">
-        <v>-18.61</v>
+        <v>-18.07</v>
       </c>
       <c r="I14">
-        <v>6.88</v>
+        <v>6.94</v>
       </c>
       <c r="J14">
-        <v>0.57</v>
+        <v>-0.39</v>
       </c>
       <c r="K14">
-        <v>-1.44</v>
+        <v>-2.19</v>
       </c>
       <c r="L14">
-        <v>-3.67</v>
+        <v>-3.42</v>
       </c>
       <c r="M14">
-        <v>6.03</v>
+        <v>7.6</v>
       </c>
       <c r="N14">
-        <v>23.32</v>
+        <v>23.47</v>
       </c>
       <c r="O14">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="Q14">
-        <v>8102.46</v>
+        <v>8096.18</v>
       </c>
       <c r="R14">
-        <v>8133.41</v>
+        <v>8125.01</v>
       </c>
       <c r="S14">
-        <v>8392.35</v>
+        <v>8383.43</v>
       </c>
       <c r="T14">
-        <v>8574.860000000001</v>
+        <v>8573.6</v>
       </c>
       <c r="U14">
-        <v>-6.22</v>
+        <v>-5.58</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2414,31 +2412,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>42.69</v>
+        <v>45.6</v>
       </c>
       <c r="AA14">
-        <v>-83.55</v>
+        <v>-77.66</v>
       </c>
       <c r="AB14">
-        <v>-100.1</v>
+        <v>-95.61</v>
       </c>
       <c r="AC14">
-        <v>16.55</v>
+        <v>17.95</v>
       </c>
       <c r="AD14">
-        <v>89.89</v>
+        <v>84.98999999999999</v>
       </c>
       <c r="AE14">
-        <v>88.73999999999999</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="AF14">
-        <v>146.8</v>
+        <v>143.57</v>
       </c>
       <c r="AH14">
-        <v>8409.030000000001</v>
+        <v>8394.190000000001</v>
       </c>
       <c r="AI14">
-        <v>7857.78</v>
+        <v>7855.83</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
@@ -2447,7 +2445,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>22.85</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2461,10 +2459,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>25817.8</v>
+        <v>25781.65</v>
       </c>
       <c r="E15">
-        <v>0.31</v>
+        <v>-0.14</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2473,43 +2471,43 @@
         <v>21549.55</v>
       </c>
       <c r="H15">
-        <v>-5.03</v>
+        <v>-5.17</v>
       </c>
       <c r="I15">
-        <v>19.81</v>
+        <v>19.64</v>
       </c>
       <c r="J15">
-        <v>-0.02</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="K15">
-        <v>-1.42</v>
+        <v>-1.39</v>
       </c>
       <c r="L15">
-        <v>-0.73</v>
+        <v>0.53</v>
       </c>
       <c r="M15">
-        <v>18.02</v>
+        <v>18.77</v>
       </c>
       <c r="N15">
-        <v>12.1</v>
+        <v>12.06</v>
       </c>
       <c r="O15">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="Q15">
-        <v>25934.13</v>
+        <v>25898.05</v>
       </c>
       <c r="R15">
-        <v>26472.3</v>
+        <v>26432.42</v>
       </c>
       <c r="S15">
-        <v>26541.51</v>
+        <v>26525.87</v>
       </c>
       <c r="T15">
-        <v>24309.9</v>
+        <v>24324.43</v>
       </c>
       <c r="U15">
-        <v>6.2</v>
+        <v>5.99</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2524,40 +2522,40 @@
         <v>2</v>
       </c>
       <c r="Z15">
-        <v>39.74</v>
+        <v>39.19</v>
       </c>
       <c r="AA15">
-        <v>-195.26</v>
+        <v>-210.16</v>
       </c>
       <c r="AB15">
-        <v>-103.68</v>
+        <v>-124.98</v>
       </c>
       <c r="AC15">
-        <v>-91.56999999999999</v>
+        <v>-85.18000000000001</v>
       </c>
       <c r="AD15">
-        <v>10.28</v>
+        <v>5.76</v>
       </c>
       <c r="AE15">
-        <v>14.21</v>
+        <v>10.11</v>
       </c>
       <c r="AF15">
-        <v>372.24</v>
+        <v>366.72</v>
       </c>
       <c r="AH15">
-        <v>27393.87</v>
+        <v>27402.27</v>
       </c>
       <c r="AI15">
-        <v>25550.72</v>
+        <v>25462.56</v>
       </c>
       <c r="AJ15">
-        <v>26891.71</v>
+        <v>26884.17</v>
       </c>
       <c r="AK15" t="s">
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>40.07</v>
+        <v>41.9</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2571,10 +2569,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>828.7</v>
+        <v>825.95</v>
       </c>
       <c r="E16">
-        <v>0.72</v>
+        <v>-0.33</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2583,43 +2581,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-14.45</v>
+        <v>-14.73</v>
       </c>
       <c r="I16">
-        <v>27.27</v>
+        <v>26.84</v>
       </c>
       <c r="J16">
-        <v>4.03</v>
+        <v>2.74</v>
       </c>
       <c r="K16">
-        <v>1.77</v>
+        <v>0.44</v>
       </c>
       <c r="L16">
-        <v>-8.550000000000001</v>
+        <v>-10.1</v>
       </c>
       <c r="M16">
-        <v>-7.07</v>
+        <v>-5.65</v>
       </c>
       <c r="N16">
-        <v>8.890000000000001</v>
+        <v>8.81</v>
       </c>
       <c r="O16">
         <v>19</v>
       </c>
       <c r="Q16">
-        <v>819.09</v>
+        <v>823.49</v>
       </c>
       <c r="R16">
-        <v>837.72</v>
+        <v>837.3099999999999</v>
       </c>
       <c r="S16">
-        <v>870.05</v>
+        <v>868.6</v>
       </c>
       <c r="T16">
-        <v>824.54</v>
+        <v>824.25</v>
       </c>
       <c r="U16">
-        <v>0.5</v>
+        <v>0.21</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2634,31 +2632,31 @@
         <v>2</v>
       </c>
       <c r="Z16">
-        <v>44.82</v>
+        <v>43.97</v>
       </c>
       <c r="AA16">
-        <v>-14.65</v>
+        <v>-13.72</v>
       </c>
       <c r="AB16">
-        <v>-15.17</v>
+        <v>-14.88</v>
       </c>
       <c r="AC16">
-        <v>0.52</v>
+        <v>1.16</v>
       </c>
       <c r="AD16">
-        <v>72.98</v>
+        <v>78.97</v>
       </c>
       <c r="AE16">
-        <v>57.63</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="AF16">
-        <v>17.41</v>
+        <v>16.92</v>
       </c>
       <c r="AH16">
-        <v>878.84</v>
+        <v>878.74</v>
       </c>
       <c r="AI16">
-        <v>796.6</v>
+        <v>795.87</v>
       </c>
       <c r="AJ16">
         <v>855.3200000000001</v>
@@ -2667,7 +2665,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>30.53</v>
+        <v>28.08</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2681,10 +2679,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29995.85</v>
+        <v>30481.85</v>
       </c>
       <c r="E17">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2693,43 +2691,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-12.04</v>
+        <v>-10.61</v>
       </c>
       <c r="I17">
-        <v>5.75</v>
+        <v>7.47</v>
       </c>
       <c r="J17">
-        <v>4.79</v>
+        <v>4.78</v>
       </c>
       <c r="K17">
-        <v>0.9</v>
+        <v>2.28</v>
       </c>
       <c r="L17">
-        <v>-3.54</v>
+        <v>-3.05</v>
       </c>
       <c r="M17">
-        <v>-8.23</v>
+        <v>-6.79</v>
       </c>
       <c r="N17">
-        <v>3.24</v>
+        <v>3.57</v>
       </c>
       <c r="O17">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="Q17">
-        <v>29365.58</v>
+        <v>29643.81</v>
       </c>
       <c r="R17">
-        <v>29415.11</v>
+        <v>29447.55</v>
       </c>
       <c r="S17">
-        <v>30206.15</v>
+        <v>30184.59</v>
       </c>
       <c r="T17">
-        <v>31059.32</v>
+        <v>31042</v>
       </c>
       <c r="U17">
-        <v>-3.42</v>
+        <v>-1.8</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2744,40 +2742,40 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>56.39</v>
+        <v>62.44</v>
       </c>
       <c r="AA17">
-        <v>-230.21</v>
+        <v>-123.72</v>
       </c>
       <c r="AB17">
-        <v>-344.59</v>
+        <v>-300.41</v>
       </c>
       <c r="AC17">
-        <v>114.37</v>
+        <v>176.69</v>
       </c>
       <c r="AD17">
         <v>100</v>
       </c>
       <c r="AE17">
-        <v>91.38</v>
+        <v>96.34</v>
       </c>
       <c r="AF17">
-        <v>373.01</v>
+        <v>381.08</v>
       </c>
       <c r="AH17">
-        <v>30329.4</v>
+        <v>30464.53</v>
       </c>
       <c r="AI17">
-        <v>28500.83</v>
+        <v>28430.57</v>
       </c>
       <c r="AJ17">
-        <v>28688.71</v>
+        <v>29148.67</v>
       </c>
       <c r="AK17" t="s">
         <v>82</v>
       </c>
       <c r="AL17">
-        <v>39.94</v>
+        <v>40.52</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2791,10 +2789,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>15724.4</v>
+        <v>15683.55</v>
       </c>
       <c r="E18">
-        <v>0.39</v>
+        <v>-0.26</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2803,31 +2801,31 @@
         <v>15403.15</v>
       </c>
       <c r="H18">
-        <v>-7.18</v>
+        <v>-7.43</v>
       </c>
       <c r="I18">
-        <v>2.09</v>
+        <v>1.82</v>
       </c>
       <c r="J18">
-        <v>0.25</v>
+        <v>-1.08</v>
       </c>
       <c r="K18">
-        <v>-3.53</v>
+        <v>-3.63</v>
       </c>
       <c r="L18">
-        <v>-4.66</v>
+        <v>-3.68</v>
       </c>
       <c r="N18">
-        <v>3.28</v>
+        <v>2.48</v>
       </c>
       <c r="Q18">
-        <v>15790.26</v>
+        <v>15755.86</v>
       </c>
       <c r="R18">
-        <v>16251.4</v>
+        <v>16209.12</v>
       </c>
       <c r="S18">
-        <v>16441.9</v>
+        <v>16421.37</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2839,40 +2837,40 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>35.24</v>
+        <v>34.36</v>
       </c>
       <c r="AA18">
-        <v>-218.95</v>
+        <v>-225.08</v>
       </c>
       <c r="AB18">
-        <v>-159.63</v>
+        <v>-172.72</v>
       </c>
       <c r="AC18">
-        <v>-59.33</v>
+        <v>-52.36</v>
       </c>
       <c r="AD18">
-        <v>17.17</v>
+        <v>17.04</v>
       </c>
       <c r="AE18">
-        <v>18.13</v>
+        <v>16.98</v>
       </c>
       <c r="AF18">
-        <v>222.43</v>
+        <v>218.8</v>
       </c>
       <c r="AH18">
-        <v>17089.62</v>
+        <v>17073.26</v>
       </c>
       <c r="AI18">
-        <v>15413.18</v>
+        <v>15344.98</v>
       </c>
       <c r="AJ18">
-        <v>16367.05</v>
+        <v>16336.92</v>
       </c>
       <c r="AK18" t="s">
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>56.04</v>
+        <v>57.98</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2886,10 +2884,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>9196.25</v>
+        <v>9210.6</v>
       </c>
       <c r="E19">
-        <v>-1.05</v>
+        <v>0.16</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2898,31 +2896,31 @@
         <v>8961.25</v>
       </c>
       <c r="H19">
-        <v>-8.029999999999999</v>
+        <v>-7.88</v>
       </c>
       <c r="I19">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="J19">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="K19">
-        <v>0.57</v>
+        <v>0.89</v>
       </c>
       <c r="L19">
-        <v>-0.97</v>
+        <v>-1.44</v>
       </c>
       <c r="N19">
-        <v>6.67</v>
+        <v>7.1</v>
       </c>
       <c r="Q19">
-        <v>9173.92</v>
+        <v>9214.709999999999</v>
       </c>
       <c r="R19">
-        <v>9255.040000000001</v>
+        <v>9251.98</v>
       </c>
       <c r="S19">
-        <v>9524.93</v>
+        <v>9521.209999999999</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2934,31 +2932,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>45.6</v>
+        <v>46.16</v>
       </c>
       <c r="AA19">
-        <v>-96.08</v>
+        <v>-89.31</v>
       </c>
       <c r="AB19">
-        <v>-108.4</v>
+        <v>-104.58</v>
       </c>
       <c r="AC19">
-        <v>12.31</v>
+        <v>15.27</v>
       </c>
       <c r="AD19">
-        <v>91.73</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AE19">
-        <v>79.23</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="AF19">
-        <v>169.45</v>
+        <v>163.55</v>
       </c>
       <c r="AH19">
-        <v>9534.68</v>
+        <v>9532.18</v>
       </c>
       <c r="AI19">
-        <v>8975.4</v>
+        <v>8971.77</v>
       </c>
       <c r="AJ19">
         <v>9494.469999999999</v>
@@ -2967,7 +2965,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>26.44</v>
+        <v>24.77</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2981,10 +2979,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10604.6</v>
+        <v>10556.75</v>
       </c>
       <c r="E20">
-        <v>1.41</v>
+        <v>-0.45</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -2993,31 +2991,31 @@
         <v>10299.4</v>
       </c>
       <c r="H20">
-        <v>-6.72</v>
+        <v>-7.14</v>
       </c>
       <c r="I20">
-        <v>2.96</v>
+        <v>2.5</v>
       </c>
       <c r="J20">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="K20">
-        <v>-1.78</v>
+        <v>-2.9</v>
       </c>
       <c r="L20">
-        <v>-5.22</v>
+        <v>-6.57</v>
       </c>
       <c r="N20">
-        <v>-10.44</v>
+        <v>-11.53</v>
       </c>
       <c r="Q20">
-        <v>10411.13</v>
+        <v>10453.42</v>
       </c>
       <c r="R20">
-        <v>10652.34</v>
+        <v>10637.31</v>
       </c>
       <c r="S20">
-        <v>10948.87</v>
+        <v>10935.68</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3029,31 +3027,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>46.01</v>
+        <v>44.08</v>
       </c>
       <c r="AA20">
-        <v>-154.54</v>
+        <v>-140.8</v>
       </c>
       <c r="AB20">
-        <v>-155.3</v>
+        <v>-152.4</v>
       </c>
       <c r="AC20">
-        <v>0.76</v>
+        <v>11.6</v>
       </c>
       <c r="AD20">
-        <v>70.73999999999999</v>
+        <v>91.97</v>
       </c>
       <c r="AE20">
-        <v>43.1</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="AF20">
-        <v>152.73</v>
+        <v>151.8</v>
       </c>
       <c r="AH20">
-        <v>11126.13</v>
+        <v>11102.71</v>
       </c>
       <c r="AI20">
-        <v>10178.55</v>
+        <v>10171.9</v>
       </c>
       <c r="AJ20">
         <v>10732.68</v>
@@ -3062,7 +3060,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>43.18</v>
+        <v>37.95</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3076,10 +3074,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27679.3</v>
+        <v>27700.55</v>
       </c>
       <c r="E21">
-        <v>1.89</v>
+        <v>0.08</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3088,43 +3086,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-5.17</v>
+        <v>-5.1</v>
       </c>
       <c r="I21">
-        <v>14.64</v>
+        <v>14.73</v>
       </c>
       <c r="J21">
-        <v>3.02</v>
+        <v>1.76</v>
       </c>
       <c r="K21">
-        <v>2.25</v>
+        <v>1.53</v>
       </c>
       <c r="L21">
-        <v>-0.85</v>
+        <v>-2.83</v>
       </c>
       <c r="M21">
-        <v>0.66</v>
+        <v>1.06</v>
       </c>
       <c r="N21">
-        <v>6.07</v>
+        <v>6.08</v>
       </c>
       <c r="O21">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="Q21">
-        <v>27303.18</v>
+        <v>27398.78</v>
       </c>
       <c r="R21">
-        <v>27037.55</v>
+        <v>27064.12</v>
       </c>
       <c r="S21">
-        <v>27314.38</v>
+        <v>27313.51</v>
       </c>
       <c r="T21">
-        <v>27437.99</v>
+        <v>27433.99</v>
       </c>
       <c r="U21">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3139,40 +3137,40 @@
         <v>1</v>
       </c>
       <c r="Z21">
-        <v>59.55</v>
+        <v>59.88</v>
       </c>
       <c r="AA21">
-        <v>-13.09</v>
+        <v>30.82</v>
       </c>
       <c r="AB21">
-        <v>-110.91</v>
+        <v>-82.56</v>
       </c>
       <c r="AC21">
-        <v>97.81999999999999</v>
+        <v>113.39</v>
       </c>
       <c r="AD21">
         <v>94.7</v>
       </c>
       <c r="AE21">
-        <v>94.09</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="AF21">
-        <v>375.17</v>
+        <v>366.1</v>
       </c>
       <c r="AH21">
-        <v>27694.68</v>
+        <v>27783.66</v>
       </c>
       <c r="AI21">
-        <v>26380.42</v>
+        <v>26344.58</v>
       </c>
       <c r="AJ21">
-        <v>26361.32</v>
+        <v>26545.98</v>
       </c>
       <c r="AK21" t="s">
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>26.94</v>
+        <v>30.27</v>
       </c>
     </row>
   </sheetData>
@@ -3313,7 +3311,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3353,7 +3351,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3371,2093 +3369,2084 @@
         <v>93</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="4" t="s">
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>98</v>
       </c>
     </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-4.41</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-4.18</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.23</v>
+      </c>
+    </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-3.59</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-3.63</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-0.04</v>
+      </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>103</v>
+      <c r="A9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-2.46</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-2.7</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-0.24</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="6">
-        <v>-7.87</v>
+        <v>-2.51</v>
       </c>
       <c r="D10" s="6">
-        <v>-4.41</v>
-      </c>
-      <c r="E10" s="7">
-        <v>3.46</v>
+        <v>-2.67</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-5.93</v>
+        <v>-0.09</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.59</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2.34</v>
+        <v>-2.07</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-4.8</v>
+        <v>1.15</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.46</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2.34</v>
+        <v>0.49</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-0.66</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-3.77</v>
+        <v>3.94</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.51</v>
+        <v>9.75</v>
       </c>
       <c r="E13" s="7">
-        <v>1.26</v>
+        <v>5.81</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>0.48</v>
+        <v>-2.97</v>
       </c>
       <c r="D14" s="6">
-        <v>-0.09</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.57</v>
+        <v>-2.83</v>
+      </c>
+      <c r="E14" s="7">
+        <v>0.14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.34</v>
+        <v>-2.52</v>
       </c>
       <c r="D15" s="6">
-        <v>1.15</v>
+        <v>-2.06</v>
       </c>
       <c r="E15" s="7">
-        <v>3.49</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>4.32</v>
+        <v>7.53</v>
       </c>
       <c r="D16" s="6">
-        <v>3.94</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.38</v>
+        <v>8.789999999999999</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.26</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-5.54</v>
+        <v>-5.14</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.97</v>
+        <v>-4.76</v>
       </c>
       <c r="E17" s="7">
-        <v>2.57</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.47</v>
+        <v>-2.22</v>
       </c>
       <c r="D18" s="6">
-        <v>-2.52</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.95</v>
+        <v>-2.61</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>6.78</v>
+        <v>-1.44</v>
       </c>
       <c r="D19" s="6">
-        <v>7.53</v>
-      </c>
-      <c r="E19" s="7">
-        <v>0.75</v>
+        <v>-2.19</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-7.63</v>
+        <v>-1.42</v>
       </c>
       <c r="D20" s="6">
-        <v>-5.14</v>
+        <v>-1.39</v>
       </c>
       <c r="E20" s="7">
-        <v>2.49</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-4.21</v>
+        <v>1.77</v>
       </c>
       <c r="D21" s="6">
-        <v>-2.22</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1.99</v>
+        <v>0.44</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.18</v>
+        <v>0.9</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.44</v>
+        <v>2.28</v>
       </c>
       <c r="E22" s="7">
-        <v>0.74</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-3</v>
+        <v>-3.53</v>
       </c>
       <c r="D23" s="6">
-        <v>-1.42</v>
-      </c>
-      <c r="E23" s="7">
-        <v>1.58</v>
+        <v>-3.63</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.03</v>
+        <v>0.57</v>
       </c>
       <c r="D24" s="6">
-        <v>1.77</v>
+        <v>0.89</v>
       </c>
       <c r="E24" s="7">
-        <v>4.8</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-1.71</v>
+        <v>-1.78</v>
       </c>
       <c r="D25" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="E25" s="7">
-        <v>2.61</v>
+        <v>-2.9</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.12</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-5.03</v>
+        <v>2.25</v>
       </c>
       <c r="D26" s="6">
-        <v>-3.53</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.5</v>
+        <v>1.53</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" s="6">
-        <v>-4.42</v>
+        <v>4.34</v>
       </c>
       <c r="D27" s="6">
-        <v>0.57</v>
-      </c>
-      <c r="E27" s="7">
-        <v>4.99</v>
+        <v>3.65</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>-4.39</v>
+        <v>2.46</v>
       </c>
       <c r="D28" s="6">
-        <v>-1.78</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.61</v>
+        <v>1.97</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-0.98</v>
+        <v>2.46</v>
       </c>
       <c r="D29" s="6">
-        <v>2.25</v>
-      </c>
-      <c r="E29" s="7">
-        <v>3.23</v>
+        <v>1.39</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-1.07</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>0.07000000000000001</v>
+        <v>1.58</v>
       </c>
       <c r="D30" s="6">
-        <v>4.34</v>
-      </c>
-      <c r="E30" s="7">
-        <v>4.27</v>
+        <v>1.13</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-1.05</v>
+        <v>2.04</v>
       </c>
       <c r="D31" s="6">
-        <v>2.46</v>
-      </c>
-      <c r="E31" s="7">
-        <v>3.51</v>
+        <v>-0.55</v>
+      </c>
+      <c r="E31" s="8">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-0.61</v>
+        <v>2.94</v>
       </c>
       <c r="D32" s="6">
-        <v>2.46</v>
-      </c>
-      <c r="E32" s="7">
-        <v>3.07</v>
+        <v>1.68</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-0.49</v>
+        <v>10.76</v>
       </c>
       <c r="D33" s="6">
-        <v>1.58</v>
+        <v>11.72</v>
       </c>
       <c r="E33" s="7">
-        <v>2.07</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>1.05</v>
+        <v>1.86</v>
       </c>
       <c r="D34" s="6">
-        <v>2.04</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.99</v>
+        <v>1.48</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>0.13</v>
+        <v>2.14</v>
       </c>
       <c r="D35" s="6">
-        <v>2.94</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2.81</v>
+        <v>1.76</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>8.69</v>
+        <v>5.39</v>
       </c>
       <c r="D36" s="6">
-        <v>10.76</v>
+        <v>6.11</v>
       </c>
       <c r="E36" s="7">
-        <v>2.07</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.05</v>
+        <v>1.25</v>
       </c>
       <c r="D37" s="6">
-        <v>1.86</v>
-      </c>
-      <c r="E37" s="7">
-        <v>2.91</v>
+        <v>1.1</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.15</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-1.7</v>
+        <v>2.74</v>
       </c>
       <c r="D38" s="6">
-        <v>2.14</v>
-      </c>
-      <c r="E38" s="7">
-        <v>3.84</v>
+        <v>1.87</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>3.98</v>
+        <v>0.57</v>
       </c>
       <c r="D39" s="6">
-        <v>5.39</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.41</v>
+        <v>-0.39</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-2.44</v>
+        <v>-0.02</v>
       </c>
       <c r="D40" s="6">
-        <v>1.25</v>
-      </c>
-      <c r="E40" s="7">
-        <v>3.69</v>
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>0.52</v>
+        <v>4.03</v>
       </c>
       <c r="D41" s="6">
         <v>2.74</v>
       </c>
-      <c r="E41" s="7">
-        <v>2.22</v>
+      <c r="E41" s="8">
+        <v>-1.29</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>0.97</v>
+        <v>4.79</v>
       </c>
       <c r="D42" s="6">
-        <v>0.57</v>
+        <v>4.78</v>
       </c>
       <c r="E42" s="8">
-        <v>-0.4</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-2.65</v>
+        <v>0.25</v>
       </c>
       <c r="D43" s="6">
-        <v>-0.02</v>
-      </c>
-      <c r="E43" s="7">
-        <v>2.63</v>
+        <v>-1.08</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>0.02</v>
+        <v>2.62</v>
       </c>
       <c r="D44" s="6">
-        <v>4.03</v>
-      </c>
-      <c r="E44" s="7">
-        <v>4.01</v>
+        <v>2.26</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>1.36</v>
+        <v>2.41</v>
       </c>
       <c r="D45" s="6">
-        <v>4.79</v>
-      </c>
-      <c r="E45" s="7">
-        <v>3.43</v>
+        <v>2.04</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-2.47</v>
+        <v>3.02</v>
       </c>
       <c r="D46" s="6">
-        <v>0.25</v>
-      </c>
-      <c r="E46" s="7">
-        <v>2.72</v>
+        <v>1.76</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-1.26</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C47" s="6">
-        <v>0.85</v>
+        <v>-5.04</v>
       </c>
       <c r="D47" s="6">
-        <v>2.62</v>
+        <v>-2.84</v>
       </c>
       <c r="E47" s="7">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48" s="6">
-        <v>-1.56</v>
+        <v>-0.31</v>
       </c>
       <c r="D48" s="6">
-        <v>2.41</v>
+        <v>0.8</v>
       </c>
       <c r="E48" s="7">
-        <v>3.97</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" s="6">
-        <v>0.19</v>
+        <v>-9.98</v>
       </c>
       <c r="D49" s="6">
-        <v>3.02</v>
+        <v>-9.27</v>
       </c>
       <c r="E49" s="7">
-        <v>2.83</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>-6.33</v>
+        <v>2.1</v>
       </c>
       <c r="D50" s="6">
-        <v>-5.04</v>
+        <v>3.15</v>
       </c>
       <c r="E50" s="7">
-        <v>1.29</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>-0.92</v>
+        <v>-18.21</v>
       </c>
       <c r="D51" s="6">
-        <v>-0.31</v>
+        <v>-18.12</v>
       </c>
       <c r="E51" s="7">
-        <v>0.61</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-10.65</v>
+        <v>-5.28</v>
       </c>
       <c r="D52" s="6">
-        <v>-9.98</v>
+        <v>-4.76</v>
       </c>
       <c r="E52" s="7">
-        <v>0.67</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>3.21</v>
+        <v>-11.49</v>
       </c>
       <c r="D53" s="6">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="E53" s="7">
         <v>2.1</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-1.11</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-17.77</v>
+        <v>-5.07</v>
       </c>
       <c r="D54" s="6">
-        <v>-18.21</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.44</v>
+        <v>-4.03</v>
+      </c>
+      <c r="E54" s="7">
+        <v>1.04</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-6.6</v>
+        <v>2.15</v>
       </c>
       <c r="D55" s="6">
-        <v>-5.28</v>
+        <v>5.93</v>
       </c>
       <c r="E55" s="7">
-        <v>1.32</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-13.11</v>
+        <v>18.33</v>
       </c>
       <c r="D56" s="6">
-        <v>-11.49</v>
+        <v>19.7</v>
       </c>
       <c r="E56" s="7">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>-5.87</v>
+        <v>-6.77</v>
       </c>
       <c r="D57" s="6">
-        <v>-5.07</v>
+        <v>-5.82</v>
       </c>
       <c r="E57" s="7">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>3.2</v>
+        <v>6.03</v>
       </c>
       <c r="D58" s="6">
-        <v>2.15</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-1.05</v>
+        <v>7.6</v>
+      </c>
+      <c r="E58" s="7">
+        <v>1.57</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>17.88</v>
+        <v>18.02</v>
       </c>
       <c r="D59" s="6">
-        <v>18.33</v>
+        <v>18.77</v>
       </c>
       <c r="E59" s="7">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>-6.44</v>
+        <v>-7.07</v>
       </c>
       <c r="D60" s="6">
-        <v>-6.77</v>
-      </c>
-      <c r="E60" s="8">
-        <v>-0.33</v>
+        <v>-5.65</v>
+      </c>
+      <c r="E60" s="7">
+        <v>1.42</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>7.25</v>
+        <v>-8.23</v>
       </c>
       <c r="D61" s="6">
-        <v>6.03</v>
-      </c>
-      <c r="E61" s="8">
-        <v>-1.22</v>
+        <v>-6.79</v>
+      </c>
+      <c r="E61" s="7">
+        <v>1.44</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>18.17</v>
+        <v>0.66</v>
       </c>
       <c r="D62" s="6">
-        <v>18.02</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.15</v>
+        <v>1.06</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.4</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>-6.72</v>
+        <v>-4.45</v>
       </c>
       <c r="D63" s="6">
-        <v>-7.07</v>
+        <v>-4.91</v>
       </c>
       <c r="E63" s="8">
-        <v>-0.35</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-9.69</v>
+        <v>-7.62</v>
       </c>
       <c r="D64" s="6">
-        <v>-8.23</v>
+        <v>-7.45</v>
       </c>
       <c r="E64" s="7">
-        <v>1.46</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-1.18</v>
+        <v>-5.62</v>
       </c>
       <c r="D65" s="6">
-        <v>0.66</v>
+        <v>-5.56</v>
       </c>
       <c r="E65" s="7">
-        <v>1.84</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-5.59</v>
+        <v>-7.96</v>
       </c>
       <c r="D66" s="6">
-        <v>-4.45</v>
+        <v>-7.86</v>
       </c>
       <c r="E66" s="7">
-        <v>1.14</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-8.289999999999999</v>
+        <v>-7.47</v>
       </c>
       <c r="D67" s="6">
-        <v>-7.62</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0.67</v>
+        <v>-8.48</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-6.23</v>
+        <v>-4.49</v>
       </c>
       <c r="D68" s="6">
-        <v>-5.62</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.61</v>
+        <v>-5.64</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-1.15</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-7.31</v>
+        <v>6.95</v>
       </c>
       <c r="D69" s="6">
-        <v>-7.96</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-0.65</v>
+        <v>9.23</v>
+      </c>
+      <c r="E69" s="7">
+        <v>2.28</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-6.24</v>
+        <v>-5.22</v>
       </c>
       <c r="D70" s="6">
-        <v>-7.47</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-1.23</v>
+        <v>-4.72</v>
+      </c>
+      <c r="E70" s="7">
+        <v>0.5</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-6.54</v>
+        <v>-6.92</v>
       </c>
       <c r="D71" s="6">
-        <v>-4.49</v>
-      </c>
-      <c r="E71" s="7">
-        <v>2.05</v>
+        <v>-6.95</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>5.74</v>
+        <v>6.3</v>
       </c>
       <c r="D72" s="6">
-        <v>6.95</v>
+        <v>8.33</v>
       </c>
       <c r="E72" s="7">
-        <v>1.21</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>-5.21</v>
+        <v>-3.82</v>
       </c>
       <c r="D73" s="6">
-        <v>-5.22</v>
-      </c>
-      <c r="E73" s="8">
-        <v>-0.01</v>
+        <v>-2.44</v>
+      </c>
+      <c r="E73" s="7">
+        <v>1.38</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-8.109999999999999</v>
+        <v>-6.6</v>
       </c>
       <c r="D74" s="6">
-        <v>-6.92</v>
-      </c>
-      <c r="E74" s="7">
-        <v>1.19</v>
+        <v>-6.96</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>9.15</v>
+        <v>-3.67</v>
       </c>
       <c r="D75" s="6">
-        <v>6.3</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-2.85</v>
+        <v>-3.42</v>
+      </c>
+      <c r="E75" s="7">
+        <v>0.25</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-4.23</v>
+        <v>-0.73</v>
       </c>
       <c r="D76" s="6">
-        <v>-3.82</v>
+        <v>0.53</v>
       </c>
       <c r="E76" s="7">
-        <v>0.41</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>-6.39</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="D77" s="6">
-        <v>-6.6</v>
+        <v>-10.1</v>
       </c>
       <c r="E77" s="8">
-        <v>-0.21</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>-2.61</v>
+        <v>-3.54</v>
       </c>
       <c r="D78" s="6">
-        <v>-3.67</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-1.06</v>
+        <v>-3.05</v>
+      </c>
+      <c r="E78" s="7">
+        <v>0.49</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-1.03</v>
+        <v>-4.66</v>
       </c>
       <c r="D79" s="6">
-        <v>-0.73</v>
+        <v>-3.68</v>
       </c>
       <c r="E79" s="7">
-        <v>0.3</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-10.09</v>
+        <v>-0.97</v>
       </c>
       <c r="D80" s="6">
-        <v>-8.550000000000001</v>
-      </c>
-      <c r="E80" s="7">
-        <v>1.54</v>
+        <v>-1.44</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-5.44</v>
+        <v>-5.22</v>
       </c>
       <c r="D81" s="6">
-        <v>-3.54</v>
-      </c>
-      <c r="E81" s="7">
-        <v>1.9</v>
+        <v>-6.57</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-1.35</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-5.12</v>
+        <v>-0.85</v>
       </c>
       <c r="D82" s="6">
-        <v>-4.66</v>
-      </c>
-      <c r="E82" s="7">
-        <v>0.46</v>
+        <v>-2.83</v>
+      </c>
+      <c r="E82" s="8">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C83" s="6">
-        <v>-0.4</v>
+        <v>-13.73</v>
       </c>
       <c r="D83" s="6">
-        <v>-0.97</v>
-      </c>
-      <c r="E83" s="8">
-        <v>-0.57</v>
+        <v>-13.08</v>
+      </c>
+      <c r="E83" s="7">
+        <v>0.65</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C84" s="6">
-        <v>-6.46</v>
+        <v>-13.65</v>
       </c>
       <c r="D84" s="6">
-        <v>-5.22</v>
+        <v>-13.36</v>
       </c>
       <c r="E84" s="7">
-        <v>1.24</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C85" s="6">
-        <v>-2.98</v>
+        <v>-12.93</v>
       </c>
       <c r="D85" s="6">
-        <v>-0.85</v>
+        <v>-12.54</v>
       </c>
       <c r="E85" s="7">
-        <v>2.13</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C86" s="6">
-        <v>-15.15</v>
+        <v>-12.81</v>
       </c>
       <c r="D86" s="6">
-        <v>-13.73</v>
-      </c>
-      <c r="E86" s="7">
-        <v>1.42</v>
+        <v>-12.87</v>
+      </c>
+      <c r="E86" s="8">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-14.2</v>
+        <v>-21.1</v>
       </c>
       <c r="D87" s="6">
-        <v>-13.65</v>
-      </c>
-      <c r="E87" s="7">
-        <v>0.55</v>
+        <v>-21.41</v>
+      </c>
+      <c r="E87" s="8">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-13.68</v>
+        <v>-10.89</v>
       </c>
       <c r="D88" s="6">
-        <v>-12.93</v>
+        <v>-10.81</v>
       </c>
       <c r="E88" s="7">
-        <v>0.75</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-12.12</v>
+        <v>-22.2</v>
       </c>
       <c r="D89" s="6">
-        <v>-12.81</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-19.15</v>
+      </c>
+      <c r="E89" s="7">
+        <v>3.05</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-20.26</v>
+        <v>-9.25</v>
       </c>
       <c r="D90" s="6">
-        <v>-21.1</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-0.84</v>
+        <v>-8.93</v>
+      </c>
+      <c r="E90" s="7">
+        <v>0.32</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-12.35</v>
+        <v>-11.06</v>
       </c>
       <c r="D91" s="6">
-        <v>-10.89</v>
+        <v>-10.65</v>
       </c>
       <c r="E91" s="7">
-        <v>1.46</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-23.59</v>
+        <v>-1.47</v>
       </c>
       <c r="D92" s="6">
-        <v>-22.2</v>
+        <v>0</v>
       </c>
       <c r="E92" s="7">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-9.48</v>
+        <v>-12.39</v>
       </c>
       <c r="D93" s="6">
-        <v>-9.25</v>
+        <v>-11.55</v>
       </c>
       <c r="E93" s="7">
-        <v>0.23</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-12.14</v>
+        <v>-14.02</v>
       </c>
       <c r="D94" s="6">
-        <v>-11.06</v>
-      </c>
-      <c r="E94" s="7">
-        <v>1.08</v>
+        <v>-14.11</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>0</v>
+        <v>-18.61</v>
       </c>
       <c r="D95" s="6">
-        <v>-1.47</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-1.47</v>
+        <v>-18.07</v>
+      </c>
+      <c r="E95" s="7">
+        <v>0.54</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-12.48</v>
+        <v>-5.03</v>
       </c>
       <c r="D96" s="6">
-        <v>-12.39</v>
-      </c>
-      <c r="E96" s="7">
-        <v>0.09</v>
+        <v>-5.17</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-13.8</v>
+        <v>-14.45</v>
       </c>
       <c r="D97" s="6">
-        <v>-14.02</v>
+        <v>-14.73</v>
       </c>
       <c r="E97" s="8">
-        <v>-0.22</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-17.33</v>
+        <v>-12.04</v>
       </c>
       <c r="D98" s="6">
-        <v>-18.61</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-1.28</v>
+        <v>-10.61</v>
+      </c>
+      <c r="E98" s="7">
+        <v>1.43</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-5.33</v>
+        <v>-7.18</v>
       </c>
       <c r="D99" s="6">
-        <v>-5.03</v>
-      </c>
-      <c r="E99" s="7">
-        <v>0.3</v>
+        <v>-7.43</v>
+      </c>
+      <c r="E99" s="8">
+        <v>-0.25</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-15.06</v>
+        <v>-8.029999999999999</v>
       </c>
       <c r="D100" s="6">
-        <v>-14.45</v>
+        <v>-7.88</v>
       </c>
       <c r="E100" s="7">
-        <v>0.61</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-13.62</v>
+        <v>-6.72</v>
       </c>
       <c r="D101" s="6">
-        <v>-12.04</v>
-      </c>
-      <c r="E101" s="7">
-        <v>1.58</v>
+        <v>-7.14</v>
+      </c>
+      <c r="E101" s="8">
+        <v>-0.42</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-7.55</v>
+        <v>-5.17</v>
       </c>
       <c r="D102" s="6">
-        <v>-7.18</v>
+        <v>-5.1</v>
       </c>
       <c r="E102" s="7">
-        <v>0.37</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C103" s="6">
-        <v>-7.05</v>
+        <v>25576.4</v>
       </c>
       <c r="D103" s="6">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-0.98</v>
+        <v>25768.5</v>
+      </c>
+      <c r="E103" s="7">
+        <v>192.1</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C104" s="6">
-        <v>-8.02</v>
+        <v>9069.450000000001</v>
       </c>
       <c r="D104" s="6">
-        <v>-6.72</v>
+        <v>9099.5</v>
       </c>
       <c r="E104" s="7">
-        <v>1.3</v>
+        <v>30.05</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C105" s="6">
-        <v>-6.92</v>
+        <v>11005.25</v>
       </c>
       <c r="D105" s="6">
-        <v>-5.17</v>
+        <v>11054.65</v>
       </c>
       <c r="E105" s="7">
-        <v>1.75</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>25156.75</v>
+        <v>36213.7</v>
       </c>
       <c r="D106" s="6">
-        <v>25576.4</v>
-      </c>
-      <c r="E106" s="7">
-        <v>419.65</v>
+        <v>36190.85</v>
+      </c>
+      <c r="E106" s="8">
+        <v>-22.85</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>9011.299999999999</v>
+        <v>44791.65</v>
       </c>
       <c r="D107" s="6">
-        <v>9069.450000000001</v>
-      </c>
-      <c r="E107" s="7">
-        <v>58.15</v>
+        <v>44616.15</v>
+      </c>
+      <c r="E107" s="8">
+        <v>-175.5</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>10910</v>
+        <v>25364.2</v>
       </c>
       <c r="D108" s="6">
-        <v>11005.25</v>
+        <v>25387.1</v>
       </c>
       <c r="E108" s="7">
-        <v>95.25</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>36503.5</v>
+        <v>30719.8</v>
       </c>
       <c r="D109" s="6">
-        <v>36213.7</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-289.8</v>
+        <v>31924.1</v>
+      </c>
+      <c r="E109" s="7">
+        <v>1204.3</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>45271.7</v>
+        <v>15121.1</v>
       </c>
       <c r="D110" s="6">
-        <v>44791.65</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-480.05</v>
+        <v>15174.1</v>
+      </c>
+      <c r="E110" s="7">
+        <v>53</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>24948.7</v>
+        <v>8685.9</v>
       </c>
       <c r="D111" s="6">
-        <v>25364.2</v>
+        <v>8725.6</v>
       </c>
       <c r="E111" s="7">
-        <v>415.5</v>
+        <v>39.7</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>30171</v>
+        <v>1617.2</v>
       </c>
       <c r="D112" s="6">
-        <v>30719.8</v>
+        <v>1648.25</v>
       </c>
       <c r="E112" s="7">
-        <v>548.8</v>
+        <v>31.05</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>15083.55</v>
+        <v>12018.5</v>
       </c>
       <c r="D113" s="6">
-        <v>15121.1</v>
+        <v>12133.2</v>
       </c>
       <c r="E113" s="7">
-        <v>37.55</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>8580.299999999999</v>
+        <v>9257.15</v>
       </c>
       <c r="D114" s="6">
-        <v>8685.9</v>
-      </c>
-      <c r="E114" s="7">
-        <v>105.6</v>
+        <v>9247.299999999999</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-9.85</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>1641.35</v>
+        <v>8041.2</v>
       </c>
       <c r="D115" s="6">
-        <v>1617.2</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-24.15</v>
+        <v>8094.95</v>
+      </c>
+      <c r="E115" s="7">
+        <v>53.75</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>12006.75</v>
+        <v>25817.8</v>
       </c>
       <c r="D116" s="6">
-        <v>12018.5</v>
-      </c>
-      <c r="E116" s="7">
-        <v>11.75</v>
+        <v>25781.65</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-36.15</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>9280.799999999999</v>
+        <v>828.7</v>
       </c>
       <c r="D117" s="6">
-        <v>9257.15</v>
+        <v>825.95</v>
       </c>
       <c r="E117" s="8">
-        <v>-23.65</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>8167.55</v>
+        <v>29995.85</v>
       </c>
       <c r="D118" s="6">
-        <v>8041.2</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-126.35</v>
+        <v>30481.85</v>
+      </c>
+      <c r="E118" s="7">
+        <v>486</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>25736.95</v>
+        <v>15724.4</v>
       </c>
       <c r="D119" s="6">
-        <v>25817.8</v>
-      </c>
-      <c r="E119" s="7">
-        <v>80.84999999999999</v>
+        <v>15683.55</v>
+      </c>
+      <c r="E119" s="8">
+        <v>-40.85</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>822.8</v>
+        <v>9196.25</v>
       </c>
       <c r="D120" s="6">
-        <v>828.7</v>
+        <v>9210.6</v>
       </c>
       <c r="E120" s="7">
-        <v>5.9</v>
+        <v>14.35</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>29455.4</v>
+        <v>10604.6</v>
       </c>
       <c r="D121" s="6">
-        <v>29995.85</v>
-      </c>
-      <c r="E121" s="7">
-        <v>540.45</v>
+        <v>10556.75</v>
+      </c>
+      <c r="E121" s="8">
+        <v>-47.85</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>15663</v>
+        <v>27679.3</v>
       </c>
       <c r="D122" s="6">
-        <v>15724.4</v>
+        <v>27700.55</v>
       </c>
       <c r="E122" s="7">
-        <v>61.4</v>
+        <v>21.25</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C123" s="6">
-        <v>9294.1</v>
+        <v>38</v>
       </c>
       <c r="D123" s="6">
-        <v>9196.25</v>
-      </c>
-      <c r="E123" s="8">
-        <v>-97.84999999999999</v>
+        <v>44</v>
+      </c>
+      <c r="E123" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124" s="6">
+        <v>50</v>
+      </c>
+      <c r="D124" s="6">
         <v>56</v>
       </c>
-      <c r="B124" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C124" s="6">
-        <v>10456.75</v>
-      </c>
-      <c r="D124" s="6">
-        <v>10604.6</v>
-      </c>
       <c r="E124" s="7">
-        <v>147.85</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C125" s="6">
-        <v>27166.8</v>
+        <v>56</v>
       </c>
       <c r="D125" s="6">
-        <v>27679.3</v>
-      </c>
-      <c r="E125" s="7">
-        <v>512.5</v>
+        <v>38</v>
+      </c>
+      <c r="E125" s="8">
+        <v>-18</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C126" s="6">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D126" s="6">
-        <v>50</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-6</v>
+        <v>81</v>
+      </c>
+      <c r="E126" s="7">
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="D127" s="6">
-        <v>56</v>
+        <v>99</v>
       </c>
       <c r="E127" s="7">
         <v>6</v>
@@ -5465,24 +5454,24 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="D128" s="6">
-        <v>32</v>
-      </c>
-      <c r="E128" s="7">
-        <v>6</v>
+        <v>74</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-7</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
@@ -5499,7 +5488,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
@@ -5508,390 +5497,373 @@
         <v>44</v>
       </c>
       <c r="D130" s="6">
-        <v>26</v>
-      </c>
-      <c r="E130" s="8">
-        <v>-18</v>
+        <v>50</v>
+      </c>
+      <c r="E130" s="7">
+        <v>6</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="6">
-        <v>93</v>
+        <v>74</v>
       </c>
       <c r="D131" s="6">
-        <v>99</v>
-      </c>
-      <c r="E131" s="7">
-        <v>6</v>
+        <v>68</v>
+      </c>
+      <c r="E131" s="8">
+        <v>-6</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C132" s="6">
-        <v>32</v>
+        <v>40.91</v>
       </c>
       <c r="D132" s="6">
-        <v>44</v>
+        <v>43.86</v>
       </c>
       <c r="E132" s="7">
-        <v>12</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C133" s="6">
-        <v>33.85</v>
+        <v>38.88</v>
       </c>
       <c r="D133" s="6">
-        <v>40.91</v>
+        <v>40.64</v>
       </c>
       <c r="E133" s="7">
-        <v>7.06</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C134" s="6">
-        <v>35.43</v>
+        <v>42.15</v>
       </c>
       <c r="D134" s="6">
-        <v>38.88</v>
+        <v>44.3</v>
       </c>
       <c r="E134" s="7">
-        <v>3.45</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>37.84</v>
+        <v>39.86</v>
       </c>
       <c r="D135" s="6">
-        <v>42.15</v>
-      </c>
-      <c r="E135" s="7">
-        <v>4.31</v>
+        <v>39.6</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>43.23</v>
+        <v>46.18</v>
       </c>
       <c r="D136" s="6">
-        <v>39.86</v>
+        <v>45</v>
       </c>
       <c r="E136" s="8">
-        <v>-3.37</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>49.5</v>
+        <v>52.94</v>
       </c>
       <c r="D137" s="6">
-        <v>46.18</v>
-      </c>
-      <c r="E137" s="8">
-        <v>-3.32</v>
+        <v>53.34</v>
+      </c>
+      <c r="E137" s="7">
+        <v>0.4</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>45.11</v>
+        <v>66.95</v>
       </c>
       <c r="D138" s="6">
-        <v>52.94</v>
+        <v>73.44</v>
       </c>
       <c r="E138" s="7">
-        <v>7.83</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>63.13</v>
+        <v>37.03</v>
       </c>
       <c r="D139" s="6">
-        <v>66.95</v>
+        <v>39.1</v>
       </c>
       <c r="E139" s="7">
-        <v>3.82</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>35.6</v>
+        <v>42.61</v>
       </c>
       <c r="D140" s="6">
-        <v>37.03</v>
+        <v>44.92</v>
       </c>
       <c r="E140" s="7">
-        <v>1.43</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>35.99</v>
+        <v>58.31</v>
       </c>
       <c r="D141" s="6">
-        <v>42.61</v>
+        <v>62.74</v>
       </c>
       <c r="E141" s="7">
-        <v>6.62</v>
+        <v>4.43</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>63.79</v>
+        <v>35.52</v>
       </c>
       <c r="D142" s="6">
-        <v>58.31</v>
-      </c>
-      <c r="E142" s="8">
-        <v>-5.48</v>
+        <v>39.22</v>
+      </c>
+      <c r="E142" s="7">
+        <v>3.7</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>35.15</v>
+        <v>42.17</v>
       </c>
       <c r="D143" s="6">
-        <v>35.52</v>
-      </c>
-      <c r="E143" s="7">
-        <v>0.37</v>
+        <v>41.7</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-0.47</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>43.24</v>
+        <v>42.69</v>
       </c>
       <c r="D144" s="6">
-        <v>42.17</v>
-      </c>
-      <c r="E144" s="8">
-        <v>-1.07</v>
+        <v>45.6</v>
+      </c>
+      <c r="E144" s="7">
+        <v>2.91</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>48.34</v>
+        <v>39.74</v>
       </c>
       <c r="D145" s="6">
-        <v>42.69</v>
+        <v>39.19</v>
       </c>
       <c r="E145" s="8">
-        <v>-5.65</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>37.94</v>
+        <v>44.82</v>
       </c>
       <c r="D146" s="6">
-        <v>39.74</v>
-      </c>
-      <c r="E146" s="7">
-        <v>1.8</v>
+        <v>43.97</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>42.62</v>
+        <v>56.39</v>
       </c>
       <c r="D147" s="6">
-        <v>44.82</v>
+        <v>62.44</v>
       </c>
       <c r="E147" s="7">
-        <v>2.2</v>
+        <v>6.05</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>47.69</v>
+        <v>35.24</v>
       </c>
       <c r="D148" s="6">
-        <v>56.39</v>
-      </c>
-      <c r="E148" s="7">
-        <v>8.699999999999999</v>
+        <v>34.36</v>
+      </c>
+      <c r="E148" s="8">
+        <v>-0.88</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>32.82</v>
+        <v>45.6</v>
       </c>
       <c r="D149" s="6">
-        <v>35.24</v>
+        <v>46.16</v>
       </c>
       <c r="E149" s="7">
-        <v>2.42</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>48.84</v>
+        <v>46.01</v>
       </c>
       <c r="D150" s="6">
-        <v>45.6</v>
+        <v>44.08</v>
       </c>
       <c r="E150" s="8">
-        <v>-3.24</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>38.25</v>
+        <v>59.55</v>
       </c>
       <c r="D151" s="6">
-        <v>46.01</v>
+        <v>59.88</v>
       </c>
       <c r="E151" s="7">
-        <v>7.76</v>
-      </c>
-    </row>
-    <row r="152" spans="1:5">
-      <c r="A152" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C152" s="6">
-        <v>50.53</v>
-      </c>
-      <c r="D152" s="6">
-        <v>59.55</v>
-      </c>
-      <c r="E152" s="7">
-        <v>9.02</v>
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5915,28 +5887,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>106</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>109</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5950,16 +5922,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>45.7</v>
+        <v>47.2</v>
       </c>
       <c r="E2" s="11">
         <v>20</v>
       </c>
       <c r="F2" s="11">
-        <v>-0.8</v>
+        <v>-0.7</v>
       </c>
       <c r="G2" s="11">
-        <v>-3.8</v>
+        <v>-3.7</v>
       </c>
       <c r="H2" s="11">
         <v>53.1</v>
@@ -6099,34 +6071,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2332</v>
+        <v>0.2347</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1674</v>
+        <v>0.169</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1574</v>
+        <v>0.1571</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1399</v>
+        <v>0.1419</v>
       </c>
       <c r="E2" s="14">
-        <v>0.121</v>
+        <v>0.1206</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1042</v>
+        <v>0.1052</v>
       </c>
       <c r="G2" s="14">
-        <v>0.08890000000000001</v>
+        <v>0.08810000000000001</v>
       </c>
       <c r="H2" s="14">
-        <v>0.0796</v>
+        <v>0.0803</v>
       </c>
       <c r="I2" s="14">
-        <v>0.0793</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="J2" s="14">
-        <v>0.07580000000000001</v>
+        <v>0.0756</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6140,10 +6112,10 @@
         <v>43</v>
       </c>
       <c r="D3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="13" t="s">
         <v>54</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>53</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>42</v>
@@ -6163,34 +6135,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0667</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0607</v>
+        <v>0.0608</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0592</v>
+        <v>0.0594</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0328</v>
+        <v>0.0357</v>
       </c>
       <c r="E4" s="14">
-        <v>0.03240000000000001</v>
+        <v>0.0248</v>
       </c>
       <c r="F4" s="14">
-        <v>0.0151</v>
+        <v>0.0143</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0329</v>
+        <v>-0.0254</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0709</v>
+        <v>-0.0673</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.0978</v>
+        <v>-0.08779999999999999</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.1044</v>
+        <v>-0.1153</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="124">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,19 +289,70 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>53.0 → 44.6</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.0</t>
-  </si>
-  <si>
-    <t>44.6</t>
+    <t>RSI Oversold Recovery</t>
+  </si>
+  <si>
+    <t>29.8 → 38.6</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>29.8</t>
+  </si>
+  <si>
+    <t>38.6</t>
+  </si>
+  <si>
+    <t>24.9 → 33.6</t>
+  </si>
+  <si>
+    <t>24.9</t>
+  </si>
+  <si>
+    <t>33.6</t>
+  </si>
+  <si>
+    <t>26.1 → 32.1</t>
+  </si>
+  <si>
+    <t>26.1</t>
+  </si>
+  <si>
+    <t>32.1</t>
+  </si>
+  <si>
+    <t>27.8 → 36.1</t>
+  </si>
+  <si>
+    <t>27.8</t>
+  </si>
+  <si>
+    <t>36.1</t>
+  </si>
+  <si>
+    <t>27.8 → 34.8</t>
+  </si>
+  <si>
+    <t>34.8</t>
+  </si>
+  <si>
+    <t>28.4 → 40.2</t>
+  </si>
+  <si>
+    <t>28.4</t>
+  </si>
+  <si>
+    <t>40.2</t>
+  </si>
+  <si>
+    <t>29.3 → 33.7</t>
+  </si>
+  <si>
+    <t>29.3</t>
+  </si>
+  <si>
+    <t>33.7</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -387,14 +438,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -427,13 +478,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1031,10 +1082,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>24862.3</v>
+        <v>24970.75</v>
       </c>
       <c r="E2">
-        <v>-0.6</v>
+        <v>0.44</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1043,43 +1094,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-16.14</v>
+        <v>-15.78</v>
       </c>
       <c r="I2">
-        <v>4.6</v>
+        <v>5.05</v>
       </c>
       <c r="J2">
-        <v>-2.79</v>
+        <v>-3.1</v>
       </c>
       <c r="K2">
-        <v>-8.210000000000001</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="L2">
-        <v>-8.26</v>
+        <v>-7.86</v>
       </c>
       <c r="M2">
-        <v>-6.67</v>
+        <v>-6.51</v>
       </c>
       <c r="N2">
-        <v>17.26</v>
+        <v>16.87</v>
       </c>
       <c r="O2">
         <v>40</v>
       </c>
       <c r="Q2">
-        <v>25286.04</v>
+        <v>25126.49</v>
       </c>
       <c r="R2">
-        <v>25559.51</v>
+        <v>25471.55</v>
       </c>
       <c r="S2">
-        <v>27172.15</v>
+        <v>27084.31</v>
       </c>
       <c r="T2">
-        <v>26906.72</v>
+        <v>26890.62</v>
       </c>
       <c r="U2">
-        <v>-7.6</v>
+        <v>-7.14</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1094,31 +1145,31 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>34.24</v>
+        <v>36.27</v>
       </c>
       <c r="AA2">
-        <v>-549.89</v>
+        <v>-539.25</v>
       </c>
       <c r="AB2">
-        <v>-598.85</v>
+        <v>-586.9299999999999</v>
       </c>
       <c r="AC2">
-        <v>48.96</v>
+        <v>47.68</v>
       </c>
       <c r="AD2">
-        <v>67.95</v>
+        <v>66.28</v>
       </c>
       <c r="AE2">
-        <v>78.26000000000001</v>
+        <v>70.73999999999999</v>
       </c>
       <c r="AF2">
-        <v>465.39</v>
+        <v>467.31</v>
       </c>
       <c r="AH2">
-        <v>26888.8</v>
+        <v>26703.99</v>
       </c>
       <c r="AI2">
-        <v>24230.22</v>
+        <v>24239.1</v>
       </c>
       <c r="AJ2">
         <v>26008.9</v>
@@ -1127,7 +1178,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>53.76</v>
+        <v>54.05</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1141,10 +1192,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>8792.299999999999</v>
+        <v>8932.700000000001</v>
       </c>
       <c r="E3">
-        <v>-1.41</v>
+        <v>1.6</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1153,43 +1204,43 @@
         <v>8792.299999999999</v>
       </c>
       <c r="H3">
-        <v>-16.29</v>
+        <v>-14.95</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J3">
-        <v>-3.06</v>
+        <v>-1.83</v>
       </c>
       <c r="K3">
-        <v>-7.93</v>
+        <v>-7.4</v>
       </c>
       <c r="L3">
-        <v>-10.58</v>
+        <v>-9.15</v>
       </c>
       <c r="M3">
-        <v>-2.85</v>
+        <v>-2.3</v>
       </c>
       <c r="N3">
-        <v>8.789999999999999</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="O3">
         <v>55</v>
       </c>
       <c r="Q3">
-        <v>8960.110000000001</v>
+        <v>8926.75</v>
       </c>
       <c r="R3">
-        <v>9110.34</v>
+        <v>9081.200000000001</v>
       </c>
       <c r="S3">
-        <v>9475.84</v>
+        <v>9456.09</v>
       </c>
       <c r="T3">
-        <v>9757.74</v>
+        <v>9754.83</v>
       </c>
       <c r="U3">
-        <v>-9.890000000000001</v>
+        <v>-8.43</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1204,31 +1255,31 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>29.83</v>
+        <v>38.62</v>
       </c>
       <c r="AA3">
-        <v>-170.15</v>
+        <v>-163.46</v>
       </c>
       <c r="AB3">
-        <v>-167.82</v>
+        <v>-166.95</v>
       </c>
       <c r="AC3">
-        <v>-2.33</v>
+        <v>3.49</v>
       </c>
       <c r="AD3">
-        <v>55.25</v>
+        <v>62.18</v>
       </c>
       <c r="AE3">
-        <v>70.47</v>
+        <v>62.99</v>
       </c>
       <c r="AF3">
-        <v>148.77</v>
+        <v>153.84</v>
       </c>
       <c r="AH3">
-        <v>9542.16</v>
+        <v>9474.84</v>
       </c>
       <c r="AI3">
-        <v>8678.530000000001</v>
+        <v>8687.549999999999</v>
       </c>
       <c r="AJ3">
         <v>9225.639999999999</v>
@@ -1237,7 +1288,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>43.54</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1251,10 +1302,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>10726.75</v>
+        <v>10804.45</v>
       </c>
       <c r="E4">
-        <v>-0.25</v>
+        <v>0.72</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1263,43 +1314,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-15.13</v>
+        <v>-14.52</v>
       </c>
       <c r="I4">
-        <v>3.8</v>
+        <v>4.55</v>
       </c>
       <c r="J4">
-        <v>-2.53</v>
+        <v>-2.26</v>
       </c>
       <c r="K4">
-        <v>-6.62</v>
+        <v>-6.42</v>
       </c>
       <c r="L4">
-        <v>-8.359999999999999</v>
+        <v>-7.69</v>
       </c>
       <c r="M4">
-        <v>-12.28</v>
+        <v>-12.51</v>
       </c>
       <c r="N4">
-        <v>8.93</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="O4">
         <v>15</v>
       </c>
       <c r="Q4">
-        <v>10861.31</v>
+        <v>10811.27</v>
       </c>
       <c r="R4">
-        <v>10988.16</v>
+        <v>10960.71</v>
       </c>
       <c r="S4">
-        <v>11449.37</v>
+        <v>11423.62</v>
       </c>
       <c r="T4">
-        <v>11489.43</v>
+        <v>11482.01</v>
       </c>
       <c r="U4">
-        <v>-6.64</v>
+        <v>-5.9</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1314,31 +1365,31 @@
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>34.38</v>
+        <v>38.43</v>
       </c>
       <c r="AA4">
-        <v>-175.92</v>
+        <v>-171.13</v>
       </c>
       <c r="AB4">
-        <v>-179.56</v>
+        <v>-177.87</v>
       </c>
       <c r="AC4">
-        <v>3.64</v>
+        <v>6.74</v>
       </c>
       <c r="AD4">
-        <v>56.81</v>
+        <v>56.02</v>
       </c>
       <c r="AE4">
-        <v>70.23999999999999</v>
+        <v>60.97</v>
       </c>
       <c r="AF4">
-        <v>155.8</v>
+        <v>159.66</v>
       </c>
       <c r="AH4">
-        <v>11375.76</v>
+        <v>11315.78</v>
       </c>
       <c r="AI4">
-        <v>10600.56</v>
+        <v>10605.64</v>
       </c>
       <c r="AJ4">
         <v>11143.46</v>
@@ -1347,7 +1398,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>51.68</v>
+        <v>52.67</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1361,10 +1412,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>34520.05</v>
+        <v>35022.35</v>
       </c>
       <c r="E5">
-        <v>-1.66</v>
+        <v>1.46</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1373,43 +1424,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-16.89</v>
+        <v>-15.68</v>
       </c>
       <c r="I5">
-        <v>4.3</v>
+        <v>5.81</v>
       </c>
       <c r="J5">
-        <v>-4.68</v>
+        <v>-3.23</v>
       </c>
       <c r="K5">
-        <v>-8.5</v>
+        <v>-7.25</v>
       </c>
       <c r="L5">
-        <v>-12.11</v>
+        <v>-10.83</v>
       </c>
       <c r="M5">
-        <v>-1.56</v>
+        <v>-0.85</v>
       </c>
       <c r="N5">
-        <v>7.41</v>
+        <v>7.52</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q5">
-        <v>35452.31</v>
+        <v>35218.61</v>
       </c>
       <c r="R5">
-        <v>36223.49</v>
+        <v>36106.56</v>
       </c>
       <c r="S5">
-        <v>37326.98</v>
+        <v>37251.88</v>
       </c>
       <c r="T5">
-        <v>37739.69</v>
+        <v>37738.18</v>
       </c>
       <c r="U5">
-        <v>-8.529999999999999</v>
+        <v>-7.2</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1424,31 +1475,31 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>24.86</v>
+        <v>33.59</v>
       </c>
       <c r="AA5">
-        <v>-623.0700000000001</v>
+        <v>-637.5599999999999</v>
       </c>
       <c r="AB5">
-        <v>-518.21</v>
+        <v>-542.08</v>
       </c>
       <c r="AC5">
-        <v>-104.86</v>
+        <v>-95.48</v>
       </c>
       <c r="AD5">
-        <v>13.45</v>
+        <v>19.27</v>
       </c>
       <c r="AE5">
-        <v>34.56</v>
+        <v>22.23</v>
       </c>
       <c r="AF5">
-        <v>575.25</v>
+        <v>598.96</v>
       </c>
       <c r="AH5">
-        <v>37651.19</v>
+        <v>37525.05</v>
       </c>
       <c r="AI5">
-        <v>34795.8</v>
+        <v>34688.08</v>
       </c>
       <c r="AJ5">
         <v>36227.11</v>
@@ -1457,7 +1508,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>44.12</v>
+        <v>47.65</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1471,10 +1522,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>42680.7</v>
+        <v>42800.75</v>
       </c>
       <c r="E6">
-        <v>-0.99</v>
+        <v>0.28</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1483,43 +1534,43 @@
         <v>42680.7</v>
       </c>
       <c r="H6">
-        <v>-24.82</v>
+        <v>-24.61</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="J6">
-        <v>-4.71</v>
+        <v>-4.07</v>
       </c>
       <c r="K6">
-        <v>-6.52</v>
+        <v>-7.48</v>
       </c>
       <c r="L6">
-        <v>-12.45</v>
+        <v>-12.2</v>
       </c>
       <c r="M6">
-        <v>-21.27</v>
+        <v>-21.82</v>
       </c>
       <c r="N6">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="O6">
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>43619.7</v>
+        <v>43256.62</v>
       </c>
       <c r="R6">
-        <v>44520.41</v>
+        <v>44372.48</v>
       </c>
       <c r="S6">
-        <v>45767.44</v>
+        <v>45654.87</v>
       </c>
       <c r="T6">
-        <v>48927.31</v>
+        <v>48863.94</v>
       </c>
       <c r="U6">
-        <v>-12.77</v>
+        <v>-12.41</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1534,40 +1585,40 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>33.56</v>
+        <v>34.8</v>
       </c>
       <c r="AA6">
-        <v>-660.23</v>
+        <v>-711.3099999999999</v>
       </c>
       <c r="AB6">
-        <v>-544.52</v>
+        <v>-577.88</v>
       </c>
       <c r="AC6">
-        <v>-115.71</v>
+        <v>-133.44</v>
       </c>
       <c r="AD6">
-        <v>29.18</v>
+        <v>14.42</v>
       </c>
       <c r="AE6">
-        <v>47.18</v>
+        <v>30.85</v>
       </c>
       <c r="AF6">
-        <v>748.85</v>
+        <v>752.13</v>
       </c>
       <c r="AH6">
-        <v>46171.64</v>
+        <v>46085.33</v>
       </c>
       <c r="AI6">
-        <v>42869.17</v>
+        <v>42659.63</v>
       </c>
       <c r="AJ6">
-        <v>44915.04</v>
+        <v>44659.77</v>
       </c>
       <c r="AK6" t="s">
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>35.89</v>
+        <v>39.45</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1581,10 +1632,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>24403</v>
+        <v>24454.35</v>
       </c>
       <c r="E7">
-        <v>-1.03</v>
+        <v>0.21</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1593,43 +1644,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-14.26</v>
+        <v>-14.08</v>
       </c>
       <c r="I7">
-        <v>3.75</v>
+        <v>3.96</v>
       </c>
       <c r="J7">
-        <v>-3.79</v>
+        <v>-3.67</v>
       </c>
       <c r="K7">
-        <v>-3.99</v>
+        <v>-4.34</v>
       </c>
       <c r="L7">
-        <v>-9.289999999999999</v>
+        <v>-9.1</v>
       </c>
       <c r="M7">
-        <v>-9.039999999999999</v>
+        <v>-9.67</v>
       </c>
       <c r="N7">
-        <v>4.53</v>
+        <v>4.47</v>
       </c>
       <c r="O7">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="Q7">
-        <v>24825.27</v>
+        <v>24638.72</v>
       </c>
       <c r="R7">
-        <v>24861.83</v>
+        <v>24836.84</v>
       </c>
       <c r="S7">
-        <v>25482.87</v>
+        <v>25443.42</v>
       </c>
       <c r="T7">
-        <v>26239.09</v>
+        <v>26223.3</v>
       </c>
       <c r="U7">
-        <v>-7</v>
+        <v>-6.75</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1644,31 +1695,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>37.43</v>
+        <v>38.61</v>
       </c>
       <c r="AA7">
-        <v>-194.76</v>
+        <v>-213.28</v>
       </c>
       <c r="AB7">
-        <v>-192.65</v>
+        <v>-196.78</v>
       </c>
       <c r="AC7">
-        <v>-2.11</v>
+        <v>-16.5</v>
       </c>
       <c r="AD7">
-        <v>40.74</v>
+        <v>29.44</v>
       </c>
       <c r="AE7">
-        <v>56.79</v>
+        <v>42.14</v>
       </c>
       <c r="AF7">
-        <v>368.6</v>
+        <v>366.58</v>
       </c>
       <c r="AH7">
-        <v>25397.5</v>
+        <v>25400.29</v>
       </c>
       <c r="AI7">
-        <v>24326.17</v>
+        <v>24273.4</v>
       </c>
       <c r="AJ7">
         <v>25420.21</v>
@@ -1677,7 +1728,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>28.98</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1691,10 +1742,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31995.5</v>
+        <v>32273.05</v>
       </c>
       <c r="E8">
-        <v>-0.27</v>
+        <v>0.87</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1703,43 +1754,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-18.97</v>
+        <v>-18.27</v>
       </c>
       <c r="I8">
-        <v>24.16</v>
+        <v>25.24</v>
       </c>
       <c r="J8">
-        <v>4.15</v>
+        <v>1.09</v>
       </c>
       <c r="K8">
-        <v>11.94</v>
+        <v>13.9</v>
       </c>
       <c r="L8">
-        <v>12.13</v>
+        <v>12.18</v>
       </c>
       <c r="M8">
-        <v>-9.140000000000001</v>
+        <v>-8.84</v>
       </c>
       <c r="N8">
-        <v>-1.78</v>
+        <v>-1.7</v>
       </c>
       <c r="O8">
         <v>95</v>
       </c>
       <c r="Q8">
-        <v>31987.93</v>
+        <v>32057.72</v>
       </c>
       <c r="R8">
-        <v>29382.65</v>
+        <v>29585.86</v>
       </c>
       <c r="S8">
-        <v>29850.54</v>
+        <v>29869.35</v>
       </c>
       <c r="T8">
-        <v>30816.45</v>
+        <v>30788.4</v>
       </c>
       <c r="U8">
-        <v>3.83</v>
+        <v>4.82</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1754,31 +1805,31 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>68.04000000000001</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="AA8">
-        <v>748.0599999999999</v>
+        <v>815.61</v>
       </c>
       <c r="AB8">
-        <v>285.72</v>
+        <v>391.7</v>
       </c>
       <c r="AC8">
-        <v>462.35</v>
+        <v>423.91</v>
       </c>
       <c r="AD8">
-        <v>91.41</v>
+        <v>88.58</v>
       </c>
       <c r="AE8">
-        <v>93.25</v>
+        <v>90.77</v>
       </c>
       <c r="AF8">
-        <v>831.4299999999999</v>
+        <v>849.78</v>
       </c>
       <c r="AH8">
-        <v>32883.74</v>
+        <v>33267.23</v>
       </c>
       <c r="AI8">
-        <v>25881.55</v>
+        <v>25904.48</v>
       </c>
       <c r="AJ8">
         <v>29979.37</v>
@@ -1787,7 +1838,7 @@
         <v>82</v>
       </c>
       <c r="AL8">
-        <v>54.67</v>
+        <v>53.06</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1801,10 +1852,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>14516.75</v>
+        <v>14665.7</v>
       </c>
       <c r="E9">
-        <v>-1.57</v>
+        <v>1.03</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1813,34 +1864,34 @@
         <v>14516.75</v>
       </c>
       <c r="H9">
-        <v>-12.88</v>
+        <v>-11.98</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="J9">
-        <v>-4</v>
+        <v>-3.35</v>
       </c>
       <c r="K9">
-        <v>-8.65</v>
+        <v>-8.44</v>
       </c>
       <c r="L9">
-        <v>-8.83</v>
+        <v>-7.44</v>
       </c>
       <c r="N9">
-        <v>-18.84</v>
+        <v>-16.2</v>
       </c>
       <c r="O9">
         <v>30</v>
       </c>
       <c r="Q9">
-        <v>14871.78</v>
+        <v>14770.1</v>
       </c>
       <c r="R9">
-        <v>15196.62</v>
+        <v>15139.42</v>
       </c>
       <c r="S9">
-        <v>15848.53</v>
+        <v>15809.23</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1852,31 +1903,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>26.1</v>
+        <v>32.14</v>
       </c>
       <c r="AA9">
-        <v>-301.49</v>
+        <v>-305.62</v>
       </c>
       <c r="AB9">
-        <v>-273.6</v>
+        <v>-280</v>
       </c>
       <c r="AC9">
-        <v>-27.9</v>
+        <v>-25.62</v>
       </c>
       <c r="AD9">
-        <v>27.69</v>
+        <v>28.71</v>
       </c>
       <c r="AE9">
-        <v>52.57</v>
+        <v>36.74</v>
       </c>
       <c r="AF9">
-        <v>231.34</v>
+        <v>234.7</v>
       </c>
       <c r="AH9">
-        <v>15891.43</v>
+        <v>15809.62</v>
       </c>
       <c r="AI9">
-        <v>14501.81</v>
+        <v>14469.21</v>
       </c>
       <c r="AJ9">
         <v>15216.01</v>
@@ -1885,7 +1936,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>60.94</v>
+        <v>63.25</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1899,10 +1950,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8554.25</v>
+        <v>8661.200000000001</v>
       </c>
       <c r="E10">
-        <v>-0.44</v>
+        <v>1.25</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1911,43 +1962,43 @@
         <v>8499.65</v>
       </c>
       <c r="H10">
-        <v>-12.41</v>
+        <v>-11.31</v>
       </c>
       <c r="I10">
-        <v>0.64</v>
+        <v>1.9</v>
       </c>
       <c r="J10">
-        <v>-1.52</v>
+        <v>-0.74</v>
       </c>
       <c r="K10">
-        <v>-5.17</v>
+        <v>-4.77</v>
       </c>
       <c r="L10">
-        <v>-8.779999999999999</v>
+        <v>-7.64</v>
       </c>
       <c r="M10">
-        <v>-6.35</v>
+        <v>-6.13</v>
       </c>
       <c r="N10">
-        <v>10.92</v>
+        <v>10.88</v>
       </c>
       <c r="O10">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q10">
-        <v>8634.49</v>
+        <v>8621.610000000001</v>
       </c>
       <c r="R10">
-        <v>8678.809999999999</v>
+        <v>8664.629999999999</v>
       </c>
       <c r="S10">
-        <v>8996.17</v>
+        <v>8981.200000000001</v>
       </c>
       <c r="T10">
-        <v>9226.08</v>
+        <v>9221.299999999999</v>
       </c>
       <c r="U10">
-        <v>-7.28</v>
+        <v>-6.07</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1962,31 +2013,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>37.21</v>
+        <v>44.43</v>
       </c>
       <c r="AA10">
-        <v>-113.65</v>
+        <v>-103.79</v>
       </c>
       <c r="AB10">
-        <v>-126.74</v>
+        <v>-122.15</v>
       </c>
       <c r="AC10">
-        <v>13.09</v>
+        <v>18.36</v>
       </c>
       <c r="AD10">
-        <v>69.18000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="AE10">
-        <v>79.76000000000001</v>
+        <v>74.73</v>
       </c>
       <c r="AF10">
-        <v>129.74</v>
+        <v>134.25</v>
       </c>
       <c r="AH10">
-        <v>8933.799999999999</v>
+        <v>8886.75</v>
       </c>
       <c r="AI10">
-        <v>8423.82</v>
+        <v>8442.5</v>
       </c>
       <c r="AJ10">
         <v>8855.59</v>
@@ -1995,7 +2046,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>34.82</v>
+        <v>32.87</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2009,10 +2060,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1563.4</v>
+        <v>1558.1</v>
       </c>
       <c r="E11">
-        <v>-1.33</v>
+        <v>-0.34</v>
       </c>
       <c r="F11">
         <v>1648.25</v>
@@ -2021,43 +2072,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-5.15</v>
+        <v>-5.47</v>
       </c>
       <c r="I11">
-        <v>24.74</v>
+        <v>24.31</v>
       </c>
       <c r="J11">
-        <v>-3.33</v>
+        <v>-5.47</v>
       </c>
       <c r="K11">
-        <v>-0.72</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L11">
-        <v>2.76</v>
+        <v>2.41</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="N11">
-        <v>-7.25</v>
+        <v>-7.78</v>
       </c>
       <c r="O11">
         <v>90</v>
       </c>
       <c r="Q11">
-        <v>1612.54</v>
+        <v>1594.51</v>
       </c>
       <c r="R11">
-        <v>1584.34</v>
+        <v>1584.53</v>
       </c>
       <c r="S11">
-        <v>1574.31</v>
+        <v>1574.09</v>
       </c>
       <c r="T11">
-        <v>1469.34</v>
+        <v>1469.91</v>
       </c>
       <c r="U11">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="V11" t="s">
         <v>80</v>
@@ -2072,31 +2123,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>46.1</v>
+        <v>45.23</v>
       </c>
       <c r="AA11">
-        <v>13.25</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="AB11">
-        <v>14.53</v>
+        <v>13.43</v>
       </c>
       <c r="AC11">
-        <v>-1.27</v>
+        <v>-4.4</v>
       </c>
       <c r="AD11">
-        <v>29.59</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AE11">
-        <v>56.57</v>
+        <v>32.11</v>
       </c>
       <c r="AF11">
-        <v>36.53</v>
+        <v>36.14</v>
       </c>
       <c r="AH11">
-        <v>1663.12</v>
+        <v>1663.02</v>
       </c>
       <c r="AI11">
-        <v>1505.56</v>
+        <v>1506.05</v>
       </c>
       <c r="AJ11">
         <v>1544.25</v>
@@ -2105,7 +2156,7 @@
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>26.22</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2119,10 +2170,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>11478.2</v>
+        <v>11731.55</v>
       </c>
       <c r="E12">
-        <v>-2.71</v>
+        <v>2.21</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2131,43 +2182,43 @@
         <v>10017.9</v>
       </c>
       <c r="H12">
-        <v>-16.33</v>
+        <v>-14.48</v>
       </c>
       <c r="I12">
-        <v>14.58</v>
+        <v>17.11</v>
       </c>
       <c r="J12">
-        <v>-4.5</v>
+        <v>-3.31</v>
       </c>
       <c r="K12">
-        <v>-11.64</v>
+        <v>-11.81</v>
       </c>
       <c r="L12">
-        <v>-7.71</v>
+        <v>-5.67</v>
       </c>
       <c r="M12">
-        <v>13.46</v>
+        <v>14.81</v>
       </c>
       <c r="N12">
-        <v>15.13</v>
+        <v>15.01</v>
       </c>
       <c r="O12">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q12">
-        <v>11867.14</v>
+        <v>11786.81</v>
       </c>
       <c r="R12">
-        <v>12291.74</v>
+        <v>12226.22</v>
       </c>
       <c r="S12">
-        <v>12802.5</v>
+        <v>12773.7</v>
       </c>
       <c r="T12">
-        <v>12478.56</v>
+        <v>12481.38</v>
       </c>
       <c r="U12">
-        <v>-8.02</v>
+        <v>-6.01</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2182,31 +2233,31 @@
         <v>1</v>
       </c>
       <c r="Z12">
-        <v>27.83</v>
+        <v>36.14</v>
       </c>
       <c r="AA12">
-        <v>-314.88</v>
+        <v>-313.8</v>
       </c>
       <c r="AB12">
-        <v>-266.07</v>
+        <v>-275.62</v>
       </c>
       <c r="AC12">
-        <v>-48.81</v>
+        <v>-38.19</v>
       </c>
       <c r="AD12">
-        <v>21.38</v>
+        <v>30.64</v>
       </c>
       <c r="AE12">
-        <v>34.68</v>
+        <v>29.73</v>
       </c>
       <c r="AF12">
-        <v>258.32</v>
+        <v>265.71</v>
       </c>
       <c r="AH12">
-        <v>13218.64</v>
+        <v>13114.28</v>
       </c>
       <c r="AI12">
-        <v>11364.84</v>
+        <v>11338.16</v>
       </c>
       <c r="AJ12">
         <v>12304.47</v>
@@ -2215,7 +2266,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>54.72</v>
+        <v>56.49</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2229,10 +2280,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>8885.75</v>
+        <v>8984.950000000001</v>
       </c>
       <c r="E13">
-        <v>-1.64</v>
+        <v>1.12</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2241,43 +2292,43 @@
         <v>8885.75</v>
       </c>
       <c r="H13">
-        <v>-17.47</v>
+        <v>-16.55</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="J13">
-        <v>-4.01</v>
+        <v>-2.84</v>
       </c>
       <c r="K13">
-        <v>-7.6</v>
+        <v>-6.77</v>
       </c>
       <c r="L13">
-        <v>-10.59</v>
+        <v>-9.59</v>
       </c>
       <c r="M13">
-        <v>-9.119999999999999</v>
+        <v>-9.25</v>
       </c>
       <c r="N13">
-        <v>16.52</v>
+        <v>16.56</v>
       </c>
       <c r="O13">
         <v>20</v>
       </c>
       <c r="Q13">
-        <v>9090.48</v>
+        <v>9038.01</v>
       </c>
       <c r="R13">
-        <v>9233.370000000001</v>
+        <v>9204.85</v>
       </c>
       <c r="S13">
-        <v>9518.5</v>
+        <v>9500.809999999999</v>
       </c>
       <c r="T13">
-        <v>9982.440000000001</v>
+        <v>9978.1</v>
       </c>
       <c r="U13">
-        <v>-10.99</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2292,31 +2343,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>27.76</v>
+        <v>34.76</v>
       </c>
       <c r="AA13">
-        <v>-141.36</v>
+        <v>-143.79</v>
       </c>
       <c r="AB13">
-        <v>-128.75</v>
+        <v>-131.76</v>
       </c>
       <c r="AC13">
-        <v>-12.61</v>
+        <v>-12.03</v>
       </c>
       <c r="AD13">
-        <v>40.42</v>
+        <v>39.36</v>
       </c>
       <c r="AE13">
-        <v>59.17</v>
+        <v>46.89</v>
       </c>
       <c r="AF13">
-        <v>141.17</v>
+        <v>144.59</v>
       </c>
       <c r="AH13">
-        <v>9578.52</v>
+        <v>9531.74</v>
       </c>
       <c r="AI13">
-        <v>8888.219999999999</v>
+        <v>8877.959999999999</v>
       </c>
       <c r="AJ13">
         <v>9317.65</v>
@@ -2325,7 +2376,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>53.9</v>
+        <v>56.58</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2339,10 +2390,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8070.7</v>
+        <v>8093.8</v>
       </c>
       <c r="E14">
-        <v>-2.26</v>
+        <v>0.29</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2351,43 +2402,43 @@
         <v>7638.75</v>
       </c>
       <c r="H14">
-        <v>-18.31</v>
+        <v>-18.08</v>
       </c>
       <c r="I14">
-        <v>5.65</v>
+        <v>5.96</v>
       </c>
       <c r="J14">
-        <v>0.37</v>
+        <v>-0.01</v>
       </c>
       <c r="K14">
-        <v>-2.43</v>
+        <v>-3.25</v>
       </c>
       <c r="L14">
-        <v>-3.71</v>
+        <v>-3.44</v>
       </c>
       <c r="M14">
-        <v>6.24</v>
+        <v>4.8</v>
       </c>
       <c r="N14">
-        <v>23.14</v>
+        <v>22.97</v>
       </c>
       <c r="O14">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Q14">
-        <v>8193.73</v>
+        <v>8193.5</v>
       </c>
       <c r="R14">
-        <v>8105.36</v>
+        <v>8096.49</v>
       </c>
       <c r="S14">
-        <v>8344.99</v>
+        <v>8330.52</v>
       </c>
       <c r="T14">
-        <v>8571.370000000001</v>
+        <v>8569.17</v>
       </c>
       <c r="U14">
-        <v>-5.84</v>
+        <v>-5.55</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2402,31 +2453,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>44.57</v>
+        <v>45.72</v>
       </c>
       <c r="AA14">
-        <v>-35.56</v>
+        <v>-37.39</v>
       </c>
       <c r="AB14">
-        <v>-62.3</v>
+        <v>-57.32</v>
       </c>
       <c r="AC14">
-        <v>26.74</v>
+        <v>19.93</v>
       </c>
       <c r="AD14">
-        <v>77.19</v>
+        <v>64.34</v>
       </c>
       <c r="AE14">
-        <v>88.09999999999999</v>
+        <v>78.77</v>
       </c>
       <c r="AF14">
-        <v>157.21</v>
+        <v>157.01</v>
       </c>
       <c r="AH14">
-        <v>8334.83</v>
+        <v>8312.290000000001</v>
       </c>
       <c r="AI14">
-        <v>7875.89</v>
+        <v>7880.7</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
@@ -2435,7 +2486,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>22.48</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2449,10 +2500,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>25329.45</v>
+        <v>25774.25</v>
       </c>
       <c r="E15">
-        <v>-1.04</v>
+        <v>1.76</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2461,43 +2512,43 @@
         <v>21549.55</v>
       </c>
       <c r="H15">
-        <v>-6.83</v>
+        <v>-5.19</v>
       </c>
       <c r="I15">
-        <v>17.54</v>
+        <v>19.6</v>
       </c>
       <c r="J15">
-        <v>-1.89</v>
+        <v>-0.03</v>
       </c>
       <c r="K15">
-        <v>-5.87</v>
+        <v>-5.07</v>
       </c>
       <c r="L15">
-        <v>-1.26</v>
+        <v>0.88</v>
       </c>
       <c r="M15">
-        <v>14.93</v>
+        <v>16.85</v>
       </c>
       <c r="N15">
-        <v>12.7</v>
+        <v>13.03</v>
       </c>
       <c r="O15">
         <v>99</v>
       </c>
       <c r="Q15">
-        <v>25577.73</v>
+        <v>25576.25</v>
       </c>
       <c r="R15">
-        <v>26148.12</v>
+        <v>26085.4</v>
       </c>
       <c r="S15">
-        <v>26441.28</v>
+        <v>26421.52</v>
       </c>
       <c r="T15">
-        <v>24382.16</v>
+        <v>24397.42</v>
       </c>
       <c r="U15">
-        <v>3.89</v>
+        <v>5.64</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2512,31 +2563,31 @@
         <v>2</v>
       </c>
       <c r="Z15">
-        <v>32.75</v>
+        <v>43.84</v>
       </c>
       <c r="AA15">
-        <v>-287.02</v>
+        <v>-268.48</v>
       </c>
       <c r="AB15">
-        <v>-206.44</v>
+        <v>-218.85</v>
       </c>
       <c r="AC15">
-        <v>-80.58</v>
+        <v>-49.63</v>
       </c>
       <c r="AD15">
-        <v>2.18</v>
+        <v>25.09</v>
       </c>
       <c r="AE15">
-        <v>2.29</v>
+        <v>9.82</v>
       </c>
       <c r="AF15">
-        <v>411.08</v>
+        <v>416.44</v>
       </c>
       <c r="AH15">
-        <v>27175.75</v>
+        <v>27037.05</v>
       </c>
       <c r="AI15">
-        <v>25120.49</v>
+        <v>25133.74</v>
       </c>
       <c r="AJ15">
         <v>26568.83</v>
@@ -2545,7 +2596,7 @@
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>48.33</v>
+        <v>47.73</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2559,10 +2610,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>784.35</v>
+        <v>789.7</v>
       </c>
       <c r="E16">
-        <v>-2.38</v>
+        <v>0.68</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2571,43 +2622,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-19.03</v>
+        <v>-18.47</v>
       </c>
       <c r="I16">
-        <v>20.46</v>
+        <v>21.28</v>
       </c>
       <c r="J16">
-        <v>-5.35</v>
+        <v>-4.39</v>
       </c>
       <c r="K16">
-        <v>-8.960000000000001</v>
+        <v>-9.33</v>
       </c>
       <c r="L16">
-        <v>-14.62</v>
+        <v>-14.04</v>
       </c>
       <c r="M16">
-        <v>-11.71</v>
+        <v>-13.73</v>
       </c>
       <c r="N16">
-        <v>9.59</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="O16">
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>807.13</v>
+        <v>799.88</v>
       </c>
       <c r="R16">
-        <v>826.26</v>
+        <v>822.6799999999999</v>
       </c>
       <c r="S16">
-        <v>861.59</v>
+        <v>859.59</v>
       </c>
       <c r="T16">
-        <v>822.72</v>
+        <v>822.28</v>
       </c>
       <c r="U16">
-        <v>-4.66</v>
+        <v>-3.96</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2622,40 +2673,40 @@
         <v>1</v>
       </c>
       <c r="Z16">
-        <v>32.51</v>
+        <v>35.08</v>
       </c>
       <c r="AA16">
-        <v>-16.44</v>
+        <v>-17.18</v>
       </c>
       <c r="AB16">
-        <v>-14.95</v>
+        <v>-15.39</v>
       </c>
       <c r="AC16">
-        <v>-1.49</v>
+        <v>-1.79</v>
       </c>
       <c r="AD16">
-        <v>35.29</v>
+        <v>27.96</v>
       </c>
       <c r="AE16">
-        <v>54.42</v>
+        <v>39.73</v>
       </c>
       <c r="AF16">
-        <v>18.83</v>
+        <v>18.76</v>
       </c>
       <c r="AH16">
-        <v>869.95</v>
+        <v>865.99</v>
       </c>
       <c r="AI16">
-        <v>782.58</v>
+        <v>779.37</v>
       </c>
       <c r="AJ16">
-        <v>843.0700000000001</v>
+        <v>838.5700000000001</v>
       </c>
       <c r="AK16" t="s">
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>35.88</v>
+        <v>39.65</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2669,10 +2720,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>29934.75</v>
+        <v>30162.5</v>
       </c>
       <c r="E17">
-        <v>-0.21</v>
+        <v>0.76</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2681,43 +2732,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-12.22</v>
+        <v>-11.55</v>
       </c>
       <c r="I17">
-        <v>5.54</v>
+        <v>6.34</v>
       </c>
       <c r="J17">
-        <v>-0.2</v>
+        <v>-1.05</v>
       </c>
       <c r="K17">
-        <v>-0.12</v>
+        <v>0.33</v>
       </c>
       <c r="L17">
-        <v>-4.79</v>
+        <v>-4.06</v>
       </c>
       <c r="M17">
-        <v>-8.98</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="N17">
-        <v>3.18</v>
+        <v>3.26</v>
       </c>
       <c r="O17">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="Q17">
-        <v>30135.63</v>
+        <v>30071.76</v>
       </c>
       <c r="R17">
-        <v>29448.88</v>
+        <v>29480.01</v>
       </c>
       <c r="S17">
-        <v>30082.45</v>
+        <v>30062.12</v>
       </c>
       <c r="T17">
-        <v>30969.4</v>
+        <v>30951.93</v>
       </c>
       <c r="U17">
-        <v>-3.34</v>
+        <v>-2.55</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2732,31 +2783,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>52.83</v>
+        <v>56.21</v>
       </c>
       <c r="AA17">
-        <v>18.63</v>
+        <v>47.94</v>
       </c>
       <c r="AB17">
-        <v>-128.43</v>
+        <v>-93.16</v>
       </c>
       <c r="AC17">
-        <v>147.06</v>
+        <v>141.1</v>
       </c>
       <c r="AD17">
-        <v>78.98</v>
+        <v>78.33</v>
       </c>
       <c r="AE17">
-        <v>83.43000000000001</v>
+        <v>79.76000000000001</v>
       </c>
       <c r="AF17">
-        <v>427.16</v>
+        <v>435.58</v>
       </c>
       <c r="AH17">
-        <v>30471.68</v>
+        <v>30551.23</v>
       </c>
       <c r="AI17">
-        <v>28426.08</v>
+        <v>28408.79</v>
       </c>
       <c r="AJ17">
         <v>29148.67</v>
@@ -2765,7 +2816,7 @@
         <v>82</v>
       </c>
       <c r="AL17">
-        <v>32.15</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2779,10 +2830,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>15387</v>
+        <v>15658.7</v>
       </c>
       <c r="E18">
-        <v>-0.83</v>
+        <v>1.77</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2791,34 +2842,34 @@
         <v>15387</v>
       </c>
       <c r="H18">
-        <v>-9.18</v>
+        <v>-7.57</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="J18">
-        <v>-2.15</v>
+        <v>-0.16</v>
       </c>
       <c r="K18">
-        <v>-7.97</v>
+        <v>-7.17</v>
       </c>
       <c r="L18">
-        <v>-5.58</v>
+        <v>-3.56</v>
       </c>
       <c r="N18">
-        <v>-2.88</v>
+        <v>1.86</v>
       </c>
       <c r="O18">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Q18">
-        <v>15530.11</v>
+        <v>15525.14</v>
       </c>
       <c r="R18">
-        <v>15957.52</v>
+        <v>15902.6</v>
       </c>
       <c r="S18">
-        <v>16325.07</v>
+        <v>16305.6</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2830,31 +2881,31 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>28.39</v>
+        <v>40.16</v>
       </c>
       <c r="AA18">
-        <v>-264.72</v>
+        <v>-248.91</v>
       </c>
       <c r="AB18">
-        <v>-220.32</v>
+        <v>-226.04</v>
       </c>
       <c r="AC18">
-        <v>-44.4</v>
+        <v>-22.88</v>
       </c>
       <c r="AD18">
-        <v>2.98</v>
+        <v>35.58</v>
       </c>
       <c r="AE18">
-        <v>6.02</v>
+        <v>14.57</v>
       </c>
       <c r="AF18">
-        <v>244</v>
+        <v>247.78</v>
       </c>
       <c r="AH18">
-        <v>16771.98</v>
+        <v>16633.91</v>
       </c>
       <c r="AI18">
-        <v>15143.06</v>
+        <v>15171.29</v>
       </c>
       <c r="AJ18">
         <v>16084.17</v>
@@ -2863,7 +2914,7 @@
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>68.18000000000001</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2877,10 +2928,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>8561.200000000001</v>
+        <v>8661.950000000001</v>
       </c>
       <c r="E19">
-        <v>-2.6</v>
+        <v>1.18</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2889,34 +2940,34 @@
         <v>8561.200000000001</v>
       </c>
       <c r="H19">
-        <v>-14.38</v>
+        <v>-13.37</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="J19">
-        <v>-6.91</v>
+        <v>-5.96</v>
       </c>
       <c r="K19">
-        <v>-9.609999999999999</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L19">
-        <v>-8.789999999999999</v>
+        <v>-7.4</v>
       </c>
       <c r="N19">
-        <v>-12.7</v>
+        <v>-9.65</v>
       </c>
       <c r="O19">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="Q19">
-        <v>8916.6</v>
+        <v>8806.870000000001</v>
       </c>
       <c r="R19">
-        <v>9135.52</v>
+        <v>9100.540000000001</v>
       </c>
       <c r="S19">
-        <v>9456.120000000001</v>
+        <v>9436.139999999999</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2928,40 +2979,40 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>29.26</v>
+        <v>33.7</v>
       </c>
       <c r="AA19">
-        <v>-161.76</v>
+        <v>-177.96</v>
       </c>
       <c r="AB19">
-        <v>-118.69</v>
+        <v>-130.55</v>
       </c>
       <c r="AC19">
-        <v>-43.07</v>
+        <v>-47.41</v>
       </c>
       <c r="AD19">
-        <v>2.03</v>
+        <v>7.56</v>
       </c>
       <c r="AE19">
-        <v>23.59</v>
+        <v>10.24</v>
       </c>
       <c r="AF19">
-        <v>188.35</v>
+        <v>190.49</v>
       </c>
       <c r="AH19">
-        <v>9547.34</v>
+        <v>9548.74</v>
       </c>
       <c r="AI19">
-        <v>8723.700000000001</v>
+        <v>8652.33</v>
       </c>
       <c r="AJ19">
-        <v>9194.360000000001</v>
+        <v>9128.139999999999</v>
       </c>
       <c r="AK19" t="s">
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>36.9</v>
+        <v>41.12</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2975,10 +3026,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10380.55</v>
+        <v>10520.95</v>
       </c>
       <c r="E20">
-        <v>-0.62</v>
+        <v>1.35</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -2987,34 +3038,34 @@
         <v>10299.4</v>
       </c>
       <c r="H20">
-        <v>-8.69</v>
+        <v>-7.46</v>
       </c>
       <c r="I20">
-        <v>0.79</v>
+        <v>2.15</v>
       </c>
       <c r="J20">
-        <v>-2.11</v>
+        <v>-0.34</v>
       </c>
       <c r="K20">
-        <v>-5.28</v>
+        <v>-4.4</v>
       </c>
       <c r="L20">
-        <v>-6.72</v>
+        <v>-5.02</v>
       </c>
       <c r="N20">
-        <v>-14.98</v>
+        <v>-11.54</v>
       </c>
       <c r="O20">
         <v>65</v>
       </c>
       <c r="Q20">
-        <v>10492.73</v>
+        <v>10485.57</v>
       </c>
       <c r="R20">
-        <v>10536.7</v>
+        <v>10519.25</v>
       </c>
       <c r="S20">
-        <v>10870.5</v>
+        <v>10855.04</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3026,31 +3077,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>36.85</v>
+        <v>45.05</v>
       </c>
       <c r="AA20">
-        <v>-120.36</v>
+        <v>-109.72</v>
       </c>
       <c r="AB20">
-        <v>-133.93</v>
+        <v>-129.09</v>
       </c>
       <c r="AC20">
-        <v>13.57</v>
+        <v>19.37</v>
       </c>
       <c r="AD20">
-        <v>66.95</v>
+        <v>69.84</v>
       </c>
       <c r="AE20">
-        <v>78.33</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="AF20">
-        <v>161.02</v>
+        <v>167.08</v>
       </c>
       <c r="AH20">
-        <v>10853.28</v>
+        <v>10794.26</v>
       </c>
       <c r="AI20">
-        <v>10220.12</v>
+        <v>10244.25</v>
       </c>
       <c r="AJ20">
         <v>10732.68</v>
@@ -3059,7 +3110,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>28.97</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3073,10 +3124,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>26656.3</v>
+        <v>26825.3</v>
       </c>
       <c r="E21">
-        <v>-0.78</v>
+        <v>0.63</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3085,43 +3136,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-8.67</v>
+        <v>-8.09</v>
       </c>
       <c r="I21">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="J21">
-        <v>-3.7</v>
+        <v>-3.16</v>
       </c>
       <c r="K21">
-        <v>-2.31</v>
+        <v>-1.97</v>
       </c>
       <c r="L21">
-        <v>-6.5</v>
+        <v>-5.9</v>
       </c>
       <c r="M21">
-        <v>-3.75</v>
+        <v>-3.25</v>
       </c>
       <c r="N21">
-        <v>4.49</v>
+        <v>4.65</v>
       </c>
       <c r="O21">
         <v>75</v>
       </c>
       <c r="Q21">
-        <v>27063.27</v>
+        <v>26888.22</v>
       </c>
       <c r="R21">
-        <v>26979.44</v>
+        <v>26982.5</v>
       </c>
       <c r="S21">
-        <v>27266.09</v>
+        <v>27254.43</v>
       </c>
       <c r="T21">
-        <v>27403.82</v>
+        <v>27394.34</v>
       </c>
       <c r="U21">
-        <v>-2.73</v>
+        <v>-2.08</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3136,31 +3187,31 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>41.01</v>
+        <v>44.54</v>
       </c>
       <c r="AA21">
-        <v>-65.47</v>
+        <v>-79.53</v>
       </c>
       <c r="AB21">
-        <v>-49.68</v>
+        <v>-55.65</v>
       </c>
       <c r="AC21">
-        <v>-15.79</v>
+        <v>-23.88</v>
       </c>
       <c r="AD21">
-        <v>19.69</v>
+        <v>16.67</v>
       </c>
       <c r="AE21">
-        <v>40.45</v>
+        <v>24.88</v>
       </c>
       <c r="AF21">
-        <v>397.07</v>
+        <v>387.68</v>
       </c>
       <c r="AH21">
-        <v>27672.12</v>
+        <v>27671.71</v>
       </c>
       <c r="AI21">
-        <v>26286.75</v>
+        <v>26293.3</v>
       </c>
       <c r="AJ21">
         <v>26545.98</v>
@@ -3169,7 +3220,7 @@
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>27.88</v>
+        <v>29.31</v>
       </c>
     </row>
   </sheetData>
@@ -3310,7 +3361,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F152"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3350,7 +3401,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3368,2518 +3419,2604 @@
         <v>93</v>
       </c>
     </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="A5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="6">
-        <v>-7.88</v>
-      </c>
-      <c r="D7" s="6">
-        <v>-8.210000000000001</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-6.56</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-7.93</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-6.57</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-6.62</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-7.18</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-8.5</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-1.32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="6">
-        <v>-6.09</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-6.52</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-3.4</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.99</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-0.59</v>
+      <c r="B12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>11.27</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="D13" s="6">
-        <v>11.94</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.67</v>
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.16</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.51</v>
+        <v>-7.93</v>
       </c>
       <c r="D14" s="6">
-        <v>-8.65</v>
+        <v>-7.4</v>
       </c>
       <c r="E14" s="7">
-        <v>-1.14</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-5.15</v>
+        <v>-6.62</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.17</v>
+        <v>-6.42</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>1.83</v>
+        <v>-8.5</v>
       </c>
       <c r="D16" s="6">
-        <v>-0.72</v>
+        <v>-7.25</v>
       </c>
       <c r="E16" s="7">
-        <v>-2.55</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-9.050000000000001</v>
+        <v>-6.52</v>
       </c>
       <c r="D17" s="6">
-        <v>-11.64</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.59</v>
+        <v>-7.48</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.93</v>
+        <v>-3.99</v>
       </c>
       <c r="D18" s="6">
-        <v>-7.6</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-1.67</v>
+        <v>-4.34</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-0.66</v>
+        <v>11.94</v>
       </c>
       <c r="D19" s="6">
-        <v>-2.43</v>
+        <v>13.9</v>
       </c>
       <c r="E19" s="7">
-        <v>-1.77</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-5.27</v>
+        <v>-8.65</v>
       </c>
       <c r="D20" s="6">
-        <v>-5.87</v>
+        <v>-8.44</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.6</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-5.9</v>
+        <v>-5.17</v>
       </c>
       <c r="D21" s="6">
-        <v>-8.960000000000001</v>
+        <v>-4.77</v>
       </c>
       <c r="E21" s="7">
-        <v>-3.06</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-0.21</v>
+        <v>-0.72</v>
       </c>
       <c r="D22" s="6">
-        <v>-0.12</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.09</v>
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E22" s="7">
+        <v>0.16</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-7.63</v>
+        <v>-11.64</v>
       </c>
       <c r="D23" s="6">
-        <v>-7.97</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-0.34</v>
+        <v>-11.81</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-6.66</v>
+        <v>-7.6</v>
       </c>
       <c r="D24" s="6">
-        <v>-9.609999999999999</v>
+        <v>-6.77</v>
       </c>
       <c r="E24" s="7">
-        <v>-2.95</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-5.09</v>
+        <v>-2.43</v>
       </c>
       <c r="D25" s="6">
-        <v>-5.28</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.19</v>
+        <v>-3.25</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-1.84</v>
+        <v>-5.87</v>
       </c>
       <c r="D26" s="6">
-        <v>-2.31</v>
+        <v>-5.07</v>
       </c>
       <c r="E26" s="7">
-        <v>-0.47</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-0.58</v>
+        <v>-8.960000000000001</v>
       </c>
       <c r="D27" s="6">
-        <v>-2.79</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.21</v>
+        <v>-9.33</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-1.04</v>
+        <v>-0.12</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.06</v>
+        <v>0.33</v>
       </c>
       <c r="E28" s="7">
-        <v>-2.02</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-1.44</v>
+        <v>-7.97</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.53</v>
+        <v>-7.17</v>
       </c>
       <c r="E29" s="7">
-        <v>-1.09</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-3.84</v>
+        <v>-9.609999999999999</v>
       </c>
       <c r="D30" s="6">
-        <v>-4.68</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="E30" s="7">
-        <v>-0.84</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6">
-        <v>-4.78</v>
+        <v>-5.28</v>
       </c>
       <c r="D31" s="6">
-        <v>-4.71</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.07000000000000001</v>
+        <v>-4.4</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.88</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6">
-        <v>-1.17</v>
+        <v>-2.31</v>
       </c>
       <c r="D32" s="6">
-        <v>-3.79</v>
+        <v>-1.97</v>
       </c>
       <c r="E32" s="7">
-        <v>-2.62</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>6.33</v>
+        <v>-2.79</v>
       </c>
       <c r="D33" s="6">
-        <v>4.15</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-2.18</v>
+        <v>-3.1</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.22</v>
+        <v>-3.06</v>
       </c>
       <c r="D34" s="6">
-        <v>-4</v>
+        <v>-1.83</v>
       </c>
       <c r="E34" s="7">
-        <v>-1.78</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>0.14</v>
+        <v>-2.53</v>
       </c>
       <c r="D35" s="6">
-        <v>-1.52</v>
+        <v>-2.26</v>
       </c>
       <c r="E35" s="7">
-        <v>-1.66</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-3.46</v>
+        <v>-4.68</v>
       </c>
       <c r="D36" s="6">
-        <v>-3.33</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.13</v>
+        <v>-3.23</v>
+      </c>
+      <c r="E36" s="7">
+        <v>1.45</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-1.74</v>
+        <v>-4.71</v>
       </c>
       <c r="D37" s="6">
-        <v>-4.5</v>
+        <v>-4.07</v>
       </c>
       <c r="E37" s="7">
-        <v>-2.76</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-2.66</v>
+        <v>-3.79</v>
       </c>
       <c r="D38" s="6">
-        <v>-4.01</v>
+        <v>-3.67</v>
       </c>
       <c r="E38" s="7">
-        <v>-1.35</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>1.1</v>
+        <v>4.15</v>
       </c>
       <c r="D39" s="6">
-        <v>0.37</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.73</v>
+        <v>1.09</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-3.06</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-0.55</v>
+        <v>-4</v>
       </c>
       <c r="D40" s="6">
-        <v>-1.89</v>
+        <v>-3.35</v>
       </c>
       <c r="E40" s="7">
-        <v>-1.34</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>-2.35</v>
+        <v>-1.52</v>
       </c>
       <c r="D41" s="6">
-        <v>-5.35</v>
+        <v>-0.74</v>
       </c>
       <c r="E41" s="7">
-        <v>-3</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>1.84</v>
+        <v>-3.33</v>
       </c>
       <c r="D42" s="6">
-        <v>-0.2</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-2.04</v>
+        <v>-5.47</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-0.9399999999999999</v>
+        <v>-4.5</v>
       </c>
       <c r="D43" s="6">
-        <v>-2.15</v>
+        <v>-3.31</v>
       </c>
       <c r="E43" s="7">
-        <v>-1.21</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>-5.43</v>
+        <v>-4.01</v>
       </c>
       <c r="D44" s="6">
-        <v>-6.91</v>
+        <v>-2.84</v>
       </c>
       <c r="E44" s="7">
-        <v>-1.48</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>-0.11</v>
+        <v>0.37</v>
       </c>
       <c r="D45" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-2</v>
+        <v>-0.01</v>
+      </c>
+      <c r="E45" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-1.11</v>
+        <v>-1.89</v>
       </c>
       <c r="D46" s="6">
-        <v>-3.7</v>
+        <v>-0.03</v>
       </c>
       <c r="E46" s="7">
-        <v>-2.59</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>-6.32</v>
+        <v>-5.35</v>
       </c>
       <c r="D47" s="6">
-        <v>-6.67</v>
+        <v>-4.39</v>
       </c>
       <c r="E47" s="7">
-        <v>-0.35</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C48" s="6">
-        <v>-2.18</v>
+        <v>-0.2</v>
       </c>
       <c r="D48" s="6">
-        <v>-2.85</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-0.67</v>
+        <v>-1.05</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.85</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C49" s="6">
-        <v>-12.32</v>
+        <v>-2.15</v>
       </c>
       <c r="D49" s="6">
-        <v>-12.28</v>
-      </c>
-      <c r="E49" s="8">
-        <v>0.04</v>
+        <v>-0.16</v>
+      </c>
+      <c r="E49" s="7">
+        <v>1.99</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" s="6">
-        <v>-0.53</v>
+        <v>-6.91</v>
       </c>
       <c r="D50" s="6">
-        <v>-1.56</v>
+        <v>-5.96</v>
       </c>
       <c r="E50" s="7">
-        <v>-1.03</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C51" s="6">
-        <v>-20.87</v>
+        <v>-2.11</v>
       </c>
       <c r="D51" s="6">
-        <v>-21.27</v>
+        <v>-0.34</v>
       </c>
       <c r="E51" s="7">
-        <v>-0.4</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C52" s="6">
-        <v>-8.289999999999999</v>
+        <v>-3.7</v>
       </c>
       <c r="D52" s="6">
-        <v>-9.039999999999999</v>
+        <v>-3.16</v>
       </c>
       <c r="E52" s="7">
-        <v>-0.75</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-9.199999999999999</v>
+        <v>-6.67</v>
       </c>
       <c r="D53" s="6">
-        <v>-9.140000000000001</v>
-      </c>
-      <c r="E53" s="8">
-        <v>0.06</v>
+        <v>-6.51</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.16</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>1.35</v>
+        <v>-2.85</v>
       </c>
       <c r="D54" s="6">
-        <v>1.04</v>
+        <v>-2.3</v>
       </c>
       <c r="E54" s="7">
-        <v>-0.31</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>15.47</v>
+        <v>-12.28</v>
       </c>
       <c r="D55" s="6">
-        <v>13.46</v>
-      </c>
-      <c r="E55" s="7">
-        <v>-2.01</v>
+        <v>-12.51</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-8.44</v>
+        <v>-1.56</v>
       </c>
       <c r="D56" s="6">
-        <v>-9.119999999999999</v>
+        <v>-0.85</v>
       </c>
       <c r="E56" s="7">
-        <v>-0.68</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>7.05</v>
+        <v>-21.27</v>
       </c>
       <c r="D57" s="6">
-        <v>6.24</v>
-      </c>
-      <c r="E57" s="7">
-        <v>-0.8100000000000001</v>
+        <v>-21.82</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>15.27</v>
+        <v>-9.039999999999999</v>
       </c>
       <c r="D58" s="6">
-        <v>14.93</v>
-      </c>
-      <c r="E58" s="7">
-        <v>-0.34</v>
+        <v>-9.67</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>-10.41</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="D59" s="6">
-        <v>-11.71</v>
+        <v>-8.84</v>
       </c>
       <c r="E59" s="7">
-        <v>-1.3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>-9.02</v>
+        <v>-6.35</v>
       </c>
       <c r="D60" s="6">
-        <v>-8.98</v>
-      </c>
-      <c r="E60" s="8">
-        <v>0.04</v>
+        <v>-6.13</v>
+      </c>
+      <c r="E60" s="7">
+        <v>0.22</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>-3.33</v>
+        <v>1.04</v>
       </c>
       <c r="D61" s="6">
-        <v>-3.75</v>
+        <v>1.22</v>
       </c>
       <c r="E61" s="7">
-        <v>-0.42</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>-7.71</v>
+        <v>13.46</v>
       </c>
       <c r="D62" s="6">
-        <v>-8.26</v>
+        <v>14.81</v>
       </c>
       <c r="E62" s="7">
-        <v>-0.55</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>-9.300000000000001</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="D63" s="6">
-        <v>-10.58</v>
-      </c>
-      <c r="E63" s="7">
-        <v>-1.28</v>
+        <v>-9.25</v>
+      </c>
+      <c r="E63" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" s="6">
-        <v>-8.130000000000001</v>
+        <v>6.24</v>
       </c>
       <c r="D64" s="6">
-        <v>-8.359999999999999</v>
-      </c>
-      <c r="E64" s="7">
-        <v>-0.23</v>
+        <v>4.8</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" s="6">
-        <v>-10.63</v>
+        <v>14.93</v>
       </c>
       <c r="D65" s="6">
-        <v>-12.11</v>
+        <v>16.85</v>
       </c>
       <c r="E65" s="7">
-        <v>-1.48</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="6">
-        <v>-11.58</v>
+        <v>-11.71</v>
       </c>
       <c r="D66" s="6">
-        <v>-12.45</v>
-      </c>
-      <c r="E66" s="7">
-        <v>-0.87</v>
+        <v>-13.73</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-2.02</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C67" s="6">
-        <v>-8.35</v>
+        <v>-8.98</v>
       </c>
       <c r="D67" s="6">
-        <v>-9.289999999999999</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="E67" s="7">
-        <v>-0.9399999999999999</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C68" s="6">
-        <v>12.37</v>
+        <v>-3.75</v>
       </c>
       <c r="D68" s="6">
-        <v>12.13</v>
+        <v>-3.25</v>
       </c>
       <c r="E68" s="7">
-        <v>-0.24</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-7.78</v>
+        <v>-8.26</v>
       </c>
       <c r="D69" s="6">
-        <v>-8.83</v>
+        <v>-7.86</v>
       </c>
       <c r="E69" s="7">
-        <v>-1.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-8.369999999999999</v>
+        <v>-10.58</v>
       </c>
       <c r="D70" s="6">
-        <v>-8.779999999999999</v>
+        <v>-9.15</v>
       </c>
       <c r="E70" s="7">
-        <v>-0.41</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>4.14</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="D71" s="6">
-        <v>2.76</v>
+        <v>-7.69</v>
       </c>
       <c r="E71" s="7">
-        <v>-1.38</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-5.13</v>
+        <v>-12.11</v>
       </c>
       <c r="D72" s="6">
-        <v>-7.71</v>
+        <v>-10.83</v>
       </c>
       <c r="E72" s="7">
-        <v>-2.58</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>-9.1</v>
+        <v>-12.45</v>
       </c>
       <c r="D73" s="6">
-        <v>-10.59</v>
+        <v>-12.2</v>
       </c>
       <c r="E73" s="7">
-        <v>-1.49</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-1.48</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="D74" s="6">
-        <v>-3.71</v>
+        <v>-9.1</v>
       </c>
       <c r="E74" s="7">
-        <v>-2.23</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-0.6</v>
+        <v>12.13</v>
       </c>
       <c r="D75" s="6">
-        <v>-1.26</v>
+        <v>12.18</v>
       </c>
       <c r="E75" s="7">
-        <v>-0.66</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-12.54</v>
+        <v>-8.83</v>
       </c>
       <c r="D76" s="6">
-        <v>-14.62</v>
+        <v>-7.44</v>
       </c>
       <c r="E76" s="7">
-        <v>-2.08</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>-4.59</v>
+        <v>-8.779999999999999</v>
       </c>
       <c r="D77" s="6">
-        <v>-4.79</v>
+        <v>-7.64</v>
       </c>
       <c r="E77" s="7">
-        <v>-0.2</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>-5.11</v>
+        <v>2.76</v>
       </c>
       <c r="D78" s="6">
-        <v>-5.58</v>
-      </c>
-      <c r="E78" s="7">
-        <v>-0.47</v>
+        <v>2.41</v>
+      </c>
+      <c r="E78" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-6.71</v>
+        <v>-7.71</v>
       </c>
       <c r="D79" s="6">
-        <v>-8.789999999999999</v>
+        <v>-5.67</v>
       </c>
       <c r="E79" s="7">
-        <v>-2.08</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-7.09</v>
+        <v>-10.59</v>
       </c>
       <c r="D80" s="6">
-        <v>-6.72</v>
-      </c>
-      <c r="E80" s="8">
-        <v>0.37</v>
+        <v>-9.59</v>
+      </c>
+      <c r="E80" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-5.76</v>
+        <v>-3.71</v>
       </c>
       <c r="D81" s="6">
-        <v>-6.5</v>
+        <v>-3.44</v>
       </c>
       <c r="E81" s="7">
-        <v>-0.74</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-15.64</v>
+        <v>-1.26</v>
       </c>
       <c r="D82" s="6">
-        <v>-16.14</v>
+        <v>0.88</v>
       </c>
       <c r="E82" s="7">
-        <v>-0.5</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-15.1</v>
+        <v>-14.62</v>
       </c>
       <c r="D83" s="6">
-        <v>-16.29</v>
+        <v>-14.04</v>
       </c>
       <c r="E83" s="7">
-        <v>-1.19</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C84" s="6">
-        <v>-14.92</v>
+        <v>-4.79</v>
       </c>
       <c r="D84" s="6">
-        <v>-15.13</v>
+        <v>-4.06</v>
       </c>
       <c r="E84" s="7">
-        <v>-0.21</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C85" s="6">
-        <v>-15.49</v>
+        <v>-5.58</v>
       </c>
       <c r="D85" s="6">
-        <v>-16.89</v>
+        <v>-3.56</v>
       </c>
       <c r="E85" s="7">
-        <v>-1.4</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C86" s="6">
-        <v>-24.07</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="D86" s="6">
-        <v>-24.82</v>
+        <v>-7.4</v>
       </c>
       <c r="E86" s="7">
-        <v>-0.75</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C87" s="6">
-        <v>-13.37</v>
+        <v>-6.72</v>
       </c>
       <c r="D87" s="6">
-        <v>-14.26</v>
+        <v>-5.02</v>
       </c>
       <c r="E87" s="7">
-        <v>-0.89</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C88" s="6">
-        <v>-18.76</v>
+        <v>-6.5</v>
       </c>
       <c r="D88" s="6">
-        <v>-18.97</v>
+        <v>-5.9</v>
       </c>
       <c r="E88" s="7">
-        <v>-0.21</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-11.49</v>
+        <v>-16.14</v>
       </c>
       <c r="D89" s="6">
-        <v>-12.88</v>
+        <v>-15.78</v>
       </c>
       <c r="E89" s="7">
-        <v>-1.39</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-12.02</v>
+        <v>-16.29</v>
       </c>
       <c r="D90" s="6">
-        <v>-12.41</v>
+        <v>-14.95</v>
       </c>
       <c r="E90" s="7">
-        <v>-0.39</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-3.87</v>
+        <v>-15.13</v>
       </c>
       <c r="D91" s="6">
-        <v>-5.15</v>
+        <v>-14.52</v>
       </c>
       <c r="E91" s="7">
-        <v>-1.28</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-14</v>
+        <v>-16.89</v>
       </c>
       <c r="D92" s="6">
-        <v>-16.33</v>
+        <v>-15.68</v>
       </c>
       <c r="E92" s="7">
-        <v>-2.33</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-16.09</v>
+        <v>-24.82</v>
       </c>
       <c r="D93" s="6">
-        <v>-17.47</v>
+        <v>-24.61</v>
       </c>
       <c r="E93" s="7">
-        <v>-1.38</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-16.42</v>
+        <v>-14.26</v>
       </c>
       <c r="D94" s="6">
-        <v>-18.31</v>
+        <v>-14.08</v>
       </c>
       <c r="E94" s="7">
-        <v>-1.89</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-5.85</v>
+        <v>-18.97</v>
       </c>
       <c r="D95" s="6">
-        <v>-6.83</v>
+        <v>-18.27</v>
       </c>
       <c r="E95" s="7">
-        <v>-0.98</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-17.05</v>
+        <v>-12.88</v>
       </c>
       <c r="D96" s="6">
-        <v>-19.03</v>
+        <v>-11.98</v>
       </c>
       <c r="E96" s="7">
-        <v>-1.98</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-12.03</v>
+        <v>-12.41</v>
       </c>
       <c r="D97" s="6">
-        <v>-12.22</v>
+        <v>-11.31</v>
       </c>
       <c r="E97" s="7">
-        <v>-0.19</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-8.42</v>
+        <v>-5.15</v>
       </c>
       <c r="D98" s="6">
-        <v>-9.18</v>
-      </c>
-      <c r="E98" s="7">
-        <v>-0.76</v>
+        <v>-5.47</v>
+      </c>
+      <c r="E98" s="8">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-12.09</v>
+        <v>-16.33</v>
       </c>
       <c r="D99" s="6">
-        <v>-14.38</v>
+        <v>-14.48</v>
       </c>
       <c r="E99" s="7">
-        <v>-2.29</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-8.119999999999999</v>
+        <v>-17.47</v>
       </c>
       <c r="D100" s="6">
-        <v>-8.69</v>
+        <v>-16.55</v>
       </c>
       <c r="E100" s="7">
-        <v>-0.57</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-7.95</v>
+        <v>-18.31</v>
       </c>
       <c r="D101" s="6">
-        <v>-8.67</v>
+        <v>-18.08</v>
       </c>
       <c r="E101" s="7">
-        <v>-0.72</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>25011.5</v>
+        <v>-6.83</v>
       </c>
       <c r="D102" s="6">
-        <v>24862.3</v>
+        <v>-5.19</v>
       </c>
       <c r="E102" s="7">
-        <v>-149.2</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C103" s="6">
-        <v>8917.6</v>
+        <v>-19.03</v>
       </c>
       <c r="D103" s="6">
-        <v>8792.299999999999</v>
+        <v>-18.47</v>
       </c>
       <c r="E103" s="7">
-        <v>-125.3</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C104" s="6">
-        <v>10753.25</v>
+        <v>-12.22</v>
       </c>
       <c r="D104" s="6">
-        <v>10726.75</v>
+        <v>-11.55</v>
       </c>
       <c r="E104" s="7">
-        <v>-26.5</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C105" s="6">
-        <v>35101.45</v>
+        <v>-9.18</v>
       </c>
       <c r="D105" s="6">
-        <v>34520.05</v>
+        <v>-7.57</v>
       </c>
       <c r="E105" s="7">
-        <v>-581.4</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C106" s="6">
-        <v>43105.45</v>
+        <v>-14.38</v>
       </c>
       <c r="D106" s="6">
-        <v>42680.7</v>
+        <v>-13.37</v>
       </c>
       <c r="E106" s="7">
-        <v>-424.75</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C107" s="6">
-        <v>24657.7</v>
+        <v>-8.69</v>
       </c>
       <c r="D107" s="6">
-        <v>24403</v>
+        <v>-7.46</v>
       </c>
       <c r="E107" s="7">
-        <v>-254.7</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C108" s="6">
-        <v>32081.25</v>
+        <v>-8.67</v>
       </c>
       <c r="D108" s="6">
-        <v>31995.5</v>
+        <v>-8.09</v>
       </c>
       <c r="E108" s="7">
-        <v>-85.75</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>14747.95</v>
+        <v>24862.3</v>
       </c>
       <c r="D109" s="6">
-        <v>14516.75</v>
+        <v>24970.75</v>
       </c>
       <c r="E109" s="7">
-        <v>-231.2</v>
+        <v>108.45</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>8592.1</v>
+        <v>8792.299999999999</v>
       </c>
       <c r="D110" s="6">
-        <v>8554.25</v>
+        <v>8932.700000000001</v>
       </c>
       <c r="E110" s="7">
-        <v>-37.85</v>
+        <v>140.4</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>1584.5</v>
+        <v>10726.75</v>
       </c>
       <c r="D111" s="6">
-        <v>1563.4</v>
+        <v>10804.45</v>
       </c>
       <c r="E111" s="7">
-        <v>-21.1</v>
+        <v>77.7</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>11798.35</v>
+        <v>34520.05</v>
       </c>
       <c r="D112" s="6">
-        <v>11478.2</v>
+        <v>35022.35</v>
       </c>
       <c r="E112" s="7">
-        <v>-320.15</v>
+        <v>502.3</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>9034.35</v>
+        <v>42680.7</v>
       </c>
       <c r="D113" s="6">
-        <v>8885.75</v>
+        <v>42800.75</v>
       </c>
       <c r="E113" s="7">
-        <v>-148.6</v>
+        <v>120.05</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>8257.4</v>
+        <v>24403</v>
       </c>
       <c r="D114" s="6">
-        <v>8070.7</v>
+        <v>24454.35</v>
       </c>
       <c r="E114" s="7">
-        <v>-186.7</v>
+        <v>51.35</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>25596.65</v>
+        <v>31995.5</v>
       </c>
       <c r="D115" s="6">
-        <v>25329.45</v>
+        <v>32273.05</v>
       </c>
       <c r="E115" s="7">
-        <v>-267.2</v>
+        <v>277.55</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>803.45</v>
+        <v>14516.75</v>
       </c>
       <c r="D116" s="6">
-        <v>784.35</v>
+        <v>14665.7</v>
       </c>
       <c r="E116" s="7">
-        <v>-19.1</v>
+        <v>148.95</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>29997.95</v>
+        <v>8554.25</v>
       </c>
       <c r="D117" s="6">
-        <v>29934.75</v>
+        <v>8661.200000000001</v>
       </c>
       <c r="E117" s="7">
-        <v>-63.2</v>
+        <v>106.95</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>15515.25</v>
+        <v>1563.4</v>
       </c>
       <c r="D118" s="6">
-        <v>15387</v>
-      </c>
-      <c r="E118" s="7">
-        <v>-128.25</v>
+        <v>1558.1</v>
+      </c>
+      <c r="E118" s="8">
+        <v>-5.3</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>8789.700000000001</v>
+        <v>11478.2</v>
       </c>
       <c r="D119" s="6">
-        <v>8561.200000000001</v>
+        <v>11731.55</v>
       </c>
       <c r="E119" s="7">
-        <v>-228.5</v>
+        <v>253.35</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>10445.65</v>
+        <v>8885.75</v>
       </c>
       <c r="D120" s="6">
-        <v>10380.55</v>
+        <v>8984.950000000001</v>
       </c>
       <c r="E120" s="7">
-        <v>-65.09999999999999</v>
+        <v>99.2</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>26866.05</v>
+        <v>8070.7</v>
       </c>
       <c r="D121" s="6">
-        <v>26656.3</v>
+        <v>8093.8</v>
       </c>
       <c r="E121" s="7">
-        <v>-209.75</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>35</v>
+        <v>25329.45</v>
       </c>
       <c r="D122" s="6">
-        <v>40</v>
-      </c>
-      <c r="E122" s="8">
-        <v>5</v>
+        <v>25774.25</v>
+      </c>
+      <c r="E122" s="7">
+        <v>444.8</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C123" s="6">
-        <v>60</v>
+        <v>784.35</v>
       </c>
       <c r="D123" s="6">
-        <v>55</v>
+        <v>789.7</v>
       </c>
       <c r="E123" s="7">
-        <v>-5</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C124" s="6">
-        <v>65</v>
+        <v>29934.75</v>
       </c>
       <c r="D124" s="6">
-        <v>45</v>
+        <v>30162.5</v>
       </c>
       <c r="E124" s="7">
-        <v>-20</v>
+        <v>227.75</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C125" s="6">
-        <v>30</v>
+        <v>15387</v>
       </c>
       <c r="D125" s="6">
-        <v>35</v>
-      </c>
-      <c r="E125" s="8">
-        <v>5</v>
+        <v>15658.7</v>
+      </c>
+      <c r="E125" s="7">
+        <v>271.7</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C126" s="6">
-        <v>25</v>
+        <v>8561.200000000001</v>
       </c>
       <c r="D126" s="6">
-        <v>30</v>
-      </c>
-      <c r="E126" s="8">
-        <v>5</v>
+        <v>8661.950000000001</v>
+      </c>
+      <c r="E126" s="7">
+        <v>100.75</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C127" s="6">
-        <v>40</v>
+        <v>10380.55</v>
       </c>
       <c r="D127" s="6">
-        <v>50</v>
-      </c>
-      <c r="E127" s="8">
-        <v>10</v>
+        <v>10520.95</v>
+      </c>
+      <c r="E127" s="7">
+        <v>140.4</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C128" s="6">
-        <v>85</v>
+        <v>26656.3</v>
       </c>
       <c r="D128" s="6">
-        <v>80</v>
+        <v>26825.3</v>
       </c>
       <c r="E128" s="7">
-        <v>-5</v>
+        <v>169</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="D129" s="6">
-        <v>85</v>
-      </c>
-      <c r="E129" s="8">
+        <v>50</v>
+      </c>
+      <c r="E129" s="7">
         <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C130" s="6">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="D130" s="6">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E130" s="8">
-        <v>5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="6">
+        <v>50</v>
+      </c>
+      <c r="D131" s="6">
         <v>45</v>
       </c>
-      <c r="D131" s="6">
-        <v>25</v>
-      </c>
-      <c r="E131" s="7">
-        <v>-20</v>
+      <c r="E131" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C132" s="6">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D132" s="6">
-        <v>65</v>
-      </c>
-      <c r="E132" s="8">
-        <v>15</v>
+        <v>85</v>
+      </c>
+      <c r="E132" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C133" s="6">
-        <v>35.69</v>
+        <v>85</v>
       </c>
       <c r="D133" s="6">
-        <v>34.24</v>
-      </c>
-      <c r="E133" s="7">
-        <v>-1.45</v>
+        <v>80</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C134" s="6">
-        <v>33.85</v>
+        <v>70</v>
       </c>
       <c r="D134" s="6">
-        <v>29.83</v>
-      </c>
-      <c r="E134" s="7">
-        <v>-4.02</v>
+        <v>60</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C135" s="6">
-        <v>35.11</v>
+        <v>60</v>
       </c>
       <c r="D135" s="6">
-        <v>34.38</v>
+        <v>70</v>
       </c>
       <c r="E135" s="7">
-        <v>-0.73</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="B136" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" s="6">
         <v>25</v>
       </c>
-      <c r="C136" s="6">
-        <v>28.95</v>
-      </c>
       <c r="D136" s="6">
-        <v>24.86</v>
+        <v>35</v>
       </c>
       <c r="E136" s="7">
-        <v>-4.09</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>35.79</v>
+        <v>34.24</v>
       </c>
       <c r="D137" s="6">
-        <v>33.56</v>
+        <v>36.27</v>
       </c>
       <c r="E137" s="7">
-        <v>-2.23</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>41.05</v>
+        <v>29.83</v>
       </c>
       <c r="D138" s="6">
-        <v>37.43</v>
+        <v>38.62</v>
       </c>
       <c r="E138" s="7">
-        <v>-3.62</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>69.01000000000001</v>
+        <v>34.38</v>
       </c>
       <c r="D139" s="6">
-        <v>68.04000000000001</v>
+        <v>38.43</v>
       </c>
       <c r="E139" s="7">
-        <v>-0.97</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>29.94</v>
+        <v>24.86</v>
       </c>
       <c r="D140" s="6">
-        <v>26.1</v>
+        <v>33.59</v>
       </c>
       <c r="E140" s="7">
-        <v>-3.84</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>38.87</v>
+        <v>33.56</v>
       </c>
       <c r="D141" s="6">
-        <v>37.21</v>
+        <v>34.8</v>
       </c>
       <c r="E141" s="7">
-        <v>-1.66</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>49.65</v>
+        <v>37.43</v>
       </c>
       <c r="D142" s="6">
-        <v>46.1</v>
+        <v>38.61</v>
       </c>
       <c r="E142" s="7">
-        <v>-3.55</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>32.85</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="D143" s="6">
-        <v>27.83</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="E143" s="7">
-        <v>-5.02</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>32.63</v>
+        <v>26.1</v>
       </c>
       <c r="D144" s="6">
-        <v>27.76</v>
+        <v>32.14</v>
       </c>
       <c r="E144" s="7">
-        <v>-4.87</v>
+        <v>6.04</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>52.99</v>
+        <v>37.21</v>
       </c>
       <c r="D145" s="6">
-        <v>44.57</v>
+        <v>44.43</v>
       </c>
       <c r="E145" s="7">
-        <v>-8.42</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>36.8</v>
+        <v>46.1</v>
       </c>
       <c r="D146" s="6">
-        <v>32.75</v>
-      </c>
-      <c r="E146" s="7">
-        <v>-4.05</v>
+        <v>45.23</v>
+      </c>
+      <c r="E146" s="8">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>37.41</v>
+        <v>27.83</v>
       </c>
       <c r="D147" s="6">
-        <v>32.51</v>
+        <v>36.14</v>
       </c>
       <c r="E147" s="7">
-        <v>-4.9</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>53.9</v>
+        <v>27.76</v>
       </c>
       <c r="D148" s="6">
-        <v>52.83</v>
+        <v>34.76</v>
       </c>
       <c r="E148" s="7">
-        <v>-1.07</v>
+        <v>7</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>31.07</v>
+        <v>44.57</v>
       </c>
       <c r="D149" s="6">
-        <v>28.39</v>
+        <v>45.72</v>
       </c>
       <c r="E149" s="7">
-        <v>-2.68</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>34.06</v>
+        <v>32.75</v>
       </c>
       <c r="D150" s="6">
-        <v>29.26</v>
+        <v>43.84</v>
       </c>
       <c r="E150" s="7">
-        <v>-4.8</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>39.38</v>
+        <v>32.51</v>
       </c>
       <c r="D151" s="6">
-        <v>36.85</v>
+        <v>35.08</v>
       </c>
       <c r="E151" s="7">
-        <v>-2.53</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C152" s="6">
-        <v>44.26</v>
+        <v>52.83</v>
       </c>
       <c r="D152" s="6">
+        <v>56.21</v>
+      </c>
+      <c r="E152" s="7">
+        <v>3.38</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
+      <c r="A153" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C153" s="6">
+        <v>28.39</v>
+      </c>
+      <c r="D153" s="6">
+        <v>40.16</v>
+      </c>
+      <c r="E153" s="7">
+        <v>11.77</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
+      <c r="A154" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C154" s="6">
+        <v>29.26</v>
+      </c>
+      <c r="D154" s="6">
+        <v>33.7</v>
+      </c>
+      <c r="E154" s="7">
+        <v>4.44</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C155" s="6">
+        <v>36.85</v>
+      </c>
+      <c r="D155" s="6">
+        <v>45.05</v>
+      </c>
+      <c r="E155" s="7">
+        <v>8.199999999999999</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C156" s="6">
         <v>41.01</v>
       </c>
-      <c r="E152" s="7">
-        <v>-3.25</v>
+      <c r="D156" s="6">
+        <v>44.54</v>
+      </c>
+      <c r="E156" s="7">
+        <v>3.53</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A11:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5903,28 +6040,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5938,16 +6075,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>36.3</v>
+        <v>41.3</v>
       </c>
       <c r="E2" s="11">
         <v>18.8</v>
       </c>
       <c r="F2" s="11">
-        <v>-5.3</v>
+        <v>-4.9</v>
       </c>
       <c r="G2" s="11">
-        <v>-6.7</v>
+        <v>-5.8</v>
       </c>
       <c r="H2" s="11">
         <v>52.4</v>
@@ -6087,42 +6224,42 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2314</v>
+        <v>0.2297</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1726</v>
+        <v>0.1687</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1652</v>
+        <v>0.1656</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1513</v>
+        <v>0.1501</v>
       </c>
       <c r="E2" s="14">
-        <v>0.127</v>
+        <v>0.1303</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1092</v>
+        <v>0.1088</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0959</v>
+        <v>0.0895</v>
       </c>
       <c r="H2" s="14">
-        <v>0.08929999999999999</v>
+        <v>0.08789999999999999</v>
       </c>
       <c r="I2" s="14">
-        <v>0.08789999999999999</v>
+        <v>0.08710000000000001</v>
       </c>
       <c r="J2" s="14">
-        <v>0.0741</v>
+        <v>0.07519999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>43</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>57</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>53</v>
@@ -6131,10 +6268,10 @@
         <v>42</v>
       </c>
       <c r="E3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="13" t="s">
         <v>44</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="G3" s="13" t="s">
         <v>47</v>
@@ -6151,34 +6288,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0453</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0449</v>
+        <v>0.0447</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0318</v>
+        <v>0.0326</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0209</v>
+        <v>0.0197</v>
       </c>
       <c r="E4" s="14">
-        <v>-0.0178</v>
+        <v>0.0186</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.0288</v>
+        <v>-0.017</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0725</v>
+        <v>-0.07780000000000001</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.127</v>
+        <v>-0.0965</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1498</v>
+        <v>-0.1154</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.1884</v>
+        <v>-0.162</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="110">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,70 +289,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Oversold Recovery</t>
-  </si>
-  <si>
-    <t>29.8 → 38.6</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.2 → 55.1</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>29.8</t>
-  </si>
-  <si>
-    <t>38.6</t>
-  </si>
-  <si>
-    <t>24.9 → 33.6</t>
-  </si>
-  <si>
-    <t>24.9</t>
-  </si>
-  <si>
-    <t>33.6</t>
-  </si>
-  <si>
-    <t>26.1 → 32.1</t>
-  </si>
-  <si>
-    <t>26.1</t>
-  </si>
-  <si>
-    <t>32.1</t>
-  </si>
-  <si>
-    <t>27.8 → 36.1</t>
-  </si>
-  <si>
-    <t>27.8</t>
-  </si>
-  <si>
-    <t>36.1</t>
-  </si>
-  <si>
-    <t>27.8 → 34.8</t>
-  </si>
-  <si>
-    <t>34.8</t>
-  </si>
-  <si>
-    <t>28.4 → 40.2</t>
-  </si>
-  <si>
-    <t>28.4</t>
-  </si>
-  <si>
-    <t>40.2</t>
-  </si>
-  <si>
-    <t>29.3 → 33.7</t>
-  </si>
-  <si>
-    <t>29.3</t>
-  </si>
-  <si>
-    <t>33.7</t>
+    <t>45.2</t>
+  </si>
+  <si>
+    <t>55.1</t>
+  </si>
+  <si>
+    <t>43.8 → 53.1</t>
+  </si>
+  <si>
+    <t>43.8</t>
+  </si>
+  <si>
+    <t>53.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1082,10 +1040,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>24970.75</v>
+        <v>25340.8</v>
       </c>
       <c r="E2">
-        <v>0.44</v>
+        <v>1.48</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1094,43 +1052,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-15.78</v>
+        <v>-14.53</v>
       </c>
       <c r="I2">
-        <v>5.05</v>
+        <v>6.61</v>
       </c>
       <c r="J2">
-        <v>-3.1</v>
+        <v>-0.98</v>
       </c>
       <c r="K2">
-        <v>-8.050000000000001</v>
+        <v>-5.2</v>
       </c>
       <c r="L2">
-        <v>-7.86</v>
+        <v>-6.49</v>
       </c>
       <c r="M2">
-        <v>-6.51</v>
+        <v>-6.31</v>
       </c>
       <c r="N2">
-        <v>16.87</v>
+        <v>17.34</v>
       </c>
       <c r="O2">
         <v>40</v>
       </c>
       <c r="Q2">
-        <v>25126.49</v>
+        <v>25076.4</v>
       </c>
       <c r="R2">
-        <v>25471.55</v>
+        <v>25390.19</v>
       </c>
       <c r="S2">
-        <v>27084.31</v>
+        <v>27003.28</v>
       </c>
       <c r="T2">
-        <v>26890.62</v>
+        <v>26876.38</v>
       </c>
       <c r="U2">
-        <v>-7.14</v>
+        <v>-5.71</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1145,31 +1103,31 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>36.27</v>
+        <v>42.77</v>
       </c>
       <c r="AA2">
-        <v>-539.25</v>
+        <v>-495.24</v>
       </c>
       <c r="AB2">
-        <v>-586.9299999999999</v>
+        <v>-568.59</v>
       </c>
       <c r="AC2">
-        <v>47.68</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="AD2">
-        <v>66.28</v>
+        <v>75.69</v>
       </c>
       <c r="AE2">
-        <v>70.73999999999999</v>
+        <v>69.97</v>
       </c>
       <c r="AF2">
-        <v>467.31</v>
+        <v>462.83</v>
       </c>
       <c r="AH2">
-        <v>26703.99</v>
+        <v>26401.76</v>
       </c>
       <c r="AI2">
-        <v>24239.1</v>
+        <v>24378.62</v>
       </c>
       <c r="AJ2">
         <v>26008.9</v>
@@ -1178,7 +1136,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>54.05</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1192,10 +1150,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>8932.700000000001</v>
+        <v>8978.65</v>
       </c>
       <c r="E3">
-        <v>1.6</v>
+        <v>0.51</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1204,43 +1162,43 @@
         <v>8792.299999999999</v>
       </c>
       <c r="H3">
-        <v>-14.95</v>
+        <v>-14.52</v>
       </c>
       <c r="I3">
-        <v>1.6</v>
+        <v>2.12</v>
       </c>
       <c r="J3">
-        <v>-1.83</v>
+        <v>-0.68</v>
       </c>
       <c r="K3">
-        <v>-7.4</v>
+        <v>-5.64</v>
       </c>
       <c r="L3">
-        <v>-9.15</v>
+        <v>-8.68</v>
       </c>
       <c r="M3">
-        <v>-2.3</v>
+        <v>-2.53</v>
       </c>
       <c r="N3">
-        <v>8.710000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="O3">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Q3">
-        <v>8926.75</v>
+        <v>8914.51</v>
       </c>
       <c r="R3">
-        <v>9081.200000000001</v>
+        <v>9053.09</v>
       </c>
       <c r="S3">
-        <v>9456.09</v>
+        <v>9438.1</v>
       </c>
       <c r="T3">
-        <v>9754.83</v>
+        <v>9752.15</v>
       </c>
       <c r="U3">
-        <v>-8.43</v>
+        <v>-7.93</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1255,31 +1213,31 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>38.62</v>
+        <v>41.22</v>
       </c>
       <c r="AA3">
-        <v>-163.46</v>
+        <v>-152.68</v>
       </c>
       <c r="AB3">
-        <v>-166.95</v>
+        <v>-164.09</v>
       </c>
       <c r="AC3">
-        <v>3.49</v>
+        <v>11.41</v>
       </c>
       <c r="AD3">
-        <v>62.18</v>
+        <v>75.27</v>
       </c>
       <c r="AE3">
-        <v>62.99</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="AF3">
-        <v>153.84</v>
+        <v>150.59</v>
       </c>
       <c r="AH3">
-        <v>9474.84</v>
+        <v>9383.83</v>
       </c>
       <c r="AI3">
-        <v>8687.549999999999</v>
+        <v>8722.360000000001</v>
       </c>
       <c r="AJ3">
         <v>9225.639999999999</v>
@@ -1288,7 +1246,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>43.59</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1302,10 +1260,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>10804.45</v>
+        <v>10936.65</v>
       </c>
       <c r="E4">
-        <v>0.72</v>
+        <v>1.22</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1314,43 +1272,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-14.52</v>
+        <v>-13.47</v>
       </c>
       <c r="I4">
-        <v>4.55</v>
+        <v>5.83</v>
       </c>
       <c r="J4">
-        <v>-2.26</v>
+        <v>-0.02</v>
       </c>
       <c r="K4">
-        <v>-6.42</v>
+        <v>-3.67</v>
       </c>
       <c r="L4">
-        <v>-7.69</v>
+        <v>-6.56</v>
       </c>
       <c r="M4">
-        <v>-12.51</v>
+        <v>-12.39</v>
       </c>
       <c r="N4">
-        <v>8.789999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="O4">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Q4">
-        <v>10811.27</v>
+        <v>10810.88</v>
       </c>
       <c r="R4">
-        <v>10960.71</v>
+        <v>10936.77</v>
       </c>
       <c r="S4">
-        <v>11423.62</v>
+        <v>11399.59</v>
       </c>
       <c r="T4">
-        <v>11482.01</v>
+        <v>11475.24</v>
       </c>
       <c r="U4">
-        <v>-5.9</v>
+        <v>-4.69</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1365,31 +1323,31 @@
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>38.43</v>
+        <v>44.7</v>
       </c>
       <c r="AA4">
-        <v>-171.13</v>
+        <v>-154.89</v>
       </c>
       <c r="AB4">
-        <v>-177.87</v>
+        <v>-173.27</v>
       </c>
       <c r="AC4">
-        <v>6.74</v>
+        <v>18.39</v>
       </c>
       <c r="AD4">
-        <v>56.02</v>
+        <v>69.8</v>
       </c>
       <c r="AE4">
-        <v>60.97</v>
+        <v>60.88</v>
       </c>
       <c r="AF4">
-        <v>159.66</v>
+        <v>158.95</v>
       </c>
       <c r="AH4">
-        <v>11315.78</v>
+        <v>11220.07</v>
       </c>
       <c r="AI4">
-        <v>10605.64</v>
+        <v>10653.47</v>
       </c>
       <c r="AJ4">
         <v>11143.46</v>
@@ -1398,7 +1356,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>52.67</v>
+        <v>48.72</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1412,10 +1370,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>35022.35</v>
+        <v>35261.85</v>
       </c>
       <c r="E5">
-        <v>1.46</v>
+        <v>0.68</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1424,43 +1382,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-15.68</v>
+        <v>-15.1</v>
       </c>
       <c r="I5">
-        <v>5.81</v>
+        <v>6.54</v>
       </c>
       <c r="J5">
-        <v>-3.23</v>
+        <v>-1.98</v>
       </c>
       <c r="K5">
-        <v>-7.25</v>
+        <v>-5.62</v>
       </c>
       <c r="L5">
-        <v>-10.83</v>
+        <v>-10.22</v>
       </c>
       <c r="M5">
-        <v>-0.85</v>
+        <v>-0.58</v>
       </c>
       <c r="N5">
-        <v>7.52</v>
+        <v>7.83</v>
       </c>
       <c r="O5">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Q5">
-        <v>35218.61</v>
+        <v>35076.09</v>
       </c>
       <c r="R5">
-        <v>36106.56</v>
+        <v>35997.64</v>
       </c>
       <c r="S5">
-        <v>37251.88</v>
+        <v>37183.32</v>
       </c>
       <c r="T5">
-        <v>37738.18</v>
+        <v>37737.86</v>
       </c>
       <c r="U5">
-        <v>-7.2</v>
+        <v>-6.56</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1475,31 +1433,31 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>33.59</v>
+        <v>37.32</v>
       </c>
       <c r="AA5">
-        <v>-637.5599999999999</v>
+        <v>-622.53</v>
       </c>
       <c r="AB5">
-        <v>-542.08</v>
+        <v>-558.17</v>
       </c>
       <c r="AC5">
-        <v>-95.48</v>
+        <v>-64.36</v>
       </c>
       <c r="AD5">
-        <v>19.27</v>
+        <v>38.46</v>
       </c>
       <c r="AE5">
-        <v>22.23</v>
+        <v>23.72</v>
       </c>
       <c r="AF5">
-        <v>598.96</v>
+        <v>585.61</v>
       </c>
       <c r="AH5">
-        <v>37525.05</v>
+        <v>37315.91</v>
       </c>
       <c r="AI5">
-        <v>34688.08</v>
+        <v>34679.37</v>
       </c>
       <c r="AJ5">
         <v>36227.11</v>
@@ -1508,7 +1466,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>47.65</v>
+        <v>47.85</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1522,10 +1480,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>42800.75</v>
+        <v>43118.2</v>
       </c>
       <c r="E6">
-        <v>0.28</v>
+        <v>0.74</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1534,43 +1492,43 @@
         <v>42680.7</v>
       </c>
       <c r="H6">
-        <v>-24.61</v>
+        <v>-24.05</v>
       </c>
       <c r="I6">
-        <v>0.28</v>
+        <v>1.03</v>
       </c>
       <c r="J6">
-        <v>-4.07</v>
+        <v>-1.95</v>
       </c>
       <c r="K6">
-        <v>-7.48</v>
+        <v>-5.77</v>
       </c>
       <c r="L6">
-        <v>-12.2</v>
+        <v>-11.55</v>
       </c>
       <c r="M6">
-        <v>-21.82</v>
+        <v>-22.8</v>
       </c>
       <c r="N6">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="O6">
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>43256.62</v>
+        <v>43085.16</v>
       </c>
       <c r="R6">
-        <v>44372.48</v>
+        <v>44231.32</v>
       </c>
       <c r="S6">
-        <v>45654.87</v>
+        <v>45540.48</v>
       </c>
       <c r="T6">
-        <v>48863.94</v>
+        <v>48802.15</v>
       </c>
       <c r="U6">
-        <v>-12.41</v>
+        <v>-11.65</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1585,31 +1543,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>34.8</v>
+        <v>38.09</v>
       </c>
       <c r="AA6">
-        <v>-711.3099999999999</v>
+        <v>-717.91</v>
       </c>
       <c r="AB6">
-        <v>-577.88</v>
+        <v>-605.88</v>
       </c>
       <c r="AC6">
-        <v>-133.44</v>
+        <v>-112.02</v>
       </c>
       <c r="AD6">
-        <v>14.42</v>
+        <v>12.06</v>
       </c>
       <c r="AE6">
-        <v>30.85</v>
+        <v>18.55</v>
       </c>
       <c r="AF6">
-        <v>752.13</v>
+        <v>745.9299999999999</v>
       </c>
       <c r="AH6">
-        <v>46085.33</v>
+        <v>45863.2</v>
       </c>
       <c r="AI6">
-        <v>42659.63</v>
+        <v>42599.45</v>
       </c>
       <c r="AJ6">
         <v>44659.77</v>
@@ -1618,7 +1576,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>39.45</v>
+        <v>40.08</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1632,10 +1590,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>24454.35</v>
+        <v>24303.75</v>
       </c>
       <c r="E7">
-        <v>0.21</v>
+        <v>-0.62</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1644,43 +1602,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-14.08</v>
+        <v>-14.61</v>
       </c>
       <c r="I7">
-        <v>3.96</v>
+        <v>3.32</v>
       </c>
       <c r="J7">
-        <v>-3.67</v>
+        <v>-2.73</v>
       </c>
       <c r="K7">
-        <v>-4.34</v>
+        <v>-2.61</v>
       </c>
       <c r="L7">
-        <v>-9.1</v>
+        <v>-9.66</v>
       </c>
       <c r="M7">
-        <v>-9.67</v>
+        <v>-11.24</v>
       </c>
       <c r="N7">
-        <v>4.47</v>
+        <v>4.5</v>
       </c>
       <c r="O7">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="Q7">
-        <v>24638.72</v>
+        <v>24502.05</v>
       </c>
       <c r="R7">
-        <v>24836.84</v>
+        <v>24797.29</v>
       </c>
       <c r="S7">
-        <v>25443.42</v>
+        <v>25402.94</v>
       </c>
       <c r="T7">
-        <v>26223.3</v>
+        <v>26206.75</v>
       </c>
       <c r="U7">
-        <v>-6.75</v>
+        <v>-7.26</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1695,31 +1653,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>38.61</v>
+        <v>36.45</v>
       </c>
       <c r="AA7">
-        <v>-213.28</v>
+        <v>-237.38</v>
       </c>
       <c r="AB7">
-        <v>-196.78</v>
+        <v>-204.9</v>
       </c>
       <c r="AC7">
-        <v>-16.5</v>
+        <v>-32.48</v>
       </c>
       <c r="AD7">
-        <v>29.44</v>
+        <v>14.75</v>
       </c>
       <c r="AE7">
-        <v>42.14</v>
+        <v>28.31</v>
       </c>
       <c r="AF7">
-        <v>366.58</v>
+        <v>359.74</v>
       </c>
       <c r="AH7">
-        <v>25400.29</v>
+        <v>25394.53</v>
       </c>
       <c r="AI7">
-        <v>24273.4</v>
+        <v>24200.05</v>
       </c>
       <c r="AJ7">
         <v>25420.21</v>
@@ -1728,7 +1686,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>31.99</v>
+        <v>34.05</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1742,10 +1700,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>32273.05</v>
+        <v>32189.45</v>
       </c>
       <c r="E8">
-        <v>0.87</v>
+        <v>-0.26</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1754,43 +1712,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-18.27</v>
+        <v>-18.48</v>
       </c>
       <c r="I8">
-        <v>25.24</v>
+        <v>24.91</v>
       </c>
       <c r="J8">
-        <v>1.09</v>
+        <v>2.14</v>
       </c>
       <c r="K8">
-        <v>13.9</v>
+        <v>14.11</v>
       </c>
       <c r="L8">
-        <v>12.18</v>
+        <v>9.33</v>
       </c>
       <c r="M8">
-        <v>-8.84</v>
+        <v>-9.4</v>
       </c>
       <c r="N8">
-        <v>-1.7</v>
+        <v>-1.94</v>
       </c>
       <c r="O8">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Q8">
-        <v>32057.72</v>
+        <v>32192.35</v>
       </c>
       <c r="R8">
-        <v>29585.86</v>
+        <v>29787.28</v>
       </c>
       <c r="S8">
-        <v>29869.35</v>
+        <v>29884.07</v>
       </c>
       <c r="T8">
-        <v>30788.4</v>
+        <v>30758.49</v>
       </c>
       <c r="U8">
-        <v>4.82</v>
+        <v>4.65</v>
       </c>
       <c r="V8" t="s">
         <v>79</v>
@@ -1805,31 +1763,31 @@
         <v>1</v>
       </c>
       <c r="Z8">
-        <v>69.54000000000001</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="AA8">
-        <v>815.61</v>
+        <v>852.5599999999999</v>
       </c>
       <c r="AB8">
-        <v>391.7</v>
+        <v>483.87</v>
       </c>
       <c r="AC8">
-        <v>423.91</v>
+        <v>368.69</v>
       </c>
       <c r="AD8">
-        <v>88.58</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="AE8">
-        <v>90.77</v>
+        <v>89.38</v>
       </c>
       <c r="AF8">
-        <v>849.78</v>
+        <v>842.75</v>
       </c>
       <c r="AH8">
-        <v>33267.23</v>
+        <v>33579.56</v>
       </c>
       <c r="AI8">
-        <v>25904.48</v>
+        <v>25995.01</v>
       </c>
       <c r="AJ8">
         <v>29979.37</v>
@@ -1838,7 +1796,7 @@
         <v>82</v>
       </c>
       <c r="AL8">
-        <v>53.06</v>
+        <v>51.65</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1852,10 +1810,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>14665.7</v>
+        <v>14878.4</v>
       </c>
       <c r="E9">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1864,34 +1822,34 @@
         <v>14516.75</v>
       </c>
       <c r="H9">
-        <v>-11.98</v>
+        <v>-10.71</v>
       </c>
       <c r="I9">
-        <v>1.03</v>
+        <v>2.49</v>
       </c>
       <c r="J9">
-        <v>-3.35</v>
+        <v>-1.33</v>
       </c>
       <c r="K9">
-        <v>-8.44</v>
+        <v>-5.89</v>
       </c>
       <c r="L9">
-        <v>-7.44</v>
+        <v>-7.1</v>
       </c>
       <c r="N9">
-        <v>-16.2</v>
+        <v>-12.81</v>
       </c>
       <c r="O9">
         <v>30</v>
       </c>
       <c r="Q9">
-        <v>14770.1</v>
+        <v>14730.12</v>
       </c>
       <c r="R9">
-        <v>15139.42</v>
+        <v>15089.24</v>
       </c>
       <c r="S9">
-        <v>15809.23</v>
+        <v>15774.39</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1903,31 +1861,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>32.14</v>
+        <v>39.72</v>
       </c>
       <c r="AA9">
-        <v>-305.62</v>
+        <v>-288.4</v>
       </c>
       <c r="AB9">
-        <v>-280</v>
+        <v>-281.68</v>
       </c>
       <c r="AC9">
-        <v>-25.62</v>
+        <v>-6.72</v>
       </c>
       <c r="AD9">
-        <v>28.71</v>
+        <v>51.08</v>
       </c>
       <c r="AE9">
-        <v>36.74</v>
+        <v>35.83</v>
       </c>
       <c r="AF9">
-        <v>234.7</v>
+        <v>234.32</v>
       </c>
       <c r="AH9">
-        <v>15809.62</v>
+        <v>15669.64</v>
       </c>
       <c r="AI9">
-        <v>14469.21</v>
+        <v>14508.85</v>
       </c>
       <c r="AJ9">
         <v>15216.01</v>
@@ -1936,7 +1894,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>63.25</v>
+        <v>59.76</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1950,10 +1908,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8661.200000000001</v>
+        <v>8726.6</v>
       </c>
       <c r="E10">
-        <v>1.25</v>
+        <v>0.76</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1962,43 +1920,43 @@
         <v>8499.65</v>
       </c>
       <c r="H10">
-        <v>-11.31</v>
+        <v>-10.64</v>
       </c>
       <c r="I10">
-        <v>1.9</v>
+        <v>2.67</v>
       </c>
       <c r="J10">
-        <v>-0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K10">
-        <v>-4.77</v>
+        <v>-2.44</v>
       </c>
       <c r="L10">
-        <v>-7.64</v>
+        <v>-6.94</v>
       </c>
       <c r="M10">
-        <v>-6.13</v>
+        <v>-6.22</v>
       </c>
       <c r="N10">
-        <v>10.88</v>
+        <v>11.14</v>
       </c>
       <c r="O10">
         <v>45</v>
       </c>
       <c r="Q10">
-        <v>8621.610000000001</v>
+        <v>8633.629999999999</v>
       </c>
       <c r="R10">
-        <v>8664.629999999999</v>
+        <v>8653.09</v>
       </c>
       <c r="S10">
-        <v>8981.200000000001</v>
+        <v>8967.860000000001</v>
       </c>
       <c r="T10">
-        <v>9221.299999999999</v>
+        <v>9216.85</v>
       </c>
       <c r="U10">
-        <v>-6.07</v>
+        <v>-5.32</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -2013,31 +1971,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>44.43</v>
+        <v>48.34</v>
       </c>
       <c r="AA10">
-        <v>-103.79</v>
+        <v>-89.66</v>
       </c>
       <c r="AB10">
-        <v>-122.15</v>
+        <v>-115.65</v>
       </c>
       <c r="AC10">
-        <v>18.36</v>
+        <v>25.99</v>
       </c>
       <c r="AD10">
-        <v>74.5</v>
+        <v>83.61</v>
       </c>
       <c r="AE10">
-        <v>74.73</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="AF10">
-        <v>134.25</v>
+        <v>133.15</v>
       </c>
       <c r="AH10">
-        <v>8886.75</v>
+        <v>8830.66</v>
       </c>
       <c r="AI10">
-        <v>8442.5</v>
+        <v>8475.51</v>
       </c>
       <c r="AJ10">
         <v>8855.59</v>
@@ -2046,7 +2004,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>32.87</v>
+        <v>28.68</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2060,10 +2018,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1558.1</v>
+        <v>1615.05</v>
       </c>
       <c r="E11">
-        <v>-0.34</v>
+        <v>3.66</v>
       </c>
       <c r="F11">
         <v>1648.25</v>
@@ -2072,43 +2030,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-5.47</v>
+        <v>-2.01</v>
       </c>
       <c r="I11">
-        <v>24.31</v>
+        <v>28.86</v>
       </c>
       <c r="J11">
-        <v>-5.47</v>
+        <v>-1.75</v>
       </c>
       <c r="K11">
-        <v>-0.5600000000000001</v>
+        <v>3.91</v>
       </c>
       <c r="L11">
-        <v>2.41</v>
+        <v>6.15</v>
       </c>
       <c r="M11">
-        <v>1.22</v>
+        <v>4.62</v>
       </c>
       <c r="N11">
-        <v>-7.78</v>
+        <v>-6.73</v>
       </c>
       <c r="O11">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Q11">
-        <v>1594.51</v>
+        <v>1588.74</v>
       </c>
       <c r="R11">
-        <v>1584.53</v>
+        <v>1587.75</v>
       </c>
       <c r="S11">
-        <v>1574.09</v>
+        <v>1574.89</v>
       </c>
       <c r="T11">
-        <v>1469.91</v>
+        <v>1470.76</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>9.81</v>
       </c>
       <c r="V11" t="s">
         <v>80</v>
@@ -2123,31 +2081,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>45.23</v>
+        <v>55.08</v>
       </c>
       <c r="AA11">
-        <v>9.029999999999999</v>
+        <v>10.16</v>
       </c>
       <c r="AB11">
-        <v>13.43</v>
+        <v>12.77</v>
       </c>
       <c r="AC11">
-        <v>-4.4</v>
+        <v>-2.61</v>
       </c>
       <c r="AD11">
-        <v>8.609999999999999</v>
+        <v>18.77</v>
       </c>
       <c r="AE11">
-        <v>32.11</v>
+        <v>18.99</v>
       </c>
       <c r="AF11">
-        <v>36.14</v>
+        <v>39.04</v>
       </c>
       <c r="AH11">
-        <v>1663.02</v>
+        <v>1665.67</v>
       </c>
       <c r="AI11">
-        <v>1506.05</v>
+        <v>1509.84</v>
       </c>
       <c r="AJ11">
         <v>1544.25</v>
@@ -2156,7 +2114,7 @@
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>28.1</v>
+        <v>25.12</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2170,10 +2128,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>11731.55</v>
+        <v>11806.7</v>
       </c>
       <c r="E12">
-        <v>2.21</v>
+        <v>0.64</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2182,43 +2140,43 @@
         <v>10017.9</v>
       </c>
       <c r="H12">
-        <v>-14.48</v>
+        <v>-13.93</v>
       </c>
       <c r="I12">
-        <v>17.11</v>
+        <v>17.86</v>
       </c>
       <c r="J12">
-        <v>-3.31</v>
+        <v>-2.15</v>
       </c>
       <c r="K12">
-        <v>-11.81</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L12">
-        <v>-5.67</v>
+        <v>-5.07</v>
       </c>
       <c r="M12">
-        <v>14.81</v>
+        <v>14.77</v>
       </c>
       <c r="N12">
-        <v>15.01</v>
+        <v>15.51</v>
       </c>
       <c r="O12">
         <v>85</v>
       </c>
       <c r="Q12">
-        <v>11786.81</v>
+        <v>11734.87</v>
       </c>
       <c r="R12">
-        <v>12226.22</v>
+        <v>12162.2</v>
       </c>
       <c r="S12">
-        <v>12773.7</v>
+        <v>12749.16</v>
       </c>
       <c r="T12">
-        <v>12481.38</v>
+        <v>12484.57</v>
       </c>
       <c r="U12">
-        <v>-6.01</v>
+        <v>-5.43</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2233,31 +2191,31 @@
         <v>1</v>
       </c>
       <c r="Z12">
-        <v>36.14</v>
+        <v>38.41</v>
       </c>
       <c r="AA12">
-        <v>-313.8</v>
+        <v>-303.39</v>
       </c>
       <c r="AB12">
-        <v>-275.62</v>
+        <v>-281.17</v>
       </c>
       <c r="AC12">
-        <v>-38.19</v>
+        <v>-22.22</v>
       </c>
       <c r="AD12">
-        <v>30.64</v>
+        <v>51.64</v>
       </c>
       <c r="AE12">
-        <v>29.73</v>
+        <v>34.55</v>
       </c>
       <c r="AF12">
-        <v>265.71</v>
+        <v>260.15</v>
       </c>
       <c r="AH12">
-        <v>13114.28</v>
+        <v>12969.91</v>
       </c>
       <c r="AI12">
-        <v>11338.16</v>
+        <v>11354.48</v>
       </c>
       <c r="AJ12">
         <v>12304.47</v>
@@ -2266,7 +2224,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>56.49</v>
+        <v>55.08</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2280,10 +2238,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>8984.950000000001</v>
+        <v>9048.6</v>
       </c>
       <c r="E13">
-        <v>1.12</v>
+        <v>0.71</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2292,43 +2250,43 @@
         <v>8885.75</v>
       </c>
       <c r="H13">
-        <v>-16.55</v>
+        <v>-15.95</v>
       </c>
       <c r="I13">
-        <v>1.12</v>
+        <v>1.83</v>
       </c>
       <c r="J13">
-        <v>-2.84</v>
+        <v>-1.55</v>
       </c>
       <c r="K13">
-        <v>-6.77</v>
+        <v>-5.3</v>
       </c>
       <c r="L13">
-        <v>-9.59</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="M13">
-        <v>-9.25</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="N13">
-        <v>16.56</v>
+        <v>16.93</v>
       </c>
       <c r="O13">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="Q13">
-        <v>9038.01</v>
+        <v>9009.610000000001</v>
       </c>
       <c r="R13">
-        <v>9204.85</v>
+        <v>9178.629999999999</v>
       </c>
       <c r="S13">
-        <v>9500.809999999999</v>
+        <v>9483.889999999999</v>
       </c>
       <c r="T13">
-        <v>9978.1</v>
+        <v>9974.07</v>
       </c>
       <c r="U13">
-        <v>-9.949999999999999</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2343,31 +2301,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>34.76</v>
+        <v>38.86</v>
       </c>
       <c r="AA13">
-        <v>-143.79</v>
+        <v>-138.98</v>
       </c>
       <c r="AB13">
-        <v>-131.76</v>
+        <v>-133.2</v>
       </c>
       <c r="AC13">
-        <v>-12.03</v>
+        <v>-5.78</v>
       </c>
       <c r="AD13">
-        <v>39.36</v>
+        <v>49.48</v>
       </c>
       <c r="AE13">
-        <v>46.89</v>
+        <v>43.09</v>
       </c>
       <c r="AF13">
-        <v>144.59</v>
+        <v>140.87</v>
       </c>
       <c r="AH13">
-        <v>9531.74</v>
+        <v>9462.52</v>
       </c>
       <c r="AI13">
-        <v>8877.959999999999</v>
+        <v>8894.75</v>
       </c>
       <c r="AJ13">
         <v>9317.65</v>
@@ -2376,7 +2334,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>56.58</v>
+        <v>55.09</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2390,10 +2348,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8093.8</v>
+        <v>8126.7</v>
       </c>
       <c r="E14">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2402,43 +2360,43 @@
         <v>7638.75</v>
       </c>
       <c r="H14">
-        <v>-18.08</v>
+        <v>-17.74</v>
       </c>
       <c r="I14">
-        <v>5.96</v>
+        <v>6.39</v>
       </c>
       <c r="J14">
-        <v>-0.01</v>
+        <v>-2.02</v>
       </c>
       <c r="K14">
-        <v>-3.25</v>
+        <v>-1.75</v>
       </c>
       <c r="L14">
-        <v>-3.44</v>
+        <v>-3.04</v>
       </c>
       <c r="M14">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="N14">
-        <v>22.97</v>
+        <v>22.57</v>
       </c>
       <c r="O14">
         <v>80</v>
       </c>
       <c r="Q14">
-        <v>8193.5</v>
+        <v>8160.02</v>
       </c>
       <c r="R14">
-        <v>8096.49</v>
+        <v>8088.11</v>
       </c>
       <c r="S14">
-        <v>8330.52</v>
+        <v>8317.27</v>
       </c>
       <c r="T14">
-        <v>8569.17</v>
+        <v>8567.139999999999</v>
       </c>
       <c r="U14">
-        <v>-5.55</v>
+        <v>-5.14</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2453,31 +2411,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>45.72</v>
+        <v>47.39</v>
       </c>
       <c r="AA14">
-        <v>-37.39</v>
+        <v>-35.78</v>
       </c>
       <c r="AB14">
-        <v>-57.32</v>
+        <v>-53.01</v>
       </c>
       <c r="AC14">
-        <v>19.93</v>
+        <v>17.24</v>
       </c>
       <c r="AD14">
-        <v>64.34</v>
+        <v>52.88</v>
       </c>
       <c r="AE14">
-        <v>78.77</v>
+        <v>64.8</v>
       </c>
       <c r="AF14">
-        <v>157.01</v>
+        <v>153.41</v>
       </c>
       <c r="AH14">
-        <v>8312.290000000001</v>
+        <v>8283.58</v>
       </c>
       <c r="AI14">
-        <v>7880.7</v>
+        <v>7892.63</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
@@ -2486,7 +2444,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>21.64</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2500,10 +2458,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>25774.25</v>
+        <v>26267.25</v>
       </c>
       <c r="E15">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2512,43 +2470,43 @@
         <v>21549.55</v>
       </c>
       <c r="H15">
-        <v>-5.19</v>
+        <v>-3.38</v>
       </c>
       <c r="I15">
-        <v>19.6</v>
+        <v>21.89</v>
       </c>
       <c r="J15">
-        <v>-0.03</v>
+        <v>2.55</v>
       </c>
       <c r="K15">
-        <v>-5.07</v>
+        <v>-2.82</v>
       </c>
       <c r="L15">
-        <v>0.88</v>
+        <v>1.24</v>
       </c>
       <c r="M15">
-        <v>16.85</v>
+        <v>18.84</v>
       </c>
       <c r="N15">
-        <v>13.03</v>
+        <v>13.26</v>
       </c>
       <c r="O15">
         <v>99</v>
       </c>
       <c r="Q15">
-        <v>25576.25</v>
+        <v>25706.7</v>
       </c>
       <c r="R15">
-        <v>26085.4</v>
+        <v>26048.61</v>
       </c>
       <c r="S15">
-        <v>26421.52</v>
+        <v>26413.13</v>
       </c>
       <c r="T15">
-        <v>24397.42</v>
+        <v>24415.13</v>
       </c>
       <c r="U15">
-        <v>5.64</v>
+        <v>7.59</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2563,31 +2521,31 @@
         <v>2</v>
       </c>
       <c r="Z15">
-        <v>43.84</v>
+        <v>53.07</v>
       </c>
       <c r="AA15">
-        <v>-268.48</v>
+        <v>-211.57</v>
       </c>
       <c r="AB15">
-        <v>-218.85</v>
+        <v>-217.39</v>
       </c>
       <c r="AC15">
-        <v>-49.63</v>
+        <v>5.82</v>
       </c>
       <c r="AD15">
-        <v>25.09</v>
+        <v>56.24</v>
       </c>
       <c r="AE15">
-        <v>9.82</v>
+        <v>27.84</v>
       </c>
       <c r="AF15">
-        <v>416.44</v>
+        <v>425.24</v>
       </c>
       <c r="AH15">
-        <v>27037.05</v>
+        <v>26902.8</v>
       </c>
       <c r="AI15">
-        <v>25133.74</v>
+        <v>25194.42</v>
       </c>
       <c r="AJ15">
         <v>26568.83</v>
@@ -2596,7 +2554,7 @@
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>47.73</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2610,10 +2568,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>789.7</v>
+        <v>805.05</v>
       </c>
       <c r="E16">
-        <v>0.68</v>
+        <v>1.94</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2622,43 +2580,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-18.47</v>
+        <v>-16.89</v>
       </c>
       <c r="I16">
-        <v>21.28</v>
+        <v>23.64</v>
       </c>
       <c r="J16">
-        <v>-4.39</v>
+        <v>-1.35</v>
       </c>
       <c r="K16">
-        <v>-9.33</v>
+        <v>-6.54</v>
       </c>
       <c r="L16">
-        <v>-14.04</v>
+        <v>-12.37</v>
       </c>
       <c r="M16">
-        <v>-13.73</v>
+        <v>-13.7</v>
       </c>
       <c r="N16">
-        <v>8.949999999999999</v>
+        <v>9.31</v>
       </c>
       <c r="O16">
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>799.88</v>
+        <v>797.6799999999999</v>
       </c>
       <c r="R16">
-        <v>822.6799999999999</v>
+        <v>819.46</v>
       </c>
       <c r="S16">
-        <v>859.59</v>
+        <v>857.72</v>
       </c>
       <c r="T16">
-        <v>822.28</v>
+        <v>821.91</v>
       </c>
       <c r="U16">
-        <v>-3.96</v>
+        <v>-2.05</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2673,31 +2631,31 @@
         <v>1</v>
       </c>
       <c r="Z16">
-        <v>35.08</v>
+        <v>41.89</v>
       </c>
       <c r="AA16">
-        <v>-17.18</v>
+        <v>-16.35</v>
       </c>
       <c r="AB16">
-        <v>-15.39</v>
+        <v>-15.59</v>
       </c>
       <c r="AC16">
-        <v>-1.79</v>
+        <v>-0.76</v>
       </c>
       <c r="AD16">
-        <v>27.96</v>
+        <v>38.92</v>
       </c>
       <c r="AE16">
-        <v>39.73</v>
+        <v>34.06</v>
       </c>
       <c r="AF16">
-        <v>18.76</v>
+        <v>18.87</v>
       </c>
       <c r="AH16">
-        <v>865.99</v>
+        <v>857.41</v>
       </c>
       <c r="AI16">
-        <v>779.37</v>
+        <v>781.52</v>
       </c>
       <c r="AJ16">
         <v>838.5700000000001</v>
@@ -2706,7 +2664,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>39.65</v>
+        <v>37.76</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2720,10 +2678,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30162.5</v>
+        <v>30236</v>
       </c>
       <c r="E17">
-        <v>0.76</v>
+        <v>0.24</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2732,43 +2690,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-11.55</v>
+        <v>-11.33</v>
       </c>
       <c r="I17">
-        <v>6.34</v>
+        <v>6.6</v>
       </c>
       <c r="J17">
-        <v>-1.05</v>
+        <v>0.45</v>
       </c>
       <c r="K17">
-        <v>0.33</v>
+        <v>2.36</v>
       </c>
       <c r="L17">
-        <v>-4.06</v>
+        <v>-3.83</v>
       </c>
       <c r="M17">
-        <v>-8.890000000000001</v>
+        <v>-9.43</v>
       </c>
       <c r="N17">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
       <c r="O17">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Q17">
-        <v>30071.76</v>
+        <v>30098.99</v>
       </c>
       <c r="R17">
-        <v>29480.01</v>
+        <v>29511.11</v>
       </c>
       <c r="S17">
-        <v>30062.12</v>
+        <v>30044.81</v>
       </c>
       <c r="T17">
-        <v>30951.93</v>
+        <v>30934.83</v>
       </c>
       <c r="U17">
-        <v>-2.55</v>
+        <v>-2.26</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2783,31 +2741,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>56.21</v>
+        <v>57.27</v>
       </c>
       <c r="AA17">
-        <v>47.94</v>
+        <v>76.23</v>
       </c>
       <c r="AB17">
-        <v>-93.16</v>
+        <v>-59.28</v>
       </c>
       <c r="AC17">
-        <v>141.1</v>
+        <v>135.51</v>
       </c>
       <c r="AD17">
-        <v>78.33</v>
+        <v>81.06</v>
       </c>
       <c r="AE17">
-        <v>79.76000000000001</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="AF17">
-        <v>435.58</v>
+        <v>427.33</v>
       </c>
       <c r="AH17">
-        <v>30551.23</v>
+        <v>30633.6</v>
       </c>
       <c r="AI17">
-        <v>28408.79</v>
+        <v>28388.63</v>
       </c>
       <c r="AJ17">
         <v>29148.67</v>
@@ -2816,7 +2774,7 @@
         <v>82</v>
       </c>
       <c r="AL17">
-        <v>29.01</v>
+        <v>25.51</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2830,10 +2788,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>15658.7</v>
+        <v>15917.6</v>
       </c>
       <c r="E18">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2842,34 +2800,34 @@
         <v>15387</v>
       </c>
       <c r="H18">
-        <v>-7.57</v>
+        <v>-6.04</v>
       </c>
       <c r="I18">
-        <v>1.77</v>
+        <v>3.45</v>
       </c>
       <c r="J18">
-        <v>-0.16</v>
+        <v>2.31</v>
       </c>
       <c r="K18">
-        <v>-7.17</v>
+        <v>-5.01</v>
       </c>
       <c r="L18">
-        <v>-3.56</v>
+        <v>-3.37</v>
       </c>
       <c r="N18">
-        <v>1.86</v>
+        <v>6.4</v>
       </c>
       <c r="O18">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Q18">
-        <v>15525.14</v>
+        <v>15597.14</v>
       </c>
       <c r="R18">
-        <v>15902.6</v>
+        <v>15864.55</v>
       </c>
       <c r="S18">
-        <v>16305.6</v>
+        <v>16292.32</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2881,31 +2839,31 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>40.16</v>
+        <v>48.79</v>
       </c>
       <c r="AA18">
-        <v>-248.91</v>
+        <v>-213.04</v>
       </c>
       <c r="AB18">
-        <v>-226.04</v>
+        <v>-223.44</v>
       </c>
       <c r="AC18">
-        <v>-22.88</v>
+        <v>10.4</v>
       </c>
       <c r="AD18">
-        <v>35.58</v>
+        <v>66.67</v>
       </c>
       <c r="AE18">
-        <v>14.57</v>
+        <v>35.07</v>
       </c>
       <c r="AF18">
-        <v>247.78</v>
+        <v>253.07</v>
       </c>
       <c r="AH18">
-        <v>16633.91</v>
+        <v>16498.59</v>
       </c>
       <c r="AI18">
-        <v>15171.29</v>
+        <v>15230.51</v>
       </c>
       <c r="AJ18">
         <v>16084.17</v>
@@ -2914,7 +2872,7 @@
         <v>81</v>
       </c>
       <c r="AL18">
-        <v>66.18000000000001</v>
+        <v>57.37</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2928,10 +2886,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>8661.950000000001</v>
+        <v>8819.9</v>
       </c>
       <c r="E19">
-        <v>1.18</v>
+        <v>1.82</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2940,34 +2898,34 @@
         <v>8561.200000000001</v>
       </c>
       <c r="H19">
-        <v>-13.37</v>
+        <v>-11.79</v>
       </c>
       <c r="I19">
-        <v>1.18</v>
+        <v>3.02</v>
       </c>
       <c r="J19">
-        <v>-5.96</v>
+        <v>-3.34</v>
       </c>
       <c r="K19">
-        <v>-8.449999999999999</v>
+        <v>-5.79</v>
       </c>
       <c r="L19">
-        <v>-7.4</v>
+        <v>-6.37</v>
       </c>
       <c r="N19">
-        <v>-9.65</v>
+        <v>-5.12</v>
       </c>
       <c r="O19">
         <v>35</v>
       </c>
       <c r="Q19">
-        <v>8806.870000000001</v>
+        <v>8745.99</v>
       </c>
       <c r="R19">
-        <v>9100.540000000001</v>
+        <v>9071.450000000001</v>
       </c>
       <c r="S19">
-        <v>9436.139999999999</v>
+        <v>9416.32</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2979,31 +2937,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>33.7</v>
+        <v>40.05</v>
       </c>
       <c r="AA19">
-        <v>-177.96</v>
+        <v>-176.02</v>
       </c>
       <c r="AB19">
-        <v>-130.55</v>
+        <v>-139.64</v>
       </c>
       <c r="AC19">
-        <v>-47.41</v>
+        <v>-36.38</v>
       </c>
       <c r="AD19">
-        <v>7.56</v>
+        <v>25.93</v>
       </c>
       <c r="AE19">
-        <v>10.24</v>
+        <v>11.84</v>
       </c>
       <c r="AF19">
-        <v>190.49</v>
+        <v>194.45</v>
       </c>
       <c r="AH19">
-        <v>9548.74</v>
+        <v>9512.83</v>
       </c>
       <c r="AI19">
-        <v>8652.33</v>
+        <v>8630.07</v>
       </c>
       <c r="AJ19">
         <v>9128.139999999999</v>
@@ -3012,7 +2970,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>41.12</v>
+        <v>39.07</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3026,10 +2984,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10520.95</v>
+        <v>10536</v>
       </c>
       <c r="E20">
-        <v>1.35</v>
+        <v>0.14</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3038,34 +2996,34 @@
         <v>10299.4</v>
       </c>
       <c r="H20">
-        <v>-7.46</v>
+        <v>-7.33</v>
       </c>
       <c r="I20">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="J20">
-        <v>-0.34</v>
+        <v>-0.08</v>
       </c>
       <c r="K20">
-        <v>-4.4</v>
+        <v>-3.07</v>
       </c>
       <c r="L20">
-        <v>-5.02</v>
+        <v>-4.9</v>
       </c>
       <c r="N20">
-        <v>-11.54</v>
+        <v>-11.12</v>
       </c>
       <c r="O20">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Q20">
-        <v>10485.57</v>
+        <v>10483.89</v>
       </c>
       <c r="R20">
-        <v>10519.25</v>
+        <v>10502.95</v>
       </c>
       <c r="S20">
-        <v>10855.04</v>
+        <v>10840.71</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3077,31 +3035,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>45.05</v>
+        <v>45.86</v>
       </c>
       <c r="AA20">
-        <v>-109.72</v>
+        <v>-98.93000000000001</v>
       </c>
       <c r="AB20">
-        <v>-129.09</v>
+        <v>-123.06</v>
       </c>
       <c r="AC20">
-        <v>19.37</v>
+        <v>24.13</v>
       </c>
       <c r="AD20">
-        <v>69.84</v>
+        <v>80.69</v>
       </c>
       <c r="AE20">
-        <v>72.29000000000001</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="AF20">
-        <v>167.08</v>
+        <v>163.46</v>
       </c>
       <c r="AH20">
-        <v>10794.26</v>
+        <v>10726.14</v>
       </c>
       <c r="AI20">
-        <v>10244.25</v>
+        <v>10279.76</v>
       </c>
       <c r="AJ20">
         <v>10732.68</v>
@@ -3110,7 +3068,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>28</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3124,10 +3082,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>26825.3</v>
+        <v>26628.45</v>
       </c>
       <c r="E21">
-        <v>0.63</v>
+        <v>-0.73</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3136,43 +3094,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-8.09</v>
+        <v>-8.77</v>
       </c>
       <c r="I21">
-        <v>11.1</v>
+        <v>10.29</v>
       </c>
       <c r="J21">
-        <v>-3.16</v>
+        <v>-2.06</v>
       </c>
       <c r="K21">
-        <v>-1.97</v>
+        <v>-0.51</v>
       </c>
       <c r="L21">
-        <v>-5.9</v>
+        <v>-6.59</v>
       </c>
       <c r="M21">
-        <v>-3.25</v>
+        <v>-5.36</v>
       </c>
       <c r="N21">
-        <v>4.65</v>
+        <v>4.79</v>
       </c>
       <c r="O21">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="Q21">
-        <v>26888.22</v>
+        <v>26776.09</v>
       </c>
       <c r="R21">
-        <v>26982.5</v>
+        <v>26969.77</v>
       </c>
       <c r="S21">
-        <v>27254.43</v>
+        <v>27241.78</v>
       </c>
       <c r="T21">
-        <v>27394.34</v>
+        <v>27383.87</v>
       </c>
       <c r="U21">
-        <v>-2.08</v>
+        <v>-2.76</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3187,31 +3145,31 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>44.54</v>
+        <v>41.43</v>
       </c>
       <c r="AA21">
-        <v>-79.53</v>
+        <v>-105.34</v>
       </c>
       <c r="AB21">
-        <v>-55.65</v>
+        <v>-65.59</v>
       </c>
       <c r="AC21">
-        <v>-23.88</v>
+        <v>-39.76</v>
       </c>
       <c r="AD21">
-        <v>16.67</v>
+        <v>9.16</v>
       </c>
       <c r="AE21">
-        <v>24.88</v>
+        <v>15.17</v>
       </c>
       <c r="AF21">
-        <v>387.68</v>
+        <v>382.46</v>
       </c>
       <c r="AH21">
-        <v>27671.71</v>
+        <v>27675.9</v>
       </c>
       <c r="AI21">
-        <v>26293.3</v>
+        <v>26263.63</v>
       </c>
       <c r="AJ21">
         <v>26545.98</v>
@@ -3220,7 +3178,7 @@
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>29.31</v>
+        <v>29.24</v>
       </c>
     </row>
   </sheetData>
@@ -3361,7 +3319,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3401,7 +3359,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3421,7 +3379,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>89</v>
@@ -3439,2116 +3397,2101 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E6" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>107</v>
+      <c r="A8" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-5.2</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.85</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>110</v>
+      <c r="A9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-7.4</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-5.64</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-6.42</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-3.67</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.75</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-7.25</v>
+      </c>
+      <c r="D11" s="6">
+        <v>-5.62</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.63</v>
+      </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>115</v>
+      <c r="A12" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6">
+        <v>-7.48</v>
+      </c>
+      <c r="D12" s="6">
+        <v>-5.77</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.71</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-8.210000000000001</v>
+        <v>-4.34</v>
       </c>
       <c r="D13" s="6">
-        <v>-8.050000000000001</v>
+        <v>-2.61</v>
       </c>
       <c r="E13" s="7">
-        <v>0.16</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-7.93</v>
+        <v>13.9</v>
       </c>
       <c r="D14" s="6">
-        <v>-7.4</v>
+        <v>14.11</v>
       </c>
       <c r="E14" s="7">
-        <v>0.53</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-6.62</v>
+        <v>-8.44</v>
       </c>
       <c r="D15" s="6">
-        <v>-6.42</v>
+        <v>-5.89</v>
       </c>
       <c r="E15" s="7">
-        <v>0.2</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-8.5</v>
+        <v>-4.77</v>
       </c>
       <c r="D16" s="6">
-        <v>-7.25</v>
+        <v>-2.44</v>
       </c>
       <c r="E16" s="7">
-        <v>1.25</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-6.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="D17" s="6">
-        <v>-7.48</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.96</v>
+        <v>3.91</v>
+      </c>
+      <c r="E17" s="7">
+        <v>4.47</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-3.99</v>
+        <v>-11.81</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.34</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.35</v>
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.34</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>11.94</v>
+        <v>-6.77</v>
       </c>
       <c r="D19" s="6">
-        <v>13.9</v>
+        <v>-5.3</v>
       </c>
       <c r="E19" s="7">
-        <v>1.96</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-8.65</v>
+        <v>-3.25</v>
       </c>
       <c r="D20" s="6">
-        <v>-8.44</v>
+        <v>-1.75</v>
       </c>
       <c r="E20" s="7">
-        <v>0.21</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-5.17</v>
+        <v>-5.07</v>
       </c>
       <c r="D21" s="6">
-        <v>-4.77</v>
+        <v>-2.82</v>
       </c>
       <c r="E21" s="7">
-        <v>0.4</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-0.72</v>
+        <v>-9.33</v>
       </c>
       <c r="D22" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-6.54</v>
       </c>
       <c r="E22" s="7">
-        <v>0.16</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-11.64</v>
+        <v>0.33</v>
       </c>
       <c r="D23" s="6">
-        <v>-11.81</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-0.17</v>
+        <v>2.36</v>
+      </c>
+      <c r="E23" s="7">
+        <v>2.03</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-7.6</v>
+        <v>-7.17</v>
       </c>
       <c r="D24" s="6">
-        <v>-6.77</v>
+        <v>-5.01</v>
       </c>
       <c r="E24" s="7">
-        <v>0.83</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-2.43</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="D25" s="6">
-        <v>-3.25</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-0.82</v>
+        <v>-5.79</v>
+      </c>
+      <c r="E25" s="7">
+        <v>2.66</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-5.87</v>
+        <v>-4.4</v>
       </c>
       <c r="D26" s="6">
-        <v>-5.07</v>
+        <v>-3.07</v>
       </c>
       <c r="E26" s="7">
-        <v>0.8</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-8.960000000000001</v>
+        <v>-1.97</v>
       </c>
       <c r="D27" s="6">
-        <v>-9.33</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-0.37</v>
+        <v>-0.51</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.46</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>-0.12</v>
+        <v>-3.1</v>
       </c>
       <c r="D28" s="6">
-        <v>0.33</v>
+        <v>-0.98</v>
       </c>
       <c r="E28" s="7">
-        <v>0.45</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-7.97</v>
+        <v>-1.83</v>
       </c>
       <c r="D29" s="6">
-        <v>-7.17</v>
+        <v>-0.68</v>
       </c>
       <c r="E29" s="7">
-        <v>0.8</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>-9.609999999999999</v>
+        <v>-2.26</v>
       </c>
       <c r="D30" s="6">
-        <v>-8.449999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="E30" s="7">
-        <v>1.16</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-5.28</v>
+        <v>-3.23</v>
       </c>
       <c r="D31" s="6">
-        <v>-4.4</v>
+        <v>-1.98</v>
       </c>
       <c r="E31" s="7">
-        <v>0.88</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-2.31</v>
+        <v>-4.07</v>
       </c>
       <c r="D32" s="6">
-        <v>-1.97</v>
+        <v>-1.95</v>
       </c>
       <c r="E32" s="7">
-        <v>0.34</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-2.79</v>
+        <v>-3.67</v>
       </c>
       <c r="D33" s="6">
-        <v>-3.1</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.31</v>
+        <v>-2.73</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>-3.06</v>
+        <v>1.09</v>
       </c>
       <c r="D34" s="6">
-        <v>-1.83</v>
+        <v>2.14</v>
       </c>
       <c r="E34" s="7">
-        <v>1.23</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>-2.53</v>
+        <v>-3.35</v>
       </c>
       <c r="D35" s="6">
-        <v>-2.26</v>
+        <v>-1.33</v>
       </c>
       <c r="E35" s="7">
-        <v>0.27</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-4.68</v>
+        <v>-0.74</v>
       </c>
       <c r="D36" s="6">
-        <v>-3.23</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E36" s="7">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-4.71</v>
+        <v>-5.47</v>
       </c>
       <c r="D37" s="6">
-        <v>-4.07</v>
+        <v>-1.75</v>
       </c>
       <c r="E37" s="7">
-        <v>0.64</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-3.79</v>
+        <v>-3.31</v>
       </c>
       <c r="D38" s="6">
-        <v>-3.67</v>
+        <v>-2.15</v>
       </c>
       <c r="E38" s="7">
-        <v>0.12</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>4.15</v>
+        <v>-2.84</v>
       </c>
       <c r="D39" s="6">
-        <v>1.09</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-3.06</v>
+        <v>-1.55</v>
+      </c>
+      <c r="E39" s="7">
+        <v>1.29</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-4</v>
+        <v>-0.01</v>
       </c>
       <c r="D40" s="6">
-        <v>-3.35</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.65</v>
+        <v>-2.02</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-2.01</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>-1.52</v>
+        <v>-0.03</v>
       </c>
       <c r="D41" s="6">
-        <v>-0.74</v>
+        <v>2.55</v>
       </c>
       <c r="E41" s="7">
-        <v>0.78</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>-3.33</v>
+        <v>-4.39</v>
       </c>
       <c r="D42" s="6">
-        <v>-5.47</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-2.14</v>
+        <v>-1.35</v>
+      </c>
+      <c r="E42" s="7">
+        <v>3.04</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-4.5</v>
+        <v>-1.05</v>
       </c>
       <c r="D43" s="6">
-        <v>-3.31</v>
+        <v>0.45</v>
       </c>
       <c r="E43" s="7">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>-4.01</v>
+        <v>-0.16</v>
       </c>
       <c r="D44" s="6">
-        <v>-2.84</v>
+        <v>2.31</v>
       </c>
       <c r="E44" s="7">
-        <v>1.17</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>0.37</v>
+        <v>-5.96</v>
       </c>
       <c r="D45" s="6">
-        <v>-0.01</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-0.38</v>
+        <v>-3.34</v>
+      </c>
+      <c r="E45" s="7">
+        <v>2.62</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-1.89</v>
+        <v>-0.34</v>
       </c>
       <c r="D46" s="6">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="E46" s="7">
-        <v>1.86</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>-5.35</v>
+        <v>-3.16</v>
       </c>
       <c r="D47" s="6">
-        <v>-4.39</v>
+        <v>-2.06</v>
       </c>
       <c r="E47" s="7">
-        <v>0.96</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48" s="6">
-        <v>-0.2</v>
+        <v>-6.51</v>
       </c>
       <c r="D48" s="6">
-        <v>-1.05</v>
-      </c>
-      <c r="E48" s="8">
-        <v>-0.85</v>
+        <v>-6.31</v>
+      </c>
+      <c r="E48" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" s="6">
-        <v>-2.15</v>
+        <v>-2.3</v>
       </c>
       <c r="D49" s="6">
-        <v>-0.16</v>
-      </c>
-      <c r="E49" s="7">
-        <v>1.99</v>
+        <v>-2.53</v>
+      </c>
+      <c r="E49" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>-6.91</v>
+        <v>-12.51</v>
       </c>
       <c r="D50" s="6">
-        <v>-5.96</v>
+        <v>-12.39</v>
       </c>
       <c r="E50" s="7">
-        <v>0.95</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>-2.11</v>
+        <v>-0.85</v>
       </c>
       <c r="D51" s="6">
-        <v>-0.34</v>
+        <v>-0.58</v>
       </c>
       <c r="E51" s="7">
-        <v>1.77</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-3.7</v>
+        <v>-21.82</v>
       </c>
       <c r="D52" s="6">
-        <v>-3.16</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.54</v>
+        <v>-22.8</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-6.67</v>
+        <v>-9.67</v>
       </c>
       <c r="D53" s="6">
-        <v>-6.51</v>
-      </c>
-      <c r="E53" s="7">
-        <v>0.16</v>
+        <v>-11.24</v>
+      </c>
+      <c r="E53" s="8">
+        <v>-1.57</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-2.85</v>
+        <v>-8.84</v>
       </c>
       <c r="D54" s="6">
-        <v>-2.3</v>
-      </c>
-      <c r="E54" s="7">
-        <v>0.55</v>
+        <v>-9.4</v>
+      </c>
+      <c r="E54" s="8">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-12.28</v>
+        <v>-6.13</v>
       </c>
       <c r="D55" s="6">
-        <v>-12.51</v>
+        <v>-6.22</v>
       </c>
       <c r="E55" s="8">
-        <v>-0.23</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-1.56</v>
+        <v>1.22</v>
       </c>
       <c r="D56" s="6">
-        <v>-0.85</v>
+        <v>4.62</v>
       </c>
       <c r="E56" s="7">
-        <v>0.71</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>-21.27</v>
+        <v>14.81</v>
       </c>
       <c r="D57" s="6">
-        <v>-21.82</v>
+        <v>14.77</v>
       </c>
       <c r="E57" s="8">
-        <v>-0.55</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>-9.039999999999999</v>
+        <v>-9.25</v>
       </c>
       <c r="D58" s="6">
-        <v>-9.67</v>
-      </c>
-      <c r="E58" s="8">
-        <v>-0.63</v>
+        <v>-8.890000000000001</v>
+      </c>
+      <c r="E58" s="7">
+        <v>0.36</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>-9.140000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="D59" s="6">
-        <v>-8.84</v>
+        <v>5.7</v>
       </c>
       <c r="E59" s="7">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>-6.35</v>
+        <v>16.85</v>
       </c>
       <c r="D60" s="6">
-        <v>-6.13</v>
+        <v>18.84</v>
       </c>
       <c r="E60" s="7">
-        <v>0.22</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>1.04</v>
+        <v>-13.73</v>
       </c>
       <c r="D61" s="6">
-        <v>1.22</v>
+        <v>-13.7</v>
       </c>
       <c r="E61" s="7">
-        <v>0.18</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>13.46</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="D62" s="6">
-        <v>14.81</v>
-      </c>
-      <c r="E62" s="7">
-        <v>1.35</v>
+        <v>-9.43</v>
+      </c>
+      <c r="E62" s="8">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>-9.119999999999999</v>
+        <v>-3.25</v>
       </c>
       <c r="D63" s="6">
-        <v>-9.25</v>
+        <v>-5.36</v>
       </c>
       <c r="E63" s="8">
-        <v>-0.13</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>6.24</v>
+        <v>-7.86</v>
       </c>
       <c r="D64" s="6">
-        <v>4.8</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-1.44</v>
+        <v>-6.49</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.37</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>14.93</v>
+        <v>-9.15</v>
       </c>
       <c r="D65" s="6">
-        <v>16.85</v>
+        <v>-8.68</v>
       </c>
       <c r="E65" s="7">
-        <v>1.92</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-11.71</v>
+        <v>-7.69</v>
       </c>
       <c r="D66" s="6">
-        <v>-13.73</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-2.02</v>
+        <v>-6.56</v>
+      </c>
+      <c r="E66" s="7">
+        <v>1.13</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-8.98</v>
+        <v>-10.83</v>
       </c>
       <c r="D67" s="6">
-        <v>-8.890000000000001</v>
+        <v>-10.22</v>
       </c>
       <c r="E67" s="7">
-        <v>0.09</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-3.75</v>
+        <v>-12.2</v>
       </c>
       <c r="D68" s="6">
-        <v>-3.25</v>
+        <v>-11.55</v>
       </c>
       <c r="E68" s="7">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-8.26</v>
+        <v>-9.1</v>
       </c>
       <c r="D69" s="6">
-        <v>-7.86</v>
-      </c>
-      <c r="E69" s="7">
-        <v>0.4</v>
+        <v>-9.66</v>
+      </c>
+      <c r="E69" s="8">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-10.58</v>
+        <v>12.18</v>
       </c>
       <c r="D70" s="6">
-        <v>-9.15</v>
-      </c>
-      <c r="E70" s="7">
-        <v>1.43</v>
+        <v>9.33</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-8.359999999999999</v>
+        <v>-7.44</v>
       </c>
       <c r="D71" s="6">
-        <v>-7.69</v>
+        <v>-7.1</v>
       </c>
       <c r="E71" s="7">
-        <v>0.67</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-12.11</v>
+        <v>-7.64</v>
       </c>
       <c r="D72" s="6">
-        <v>-10.83</v>
+        <v>-6.94</v>
       </c>
       <c r="E72" s="7">
-        <v>1.28</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>-12.45</v>
+        <v>2.41</v>
       </c>
       <c r="D73" s="6">
-        <v>-12.2</v>
+        <v>6.15</v>
       </c>
       <c r="E73" s="7">
-        <v>0.25</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-9.289999999999999</v>
+        <v>-5.67</v>
       </c>
       <c r="D74" s="6">
-        <v>-9.1</v>
+        <v>-5.07</v>
       </c>
       <c r="E74" s="7">
-        <v>0.19</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>12.13</v>
+        <v>-9.59</v>
       </c>
       <c r="D75" s="6">
-        <v>12.18</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="E75" s="7">
-        <v>0.05</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-8.83</v>
+        <v>-3.44</v>
       </c>
       <c r="D76" s="6">
-        <v>-7.44</v>
+        <v>-3.04</v>
       </c>
       <c r="E76" s="7">
-        <v>1.39</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>-8.779999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="D77" s="6">
-        <v>-7.64</v>
+        <v>1.24</v>
       </c>
       <c r="E77" s="7">
-        <v>1.14</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>2.76</v>
+        <v>-14.04</v>
       </c>
       <c r="D78" s="6">
-        <v>2.41</v>
-      </c>
-      <c r="E78" s="8">
-        <v>-0.35</v>
+        <v>-12.37</v>
+      </c>
+      <c r="E78" s="7">
+        <v>1.67</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-7.71</v>
+        <v>-4.06</v>
       </c>
       <c r="D79" s="6">
-        <v>-5.67</v>
+        <v>-3.83</v>
       </c>
       <c r="E79" s="7">
-        <v>2.04</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-10.59</v>
+        <v>-3.56</v>
       </c>
       <c r="D80" s="6">
-        <v>-9.59</v>
+        <v>-3.37</v>
       </c>
       <c r="E80" s="7">
-        <v>1</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-3.71</v>
+        <v>-7.4</v>
       </c>
       <c r="D81" s="6">
-        <v>-3.44</v>
+        <v>-6.37</v>
       </c>
       <c r="E81" s="7">
-        <v>0.27</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-1.26</v>
+        <v>-5.02</v>
       </c>
       <c r="D82" s="6">
-        <v>0.88</v>
+        <v>-4.9</v>
       </c>
       <c r="E82" s="7">
-        <v>2.14</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-14.62</v>
+        <v>-5.9</v>
       </c>
       <c r="D83" s="6">
-        <v>-14.04</v>
-      </c>
-      <c r="E83" s="7">
-        <v>0.58</v>
+        <v>-6.59</v>
+      </c>
+      <c r="E83" s="8">
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C84" s="6">
-        <v>-4.79</v>
+        <v>-15.78</v>
       </c>
       <c r="D84" s="6">
-        <v>-4.06</v>
+        <v>-14.53</v>
       </c>
       <c r="E84" s="7">
-        <v>0.73</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C85" s="6">
-        <v>-5.58</v>
+        <v>-14.95</v>
       </c>
       <c r="D85" s="6">
-        <v>-3.56</v>
+        <v>-14.52</v>
       </c>
       <c r="E85" s="7">
-        <v>2.02</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C86" s="6">
-        <v>-8.789999999999999</v>
+        <v>-14.52</v>
       </c>
       <c r="D86" s="6">
-        <v>-7.4</v>
+        <v>-13.47</v>
       </c>
       <c r="E86" s="7">
-        <v>1.39</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-6.72</v>
+        <v>-15.68</v>
       </c>
       <c r="D87" s="6">
-        <v>-5.02</v>
+        <v>-15.1</v>
       </c>
       <c r="E87" s="7">
-        <v>1.7</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-6.5</v>
+        <v>-24.61</v>
       </c>
       <c r="D88" s="6">
-        <v>-5.9</v>
+        <v>-24.05</v>
       </c>
       <c r="E88" s="7">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-16.14</v>
+        <v>-14.08</v>
       </c>
       <c r="D89" s="6">
-        <v>-15.78</v>
-      </c>
-      <c r="E89" s="7">
-        <v>0.36</v>
+        <v>-14.61</v>
+      </c>
+      <c r="E89" s="8">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-16.29</v>
+        <v>-18.27</v>
       </c>
       <c r="D90" s="6">
-        <v>-14.95</v>
-      </c>
-      <c r="E90" s="7">
-        <v>1.34</v>
+        <v>-18.48</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-15.13</v>
+        <v>-11.98</v>
       </c>
       <c r="D91" s="6">
-        <v>-14.52</v>
+        <v>-10.71</v>
       </c>
       <c r="E91" s="7">
-        <v>0.61</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-16.89</v>
+        <v>-11.31</v>
       </c>
       <c r="D92" s="6">
-        <v>-15.68</v>
+        <v>-10.64</v>
       </c>
       <c r="E92" s="7">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-24.82</v>
+        <v>-5.47</v>
       </c>
       <c r="D93" s="6">
-        <v>-24.61</v>
+        <v>-2.01</v>
       </c>
       <c r="E93" s="7">
-        <v>0.21</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-14.26</v>
+        <v>-14.48</v>
       </c>
       <c r="D94" s="6">
-        <v>-14.08</v>
+        <v>-13.93</v>
       </c>
       <c r="E94" s="7">
-        <v>0.18</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-18.97</v>
+        <v>-16.55</v>
       </c>
       <c r="D95" s="6">
-        <v>-18.27</v>
+        <v>-15.95</v>
       </c>
       <c r="E95" s="7">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-12.88</v>
+        <v>-18.08</v>
       </c>
       <c r="D96" s="6">
-        <v>-11.98</v>
+        <v>-17.74</v>
       </c>
       <c r="E96" s="7">
-        <v>0.9</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-12.41</v>
+        <v>-5.19</v>
       </c>
       <c r="D97" s="6">
-        <v>-11.31</v>
+        <v>-3.38</v>
       </c>
       <c r="E97" s="7">
-        <v>1.1</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-5.15</v>
+        <v>-18.47</v>
       </c>
       <c r="D98" s="6">
-        <v>-5.47</v>
-      </c>
-      <c r="E98" s="8">
-        <v>-0.32</v>
+        <v>-16.89</v>
+      </c>
+      <c r="E98" s="7">
+        <v>1.58</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-16.33</v>
+        <v>-11.55</v>
       </c>
       <c r="D99" s="6">
-        <v>-14.48</v>
+        <v>-11.33</v>
       </c>
       <c r="E99" s="7">
-        <v>1.85</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-17.47</v>
+        <v>-7.57</v>
       </c>
       <c r="D100" s="6">
-        <v>-16.55</v>
+        <v>-6.04</v>
       </c>
       <c r="E100" s="7">
-        <v>0.92</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-18.31</v>
+        <v>-13.37</v>
       </c>
       <c r="D101" s="6">
-        <v>-18.08</v>
+        <v>-11.79</v>
       </c>
       <c r="E101" s="7">
-        <v>0.23</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-6.83</v>
+        <v>-7.46</v>
       </c>
       <c r="D102" s="6">
-        <v>-5.19</v>
+        <v>-7.33</v>
       </c>
       <c r="E102" s="7">
-        <v>1.64</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="6">
-        <v>-19.03</v>
+        <v>-8.09</v>
       </c>
       <c r="D103" s="6">
-        <v>-18.47</v>
-      </c>
-      <c r="E103" s="7">
-        <v>0.5600000000000001</v>
+        <v>-8.77</v>
+      </c>
+      <c r="E103" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C104" s="6">
-        <v>-12.22</v>
+        <v>24970.75</v>
       </c>
       <c r="D104" s="6">
-        <v>-11.55</v>
+        <v>25340.8</v>
       </c>
       <c r="E104" s="7">
-        <v>0.67</v>
+        <v>370.05</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C105" s="6">
-        <v>-9.18</v>
+        <v>8932.700000000001</v>
       </c>
       <c r="D105" s="6">
-        <v>-7.57</v>
+        <v>8978.65</v>
       </c>
       <c r="E105" s="7">
-        <v>1.61</v>
+        <v>45.95</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>-14.38</v>
+        <v>10804.45</v>
       </c>
       <c r="D106" s="6">
-        <v>-13.37</v>
+        <v>10936.65</v>
       </c>
       <c r="E106" s="7">
-        <v>1.01</v>
+        <v>132.2</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>-8.69</v>
+        <v>35022.35</v>
       </c>
       <c r="D107" s="6">
-        <v>-7.46</v>
+        <v>35261.85</v>
       </c>
       <c r="E107" s="7">
-        <v>1.23</v>
+        <v>239.5</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>-8.67</v>
+        <v>42800.75</v>
       </c>
       <c r="D108" s="6">
-        <v>-8.09</v>
+        <v>43118.2</v>
       </c>
       <c r="E108" s="7">
-        <v>0.58</v>
+        <v>317.45</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>24862.3</v>
+        <v>24454.35</v>
       </c>
       <c r="D109" s="6">
-        <v>24970.75</v>
-      </c>
-      <c r="E109" s="7">
-        <v>108.45</v>
+        <v>24303.75</v>
+      </c>
+      <c r="E109" s="8">
+        <v>-150.6</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>8792.299999999999</v>
+        <v>32273.05</v>
       </c>
       <c r="D110" s="6">
-        <v>8932.700000000001</v>
-      </c>
-      <c r="E110" s="7">
-        <v>140.4</v>
+        <v>32189.45</v>
+      </c>
+      <c r="E110" s="8">
+        <v>-83.59999999999999</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>10726.75</v>
+        <v>14665.7</v>
       </c>
       <c r="D111" s="6">
-        <v>10804.45</v>
+        <v>14878.4</v>
       </c>
       <c r="E111" s="7">
-        <v>77.7</v>
+        <v>212.7</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>34520.05</v>
+        <v>8661.200000000001</v>
       </c>
       <c r="D112" s="6">
-        <v>35022.35</v>
+        <v>8726.6</v>
       </c>
       <c r="E112" s="7">
-        <v>502.3</v>
+        <v>65.40000000000001</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>42680.7</v>
+        <v>1558.1</v>
       </c>
       <c r="D113" s="6">
-        <v>42800.75</v>
+        <v>1615.05</v>
       </c>
       <c r="E113" s="7">
-        <v>120.05</v>
+        <v>56.95</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>24403</v>
+        <v>11731.55</v>
       </c>
       <c r="D114" s="6">
-        <v>24454.35</v>
+        <v>11806.7</v>
       </c>
       <c r="E114" s="7">
-        <v>51.35</v>
+        <v>75.15000000000001</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>31995.5</v>
+        <v>8984.950000000001</v>
       </c>
       <c r="D115" s="6">
-        <v>32273.05</v>
+        <v>9048.6</v>
       </c>
       <c r="E115" s="7">
-        <v>277.55</v>
+        <v>63.65</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>14516.75</v>
+        <v>8093.8</v>
       </c>
       <c r="D116" s="6">
-        <v>14665.7</v>
+        <v>8126.7</v>
       </c>
       <c r="E116" s="7">
-        <v>148.95</v>
+        <v>32.9</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>8554.25</v>
+        <v>25774.25</v>
       </c>
       <c r="D117" s="6">
-        <v>8661.200000000001</v>
+        <v>26267.25</v>
       </c>
       <c r="E117" s="7">
-        <v>106.95</v>
+        <v>493</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>1563.4</v>
+        <v>789.7</v>
       </c>
       <c r="D118" s="6">
-        <v>1558.1</v>
-      </c>
-      <c r="E118" s="8">
-        <v>-5.3</v>
+        <v>805.05</v>
+      </c>
+      <c r="E118" s="7">
+        <v>15.35</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>11478.2</v>
+        <v>30162.5</v>
       </c>
       <c r="D119" s="6">
-        <v>11731.55</v>
+        <v>30236</v>
       </c>
       <c r="E119" s="7">
-        <v>253.35</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>8885.75</v>
+        <v>15658.7</v>
       </c>
       <c r="D120" s="6">
-        <v>8984.950000000001</v>
+        <v>15917.6</v>
       </c>
       <c r="E120" s="7">
-        <v>99.2</v>
+        <v>258.9</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>8070.7</v>
+        <v>8661.950000000001</v>
       </c>
       <c r="D121" s="6">
-        <v>8093.8</v>
+        <v>8819.9</v>
       </c>
       <c r="E121" s="7">
-        <v>23.1</v>
+        <v>157.95</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>25329.45</v>
+        <v>10520.95</v>
       </c>
       <c r="D122" s="6">
-        <v>25774.25</v>
+        <v>10536</v>
       </c>
       <c r="E122" s="7">
-        <v>444.8</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="6">
-        <v>784.35</v>
+        <v>26825.3</v>
       </c>
       <c r="D123" s="6">
-        <v>789.7</v>
-      </c>
-      <c r="E123" s="7">
-        <v>5.35</v>
+        <v>26628.45</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-196.85</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C124" s="6">
-        <v>29934.75</v>
+        <v>55</v>
       </c>
       <c r="D124" s="6">
-        <v>30162.5</v>
-      </c>
-      <c r="E124" s="7">
-        <v>227.75</v>
+        <v>50</v>
+      </c>
+      <c r="E124" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C125" s="6">
-        <v>15387</v>
+        <v>15</v>
       </c>
       <c r="D125" s="6">
-        <v>15658.7</v>
+        <v>20</v>
       </c>
       <c r="E125" s="7">
-        <v>271.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126" s="6">
+        <v>50</v>
+      </c>
+      <c r="D126" s="6">
         <v>55</v>
       </c>
-      <c r="B126" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C126" s="6">
-        <v>8561.200000000001</v>
-      </c>
-      <c r="D126" s="6">
-        <v>8661.950000000001</v>
-      </c>
       <c r="E126" s="7">
-        <v>100.75</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>10380.55</v>
+        <v>25</v>
       </c>
       <c r="D127" s="6">
-        <v>10520.95</v>
-      </c>
-      <c r="E127" s="7">
-        <v>140.4</v>
+        <v>15</v>
+      </c>
+      <c r="E127" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>26656.3</v>
+        <v>95</v>
       </c>
       <c r="D128" s="6">
-        <v>26825.3</v>
-      </c>
-      <c r="E128" s="7">
-        <v>169</v>
+        <v>90</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="D129" s="6">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="E129" s="7">
         <v>5</v>
@@ -5556,50 +5499,50 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C130" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D130" s="6">
         <v>25</v>
       </c>
-      <c r="E130" s="8">
-        <v>-10</v>
+      <c r="E130" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="6">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D131" s="6">
-        <v>45</v>
-      </c>
-      <c r="E131" s="8">
-        <v>-5</v>
+        <v>65</v>
+      </c>
+      <c r="E131" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C132" s="6">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="D132" s="6">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E132" s="7">
         <v>5</v>
@@ -5607,416 +5550,382 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C133" s="6">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="D133" s="6">
-        <v>80</v>
-      </c>
-      <c r="E133" s="8">
-        <v>-5</v>
+        <v>70</v>
+      </c>
+      <c r="E133" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C134" s="6">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D134" s="6">
         <v>60</v>
       </c>
       <c r="E134" s="8">
-        <v>-10</v>
+        <v>-15</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>60</v>
+        <v>36.27</v>
       </c>
       <c r="D135" s="6">
-        <v>70</v>
+        <v>42.77</v>
       </c>
       <c r="E135" s="7">
-        <v>10</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>25</v>
+        <v>38.62</v>
       </c>
       <c r="D136" s="6">
-        <v>35</v>
+        <v>41.22</v>
       </c>
       <c r="E136" s="7">
-        <v>10</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>34.24</v>
+        <v>38.43</v>
       </c>
       <c r="D137" s="6">
-        <v>36.27</v>
+        <v>44.7</v>
       </c>
       <c r="E137" s="7">
-        <v>2.03</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>29.83</v>
+        <v>33.59</v>
       </c>
       <c r="D138" s="6">
-        <v>38.62</v>
+        <v>37.32</v>
       </c>
       <c r="E138" s="7">
-        <v>8.789999999999999</v>
+        <v>3.73</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>34.38</v>
+        <v>34.8</v>
       </c>
       <c r="D139" s="6">
-        <v>38.43</v>
+        <v>38.09</v>
       </c>
       <c r="E139" s="7">
-        <v>4.05</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>24.86</v>
+        <v>38.61</v>
       </c>
       <c r="D140" s="6">
-        <v>33.59</v>
-      </c>
-      <c r="E140" s="7">
-        <v>8.73</v>
+        <v>36.45</v>
+      </c>
+      <c r="E140" s="8">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>33.56</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="D141" s="6">
-        <v>34.8</v>
-      </c>
-      <c r="E141" s="7">
-        <v>1.24</v>
+        <v>68.48999999999999</v>
+      </c>
+      <c r="E141" s="8">
+        <v>-1.05</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>37.43</v>
+        <v>32.14</v>
       </c>
       <c r="D142" s="6">
-        <v>38.61</v>
+        <v>39.72</v>
       </c>
       <c r="E142" s="7">
-        <v>1.18</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>68.04000000000001</v>
+        <v>44.43</v>
       </c>
       <c r="D143" s="6">
-        <v>69.54000000000001</v>
+        <v>48.34</v>
       </c>
       <c r="E143" s="7">
-        <v>1.5</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>26.1</v>
+        <v>45.23</v>
       </c>
       <c r="D144" s="6">
-        <v>32.14</v>
+        <v>55.08</v>
       </c>
       <c r="E144" s="7">
-        <v>6.04</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>37.21</v>
+        <v>36.14</v>
       </c>
       <c r="D145" s="6">
-        <v>44.43</v>
+        <v>38.41</v>
       </c>
       <c r="E145" s="7">
-        <v>7.22</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>46.1</v>
+        <v>34.76</v>
       </c>
       <c r="D146" s="6">
-        <v>45.23</v>
-      </c>
-      <c r="E146" s="8">
-        <v>-0.87</v>
+        <v>38.86</v>
+      </c>
+      <c r="E146" s="7">
+        <v>4.1</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>27.83</v>
+        <v>45.72</v>
       </c>
       <c r="D147" s="6">
-        <v>36.14</v>
+        <v>47.39</v>
       </c>
       <c r="E147" s="7">
-        <v>8.31</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>27.76</v>
+        <v>43.84</v>
       </c>
       <c r="D148" s="6">
-        <v>34.76</v>
+        <v>53.07</v>
       </c>
       <c r="E148" s="7">
-        <v>7</v>
+        <v>9.23</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>44.57</v>
+        <v>35.08</v>
       </c>
       <c r="D149" s="6">
-        <v>45.72</v>
+        <v>41.89</v>
       </c>
       <c r="E149" s="7">
-        <v>1.15</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>32.75</v>
+        <v>56.21</v>
       </c>
       <c r="D150" s="6">
-        <v>43.84</v>
+        <v>57.27</v>
       </c>
       <c r="E150" s="7">
-        <v>11.09</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>32.51</v>
+        <v>40.16</v>
       </c>
       <c r="D151" s="6">
-        <v>35.08</v>
+        <v>48.79</v>
       </c>
       <c r="E151" s="7">
-        <v>2.57</v>
+        <v>8.630000000000001</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C152" s="6">
-        <v>52.83</v>
+        <v>33.7</v>
       </c>
       <c r="D152" s="6">
-        <v>56.21</v>
+        <v>40.05</v>
       </c>
       <c r="E152" s="7">
-        <v>3.38</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C153" s="6">
-        <v>28.39</v>
+        <v>45.05</v>
       </c>
       <c r="D153" s="6">
-        <v>40.16</v>
+        <v>45.86</v>
       </c>
       <c r="E153" s="7">
-        <v>11.77</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C154" s="6">
-        <v>29.26</v>
+        <v>44.54</v>
       </c>
       <c r="D154" s="6">
-        <v>33.7</v>
-      </c>
-      <c r="E154" s="7">
-        <v>4.44</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C155" s="6">
-        <v>36.85</v>
-      </c>
-      <c r="D155" s="6">
-        <v>45.05</v>
-      </c>
-      <c r="E155" s="7">
-        <v>8.199999999999999</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C156" s="6">
-        <v>41.01</v>
-      </c>
-      <c r="D156" s="6">
-        <v>44.54</v>
-      </c>
-      <c r="E156" s="7">
-        <v>3.53</v>
+        <v>41.43</v>
+      </c>
+      <c r="E154" s="8">
+        <v>-3.11</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6040,28 +5949,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6075,16 +5984,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>41.3</v>
+        <v>45.3</v>
       </c>
       <c r="E2" s="11">
         <v>18.8</v>
       </c>
       <c r="F2" s="11">
-        <v>-4.9</v>
+        <v>-2.8</v>
       </c>
       <c r="G2" s="11">
-        <v>-5.8</v>
+        <v>-5.2</v>
       </c>
       <c r="H2" s="11">
         <v>52.4</v>
@@ -6213,10 +6122,10 @@
         <v>52</v>
       </c>
       <c r="H1" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>39</v>
       </c>
       <c r="J1" s="13" t="s">
         <v>41</v>
@@ -6224,60 +6133,60 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2297</v>
+        <v>0.2257</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1687</v>
+        <v>0.1734</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1656</v>
+        <v>0.1693</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1501</v>
+        <v>0.1551</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1303</v>
+        <v>0.1326</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1088</v>
+        <v>0.1114</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0895</v>
+        <v>0.0931</v>
       </c>
       <c r="H2" s="14">
-        <v>0.08789999999999999</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="I2" s="14">
-        <v>0.08710000000000001</v>
+        <v>0.08900000000000001</v>
       </c>
       <c r="J2" s="14">
-        <v>0.07519999999999999</v>
+        <v>0.07829999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="C3" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="D3" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="E3" s="13" t="s">
         <v>42</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="F3" s="13" t="s">
         <v>44</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>56</v>
@@ -6288,34 +6197,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.04650000000000001</v>
+        <v>0.064</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0447</v>
+        <v>0.0479</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0326</v>
+        <v>0.045</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0197</v>
+        <v>0.0336</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0186</v>
+        <v>0.0206</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.017</v>
+        <v>-0.0194</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.07780000000000001</v>
+        <v>-0.0512</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0965</v>
+        <v>-0.0673</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1154</v>
+        <v>-0.1112</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.162</v>
+        <v>-0.1281</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="114">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,28 +289,40 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.0% → -0.7%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.0%</t>
+  </si>
+  <si>
+    <t>-0.7%</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>45.2 → 55.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.2</t>
-  </si>
-  <si>
-    <t>55.1</t>
-  </si>
-  <si>
-    <t>43.8 → 53.1</t>
-  </si>
-  <si>
-    <t>43.8</t>
-  </si>
-  <si>
-    <t>53.1</t>
+    <t>48.8 → 53.9</t>
+  </si>
+  <si>
+    <t>48.8</t>
+  </si>
+  <si>
+    <t>53.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1040,10 +1052,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>25340.8</v>
+        <v>25707.35</v>
       </c>
       <c r="E2">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1052,43 +1064,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-14.53</v>
+        <v>-13.29</v>
       </c>
       <c r="I2">
-        <v>6.61</v>
+        <v>8.15</v>
       </c>
       <c r="J2">
-        <v>-0.98</v>
+        <v>2.03</v>
       </c>
       <c r="K2">
-        <v>-5.2</v>
+        <v>-4.67</v>
       </c>
       <c r="L2">
-        <v>-6.49</v>
+        <v>-5.14</v>
       </c>
       <c r="M2">
-        <v>-6.31</v>
+        <v>-5.59</v>
       </c>
       <c r="N2">
-        <v>17.34</v>
+        <v>17.95</v>
       </c>
       <c r="O2">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Q2">
-        <v>25076.4</v>
+        <v>25178.54</v>
       </c>
       <c r="R2">
-        <v>25390.19</v>
+        <v>25349.3</v>
       </c>
       <c r="S2">
-        <v>27003.28</v>
+        <v>26933.27</v>
       </c>
       <c r="T2">
-        <v>26876.38</v>
+        <v>26860.9</v>
       </c>
       <c r="U2">
-        <v>-5.71</v>
+        <v>-4.29</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1103,31 +1115,31 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>42.77</v>
+        <v>48.38</v>
       </c>
       <c r="AA2">
-        <v>-495.24</v>
+        <v>-425.88</v>
       </c>
       <c r="AB2">
-        <v>-568.59</v>
+        <v>-540.05</v>
       </c>
       <c r="AC2">
-        <v>73.34999999999999</v>
+        <v>114.17</v>
       </c>
       <c r="AD2">
-        <v>75.69</v>
+        <v>88.47</v>
       </c>
       <c r="AE2">
-        <v>69.97</v>
+        <v>76.81</v>
       </c>
       <c r="AF2">
-        <v>462.83</v>
+        <v>464.47</v>
       </c>
       <c r="AH2">
-        <v>26401.76</v>
+        <v>26224.68</v>
       </c>
       <c r="AI2">
-        <v>24378.62</v>
+        <v>24473.93</v>
       </c>
       <c r="AJ2">
         <v>26008.9</v>
@@ -1136,7 +1148,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>49.6</v>
+        <v>43.52</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1150,10 +1162,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>8978.65</v>
+        <v>8893.5</v>
       </c>
       <c r="E3">
-        <v>0.51</v>
+        <v>-0.95</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1162,43 +1174,43 @@
         <v>8792.299999999999</v>
       </c>
       <c r="H3">
-        <v>-14.52</v>
+        <v>-15.33</v>
       </c>
       <c r="I3">
-        <v>2.12</v>
+        <v>1.15</v>
       </c>
       <c r="J3">
-        <v>-0.68</v>
+        <v>-0.65</v>
       </c>
       <c r="K3">
-        <v>-5.64</v>
+        <v>-6.78</v>
       </c>
       <c r="L3">
-        <v>-8.68</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="M3">
-        <v>-2.53</v>
+        <v>-3.27</v>
       </c>
       <c r="N3">
-        <v>8.94</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="O3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q3">
-        <v>8914.51</v>
+        <v>8902.950000000001</v>
       </c>
       <c r="R3">
-        <v>9053.09</v>
+        <v>9029.450000000001</v>
       </c>
       <c r="S3">
-        <v>9438.1</v>
+        <v>9419.52</v>
       </c>
       <c r="T3">
-        <v>9752.15</v>
+        <v>9747.940000000001</v>
       </c>
       <c r="U3">
-        <v>-7.93</v>
+        <v>-8.77</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1213,31 +1225,31 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>41.22</v>
+        <v>38.01</v>
       </c>
       <c r="AA3">
-        <v>-152.68</v>
+        <v>-149.3</v>
       </c>
       <c r="AB3">
-        <v>-164.09</v>
+        <v>-161.13</v>
       </c>
       <c r="AC3">
-        <v>11.41</v>
+        <v>11.84</v>
       </c>
       <c r="AD3">
-        <v>75.27</v>
+        <v>90.13</v>
       </c>
       <c r="AE3">
-        <v>64.23999999999999</v>
+        <v>75.86</v>
       </c>
       <c r="AF3">
-        <v>150.59</v>
+        <v>148.27</v>
       </c>
       <c r="AH3">
-        <v>9383.83</v>
+        <v>9332.309999999999</v>
       </c>
       <c r="AI3">
-        <v>8722.360000000001</v>
+        <v>8726.58</v>
       </c>
       <c r="AJ3">
         <v>9225.639999999999</v>
@@ -1246,7 +1258,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>41.51</v>
+        <v>40.18</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1260,10 +1272,10 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>10936.65</v>
+        <v>10944.35</v>
       </c>
       <c r="E4">
-        <v>1.22</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F4">
         <v>12639.05</v>
@@ -1272,43 +1284,43 @@
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-13.47</v>
+        <v>-13.41</v>
       </c>
       <c r="I4">
-        <v>5.83</v>
+        <v>5.9</v>
       </c>
       <c r="J4">
-        <v>-0.02</v>
+        <v>1.03</v>
       </c>
       <c r="K4">
-        <v>-3.67</v>
+        <v>-4.13</v>
       </c>
       <c r="L4">
-        <v>-6.56</v>
+        <v>-6.5</v>
       </c>
       <c r="M4">
-        <v>-12.39</v>
+        <v>-13.28</v>
       </c>
       <c r="N4">
-        <v>8.9</v>
+        <v>9.23</v>
       </c>
       <c r="O4">
         <v>20</v>
       </c>
       <c r="Q4">
-        <v>10810.88</v>
+        <v>10833.09</v>
       </c>
       <c r="R4">
-        <v>10936.77</v>
+        <v>10920.49</v>
       </c>
       <c r="S4">
-        <v>11399.59</v>
+        <v>11375.62</v>
       </c>
       <c r="T4">
-        <v>11475.24</v>
+        <v>11468.68</v>
       </c>
       <c r="U4">
-        <v>-4.69</v>
+        <v>-4.57</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1323,31 +1335,31 @@
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>44.7</v>
+        <v>45.05</v>
       </c>
       <c r="AA4">
-        <v>-154.89</v>
+        <v>-139.78</v>
       </c>
       <c r="AB4">
-        <v>-173.27</v>
+        <v>-166.58</v>
       </c>
       <c r="AC4">
-        <v>18.39</v>
+        <v>26.79</v>
       </c>
       <c r="AD4">
-        <v>69.8</v>
+        <v>88.78</v>
       </c>
       <c r="AE4">
-        <v>60.88</v>
+        <v>71.53</v>
       </c>
       <c r="AF4">
-        <v>158.95</v>
+        <v>158.79</v>
       </c>
       <c r="AH4">
-        <v>11220.07</v>
+        <v>11156.63</v>
       </c>
       <c r="AI4">
-        <v>10653.47</v>
+        <v>10684.34</v>
       </c>
       <c r="AJ4">
         <v>11143.46</v>
@@ -1356,7 +1368,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>48.72</v>
+        <v>44.51</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1370,10 +1382,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>35261.85</v>
+        <v>34946.3</v>
       </c>
       <c r="E5">
-        <v>0.68</v>
+        <v>-0.89</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1382,43 +1394,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-15.1</v>
+        <v>-15.86</v>
       </c>
       <c r="I5">
-        <v>6.54</v>
+        <v>5.58</v>
       </c>
       <c r="J5">
-        <v>-1.98</v>
+        <v>-1.49</v>
       </c>
       <c r="K5">
-        <v>-5.62</v>
+        <v>-6.66</v>
       </c>
       <c r="L5">
-        <v>-10.22</v>
+        <v>-11.03</v>
       </c>
       <c r="M5">
-        <v>-0.58</v>
+        <v>-1.27</v>
       </c>
       <c r="N5">
-        <v>7.83</v>
+        <v>8.19</v>
       </c>
       <c r="O5">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="Q5">
-        <v>35076.09</v>
+        <v>34970.4</v>
       </c>
       <c r="R5">
-        <v>35997.64</v>
+        <v>35910.29</v>
       </c>
       <c r="S5">
-        <v>37183.32</v>
+        <v>37111.16</v>
       </c>
       <c r="T5">
-        <v>37737.86</v>
+        <v>37731.21</v>
       </c>
       <c r="U5">
-        <v>-6.56</v>
+        <v>-7.38</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1433,31 +1445,31 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>37.32</v>
+        <v>34.56</v>
       </c>
       <c r="AA5">
-        <v>-622.53</v>
+        <v>-628.84</v>
       </c>
       <c r="AB5">
-        <v>-558.17</v>
+        <v>-572.3</v>
       </c>
       <c r="AC5">
-        <v>-64.36</v>
+        <v>-56.54</v>
       </c>
       <c r="AD5">
-        <v>38.46</v>
+        <v>56.07</v>
       </c>
       <c r="AE5">
-        <v>23.72</v>
+        <v>37.93</v>
       </c>
       <c r="AF5">
-        <v>585.61</v>
+        <v>574.01</v>
       </c>
       <c r="AH5">
-        <v>37315.91</v>
+        <v>37265.49</v>
       </c>
       <c r="AI5">
-        <v>34679.37</v>
+        <v>34555.1</v>
       </c>
       <c r="AJ5">
         <v>36227.11</v>
@@ -1466,7 +1478,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>47.85</v>
+        <v>48.28</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1480,10 +1492,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>43118.2</v>
+        <v>42878.35</v>
       </c>
       <c r="E6">
-        <v>0.74</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1492,43 +1504,43 @@
         <v>42680.7</v>
       </c>
       <c r="H6">
-        <v>-24.05</v>
+        <v>-24.47</v>
       </c>
       <c r="I6">
-        <v>1.03</v>
+        <v>0.46</v>
       </c>
       <c r="J6">
-        <v>-1.95</v>
+        <v>-1.93</v>
       </c>
       <c r="K6">
-        <v>-5.77</v>
+        <v>-6.67</v>
       </c>
       <c r="L6">
-        <v>-11.55</v>
+        <v>-12.04</v>
       </c>
       <c r="M6">
-        <v>-22.8</v>
+        <v>-24.27</v>
       </c>
       <c r="N6">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="O6">
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>43085.16</v>
+        <v>42916.69</v>
       </c>
       <c r="R6">
-        <v>44231.32</v>
+        <v>44112.02</v>
       </c>
       <c r="S6">
-        <v>45540.48</v>
+        <v>45425.75</v>
       </c>
       <c r="T6">
-        <v>48802.15</v>
+        <v>48751.15</v>
       </c>
       <c r="U6">
-        <v>-11.65</v>
+        <v>-12.05</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1543,31 +1555,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>38.09</v>
+        <v>36.58</v>
       </c>
       <c r="AA6">
-        <v>-717.91</v>
+        <v>-734.02</v>
       </c>
       <c r="AB6">
-        <v>-605.88</v>
+        <v>-631.51</v>
       </c>
       <c r="AC6">
-        <v>-112.02</v>
+        <v>-102.51</v>
       </c>
       <c r="AD6">
-        <v>12.06</v>
+        <v>18.39</v>
       </c>
       <c r="AE6">
-        <v>18.55</v>
+        <v>14.95</v>
       </c>
       <c r="AF6">
-        <v>745.9299999999999</v>
+        <v>755.34</v>
       </c>
       <c r="AH6">
-        <v>45863.2</v>
+        <v>45774.49</v>
       </c>
       <c r="AI6">
-        <v>42599.45</v>
+        <v>42449.55</v>
       </c>
       <c r="AJ6">
         <v>44659.77</v>
@@ -1576,7 +1588,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>40.08</v>
+        <v>41.22</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1590,10 +1602,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>24303.75</v>
+        <v>24418.25</v>
       </c>
       <c r="E7">
-        <v>-0.62</v>
+        <v>0.47</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1602,43 +1614,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-14.61</v>
+        <v>-14.21</v>
       </c>
       <c r="I7">
-        <v>3.32</v>
+        <v>3.81</v>
       </c>
       <c r="J7">
-        <v>-2.73</v>
+        <v>-1.11</v>
       </c>
       <c r="K7">
-        <v>-2.61</v>
+        <v>-2.7</v>
       </c>
       <c r="L7">
-        <v>-9.66</v>
+        <v>-9.24</v>
       </c>
       <c r="M7">
-        <v>-11.24</v>
+        <v>-11.33</v>
       </c>
       <c r="N7">
-        <v>4.5</v>
+        <v>5.16</v>
       </c>
       <c r="O7">
         <v>15</v>
       </c>
       <c r="Q7">
-        <v>24502.05</v>
+        <v>24447.41</v>
       </c>
       <c r="R7">
-        <v>24797.29</v>
+        <v>24784.62</v>
       </c>
       <c r="S7">
-        <v>25402.94</v>
+        <v>25367.03</v>
       </c>
       <c r="T7">
-        <v>26206.75</v>
+        <v>26189.34</v>
       </c>
       <c r="U7">
-        <v>-7.26</v>
+        <v>-6.76</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1653,40 +1665,40 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>36.45</v>
+        <v>39.23</v>
       </c>
       <c r="AA7">
-        <v>-237.38</v>
+        <v>-244.41</v>
       </c>
       <c r="AB7">
-        <v>-204.9</v>
+        <v>-212.8</v>
       </c>
       <c r="AC7">
-        <v>-32.48</v>
+        <v>-31.61</v>
       </c>
       <c r="AD7">
-        <v>14.75</v>
+        <v>13.82</v>
       </c>
       <c r="AE7">
-        <v>28.31</v>
+        <v>19.34</v>
       </c>
       <c r="AF7">
-        <v>359.74</v>
+        <v>359.21</v>
       </c>
       <c r="AH7">
-        <v>25394.53</v>
+        <v>25403.45</v>
       </c>
       <c r="AI7">
-        <v>24200.05</v>
+        <v>24165.79</v>
       </c>
       <c r="AJ7">
-        <v>25420.21</v>
+        <v>25375.42</v>
       </c>
       <c r="AK7" t="s">
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>34.05</v>
+        <v>36.79</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1700,10 +1712,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>32189.45</v>
+        <v>31553.4</v>
       </c>
       <c r="E8">
-        <v>-0.26</v>
+        <v>-1.98</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1712,46 +1724,46 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-18.48</v>
+        <v>-20.09</v>
       </c>
       <c r="I8">
-        <v>24.91</v>
+        <v>22.44</v>
       </c>
       <c r="J8">
-        <v>2.14</v>
+        <v>-2.68</v>
       </c>
       <c r="K8">
-        <v>14.11</v>
+        <v>12.05</v>
       </c>
       <c r="L8">
-        <v>9.33</v>
+        <v>3.73</v>
       </c>
       <c r="M8">
-        <v>-9.4</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="N8">
-        <v>-1.94</v>
+        <v>-2</v>
       </c>
       <c r="O8">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q8">
-        <v>32192.35</v>
+        <v>32018.53</v>
       </c>
       <c r="R8">
-        <v>29787.28</v>
+        <v>29960.63</v>
       </c>
       <c r="S8">
-        <v>29884.07</v>
+        <v>29887.98</v>
       </c>
       <c r="T8">
-        <v>30758.49</v>
+        <v>30724.65</v>
       </c>
       <c r="U8">
-        <v>4.65</v>
+        <v>2.7</v>
       </c>
       <c r="V8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="W8" t="b">
         <v>0</v>
@@ -1760,34 +1772,34 @@
         <v>79</v>
       </c>
       <c r="Y8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z8">
-        <v>68.48999999999999</v>
+        <v>61</v>
       </c>
       <c r="AA8">
-        <v>852.5599999999999</v>
+        <v>821.0599999999999</v>
       </c>
       <c r="AB8">
-        <v>483.87</v>
+        <v>551.3099999999999</v>
       </c>
       <c r="AC8">
-        <v>368.69</v>
+        <v>269.75</v>
       </c>
       <c r="AD8">
-        <v>88.15000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="AE8">
-        <v>89.38</v>
+        <v>86.34</v>
       </c>
       <c r="AF8">
-        <v>842.75</v>
+        <v>872.65</v>
       </c>
       <c r="AH8">
-        <v>33579.56</v>
+        <v>33742.49</v>
       </c>
       <c r="AI8">
-        <v>25995.01</v>
+        <v>26178.76</v>
       </c>
       <c r="AJ8">
         <v>29979.37</v>
@@ -1796,7 +1808,7 @@
         <v>82</v>
       </c>
       <c r="AL8">
-        <v>51.65</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1810,10 +1822,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>14878.4</v>
+        <v>14931.6</v>
       </c>
       <c r="E9">
-        <v>1.45</v>
+        <v>0.36</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1822,34 +1834,34 @@
         <v>14516.75</v>
       </c>
       <c r="H9">
-        <v>-10.71</v>
+        <v>-10.39</v>
       </c>
       <c r="I9">
-        <v>2.49</v>
+        <v>2.86</v>
       </c>
       <c r="J9">
-        <v>-1.33</v>
+        <v>0.61</v>
       </c>
       <c r="K9">
-        <v>-5.89</v>
+        <v>-5.98</v>
       </c>
       <c r="L9">
-        <v>-7.1</v>
+        <v>-6.33</v>
       </c>
       <c r="N9">
-        <v>-12.81</v>
+        <v>-11.89</v>
       </c>
       <c r="O9">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Q9">
-        <v>14730.12</v>
+        <v>14748.08</v>
       </c>
       <c r="R9">
-        <v>15089.24</v>
+        <v>15053.77</v>
       </c>
       <c r="S9">
-        <v>15774.39</v>
+        <v>15742.12</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1861,31 +1873,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>39.72</v>
+        <v>41.48</v>
       </c>
       <c r="AA9">
-        <v>-288.4</v>
+        <v>-267.38</v>
       </c>
       <c r="AB9">
-        <v>-281.68</v>
+        <v>-278.82</v>
       </c>
       <c r="AC9">
-        <v>-6.72</v>
+        <v>11.44</v>
       </c>
       <c r="AD9">
-        <v>51.08</v>
+        <v>82.95</v>
       </c>
       <c r="AE9">
-        <v>35.83</v>
+        <v>54.25</v>
       </c>
       <c r="AF9">
-        <v>234.32</v>
+        <v>230.34</v>
       </c>
       <c r="AH9">
-        <v>15669.64</v>
+        <v>15575.96</v>
       </c>
       <c r="AI9">
-        <v>14508.85</v>
+        <v>14531.58</v>
       </c>
       <c r="AJ9">
         <v>15216.01</v>
@@ -1894,7 +1906,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>59.76</v>
+        <v>54.88</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1908,10 +1920,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8726.6</v>
+        <v>8690.049999999999</v>
       </c>
       <c r="E10">
-        <v>0.76</v>
+        <v>-0.42</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1920,43 +1932,43 @@
         <v>8499.65</v>
       </c>
       <c r="H10">
-        <v>-10.64</v>
+        <v>-11.02</v>
       </c>
       <c r="I10">
-        <v>2.67</v>
+        <v>2.24</v>
       </c>
       <c r="J10">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="K10">
-        <v>-2.44</v>
+        <v>-2.99</v>
       </c>
       <c r="L10">
+        <v>-7.33</v>
+      </c>
+      <c r="M10">
         <v>-6.94</v>
       </c>
-      <c r="M10">
-        <v>-6.22</v>
-      </c>
       <c r="N10">
-        <v>11.14</v>
+        <v>11.33</v>
       </c>
       <c r="O10">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="Q10">
-        <v>8633.629999999999</v>
+        <v>8644.84</v>
       </c>
       <c r="R10">
-        <v>8653.09</v>
+        <v>8648.459999999999</v>
       </c>
       <c r="S10">
-        <v>8967.860000000001</v>
+        <v>8953.280000000001</v>
       </c>
       <c r="T10">
-        <v>9216.85</v>
+        <v>9211.469999999999</v>
       </c>
       <c r="U10">
-        <v>-5.32</v>
+        <v>-5.66</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1971,31 +1983,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>48.34</v>
+        <v>46.38</v>
       </c>
       <c r="AA10">
-        <v>-89.66</v>
+        <v>-80.48</v>
       </c>
       <c r="AB10">
-        <v>-115.65</v>
+        <v>-108.62</v>
       </c>
       <c r="AC10">
-        <v>25.99</v>
+        <v>28.13</v>
       </c>
       <c r="AD10">
-        <v>83.61</v>
+        <v>95.77</v>
       </c>
       <c r="AE10">
-        <v>75.76000000000001</v>
+        <v>84.63</v>
       </c>
       <c r="AF10">
-        <v>133.15</v>
+        <v>130.12</v>
       </c>
       <c r="AH10">
-        <v>8830.66</v>
+        <v>8816.41</v>
       </c>
       <c r="AI10">
-        <v>8475.51</v>
+        <v>8480.52</v>
       </c>
       <c r="AJ10">
         <v>8855.59</v>
@@ -2004,7 +2016,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>28.68</v>
+        <v>25.59</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2018,10 +2030,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1615.05</v>
+        <v>1637.4</v>
       </c>
       <c r="E11">
-        <v>3.66</v>
+        <v>1.38</v>
       </c>
       <c r="F11">
         <v>1648.25</v>
@@ -2030,43 +2042,43 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-2.01</v>
+        <v>-0.66</v>
       </c>
       <c r="I11">
-        <v>28.86</v>
+        <v>30.64</v>
       </c>
       <c r="J11">
-        <v>-1.75</v>
+        <v>0.91</v>
       </c>
       <c r="K11">
-        <v>3.91</v>
+        <v>5.59</v>
       </c>
       <c r="L11">
-        <v>6.15</v>
+        <v>7.62</v>
       </c>
       <c r="M11">
-        <v>4.62</v>
+        <v>7.75</v>
       </c>
       <c r="N11">
-        <v>-6.73</v>
+        <v>-6.01</v>
       </c>
       <c r="O11">
         <v>95</v>
       </c>
       <c r="Q11">
-        <v>1588.74</v>
+        <v>1591.69</v>
       </c>
       <c r="R11">
-        <v>1587.75</v>
+        <v>1592.66</v>
       </c>
       <c r="S11">
-        <v>1574.89</v>
+        <v>1575.84</v>
       </c>
       <c r="T11">
-        <v>1470.76</v>
+        <v>1471.63</v>
       </c>
       <c r="U11">
-        <v>9.81</v>
+        <v>11.26</v>
       </c>
       <c r="V11" t="s">
         <v>80</v>
@@ -2081,31 +2093,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>55.08</v>
+        <v>58.26</v>
       </c>
       <c r="AA11">
-        <v>10.16</v>
+        <v>12.71</v>
       </c>
       <c r="AB11">
-        <v>12.77</v>
+        <v>12.76</v>
       </c>
       <c r="AC11">
-        <v>-2.61</v>
+        <v>-0.05</v>
       </c>
       <c r="AD11">
-        <v>18.77</v>
+        <v>41.09</v>
       </c>
       <c r="AE11">
-        <v>18.99</v>
+        <v>22.82</v>
       </c>
       <c r="AF11">
-        <v>39.04</v>
+        <v>40.31</v>
       </c>
       <c r="AH11">
-        <v>1665.67</v>
+        <v>1670.08</v>
       </c>
       <c r="AI11">
-        <v>1509.84</v>
+        <v>1515.25</v>
       </c>
       <c r="AJ11">
         <v>1544.25</v>
@@ -2114,7 +2126,7 @@
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>25.12</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2128,10 +2140,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>11806.7</v>
+        <v>11769.35</v>
       </c>
       <c r="E12">
-        <v>0.64</v>
+        <v>-0.32</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2140,43 +2152,43 @@
         <v>10017.9</v>
       </c>
       <c r="H12">
-        <v>-13.93</v>
+        <v>-14.21</v>
       </c>
       <c r="I12">
-        <v>17.86</v>
+        <v>17.48</v>
       </c>
       <c r="J12">
-        <v>-2.15</v>
+        <v>-0.76</v>
       </c>
       <c r="K12">
-        <v>-9.470000000000001</v>
+        <v>-10.07</v>
       </c>
       <c r="L12">
-        <v>-5.07</v>
+        <v>-5.37</v>
       </c>
       <c r="M12">
-        <v>14.77</v>
+        <v>15.39</v>
       </c>
       <c r="N12">
-        <v>15.51</v>
+        <v>16.25</v>
       </c>
       <c r="O12">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="Q12">
-        <v>11734.87</v>
+        <v>11716.83</v>
       </c>
       <c r="R12">
-        <v>12162.2</v>
+        <v>12107.94</v>
       </c>
       <c r="S12">
-        <v>12749.16</v>
+        <v>12725.71</v>
       </c>
       <c r="T12">
-        <v>12484.57</v>
+        <v>12486.31</v>
       </c>
       <c r="U12">
-        <v>-5.43</v>
+        <v>-5.74</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2191,31 +2203,31 @@
         <v>1</v>
       </c>
       <c r="Z12">
-        <v>38.41</v>
+        <v>37.69</v>
       </c>
       <c r="AA12">
-        <v>-303.39</v>
+        <v>-294.75</v>
       </c>
       <c r="AB12">
-        <v>-281.17</v>
+        <v>-283.89</v>
       </c>
       <c r="AC12">
-        <v>-22.22</v>
+        <v>-10.86</v>
       </c>
       <c r="AD12">
-        <v>51.64</v>
+        <v>80.5</v>
       </c>
       <c r="AE12">
-        <v>34.55</v>
+        <v>54.26</v>
       </c>
       <c r="AF12">
-        <v>260.15</v>
+        <v>252.11</v>
       </c>
       <c r="AH12">
-        <v>12969.91</v>
+        <v>12864</v>
       </c>
       <c r="AI12">
-        <v>11354.48</v>
+        <v>11351.88</v>
       </c>
       <c r="AJ12">
         <v>12304.47</v>
@@ -2224,7 +2236,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>55.08</v>
+        <v>53.74</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2238,10 +2250,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9048.6</v>
+        <v>8993.65</v>
       </c>
       <c r="E13">
-        <v>0.71</v>
+        <v>-0.61</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2250,43 +2262,43 @@
         <v>8885.75</v>
       </c>
       <c r="H13">
-        <v>-15.95</v>
+        <v>-16.46</v>
       </c>
       <c r="I13">
-        <v>1.83</v>
+        <v>1.21</v>
       </c>
       <c r="J13">
-        <v>-1.55</v>
+        <v>-1.11</v>
       </c>
       <c r="K13">
-        <v>-5.3</v>
+        <v>-6.05</v>
       </c>
       <c r="L13">
-        <v>-8.949999999999999</v>
+        <v>-9.51</v>
       </c>
       <c r="M13">
-        <v>-8.890000000000001</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="N13">
-        <v>16.93</v>
+        <v>17.37</v>
       </c>
       <c r="O13">
         <v>25</v>
       </c>
       <c r="Q13">
-        <v>9009.610000000001</v>
+        <v>8989.459999999999</v>
       </c>
       <c r="R13">
-        <v>9178.629999999999</v>
+        <v>9158.799999999999</v>
       </c>
       <c r="S13">
-        <v>9483.889999999999</v>
+        <v>9466.860000000001</v>
       </c>
       <c r="T13">
-        <v>9974.07</v>
+        <v>9968.389999999999</v>
       </c>
       <c r="U13">
-        <v>-9.279999999999999</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2301,31 +2313,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>38.86</v>
+        <v>36.72</v>
       </c>
       <c r="AA13">
-        <v>-138.98</v>
+        <v>-138.01</v>
       </c>
       <c r="AB13">
-        <v>-133.2</v>
+        <v>-134.16</v>
       </c>
       <c r="AC13">
-        <v>-5.78</v>
+        <v>-3.85</v>
       </c>
       <c r="AD13">
-        <v>49.48</v>
+        <v>65.44</v>
       </c>
       <c r="AE13">
-        <v>43.09</v>
+        <v>51.42</v>
       </c>
       <c r="AF13">
-        <v>140.87</v>
+        <v>139.2</v>
       </c>
       <c r="AH13">
-        <v>9462.52</v>
+        <v>9435.77</v>
       </c>
       <c r="AI13">
-        <v>8894.75</v>
+        <v>8881.84</v>
       </c>
       <c r="AJ13">
         <v>9317.65</v>
@@ -2334,7 +2346,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>55.09</v>
+        <v>54.51</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2348,55 +2360,55 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8126.7</v>
+        <v>8133.6</v>
       </c>
       <c r="E14">
-        <v>0.41</v>
+        <v>0.08</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
       </c>
       <c r="G14">
-        <v>7638.75</v>
+        <v>7817.4</v>
       </c>
       <c r="H14">
-        <v>-17.74</v>
+        <v>-17.67</v>
       </c>
       <c r="I14">
-        <v>6.39</v>
+        <v>4.04</v>
       </c>
       <c r="J14">
-        <v>-2.02</v>
+        <v>-1.43</v>
       </c>
       <c r="K14">
-        <v>-1.75</v>
+        <v>-1.94</v>
       </c>
       <c r="L14">
-        <v>-3.04</v>
+        <v>-2.96</v>
       </c>
       <c r="M14">
-        <v>5.7</v>
+        <v>6.48</v>
       </c>
       <c r="N14">
-        <v>22.57</v>
+        <v>23.91</v>
       </c>
       <c r="O14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Q14">
-        <v>8160.02</v>
+        <v>8136.44</v>
       </c>
       <c r="R14">
-        <v>8088.11</v>
+        <v>8093.48</v>
       </c>
       <c r="S14">
-        <v>8317.27</v>
+        <v>8305.17</v>
       </c>
       <c r="T14">
-        <v>8567.139999999999</v>
+        <v>8564.309999999999</v>
       </c>
       <c r="U14">
-        <v>-5.14</v>
+        <v>-5.03</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2411,31 +2423,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>47.39</v>
+        <v>47.75</v>
       </c>
       <c r="AA14">
-        <v>-35.78</v>
+        <v>-33.56</v>
       </c>
       <c r="AB14">
-        <v>-53.01</v>
+        <v>-49.12</v>
       </c>
       <c r="AC14">
-        <v>17.24</v>
+        <v>15.57</v>
       </c>
       <c r="AD14">
-        <v>52.88</v>
+        <v>57.29</v>
       </c>
       <c r="AE14">
-        <v>64.8</v>
+        <v>58.17</v>
       </c>
       <c r="AF14">
-        <v>153.41</v>
+        <v>150.48</v>
       </c>
       <c r="AH14">
-        <v>8283.58</v>
+        <v>8287.68</v>
       </c>
       <c r="AI14">
-        <v>7892.63</v>
+        <v>7899.28</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
@@ -2444,7 +2456,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>19.15</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2458,10 +2470,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26267.25</v>
+        <v>26541.35</v>
       </c>
       <c r="E15">
-        <v>1.91</v>
+        <v>1.04</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2470,43 +2482,43 @@
         <v>21549.55</v>
       </c>
       <c r="H15">
-        <v>-3.38</v>
+        <v>-2.37</v>
       </c>
       <c r="I15">
-        <v>21.89</v>
+        <v>23.16</v>
       </c>
       <c r="J15">
-        <v>2.55</v>
+        <v>3.82</v>
       </c>
       <c r="K15">
-        <v>-2.82</v>
+        <v>-1.71</v>
       </c>
       <c r="L15">
-        <v>1.24</v>
+        <v>2.09</v>
       </c>
       <c r="M15">
-        <v>18.84</v>
+        <v>19.27</v>
       </c>
       <c r="N15">
-        <v>13.26</v>
+        <v>14.01</v>
       </c>
       <c r="O15">
         <v>99</v>
       </c>
       <c r="Q15">
-        <v>25706.7</v>
+        <v>25901.79</v>
       </c>
       <c r="R15">
-        <v>26048.61</v>
+        <v>26037.59</v>
       </c>
       <c r="S15">
-        <v>26413.13</v>
+        <v>26415.04</v>
       </c>
       <c r="T15">
-        <v>24415.13</v>
+        <v>24433.89</v>
       </c>
       <c r="U15">
-        <v>7.59</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2521,31 +2533,31 @@
         <v>2</v>
       </c>
       <c r="Z15">
-        <v>53.07</v>
+        <v>57.28</v>
       </c>
       <c r="AA15">
-        <v>-211.57</v>
+        <v>-142.71</v>
       </c>
       <c r="AB15">
-        <v>-217.39</v>
+        <v>-202.45</v>
       </c>
       <c r="AC15">
-        <v>5.82</v>
+        <v>59.75</v>
       </c>
       <c r="AD15">
-        <v>56.24</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="AE15">
-        <v>27.84</v>
+        <v>56.96</v>
       </c>
       <c r="AF15">
-        <v>425.24</v>
+        <v>431.92</v>
       </c>
       <c r="AH15">
-        <v>26902.8</v>
+        <v>26858.08</v>
       </c>
       <c r="AI15">
-        <v>25194.42</v>
+        <v>25217.1</v>
       </c>
       <c r="AJ15">
         <v>26568.83</v>
@@ -2554,7 +2566,7 @@
         <v>81</v>
       </c>
       <c r="AL15">
-        <v>42.54</v>
+        <v>40.21</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2568,10 +2580,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>805.05</v>
+        <v>797.85</v>
       </c>
       <c r="E16">
-        <v>1.94</v>
+        <v>-0.89</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2580,43 +2592,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-16.89</v>
+        <v>-17.63</v>
       </c>
       <c r="I16">
-        <v>23.64</v>
+        <v>22.53</v>
       </c>
       <c r="J16">
-        <v>-1.35</v>
+        <v>-0.99</v>
       </c>
       <c r="K16">
-        <v>-6.54</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="L16">
-        <v>-12.37</v>
+        <v>-13.15</v>
       </c>
       <c r="M16">
-        <v>-13.7</v>
+        <v>-14.55</v>
       </c>
       <c r="N16">
-        <v>9.31</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="O16">
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>797.6799999999999</v>
+        <v>796.08</v>
       </c>
       <c r="R16">
-        <v>819.46</v>
+        <v>816.8099999999999</v>
       </c>
       <c r="S16">
-        <v>857.72</v>
+        <v>855.77</v>
       </c>
       <c r="T16">
-        <v>821.91</v>
+        <v>821.41</v>
       </c>
       <c r="U16">
-        <v>-2.05</v>
+        <v>-2.87</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2631,31 +2643,31 @@
         <v>1</v>
       </c>
       <c r="Z16">
-        <v>41.89</v>
+        <v>39.78</v>
       </c>
       <c r="AA16">
-        <v>-16.35</v>
+        <v>-16.08</v>
       </c>
       <c r="AB16">
-        <v>-15.59</v>
+        <v>-15.69</v>
       </c>
       <c r="AC16">
-        <v>-0.76</v>
+        <v>-0.4</v>
       </c>
       <c r="AD16">
-        <v>38.92</v>
+        <v>56.69</v>
       </c>
       <c r="AE16">
-        <v>34.06</v>
+        <v>41.19</v>
       </c>
       <c r="AF16">
-        <v>18.87</v>
+        <v>18.08</v>
       </c>
       <c r="AH16">
-        <v>857.41</v>
+        <v>852.87</v>
       </c>
       <c r="AI16">
-        <v>781.52</v>
+        <v>780.75</v>
       </c>
       <c r="AJ16">
         <v>838.5700000000001</v>
@@ -2664,7 +2676,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>37.76</v>
+        <v>36.12</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2678,10 +2690,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30236</v>
+        <v>30022.85</v>
       </c>
       <c r="E17">
-        <v>0.24</v>
+        <v>-0.7</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2690,43 +2702,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-11.33</v>
+        <v>-11.96</v>
       </c>
       <c r="I17">
-        <v>6.6</v>
+        <v>5.85</v>
       </c>
       <c r="J17">
-        <v>0.45</v>
+        <v>-0.47</v>
       </c>
       <c r="K17">
-        <v>2.36</v>
+        <v>1.38</v>
       </c>
       <c r="L17">
-        <v>-3.83</v>
+        <v>-4.51</v>
       </c>
       <c r="M17">
-        <v>-9.43</v>
+        <v>-10.28</v>
       </c>
       <c r="N17">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="O17">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Q17">
-        <v>30098.99</v>
+        <v>30070.81</v>
       </c>
       <c r="R17">
-        <v>29511.11</v>
+        <v>29552.57</v>
       </c>
       <c r="S17">
-        <v>30044.81</v>
+        <v>30022.7</v>
       </c>
       <c r="T17">
-        <v>30934.83</v>
+        <v>30914.71</v>
       </c>
       <c r="U17">
-        <v>-2.26</v>
+        <v>-2.88</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2741,31 +2753,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>57.27</v>
+        <v>53.23</v>
       </c>
       <c r="AA17">
-        <v>76.23</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="AB17">
-        <v>-59.28</v>
+        <v>-31.32</v>
       </c>
       <c r="AC17">
-        <v>135.51</v>
+        <v>111.84</v>
       </c>
       <c r="AD17">
-        <v>81.06</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="AE17">
-        <v>79.45999999999999</v>
+        <v>80.27</v>
       </c>
       <c r="AF17">
-        <v>427.33</v>
+        <v>436.11</v>
       </c>
       <c r="AH17">
-        <v>30633.6</v>
+        <v>30686.88</v>
       </c>
       <c r="AI17">
-        <v>28388.63</v>
+        <v>28418.26</v>
       </c>
       <c r="AJ17">
         <v>29148.67</v>
@@ -2774,7 +2786,7 @@
         <v>82</v>
       </c>
       <c r="AL17">
-        <v>25.51</v>
+        <v>24.59</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2788,10 +2800,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>15917.6</v>
+        <v>16100.1</v>
       </c>
       <c r="E18">
-        <v>1.65</v>
+        <v>1.15</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2800,34 +2812,34 @@
         <v>15387</v>
       </c>
       <c r="H18">
-        <v>-6.04</v>
+        <v>-4.97</v>
       </c>
       <c r="I18">
-        <v>3.45</v>
+        <v>4.63</v>
       </c>
       <c r="J18">
-        <v>2.31</v>
+        <v>3.82</v>
       </c>
       <c r="K18">
-        <v>-5.01</v>
+        <v>-3.47</v>
       </c>
       <c r="L18">
-        <v>-3.37</v>
+        <v>-2.41</v>
       </c>
       <c r="N18">
-        <v>6.4</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="O18">
         <v>75</v>
       </c>
       <c r="Q18">
-        <v>15597.14</v>
+        <v>15715.73</v>
       </c>
       <c r="R18">
-        <v>15864.55</v>
+        <v>15842.7</v>
       </c>
       <c r="S18">
-        <v>16292.32</v>
+        <v>16284.21</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2839,40 +2851,40 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>48.79</v>
+        <v>53.85</v>
       </c>
       <c r="AA18">
-        <v>-213.04</v>
+        <v>-167.94</v>
       </c>
       <c r="AB18">
-        <v>-223.44</v>
+        <v>-212.34</v>
       </c>
       <c r="AC18">
-        <v>10.4</v>
+        <v>44.4</v>
       </c>
       <c r="AD18">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="AE18">
-        <v>35.07</v>
+        <v>67.41</v>
       </c>
       <c r="AF18">
-        <v>253.07</v>
+        <v>259.68</v>
       </c>
       <c r="AH18">
-        <v>16498.59</v>
+        <v>16405.23</v>
       </c>
       <c r="AI18">
-        <v>15230.51</v>
+        <v>15280.17</v>
       </c>
       <c r="AJ18">
-        <v>16084.17</v>
+        <v>15174.9</v>
       </c>
       <c r="AK18" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL18">
-        <v>57.37</v>
+        <v>51.79</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2886,10 +2898,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>8819.9</v>
+        <v>8782.700000000001</v>
       </c>
       <c r="E19">
-        <v>1.82</v>
+        <v>-0.42</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2898,34 +2910,34 @@
         <v>8561.200000000001</v>
       </c>
       <c r="H19">
-        <v>-11.79</v>
+        <v>-12.16</v>
       </c>
       <c r="I19">
-        <v>3.02</v>
+        <v>2.59</v>
       </c>
       <c r="J19">
-        <v>-3.34</v>
+        <v>-1.29</v>
       </c>
       <c r="K19">
-        <v>-5.79</v>
+        <v>-6.58</v>
       </c>
       <c r="L19">
-        <v>-6.37</v>
+        <v>-4.69</v>
       </c>
       <c r="N19">
-        <v>-5.12</v>
+        <v>-6.14</v>
       </c>
       <c r="O19">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="Q19">
-        <v>8745.99</v>
+        <v>8723.09</v>
       </c>
       <c r="R19">
-        <v>9071.450000000001</v>
+        <v>9049.02</v>
       </c>
       <c r="S19">
-        <v>9416.32</v>
+        <v>9395.74</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2937,31 +2949,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>40.05</v>
+        <v>39.1</v>
       </c>
       <c r="AA19">
-        <v>-176.02</v>
+        <v>-175.46</v>
       </c>
       <c r="AB19">
-        <v>-139.64</v>
+        <v>-146.8</v>
       </c>
       <c r="AC19">
-        <v>-36.38</v>
+        <v>-28.66</v>
       </c>
       <c r="AD19">
-        <v>25.93</v>
+        <v>42.68</v>
       </c>
       <c r="AE19">
-        <v>11.84</v>
+        <v>25.39</v>
       </c>
       <c r="AF19">
-        <v>194.45</v>
+        <v>190.59</v>
       </c>
       <c r="AH19">
-        <v>9512.83</v>
+        <v>9501.66</v>
       </c>
       <c r="AI19">
-        <v>8630.07</v>
+        <v>8596.389999999999</v>
       </c>
       <c r="AJ19">
         <v>9128.139999999999</v>
@@ -2970,7 +2982,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>39.07</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2984,46 +2996,46 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10536</v>
+        <v>10296.6</v>
       </c>
       <c r="E20">
-        <v>0.14</v>
+        <v>-2.27</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
       </c>
       <c r="G20">
-        <v>10299.4</v>
+        <v>10296.6</v>
       </c>
       <c r="H20">
-        <v>-7.33</v>
+        <v>-9.43</v>
       </c>
       <c r="I20">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J20">
-        <v>-0.08</v>
+        <v>-2.27</v>
       </c>
       <c r="K20">
-        <v>-3.07</v>
+        <v>-5.21</v>
       </c>
       <c r="L20">
-        <v>-4.9</v>
+        <v>-6.97</v>
       </c>
       <c r="N20">
-        <v>-11.12</v>
+        <v>-16.29</v>
       </c>
       <c r="O20">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="Q20">
-        <v>10483.89</v>
+        <v>10435.95</v>
       </c>
       <c r="R20">
-        <v>10502.95</v>
+        <v>10484.75</v>
       </c>
       <c r="S20">
-        <v>10840.71</v>
+        <v>10822.64</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3035,31 +3047,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>45.86</v>
+        <v>36.6</v>
       </c>
       <c r="AA20">
-        <v>-98.93000000000001</v>
+        <v>-108.45</v>
       </c>
       <c r="AB20">
-        <v>-123.06</v>
+        <v>-120.13</v>
       </c>
       <c r="AC20">
-        <v>24.13</v>
+        <v>11.69</v>
       </c>
       <c r="AD20">
-        <v>80.69</v>
+        <v>80.23</v>
       </c>
       <c r="AE20">
-        <v>72.48999999999999</v>
+        <v>76.92</v>
       </c>
       <c r="AF20">
-        <v>163.46</v>
+        <v>169.92</v>
       </c>
       <c r="AH20">
-        <v>10726.14</v>
+        <v>10713.11</v>
       </c>
       <c r="AI20">
-        <v>10279.76</v>
+        <v>10256.38</v>
       </c>
       <c r="AJ20">
         <v>10732.68</v>
@@ -3068,7 +3080,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>26.77</v>
+        <v>28.07</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3082,10 +3094,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>26628.45</v>
+        <v>26722.1</v>
       </c>
       <c r="E21">
-        <v>-0.73</v>
+        <v>0.35</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3094,43 +3106,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-8.77</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="I21">
-        <v>10.29</v>
+        <v>10.67</v>
       </c>
       <c r="J21">
-        <v>-2.06</v>
+        <v>-0.68</v>
       </c>
       <c r="K21">
-        <v>-0.51</v>
+        <v>-0.6</v>
       </c>
       <c r="L21">
-        <v>-6.59</v>
+        <v>-6.27</v>
       </c>
       <c r="M21">
-        <v>-5.36</v>
+        <v>-5.37</v>
       </c>
       <c r="N21">
-        <v>4.79</v>
+        <v>5.46</v>
       </c>
       <c r="O21">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="Q21">
-        <v>26776.09</v>
+        <v>26739.64</v>
       </c>
       <c r="R21">
-        <v>26969.77</v>
+        <v>26982.05</v>
       </c>
       <c r="S21">
-        <v>27241.78</v>
+        <v>27231.28</v>
       </c>
       <c r="T21">
-        <v>27383.87</v>
+        <v>27372.97</v>
       </c>
       <c r="U21">
-        <v>-2.76</v>
+        <v>-2.38</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3145,31 +3157,31 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>41.43</v>
+        <v>43.45</v>
       </c>
       <c r="AA21">
-        <v>-105.34</v>
+        <v>-116.9</v>
       </c>
       <c r="AB21">
-        <v>-65.59</v>
+        <v>-75.84999999999999</v>
       </c>
       <c r="AC21">
-        <v>-39.76</v>
+        <v>-41.05</v>
       </c>
       <c r="AD21">
-        <v>9.16</v>
+        <v>11.3</v>
       </c>
       <c r="AE21">
-        <v>15.17</v>
+        <v>12.38</v>
       </c>
       <c r="AF21">
-        <v>382.46</v>
+        <v>382.65</v>
       </c>
       <c r="AH21">
-        <v>27675.9</v>
+        <v>27660.04</v>
       </c>
       <c r="AI21">
-        <v>26263.63</v>
+        <v>26304.06</v>
       </c>
       <c r="AJ21">
         <v>26545.98</v>
@@ -3178,7 +3190,7 @@
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>29.24</v>
+        <v>30.8</v>
       </c>
     </row>
   </sheetData>
@@ -3319,7 +3331,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F154"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3379,1379 +3391,1382 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="E5" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="6">
-        <v>-8.050000000000001</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-5.2</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2.85</v>
+      <c r="B8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C9" s="6">
-        <v>-7.4</v>
+        <v>-5.2</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.64</v>
+        <v>-4.67</v>
       </c>
       <c r="E9" s="7">
-        <v>1.76</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C10" s="6">
-        <v>-6.42</v>
+        <v>-5.64</v>
       </c>
       <c r="D10" s="6">
-        <v>-3.67</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.75</v>
+        <v>-6.78</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.14</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-7.25</v>
+        <v>-3.67</v>
       </c>
       <c r="D11" s="6">
-        <v>-5.62</v>
-      </c>
-      <c r="E11" s="7">
-        <v>1.63</v>
+        <v>-4.13</v>
+      </c>
+      <c r="E11" s="8">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-7.48</v>
+        <v>-5.62</v>
       </c>
       <c r="D12" s="6">
-        <v>-5.77</v>
-      </c>
-      <c r="E12" s="7">
-        <v>1.71</v>
+        <v>-6.66</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-1.04</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-4.34</v>
+        <v>-5.77</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.61</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.73</v>
+        <v>-6.67</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.9</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>13.9</v>
+        <v>-2.61</v>
       </c>
       <c r="D14" s="6">
-        <v>14.11</v>
-      </c>
-      <c r="E14" s="7">
-        <v>0.21</v>
+        <v>-2.7</v>
+      </c>
+      <c r="E14" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-8.44</v>
+        <v>14.11</v>
       </c>
       <c r="D15" s="6">
-        <v>-5.89</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.55</v>
+        <v>12.05</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-2.06</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-4.77</v>
+        <v>-5.89</v>
       </c>
       <c r="D16" s="6">
-        <v>-2.44</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.33</v>
+        <v>-5.98</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-0.5600000000000001</v>
+        <v>-2.44</v>
       </c>
       <c r="D17" s="6">
-        <v>3.91</v>
-      </c>
-      <c r="E17" s="7">
-        <v>4.47</v>
+        <v>-2.99</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-11.81</v>
+        <v>3.91</v>
       </c>
       <c r="D18" s="6">
-        <v>-9.470000000000001</v>
+        <v>5.59</v>
       </c>
       <c r="E18" s="7">
-        <v>2.34</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-6.77</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="D19" s="6">
-        <v>-5.3</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.47</v>
+        <v>-10.07</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-3.25</v>
+        <v>-5.3</v>
       </c>
       <c r="D20" s="6">
-        <v>-1.75</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.5</v>
+        <v>-6.05</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.75</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-5.07</v>
+        <v>-1.75</v>
       </c>
       <c r="D21" s="6">
-        <v>-2.82</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.25</v>
+        <v>-1.94</v>
+      </c>
+      <c r="E21" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-9.33</v>
+        <v>-2.82</v>
       </c>
       <c r="D22" s="6">
-        <v>-6.54</v>
+        <v>-1.71</v>
       </c>
       <c r="E22" s="7">
-        <v>2.79</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>0.33</v>
+        <v>-6.54</v>
       </c>
       <c r="D23" s="6">
-        <v>2.36</v>
-      </c>
-      <c r="E23" s="7">
-        <v>2.03</v>
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-7.17</v>
+        <v>2.36</v>
       </c>
       <c r="D24" s="6">
-        <v>-5.01</v>
-      </c>
-      <c r="E24" s="7">
-        <v>2.16</v>
+        <v>1.38</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-8.449999999999999</v>
+        <v>-5.01</v>
       </c>
       <c r="D25" s="6">
-        <v>-5.79</v>
+        <v>-3.47</v>
       </c>
       <c r="E25" s="7">
-        <v>2.66</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-4.4</v>
+        <v>-5.79</v>
       </c>
       <c r="D26" s="6">
-        <v>-3.07</v>
-      </c>
-      <c r="E26" s="7">
-        <v>1.33</v>
+        <v>-6.58</v>
+      </c>
+      <c r="E26" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-1.97</v>
+        <v>-3.07</v>
       </c>
       <c r="D27" s="6">
-        <v>-0.51</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.46</v>
+        <v>-5.21</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-3.1</v>
+        <v>-0.51</v>
       </c>
       <c r="D28" s="6">
-        <v>-0.98</v>
-      </c>
-      <c r="E28" s="7">
-        <v>2.12</v>
+        <v>-0.6</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.09</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-1.83</v>
+        <v>-0.98</v>
       </c>
       <c r="D29" s="6">
-        <v>-0.68</v>
+        <v>2.03</v>
       </c>
       <c r="E29" s="7">
-        <v>1.15</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>-2.26</v>
+        <v>-0.68</v>
       </c>
       <c r="D30" s="6">
-        <v>-0.02</v>
+        <v>-0.65</v>
       </c>
       <c r="E30" s="7">
-        <v>2.24</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-3.23</v>
+        <v>-0.02</v>
       </c>
       <c r="D31" s="6">
-        <v>-1.98</v>
+        <v>1.03</v>
       </c>
       <c r="E31" s="7">
-        <v>1.25</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-4.07</v>
+        <v>-1.98</v>
       </c>
       <c r="D32" s="6">
-        <v>-1.95</v>
+        <v>-1.49</v>
       </c>
       <c r="E32" s="7">
-        <v>2.12</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-3.67</v>
+        <v>-1.95</v>
       </c>
       <c r="D33" s="6">
-        <v>-2.73</v>
+        <v>-1.93</v>
       </c>
       <c r="E33" s="7">
-        <v>0.9399999999999999</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>1.09</v>
+        <v>-2.73</v>
       </c>
       <c r="D34" s="6">
-        <v>2.14</v>
+        <v>-1.11</v>
       </c>
       <c r="E34" s="7">
-        <v>1.05</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>-3.35</v>
+        <v>2.14</v>
       </c>
       <c r="D35" s="6">
-        <v>-1.33</v>
-      </c>
-      <c r="E35" s="7">
-        <v>2.02</v>
+        <v>-2.68</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-4.82</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-0.74</v>
+        <v>-1.33</v>
       </c>
       <c r="D36" s="6">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="E36" s="7">
-        <v>1.43</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-5.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D37" s="6">
-        <v>-1.75</v>
-      </c>
-      <c r="E37" s="7">
-        <v>3.72</v>
+        <v>0.65</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-3.31</v>
+        <v>-1.75</v>
       </c>
       <c r="D38" s="6">
-        <v>-2.15</v>
+        <v>0.91</v>
       </c>
       <c r="E38" s="7">
-        <v>1.16</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>-2.84</v>
+        <v>-2.15</v>
       </c>
       <c r="D39" s="6">
-        <v>-1.55</v>
+        <v>-0.76</v>
       </c>
       <c r="E39" s="7">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-0.01</v>
+        <v>-1.55</v>
       </c>
       <c r="D40" s="6">
-        <v>-2.02</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-2.01</v>
+        <v>-1.11</v>
+      </c>
+      <c r="E40" s="7">
+        <v>0.44</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>-0.03</v>
+        <v>-2.02</v>
       </c>
       <c r="D41" s="6">
-        <v>2.55</v>
+        <v>-1.43</v>
       </c>
       <c r="E41" s="7">
-        <v>2.58</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>-4.39</v>
+        <v>2.55</v>
       </c>
       <c r="D42" s="6">
-        <v>-1.35</v>
+        <v>3.82</v>
       </c>
       <c r="E42" s="7">
-        <v>3.04</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-1.05</v>
+        <v>-1.35</v>
       </c>
       <c r="D43" s="6">
-        <v>0.45</v>
+        <v>-0.99</v>
       </c>
       <c r="E43" s="7">
-        <v>1.5</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>-0.16</v>
+        <v>0.45</v>
       </c>
       <c r="D44" s="6">
-        <v>2.31</v>
-      </c>
-      <c r="E44" s="7">
-        <v>2.47</v>
+        <v>-0.47</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-0.92</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>-5.96</v>
+        <v>2.31</v>
       </c>
       <c r="D45" s="6">
-        <v>-3.34</v>
+        <v>3.82</v>
       </c>
       <c r="E45" s="7">
-        <v>2.62</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-0.34</v>
+        <v>-3.34</v>
       </c>
       <c r="D46" s="6">
-        <v>-0.08</v>
+        <v>-1.29</v>
       </c>
       <c r="E46" s="7">
-        <v>0.26</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>-3.16</v>
+        <v>-0.08</v>
       </c>
       <c r="D47" s="6">
-        <v>-2.06</v>
-      </c>
-      <c r="E47" s="7">
-        <v>1.1</v>
+        <v>-2.27</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C48" s="6">
-        <v>-6.51</v>
+        <v>-2.06</v>
       </c>
       <c r="D48" s="6">
-        <v>-6.31</v>
+        <v>-0.68</v>
       </c>
       <c r="E48" s="7">
-        <v>0.2</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C49" s="6">
-        <v>-2.3</v>
+        <v>-6.31</v>
       </c>
       <c r="D49" s="6">
-        <v>-2.53</v>
-      </c>
-      <c r="E49" s="8">
-        <v>-0.23</v>
+        <v>-5.59</v>
+      </c>
+      <c r="E49" s="7">
+        <v>0.72</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>-12.51</v>
+        <v>-2.53</v>
       </c>
       <c r="D50" s="6">
-        <v>-12.39</v>
-      </c>
-      <c r="E50" s="7">
-        <v>0.12</v>
+        <v>-3.27</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>-0.85</v>
+        <v>-12.39</v>
       </c>
       <c r="D51" s="6">
-        <v>-0.58</v>
-      </c>
-      <c r="E51" s="7">
-        <v>0.27</v>
+        <v>-13.28</v>
+      </c>
+      <c r="E51" s="8">
+        <v>-0.89</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-21.82</v>
+        <v>-0.58</v>
       </c>
       <c r="D52" s="6">
-        <v>-22.8</v>
+        <v>-1.27</v>
       </c>
       <c r="E52" s="8">
-        <v>-0.98</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-9.67</v>
+        <v>-22.8</v>
       </c>
       <c r="D53" s="6">
-        <v>-11.24</v>
+        <v>-24.27</v>
       </c>
       <c r="E53" s="8">
-        <v>-1.57</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-8.84</v>
+        <v>-11.24</v>
       </c>
       <c r="D54" s="6">
-        <v>-9.4</v>
+        <v>-11.33</v>
       </c>
       <c r="E54" s="8">
-        <v>-0.5600000000000001</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-6.13</v>
+        <v>-9.4</v>
       </c>
       <c r="D55" s="6">
-        <v>-6.22</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="E55" s="8">
-        <v>-0.09</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>1.22</v>
+        <v>-6.22</v>
       </c>
       <c r="D56" s="6">
-        <v>4.62</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3.4</v>
+        <v>-6.94</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>14.81</v>
+        <v>4.62</v>
       </c>
       <c r="D57" s="6">
-        <v>14.77</v>
-      </c>
-      <c r="E57" s="8">
-        <v>-0.04</v>
+        <v>7.75</v>
+      </c>
+      <c r="E57" s="7">
+        <v>3.13</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>-9.25</v>
+        <v>14.77</v>
       </c>
       <c r="D58" s="6">
-        <v>-8.890000000000001</v>
+        <v>15.39</v>
       </c>
       <c r="E58" s="7">
-        <v>0.36</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>4.8</v>
+        <v>-8.890000000000001</v>
       </c>
       <c r="D59" s="6">
-        <v>5.7</v>
-      </c>
-      <c r="E59" s="7">
-        <v>0.9</v>
+        <v>-9.109999999999999</v>
+      </c>
+      <c r="E59" s="8">
+        <v>-0.22</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>16.85</v>
+        <v>5.7</v>
       </c>
       <c r="D60" s="6">
-        <v>18.84</v>
+        <v>6.48</v>
       </c>
       <c r="E60" s="7">
-        <v>1.99</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>-13.73</v>
+        <v>18.84</v>
       </c>
       <c r="D61" s="6">
-        <v>-13.7</v>
+        <v>19.27</v>
       </c>
       <c r="E61" s="7">
-        <v>0.03</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>-8.890000000000001</v>
+        <v>-13.7</v>
       </c>
       <c r="D62" s="6">
-        <v>-9.43</v>
+        <v>-14.55</v>
       </c>
       <c r="E62" s="8">
-        <v>-0.54</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>-3.25</v>
+        <v>-9.43</v>
       </c>
       <c r="D63" s="6">
-        <v>-5.36</v>
+        <v>-10.28</v>
       </c>
       <c r="E63" s="8">
-        <v>-2.11</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C64" s="6">
-        <v>-7.86</v>
+        <v>-5.36</v>
       </c>
       <c r="D64" s="6">
-        <v>-6.49</v>
-      </c>
-      <c r="E64" s="7">
-        <v>1.37</v>
+        <v>-5.37</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.01</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-9.15</v>
+        <v>-6.49</v>
       </c>
       <c r="D65" s="6">
-        <v>-8.68</v>
+        <v>-5.14</v>
       </c>
       <c r="E65" s="7">
-        <v>0.47</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-7.69</v>
+        <v>-8.68</v>
       </c>
       <c r="D66" s="6">
-        <v>-6.56</v>
-      </c>
-      <c r="E66" s="7">
-        <v>1.13</v>
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="E66" s="8">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-10.83</v>
+        <v>-6.56</v>
       </c>
       <c r="D67" s="6">
-        <v>-10.22</v>
+        <v>-6.5</v>
       </c>
       <c r="E67" s="7">
-        <v>0.61</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-12.2</v>
+        <v>-10.22</v>
       </c>
       <c r="D68" s="6">
-        <v>-11.55</v>
-      </c>
-      <c r="E68" s="7">
-        <v>0.65</v>
+        <v>-11.03</v>
+      </c>
+      <c r="E68" s="8">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-9.1</v>
+        <v>-11.55</v>
       </c>
       <c r="D69" s="6">
-        <v>-9.66</v>
+        <v>-12.04</v>
       </c>
       <c r="E69" s="8">
-        <v>-0.5600000000000001</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>12.18</v>
+        <v>-9.66</v>
       </c>
       <c r="D70" s="6">
-        <v>9.33</v>
-      </c>
-      <c r="E70" s="8">
-        <v>-2.85</v>
+        <v>-9.24</v>
+      </c>
+      <c r="E70" s="7">
+        <v>0.42</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-7.44</v>
+        <v>9.33</v>
       </c>
       <c r="D71" s="6">
-        <v>-7.1</v>
-      </c>
-      <c r="E71" s="7">
-        <v>0.34</v>
+        <v>3.73</v>
+      </c>
+      <c r="E71" s="8">
+        <v>-5.6</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-7.64</v>
+        <v>-7.1</v>
       </c>
       <c r="D72" s="6">
-        <v>-6.94</v>
+        <v>-6.33</v>
       </c>
       <c r="E72" s="7">
-        <v>0.7</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>2.41</v>
+        <v>-6.94</v>
       </c>
       <c r="D73" s="6">
-        <v>6.15</v>
-      </c>
-      <c r="E73" s="7">
-        <v>3.74</v>
+        <v>-7.33</v>
+      </c>
+      <c r="E73" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-5.67</v>
+        <v>6.15</v>
       </c>
       <c r="D74" s="6">
-        <v>-5.07</v>
+        <v>7.62</v>
       </c>
       <c r="E74" s="7">
-        <v>0.6</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-9.59</v>
+        <v>-5.07</v>
       </c>
       <c r="D75" s="6">
-        <v>-8.949999999999999</v>
-      </c>
-      <c r="E75" s="7">
-        <v>0.64</v>
+        <v>-5.37</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-3.44</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="D76" s="6">
-        <v>-3.04</v>
-      </c>
-      <c r="E76" s="7">
-        <v>0.4</v>
+        <v>-9.51</v>
+      </c>
+      <c r="E76" s="8">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>0.88</v>
+        <v>-3.04</v>
       </c>
       <c r="D77" s="6">
-        <v>1.24</v>
+        <v>-2.96</v>
       </c>
       <c r="E77" s="7">
-        <v>0.36</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>-14.04</v>
+        <v>1.24</v>
       </c>
       <c r="D78" s="6">
-        <v>-12.37</v>
+        <v>2.09</v>
       </c>
       <c r="E78" s="7">
-        <v>1.67</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-4.06</v>
+        <v>-12.37</v>
       </c>
       <c r="D79" s="6">
-        <v>-3.83</v>
-      </c>
-      <c r="E79" s="7">
-        <v>0.23</v>
+        <v>-13.15</v>
+      </c>
+      <c r="E79" s="8">
+        <v>-0.78</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-3.56</v>
+        <v>-3.83</v>
       </c>
       <c r="D80" s="6">
-        <v>-3.37</v>
-      </c>
-      <c r="E80" s="7">
-        <v>0.19</v>
+        <v>-4.51</v>
+      </c>
+      <c r="E80" s="8">
+        <v>-0.68</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-7.4</v>
+        <v>-3.37</v>
       </c>
       <c r="D81" s="6">
-        <v>-6.37</v>
+        <v>-2.41</v>
       </c>
       <c r="E81" s="7">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-5.02</v>
+        <v>-6.37</v>
       </c>
       <c r="D82" s="6">
-        <v>-4.9</v>
+        <v>-4.69</v>
       </c>
       <c r="E82" s="7">
-        <v>0.12</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-5.9</v>
+        <v>-4.9</v>
       </c>
       <c r="D83" s="6">
-        <v>-6.59</v>
+        <v>-6.97</v>
       </c>
       <c r="E83" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-2.07</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C84" s="6">
-        <v>-15.78</v>
+        <v>-6.59</v>
       </c>
       <c r="D84" s="6">
-        <v>-14.53</v>
+        <v>-6.27</v>
       </c>
       <c r="E84" s="7">
-        <v>1.25</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C85" s="6">
-        <v>-14.95</v>
+        <v>-14.53</v>
       </c>
       <c r="D85" s="6">
-        <v>-14.52</v>
+        <v>-13.29</v>
       </c>
       <c r="E85" s="7">
-        <v>0.43</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>7</v>
@@ -4760,678 +4775,678 @@
         <v>-14.52</v>
       </c>
       <c r="D86" s="6">
-        <v>-13.47</v>
-      </c>
-      <c r="E86" s="7">
-        <v>1.05</v>
+        <v>-15.33</v>
+      </c>
+      <c r="E86" s="8">
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-15.68</v>
+        <v>-13.47</v>
       </c>
       <c r="D87" s="6">
-        <v>-15.1</v>
+        <v>-13.41</v>
       </c>
       <c r="E87" s="7">
-        <v>0.58</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-24.61</v>
+        <v>-15.1</v>
       </c>
       <c r="D88" s="6">
-        <v>-24.05</v>
-      </c>
-      <c r="E88" s="7">
-        <v>0.5600000000000001</v>
+        <v>-15.86</v>
+      </c>
+      <c r="E88" s="8">
+        <v>-0.76</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-14.08</v>
+        <v>-24.05</v>
       </c>
       <c r="D89" s="6">
-        <v>-14.61</v>
+        <v>-24.47</v>
       </c>
       <c r="E89" s="8">
-        <v>-0.53</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-18.27</v>
+        <v>-14.61</v>
       </c>
       <c r="D90" s="6">
-        <v>-18.48</v>
-      </c>
-      <c r="E90" s="8">
-        <v>-0.21</v>
+        <v>-14.21</v>
+      </c>
+      <c r="E90" s="7">
+        <v>0.4</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-11.98</v>
+        <v>-18.48</v>
       </c>
       <c r="D91" s="6">
-        <v>-10.71</v>
-      </c>
-      <c r="E91" s="7">
-        <v>1.27</v>
+        <v>-20.09</v>
+      </c>
+      <c r="E91" s="8">
+        <v>-1.61</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-11.31</v>
+        <v>-10.71</v>
       </c>
       <c r="D92" s="6">
-        <v>-10.64</v>
+        <v>-10.39</v>
       </c>
       <c r="E92" s="7">
-        <v>0.67</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-5.47</v>
+        <v>-10.64</v>
       </c>
       <c r="D93" s="6">
-        <v>-2.01</v>
-      </c>
-      <c r="E93" s="7">
-        <v>3.46</v>
+        <v>-11.02</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-0.38</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-14.48</v>
+        <v>-2.01</v>
       </c>
       <c r="D94" s="6">
-        <v>-13.93</v>
+        <v>-0.66</v>
       </c>
       <c r="E94" s="7">
-        <v>0.55</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-16.55</v>
+        <v>-13.93</v>
       </c>
       <c r="D95" s="6">
-        <v>-15.95</v>
-      </c>
-      <c r="E95" s="7">
-        <v>0.6</v>
+        <v>-14.21</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-18.08</v>
+        <v>-15.95</v>
       </c>
       <c r="D96" s="6">
-        <v>-17.74</v>
-      </c>
-      <c r="E96" s="7">
-        <v>0.34</v>
+        <v>-16.46</v>
+      </c>
+      <c r="E96" s="8">
+        <v>-0.51</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-5.19</v>
+        <v>-17.74</v>
       </c>
       <c r="D97" s="6">
-        <v>-3.38</v>
+        <v>-17.67</v>
       </c>
       <c r="E97" s="7">
-        <v>1.81</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-18.47</v>
+        <v>-3.38</v>
       </c>
       <c r="D98" s="6">
-        <v>-16.89</v>
+        <v>-2.37</v>
       </c>
       <c r="E98" s="7">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-11.55</v>
+        <v>-16.89</v>
       </c>
       <c r="D99" s="6">
-        <v>-11.33</v>
-      </c>
-      <c r="E99" s="7">
-        <v>0.22</v>
+        <v>-17.63</v>
+      </c>
+      <c r="E99" s="8">
+        <v>-0.74</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-7.57</v>
+        <v>-11.33</v>
       </c>
       <c r="D100" s="6">
-        <v>-6.04</v>
-      </c>
-      <c r="E100" s="7">
-        <v>1.53</v>
+        <v>-11.96</v>
+      </c>
+      <c r="E100" s="8">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-13.37</v>
+        <v>-6.04</v>
       </c>
       <c r="D101" s="6">
-        <v>-11.79</v>
+        <v>-4.97</v>
       </c>
       <c r="E101" s="7">
-        <v>1.58</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-7.46</v>
+        <v>-11.79</v>
       </c>
       <c r="D102" s="6">
-        <v>-7.33</v>
-      </c>
-      <c r="E102" s="7">
-        <v>0.13</v>
+        <v>-12.16</v>
+      </c>
+      <c r="E102" s="8">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="6">
-        <v>-8.09</v>
+        <v>-7.33</v>
       </c>
       <c r="D103" s="6">
-        <v>-8.77</v>
+        <v>-9.43</v>
       </c>
       <c r="E103" s="8">
-        <v>-0.68</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C104" s="6">
-        <v>24970.75</v>
+        <v>-8.77</v>
       </c>
       <c r="D104" s="6">
-        <v>25340.8</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="E104" s="7">
-        <v>370.05</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C105" s="6">
-        <v>8932.700000000001</v>
+        <v>25340.8</v>
       </c>
       <c r="D105" s="6">
-        <v>8978.65</v>
+        <v>25707.35</v>
       </c>
       <c r="E105" s="7">
-        <v>45.95</v>
+        <v>366.55</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>10804.45</v>
+        <v>8978.65</v>
       </c>
       <c r="D106" s="6">
-        <v>10936.65</v>
-      </c>
-      <c r="E106" s="7">
-        <v>132.2</v>
+        <v>8893.5</v>
+      </c>
+      <c r="E106" s="8">
+        <v>-85.15000000000001</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>35022.35</v>
+        <v>10936.65</v>
       </c>
       <c r="D107" s="6">
-        <v>35261.85</v>
+        <v>10944.35</v>
       </c>
       <c r="E107" s="7">
-        <v>239.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>42800.75</v>
+        <v>35261.85</v>
       </c>
       <c r="D108" s="6">
-        <v>43118.2</v>
-      </c>
-      <c r="E108" s="7">
-        <v>317.45</v>
+        <v>34946.3</v>
+      </c>
+      <c r="E108" s="8">
+        <v>-315.55</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>24454.35</v>
+        <v>43118.2</v>
       </c>
       <c r="D109" s="6">
-        <v>24303.75</v>
+        <v>42878.35</v>
       </c>
       <c r="E109" s="8">
-        <v>-150.6</v>
+        <v>-239.85</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>32273.05</v>
+        <v>24303.75</v>
       </c>
       <c r="D110" s="6">
-        <v>32189.45</v>
-      </c>
-      <c r="E110" s="8">
-        <v>-83.59999999999999</v>
+        <v>24418.25</v>
+      </c>
+      <c r="E110" s="7">
+        <v>114.5</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>14665.7</v>
+        <v>32189.45</v>
       </c>
       <c r="D111" s="6">
-        <v>14878.4</v>
-      </c>
-      <c r="E111" s="7">
-        <v>212.7</v>
+        <v>31553.4</v>
+      </c>
+      <c r="E111" s="8">
+        <v>-636.05</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>8661.200000000001</v>
+        <v>14878.4</v>
       </c>
       <c r="D112" s="6">
-        <v>8726.6</v>
+        <v>14931.6</v>
       </c>
       <c r="E112" s="7">
-        <v>65.40000000000001</v>
+        <v>53.2</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>1558.1</v>
+        <v>8726.6</v>
       </c>
       <c r="D113" s="6">
-        <v>1615.05</v>
-      </c>
-      <c r="E113" s="7">
-        <v>56.95</v>
+        <v>8690.049999999999</v>
+      </c>
+      <c r="E113" s="8">
+        <v>-36.55</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>11731.55</v>
+        <v>1615.05</v>
       </c>
       <c r="D114" s="6">
-        <v>11806.7</v>
+        <v>1637.4</v>
       </c>
       <c r="E114" s="7">
-        <v>75.15000000000001</v>
+        <v>22.35</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>8984.950000000001</v>
+        <v>11806.7</v>
       </c>
       <c r="D115" s="6">
-        <v>9048.6</v>
-      </c>
-      <c r="E115" s="7">
-        <v>63.65</v>
+        <v>11769.35</v>
+      </c>
+      <c r="E115" s="8">
+        <v>-37.35</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>8093.8</v>
+        <v>9048.6</v>
       </c>
       <c r="D116" s="6">
-        <v>8126.7</v>
-      </c>
-      <c r="E116" s="7">
-        <v>32.9</v>
+        <v>8993.65</v>
+      </c>
+      <c r="E116" s="8">
+        <v>-54.95</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>25774.25</v>
+        <v>8126.7</v>
       </c>
       <c r="D117" s="6">
-        <v>26267.25</v>
+        <v>8133.6</v>
       </c>
       <c r="E117" s="7">
-        <v>493</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>789.7</v>
+        <v>26267.25</v>
       </c>
       <c r="D118" s="6">
-        <v>805.05</v>
+        <v>26541.35</v>
       </c>
       <c r="E118" s="7">
-        <v>15.35</v>
+        <v>274.1</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>30162.5</v>
+        <v>805.05</v>
       </c>
       <c r="D119" s="6">
-        <v>30236</v>
-      </c>
-      <c r="E119" s="7">
-        <v>73.5</v>
+        <v>797.85</v>
+      </c>
+      <c r="E119" s="8">
+        <v>-7.2</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>15658.7</v>
+        <v>30236</v>
       </c>
       <c r="D120" s="6">
-        <v>15917.6</v>
-      </c>
-      <c r="E120" s="7">
-        <v>258.9</v>
+        <v>30022.85</v>
+      </c>
+      <c r="E120" s="8">
+        <v>-213.15</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>8661.950000000001</v>
+        <v>15917.6</v>
       </c>
       <c r="D121" s="6">
-        <v>8819.9</v>
+        <v>16100.1</v>
       </c>
       <c r="E121" s="7">
-        <v>157.95</v>
+        <v>182.5</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>10520.95</v>
+        <v>8819.9</v>
       </c>
       <c r="D122" s="6">
-        <v>10536</v>
-      </c>
-      <c r="E122" s="7">
-        <v>15.05</v>
+        <v>8782.700000000001</v>
+      </c>
+      <c r="E122" s="8">
+        <v>-37.2</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="6">
-        <v>26825.3</v>
+        <v>10536</v>
       </c>
       <c r="D123" s="6">
-        <v>26628.45</v>
+        <v>10296.6</v>
       </c>
       <c r="E123" s="8">
-        <v>-196.85</v>
+        <v>-239.4</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C124" s="6">
-        <v>55</v>
+        <v>26628.45</v>
       </c>
       <c r="D124" s="6">
-        <v>50</v>
-      </c>
-      <c r="E124" s="8">
-        <v>-5</v>
+        <v>26722.1</v>
+      </c>
+      <c r="E124" s="7">
+        <v>93.65000000000001</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C125" s="6">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D125" s="6">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="E125" s="7">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>14</v>
@@ -5440,24 +5455,24 @@
         <v>50</v>
       </c>
       <c r="D126" s="6">
-        <v>55</v>
-      </c>
-      <c r="E126" s="7">
-        <v>5</v>
+        <v>30</v>
+      </c>
+      <c r="E126" s="8">
+        <v>-20</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D127" s="6">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="E127" s="8">
         <v>-10</v>
@@ -5471,61 +5486,61 @@
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D128" s="6">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E128" s="8">
-        <v>-5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D129" s="6">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="E129" s="7">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C130" s="6">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D130" s="6">
-        <v>25</v>
-      </c>
-      <c r="E130" s="7">
-        <v>5</v>
+        <v>40</v>
+      </c>
+      <c r="E130" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="6">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="D131" s="6">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="E131" s="7">
         <v>5</v>
@@ -5533,16 +5548,16 @@
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C132" s="6">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="D132" s="6">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E132" s="7">
         <v>5</v>
@@ -5550,7 +5565,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>14</v>
@@ -5559,373 +5574,407 @@
         <v>65</v>
       </c>
       <c r="D133" s="6">
-        <v>70</v>
-      </c>
-      <c r="E133" s="7">
-        <v>5</v>
+        <v>55</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-10</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C134" s="6">
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="D134" s="6">
         <v>60</v>
       </c>
-      <c r="E134" s="8">
-        <v>-15</v>
+      <c r="E134" s="7">
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C135" s="6">
-        <v>36.27</v>
+        <v>70</v>
       </c>
       <c r="D135" s="6">
-        <v>42.77</v>
-      </c>
-      <c r="E135" s="7">
-        <v>6.5</v>
+        <v>35</v>
+      </c>
+      <c r="E135" s="8">
+        <v>-35</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C136" s="6">
-        <v>38.62</v>
+        <v>60</v>
       </c>
       <c r="D136" s="6">
-        <v>41.22</v>
+        <v>70</v>
       </c>
       <c r="E136" s="7">
-        <v>2.6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>38.43</v>
+        <v>42.77</v>
       </c>
       <c r="D137" s="6">
-        <v>44.7</v>
+        <v>48.38</v>
       </c>
       <c r="E137" s="7">
-        <v>6.27</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>33.59</v>
+        <v>41.22</v>
       </c>
       <c r="D138" s="6">
-        <v>37.32</v>
-      </c>
-      <c r="E138" s="7">
-        <v>3.73</v>
+        <v>38.01</v>
+      </c>
+      <c r="E138" s="8">
+        <v>-3.21</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>34.8</v>
+        <v>44.7</v>
       </c>
       <c r="D139" s="6">
-        <v>38.09</v>
+        <v>45.05</v>
       </c>
       <c r="E139" s="7">
-        <v>3.29</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>38.61</v>
+        <v>37.32</v>
       </c>
       <c r="D140" s="6">
-        <v>36.45</v>
+        <v>34.56</v>
       </c>
       <c r="E140" s="8">
-        <v>-2.16</v>
+        <v>-2.76</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>69.54000000000001</v>
+        <v>38.09</v>
       </c>
       <c r="D141" s="6">
-        <v>68.48999999999999</v>
+        <v>36.58</v>
       </c>
       <c r="E141" s="8">
-        <v>-1.05</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>32.14</v>
+        <v>36.45</v>
       </c>
       <c r="D142" s="6">
-        <v>39.72</v>
+        <v>39.23</v>
       </c>
       <c r="E142" s="7">
-        <v>7.58</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>44.43</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="D143" s="6">
-        <v>48.34</v>
-      </c>
-      <c r="E143" s="7">
-        <v>3.91</v>
+        <v>61</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-7.49</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>45.23</v>
+        <v>39.72</v>
       </c>
       <c r="D144" s="6">
-        <v>55.08</v>
+        <v>41.48</v>
       </c>
       <c r="E144" s="7">
-        <v>9.85</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>36.14</v>
+        <v>48.34</v>
       </c>
       <c r="D145" s="6">
-        <v>38.41</v>
-      </c>
-      <c r="E145" s="7">
-        <v>2.27</v>
+        <v>46.38</v>
+      </c>
+      <c r="E145" s="8">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>34.76</v>
+        <v>55.08</v>
       </c>
       <c r="D146" s="6">
-        <v>38.86</v>
+        <v>58.26</v>
       </c>
       <c r="E146" s="7">
-        <v>4.1</v>
+        <v>3.18</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>45.72</v>
+        <v>38.41</v>
       </c>
       <c r="D147" s="6">
-        <v>47.39</v>
-      </c>
-      <c r="E147" s="7">
-        <v>1.67</v>
+        <v>37.69</v>
+      </c>
+      <c r="E147" s="8">
+        <v>-0.72</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>43.84</v>
+        <v>38.86</v>
       </c>
       <c r="D148" s="6">
-        <v>53.07</v>
-      </c>
-      <c r="E148" s="7">
-        <v>9.23</v>
+        <v>36.72</v>
+      </c>
+      <c r="E148" s="8">
+        <v>-2.14</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>35.08</v>
+        <v>47.39</v>
       </c>
       <c r="D149" s="6">
-        <v>41.89</v>
+        <v>47.75</v>
       </c>
       <c r="E149" s="7">
-        <v>6.81</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>56.21</v>
+        <v>53.07</v>
       </c>
       <c r="D150" s="6">
-        <v>57.27</v>
+        <v>57.28</v>
       </c>
       <c r="E150" s="7">
-        <v>1.06</v>
+        <v>4.21</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>40.16</v>
+        <v>41.89</v>
       </c>
       <c r="D151" s="6">
-        <v>48.79</v>
-      </c>
-      <c r="E151" s="7">
-        <v>8.630000000000001</v>
+        <v>39.78</v>
+      </c>
+      <c r="E151" s="8">
+        <v>-2.11</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C152" s="6">
-        <v>33.7</v>
+        <v>57.27</v>
       </c>
       <c r="D152" s="6">
-        <v>40.05</v>
-      </c>
-      <c r="E152" s="7">
-        <v>6.35</v>
+        <v>53.23</v>
+      </c>
+      <c r="E152" s="8">
+        <v>-4.04</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C153" s="6">
-        <v>45.05</v>
+        <v>48.79</v>
       </c>
       <c r="D153" s="6">
-        <v>45.86</v>
+        <v>53.85</v>
       </c>
       <c r="E153" s="7">
-        <v>0.8100000000000001</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C154" s="6">
-        <v>44.54</v>
+        <v>40.05</v>
       </c>
       <c r="D154" s="6">
+        <v>39.1</v>
+      </c>
+      <c r="E154" s="8">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
+      <c r="A155" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C155" s="6">
+        <v>45.86</v>
+      </c>
+      <c r="D155" s="6">
+        <v>36.6</v>
+      </c>
+      <c r="E155" s="8">
+        <v>-9.26</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
+      <c r="A156" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C156" s="6">
         <v>41.43</v>
       </c>
-      <c r="E154" s="8">
-        <v>-3.11</v>
+      <c r="D156" s="6">
+        <v>43.45</v>
+      </c>
+      <c r="E156" s="7">
+        <v>2.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5949,28 +5998,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5984,16 +6033,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>45.3</v>
+        <v>44.7</v>
       </c>
       <c r="E2" s="11">
         <v>18.8</v>
       </c>
       <c r="F2" s="11">
-        <v>-2.8</v>
+        <v>-3.3</v>
       </c>
       <c r="G2" s="11">
-        <v>-5.2</v>
+        <v>-5.5</v>
       </c>
       <c r="H2" s="11">
         <v>52.4</v>
@@ -6122,50 +6171,50 @@
         <v>52</v>
       </c>
       <c r="H1" s="13" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>40</v>
       </c>
       <c r="J1" s="13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2257</v>
+        <v>0.2391</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1734</v>
+        <v>0.1795</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1693</v>
+        <v>0.1737</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1551</v>
+        <v>0.1625</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1326</v>
+        <v>0.1401</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1114</v>
+        <v>0.1133</v>
       </c>
       <c r="G2" s="14">
-        <v>0.0931</v>
+        <v>0.09949999999999999</v>
       </c>
       <c r="H2" s="14">
-        <v>0.08939999999999999</v>
+        <v>0.09609999999999999</v>
       </c>
       <c r="I2" s="14">
-        <v>0.08900000000000001</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="J2" s="14">
-        <v>0.07829999999999999</v>
+        <v>0.09140000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="13" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>57</v>
@@ -6183,48 +6232,48 @@
         <v>44</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="H3" s="13" t="s">
-        <v>47</v>
-      </c>
       <c r="I3" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="13" t="s">
         <v>56</v>
-      </c>
-      <c r="J3" s="13" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.064</v>
+        <v>0.0819</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0479</v>
+        <v>0.0546</v>
       </c>
       <c r="C4" s="14">
-        <v>0.045</v>
+        <v>0.0516</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0336</v>
+        <v>0.03700000000000001</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0206</v>
+        <v>0.0233</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.0194</v>
+        <v>-0.02</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0512</v>
+        <v>-0.0601</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0673</v>
+        <v>-0.0614</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1112</v>
+        <v>-0.1189</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.1281</v>
+        <v>-0.1629</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="121">
   <si>
     <t>Symbol</t>
   </si>
@@ -292,37 +292,58 @@
     <t>Near 52W High</t>
   </si>
   <si>
-    <t>-2.0% → -0.7%</t>
+    <t>-2.4% → -1.8%</t>
   </si>
   <si>
     <t>🟢 BREAKOUT WATCH</t>
   </si>
   <si>
-    <t>-2.0%</t>
-  </si>
-  <si>
-    <t>-0.7%</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
+    <t>-2.4%</t>
+  </si>
+  <si>
+    <t>-1.8%</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>45.0 → 50.1</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.8 → 53.9</t>
-  </si>
-  <si>
-    <t>48.8</t>
-  </si>
-  <si>
-    <t>53.9</t>
+    <t>45.0</t>
+  </si>
+  <si>
+    <t>50.1</t>
+  </si>
+  <si>
+    <t>46.4 → 52.2</t>
+  </si>
+  <si>
+    <t>46.4</t>
+  </si>
+  <si>
+    <t>52.2</t>
+  </si>
+  <si>
+    <t>47.8 → 56.2</t>
+  </si>
+  <si>
+    <t>47.8</t>
+  </si>
+  <si>
+    <t>56.2</t>
+  </si>
+  <si>
+    <t>43.5 → 50.0</t>
+  </si>
+  <si>
+    <t>43.5</t>
+  </si>
+  <si>
+    <t>50.0</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -1052,10 +1073,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>25707.35</v>
+        <v>25645.6</v>
       </c>
       <c r="E2">
-        <v>1.45</v>
+        <v>-0.24</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1064,43 +1085,43 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-13.29</v>
+        <v>-13.5</v>
       </c>
       <c r="I2">
-        <v>8.15</v>
+        <v>7.89</v>
       </c>
       <c r="J2">
-        <v>2.03</v>
+        <v>2.54</v>
       </c>
       <c r="K2">
-        <v>-4.67</v>
+        <v>-3.32</v>
       </c>
       <c r="L2">
-        <v>-5.14</v>
+        <v>-5.37</v>
       </c>
       <c r="M2">
-        <v>-5.59</v>
+        <v>-5.66</v>
       </c>
       <c r="N2">
-        <v>17.95</v>
+        <v>17.82</v>
       </c>
       <c r="O2">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Q2">
-        <v>25178.54</v>
+        <v>25305.36</v>
       </c>
       <c r="R2">
-        <v>25349.3</v>
+        <v>25322.92</v>
       </c>
       <c r="S2">
-        <v>26933.27</v>
+        <v>26862.62</v>
       </c>
       <c r="T2">
-        <v>26860.9</v>
+        <v>26844.65</v>
       </c>
       <c r="U2">
-        <v>-4.29</v>
+        <v>-4.47</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
@@ -1115,31 +1136,31 @@
         <v>1</v>
       </c>
       <c r="Z2">
-        <v>48.38</v>
+        <v>47.54</v>
       </c>
       <c r="AA2">
-        <v>-425.88</v>
+        <v>-371.61</v>
       </c>
       <c r="AB2">
-        <v>-540.05</v>
+        <v>-506.36</v>
       </c>
       <c r="AC2">
-        <v>114.17</v>
+        <v>134.75</v>
       </c>
       <c r="AD2">
-        <v>88.47</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="AE2">
-        <v>76.81</v>
+        <v>87.15000000000001</v>
       </c>
       <c r="AF2">
-        <v>464.47</v>
+        <v>449.95</v>
       </c>
       <c r="AH2">
-        <v>26224.68</v>
+        <v>26122.21</v>
       </c>
       <c r="AI2">
-        <v>24473.93</v>
+        <v>24523.63</v>
       </c>
       <c r="AJ2">
         <v>26008.9</v>
@@ -1148,7 +1169,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>43.52</v>
+        <v>38.25</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1162,10 +1183,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>8893.5</v>
+        <v>8986.450000000001</v>
       </c>
       <c r="E3">
-        <v>-0.95</v>
+        <v>1.05</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1174,43 +1195,43 @@
         <v>8792.299999999999</v>
       </c>
       <c r="H3">
-        <v>-15.33</v>
+        <v>-14.44</v>
       </c>
       <c r="I3">
-        <v>1.15</v>
+        <v>2.21</v>
       </c>
       <c r="J3">
-        <v>-0.65</v>
+        <v>0.77</v>
       </c>
       <c r="K3">
-        <v>-6.78</v>
+        <v>-4.06</v>
       </c>
       <c r="L3">
-        <v>-9.550000000000001</v>
+        <v>-8.6</v>
       </c>
       <c r="M3">
-        <v>-3.27</v>
+        <v>-2.73</v>
       </c>
       <c r="N3">
-        <v>9.140000000000001</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="O3">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="Q3">
-        <v>8902.950000000001</v>
+        <v>8916.719999999999</v>
       </c>
       <c r="R3">
-        <v>9029.450000000001</v>
+        <v>9012.389999999999</v>
       </c>
       <c r="S3">
-        <v>9419.52</v>
+        <v>9402.379999999999</v>
       </c>
       <c r="T3">
-        <v>9747.940000000001</v>
+        <v>9744.190000000001</v>
       </c>
       <c r="U3">
-        <v>-8.77</v>
+        <v>-7.78</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
@@ -1225,31 +1246,31 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>38.01</v>
+        <v>43.21</v>
       </c>
       <c r="AA3">
-        <v>-149.3</v>
+        <v>-137.52</v>
       </c>
       <c r="AB3">
-        <v>-161.13</v>
+        <v>-156.41</v>
       </c>
       <c r="AC3">
-        <v>11.84</v>
+        <v>18.89</v>
       </c>
       <c r="AD3">
-        <v>90.13</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="AE3">
-        <v>75.86</v>
+        <v>86.47</v>
       </c>
       <c r="AF3">
-        <v>148.27</v>
+        <v>146.32</v>
       </c>
       <c r="AH3">
-        <v>9332.309999999999</v>
+        <v>9281.02</v>
       </c>
       <c r="AI3">
-        <v>8726.58</v>
+        <v>8743.75</v>
       </c>
       <c r="AJ3">
         <v>9225.639999999999</v>
@@ -1258,7 +1279,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>40.18</v>
+        <v>37.46</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1272,55 +1293,55 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>10944.35</v>
+        <v>11059.15</v>
       </c>
       <c r="E4">
-        <v>0.07000000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="F4">
-        <v>12639.05</v>
+        <v>12633.9</v>
       </c>
       <c r="G4">
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-13.41</v>
+        <v>-12.46</v>
       </c>
       <c r="I4">
-        <v>5.9</v>
+        <v>7.01</v>
       </c>
       <c r="J4">
-        <v>1.03</v>
+        <v>2.84</v>
       </c>
       <c r="K4">
-        <v>-4.13</v>
+        <v>-1.87</v>
       </c>
       <c r="L4">
-        <v>-6.5</v>
+        <v>-5.52</v>
       </c>
       <c r="M4">
-        <v>-13.28</v>
+        <v>-12.5</v>
       </c>
       <c r="N4">
-        <v>9.23</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="Q4">
-        <v>10833.09</v>
+        <v>10894.27</v>
       </c>
       <c r="R4">
-        <v>10920.49</v>
+        <v>10915.66</v>
       </c>
       <c r="S4">
-        <v>11375.62</v>
+        <v>11355.51</v>
       </c>
       <c r="T4">
-        <v>11468.68</v>
+        <v>11462.56</v>
       </c>
       <c r="U4">
-        <v>-4.57</v>
+        <v>-3.52</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
@@ -1335,31 +1356,31 @@
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>45.05</v>
+        <v>50.12</v>
       </c>
       <c r="AA4">
-        <v>-139.78</v>
+        <v>-117.19</v>
       </c>
       <c r="AB4">
-        <v>-166.58</v>
+        <v>-156.7</v>
       </c>
       <c r="AC4">
-        <v>26.79</v>
+        <v>39.5</v>
       </c>
       <c r="AD4">
-        <v>88.78</v>
+        <v>100</v>
       </c>
       <c r="AE4">
-        <v>71.53</v>
+        <v>86.19</v>
       </c>
       <c r="AF4">
-        <v>158.79</v>
+        <v>158.71</v>
       </c>
       <c r="AH4">
-        <v>11156.63</v>
+        <v>11134.88</v>
       </c>
       <c r="AI4">
-        <v>10684.34</v>
+        <v>10696.43</v>
       </c>
       <c r="AJ4">
         <v>11143.46</v>
@@ -1368,7 +1389,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>44.51</v>
+        <v>39.42</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1382,10 +1403,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>34946.3</v>
+        <v>35299</v>
       </c>
       <c r="E5">
-        <v>-0.89</v>
+        <v>1.01</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1394,43 +1415,43 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-15.86</v>
+        <v>-15.02</v>
       </c>
       <c r="I5">
-        <v>5.58</v>
+        <v>6.65</v>
       </c>
       <c r="J5">
-        <v>-1.49</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K5">
-        <v>-6.66</v>
+        <v>-3.8</v>
       </c>
       <c r="L5">
-        <v>-11.03</v>
+        <v>-10.13</v>
       </c>
       <c r="M5">
-        <v>-1.27</v>
+        <v>-0.74</v>
       </c>
       <c r="N5">
-        <v>8.19</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O5">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="Q5">
-        <v>34970.4</v>
+        <v>35009.91</v>
       </c>
       <c r="R5">
-        <v>35910.29</v>
+        <v>35849.75</v>
       </c>
       <c r="S5">
-        <v>37111.16</v>
+        <v>37044.09</v>
       </c>
       <c r="T5">
-        <v>37731.21</v>
+        <v>37727.46</v>
       </c>
       <c r="U5">
-        <v>-7.38</v>
+        <v>-6.44</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
@@ -1445,31 +1466,31 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>34.56</v>
+        <v>39.91</v>
       </c>
       <c r="AA5">
-        <v>-628.84</v>
+        <v>-598.48</v>
       </c>
       <c r="AB5">
-        <v>-572.3</v>
+        <v>-577.54</v>
       </c>
       <c r="AC5">
-        <v>-56.54</v>
+        <v>-20.94</v>
       </c>
       <c r="AD5">
-        <v>56.07</v>
+        <v>67.55</v>
       </c>
       <c r="AE5">
-        <v>37.93</v>
+        <v>54.02</v>
       </c>
       <c r="AF5">
-        <v>574.01</v>
+        <v>573.4</v>
       </c>
       <c r="AH5">
-        <v>37265.49</v>
+        <v>37200.36</v>
       </c>
       <c r="AI5">
-        <v>34555.1</v>
+        <v>34499.15</v>
       </c>
       <c r="AJ5">
         <v>36227.11</v>
@@ -1478,7 +1499,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>48.28</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1492,10 +1513,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>42878.35</v>
+        <v>43882.95</v>
       </c>
       <c r="E6">
-        <v>-0.5600000000000001</v>
+        <v>2.34</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1504,43 +1525,43 @@
         <v>42680.7</v>
       </c>
       <c r="H6">
-        <v>-24.47</v>
+        <v>-22.7</v>
       </c>
       <c r="I6">
-        <v>0.46</v>
+        <v>2.82</v>
       </c>
       <c r="J6">
-        <v>-1.93</v>
+        <v>1.8</v>
       </c>
       <c r="K6">
-        <v>-6.67</v>
+        <v>-3.05</v>
       </c>
       <c r="L6">
-        <v>-12.04</v>
+        <v>-9.98</v>
       </c>
       <c r="M6">
-        <v>-24.27</v>
+        <v>-22.46</v>
       </c>
       <c r="N6">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="O6">
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>42916.69</v>
+        <v>43072.19</v>
       </c>
       <c r="R6">
-        <v>44112.02</v>
+        <v>44066.65</v>
       </c>
       <c r="S6">
-        <v>45425.75</v>
+        <v>45341.31</v>
       </c>
       <c r="T6">
-        <v>48751.15</v>
+        <v>48703.35</v>
       </c>
       <c r="U6">
-        <v>-12.05</v>
+        <v>-9.9</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
@@ -1555,31 +1576,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>36.58</v>
+        <v>46.16</v>
       </c>
       <c r="AA6">
-        <v>-734.02</v>
+        <v>-658.15</v>
       </c>
       <c r="AB6">
-        <v>-631.51</v>
+        <v>-636.84</v>
       </c>
       <c r="AC6">
-        <v>-102.51</v>
+        <v>-21.31</v>
       </c>
       <c r="AD6">
-        <v>18.39</v>
+        <v>42.14</v>
       </c>
       <c r="AE6">
-        <v>14.95</v>
+        <v>24.19</v>
       </c>
       <c r="AF6">
-        <v>755.34</v>
+        <v>791.45</v>
       </c>
       <c r="AH6">
-        <v>45774.49</v>
+        <v>45700.46</v>
       </c>
       <c r="AI6">
-        <v>42449.55</v>
+        <v>42432.85</v>
       </c>
       <c r="AJ6">
         <v>44659.77</v>
@@ -1588,7 +1609,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>41.22</v>
+        <v>35.75</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1602,10 +1623,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>24418.25</v>
+        <v>24704.55</v>
       </c>
       <c r="E7">
-        <v>0.47</v>
+        <v>1.17</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1614,43 +1635,43 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-14.21</v>
+        <v>-13.21</v>
       </c>
       <c r="I7">
-        <v>3.81</v>
+        <v>5.03</v>
       </c>
       <c r="J7">
-        <v>-1.11</v>
+        <v>0.19</v>
       </c>
       <c r="K7">
-        <v>-2.7</v>
+        <v>0.13</v>
       </c>
       <c r="L7">
-        <v>-9.24</v>
+        <v>-8.17</v>
       </c>
       <c r="M7">
-        <v>-11.33</v>
+        <v>-10.18</v>
       </c>
       <c r="N7">
-        <v>5.16</v>
+        <v>5.62</v>
       </c>
       <c r="O7">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="Q7">
-        <v>24447.41</v>
+        <v>24456.78</v>
       </c>
       <c r="R7">
-        <v>24784.62</v>
+        <v>24787.42</v>
       </c>
       <c r="S7">
-        <v>25367.03</v>
+        <v>25336.78</v>
       </c>
       <c r="T7">
-        <v>26189.34</v>
+        <v>26173.61</v>
       </c>
       <c r="U7">
-        <v>-6.76</v>
+        <v>-5.61</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
@@ -1665,31 +1686,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>39.23</v>
+        <v>45.65</v>
       </c>
       <c r="AA7">
-        <v>-244.41</v>
+        <v>-224.3</v>
       </c>
       <c r="AB7">
-        <v>-212.8</v>
+        <v>-215.1</v>
       </c>
       <c r="AC7">
-        <v>-31.61</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>13.82</v>
+        <v>26.41</v>
       </c>
       <c r="AE7">
-        <v>19.34</v>
+        <v>18.33</v>
       </c>
       <c r="AF7">
-        <v>359.21</v>
+        <v>363.75</v>
       </c>
       <c r="AH7">
-        <v>25403.45</v>
+        <v>25404.16</v>
       </c>
       <c r="AI7">
-        <v>24165.79</v>
+        <v>24170.69</v>
       </c>
       <c r="AJ7">
         <v>25375.42</v>
@@ -1698,7 +1719,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>36.79</v>
+        <v>34.33</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1712,10 +1733,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31553.4</v>
+        <v>31866.4</v>
       </c>
       <c r="E8">
-        <v>-1.98</v>
+        <v>0.99</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1724,43 +1745,43 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-20.09</v>
+        <v>-19.3</v>
       </c>
       <c r="I8">
-        <v>22.44</v>
+        <v>23.66</v>
       </c>
       <c r="J8">
-        <v>-2.68</v>
+        <v>-0.67</v>
       </c>
       <c r="K8">
-        <v>12.05</v>
+        <v>13.46</v>
       </c>
       <c r="L8">
-        <v>3.73</v>
+        <v>2.39</v>
       </c>
       <c r="M8">
-        <v>-9.720000000000001</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="N8">
-        <v>-2</v>
+        <v>-1.52</v>
       </c>
       <c r="O8">
         <v>80</v>
       </c>
       <c r="Q8">
-        <v>32018.53</v>
+        <v>31975.56</v>
       </c>
       <c r="R8">
-        <v>29960.63</v>
+        <v>30170.45</v>
       </c>
       <c r="S8">
-        <v>29887.98</v>
+        <v>29898.15</v>
       </c>
       <c r="T8">
-        <v>30724.65</v>
+        <v>30695.13</v>
       </c>
       <c r="U8">
-        <v>2.7</v>
+        <v>3.82</v>
       </c>
       <c r="V8" t="s">
         <v>80</v>
@@ -1775,31 +1796,31 @@
         <v>2</v>
       </c>
       <c r="Z8">
-        <v>61</v>
+        <v>63.14</v>
       </c>
       <c r="AA8">
-        <v>821.0599999999999</v>
+        <v>811.99</v>
       </c>
       <c r="AB8">
-        <v>551.3099999999999</v>
+        <v>603.4400000000001</v>
       </c>
       <c r="AC8">
-        <v>269.75</v>
+        <v>208.55</v>
       </c>
       <c r="AD8">
-        <v>82.3</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="AE8">
-        <v>86.34</v>
+        <v>81.36</v>
       </c>
       <c r="AF8">
-        <v>872.65</v>
+        <v>841</v>
       </c>
       <c r="AH8">
-        <v>33742.49</v>
+        <v>33882.21</v>
       </c>
       <c r="AI8">
-        <v>26178.76</v>
+        <v>26458.69</v>
       </c>
       <c r="AJ8">
         <v>29979.37</v>
@@ -1808,7 +1829,7 @@
         <v>82</v>
       </c>
       <c r="AL8">
-        <v>46.16</v>
+        <v>43.12</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1822,10 +1843,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>14931.6</v>
+        <v>14975.8</v>
       </c>
       <c r="E9">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1834,34 +1855,34 @@
         <v>14516.75</v>
       </c>
       <c r="H9">
-        <v>-10.39</v>
+        <v>-10.12</v>
       </c>
       <c r="I9">
-        <v>2.86</v>
+        <v>3.16</v>
       </c>
       <c r="J9">
-        <v>0.61</v>
+        <v>1.54</v>
       </c>
       <c r="K9">
-        <v>-5.98</v>
+        <v>-4.25</v>
       </c>
       <c r="L9">
-        <v>-6.33</v>
+        <v>-6.72</v>
       </c>
       <c r="N9">
-        <v>-11.89</v>
+        <v>-11.12</v>
       </c>
       <c r="O9">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="Q9">
-        <v>14748.08</v>
+        <v>14793.65</v>
       </c>
       <c r="R9">
-        <v>15053.77</v>
+        <v>15027.06</v>
       </c>
       <c r="S9">
-        <v>15742.12</v>
+        <v>15709.96</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
@@ -1873,31 +1894,31 @@
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>41.48</v>
+        <v>42.97</v>
       </c>
       <c r="AA9">
-        <v>-267.38</v>
+        <v>-244.34</v>
       </c>
       <c r="AB9">
-        <v>-278.82</v>
+        <v>-271.93</v>
       </c>
       <c r="AC9">
-        <v>11.44</v>
+        <v>27.59</v>
       </c>
       <c r="AD9">
-        <v>82.95</v>
+        <v>100</v>
       </c>
       <c r="AE9">
-        <v>54.25</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="AF9">
-        <v>230.34</v>
+        <v>222.23</v>
       </c>
       <c r="AH9">
-        <v>15575.96</v>
+        <v>15503.67</v>
       </c>
       <c r="AI9">
-        <v>14531.58</v>
+        <v>14550.46</v>
       </c>
       <c r="AJ9">
         <v>15216.01</v>
@@ -1906,7 +1927,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>54.88</v>
+        <v>50.66</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1920,10 +1941,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8690.049999999999</v>
+        <v>8792.5</v>
       </c>
       <c r="E10">
-        <v>-0.42</v>
+        <v>1.18</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1932,43 +1953,43 @@
         <v>8499.65</v>
       </c>
       <c r="H10">
-        <v>-11.02</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="I10">
-        <v>2.24</v>
+        <v>3.45</v>
       </c>
       <c r="J10">
-        <v>0.65</v>
+        <v>2.33</v>
       </c>
       <c r="K10">
-        <v>-2.99</v>
+        <v>0.11</v>
       </c>
       <c r="L10">
-        <v>-7.33</v>
+        <v>-6.24</v>
       </c>
       <c r="M10">
-        <v>-6.94</v>
+        <v>-7.07</v>
       </c>
       <c r="N10">
-        <v>11.33</v>
+        <v>11.75</v>
       </c>
       <c r="O10">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="Q10">
-        <v>8644.84</v>
+        <v>8684.92</v>
       </c>
       <c r="R10">
-        <v>8648.459999999999</v>
+        <v>8651.16</v>
       </c>
       <c r="S10">
-        <v>8953.280000000001</v>
+        <v>8940.799999999999</v>
       </c>
       <c r="T10">
-        <v>9211.469999999999</v>
+        <v>9206.799999999999</v>
       </c>
       <c r="U10">
-        <v>-5.66</v>
+        <v>-4.5</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
@@ -1983,31 +2004,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>46.38</v>
+        <v>52.23</v>
       </c>
       <c r="AA10">
-        <v>-80.48</v>
+        <v>-64.20999999999999</v>
       </c>
       <c r="AB10">
-        <v>-108.62</v>
+        <v>-99.73</v>
       </c>
       <c r="AC10">
-        <v>28.13</v>
+        <v>35.53</v>
       </c>
       <c r="AD10">
-        <v>95.77</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="AE10">
-        <v>84.63</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="AF10">
-        <v>130.12</v>
+        <v>129.67</v>
       </c>
       <c r="AH10">
-        <v>8816.41</v>
+        <v>8826.77</v>
       </c>
       <c r="AI10">
-        <v>8480.52</v>
+        <v>8475.559999999999</v>
       </c>
       <c r="AJ10">
         <v>8855.59</v>
@@ -2016,7 +2037,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>25.59</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2030,55 +2051,55 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1637.4</v>
+        <v>1655.35</v>
       </c>
       <c r="E11">
-        <v>1.38</v>
+        <v>1.1</v>
       </c>
       <c r="F11">
-        <v>1648.25</v>
+        <v>1655.35</v>
       </c>
       <c r="G11">
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>-0.66</v>
+        <v>0</v>
       </c>
       <c r="I11">
-        <v>30.64</v>
+        <v>32.07</v>
       </c>
       <c r="J11">
-        <v>0.91</v>
+        <v>4.47</v>
       </c>
       <c r="K11">
-        <v>5.59</v>
+        <v>7.54</v>
       </c>
       <c r="L11">
-        <v>7.62</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M11">
-        <v>7.75</v>
+        <v>7.99</v>
       </c>
       <c r="N11">
-        <v>-6.01</v>
+        <v>-5.92</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="Q11">
-        <v>1591.69</v>
+        <v>1605.86</v>
       </c>
       <c r="R11">
-        <v>1592.66</v>
+        <v>1598.38</v>
       </c>
       <c r="S11">
-        <v>1575.84</v>
+        <v>1577.03</v>
       </c>
       <c r="T11">
-        <v>1471.63</v>
+        <v>1472.55</v>
       </c>
       <c r="U11">
-        <v>11.26</v>
+        <v>12.41</v>
       </c>
       <c r="V11" t="s">
         <v>80</v>
@@ -2093,31 +2114,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>58.26</v>
+        <v>60.66</v>
       </c>
       <c r="AA11">
-        <v>12.71</v>
+        <v>16</v>
       </c>
       <c r="AB11">
-        <v>12.76</v>
+        <v>13.41</v>
       </c>
       <c r="AC11">
-        <v>-0.05</v>
+        <v>2.59</v>
       </c>
       <c r="AD11">
-        <v>41.09</v>
+        <v>68.8</v>
       </c>
       <c r="AE11">
-        <v>22.82</v>
+        <v>42.88</v>
       </c>
       <c r="AF11">
-        <v>40.31</v>
+        <v>39.92</v>
       </c>
       <c r="AH11">
-        <v>1670.08</v>
+        <v>1676.61</v>
       </c>
       <c r="AI11">
-        <v>1515.25</v>
+        <v>1520.15</v>
       </c>
       <c r="AJ11">
         <v>1544.25</v>
@@ -2126,7 +2147,7 @@
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>23.2</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2140,10 +2161,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>11769.35</v>
+        <v>11848.45</v>
       </c>
       <c r="E12">
-        <v>-0.32</v>
+        <v>0.67</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2152,43 +2173,43 @@
         <v>10017.9</v>
       </c>
       <c r="H12">
-        <v>-14.21</v>
+        <v>-13.63</v>
       </c>
       <c r="I12">
-        <v>17.48</v>
+        <v>18.27</v>
       </c>
       <c r="J12">
-        <v>-0.76</v>
+        <v>0.42</v>
       </c>
       <c r="K12">
-        <v>-10.07</v>
+        <v>-7.83</v>
       </c>
       <c r="L12">
-        <v>-5.37</v>
+        <v>-4.73</v>
       </c>
       <c r="M12">
-        <v>15.39</v>
+        <v>16.25</v>
       </c>
       <c r="N12">
-        <v>16.25</v>
+        <v>16.33</v>
       </c>
       <c r="O12">
         <v>90</v>
       </c>
       <c r="Q12">
-        <v>11716.83</v>
+        <v>11726.85</v>
       </c>
       <c r="R12">
-        <v>12107.94</v>
+        <v>12052.64</v>
       </c>
       <c r="S12">
-        <v>12725.71</v>
+        <v>12700.59</v>
       </c>
       <c r="T12">
-        <v>12486.31</v>
+        <v>12488.1</v>
       </c>
       <c r="U12">
-        <v>-5.74</v>
+        <v>-5.12</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
@@ -2203,31 +2224,31 @@
         <v>1</v>
       </c>
       <c r="Z12">
-        <v>37.69</v>
+        <v>40.23</v>
       </c>
       <c r="AA12">
-        <v>-294.75</v>
+        <v>-278.31</v>
       </c>
       <c r="AB12">
-        <v>-283.89</v>
+        <v>-282.77</v>
       </c>
       <c r="AC12">
-        <v>-10.86</v>
+        <v>4.46</v>
       </c>
       <c r="AD12">
-        <v>80.5</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="AE12">
-        <v>54.26</v>
+        <v>75.09</v>
       </c>
       <c r="AF12">
-        <v>252.11</v>
+        <v>244.7</v>
       </c>
       <c r="AH12">
-        <v>12864</v>
+        <v>12702.31</v>
       </c>
       <c r="AI12">
-        <v>11351.88</v>
+        <v>11402.98</v>
       </c>
       <c r="AJ12">
         <v>12304.47</v>
@@ -2236,7 +2257,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>53.74</v>
+        <v>52.62</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2250,10 +2271,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>8993.65</v>
+        <v>9097.1</v>
       </c>
       <c r="E13">
-        <v>-0.61</v>
+        <v>1.15</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2262,43 +2283,43 @@
         <v>8885.75</v>
       </c>
       <c r="H13">
-        <v>-16.46</v>
+        <v>-15.5</v>
       </c>
       <c r="I13">
-        <v>1.21</v>
+        <v>2.38</v>
       </c>
       <c r="J13">
-        <v>-1.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K13">
-        <v>-6.05</v>
+        <v>-3.12</v>
       </c>
       <c r="L13">
-        <v>-9.51</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="M13">
-        <v>-9.109999999999999</v>
+        <v>-8.32</v>
       </c>
       <c r="N13">
-        <v>17.37</v>
+        <v>17.83</v>
       </c>
       <c r="O13">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q13">
-        <v>8989.459999999999</v>
+        <v>9002.01</v>
       </c>
       <c r="R13">
-        <v>9158.799999999999</v>
+        <v>9146.469999999999</v>
       </c>
       <c r="S13">
-        <v>9466.860000000001</v>
+        <v>9451.57</v>
       </c>
       <c r="T13">
-        <v>9968.389999999999</v>
+        <v>9963.23</v>
       </c>
       <c r="U13">
-        <v>-9.779999999999999</v>
+        <v>-8.69</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
@@ -2313,31 +2334,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>36.72</v>
+        <v>43.08</v>
       </c>
       <c r="AA13">
-        <v>-138.01</v>
+        <v>-127.42</v>
       </c>
       <c r="AB13">
-        <v>-134.16</v>
+        <v>-132.82</v>
       </c>
       <c r="AC13">
-        <v>-3.85</v>
+        <v>5.39</v>
       </c>
       <c r="AD13">
-        <v>65.44</v>
+        <v>80.2</v>
       </c>
       <c r="AE13">
-        <v>51.42</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="AF13">
-        <v>139.2</v>
+        <v>139.38</v>
       </c>
       <c r="AH13">
-        <v>9435.77</v>
+        <v>9410.43</v>
       </c>
       <c r="AI13">
-        <v>8881.84</v>
+        <v>8882.52</v>
       </c>
       <c r="AJ13">
         <v>9317.65</v>
@@ -2346,7 +2367,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>54.51</v>
+        <v>51.27</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2360,10 +2381,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8133.6</v>
+        <v>8312.5</v>
       </c>
       <c r="E14">
-        <v>0.08</v>
+        <v>2.2</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2372,43 +2393,43 @@
         <v>7817.4</v>
       </c>
       <c r="H14">
-        <v>-17.67</v>
+        <v>-15.86</v>
       </c>
       <c r="I14">
-        <v>4.04</v>
+        <v>6.33</v>
       </c>
       <c r="J14">
-        <v>-1.43</v>
+        <v>0.67</v>
       </c>
       <c r="K14">
-        <v>-1.94</v>
+        <v>3.57</v>
       </c>
       <c r="L14">
-        <v>-2.96</v>
+        <v>-0.83</v>
       </c>
       <c r="M14">
-        <v>6.48</v>
+        <v>5.79</v>
       </c>
       <c r="N14">
-        <v>23.91</v>
+        <v>24.09</v>
       </c>
       <c r="O14">
         <v>85</v>
       </c>
       <c r="Q14">
-        <v>8136.44</v>
+        <v>8147.46</v>
       </c>
       <c r="R14">
-        <v>8093.48</v>
+        <v>8110.47</v>
       </c>
       <c r="S14">
-        <v>8305.17</v>
+        <v>8297.290000000001</v>
       </c>
       <c r="T14">
-        <v>8564.309999999999</v>
+        <v>8562.17</v>
       </c>
       <c r="U14">
-        <v>-5.03</v>
+        <v>-2.92</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
@@ -2423,31 +2444,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>47.75</v>
+        <v>56.21</v>
       </c>
       <c r="AA14">
-        <v>-33.56</v>
+        <v>-17.16</v>
       </c>
       <c r="AB14">
-        <v>-49.12</v>
+        <v>-42.73</v>
       </c>
       <c r="AC14">
-        <v>15.57</v>
+        <v>25.57</v>
       </c>
       <c r="AD14">
-        <v>57.29</v>
+        <v>72.92</v>
       </c>
       <c r="AE14">
-        <v>58.17</v>
+        <v>61.03</v>
       </c>
       <c r="AF14">
-        <v>150.48</v>
+        <v>153.82</v>
       </c>
       <c r="AH14">
-        <v>8287.68</v>
+        <v>8319.110000000001</v>
       </c>
       <c r="AI14">
-        <v>7899.28</v>
+        <v>7901.82</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
@@ -2456,7 +2477,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>17.15</v>
+        <v>17.68</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2470,10 +2491,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26541.35</v>
+        <v>26710.8</v>
       </c>
       <c r="E15">
-        <v>1.04</v>
+        <v>0.64</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2482,43 +2503,43 @@
         <v>21549.55</v>
       </c>
       <c r="H15">
-        <v>-2.37</v>
+        <v>-1.75</v>
       </c>
       <c r="I15">
-        <v>23.16</v>
+        <v>23.95</v>
       </c>
       <c r="J15">
-        <v>3.82</v>
+        <v>4.35</v>
       </c>
       <c r="K15">
-        <v>-1.71</v>
+        <v>-0.19</v>
       </c>
       <c r="L15">
-        <v>2.09</v>
+        <v>1.28</v>
       </c>
       <c r="M15">
-        <v>19.27</v>
+        <v>19.03</v>
       </c>
       <c r="N15">
-        <v>14.01</v>
+        <v>13.99</v>
       </c>
       <c r="O15">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="Q15">
-        <v>25901.79</v>
+        <v>26124.62</v>
       </c>
       <c r="R15">
-        <v>26037.59</v>
+        <v>26026.45</v>
       </c>
       <c r="S15">
-        <v>26415.04</v>
+        <v>26420.35</v>
       </c>
       <c r="T15">
-        <v>24433.89</v>
+        <v>24453.72</v>
       </c>
       <c r="U15">
-        <v>8.630000000000001</v>
+        <v>9.23</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
@@ -2533,40 +2554,40 @@
         <v>2</v>
       </c>
       <c r="Z15">
-        <v>57.28</v>
+        <v>59.68</v>
       </c>
       <c r="AA15">
-        <v>-142.71</v>
+        <v>-73.61</v>
       </c>
       <c r="AB15">
-        <v>-202.45</v>
+        <v>-176.69</v>
       </c>
       <c r="AC15">
-        <v>59.75</v>
+        <v>103.08</v>
       </c>
       <c r="AD15">
-        <v>89.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="AE15">
-        <v>56.96</v>
+        <v>81.94</v>
       </c>
       <c r="AF15">
-        <v>431.92</v>
+        <v>419.22</v>
       </c>
       <c r="AH15">
-        <v>26858.08</v>
+        <v>26800.44</v>
       </c>
       <c r="AI15">
-        <v>25217.1</v>
+        <v>25252.46</v>
       </c>
       <c r="AJ15">
-        <v>26568.83</v>
+        <v>25337.07</v>
       </c>
       <c r="AK15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AL15">
-        <v>40.21</v>
+        <v>39.11</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2580,10 +2601,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>797.85</v>
+        <v>819.8</v>
       </c>
       <c r="E16">
-        <v>-0.89</v>
+        <v>2.75</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2592,43 +2613,43 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-17.63</v>
+        <v>-15.37</v>
       </c>
       <c r="I16">
-        <v>22.53</v>
+        <v>25.9</v>
       </c>
       <c r="J16">
-        <v>-0.99</v>
+        <v>2.03</v>
       </c>
       <c r="K16">
-        <v>-8.220000000000001</v>
+        <v>-3.65</v>
       </c>
       <c r="L16">
-        <v>-13.15</v>
+        <v>-10.77</v>
       </c>
       <c r="M16">
-        <v>-14.55</v>
+        <v>-12.62</v>
       </c>
       <c r="N16">
-        <v>9.949999999999999</v>
+        <v>10.45</v>
       </c>
       <c r="O16">
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>796.08</v>
+        <v>799.35</v>
       </c>
       <c r="R16">
-        <v>816.8099999999999</v>
+        <v>816.11</v>
       </c>
       <c r="S16">
-        <v>855.77</v>
+        <v>853.99</v>
       </c>
       <c r="T16">
-        <v>821.41</v>
+        <v>820.92</v>
       </c>
       <c r="U16">
-        <v>-2.87</v>
+        <v>-0.14</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
@@ -2643,31 +2664,31 @@
         <v>1</v>
       </c>
       <c r="Z16">
-        <v>39.78</v>
+        <v>48.33</v>
       </c>
       <c r="AA16">
-        <v>-16.08</v>
+        <v>-13.94</v>
       </c>
       <c r="AB16">
-        <v>-15.69</v>
+        <v>-15.34</v>
       </c>
       <c r="AC16">
-        <v>-0.4</v>
+        <v>1.4</v>
       </c>
       <c r="AD16">
-        <v>56.69</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="AE16">
-        <v>41.19</v>
+        <v>58.71</v>
       </c>
       <c r="AF16">
-        <v>18.08</v>
+        <v>18.69</v>
       </c>
       <c r="AH16">
-        <v>852.87</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AI16">
-        <v>780.75</v>
+        <v>780.91</v>
       </c>
       <c r="AJ16">
         <v>838.5700000000001</v>
@@ -2676,7 +2697,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>36.12</v>
+        <v>31.84</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2690,10 +2711,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30022.85</v>
+        <v>30506.2</v>
       </c>
       <c r="E17">
-        <v>-0.7</v>
+        <v>1.61</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2702,43 +2723,43 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-11.96</v>
+        <v>-10.54</v>
       </c>
       <c r="I17">
-        <v>5.85</v>
+        <v>7.55</v>
       </c>
       <c r="J17">
-        <v>-0.47</v>
+        <v>1.69</v>
       </c>
       <c r="K17">
-        <v>1.38</v>
+        <v>4.5</v>
       </c>
       <c r="L17">
-        <v>-4.51</v>
+        <v>-2.97</v>
       </c>
       <c r="M17">
-        <v>-10.28</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="N17">
-        <v>3.7</v>
+        <v>4.28</v>
       </c>
       <c r="O17">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="Q17">
-        <v>30070.81</v>
+        <v>30172.46</v>
       </c>
       <c r="R17">
-        <v>29552.57</v>
+        <v>29619.9</v>
       </c>
       <c r="S17">
-        <v>30022.7</v>
+        <v>30013.39</v>
       </c>
       <c r="T17">
-        <v>30914.71</v>
+        <v>30898.15</v>
       </c>
       <c r="U17">
-        <v>-2.88</v>
+        <v>-1.27</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
@@ -2753,31 +2774,31 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>53.23</v>
+        <v>60.1</v>
       </c>
       <c r="AA17">
-        <v>80.51000000000001</v>
+        <v>121.51</v>
       </c>
       <c r="AB17">
-        <v>-31.32</v>
+        <v>-0.76</v>
       </c>
       <c r="AC17">
-        <v>111.84</v>
+        <v>122.27</v>
       </c>
       <c r="AD17">
-        <v>81.43000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="AE17">
-        <v>80.27</v>
+        <v>82.23</v>
       </c>
       <c r="AF17">
-        <v>436.11</v>
+        <v>440.77</v>
       </c>
       <c r="AH17">
-        <v>30686.88</v>
+        <v>30814.27</v>
       </c>
       <c r="AI17">
-        <v>28418.26</v>
+        <v>28425.53</v>
       </c>
       <c r="AJ17">
         <v>29148.67</v>
@@ -2786,7 +2807,7 @@
         <v>82</v>
       </c>
       <c r="AL17">
-        <v>24.59</v>
+        <v>22.9</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2800,10 +2821,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16100.1</v>
+        <v>16193.9</v>
       </c>
       <c r="E18">
-        <v>1.15</v>
+        <v>0.58</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2812,34 +2833,34 @@
         <v>15387</v>
       </c>
       <c r="H18">
-        <v>-4.97</v>
+        <v>-4.41</v>
       </c>
       <c r="I18">
-        <v>4.63</v>
+        <v>5.24</v>
       </c>
       <c r="J18">
-        <v>3.82</v>
+        <v>4.37</v>
       </c>
       <c r="K18">
-        <v>-3.47</v>
+        <v>-2.08</v>
       </c>
       <c r="L18">
-        <v>-2.41</v>
+        <v>-3.01</v>
       </c>
       <c r="N18">
-        <v>9.609999999999999</v>
+        <v>11.22</v>
       </c>
       <c r="O18">
         <v>75</v>
       </c>
       <c r="Q18">
-        <v>15715.73</v>
+        <v>15851.46</v>
       </c>
       <c r="R18">
-        <v>15842.7</v>
+        <v>15824.26</v>
       </c>
       <c r="S18">
-        <v>16284.21</v>
+        <v>16279.5</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
@@ -2851,40 +2872,40 @@
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>53.85</v>
+        <v>56.24</v>
       </c>
       <c r="AA18">
-        <v>-167.94</v>
+        <v>-123.22</v>
       </c>
       <c r="AB18">
-        <v>-212.34</v>
+        <v>-194.51</v>
       </c>
       <c r="AC18">
-        <v>44.4</v>
+        <v>71.3</v>
       </c>
       <c r="AD18">
         <v>100</v>
       </c>
       <c r="AE18">
-        <v>67.41</v>
+        <v>88.89</v>
       </c>
       <c r="AF18">
-        <v>259.68</v>
+        <v>251.91</v>
       </c>
       <c r="AH18">
-        <v>16405.23</v>
+        <v>16305.77</v>
       </c>
       <c r="AI18">
-        <v>15280.17</v>
+        <v>15342.75</v>
       </c>
       <c r="AJ18">
-        <v>15174.9</v>
+        <v>15386.85</v>
       </c>
       <c r="AK18" t="s">
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>51.79</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2898,10 +2919,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>8782.700000000001</v>
+        <v>8882.9</v>
       </c>
       <c r="E19">
-        <v>-0.42</v>
+        <v>1.14</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2910,34 +2931,34 @@
         <v>8561.200000000001</v>
       </c>
       <c r="H19">
-        <v>-12.16</v>
+        <v>-11.16</v>
       </c>
       <c r="I19">
-        <v>2.59</v>
+        <v>3.76</v>
       </c>
       <c r="J19">
-        <v>-1.29</v>
+        <v>1.06</v>
       </c>
       <c r="K19">
-        <v>-6.58</v>
+        <v>-3.77</v>
       </c>
       <c r="L19">
-        <v>-4.69</v>
+        <v>-3.67</v>
       </c>
       <c r="N19">
-        <v>-6.14</v>
+        <v>-3.25</v>
       </c>
       <c r="O19">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Q19">
-        <v>8723.09</v>
+        <v>8741.73</v>
       </c>
       <c r="R19">
-        <v>9049.02</v>
+        <v>9036.190000000001</v>
       </c>
       <c r="S19">
-        <v>9395.74</v>
+        <v>9376.57</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
@@ -2949,31 +2970,31 @@
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>39.1</v>
+        <v>43.02</v>
       </c>
       <c r="AA19">
-        <v>-175.46</v>
+        <v>-165.03</v>
       </c>
       <c r="AB19">
-        <v>-146.8</v>
+        <v>-150.45</v>
       </c>
       <c r="AC19">
-        <v>-28.66</v>
+        <v>-14.58</v>
       </c>
       <c r="AD19">
-        <v>42.68</v>
+        <v>58.55</v>
       </c>
       <c r="AE19">
-        <v>25.39</v>
+        <v>42.39</v>
       </c>
       <c r="AF19">
-        <v>190.59</v>
+        <v>188.11</v>
       </c>
       <c r="AH19">
-        <v>9501.66</v>
+        <v>9492.549999999999</v>
       </c>
       <c r="AI19">
-        <v>8596.389999999999</v>
+        <v>8579.82</v>
       </c>
       <c r="AJ19">
         <v>9128.139999999999</v>
@@ -2982,7 +3003,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>37.29</v>
+        <v>34.81</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -2996,10 +3017,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10296.6</v>
+        <v>10352.4</v>
       </c>
       <c r="E20">
-        <v>-2.27</v>
+        <v>0.54</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3008,34 +3029,34 @@
         <v>10296.6</v>
       </c>
       <c r="H20">
-        <v>-9.43</v>
+        <v>-8.94</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="J20">
-        <v>-2.27</v>
+        <v>-0.89</v>
       </c>
       <c r="K20">
-        <v>-5.21</v>
+        <v>-2.89</v>
       </c>
       <c r="L20">
-        <v>-6.97</v>
+        <v>-6.54</v>
       </c>
       <c r="N20">
-        <v>-16.29</v>
+        <v>-14.99</v>
       </c>
       <c r="O20">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="Q20">
-        <v>10435.95</v>
+        <v>10417.3</v>
       </c>
       <c r="R20">
-        <v>10484.75</v>
+        <v>10473.98</v>
       </c>
       <c r="S20">
-        <v>10822.64</v>
+        <v>10805.52</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
@@ -3047,31 +3068,31 @@
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>36.6</v>
+        <v>39.66</v>
       </c>
       <c r="AA20">
-        <v>-108.45</v>
+        <v>-110.22</v>
       </c>
       <c r="AB20">
-        <v>-120.13</v>
+        <v>-118.15</v>
       </c>
       <c r="AC20">
-        <v>11.69</v>
+        <v>7.93</v>
       </c>
       <c r="AD20">
-        <v>80.23</v>
+        <v>70.09</v>
       </c>
       <c r="AE20">
-        <v>76.92</v>
+        <v>77</v>
       </c>
       <c r="AF20">
-        <v>169.92</v>
+        <v>166.29</v>
       </c>
       <c r="AH20">
-        <v>10713.11</v>
+        <v>10706.16</v>
       </c>
       <c r="AI20">
-        <v>10256.38</v>
+        <v>10241.81</v>
       </c>
       <c r="AJ20">
         <v>10732.68</v>
@@ -3080,7 +3101,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>28.07</v>
+        <v>29.53</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3094,10 +3115,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>26722.1</v>
+        <v>27052.6</v>
       </c>
       <c r="E21">
-        <v>0.35</v>
+        <v>1.24</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3106,43 +3127,43 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-8.449999999999999</v>
+        <v>-7.32</v>
       </c>
       <c r="I21">
-        <v>10.67</v>
+        <v>12.04</v>
       </c>
       <c r="J21">
-        <v>-0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K21">
-        <v>-0.6</v>
+        <v>2.18</v>
       </c>
       <c r="L21">
-        <v>-6.27</v>
+        <v>-5.11</v>
       </c>
       <c r="M21">
-        <v>-5.37</v>
+        <v>-4.84</v>
       </c>
       <c r="N21">
-        <v>5.46</v>
+        <v>6.03</v>
       </c>
       <c r="O21">
         <v>70</v>
       </c>
       <c r="Q21">
-        <v>26739.64</v>
+        <v>26776.95</v>
       </c>
       <c r="R21">
-        <v>26982.05</v>
+        <v>27012.52</v>
       </c>
       <c r="S21">
-        <v>27231.28</v>
+        <v>27226.11</v>
       </c>
       <c r="T21">
-        <v>27372.97</v>
+        <v>27363.8</v>
       </c>
       <c r="U21">
-        <v>-2.38</v>
+        <v>-1.14</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
@@ -3157,31 +3178,31 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>43.45</v>
+        <v>50.02</v>
       </c>
       <c r="AA21">
-        <v>-116.9</v>
+        <v>-98.26000000000001</v>
       </c>
       <c r="AB21">
-        <v>-75.84999999999999</v>
+        <v>-80.33</v>
       </c>
       <c r="AC21">
-        <v>-41.05</v>
+        <v>-17.92</v>
       </c>
       <c r="AD21">
-        <v>11.3</v>
+        <v>20.98</v>
       </c>
       <c r="AE21">
-        <v>12.38</v>
+        <v>13.81</v>
       </c>
       <c r="AF21">
-        <v>382.65</v>
+        <v>391.86</v>
       </c>
       <c r="AH21">
-        <v>27660.04</v>
+        <v>27641.54</v>
       </c>
       <c r="AI21">
-        <v>26304.06</v>
+        <v>26383.5</v>
       </c>
       <c r="AJ21">
         <v>26545.98</v>
@@ -3190,7 +3211,7 @@
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>30.8</v>
+        <v>27.9</v>
       </c>
     </row>
   </sheetData>
@@ -3331,7 +3352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F159"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3371,7 +3392,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3391,7 +3412,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>94</v>
@@ -3403,2076 +3424,2082 @@
         <v>96</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>96</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-5.2</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-4.67</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.64</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-6.78</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.14</v>
+      <c r="B10" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-3.67</v>
+        <v>-4.67</v>
       </c>
       <c r="D11" s="6">
-        <v>-4.13</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-0.46</v>
+        <v>-3.32</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1.35</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-5.62</v>
+        <v>-6.78</v>
       </c>
       <c r="D12" s="6">
-        <v>-6.66</v>
-      </c>
-      <c r="E12" s="8">
-        <v>-1.04</v>
+        <v>-4.06</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2.72</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-5.77</v>
+        <v>-4.13</v>
       </c>
       <c r="D13" s="6">
-        <v>-6.67</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.9</v>
+        <v>-1.87</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2.26</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.61</v>
+        <v>-6.66</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.7</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.09</v>
+        <v>-3.8</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2.86</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>14.11</v>
+        <v>-6.67</v>
       </c>
       <c r="D15" s="6">
-        <v>12.05</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-2.06</v>
+        <v>-3.05</v>
+      </c>
+      <c r="E15" s="7">
+        <v>3.62</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.89</v>
+        <v>-2.7</v>
       </c>
       <c r="D16" s="6">
-        <v>-5.98</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-0.09</v>
+        <v>0.13</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2.83</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>-2.44</v>
+        <v>12.05</v>
       </c>
       <c r="D17" s="6">
-        <v>-2.99</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-0.55</v>
+        <v>13.46</v>
+      </c>
+      <c r="E17" s="7">
+        <v>1.41</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>3.91</v>
+        <v>-5.98</v>
       </c>
       <c r="D18" s="6">
-        <v>5.59</v>
+        <v>-4.25</v>
       </c>
       <c r="E18" s="7">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-9.470000000000001</v>
+        <v>-2.99</v>
       </c>
       <c r="D19" s="6">
-        <v>-10.07</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.6</v>
+        <v>0.11</v>
+      </c>
+      <c r="E19" s="7">
+        <v>3.1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>-5.3</v>
+        <v>5.59</v>
       </c>
       <c r="D20" s="6">
-        <v>-6.05</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-0.75</v>
+        <v>7.54</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.95</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-1.75</v>
+        <v>-10.07</v>
       </c>
       <c r="D21" s="6">
-        <v>-1.94</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-0.19</v>
+        <v>-7.83</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.24</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-2.82</v>
+        <v>-6.05</v>
       </c>
       <c r="D22" s="6">
-        <v>-1.71</v>
+        <v>-3.12</v>
       </c>
       <c r="E22" s="7">
-        <v>1.11</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-6.54</v>
+        <v>-1.94</v>
       </c>
       <c r="D23" s="6">
-        <v>-8.220000000000001</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-1.68</v>
+        <v>3.57</v>
+      </c>
+      <c r="E23" s="7">
+        <v>5.51</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>2.36</v>
+        <v>-1.71</v>
       </c>
       <c r="D24" s="6">
-        <v>1.38</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-0.98</v>
+        <v>-0.19</v>
+      </c>
+      <c r="E24" s="7">
+        <v>1.52</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-5.01</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="D25" s="6">
-        <v>-3.47</v>
+        <v>-3.65</v>
       </c>
       <c r="E25" s="7">
-        <v>1.54</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-5.79</v>
+        <v>1.38</v>
       </c>
       <c r="D26" s="6">
-        <v>-6.58</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.79</v>
+        <v>4.5</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.12</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-3.07</v>
+        <v>-3.47</v>
       </c>
       <c r="D27" s="6">
-        <v>-5.21</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.14</v>
+        <v>-2.08</v>
+      </c>
+      <c r="E27" s="7">
+        <v>1.39</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="6">
-        <v>-0.51</v>
+        <v>-6.58</v>
       </c>
       <c r="D28" s="6">
-        <v>-0.6</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.09</v>
+        <v>-3.77</v>
+      </c>
+      <c r="E28" s="7">
+        <v>2.81</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6">
-        <v>-0.98</v>
+        <v>-5.21</v>
       </c>
       <c r="D29" s="6">
-        <v>2.03</v>
+        <v>-2.89</v>
       </c>
       <c r="E29" s="7">
-        <v>3.01</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30" s="6">
-        <v>-0.68</v>
+        <v>-0.6</v>
       </c>
       <c r="D30" s="6">
-        <v>-0.65</v>
+        <v>2.18</v>
       </c>
       <c r="E30" s="7">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>-0.02</v>
+        <v>2.03</v>
       </c>
       <c r="D31" s="6">
-        <v>1.03</v>
+        <v>2.54</v>
       </c>
       <c r="E31" s="7">
-        <v>1.05</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-1.98</v>
+        <v>-0.65</v>
       </c>
       <c r="D32" s="6">
-        <v>-1.49</v>
+        <v>0.77</v>
       </c>
       <c r="E32" s="7">
-        <v>0.49</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>-1.95</v>
+        <v>1.03</v>
       </c>
       <c r="D33" s="6">
-        <v>-1.93</v>
+        <v>2.84</v>
       </c>
       <c r="E33" s="7">
-        <v>0.02</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>-2.73</v>
+        <v>-1.49</v>
       </c>
       <c r="D34" s="6">
-        <v>-1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E34" s="7">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>2.14</v>
+        <v>-1.93</v>
       </c>
       <c r="D35" s="6">
-        <v>-2.68</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-4.82</v>
+        <v>1.8</v>
+      </c>
+      <c r="E35" s="7">
+        <v>3.73</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.33</v>
+        <v>-1.11</v>
       </c>
       <c r="D36" s="6">
-        <v>0.61</v>
+        <v>0.19</v>
       </c>
       <c r="E36" s="7">
-        <v>1.94</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>0.6899999999999999</v>
+        <v>-2.68</v>
       </c>
       <c r="D37" s="6">
-        <v>0.65</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.04</v>
+        <v>-0.67</v>
+      </c>
+      <c r="E37" s="7">
+        <v>2.01</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>-1.75</v>
+        <v>0.61</v>
       </c>
       <c r="D38" s="6">
-        <v>0.91</v>
+        <v>1.54</v>
       </c>
       <c r="E38" s="7">
-        <v>2.66</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>-2.15</v>
+        <v>0.65</v>
       </c>
       <c r="D39" s="6">
-        <v>-0.76</v>
+        <v>2.33</v>
       </c>
       <c r="E39" s="7">
-        <v>1.39</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>-1.55</v>
+        <v>0.91</v>
       </c>
       <c r="D40" s="6">
-        <v>-1.11</v>
+        <v>4.47</v>
       </c>
       <c r="E40" s="7">
-        <v>0.44</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>-2.02</v>
+        <v>-0.76</v>
       </c>
       <c r="D41" s="6">
-        <v>-1.43</v>
+        <v>0.42</v>
       </c>
       <c r="E41" s="7">
-        <v>0.59</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>2.55</v>
+        <v>-1.11</v>
       </c>
       <c r="D42" s="6">
-        <v>3.82</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E42" s="7">
-        <v>1.27</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-1.35</v>
+        <v>-1.43</v>
       </c>
       <c r="D43" s="6">
-        <v>-0.99</v>
+        <v>0.67</v>
       </c>
       <c r="E43" s="7">
-        <v>0.36</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>0.45</v>
+        <v>3.82</v>
       </c>
       <c r="D44" s="6">
-        <v>-0.47</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-0.92</v>
+        <v>4.35</v>
+      </c>
+      <c r="E44" s="7">
+        <v>0.53</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>2.31</v>
+        <v>-0.99</v>
       </c>
       <c r="D45" s="6">
-        <v>3.82</v>
+        <v>2.03</v>
       </c>
       <c r="E45" s="7">
-        <v>1.51</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-3.34</v>
+        <v>-0.47</v>
       </c>
       <c r="D46" s="6">
-        <v>-1.29</v>
+        <v>1.69</v>
       </c>
       <c r="E46" s="7">
-        <v>2.05</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C47" s="6">
-        <v>-0.08</v>
+        <v>3.82</v>
       </c>
       <c r="D47" s="6">
-        <v>-2.27</v>
-      </c>
-      <c r="E47" s="8">
-        <v>-2.19</v>
+        <v>4.37</v>
+      </c>
+      <c r="E47" s="7">
+        <v>0.55</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C48" s="6">
-        <v>-2.06</v>
+        <v>-1.29</v>
       </c>
       <c r="D48" s="6">
-        <v>-0.68</v>
+        <v>1.06</v>
       </c>
       <c r="E48" s="7">
-        <v>1.38</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C49" s="6">
-        <v>-6.31</v>
+        <v>-2.27</v>
       </c>
       <c r="D49" s="6">
-        <v>-5.59</v>
+        <v>-0.89</v>
       </c>
       <c r="E49" s="7">
-        <v>0.72</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C50" s="6">
-        <v>-2.53</v>
+        <v>-0.68</v>
       </c>
       <c r="D50" s="6">
-        <v>-3.27</v>
-      </c>
-      <c r="E50" s="8">
-        <v>-0.74</v>
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="E50" s="7">
+        <v>1.37</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>-12.39</v>
+        <v>-5.59</v>
       </c>
       <c r="D51" s="6">
-        <v>-13.28</v>
+        <v>-5.66</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.89</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-0.58</v>
+        <v>-3.27</v>
       </c>
       <c r="D52" s="6">
-        <v>-1.27</v>
-      </c>
-      <c r="E52" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-2.73</v>
+      </c>
+      <c r="E52" s="7">
+        <v>0.54</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-22.8</v>
+        <v>-13.28</v>
       </c>
       <c r="D53" s="6">
-        <v>-24.27</v>
-      </c>
-      <c r="E53" s="8">
-        <v>-1.47</v>
+        <v>-12.5</v>
+      </c>
+      <c r="E53" s="7">
+        <v>0.78</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-11.24</v>
+        <v>-1.27</v>
       </c>
       <c r="D54" s="6">
-        <v>-11.33</v>
-      </c>
-      <c r="E54" s="8">
-        <v>-0.09</v>
+        <v>-0.74</v>
+      </c>
+      <c r="E54" s="7">
+        <v>0.53</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-9.4</v>
+        <v>-24.27</v>
       </c>
       <c r="D55" s="6">
-        <v>-9.720000000000001</v>
-      </c>
-      <c r="E55" s="8">
-        <v>-0.32</v>
+        <v>-22.46</v>
+      </c>
+      <c r="E55" s="7">
+        <v>1.81</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-6.22</v>
+        <v>-11.33</v>
       </c>
       <c r="D56" s="6">
-        <v>-6.94</v>
-      </c>
-      <c r="E56" s="8">
-        <v>-0.72</v>
+        <v>-10.18</v>
+      </c>
+      <c r="E56" s="7">
+        <v>1.15</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>4.62</v>
+        <v>-9.720000000000001</v>
       </c>
       <c r="D57" s="6">
-        <v>7.75</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="E57" s="7">
-        <v>3.13</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>14.77</v>
+        <v>-6.94</v>
       </c>
       <c r="D58" s="6">
-        <v>15.39</v>
-      </c>
-      <c r="E58" s="7">
-        <v>0.62</v>
+        <v>-7.07</v>
+      </c>
+      <c r="E58" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>-8.890000000000001</v>
+        <v>7.75</v>
       </c>
       <c r="D59" s="6">
-        <v>-9.109999999999999</v>
-      </c>
-      <c r="E59" s="8">
-        <v>-0.22</v>
+        <v>7.99</v>
+      </c>
+      <c r="E59" s="7">
+        <v>0.24</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>5.7</v>
+        <v>15.39</v>
       </c>
       <c r="D60" s="6">
-        <v>6.48</v>
+        <v>16.25</v>
       </c>
       <c r="E60" s="7">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>18.84</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="D61" s="6">
-        <v>19.27</v>
+        <v>-8.32</v>
       </c>
       <c r="E61" s="7">
-        <v>0.43</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>-13.7</v>
+        <v>6.48</v>
       </c>
       <c r="D62" s="6">
-        <v>-14.55</v>
+        <v>5.79</v>
       </c>
       <c r="E62" s="8">
-        <v>-0.85</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C63" s="6">
-        <v>-9.43</v>
+        <v>19.27</v>
       </c>
       <c r="D63" s="6">
-        <v>-10.28</v>
+        <v>19.03</v>
       </c>
       <c r="E63" s="8">
-        <v>-0.85</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C64" s="6">
-        <v>-5.36</v>
+        <v>-14.55</v>
       </c>
       <c r="D64" s="6">
-        <v>-5.37</v>
-      </c>
-      <c r="E64" s="8">
-        <v>-0.01</v>
+        <v>-12.62</v>
+      </c>
+      <c r="E64" s="7">
+        <v>1.93</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65" s="6">
-        <v>-6.49</v>
+        <v>-10.28</v>
       </c>
       <c r="D65" s="6">
-        <v>-5.14</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="E65" s="7">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66" s="6">
-        <v>-8.68</v>
+        <v>-5.37</v>
       </c>
       <c r="D66" s="6">
-        <v>-9.550000000000001</v>
-      </c>
-      <c r="E66" s="8">
-        <v>-0.87</v>
+        <v>-4.84</v>
+      </c>
+      <c r="E66" s="7">
+        <v>0.53</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-6.56</v>
+        <v>-5.14</v>
       </c>
       <c r="D67" s="6">
-        <v>-6.5</v>
-      </c>
-      <c r="E67" s="7">
-        <v>0.06</v>
+        <v>-5.37</v>
+      </c>
+      <c r="E67" s="8">
+        <v>-0.23</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-10.22</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="D68" s="6">
-        <v>-11.03</v>
-      </c>
-      <c r="E68" s="8">
-        <v>-0.8100000000000001</v>
+        <v>-8.6</v>
+      </c>
+      <c r="E68" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-11.55</v>
+        <v>-6.5</v>
       </c>
       <c r="D69" s="6">
-        <v>-12.04</v>
-      </c>
-      <c r="E69" s="8">
-        <v>-0.49</v>
+        <v>-5.52</v>
+      </c>
+      <c r="E69" s="7">
+        <v>0.98</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-9.66</v>
+        <v>-11.03</v>
       </c>
       <c r="D70" s="6">
-        <v>-9.24</v>
+        <v>-10.13</v>
       </c>
       <c r="E70" s="7">
-        <v>0.42</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>9.33</v>
+        <v>-12.04</v>
       </c>
       <c r="D71" s="6">
-        <v>3.73</v>
-      </c>
-      <c r="E71" s="8">
-        <v>-5.6</v>
+        <v>-9.98</v>
+      </c>
+      <c r="E71" s="7">
+        <v>2.06</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-7.1</v>
+        <v>-9.24</v>
       </c>
       <c r="D72" s="6">
-        <v>-6.33</v>
+        <v>-8.17</v>
       </c>
       <c r="E72" s="7">
-        <v>0.77</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>-6.94</v>
+        <v>3.73</v>
       </c>
       <c r="D73" s="6">
-        <v>-7.33</v>
+        <v>2.39</v>
       </c>
       <c r="E73" s="8">
-        <v>-0.39</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>6.15</v>
+        <v>-6.33</v>
       </c>
       <c r="D74" s="6">
-        <v>7.62</v>
-      </c>
-      <c r="E74" s="7">
-        <v>1.47</v>
+        <v>-6.72</v>
+      </c>
+      <c r="E74" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-5.07</v>
+        <v>-7.33</v>
       </c>
       <c r="D75" s="6">
-        <v>-5.37</v>
-      </c>
-      <c r="E75" s="8">
-        <v>-0.3</v>
+        <v>-6.24</v>
+      </c>
+      <c r="E75" s="7">
+        <v>1.09</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>-8.949999999999999</v>
+        <v>7.62</v>
       </c>
       <c r="D76" s="6">
-        <v>-9.51</v>
-      </c>
-      <c r="E76" s="8">
-        <v>-0.5600000000000001</v>
+        <v>8.800000000000001</v>
+      </c>
+      <c r="E76" s="7">
+        <v>1.18</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>-3.04</v>
+        <v>-5.37</v>
       </c>
       <c r="D77" s="6">
-        <v>-2.96</v>
+        <v>-4.73</v>
       </c>
       <c r="E77" s="7">
-        <v>0.08</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>1.24</v>
+        <v>-9.51</v>
       </c>
       <c r="D78" s="6">
-        <v>2.09</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="E78" s="7">
-        <v>0.85</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-12.37</v>
+        <v>-2.96</v>
       </c>
       <c r="D79" s="6">
-        <v>-13.15</v>
-      </c>
-      <c r="E79" s="8">
-        <v>-0.78</v>
+        <v>-0.83</v>
+      </c>
+      <c r="E79" s="7">
+        <v>2.13</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>-3.83</v>
+        <v>2.09</v>
       </c>
       <c r="D80" s="6">
-        <v>-4.51</v>
+        <v>1.28</v>
       </c>
       <c r="E80" s="8">
-        <v>-0.68</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-3.37</v>
+        <v>-13.15</v>
       </c>
       <c r="D81" s="6">
-        <v>-2.41</v>
+        <v>-10.77</v>
       </c>
       <c r="E81" s="7">
-        <v>0.96</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-6.37</v>
+        <v>-4.51</v>
       </c>
       <c r="D82" s="6">
-        <v>-4.69</v>
+        <v>-2.97</v>
       </c>
       <c r="E82" s="7">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C83" s="6">
-        <v>-4.9</v>
+        <v>-2.41</v>
       </c>
       <c r="D83" s="6">
-        <v>-6.97</v>
+        <v>-3.01</v>
       </c>
       <c r="E83" s="8">
-        <v>-2.07</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C84" s="6">
-        <v>-6.59</v>
+        <v>-4.69</v>
       </c>
       <c r="D84" s="6">
-        <v>-6.27</v>
+        <v>-3.67</v>
       </c>
       <c r="E84" s="7">
-        <v>0.32</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C85" s="6">
-        <v>-14.53</v>
+        <v>-6.97</v>
       </c>
       <c r="D85" s="6">
-        <v>-13.29</v>
+        <v>-6.54</v>
       </c>
       <c r="E85" s="7">
-        <v>1.24</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C86" s="6">
-        <v>-14.52</v>
+        <v>-6.27</v>
       </c>
       <c r="D86" s="6">
-        <v>-15.33</v>
-      </c>
-      <c r="E86" s="8">
-        <v>-0.8100000000000001</v>
+        <v>-5.11</v>
+      </c>
+      <c r="E86" s="7">
+        <v>1.16</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-13.47</v>
+        <v>-13.29</v>
       </c>
       <c r="D87" s="6">
-        <v>-13.41</v>
-      </c>
-      <c r="E87" s="7">
-        <v>0.06</v>
+        <v>-13.5</v>
+      </c>
+      <c r="E87" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-15.1</v>
+        <v>-15.33</v>
       </c>
       <c r="D88" s="6">
-        <v>-15.86</v>
-      </c>
-      <c r="E88" s="8">
-        <v>-0.76</v>
+        <v>-14.44</v>
+      </c>
+      <c r="E88" s="7">
+        <v>0.89</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-24.05</v>
+        <v>-13.41</v>
       </c>
       <c r="D89" s="6">
-        <v>-24.47</v>
-      </c>
-      <c r="E89" s="8">
-        <v>-0.42</v>
+        <v>-12.46</v>
+      </c>
+      <c r="E89" s="7">
+        <v>0.95</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-14.61</v>
+        <v>-15.86</v>
       </c>
       <c r="D90" s="6">
-        <v>-14.21</v>
+        <v>-15.02</v>
       </c>
       <c r="E90" s="7">
-        <v>0.4</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-18.48</v>
+        <v>-24.47</v>
       </c>
       <c r="D91" s="6">
-        <v>-20.09</v>
-      </c>
-      <c r="E91" s="8">
-        <v>-1.61</v>
+        <v>-22.7</v>
+      </c>
+      <c r="E91" s="7">
+        <v>1.77</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-10.71</v>
+        <v>-14.21</v>
       </c>
       <c r="D92" s="6">
-        <v>-10.39</v>
+        <v>-13.21</v>
       </c>
       <c r="E92" s="7">
-        <v>0.32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-10.64</v>
+        <v>-20.09</v>
       </c>
       <c r="D93" s="6">
-        <v>-11.02</v>
-      </c>
-      <c r="E93" s="8">
-        <v>-0.38</v>
+        <v>-19.3</v>
+      </c>
+      <c r="E93" s="7">
+        <v>0.79</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-2.01</v>
+        <v>-10.39</v>
       </c>
       <c r="D94" s="6">
-        <v>-0.66</v>
+        <v>-10.12</v>
       </c>
       <c r="E94" s="7">
-        <v>1.35</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-13.93</v>
+        <v>-11.02</v>
       </c>
       <c r="D95" s="6">
-        <v>-14.21</v>
-      </c>
-      <c r="E95" s="8">
-        <v>-0.28</v>
+        <v>-9.970000000000001</v>
+      </c>
+      <c r="E95" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-15.95</v>
+        <v>-0.66</v>
       </c>
       <c r="D96" s="6">
-        <v>-16.46</v>
-      </c>
-      <c r="E96" s="8">
-        <v>-0.51</v>
+        <v>0</v>
+      </c>
+      <c r="E96" s="7">
+        <v>0.66</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-17.74</v>
+        <v>-14.21</v>
       </c>
       <c r="D97" s="6">
-        <v>-17.67</v>
+        <v>-13.63</v>
       </c>
       <c r="E97" s="7">
-        <v>0.07000000000000001</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-3.38</v>
+        <v>-16.46</v>
       </c>
       <c r="D98" s="6">
-        <v>-2.37</v>
+        <v>-15.5</v>
       </c>
       <c r="E98" s="7">
-        <v>1.01</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-16.89</v>
+        <v>-17.67</v>
       </c>
       <c r="D99" s="6">
-        <v>-17.63</v>
-      </c>
-      <c r="E99" s="8">
-        <v>-0.74</v>
+        <v>-15.86</v>
+      </c>
+      <c r="E99" s="7">
+        <v>1.81</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-11.33</v>
+        <v>-2.37</v>
       </c>
       <c r="D100" s="6">
-        <v>-11.96</v>
-      </c>
-      <c r="E100" s="8">
-        <v>-0.63</v>
+        <v>-1.75</v>
+      </c>
+      <c r="E100" s="7">
+        <v>0.62</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-6.04</v>
+        <v>-17.63</v>
       </c>
       <c r="D101" s="6">
-        <v>-4.97</v>
+        <v>-15.37</v>
       </c>
       <c r="E101" s="7">
-        <v>1.07</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-11.79</v>
+        <v>-11.96</v>
       </c>
       <c r="D102" s="6">
-        <v>-12.16</v>
-      </c>
-      <c r="E102" s="8">
-        <v>-0.37</v>
+        <v>-10.54</v>
+      </c>
+      <c r="E102" s="7">
+        <v>1.42</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="6">
-        <v>-7.33</v>
+        <v>-4.97</v>
       </c>
       <c r="D103" s="6">
-        <v>-9.43</v>
-      </c>
-      <c r="E103" s="8">
-        <v>-2.1</v>
+        <v>-4.41</v>
+      </c>
+      <c r="E103" s="7">
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C104" s="6">
-        <v>-8.77</v>
+        <v>-12.16</v>
       </c>
       <c r="D104" s="6">
-        <v>-8.449999999999999</v>
+        <v>-11.16</v>
       </c>
       <c r="E104" s="7">
-        <v>0.32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C105" s="6">
-        <v>25340.8</v>
+        <v>-9.43</v>
       </c>
       <c r="D105" s="6">
-        <v>25707.35</v>
+        <v>-8.94</v>
       </c>
       <c r="E105" s="7">
-        <v>366.55</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C106" s="6">
-        <v>8978.65</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="D106" s="6">
-        <v>8893.5</v>
-      </c>
-      <c r="E106" s="8">
-        <v>-85.15000000000001</v>
+        <v>-7.32</v>
+      </c>
+      <c r="E106" s="7">
+        <v>1.13</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>10936.65</v>
+        <v>25707.35</v>
       </c>
       <c r="D107" s="6">
-        <v>10944.35</v>
-      </c>
-      <c r="E107" s="7">
-        <v>7.7</v>
+        <v>25645.6</v>
+      </c>
+      <c r="E107" s="8">
+        <v>-61.75</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>35261.85</v>
+        <v>8893.5</v>
       </c>
       <c r="D108" s="6">
-        <v>34946.3</v>
-      </c>
-      <c r="E108" s="8">
-        <v>-315.55</v>
+        <v>8986.450000000001</v>
+      </c>
+      <c r="E108" s="7">
+        <v>92.95</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>43118.2</v>
+        <v>10944.35</v>
       </c>
       <c r="D109" s="6">
-        <v>42878.35</v>
-      </c>
-      <c r="E109" s="8">
-        <v>-239.85</v>
+        <v>11059.15</v>
+      </c>
+      <c r="E109" s="7">
+        <v>114.8</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>24303.75</v>
+        <v>34946.3</v>
       </c>
       <c r="D110" s="6">
-        <v>24418.25</v>
+        <v>35299</v>
       </c>
       <c r="E110" s="7">
-        <v>114.5</v>
+        <v>352.7</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>32189.45</v>
+        <v>42878.35</v>
       </c>
       <c r="D111" s="6">
-        <v>31553.4</v>
-      </c>
-      <c r="E111" s="8">
-        <v>-636.05</v>
+        <v>43882.95</v>
+      </c>
+      <c r="E111" s="7">
+        <v>1004.6</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>14878.4</v>
+        <v>24418.25</v>
       </c>
       <c r="D112" s="6">
-        <v>14931.6</v>
+        <v>24704.55</v>
       </c>
       <c r="E112" s="7">
-        <v>53.2</v>
+        <v>286.3</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>8726.6</v>
+        <v>31553.4</v>
       </c>
       <c r="D113" s="6">
-        <v>8690.049999999999</v>
-      </c>
-      <c r="E113" s="8">
-        <v>-36.55</v>
+        <v>31866.4</v>
+      </c>
+      <c r="E113" s="7">
+        <v>313</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>1615.05</v>
+        <v>14931.6</v>
       </c>
       <c r="D114" s="6">
-        <v>1637.4</v>
+        <v>14975.8</v>
       </c>
       <c r="E114" s="7">
-        <v>22.35</v>
+        <v>44.2</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>11806.7</v>
+        <v>8690.049999999999</v>
       </c>
       <c r="D115" s="6">
-        <v>11769.35</v>
-      </c>
-      <c r="E115" s="8">
-        <v>-37.35</v>
+        <v>8792.5</v>
+      </c>
+      <c r="E115" s="7">
+        <v>102.45</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>9048.6</v>
+        <v>1637.4</v>
       </c>
       <c r="D116" s="6">
-        <v>8993.65</v>
-      </c>
-      <c r="E116" s="8">
-        <v>-54.95</v>
+        <v>1655.35</v>
+      </c>
+      <c r="E116" s="7">
+        <v>17.95</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>8126.7</v>
+        <v>11769.35</v>
       </c>
       <c r="D117" s="6">
-        <v>8133.6</v>
+        <v>11848.45</v>
       </c>
       <c r="E117" s="7">
-        <v>6.9</v>
+        <v>79.09999999999999</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>26267.25</v>
+        <v>8993.65</v>
       </c>
       <c r="D118" s="6">
-        <v>26541.35</v>
+        <v>9097.1</v>
       </c>
       <c r="E118" s="7">
-        <v>274.1</v>
+        <v>103.45</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>805.05</v>
+        <v>8133.6</v>
       </c>
       <c r="D119" s="6">
-        <v>797.85</v>
-      </c>
-      <c r="E119" s="8">
-        <v>-7.2</v>
+        <v>8312.5</v>
+      </c>
+      <c r="E119" s="7">
+        <v>178.9</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>30236</v>
+        <v>26541.35</v>
       </c>
       <c r="D120" s="6">
-        <v>30022.85</v>
-      </c>
-      <c r="E120" s="8">
-        <v>-213.15</v>
+        <v>26710.8</v>
+      </c>
+      <c r="E120" s="7">
+        <v>169.45</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>15917.6</v>
+        <v>797.85</v>
       </c>
       <c r="D121" s="6">
-        <v>16100.1</v>
+        <v>819.8</v>
       </c>
       <c r="E121" s="7">
-        <v>182.5</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>8819.9</v>
+        <v>30022.85</v>
       </c>
       <c r="D122" s="6">
-        <v>8782.700000000001</v>
-      </c>
-      <c r="E122" s="8">
-        <v>-37.2</v>
+        <v>30506.2</v>
+      </c>
+      <c r="E122" s="7">
+        <v>483.35</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C123" s="6">
-        <v>10536</v>
+        <v>16100.1</v>
       </c>
       <c r="D123" s="6">
-        <v>10296.6</v>
-      </c>
-      <c r="E123" s="8">
-        <v>-239.4</v>
+        <v>16193.9</v>
+      </c>
+      <c r="E123" s="7">
+        <v>93.8</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C124" s="6">
-        <v>26628.45</v>
+        <v>8782.700000000001</v>
       </c>
       <c r="D124" s="6">
-        <v>26722.1</v>
+        <v>8882.9</v>
       </c>
       <c r="E124" s="7">
-        <v>93.65000000000001</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C125" s="6">
-        <v>40</v>
+        <v>10296.6</v>
       </c>
       <c r="D125" s="6">
-        <v>65</v>
+        <v>10352.4</v>
       </c>
       <c r="E125" s="7">
-        <v>25</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C126" s="6">
-        <v>50</v>
+        <v>26722.1</v>
       </c>
       <c r="D126" s="6">
-        <v>30</v>
-      </c>
-      <c r="E126" s="8">
-        <v>-20</v>
+        <v>27052.6</v>
+      </c>
+      <c r="E126" s="7">
+        <v>330.5</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="6">
+        <v>65</v>
+      </c>
+      <c r="D127" s="6">
         <v>55</v>
-      </c>
-      <c r="D127" s="6">
-        <v>45</v>
       </c>
       <c r="E127" s="8">
         <v>-10</v>
@@ -5480,41 +5507,41 @@
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="D128" s="6">
-        <v>80</v>
-      </c>
-      <c r="E128" s="8">
-        <v>-10</v>
+        <v>35</v>
+      </c>
+      <c r="E128" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D129" s="6">
-        <v>50</v>
-      </c>
-      <c r="E129" s="7">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="E129" s="8">
+        <v>-5</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
@@ -5523,458 +5550,509 @@
         <v>45</v>
       </c>
       <c r="D130" s="6">
-        <v>40</v>
-      </c>
-      <c r="E130" s="8">
-        <v>-5</v>
+        <v>50</v>
+      </c>
+      <c r="E130" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="6">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="D131" s="6">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="E131" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C132" s="6">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D132" s="6">
-        <v>85</v>
-      </c>
-      <c r="E132" s="7">
-        <v>5</v>
+        <v>30</v>
+      </c>
+      <c r="E132" s="8">
+        <v>-20</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C133" s="6">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="D133" s="6">
-        <v>55</v>
-      </c>
-      <c r="E133" s="8">
-        <v>-10</v>
+        <v>45</v>
+      </c>
+      <c r="E133" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C134" s="6">
-        <v>35</v>
+        <v>95</v>
       </c>
       <c r="D134" s="6">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="E134" s="7">
-        <v>25</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C135" s="6">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="D135" s="6">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E135" s="8">
-        <v>-35</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C136" s="6">
-        <v>60</v>
+        <v>99</v>
       </c>
       <c r="D136" s="6">
-        <v>70</v>
-      </c>
-      <c r="E136" s="7">
-        <v>10</v>
+        <v>95</v>
+      </c>
+      <c r="E136" s="8">
+        <v>-4</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C137" s="6">
-        <v>42.77</v>
+        <v>55</v>
       </c>
       <c r="D137" s="6">
-        <v>48.38</v>
+        <v>60</v>
       </c>
       <c r="E137" s="7">
-        <v>5.61</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C138" s="6">
-        <v>41.22</v>
+        <v>60</v>
       </c>
       <c r="D138" s="6">
-        <v>38.01</v>
-      </c>
-      <c r="E138" s="8">
-        <v>-3.21</v>
+        <v>65</v>
+      </c>
+      <c r="E138" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C139" s="6">
+        <v>35</v>
+      </c>
+      <c r="D139" s="6">
         <v>40</v>
       </c>
-      <c r="B139" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C139" s="6">
-        <v>44.7</v>
-      </c>
-      <c r="D139" s="6">
-        <v>45.05</v>
-      </c>
       <c r="E139" s="7">
-        <v>0.35</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>37.32</v>
+        <v>48.38</v>
       </c>
       <c r="D140" s="6">
-        <v>34.56</v>
+        <v>47.54</v>
       </c>
       <c r="E140" s="8">
-        <v>-2.76</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>38.09</v>
+        <v>38.01</v>
       </c>
       <c r="D141" s="6">
-        <v>36.58</v>
-      </c>
-      <c r="E141" s="8">
-        <v>-1.51</v>
+        <v>43.21</v>
+      </c>
+      <c r="E141" s="7">
+        <v>5.2</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>36.45</v>
+        <v>45.05</v>
       </c>
       <c r="D142" s="6">
-        <v>39.23</v>
+        <v>50.12</v>
       </c>
       <c r="E142" s="7">
-        <v>2.78</v>
+        <v>5.07</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>68.48999999999999</v>
+        <v>34.56</v>
       </c>
       <c r="D143" s="6">
-        <v>61</v>
-      </c>
-      <c r="E143" s="8">
-        <v>-7.49</v>
+        <v>39.91</v>
+      </c>
+      <c r="E143" s="7">
+        <v>5.35</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>39.72</v>
+        <v>36.58</v>
       </c>
       <c r="D144" s="6">
-        <v>41.48</v>
+        <v>46.16</v>
       </c>
       <c r="E144" s="7">
-        <v>1.76</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>48.34</v>
+        <v>39.23</v>
       </c>
       <c r="D145" s="6">
-        <v>46.38</v>
-      </c>
-      <c r="E145" s="8">
-        <v>-1.96</v>
+        <v>45.65</v>
+      </c>
+      <c r="E145" s="7">
+        <v>6.42</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>55.08</v>
+        <v>61</v>
       </c>
       <c r="D146" s="6">
-        <v>58.26</v>
+        <v>63.14</v>
       </c>
       <c r="E146" s="7">
-        <v>3.18</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>38.41</v>
+        <v>41.48</v>
       </c>
       <c r="D147" s="6">
-        <v>37.69</v>
-      </c>
-      <c r="E147" s="8">
-        <v>-0.72</v>
+        <v>42.97</v>
+      </c>
+      <c r="E147" s="7">
+        <v>1.49</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>38.86</v>
+        <v>46.38</v>
       </c>
       <c r="D148" s="6">
-        <v>36.72</v>
-      </c>
-      <c r="E148" s="8">
-        <v>-2.14</v>
+        <v>52.23</v>
+      </c>
+      <c r="E148" s="7">
+        <v>5.85</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>47.39</v>
+        <v>58.26</v>
       </c>
       <c r="D149" s="6">
-        <v>47.75</v>
+        <v>60.66</v>
       </c>
       <c r="E149" s="7">
-        <v>0.36</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>53.07</v>
+        <v>37.69</v>
       </c>
       <c r="D150" s="6">
-        <v>57.28</v>
+        <v>40.23</v>
       </c>
       <c r="E150" s="7">
-        <v>4.21</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>41.89</v>
+        <v>36.72</v>
       </c>
       <c r="D151" s="6">
-        <v>39.78</v>
-      </c>
-      <c r="E151" s="8">
-        <v>-2.11</v>
+        <v>43.08</v>
+      </c>
+      <c r="E151" s="7">
+        <v>6.36</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C152" s="6">
-        <v>57.27</v>
+        <v>47.75</v>
       </c>
       <c r="D152" s="6">
-        <v>53.23</v>
-      </c>
-      <c r="E152" s="8">
-        <v>-4.04</v>
+        <v>56.21</v>
+      </c>
+      <c r="E152" s="7">
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C153" s="6">
-        <v>48.79</v>
+        <v>57.28</v>
       </c>
       <c r="D153" s="6">
-        <v>53.85</v>
+        <v>59.68</v>
       </c>
       <c r="E153" s="7">
-        <v>5.06</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C154" s="6">
-        <v>40.05</v>
+        <v>39.78</v>
       </c>
       <c r="D154" s="6">
-        <v>39.1</v>
-      </c>
-      <c r="E154" s="8">
-        <v>-0.95</v>
+        <v>48.33</v>
+      </c>
+      <c r="E154" s="7">
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C155" s="6">
-        <v>45.86</v>
+        <v>53.23</v>
       </c>
       <c r="D155" s="6">
-        <v>36.6</v>
-      </c>
-      <c r="E155" s="8">
-        <v>-9.26</v>
+        <v>60.1</v>
+      </c>
+      <c r="E155" s="7">
+        <v>6.87</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C156" s="6">
-        <v>41.43</v>
+        <v>53.85</v>
       </c>
       <c r="D156" s="6">
+        <v>56.24</v>
+      </c>
+      <c r="E156" s="7">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
+      <c r="A157" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C157" s="6">
+        <v>39.1</v>
+      </c>
+      <c r="D157" s="6">
+        <v>43.02</v>
+      </c>
+      <c r="E157" s="7">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
+      <c r="A158" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C158" s="6">
+        <v>36.6</v>
+      </c>
+      <c r="D158" s="6">
+        <v>39.66</v>
+      </c>
+      <c r="E158" s="7">
+        <v>3.06</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
+      <c r="A159" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C159" s="6">
         <v>43.45</v>
       </c>
-      <c r="E156" s="7">
-        <v>2.02</v>
+      <c r="D159" s="6">
+        <v>50.02</v>
+      </c>
+      <c r="E159" s="7">
+        <v>6.57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5998,28 +6076,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6033,16 +6111,16 @@
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>44.7</v>
+        <v>49.4</v>
       </c>
       <c r="E2" s="11">
         <v>18.8</v>
       </c>
       <c r="F2" s="11">
-        <v>-3.3</v>
+        <v>-0.6</v>
       </c>
       <c r="G2" s="11">
-        <v>-5.5</v>
+        <v>-4.7</v>
       </c>
       <c r="H2" s="11">
         <v>52.4</v>
@@ -6153,10 +6231,10 @@
         <v>50</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>38</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>49</v>
       </c>
       <c r="D1" s="13" t="s">
         <v>48</v>
@@ -6168,10 +6246,10 @@
         <v>46</v>
       </c>
       <c r="G1" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="H1" s="13" t="s">
         <v>52</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="I1" s="13" t="s">
         <v>40</v>
@@ -6182,34 +6260,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2391</v>
+        <v>0.2409</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1795</v>
+        <v>0.1783</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1737</v>
+        <v>0.1782</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1625</v>
+        <v>0.1633</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1401</v>
+        <v>0.1399</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1133</v>
+        <v>0.1175</v>
       </c>
       <c r="G2" s="14">
-        <v>0.09949999999999999</v>
+        <v>0.1122</v>
       </c>
       <c r="H2" s="14">
-        <v>0.09609999999999999</v>
+        <v>0.1045</v>
       </c>
       <c r="I2" s="14">
-        <v>0.09230000000000001</v>
+        <v>0.09449999999999999</v>
       </c>
       <c r="J2" s="14">
-        <v>0.09140000000000001</v>
+        <v>0.09390000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6232,10 +6310,10 @@
         <v>44</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>55</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>45</v>
@@ -6246,34 +6324,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0819</v>
+        <v>0.0872</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0546</v>
+        <v>0.0603</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0516</v>
+        <v>0.0562</v>
       </c>
       <c r="D4" s="14">
-        <v>0.03700000000000001</v>
+        <v>0.0428</v>
       </c>
       <c r="E4" s="14">
-        <v>0.0233</v>
+        <v>0.028</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.02</v>
+        <v>-0.0152</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0601</v>
+        <v>-0.0325</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0614</v>
+        <v>-0.0592</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1189</v>
+        <v>-0.1112</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.1629</v>
+        <v>-0.1499</v>
       </c>
     </row>
   </sheetData>

--- a/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
+++ b/NSE_SECTORAL_INDICES_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="105">
   <si>
     <t>Symbol</t>
   </si>
@@ -289,61 +289,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-2.4% → -1.8%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-2.4%</t>
-  </si>
-  <si>
-    <t>-1.8%</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>45.0 → 50.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>45.0</t>
-  </si>
-  <si>
-    <t>50.1</t>
-  </si>
-  <si>
-    <t>46.4 → 52.2</t>
-  </si>
-  <si>
-    <t>46.4</t>
-  </si>
-  <si>
-    <t>52.2</t>
-  </si>
-  <si>
-    <t>47.8 → 56.2</t>
-  </si>
-  <si>
-    <t>47.8</t>
-  </si>
-  <si>
-    <t>56.2</t>
-  </si>
-  <si>
-    <t>43.5 → 50.0</t>
-  </si>
-  <si>
-    <t>43.5</t>
-  </si>
-  <si>
-    <t>50.0</t>
+    <t>50 DMA &gt; 200 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
+  </si>
+  <si>
+    <t>🔴 DEATH CROSS</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -429,14 +381,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -469,13 +421,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -555,8 +507,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1073,10 +1025,10 @@
         <v>78</v>
       </c>
       <c r="D2">
-        <v>25645.6</v>
+        <v>25422.7</v>
       </c>
       <c r="E2">
-        <v>-0.24</v>
+        <v>-0.87</v>
       </c>
       <c r="F2">
         <v>29647.9</v>
@@ -1085,82 +1037,82 @@
         <v>23769.6</v>
       </c>
       <c r="H2">
-        <v>-13.5</v>
+        <v>-14.25</v>
       </c>
       <c r="I2">
-        <v>7.89</v>
+        <v>6.95</v>
       </c>
       <c r="J2">
-        <v>2.54</v>
+        <v>2.25</v>
       </c>
       <c r="K2">
-        <v>-3.32</v>
+        <v>-2.87</v>
       </c>
       <c r="L2">
-        <v>-5.37</v>
+        <v>-10.1</v>
       </c>
       <c r="M2">
-        <v>-5.66</v>
+        <v>-6.64</v>
       </c>
       <c r="N2">
-        <v>17.82</v>
+        <v>17.38</v>
       </c>
       <c r="O2">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="Q2">
-        <v>25305.36</v>
+        <v>25417.44</v>
       </c>
       <c r="R2">
-        <v>25322.92</v>
+        <v>25279.35</v>
       </c>
       <c r="S2">
-        <v>26862.62</v>
+        <v>26785.78</v>
       </c>
       <c r="T2">
-        <v>26844.65</v>
+        <v>26827.16</v>
       </c>
       <c r="U2">
-        <v>-4.47</v>
+        <v>-5.24</v>
       </c>
       <c r="V2" t="s">
         <v>79</v>
       </c>
-      <c r="W2" t="b">
-        <v>1</v>
+      <c r="W2" t="s">
+        <v>79</v>
       </c>
       <c r="X2" t="s">
         <v>79</v>
       </c>
       <c r="Y2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z2">
-        <v>47.54</v>
+        <v>44.51</v>
       </c>
       <c r="AA2">
-        <v>-371.61</v>
+        <v>-342.64</v>
       </c>
       <c r="AB2">
-        <v>-506.36</v>
+        <v>-473.62</v>
       </c>
       <c r="AC2">
-        <v>134.75</v>
+        <v>130.98</v>
       </c>
       <c r="AD2">
-        <v>97.29000000000001</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="AE2">
-        <v>87.15000000000001</v>
+        <v>92.42</v>
       </c>
       <c r="AF2">
-        <v>449.95</v>
+        <v>436.6</v>
       </c>
       <c r="AH2">
-        <v>26122.21</v>
+        <v>25938.5</v>
       </c>
       <c r="AI2">
-        <v>24523.63</v>
+        <v>24620.21</v>
       </c>
       <c r="AJ2">
         <v>26008.9</v>
@@ -1169,7 +1121,7 @@
         <v>81</v>
       </c>
       <c r="AL2">
-        <v>38.25</v>
+        <v>33.19</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -1183,10 +1135,10 @@
         <v>78</v>
       </c>
       <c r="D3">
-        <v>8986.450000000001</v>
+        <v>8966.450000000001</v>
       </c>
       <c r="E3">
-        <v>1.05</v>
+        <v>-0.22</v>
       </c>
       <c r="F3">
         <v>10503.2</v>
@@ -1195,49 +1147,49 @@
         <v>8792.299999999999</v>
       </c>
       <c r="H3">
-        <v>-14.44</v>
+        <v>-14.63</v>
       </c>
       <c r="I3">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="J3">
-        <v>0.77</v>
+        <v>1.98</v>
       </c>
       <c r="K3">
-        <v>-4.06</v>
+        <v>-3.87</v>
       </c>
       <c r="L3">
-        <v>-8.6</v>
+        <v>-8.74</v>
       </c>
       <c r="M3">
-        <v>-2.73</v>
+        <v>-3.09</v>
       </c>
       <c r="N3">
-        <v>9.390000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="O3">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="Q3">
-        <v>8916.719999999999</v>
+        <v>8951.549999999999</v>
       </c>
       <c r="R3">
-        <v>9012.389999999999</v>
+        <v>8995.209999999999</v>
       </c>
       <c r="S3">
-        <v>9402.379999999999</v>
+        <v>9385.41</v>
       </c>
       <c r="T3">
-        <v>9744.190000000001</v>
+        <v>9740.52</v>
       </c>
       <c r="U3">
-        <v>-7.78</v>
+        <v>-7.95</v>
       </c>
       <c r="V3" t="s">
         <v>79</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="W3" t="s">
+        <v>79</v>
       </c>
       <c r="X3" t="s">
         <v>79</v>
@@ -1246,31 +1198,31 @@
         <v>0</v>
       </c>
       <c r="Z3">
-        <v>43.21</v>
+        <v>42.39</v>
       </c>
       <c r="AA3">
-        <v>-137.52</v>
+        <v>-128.33</v>
       </c>
       <c r="AB3">
-        <v>-156.41</v>
+        <v>-150.8</v>
       </c>
       <c r="AC3">
-        <v>18.89</v>
+        <v>22.46</v>
       </c>
       <c r="AD3">
-        <v>94.01000000000001</v>
+        <v>92.33</v>
       </c>
       <c r="AE3">
-        <v>86.47</v>
+        <v>92.16</v>
       </c>
       <c r="AF3">
-        <v>146.32</v>
+        <v>142.18</v>
       </c>
       <c r="AH3">
-        <v>9281.02</v>
+        <v>9224.809999999999</v>
       </c>
       <c r="AI3">
-        <v>8743.75</v>
+        <v>8765.6</v>
       </c>
       <c r="AJ3">
         <v>9225.639999999999</v>
@@ -1279,7 +1231,7 @@
         <v>81</v>
       </c>
       <c r="AL3">
-        <v>37.46</v>
+        <v>35.11</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -1293,61 +1245,61 @@
         <v>78</v>
       </c>
       <c r="D4">
-        <v>11059.15</v>
+        <v>11090.7</v>
       </c>
       <c r="E4">
-        <v>1.05</v>
+        <v>0.29</v>
       </c>
       <c r="F4">
-        <v>12633.9</v>
+        <v>12601.65</v>
       </c>
       <c r="G4">
         <v>10334.35</v>
       </c>
       <c r="H4">
-        <v>-12.46</v>
+        <v>-11.99</v>
       </c>
       <c r="I4">
-        <v>7.01</v>
+        <v>7.32</v>
       </c>
       <c r="J4">
-        <v>2.84</v>
+        <v>3.39</v>
       </c>
       <c r="K4">
-        <v>-1.87</v>
+        <v>-0.58</v>
       </c>
       <c r="L4">
-        <v>-5.52</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="M4">
-        <v>-12.5</v>
+        <v>-12.21</v>
       </c>
       <c r="N4">
-        <v>9.449999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="O4">
         <v>15</v>
       </c>
       <c r="Q4">
-        <v>10894.27</v>
+        <v>10967.06</v>
       </c>
       <c r="R4">
-        <v>10915.66</v>
+        <v>10916.56</v>
       </c>
       <c r="S4">
-        <v>11355.51</v>
+        <v>11337.23</v>
       </c>
       <c r="T4">
-        <v>11462.56</v>
+        <v>11456.64</v>
       </c>
       <c r="U4">
-        <v>-3.52</v>
+        <v>-3.19</v>
       </c>
       <c r="V4" t="s">
         <v>79</v>
       </c>
-      <c r="W4" t="b">
-        <v>0</v>
+      <c r="W4" t="s">
+        <v>79</v>
       </c>
       <c r="X4" t="s">
         <v>79</v>
@@ -1356,31 +1308,31 @@
         <v>0</v>
       </c>
       <c r="Z4">
-        <v>50.12</v>
+        <v>51.45</v>
       </c>
       <c r="AA4">
-        <v>-117.19</v>
+        <v>-95.65000000000001</v>
       </c>
       <c r="AB4">
-        <v>-156.7</v>
+        <v>-144.49</v>
       </c>
       <c r="AC4">
-        <v>39.5</v>
+        <v>48.84</v>
       </c>
       <c r="AD4">
         <v>100</v>
       </c>
       <c r="AE4">
-        <v>86.19</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="AF4">
-        <v>158.71</v>
+        <v>155.28</v>
       </c>
       <c r="AH4">
-        <v>11134.88</v>
+        <v>11138.64</v>
       </c>
       <c r="AI4">
-        <v>10696.43</v>
+        <v>10694.48</v>
       </c>
       <c r="AJ4">
         <v>11143.46</v>
@@ -1389,7 +1341,7 @@
         <v>81</v>
       </c>
       <c r="AL4">
-        <v>39.42</v>
+        <v>36.48</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1403,10 +1355,10 @@
         <v>78</v>
       </c>
       <c r="D5">
-        <v>35299</v>
+        <v>34957.9</v>
       </c>
       <c r="E5">
-        <v>1.01</v>
+        <v>-0.97</v>
       </c>
       <c r="F5">
         <v>41535.75</v>
@@ -1415,49 +1367,49 @@
         <v>33098.3</v>
       </c>
       <c r="H5">
-        <v>-15.02</v>
+        <v>-15.84</v>
       </c>
       <c r="I5">
-        <v>6.65</v>
+        <v>5.62</v>
       </c>
       <c r="J5">
-        <v>0.5600000000000001</v>
+        <v>1.27</v>
       </c>
       <c r="K5">
-        <v>-3.8</v>
+        <v>-4.25</v>
       </c>
       <c r="L5">
-        <v>-10.13</v>
+        <v>-8.76</v>
       </c>
       <c r="M5">
-        <v>-0.74</v>
+        <v>-1.93</v>
       </c>
       <c r="N5">
-        <v>8.720000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="O5">
         <v>50</v>
       </c>
       <c r="Q5">
-        <v>35009.91</v>
+        <v>35097.48</v>
       </c>
       <c r="R5">
-        <v>35849.75</v>
+        <v>35765.85</v>
       </c>
       <c r="S5">
-        <v>37044.09</v>
+        <v>36971.67</v>
       </c>
       <c r="T5">
-        <v>37727.46</v>
+        <v>37723</v>
       </c>
       <c r="U5">
-        <v>-6.44</v>
+        <v>-7.33</v>
       </c>
       <c r="V5" t="s">
         <v>79</v>
       </c>
-      <c r="W5" t="b">
-        <v>0</v>
+      <c r="W5" t="s">
+        <v>79</v>
       </c>
       <c r="X5" t="s">
         <v>79</v>
@@ -1466,31 +1418,31 @@
         <v>0</v>
       </c>
       <c r="Z5">
-        <v>39.91</v>
+        <v>36.78</v>
       </c>
       <c r="AA5">
-        <v>-598.48</v>
+        <v>-595.08</v>
       </c>
       <c r="AB5">
-        <v>-577.54</v>
+        <v>-581.05</v>
       </c>
       <c r="AC5">
-        <v>-20.94</v>
+        <v>-14.04</v>
       </c>
       <c r="AD5">
-        <v>67.55</v>
+        <v>66.56</v>
       </c>
       <c r="AE5">
-        <v>54.02</v>
+        <v>63.39</v>
       </c>
       <c r="AF5">
-        <v>573.4</v>
+        <v>571.5599999999999</v>
       </c>
       <c r="AH5">
-        <v>37200.36</v>
+        <v>37119.29</v>
       </c>
       <c r="AI5">
-        <v>34499.15</v>
+        <v>34412.41</v>
       </c>
       <c r="AJ5">
         <v>36227.11</v>
@@ -1499,7 +1451,7 @@
         <v>81</v>
       </c>
       <c r="AL5">
-        <v>47.01</v>
+        <v>46.24</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1513,10 +1465,10 @@
         <v>78</v>
       </c>
       <c r="D6">
-        <v>43882.95</v>
+        <v>43609.2</v>
       </c>
       <c r="E6">
-        <v>2.34</v>
+        <v>-0.62</v>
       </c>
       <c r="F6">
         <v>56772.45</v>
@@ -1525,49 +1477,49 @@
         <v>42680.7</v>
       </c>
       <c r="H6">
-        <v>-22.7</v>
+        <v>-23.19</v>
       </c>
       <c r="I6">
-        <v>2.82</v>
+        <v>2.18</v>
       </c>
       <c r="J6">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="K6">
-        <v>-3.05</v>
+        <v>-2.64</v>
       </c>
       <c r="L6">
-        <v>-9.98</v>
+        <v>-12.15</v>
       </c>
       <c r="M6">
-        <v>-22.46</v>
+        <v>-22.96</v>
       </c>
       <c r="N6">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="O6">
         <v>5</v>
       </c>
       <c r="Q6">
-        <v>43072.19</v>
+        <v>43257.89</v>
       </c>
       <c r="R6">
-        <v>44066.65</v>
+        <v>44021.69</v>
       </c>
       <c r="S6">
-        <v>45341.31</v>
+        <v>45258.8</v>
       </c>
       <c r="T6">
-        <v>48703.35</v>
+        <v>48653.59</v>
       </c>
       <c r="U6">
-        <v>-9.9</v>
+        <v>-10.37</v>
       </c>
       <c r="V6" t="s">
         <v>79</v>
       </c>
-      <c r="W6" t="b">
-        <v>0</v>
+      <c r="W6" t="s">
+        <v>79</v>
       </c>
       <c r="X6" t="s">
         <v>79</v>
@@ -1576,31 +1528,31 @@
         <v>0</v>
       </c>
       <c r="Z6">
-        <v>46.16</v>
+        <v>44.2</v>
       </c>
       <c r="AA6">
-        <v>-658.15</v>
+        <v>-613.04</v>
       </c>
       <c r="AB6">
-        <v>-636.84</v>
+        <v>-632.08</v>
       </c>
       <c r="AC6">
-        <v>-21.31</v>
+        <v>19.04</v>
       </c>
       <c r="AD6">
-        <v>42.14</v>
+        <v>54.92</v>
       </c>
       <c r="AE6">
-        <v>24.19</v>
+        <v>38.48</v>
       </c>
       <c r="AF6">
-        <v>791.45</v>
+        <v>768.1</v>
       </c>
       <c r="AH6">
-        <v>45700.46</v>
+        <v>45653.8</v>
       </c>
       <c r="AI6">
-        <v>42432.85</v>
+        <v>42389.58</v>
       </c>
       <c r="AJ6">
         <v>44659.77</v>
@@ -1609,7 +1561,7 @@
         <v>81</v>
       </c>
       <c r="AL6">
-        <v>35.75</v>
+        <v>31.01</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1623,10 +1575,10 @@
         <v>78</v>
       </c>
       <c r="D7">
-        <v>24704.55</v>
+        <v>24712.2</v>
       </c>
       <c r="E7">
-        <v>1.17</v>
+        <v>0.03</v>
       </c>
       <c r="F7">
         <v>28463.25</v>
@@ -1635,49 +1587,49 @@
         <v>23521.8</v>
       </c>
       <c r="H7">
-        <v>-13.21</v>
+        <v>-13.18</v>
       </c>
       <c r="I7">
-        <v>5.03</v>
+        <v>5.06</v>
       </c>
       <c r="J7">
-        <v>0.19</v>
+        <v>1.27</v>
       </c>
       <c r="K7">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="L7">
-        <v>-8.17</v>
+        <v>-5.86</v>
       </c>
       <c r="M7">
-        <v>-10.18</v>
+        <v>-10.26</v>
       </c>
       <c r="N7">
-        <v>5.62</v>
+        <v>5.39</v>
       </c>
       <c r="O7">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="Q7">
-        <v>24456.78</v>
+        <v>24518.62</v>
       </c>
       <c r="R7">
-        <v>24787.42</v>
+        <v>24790.56</v>
       </c>
       <c r="S7">
-        <v>25336.78</v>
+        <v>25308.86</v>
       </c>
       <c r="T7">
-        <v>26173.61</v>
+        <v>26157.45</v>
       </c>
       <c r="U7">
-        <v>-5.61</v>
+        <v>-5.53</v>
       </c>
       <c r="V7" t="s">
         <v>79</v>
       </c>
-      <c r="W7" t="b">
-        <v>0</v>
+      <c r="W7" t="s">
+        <v>79</v>
       </c>
       <c r="X7" t="s">
         <v>79</v>
@@ -1686,31 +1638,31 @@
         <v>0</v>
       </c>
       <c r="Z7">
-        <v>45.65</v>
+        <v>45.82</v>
       </c>
       <c r="AA7">
-        <v>-224.3</v>
+        <v>-205.38</v>
       </c>
       <c r="AB7">
-        <v>-215.1</v>
+        <v>-213.16</v>
       </c>
       <c r="AC7">
-        <v>-9.199999999999999</v>
+        <v>7.78</v>
       </c>
       <c r="AD7">
-        <v>26.41</v>
+        <v>43.4</v>
       </c>
       <c r="AE7">
-        <v>18.33</v>
+        <v>27.88</v>
       </c>
       <c r="AF7">
-        <v>363.75</v>
+        <v>354.52</v>
       </c>
       <c r="AH7">
-        <v>25404.16</v>
+        <v>25404.98</v>
       </c>
       <c r="AI7">
-        <v>24170.69</v>
+        <v>24176.14</v>
       </c>
       <c r="AJ7">
         <v>25375.42</v>
@@ -1719,7 +1671,7 @@
         <v>81</v>
       </c>
       <c r="AL7">
-        <v>34.33</v>
+        <v>30.76</v>
       </c>
     </row>
     <row r="8" spans="1:38">
@@ -1733,10 +1685,10 @@
         <v>78</v>
       </c>
       <c r="D8">
-        <v>31866.4</v>
+        <v>32606.9</v>
       </c>
       <c r="E8">
-        <v>0.99</v>
+        <v>2.32</v>
       </c>
       <c r="F8">
         <v>39488</v>
@@ -1745,49 +1697,49 @@
         <v>25769.8</v>
       </c>
       <c r="H8">
-        <v>-19.3</v>
+        <v>-17.43</v>
       </c>
       <c r="I8">
-        <v>23.66</v>
+        <v>26.53</v>
       </c>
       <c r="J8">
-        <v>-0.67</v>
+        <v>1.91</v>
       </c>
       <c r="K8">
-        <v>13.46</v>
+        <v>17.84</v>
       </c>
       <c r="L8">
-        <v>2.39</v>
+        <v>4.53</v>
       </c>
       <c r="M8">
-        <v>-9.710000000000001</v>
+        <v>-7.63</v>
       </c>
       <c r="N8">
-        <v>-1.52</v>
+        <v>-1.57</v>
       </c>
       <c r="O8">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Q8">
-        <v>31975.56</v>
+        <v>32097.84</v>
       </c>
       <c r="R8">
-        <v>30170.45</v>
+        <v>30415.55</v>
       </c>
       <c r="S8">
-        <v>29898.15</v>
+        <v>29946.02</v>
       </c>
       <c r="T8">
-        <v>30695.13</v>
+        <v>30668.28</v>
       </c>
       <c r="U8">
-        <v>3.82</v>
+        <v>6.32</v>
       </c>
       <c r="V8" t="s">
         <v>80</v>
       </c>
-      <c r="W8" t="b">
-        <v>0</v>
+      <c r="W8" t="s">
+        <v>79</v>
       </c>
       <c r="X8" t="s">
         <v>79</v>
@@ -1796,31 +1748,31 @@
         <v>2</v>
       </c>
       <c r="Z8">
-        <v>63.14</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="AA8">
-        <v>811.99</v>
+        <v>854.7</v>
       </c>
       <c r="AB8">
-        <v>603.4400000000001</v>
+        <v>653.7</v>
       </c>
       <c r="AC8">
-        <v>208.55</v>
+        <v>201.01</v>
       </c>
       <c r="AD8">
-        <v>73.65000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="AE8">
-        <v>81.36</v>
+        <v>75.67</v>
       </c>
       <c r="AF8">
-        <v>841</v>
+        <v>840.86</v>
       </c>
       <c r="AH8">
-        <v>33882.21</v>
+        <v>34088.98</v>
       </c>
       <c r="AI8">
-        <v>26458.69</v>
+        <v>26742.13</v>
       </c>
       <c r="AJ8">
         <v>29979.37</v>
@@ -1829,7 +1781,7 @@
         <v>82</v>
       </c>
       <c r="AL8">
-        <v>43.12</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1843,10 +1795,10 @@
         <v>78</v>
       </c>
       <c r="D9">
-        <v>14975.8</v>
+        <v>14901.5</v>
       </c>
       <c r="E9">
-        <v>0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="F9">
         <v>16662.45</v>
@@ -1855,70 +1807,67 @@
         <v>14516.75</v>
       </c>
       <c r="H9">
-        <v>-10.12</v>
+        <v>-10.57</v>
       </c>
       <c r="I9">
-        <v>3.16</v>
+        <v>2.65</v>
       </c>
       <c r="J9">
-        <v>1.54</v>
+        <v>2.65</v>
       </c>
       <c r="K9">
-        <v>-4.25</v>
+        <v>-3.92</v>
       </c>
       <c r="L9">
-        <v>-6.72</v>
+        <v>-7.65</v>
       </c>
       <c r="N9">
-        <v>-11.12</v>
+        <v>-12.19</v>
       </c>
       <c r="O9">
         <v>30</v>
       </c>
       <c r="Q9">
-        <v>14793.65</v>
+        <v>14870.6</v>
       </c>
       <c r="R9">
-        <v>15027.06</v>
+        <v>14999.42</v>
       </c>
       <c r="S9">
-        <v>15709.96</v>
+        <v>15676.92</v>
       </c>
       <c r="V9" t="s">
         <v>79</v>
       </c>
-      <c r="X9" t="s">
-        <v>79</v>
-      </c>
       <c r="Y9">
         <v>0</v>
       </c>
       <c r="Z9">
-        <v>42.97</v>
+        <v>41.08</v>
       </c>
       <c r="AA9">
-        <v>-244.34</v>
+        <v>-229.43</v>
       </c>
       <c r="AB9">
-        <v>-271.93</v>
+        <v>-263.43</v>
       </c>
       <c r="AC9">
-        <v>27.59</v>
+        <v>34</v>
       </c>
       <c r="AD9">
-        <v>100</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="AE9">
-        <v>78.01000000000001</v>
+        <v>93.06999999999999</v>
       </c>
       <c r="AF9">
-        <v>222.23</v>
+        <v>215.91</v>
       </c>
       <c r="AH9">
-        <v>15503.67</v>
+        <v>15433.94</v>
       </c>
       <c r="AI9">
-        <v>14550.46</v>
+        <v>14564.9</v>
       </c>
       <c r="AJ9">
         <v>15216.01</v>
@@ -1927,7 +1876,7 @@
         <v>81</v>
       </c>
       <c r="AL9">
-        <v>50.66</v>
+        <v>47.34</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1941,10 +1890,10 @@
         <v>78</v>
       </c>
       <c r="D10">
-        <v>8792.5</v>
+        <v>8799</v>
       </c>
       <c r="E10">
-        <v>1.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F10">
         <v>9765.75</v>
@@ -1953,49 +1902,49 @@
         <v>8499.65</v>
       </c>
       <c r="H10">
-        <v>-9.970000000000001</v>
+        <v>-9.9</v>
       </c>
       <c r="I10">
-        <v>3.45</v>
+        <v>3.52</v>
       </c>
       <c r="J10">
-        <v>2.33</v>
+        <v>2.86</v>
       </c>
       <c r="K10">
-        <v>0.11</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="L10">
-        <v>-6.24</v>
+        <v>-5.84</v>
       </c>
       <c r="M10">
-        <v>-7.07</v>
+        <v>-7.04</v>
       </c>
       <c r="N10">
-        <v>11.75</v>
+        <v>11.38</v>
       </c>
       <c r="O10">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="Q10">
-        <v>8684.92</v>
+        <v>8733.870000000001</v>
       </c>
       <c r="R10">
-        <v>8651.16</v>
+        <v>8654.42</v>
       </c>
       <c r="S10">
-        <v>8940.799999999999</v>
+        <v>8929.25</v>
       </c>
       <c r="T10">
-        <v>9206.799999999999</v>
+        <v>9202.74</v>
       </c>
       <c r="U10">
-        <v>-4.5</v>
+        <v>-4.39</v>
       </c>
       <c r="V10" t="s">
         <v>79</v>
       </c>
-      <c r="W10" t="b">
-        <v>0</v>
+      <c r="W10" t="s">
+        <v>79</v>
       </c>
       <c r="X10" t="s">
         <v>79</v>
@@ -2004,31 +1953,31 @@
         <v>0</v>
       </c>
       <c r="Z10">
-        <v>52.23</v>
+        <v>52.59</v>
       </c>
       <c r="AA10">
-        <v>-64.20999999999999</v>
+        <v>-50.2</v>
       </c>
       <c r="AB10">
-        <v>-99.73</v>
+        <v>-89.83</v>
       </c>
       <c r="AC10">
-        <v>35.53</v>
+        <v>39.63</v>
       </c>
       <c r="AD10">
         <v>96.73999999999999</v>
       </c>
       <c r="AE10">
-        <v>92.04000000000001</v>
+        <v>96.42</v>
       </c>
       <c r="AF10">
-        <v>129.67</v>
+        <v>126.18</v>
       </c>
       <c r="AH10">
-        <v>8826.77</v>
+        <v>8838.68</v>
       </c>
       <c r="AI10">
-        <v>8475.559999999999</v>
+        <v>8470.16</v>
       </c>
       <c r="AJ10">
         <v>8855.59</v>
@@ -2037,7 +1986,7 @@
         <v>81</v>
       </c>
       <c r="AL10">
-        <v>23.94</v>
+        <v>22.51</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -2051,10 +2000,10 @@
         <v>78</v>
       </c>
       <c r="D11">
-        <v>1655.35</v>
+        <v>1631.25</v>
       </c>
       <c r="E11">
-        <v>1.1</v>
+        <v>-1.46</v>
       </c>
       <c r="F11">
         <v>1655.35</v>
@@ -2063,49 +2012,49 @@
         <v>1253.35</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>-1.46</v>
       </c>
       <c r="I11">
-        <v>32.07</v>
+        <v>30.15</v>
       </c>
       <c r="J11">
-        <v>4.47</v>
+        <v>4.34</v>
       </c>
       <c r="K11">
-        <v>7.54</v>
+        <v>5.86</v>
       </c>
       <c r="L11">
-        <v>8.800000000000001</v>
+        <v>2.89</v>
       </c>
       <c r="M11">
-        <v>7.99</v>
+        <v>5.82</v>
       </c>
       <c r="N11">
-        <v>-5.92</v>
+        <v>-6.68</v>
       </c>
       <c r="O11">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="Q11">
-        <v>1605.86</v>
+        <v>1619.43</v>
       </c>
       <c r="R11">
-        <v>1598.38</v>
+        <v>1600.79</v>
       </c>
       <c r="S11">
-        <v>1577.03</v>
+        <v>1577.61</v>
       </c>
       <c r="T11">
-        <v>1472.55</v>
+        <v>1473.42</v>
       </c>
       <c r="U11">
-        <v>12.41</v>
+        <v>10.71</v>
       </c>
       <c r="V11" t="s">
         <v>80</v>
       </c>
-      <c r="W11" t="b">
-        <v>1</v>
+      <c r="W11" t="s">
+        <v>80</v>
       </c>
       <c r="X11" t="s">
         <v>80</v>
@@ -2114,31 +2063,31 @@
         <v>3</v>
       </c>
       <c r="Z11">
-        <v>60.66</v>
+        <v>56</v>
       </c>
       <c r="AA11">
-        <v>16</v>
+        <v>16.47</v>
       </c>
       <c r="AB11">
-        <v>13.41</v>
+        <v>14.02</v>
       </c>
       <c r="AC11">
-        <v>2.59</v>
+        <v>2.45</v>
       </c>
       <c r="AD11">
-        <v>68.8</v>
+        <v>70.44</v>
       </c>
       <c r="AE11">
-        <v>42.88</v>
+        <v>60.11</v>
       </c>
       <c r="AF11">
-        <v>39.92</v>
+        <v>39.46</v>
       </c>
       <c r="AH11">
-        <v>1676.61</v>
+        <v>1680</v>
       </c>
       <c r="AI11">
-        <v>1520.15</v>
+        <v>1521.57</v>
       </c>
       <c r="AJ11">
         <v>1544.25</v>
@@ -2147,7 +2096,7 @@
         <v>82</v>
       </c>
       <c r="AL11">
-        <v>22.24</v>
+        <v>21.1</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -2161,10 +2110,10 @@
         <v>78</v>
       </c>
       <c r="D12">
-        <v>11848.45</v>
+        <v>11784.9</v>
       </c>
       <c r="E12">
-        <v>0.67</v>
+        <v>-0.54</v>
       </c>
       <c r="F12">
         <v>13718.3</v>
@@ -2173,49 +2122,49 @@
         <v>10017.9</v>
       </c>
       <c r="H12">
-        <v>-13.63</v>
+        <v>-14.09</v>
       </c>
       <c r="I12">
-        <v>18.27</v>
+        <v>17.64</v>
       </c>
       <c r="J12">
-        <v>0.42</v>
+        <v>2.67</v>
       </c>
       <c r="K12">
-        <v>-7.83</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L12">
-        <v>-4.73</v>
+        <v>-7.22</v>
       </c>
       <c r="M12">
-        <v>16.25</v>
+        <v>15.17</v>
       </c>
       <c r="N12">
-        <v>16.33</v>
+        <v>15.52</v>
       </c>
       <c r="O12">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Q12">
-        <v>11726.85</v>
+        <v>11788.19</v>
       </c>
       <c r="R12">
-        <v>12052.64</v>
+        <v>12003.86</v>
       </c>
       <c r="S12">
-        <v>12700.59</v>
+        <v>12675.78</v>
       </c>
       <c r="T12">
-        <v>12488.1</v>
+        <v>12489.4</v>
       </c>
       <c r="U12">
-        <v>-5.12</v>
+        <v>-5.64</v>
       </c>
       <c r="V12" t="s">
         <v>79</v>
       </c>
-      <c r="W12" t="b">
-        <v>1</v>
+      <c r="W12" t="s">
+        <v>80</v>
       </c>
       <c r="X12" t="s">
         <v>79</v>
@@ -2224,31 +2173,31 @@
         <v>1</v>
       </c>
       <c r="Z12">
-        <v>40.23</v>
+        <v>38.86</v>
       </c>
       <c r="AA12">
-        <v>-278.31</v>
+        <v>-267.33</v>
       </c>
       <c r="AB12">
-        <v>-282.77</v>
+        <v>-279.68</v>
       </c>
       <c r="AC12">
-        <v>4.46</v>
+        <v>12.35</v>
       </c>
       <c r="AD12">
-        <v>93.15000000000001</v>
+        <v>91.84</v>
       </c>
       <c r="AE12">
-        <v>75.09</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="AF12">
-        <v>244.7</v>
+        <v>236.4</v>
       </c>
       <c r="AH12">
-        <v>12702.31</v>
+        <v>12571.01</v>
       </c>
       <c r="AI12">
-        <v>11402.98</v>
+        <v>11436.72</v>
       </c>
       <c r="AJ12">
         <v>12304.47</v>
@@ -2257,7 +2206,7 @@
         <v>81</v>
       </c>
       <c r="AL12">
-        <v>52.62</v>
+        <v>51.64</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2271,10 +2220,10 @@
         <v>78</v>
       </c>
       <c r="D13">
-        <v>9097.1</v>
+        <v>9075.35</v>
       </c>
       <c r="E13">
-        <v>1.15</v>
+        <v>-0.24</v>
       </c>
       <c r="F13">
         <v>10766.3</v>
@@ -2283,49 +2232,49 @@
         <v>8885.75</v>
       </c>
       <c r="H13">
-        <v>-15.5</v>
+        <v>-15.71</v>
       </c>
       <c r="I13">
-        <v>2.38</v>
+        <v>2.13</v>
       </c>
       <c r="J13">
-        <v>0.6899999999999999</v>
+        <v>2.13</v>
       </c>
       <c r="K13">
-        <v>-3.12</v>
+        <v>-2.87</v>
       </c>
       <c r="L13">
-        <v>-8.470000000000001</v>
+        <v>-8.27</v>
       </c>
       <c r="M13">
-        <v>-8.32</v>
+        <v>-8.67</v>
       </c>
       <c r="N13">
-        <v>17.83</v>
+        <v>17.36</v>
       </c>
       <c r="O13">
         <v>20</v>
       </c>
       <c r="Q13">
-        <v>9002.01</v>
+        <v>9039.93</v>
       </c>
       <c r="R13">
-        <v>9146.469999999999</v>
+        <v>9132.219999999999</v>
       </c>
       <c r="S13">
-        <v>9451.57</v>
+        <v>9436.309999999999</v>
       </c>
       <c r="T13">
-        <v>9963.23</v>
+        <v>9958.129999999999</v>
       </c>
       <c r="U13">
-        <v>-8.69</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="V13" t="s">
         <v>79</v>
       </c>
-      <c r="W13" t="b">
-        <v>0</v>
+      <c r="W13" t="s">
+        <v>79</v>
       </c>
       <c r="X13" t="s">
         <v>79</v>
@@ -2334,31 +2283,31 @@
         <v>0</v>
       </c>
       <c r="Z13">
-        <v>43.08</v>
+        <v>42.12</v>
       </c>
       <c r="AA13">
-        <v>-127.42</v>
+        <v>-119.41</v>
       </c>
       <c r="AB13">
-        <v>-132.82</v>
+        <v>-130.14</v>
       </c>
       <c r="AC13">
-        <v>5.39</v>
+        <v>10.72</v>
       </c>
       <c r="AD13">
-        <v>80.2</v>
+        <v>85.59</v>
       </c>
       <c r="AE13">
-        <v>65.04000000000001</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="AF13">
-        <v>139.38</v>
+        <v>136.47</v>
       </c>
       <c r="AH13">
-        <v>9410.43</v>
+        <v>9377.67</v>
       </c>
       <c r="AI13">
-        <v>8882.52</v>
+        <v>8886.77</v>
       </c>
       <c r="AJ13">
         <v>9317.65</v>
@@ -2367,7 +2316,7 @@
         <v>81</v>
       </c>
       <c r="AL13">
-        <v>51.27</v>
+        <v>48.46</v>
       </c>
     </row>
     <row r="14" spans="1:38">
@@ -2381,10 +2330,10 @@
         <v>78</v>
       </c>
       <c r="D14">
-        <v>8312.5</v>
+        <v>8234.85</v>
       </c>
       <c r="E14">
-        <v>2.2</v>
+        <v>-0.93</v>
       </c>
       <c r="F14">
         <v>9879.85</v>
@@ -2393,49 +2342,49 @@
         <v>7817.4</v>
       </c>
       <c r="H14">
-        <v>-15.86</v>
+        <v>-16.65</v>
       </c>
       <c r="I14">
-        <v>6.33</v>
+        <v>5.34</v>
       </c>
       <c r="J14">
-        <v>0.67</v>
+        <v>2.03</v>
       </c>
       <c r="K14">
-        <v>3.57</v>
+        <v>3.29</v>
       </c>
       <c r="L14">
-        <v>-0.83</v>
+        <v>-1.11</v>
       </c>
       <c r="M14">
-        <v>5.79</v>
+        <v>4.86</v>
       </c>
       <c r="N14">
-        <v>24.09</v>
+        <v>23.59</v>
       </c>
       <c r="O14">
         <v>85</v>
       </c>
       <c r="Q14">
-        <v>8147.46</v>
+        <v>8180.29</v>
       </c>
       <c r="R14">
-        <v>8110.47</v>
+        <v>8121.41</v>
       </c>
       <c r="S14">
-        <v>8297.290000000001</v>
+        <v>8289.620000000001</v>
       </c>
       <c r="T14">
-        <v>8562.17</v>
+        <v>8559.389999999999</v>
       </c>
       <c r="U14">
-        <v>-2.92</v>
+        <v>-3.79</v>
       </c>
       <c r="V14" t="s">
         <v>79</v>
       </c>
-      <c r="W14" t="b">
-        <v>0</v>
+      <c r="W14" t="s">
+        <v>79</v>
       </c>
       <c r="X14" t="s">
         <v>79</v>
@@ -2444,31 +2393,31 @@
         <v>0</v>
       </c>
       <c r="Z14">
-        <v>56.21</v>
+        <v>52.26</v>
       </c>
       <c r="AA14">
-        <v>-17.16</v>
+        <v>-10.31</v>
       </c>
       <c r="AB14">
-        <v>-42.73</v>
+        <v>-36.25</v>
       </c>
       <c r="AC14">
-        <v>25.57</v>
+        <v>25.93</v>
       </c>
       <c r="AD14">
-        <v>72.92</v>
+        <v>78.17</v>
       </c>
       <c r="AE14">
-        <v>61.03</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="AF14">
-        <v>153.82</v>
+        <v>150.99</v>
       </c>
       <c r="AH14">
-        <v>8319.110000000001</v>
+        <v>8332.139999999999</v>
       </c>
       <c r="AI14">
-        <v>7901.82</v>
+        <v>7910.67</v>
       </c>
       <c r="AJ14">
         <v>8354.280000000001</v>
@@ -2477,7 +2426,7 @@
         <v>81</v>
       </c>
       <c r="AL14">
-        <v>17.68</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="15" spans="1:38">
@@ -2491,10 +2440,10 @@
         <v>78</v>
       </c>
       <c r="D15">
-        <v>26710.8</v>
+        <v>27124.85</v>
       </c>
       <c r="E15">
-        <v>0.64</v>
+        <v>1.55</v>
       </c>
       <c r="F15">
         <v>27186.45</v>
@@ -2503,49 +2452,49 @@
         <v>21549.55</v>
       </c>
       <c r="H15">
-        <v>-1.75</v>
+        <v>-0.23</v>
       </c>
       <c r="I15">
-        <v>23.95</v>
+        <v>25.87</v>
       </c>
       <c r="J15">
-        <v>4.35</v>
+        <v>7.09</v>
       </c>
       <c r="K15">
-        <v>-0.19</v>
+        <v>0.71</v>
       </c>
       <c r="L15">
-        <v>1.28</v>
+        <v>2.96</v>
       </c>
       <c r="M15">
-        <v>19.03</v>
+        <v>20.47</v>
       </c>
       <c r="N15">
-        <v>13.99</v>
+        <v>14.08</v>
       </c>
       <c r="O15">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="Q15">
-        <v>26124.62</v>
+        <v>26483.7</v>
       </c>
       <c r="R15">
-        <v>26026.45</v>
+        <v>26060.79</v>
       </c>
       <c r="S15">
-        <v>26420.35</v>
+        <v>26435.61</v>
       </c>
       <c r="T15">
-        <v>24453.72</v>
+        <v>24473.71</v>
       </c>
       <c r="U15">
-        <v>9.23</v>
+        <v>10.83</v>
       </c>
       <c r="V15" t="s">
         <v>79</v>
       </c>
-      <c r="W15" t="b">
-        <v>1</v>
+      <c r="W15" t="s">
+        <v>80</v>
       </c>
       <c r="X15" t="s">
         <v>79</v>
@@ -2554,40 +2503,40 @@
         <v>2</v>
       </c>
       <c r="Z15">
-        <v>59.68</v>
+        <v>64.88</v>
       </c>
       <c r="AA15">
-        <v>-73.61</v>
+        <v>14.4</v>
       </c>
       <c r="AB15">
-        <v>-176.69</v>
+        <v>-138.47</v>
       </c>
       <c r="AC15">
-        <v>103.08</v>
+        <v>152.87</v>
       </c>
       <c r="AD15">
         <v>100</v>
       </c>
       <c r="AE15">
-        <v>81.94</v>
+        <v>96.52</v>
       </c>
       <c r="AF15">
-        <v>419.22</v>
+        <v>437.32</v>
       </c>
       <c r="AH15">
-        <v>26800.44</v>
+        <v>26962.14</v>
       </c>
       <c r="AI15">
-        <v>25252.46</v>
+        <v>25159.44</v>
       </c>
       <c r="AJ15">
-        <v>25337.07</v>
+        <v>25705.58</v>
       </c>
       <c r="AK15" t="s">
         <v>82</v>
       </c>
       <c r="AL15">
-        <v>39.11</v>
+        <v>41.18</v>
       </c>
     </row>
     <row r="16" spans="1:38">
@@ -2601,10 +2550,10 @@
         <v>78</v>
       </c>
       <c r="D16">
-        <v>819.8</v>
+        <v>813.9</v>
       </c>
       <c r="E16">
-        <v>2.75</v>
+        <v>-0.72</v>
       </c>
       <c r="F16">
         <v>968.65</v>
@@ -2613,49 +2562,49 @@
         <v>651.15</v>
       </c>
       <c r="H16">
-        <v>-15.37</v>
+        <v>-15.98</v>
       </c>
       <c r="I16">
-        <v>25.9</v>
+        <v>24.99</v>
       </c>
       <c r="J16">
-        <v>2.03</v>
+        <v>3.77</v>
       </c>
       <c r="K16">
-        <v>-3.65</v>
+        <v>-2.39</v>
       </c>
       <c r="L16">
-        <v>-10.77</v>
+        <v>-9.52</v>
       </c>
       <c r="M16">
-        <v>-12.62</v>
+        <v>-13.17</v>
       </c>
       <c r="N16">
-        <v>10.45</v>
+        <v>9.44</v>
       </c>
       <c r="O16">
         <v>10</v>
       </c>
       <c r="Q16">
-        <v>799.35</v>
+        <v>805.26</v>
       </c>
       <c r="R16">
-        <v>816.11</v>
+        <v>814.4400000000001</v>
       </c>
       <c r="S16">
-        <v>853.99</v>
+        <v>852.35</v>
       </c>
       <c r="T16">
-        <v>820.92</v>
+        <v>820.42</v>
       </c>
       <c r="U16">
-        <v>-0.14</v>
+        <v>-0.79</v>
       </c>
       <c r="V16" t="s">
         <v>79</v>
       </c>
-      <c r="W16" t="b">
-        <v>1</v>
+      <c r="W16" t="s">
+        <v>80</v>
       </c>
       <c r="X16" t="s">
         <v>79</v>
@@ -2664,31 +2613,31 @@
         <v>1</v>
       </c>
       <c r="Z16">
-        <v>48.33</v>
+        <v>46.42</v>
       </c>
       <c r="AA16">
-        <v>-13.94</v>
+        <v>-12.57</v>
       </c>
       <c r="AB16">
-        <v>-15.34</v>
+        <v>-14.78</v>
       </c>
       <c r="AC16">
-        <v>1.4</v>
+        <v>2.21</v>
       </c>
       <c r="AD16">
-        <v>80.51000000000001</v>
+        <v>83.66</v>
       </c>
       <c r="AE16">
-        <v>58.71</v>
+        <v>73.62</v>
       </c>
       <c r="AF16">
-        <v>18.69</v>
+        <v>18.28</v>
       </c>
       <c r="AH16">
-        <v>851.3099999999999</v>
+        <v>846.42</v>
       </c>
       <c r="AI16">
-        <v>780.91</v>
+        <v>782.46</v>
       </c>
       <c r="AJ16">
         <v>838.5700000000001</v>
@@ -2697,7 +2646,7 @@
         <v>81</v>
       </c>
       <c r="AL16">
-        <v>31.84</v>
+        <v>28.44</v>
       </c>
     </row>
     <row r="17" spans="1:38">
@@ -2711,10 +2660,10 @@
         <v>78</v>
       </c>
       <c r="D17">
-        <v>30506.2</v>
+        <v>30861.75</v>
       </c>
       <c r="E17">
-        <v>1.61</v>
+        <v>1.17</v>
       </c>
       <c r="F17">
         <v>34101.05</v>
@@ -2723,49 +2672,49 @@
         <v>28363.6</v>
       </c>
       <c r="H17">
-        <v>-10.54</v>
+        <v>-9.5</v>
       </c>
       <c r="I17">
-        <v>7.55</v>
+        <v>8.81</v>
       </c>
       <c r="J17">
-        <v>1.69</v>
+        <v>3.1</v>
       </c>
       <c r="K17">
-        <v>4.5</v>
+        <v>5.84</v>
       </c>
       <c r="L17">
-        <v>-2.97</v>
+        <v>-1.04</v>
       </c>
       <c r="M17">
-        <v>-9.029999999999999</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="N17">
-        <v>4.28</v>
+        <v>4.18</v>
       </c>
       <c r="O17">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="Q17">
-        <v>30172.46</v>
+        <v>30357.86</v>
       </c>
       <c r="R17">
-        <v>29619.9</v>
+        <v>29712.29</v>
       </c>
       <c r="S17">
-        <v>30013.39</v>
+        <v>30015.43</v>
       </c>
       <c r="T17">
-        <v>30898.15</v>
+        <v>30883.07</v>
       </c>
       <c r="U17">
-        <v>-1.27</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="V17" t="s">
         <v>79</v>
       </c>
-      <c r="W17" t="b">
-        <v>0</v>
+      <c r="W17" t="s">
+        <v>79</v>
       </c>
       <c r="X17" t="s">
         <v>79</v>
@@ -2774,40 +2723,40 @@
         <v>0</v>
       </c>
       <c r="Z17">
-        <v>60.1</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="AA17">
-        <v>121.51</v>
+        <v>180.61</v>
       </c>
       <c r="AB17">
-        <v>-0.76</v>
+        <v>35.52</v>
       </c>
       <c r="AC17">
-        <v>122.27</v>
+        <v>145.1</v>
       </c>
       <c r="AD17">
-        <v>84.2</v>
+        <v>88.86</v>
       </c>
       <c r="AE17">
-        <v>82.23</v>
+        <v>84.83</v>
       </c>
       <c r="AF17">
-        <v>440.77</v>
+        <v>439.8</v>
       </c>
       <c r="AH17">
-        <v>30814.27</v>
+        <v>30992.11</v>
       </c>
       <c r="AI17">
-        <v>28425.53</v>
+        <v>28432.48</v>
       </c>
       <c r="AJ17">
-        <v>29148.67</v>
+        <v>29400.86</v>
       </c>
       <c r="AK17" t="s">
         <v>82</v>
       </c>
       <c r="AL17">
-        <v>22.9</v>
+        <v>24.07</v>
       </c>
     </row>
     <row r="18" spans="1:38">
@@ -2821,10 +2770,10 @@
         <v>78</v>
       </c>
       <c r="D18">
-        <v>16193.9</v>
+        <v>16449.55</v>
       </c>
       <c r="E18">
-        <v>0.58</v>
+        <v>1.58</v>
       </c>
       <c r="F18">
         <v>16941.5</v>
@@ -2833,79 +2782,76 @@
         <v>15387</v>
       </c>
       <c r="H18">
-        <v>-4.41</v>
+        <v>-2.9</v>
       </c>
       <c r="I18">
-        <v>5.24</v>
+        <v>6.91</v>
       </c>
       <c r="J18">
-        <v>4.37</v>
+        <v>6.91</v>
       </c>
       <c r="K18">
-        <v>-2.08</v>
+        <v>-0.68</v>
       </c>
       <c r="L18">
-        <v>-3.01</v>
+        <v>-1.5</v>
       </c>
       <c r="N18">
-        <v>11.22</v>
+        <v>15.77</v>
       </c>
       <c r="O18">
         <v>75</v>
       </c>
       <c r="Q18">
-        <v>15851.46</v>
+        <v>16063.97</v>
       </c>
       <c r="R18">
-        <v>15824.26</v>
+        <v>15839.85</v>
       </c>
       <c r="S18">
-        <v>16279.5</v>
+        <v>16279.22</v>
       </c>
       <c r="V18" t="s">
         <v>79</v>
       </c>
-      <c r="X18" t="s">
-        <v>79</v>
-      </c>
       <c r="Y18">
         <v>0</v>
       </c>
       <c r="Z18">
-        <v>56.24</v>
+        <v>62.02</v>
       </c>
       <c r="AA18">
-        <v>-123.22</v>
+        <v>-66.37</v>
       </c>
       <c r="AB18">
-        <v>-194.51</v>
+        <v>-168.89</v>
       </c>
       <c r="AC18">
-        <v>71.3</v>
+        <v>102.51</v>
       </c>
       <c r="AD18">
         <v>100</v>
       </c>
       <c r="AE18">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="AF18">
-        <v>251.91</v>
+        <v>261.93</v>
       </c>
       <c r="AH18">
-        <v>16305.77</v>
+        <v>16380.64</v>
       </c>
       <c r="AI18">
-        <v>15342.75</v>
+        <v>15299.06</v>
       </c>
       <c r="AJ18">
-        <v>15386.85</v>
+        <v>15585</v>
       </c>
       <c r="AK18" t="s">
         <v>82</v>
       </c>
       <c r="AL18">
-        <v>48.09</v>
+        <v>48.01</v>
       </c>
     </row>
     <row r="19" spans="1:38">
@@ -2919,10 +2865,10 @@
         <v>78</v>
       </c>
       <c r="D19">
-        <v>8882.9</v>
+        <v>8704.450000000001</v>
       </c>
       <c r="E19">
-        <v>1.14</v>
+        <v>-2.01</v>
       </c>
       <c r="F19">
         <v>9998.700000000001</v>
@@ -2931,70 +2877,67 @@
         <v>8561.200000000001</v>
       </c>
       <c r="H19">
-        <v>-11.16</v>
+        <v>-12.94</v>
       </c>
       <c r="I19">
-        <v>3.76</v>
+        <v>1.67</v>
       </c>
       <c r="J19">
-        <v>1.06</v>
+        <v>1.67</v>
       </c>
       <c r="K19">
-        <v>-3.77</v>
+        <v>-4.76</v>
       </c>
       <c r="L19">
-        <v>-3.67</v>
+        <v>-5.27</v>
       </c>
       <c r="N19">
-        <v>-3.25</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="O19">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="Q19">
-        <v>8741.73</v>
+        <v>8770.379999999999</v>
       </c>
       <c r="R19">
-        <v>9036.190000000001</v>
+        <v>9007.57</v>
       </c>
       <c r="S19">
-        <v>9376.57</v>
+        <v>9351.290000000001</v>
       </c>
       <c r="V19" t="s">
         <v>79</v>
       </c>
-      <c r="X19" t="s">
-        <v>79</v>
-      </c>
       <c r="Y19">
         <v>0</v>
       </c>
       <c r="Z19">
-        <v>43.02</v>
+        <v>38.29</v>
       </c>
       <c r="AA19">
-        <v>-165.03</v>
+        <v>-169.22</v>
       </c>
       <c r="AB19">
-        <v>-150.45</v>
+        <v>-154.2</v>
       </c>
       <c r="AC19">
-        <v>-14.58</v>
+        <v>-15.01</v>
       </c>
       <c r="AD19">
-        <v>58.55</v>
+        <v>55.56</v>
       </c>
       <c r="AE19">
-        <v>42.39</v>
+        <v>52.26</v>
       </c>
       <c r="AF19">
-        <v>188.11</v>
+        <v>190.96</v>
       </c>
       <c r="AH19">
-        <v>9492.549999999999</v>
+        <v>9472.120000000001</v>
       </c>
       <c r="AI19">
-        <v>8579.82</v>
+        <v>8543.02</v>
       </c>
       <c r="AJ19">
         <v>9128.139999999999</v>
@@ -3003,7 +2946,7 @@
         <v>81</v>
       </c>
       <c r="AL19">
-        <v>34.81</v>
+        <v>33.54</v>
       </c>
     </row>
     <row r="20" spans="1:38">
@@ -3017,10 +2960,10 @@
         <v>78</v>
       </c>
       <c r="D20">
-        <v>10352.4</v>
+        <v>10303.25</v>
       </c>
       <c r="E20">
-        <v>0.54</v>
+        <v>-0.47</v>
       </c>
       <c r="F20">
         <v>11369.05</v>
@@ -3029,70 +2972,67 @@
         <v>10296.6</v>
       </c>
       <c r="H20">
-        <v>-8.94</v>
+        <v>-9.369999999999999</v>
       </c>
       <c r="I20">
-        <v>0.54</v>
+        <v>0.06</v>
       </c>
       <c r="J20">
-        <v>-0.89</v>
+        <v>-0.74</v>
       </c>
       <c r="K20">
-        <v>-2.89</v>
+        <v>-2.5</v>
       </c>
       <c r="L20">
-        <v>-6.54</v>
+        <v>-7.41</v>
       </c>
       <c r="N20">
-        <v>-14.99</v>
+        <v>-15.94</v>
       </c>
       <c r="O20">
         <v>40</v>
       </c>
       <c r="Q20">
-        <v>10417.3</v>
+        <v>10401.84</v>
       </c>
       <c r="R20">
-        <v>10473.98</v>
+        <v>10458.42</v>
       </c>
       <c r="S20">
-        <v>10805.52</v>
+        <v>10786.96</v>
       </c>
       <c r="V20" t="s">
         <v>79</v>
       </c>
-      <c r="X20" t="s">
-        <v>79</v>
-      </c>
       <c r="Y20">
         <v>0</v>
       </c>
       <c r="Z20">
-        <v>39.66</v>
+        <v>37.93</v>
       </c>
       <c r="AA20">
-        <v>-110.22</v>
+        <v>-114.27</v>
       </c>
       <c r="AB20">
-        <v>-118.15</v>
+        <v>-117.37</v>
       </c>
       <c r="AC20">
-        <v>7.93</v>
+        <v>3.11</v>
       </c>
       <c r="AD20">
-        <v>70.09</v>
+        <v>55.17</v>
       </c>
       <c r="AE20">
-        <v>77</v>
+        <v>68.5</v>
       </c>
       <c r="AF20">
-        <v>166.29</v>
+        <v>162.97</v>
       </c>
       <c r="AH20">
-        <v>10706.16</v>
+        <v>10692.64</v>
       </c>
       <c r="AI20">
-        <v>10241.81</v>
+        <v>10224.2</v>
       </c>
       <c r="AJ20">
         <v>10732.68</v>
@@ -3101,7 +3041,7 @@
         <v>81</v>
       </c>
       <c r="AL20">
-        <v>29.53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:38">
@@ -3115,10 +3055,10 @@
         <v>78</v>
       </c>
       <c r="D21">
-        <v>27052.6</v>
+        <v>27053.5</v>
       </c>
       <c r="E21">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>29187.95</v>
@@ -3127,49 +3067,49 @@
         <v>24144.85</v>
       </c>
       <c r="H21">
-        <v>-7.32</v>
+        <v>-7.31</v>
       </c>
       <c r="I21">
-        <v>12.04</v>
+        <v>12.05</v>
       </c>
       <c r="J21">
-        <v>0.6899999999999999</v>
+        <v>1.49</v>
       </c>
       <c r="K21">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="L21">
-        <v>-5.11</v>
+        <v>-1.68</v>
       </c>
       <c r="M21">
-        <v>-4.84</v>
+        <v>-4.83</v>
       </c>
       <c r="N21">
-        <v>6.03</v>
+        <v>5.64</v>
       </c>
       <c r="O21">
         <v>70</v>
       </c>
       <c r="Q21">
-        <v>26776.95</v>
+        <v>26856.39</v>
       </c>
       <c r="R21">
-        <v>27012.52</v>
+        <v>27030.42</v>
       </c>
       <c r="S21">
-        <v>27226.11</v>
+        <v>27222.22</v>
       </c>
       <c r="T21">
-        <v>27363.8</v>
+        <v>27354.67</v>
       </c>
       <c r="U21">
-        <v>-1.14</v>
+        <v>-1.1</v>
       </c>
       <c r="V21" t="s">
         <v>79</v>
       </c>
-      <c r="W21" t="b">
-        <v>0</v>
+      <c r="W21" t="s">
+        <v>79</v>
       </c>
       <c r="X21" t="s">
         <v>79</v>
@@ -3178,31 +3118,31 @@
         <v>0</v>
       </c>
       <c r="Z21">
-        <v>50.02</v>
+        <v>50.04</v>
       </c>
       <c r="AA21">
-        <v>-98.26000000000001</v>
+        <v>-82.45999999999999</v>
       </c>
       <c r="AB21">
-        <v>-80.33</v>
+        <v>-80.76000000000001</v>
       </c>
       <c r="AC21">
-        <v>-17.92</v>
+        <v>-1.7</v>
       </c>
       <c r="AD21">
-        <v>20.98</v>
+        <v>36.18</v>
       </c>
       <c r="AE21">
-        <v>13.81</v>
+        <v>22.82</v>
       </c>
       <c r="AF21">
-        <v>391.86</v>
+        <v>381.74</v>
       </c>
       <c r="AH21">
-        <v>27641.54</v>
+        <v>27641.58</v>
       </c>
       <c r="AI21">
-        <v>26383.5</v>
+        <v>26419.25</v>
       </c>
       <c r="AJ21">
         <v>26545.98</v>
@@ -3211,7 +3151,7 @@
         <v>82</v>
       </c>
       <c r="AL21">
-        <v>27.9</v>
+        <v>24.22</v>
       </c>
     </row>
   </sheetData>
@@ -3315,27 +3255,27 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:V21">
-    <cfRule type="containsText" dxfId="1" priority="14" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",V2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="16" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="15" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",V2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="17" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W2:W21">
-    <cfRule type="containsText" dxfId="1" priority="16" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",W2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="18" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",W2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="19" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:X21">
-    <cfRule type="containsText" dxfId="1" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",X2)))</formula>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"Yes"</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="19" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",X2)))</formula>
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"No"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z21">
@@ -3352,7 +3292,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F159"/>
+  <dimension ref="A1:F152"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -3392,7 +3332,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>89</v>
@@ -3404,2655 +3344,2524 @@
         <v>91</v>
       </c>
       <c r="E3" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
+      <c r="C6" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-3.32</v>
+      </c>
+      <c r="D7" s="6">
+        <v>-2.87</v>
+      </c>
+      <c r="E7" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-4.06</v>
+      </c>
+      <c r="D8" s="6">
+        <v>-3.87</v>
+      </c>
+      <c r="E8" s="7">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="B9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-1.87</v>
+      </c>
+      <c r="D9" s="6">
+        <v>-0.58</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.29</v>
+      </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>112</v>
+      <c r="A10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-3.8</v>
+      </c>
+      <c r="D10" s="6">
+        <v>-4.25</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.67</v>
+        <v>-3.05</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.32</v>
+        <v>-2.64</v>
       </c>
       <c r="E11" s="7">
-        <v>1.35</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.78</v>
+        <v>0.13</v>
       </c>
       <c r="D12" s="6">
-        <v>-4.06</v>
+        <v>0.26</v>
       </c>
       <c r="E12" s="7">
-        <v>2.72</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="6">
-        <v>-4.13</v>
+        <v>13.46</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.87</v>
+        <v>17.84</v>
       </c>
       <c r="E13" s="7">
-        <v>2.26</v>
+        <v>4.38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="6">
-        <v>-6.66</v>
+        <v>-4.25</v>
       </c>
       <c r="D14" s="6">
-        <v>-3.8</v>
+        <v>-3.92</v>
       </c>
       <c r="E14" s="7">
-        <v>2.86</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C15" s="6">
-        <v>-6.67</v>
+        <v>0.11</v>
       </c>
       <c r="D15" s="6">
-        <v>-3.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E15" s="7">
-        <v>3.62</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C16" s="6">
-        <v>-2.7</v>
+        <v>7.54</v>
       </c>
       <c r="D16" s="6">
-        <v>0.13</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2.83</v>
+        <v>5.86</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C17" s="6">
-        <v>12.05</v>
+        <v>-7.83</v>
       </c>
       <c r="D17" s="6">
-        <v>13.46</v>
-      </c>
-      <c r="E17" s="7">
-        <v>1.41</v>
+        <v>-9.029999999999999</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C18" s="6">
-        <v>-5.98</v>
+        <v>-3.12</v>
       </c>
       <c r="D18" s="6">
-        <v>-4.25</v>
+        <v>-2.87</v>
       </c>
       <c r="E18" s="7">
-        <v>1.73</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="6">
-        <v>-2.99</v>
+        <v>3.57</v>
       </c>
       <c r="D19" s="6">
-        <v>0.11</v>
-      </c>
-      <c r="E19" s="7">
-        <v>3.1</v>
+        <v>3.29</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C20" s="6">
-        <v>5.59</v>
+        <v>-0.19</v>
       </c>
       <c r="D20" s="6">
-        <v>7.54</v>
+        <v>0.71</v>
       </c>
       <c r="E20" s="7">
-        <v>1.95</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="6">
-        <v>-10.07</v>
+        <v>-3.65</v>
       </c>
       <c r="D21" s="6">
-        <v>-7.83</v>
+        <v>-2.39</v>
       </c>
       <c r="E21" s="7">
-        <v>2.24</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>-6.05</v>
+        <v>4.5</v>
       </c>
       <c r="D22" s="6">
-        <v>-3.12</v>
+        <v>5.84</v>
       </c>
       <c r="E22" s="7">
-        <v>2.93</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-1.94</v>
+        <v>-2.08</v>
       </c>
       <c r="D23" s="6">
-        <v>3.57</v>
+        <v>-0.68</v>
       </c>
       <c r="E23" s="7">
-        <v>5.51</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.71</v>
+        <v>-3.77</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.19</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.52</v>
+        <v>-4.76</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>-8.220000000000001</v>
+        <v>-2.89</v>
       </c>
       <c r="D25" s="6">
-        <v>-3.65</v>
+        <v>-2.5</v>
       </c>
       <c r="E25" s="7">
-        <v>4.57</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="D26" s="6">
-        <v>4.5</v>
+        <v>2.31</v>
       </c>
       <c r="E26" s="7">
-        <v>3.12</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" s="6">
-        <v>-3.47</v>
+        <v>2.54</v>
       </c>
       <c r="D27" s="6">
-        <v>-2.08</v>
-      </c>
-      <c r="E27" s="7">
-        <v>1.39</v>
+        <v>2.25</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6">
-        <v>-6.58</v>
+        <v>0.77</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.77</v>
+        <v>1.98</v>
       </c>
       <c r="E28" s="7">
-        <v>2.81</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" s="6">
-        <v>-5.21</v>
+        <v>2.84</v>
       </c>
       <c r="D29" s="6">
-        <v>-2.89</v>
+        <v>3.39</v>
       </c>
       <c r="E29" s="7">
-        <v>2.32</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" s="6">
-        <v>-0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D30" s="6">
-        <v>2.18</v>
+        <v>1.27</v>
       </c>
       <c r="E30" s="7">
-        <v>2.78</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="6">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="D31" s="6">
-        <v>2.54</v>
+        <v>2.18</v>
       </c>
       <c r="E31" s="7">
-        <v>0.51</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="6">
-        <v>-0.65</v>
+        <v>0.19</v>
       </c>
       <c r="D32" s="6">
-        <v>0.77</v>
+        <v>1.27</v>
       </c>
       <c r="E32" s="7">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="6">
-        <v>1.03</v>
+        <v>-0.67</v>
       </c>
       <c r="D33" s="6">
-        <v>2.84</v>
+        <v>1.91</v>
       </c>
       <c r="E33" s="7">
-        <v>1.81</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="6">
-        <v>-1.49</v>
+        <v>1.54</v>
       </c>
       <c r="D34" s="6">
-        <v>0.5600000000000001</v>
+        <v>2.65</v>
       </c>
       <c r="E34" s="7">
-        <v>2.05</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="6">
-        <v>-1.93</v>
+        <v>2.33</v>
       </c>
       <c r="D35" s="6">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="E35" s="7">
-        <v>3.73</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="6">
-        <v>-1.11</v>
+        <v>4.47</v>
       </c>
       <c r="D36" s="6">
-        <v>0.19</v>
-      </c>
-      <c r="E36" s="7">
-        <v>1.3</v>
+        <v>4.34</v>
+      </c>
+      <c r="E36" s="8">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="6">
-        <v>-2.68</v>
+        <v>0.42</v>
       </c>
       <c r="D37" s="6">
-        <v>-0.67</v>
+        <v>2.67</v>
       </c>
       <c r="E37" s="7">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C38" s="6">
-        <v>0.61</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D38" s="6">
-        <v>1.54</v>
+        <v>2.13</v>
       </c>
       <c r="E38" s="7">
-        <v>0.93</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C39" s="6">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="D39" s="6">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="E39" s="7">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C40" s="6">
-        <v>0.91</v>
+        <v>4.35</v>
       </c>
       <c r="D40" s="6">
-        <v>4.47</v>
+        <v>7.09</v>
       </c>
       <c r="E40" s="7">
-        <v>3.56</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C41" s="6">
-        <v>-0.76</v>
+        <v>2.03</v>
       </c>
       <c r="D41" s="6">
-        <v>0.42</v>
+        <v>3.77</v>
       </c>
       <c r="E41" s="7">
-        <v>1.18</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C42" s="6">
-        <v>-1.11</v>
+        <v>1.69</v>
       </c>
       <c r="D42" s="6">
-        <v>0.6899999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="E42" s="7">
-        <v>1.8</v>
+        <v>1.41</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C43" s="6">
-        <v>-1.43</v>
+        <v>4.37</v>
       </c>
       <c r="D43" s="6">
-        <v>0.67</v>
+        <v>6.91</v>
       </c>
       <c r="E43" s="7">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C44" s="6">
-        <v>3.82</v>
+        <v>1.06</v>
       </c>
       <c r="D44" s="6">
-        <v>4.35</v>
+        <v>1.67</v>
       </c>
       <c r="E44" s="7">
-        <v>0.53</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C45" s="6">
-        <v>-0.99</v>
+        <v>-0.89</v>
       </c>
       <c r="D45" s="6">
-        <v>2.03</v>
+        <v>-0.74</v>
       </c>
       <c r="E45" s="7">
-        <v>3.02</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C46" s="6">
-        <v>-0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="D46" s="6">
-        <v>1.69</v>
+        <v>1.49</v>
       </c>
       <c r="E46" s="7">
-        <v>2.16</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C47" s="6">
-        <v>3.82</v>
+        <v>-5.66</v>
       </c>
       <c r="D47" s="6">
-        <v>4.37</v>
-      </c>
-      <c r="E47" s="7">
-        <v>0.55</v>
+        <v>-6.64</v>
+      </c>
+      <c r="E47" s="8">
+        <v>-0.98</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48" s="6">
-        <v>-1.29</v>
+        <v>-2.73</v>
       </c>
       <c r="D48" s="6">
-        <v>1.06</v>
-      </c>
-      <c r="E48" s="7">
-        <v>2.35</v>
+        <v>-3.09</v>
+      </c>
+      <c r="E48" s="8">
+        <v>-0.36</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" s="6">
-        <v>-2.27</v>
+        <v>-12.5</v>
       </c>
       <c r="D49" s="6">
-        <v>-0.89</v>
+        <v>-12.21</v>
       </c>
       <c r="E49" s="7">
-        <v>1.38</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="5" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" s="6">
-        <v>-0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="D50" s="6">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E50" s="7">
-        <v>1.37</v>
+        <v>-1.93</v>
+      </c>
+      <c r="E50" s="8">
+        <v>-1.19</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="6">
-        <v>-5.59</v>
+        <v>-22.46</v>
       </c>
       <c r="D51" s="6">
-        <v>-5.66</v>
+        <v>-22.96</v>
       </c>
       <c r="E51" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C52" s="6">
-        <v>-3.27</v>
+        <v>-10.18</v>
       </c>
       <c r="D52" s="6">
-        <v>-2.73</v>
-      </c>
-      <c r="E52" s="7">
-        <v>0.54</v>
+        <v>-10.26</v>
+      </c>
+      <c r="E52" s="8">
+        <v>-0.08</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C53" s="6">
-        <v>-13.28</v>
+        <v>-9.710000000000001</v>
       </c>
       <c r="D53" s="6">
-        <v>-12.5</v>
+        <v>-7.63</v>
       </c>
       <c r="E53" s="7">
-        <v>0.78</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="6">
-        <v>-1.27</v>
+        <v>-7.07</v>
       </c>
       <c r="D54" s="6">
-        <v>-0.74</v>
+        <v>-7.04</v>
       </c>
       <c r="E54" s="7">
-        <v>0.53</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C55" s="6">
-        <v>-24.27</v>
+        <v>7.99</v>
       </c>
       <c r="D55" s="6">
-        <v>-22.46</v>
-      </c>
-      <c r="E55" s="7">
-        <v>1.81</v>
+        <v>5.82</v>
+      </c>
+      <c r="E55" s="8">
+        <v>-2.17</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="5" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C56" s="6">
-        <v>-11.33</v>
+        <v>16.25</v>
       </c>
       <c r="D56" s="6">
-        <v>-10.18</v>
-      </c>
-      <c r="E56" s="7">
-        <v>1.15</v>
+        <v>15.17</v>
+      </c>
+      <c r="E56" s="8">
+        <v>-1.08</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C57" s="6">
-        <v>-9.720000000000001</v>
+        <v>-8.32</v>
       </c>
       <c r="D57" s="6">
-        <v>-9.710000000000001</v>
-      </c>
-      <c r="E57" s="7">
-        <v>0.01</v>
+        <v>-8.67</v>
+      </c>
+      <c r="E57" s="8">
+        <v>-0.35</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="6">
-        <v>-6.94</v>
+        <v>5.79</v>
       </c>
       <c r="D58" s="6">
-        <v>-7.07</v>
+        <v>4.86</v>
       </c>
       <c r="E58" s="8">
-        <v>-0.13</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C59" s="6">
-        <v>7.75</v>
+        <v>19.03</v>
       </c>
       <c r="D59" s="6">
-        <v>7.99</v>
+        <v>20.47</v>
       </c>
       <c r="E59" s="7">
-        <v>0.24</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C60" s="6">
-        <v>15.39</v>
+        <v>-12.62</v>
       </c>
       <c r="D60" s="6">
-        <v>16.25</v>
-      </c>
-      <c r="E60" s="7">
-        <v>0.86</v>
+        <v>-13.17</v>
+      </c>
+      <c r="E60" s="8">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C61" s="6">
-        <v>-9.109999999999999</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="D61" s="6">
-        <v>-8.32</v>
+        <v>-8.050000000000001</v>
       </c>
       <c r="E61" s="7">
-        <v>0.79</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="6">
-        <v>6.48</v>
+        <v>-4.84</v>
       </c>
       <c r="D62" s="6">
-        <v>5.79</v>
-      </c>
-      <c r="E62" s="8">
-        <v>-0.6899999999999999</v>
+        <v>-4.83</v>
+      </c>
+      <c r="E62" s="7">
+        <v>0.01</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C63" s="6">
-        <v>19.27</v>
+        <v>-5.37</v>
       </c>
       <c r="D63" s="6">
-        <v>19.03</v>
+        <v>-10.1</v>
       </c>
       <c r="E63" s="8">
-        <v>-0.24</v>
+        <v>-4.73</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C64" s="6">
-        <v>-14.55</v>
+        <v>-8.6</v>
       </c>
       <c r="D64" s="6">
-        <v>-12.62</v>
-      </c>
-      <c r="E64" s="7">
-        <v>1.93</v>
+        <v>-8.74</v>
+      </c>
+      <c r="E64" s="8">
+        <v>-0.14</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65" s="6">
-        <v>-10.28</v>
+        <v>-5.52</v>
       </c>
       <c r="D65" s="6">
-        <v>-9.029999999999999</v>
-      </c>
-      <c r="E65" s="7">
-        <v>1.25</v>
+        <v>-8.220000000000001</v>
+      </c>
+      <c r="E65" s="8">
+        <v>-2.7</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="5" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C66" s="6">
-        <v>-5.37</v>
+        <v>-10.13</v>
       </c>
       <c r="D66" s="6">
-        <v>-4.84</v>
+        <v>-8.76</v>
       </c>
       <c r="E66" s="7">
-        <v>0.53</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C67" s="6">
-        <v>-5.14</v>
+        <v>-9.98</v>
       </c>
       <c r="D67" s="6">
-        <v>-5.37</v>
+        <v>-12.15</v>
       </c>
       <c r="E67" s="8">
-        <v>-0.23</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C68" s="6">
-        <v>-9.550000000000001</v>
+        <v>-8.17</v>
       </c>
       <c r="D68" s="6">
-        <v>-8.6</v>
+        <v>-5.86</v>
       </c>
       <c r="E68" s="7">
-        <v>0.95</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C69" s="6">
-        <v>-6.5</v>
+        <v>2.39</v>
       </c>
       <c r="D69" s="6">
-        <v>-5.52</v>
+        <v>4.53</v>
       </c>
       <c r="E69" s="7">
-        <v>0.98</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C70" s="6">
-        <v>-11.03</v>
+        <v>-6.72</v>
       </c>
       <c r="D70" s="6">
-        <v>-10.13</v>
-      </c>
-      <c r="E70" s="7">
-        <v>0.9</v>
+        <v>-7.65</v>
+      </c>
+      <c r="E70" s="8">
+        <v>-0.93</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C71" s="6">
-        <v>-12.04</v>
+        <v>-6.24</v>
       </c>
       <c r="D71" s="6">
-        <v>-9.98</v>
+        <v>-5.84</v>
       </c>
       <c r="E71" s="7">
-        <v>2.06</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C72" s="6">
-        <v>-9.24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D72" s="6">
-        <v>-8.17</v>
-      </c>
-      <c r="E72" s="7">
-        <v>1.07</v>
+        <v>2.89</v>
+      </c>
+      <c r="E72" s="8">
+        <v>-5.91</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C73" s="6">
-        <v>3.73</v>
+        <v>-4.73</v>
       </c>
       <c r="D73" s="6">
-        <v>2.39</v>
+        <v>-7.22</v>
       </c>
       <c r="E73" s="8">
-        <v>-1.34</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C74" s="6">
-        <v>-6.33</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="D74" s="6">
-        <v>-6.72</v>
-      </c>
-      <c r="E74" s="8">
-        <v>-0.39</v>
+        <v>-8.27</v>
+      </c>
+      <c r="E74" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C75" s="6">
-        <v>-7.33</v>
+        <v>-0.83</v>
       </c>
       <c r="D75" s="6">
-        <v>-6.24</v>
-      </c>
-      <c r="E75" s="7">
-        <v>1.09</v>
+        <v>-1.11</v>
+      </c>
+      <c r="E75" s="8">
+        <v>-0.28</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C76" s="6">
-        <v>7.62</v>
+        <v>1.28</v>
       </c>
       <c r="D76" s="6">
-        <v>8.800000000000001</v>
+        <v>2.96</v>
       </c>
       <c r="E76" s="7">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C77" s="6">
-        <v>-5.37</v>
+        <v>-10.77</v>
       </c>
       <c r="D77" s="6">
-        <v>-4.73</v>
+        <v>-9.52</v>
       </c>
       <c r="E77" s="7">
-        <v>0.64</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C78" s="6">
-        <v>-9.51</v>
+        <v>-2.97</v>
       </c>
       <c r="D78" s="6">
-        <v>-8.470000000000001</v>
+        <v>-1.04</v>
       </c>
       <c r="E78" s="7">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C79" s="6">
-        <v>-2.96</v>
+        <v>-3.01</v>
       </c>
       <c r="D79" s="6">
-        <v>-0.83</v>
+        <v>-1.5</v>
       </c>
       <c r="E79" s="7">
-        <v>2.13</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C80" s="6">
-        <v>2.09</v>
+        <v>-3.67</v>
       </c>
       <c r="D80" s="6">
-        <v>1.28</v>
+        <v>-5.27</v>
       </c>
       <c r="E80" s="8">
-        <v>-0.8100000000000001</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C81" s="6">
-        <v>-13.15</v>
+        <v>-6.54</v>
       </c>
       <c r="D81" s="6">
-        <v>-10.77</v>
-      </c>
-      <c r="E81" s="7">
-        <v>2.38</v>
+        <v>-7.41</v>
+      </c>
+      <c r="E81" s="8">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C82" s="6">
-        <v>-4.51</v>
+        <v>-5.11</v>
       </c>
       <c r="D82" s="6">
-        <v>-2.97</v>
+        <v>-1.68</v>
       </c>
       <c r="E82" s="7">
-        <v>1.54</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C83" s="6">
-        <v>-2.41</v>
+        <v>-13.5</v>
       </c>
       <c r="D83" s="6">
-        <v>-3.01</v>
+        <v>-14.25</v>
       </c>
       <c r="E83" s="8">
-        <v>-0.6</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C84" s="6">
-        <v>-4.69</v>
+        <v>-14.44</v>
       </c>
       <c r="D84" s="6">
-        <v>-3.67</v>
-      </c>
-      <c r="E84" s="7">
-        <v>1.02</v>
+        <v>-14.63</v>
+      </c>
+      <c r="E84" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C85" s="6">
-        <v>-6.97</v>
+        <v>-12.46</v>
       </c>
       <c r="D85" s="6">
-        <v>-6.54</v>
+        <v>-11.99</v>
       </c>
       <c r="E85" s="7">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="5" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C86" s="6">
-        <v>-6.27</v>
+        <v>-15.02</v>
       </c>
       <c r="D86" s="6">
-        <v>-5.11</v>
-      </c>
-      <c r="E86" s="7">
-        <v>1.16</v>
+        <v>-15.84</v>
+      </c>
+      <c r="E86" s="8">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C87" s="6">
-        <v>-13.29</v>
+        <v>-22.7</v>
       </c>
       <c r="D87" s="6">
-        <v>-13.5</v>
+        <v>-23.19</v>
       </c>
       <c r="E87" s="8">
-        <v>-0.21</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C88" s="6">
-        <v>-15.33</v>
+        <v>-13.21</v>
       </c>
       <c r="D88" s="6">
-        <v>-14.44</v>
+        <v>-13.18</v>
       </c>
       <c r="E88" s="7">
-        <v>0.89</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C89" s="6">
-        <v>-13.41</v>
+        <v>-19.3</v>
       </c>
       <c r="D89" s="6">
-        <v>-12.46</v>
+        <v>-17.43</v>
       </c>
       <c r="E89" s="7">
-        <v>0.95</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6">
-        <v>-15.86</v>
+        <v>-10.12</v>
       </c>
       <c r="D90" s="6">
-        <v>-15.02</v>
-      </c>
-      <c r="E90" s="7">
-        <v>0.84</v>
+        <v>-10.57</v>
+      </c>
+      <c r="E90" s="8">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C91" s="6">
-        <v>-24.47</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="D91" s="6">
-        <v>-22.7</v>
+        <v>-9.9</v>
       </c>
       <c r="E91" s="7">
-        <v>1.77</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C92" s="6">
-        <v>-14.21</v>
+        <v>0</v>
       </c>
       <c r="D92" s="6">
-        <v>-13.21</v>
-      </c>
-      <c r="E92" s="7">
-        <v>1</v>
+        <v>-1.46</v>
+      </c>
+      <c r="E92" s="8">
+        <v>-1.46</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6">
-        <v>-20.09</v>
+        <v>-13.63</v>
       </c>
       <c r="D93" s="6">
-        <v>-19.3</v>
-      </c>
-      <c r="E93" s="7">
-        <v>0.79</v>
+        <v>-14.09</v>
+      </c>
+      <c r="E93" s="8">
+        <v>-0.46</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B94" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C94" s="6">
-        <v>-10.39</v>
+        <v>-15.5</v>
       </c>
       <c r="D94" s="6">
-        <v>-10.12</v>
-      </c>
-      <c r="E94" s="7">
-        <v>0.27</v>
+        <v>-15.71</v>
+      </c>
+      <c r="E94" s="8">
+        <v>-0.21</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C95" s="6">
-        <v>-11.02</v>
+        <v>-15.86</v>
       </c>
       <c r="D95" s="6">
-        <v>-9.970000000000001</v>
-      </c>
-      <c r="E95" s="7">
-        <v>1.05</v>
+        <v>-16.65</v>
+      </c>
+      <c r="E95" s="8">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B96" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C96" s="6">
-        <v>-0.66</v>
+        <v>-1.75</v>
       </c>
       <c r="D96" s="6">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="E96" s="7">
-        <v>0.66</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C97" s="6">
-        <v>-14.21</v>
+        <v>-15.37</v>
       </c>
       <c r="D97" s="6">
-        <v>-13.63</v>
-      </c>
-      <c r="E97" s="7">
-        <v>0.58</v>
+        <v>-15.98</v>
+      </c>
+      <c r="E97" s="8">
+        <v>-0.61</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C98" s="6">
-        <v>-16.46</v>
+        <v>-10.54</v>
       </c>
       <c r="D98" s="6">
-        <v>-15.5</v>
+        <v>-9.5</v>
       </c>
       <c r="E98" s="7">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6">
-        <v>-17.67</v>
+        <v>-4.41</v>
       </c>
       <c r="D99" s="6">
-        <v>-15.86</v>
+        <v>-2.9</v>
       </c>
       <c r="E99" s="7">
-        <v>1.81</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C100" s="6">
-        <v>-2.37</v>
+        <v>-11.16</v>
       </c>
       <c r="D100" s="6">
-        <v>-1.75</v>
-      </c>
-      <c r="E100" s="7">
-        <v>0.62</v>
+        <v>-12.94</v>
+      </c>
+      <c r="E100" s="8">
+        <v>-1.78</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C101" s="6">
-        <v>-17.63</v>
+        <v>-8.94</v>
       </c>
       <c r="D101" s="6">
-        <v>-15.37</v>
-      </c>
-      <c r="E101" s="7">
-        <v>2.26</v>
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="E101" s="8">
+        <v>-0.43</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C102" s="6">
-        <v>-11.96</v>
+        <v>-7.32</v>
       </c>
       <c r="D102" s="6">
-        <v>-10.54</v>
+        <v>-7.31</v>
       </c>
       <c r="E102" s="7">
-        <v>1.42</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C103" s="6">
-        <v>-4.97</v>
+        <v>25645.6</v>
       </c>
       <c r="D103" s="6">
-        <v>-4.41</v>
-      </c>
-      <c r="E103" s="7">
-        <v>0.5600000000000001</v>
+        <v>25422.7</v>
+      </c>
+      <c r="E103" s="8">
+        <v>-222.9</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C104" s="6">
-        <v>-12.16</v>
+        <v>8986.450000000001</v>
       </c>
       <c r="D104" s="6">
-        <v>-11.16</v>
-      </c>
-      <c r="E104" s="7">
-        <v>1</v>
+        <v>8966.450000000001</v>
+      </c>
+      <c r="E104" s="8">
+        <v>-20</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C105" s="6">
-        <v>-9.43</v>
+        <v>11059.15</v>
       </c>
       <c r="D105" s="6">
-        <v>-8.94</v>
+        <v>11090.7</v>
       </c>
       <c r="E105" s="7">
-        <v>0.49</v>
+        <v>31.55</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="5" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C106" s="6">
-        <v>-8.449999999999999</v>
+        <v>35299</v>
       </c>
       <c r="D106" s="6">
-        <v>-7.32</v>
-      </c>
-      <c r="E106" s="7">
-        <v>1.13</v>
+        <v>34957.9</v>
+      </c>
+      <c r="E106" s="8">
+        <v>-341.1</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C107" s="6">
-        <v>25707.35</v>
+        <v>43882.95</v>
       </c>
       <c r="D107" s="6">
-        <v>25645.6</v>
+        <v>43609.2</v>
       </c>
       <c r="E107" s="8">
-        <v>-61.75</v>
+        <v>-273.75</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="5" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C108" s="6">
-        <v>8893.5</v>
+        <v>24704.55</v>
       </c>
       <c r="D108" s="6">
-        <v>8986.450000000001</v>
+        <v>24712.2</v>
       </c>
       <c r="E108" s="7">
-        <v>92.95</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C109" s="6">
-        <v>10944.35</v>
+        <v>31866.4</v>
       </c>
       <c r="D109" s="6">
-        <v>11059.15</v>
+        <v>32606.9</v>
       </c>
       <c r="E109" s="7">
-        <v>114.8</v>
+        <v>740.5</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C110" s="6">
-        <v>34946.3</v>
+        <v>14975.8</v>
       </c>
       <c r="D110" s="6">
-        <v>35299</v>
-      </c>
-      <c r="E110" s="7">
-        <v>352.7</v>
+        <v>14901.5</v>
+      </c>
+      <c r="E110" s="8">
+        <v>-74.3</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C111" s="6">
-        <v>42878.35</v>
+        <v>8792.5</v>
       </c>
       <c r="D111" s="6">
-        <v>43882.95</v>
+        <v>8799</v>
       </c>
       <c r="E111" s="7">
-        <v>1004.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C112" s="6">
-        <v>24418.25</v>
+        <v>1655.35</v>
       </c>
       <c r="D112" s="6">
-        <v>24704.55</v>
-      </c>
-      <c r="E112" s="7">
-        <v>286.3</v>
+        <v>1631.25</v>
+      </c>
+      <c r="E112" s="8">
+        <v>-24.1</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C113" s="6">
-        <v>31553.4</v>
+        <v>11848.45</v>
       </c>
       <c r="D113" s="6">
-        <v>31866.4</v>
-      </c>
-      <c r="E113" s="7">
-        <v>313</v>
+        <v>11784.9</v>
+      </c>
+      <c r="E113" s="8">
+        <v>-63.55</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C114" s="6">
-        <v>14931.6</v>
+        <v>9097.1</v>
       </c>
       <c r="D114" s="6">
-        <v>14975.8</v>
-      </c>
-      <c r="E114" s="7">
-        <v>44.2</v>
+        <v>9075.35</v>
+      </c>
+      <c r="E114" s="8">
+        <v>-21.75</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C115" s="6">
-        <v>8690.049999999999</v>
+        <v>8312.5</v>
       </c>
       <c r="D115" s="6">
-        <v>8792.5</v>
-      </c>
-      <c r="E115" s="7">
-        <v>102.45</v>
+        <v>8234.85</v>
+      </c>
+      <c r="E115" s="8">
+        <v>-77.65000000000001</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C116" s="6">
-        <v>1637.4</v>
+        <v>26710.8</v>
       </c>
       <c r="D116" s="6">
-        <v>1655.35</v>
+        <v>27124.85</v>
       </c>
       <c r="E116" s="7">
-        <v>17.95</v>
+        <v>414.05</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C117" s="6">
-        <v>11769.35</v>
+        <v>819.8</v>
       </c>
       <c r="D117" s="6">
-        <v>11848.45</v>
-      </c>
-      <c r="E117" s="7">
-        <v>79.09999999999999</v>
+        <v>813.9</v>
+      </c>
+      <c r="E117" s="8">
+        <v>-5.9</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C118" s="6">
-        <v>8993.65</v>
+        <v>30506.2</v>
       </c>
       <c r="D118" s="6">
-        <v>9097.1</v>
+        <v>30861.75</v>
       </c>
       <c r="E118" s="7">
-        <v>103.45</v>
+        <v>355.55</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C119" s="6">
-        <v>8133.6</v>
+        <v>16193.9</v>
       </c>
       <c r="D119" s="6">
-        <v>8312.5</v>
+        <v>16449.55</v>
       </c>
       <c r="E119" s="7">
-        <v>178.9</v>
+        <v>255.65</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C120" s="6">
-        <v>26541.35</v>
+        <v>8882.9</v>
       </c>
       <c r="D120" s="6">
-        <v>26710.8</v>
-      </c>
-      <c r="E120" s="7">
-        <v>169.45</v>
+        <v>8704.450000000001</v>
+      </c>
+      <c r="E120" s="8">
+        <v>-178.45</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C121" s="6">
-        <v>797.85</v>
+        <v>10352.4</v>
       </c>
       <c r="D121" s="6">
-        <v>819.8</v>
-      </c>
-      <c r="E121" s="7">
-        <v>21.95</v>
+        <v>10303.25</v>
+      </c>
+      <c r="E121" s="8">
+        <v>-49.15</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C122" s="6">
-        <v>30022.85</v>
+        <v>27052.6</v>
       </c>
       <c r="D122" s="6">
-        <v>30506.2</v>
+        <v>27053.5</v>
       </c>
       <c r="E122" s="7">
-        <v>483.35</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C123" s="6">
-        <v>16100.1</v>
+        <v>55</v>
       </c>
       <c r="D123" s="6">
-        <v>16193.9</v>
-      </c>
-      <c r="E123" s="7">
-        <v>93.8</v>
+        <v>25</v>
+      </c>
+      <c r="E123" s="8">
+        <v>-30</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="5" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C124" s="6">
-        <v>8782.700000000001</v>
+        <v>35</v>
       </c>
       <c r="D124" s="6">
-        <v>8882.9</v>
+        <v>45</v>
       </c>
       <c r="E124" s="7">
-        <v>100.2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C125" s="6">
-        <v>10296.6</v>
+        <v>25</v>
       </c>
       <c r="D125" s="6">
-        <v>10352.4</v>
+        <v>35</v>
       </c>
       <c r="E125" s="7">
-        <v>55.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="5" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C126" s="6">
-        <v>26722.1</v>
+        <v>80</v>
       </c>
       <c r="D126" s="6">
-        <v>27052.6</v>
+        <v>90</v>
       </c>
       <c r="E126" s="7">
-        <v>330.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C127" s="6">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="D127" s="6">
-        <v>55</v>
-      </c>
-      <c r="E127" s="8">
-        <v>-10</v>
+        <v>60</v>
+      </c>
+      <c r="E127" s="7">
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C128" s="6">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="D128" s="6">
-        <v>35</v>
-      </c>
-      <c r="E128" s="7">
-        <v>5</v>
+        <v>95</v>
+      </c>
+      <c r="E128" s="8">
+        <v>-4</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C129" s="6">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D129" s="6">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="E129" s="8">
-        <v>-5</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="5" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C130" s="6">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="D130" s="6">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="E130" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C131" s="6">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="D131" s="6">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="E131" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C132" s="6">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="D132" s="6">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="E132" s="8">
-        <v>-20</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C133" s="6">
-        <v>40</v>
+        <v>47.54</v>
       </c>
       <c r="D133" s="6">
-        <v>45</v>
-      </c>
-      <c r="E133" s="7">
-        <v>5</v>
+        <v>44.51</v>
+      </c>
+      <c r="E133" s="8">
+        <v>-3.03</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="5" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C134" s="6">
-        <v>95</v>
+        <v>43.21</v>
       </c>
       <c r="D134" s="6">
-        <v>99</v>
-      </c>
-      <c r="E134" s="7">
-        <v>4</v>
+        <v>42.39</v>
+      </c>
+      <c r="E134" s="8">
+        <v>-0.82</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C135" s="6">
-        <v>25</v>
+        <v>50.12</v>
       </c>
       <c r="D135" s="6">
-        <v>20</v>
-      </c>
-      <c r="E135" s="8">
-        <v>-5</v>
+        <v>51.45</v>
+      </c>
+      <c r="E135" s="7">
+        <v>1.33</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="5" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C136" s="6">
-        <v>99</v>
+        <v>39.91</v>
       </c>
       <c r="D136" s="6">
-        <v>95</v>
+        <v>36.78</v>
       </c>
       <c r="E136" s="8">
-        <v>-4</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C137" s="6">
-        <v>55</v>
+        <v>46.16</v>
       </c>
       <c r="D137" s="6">
-        <v>60</v>
-      </c>
-      <c r="E137" s="7">
-        <v>5</v>
+        <v>44.2</v>
+      </c>
+      <c r="E137" s="8">
+        <v>-1.96</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="5" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C138" s="6">
-        <v>60</v>
+        <v>45.65</v>
       </c>
       <c r="D138" s="6">
-        <v>65</v>
+        <v>45.82</v>
       </c>
       <c r="E138" s="7">
-        <v>5</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C139" s="6">
-        <v>35</v>
+        <v>63.14</v>
       </c>
       <c r="D139" s="6">
-        <v>40</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E139" s="7">
-        <v>5</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C140" s="6">
-        <v>48.38</v>
+        <v>42.97</v>
       </c>
       <c r="D140" s="6">
-        <v>47.54</v>
+        <v>41.08</v>
       </c>
       <c r="E140" s="8">
-        <v>-0.84</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C141" s="6">
-        <v>38.01</v>
+        <v>52.23</v>
       </c>
       <c r="D141" s="6">
-        <v>43.21</v>
+        <v>52.59</v>
       </c>
       <c r="E141" s="7">
-        <v>5.2</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C142" s="6">
-        <v>45.05</v>
+        <v>60.66</v>
       </c>
       <c r="D142" s="6">
-        <v>50.12</v>
-      </c>
-      <c r="E142" s="7">
-        <v>5.07</v>
+        <v>56</v>
+      </c>
+      <c r="E142" s="8">
+        <v>-4.66</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C143" s="6">
-        <v>34.56</v>
+        <v>40.23</v>
       </c>
       <c r="D143" s="6">
-        <v>39.91</v>
-      </c>
-      <c r="E143" s="7">
-        <v>5.35</v>
+        <v>38.86</v>
+      </c>
+      <c r="E143" s="8">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C144" s="6">
-        <v>36.58</v>
+        <v>43.08</v>
       </c>
       <c r="D144" s="6">
-        <v>46.16</v>
-      </c>
-      <c r="E144" s="7">
-        <v>9.58</v>
+        <v>42.12</v>
+      </c>
+      <c r="E144" s="8">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C145" s="6">
-        <v>39.23</v>
+        <v>56.21</v>
       </c>
       <c r="D145" s="6">
-        <v>45.65</v>
-      </c>
-      <c r="E145" s="7">
-        <v>6.42</v>
+        <v>52.26</v>
+      </c>
+      <c r="E145" s="8">
+        <v>-3.95</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="5" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C146" s="6">
-        <v>61</v>
+        <v>59.68</v>
       </c>
       <c r="D146" s="6">
-        <v>63.14</v>
+        <v>64.88</v>
       </c>
       <c r="E146" s="7">
-        <v>2.14</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C147" s="6">
-        <v>41.48</v>
+        <v>48.33</v>
       </c>
       <c r="D147" s="6">
-        <v>42.97</v>
-      </c>
-      <c r="E147" s="7">
-        <v>1.49</v>
+        <v>46.42</v>
+      </c>
+      <c r="E147" s="8">
+        <v>-1.91</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="5" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C148" s="6">
-        <v>46.38</v>
+        <v>60.1</v>
       </c>
       <c r="D148" s="6">
-        <v>52.23</v>
+        <v>64.26000000000001</v>
       </c>
       <c r="E148" s="7">
-        <v>5.85</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C149" s="6">
-        <v>58.26</v>
+        <v>56.24</v>
       </c>
       <c r="D149" s="6">
-        <v>60.66</v>
+        <v>62.02</v>
       </c>
       <c r="E149" s="7">
-        <v>2.4</v>
+        <v>5.78</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="5" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C150" s="6">
-        <v>37.69</v>
+        <v>43.02</v>
       </c>
       <c r="D150" s="6">
-        <v>40.23</v>
-      </c>
-      <c r="E150" s="7">
-        <v>2.54</v>
+        <v>38.29</v>
+      </c>
+      <c r="E150" s="8">
+        <v>-4.73</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C151" s="6">
-        <v>36.72</v>
+        <v>39.66</v>
       </c>
       <c r="D151" s="6">
-        <v>43.08</v>
-      </c>
-      <c r="E151" s="7">
-        <v>6.36</v>
+        <v>37.93</v>
+      </c>
+      <c r="E151" s="8">
+        <v>-1.73</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>25</v>
       </c>
       <c r="C152" s="6">
-        <v>47.75</v>
+        <v>50.02</v>
       </c>
       <c r="D152" s="6">
-        <v>56.21</v>
+        <v>50.04</v>
       </c>
       <c r="E152" s="7">
-        <v>8.460000000000001</v>
-      </c>
-    </row>
-    <row r="153" spans="1:5">
-      <c r="A153" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C153" s="6">
-        <v>57.28</v>
-      </c>
-      <c r="D153" s="6">
-        <v>59.68</v>
-      </c>
-      <c r="E153" s="7">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="154" spans="1:5">
-      <c r="A154" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C154" s="6">
-        <v>39.78</v>
-      </c>
-      <c r="D154" s="6">
-        <v>48.33</v>
-      </c>
-      <c r="E154" s="7">
-        <v>8.550000000000001</v>
-      </c>
-    </row>
-    <row r="155" spans="1:5">
-      <c r="A155" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C155" s="6">
-        <v>53.23</v>
-      </c>
-      <c r="D155" s="6">
-        <v>60.1</v>
-      </c>
-      <c r="E155" s="7">
-        <v>6.87</v>
-      </c>
-    </row>
-    <row r="156" spans="1:5">
-      <c r="A156" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C156" s="6">
-        <v>53.85</v>
-      </c>
-      <c r="D156" s="6">
-        <v>56.24</v>
-      </c>
-      <c r="E156" s="7">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="157" spans="1:5">
-      <c r="A157" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C157" s="6">
-        <v>39.1</v>
-      </c>
-      <c r="D157" s="6">
-        <v>43.02</v>
-      </c>
-      <c r="E157" s="7">
-        <v>3.92</v>
-      </c>
-    </row>
-    <row r="158" spans="1:5">
-      <c r="A158" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C158" s="6">
-        <v>36.6</v>
-      </c>
-      <c r="D158" s="6">
-        <v>39.66</v>
-      </c>
-      <c r="E158" s="7">
-        <v>3.06</v>
-      </c>
-    </row>
-    <row r="159" spans="1:5">
-      <c r="A159" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B159" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C159" s="6">
-        <v>43.45</v>
-      </c>
-      <c r="D159" s="6">
-        <v>50.02</v>
-      </c>
-      <c r="E159" s="7">
-        <v>6.57</v>
+        <v>0.02</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6076,28 +5885,28 @@
         <v>2</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6105,28 +5914,28 @@
         <v>78</v>
       </c>
       <c r="B2" s="11">
-        <v>38.48</v>
+        <v>38.5</v>
       </c>
       <c r="C2" s="12">
         <v>20</v>
       </c>
       <c r="D2" s="11">
-        <v>49.4</v>
+        <v>49</v>
       </c>
       <c r="E2" s="11">
         <v>18.8</v>
       </c>
       <c r="F2" s="11">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
       <c r="G2" s="11">
-        <v>-4.7</v>
+        <v>-5</v>
       </c>
       <c r="H2" s="11">
         <v>52.4</v>
       </c>
       <c r="I2" s="11">
-        <v>5</v>
+        <v>6.2</v>
       </c>
     </row>
   </sheetData>
@@ -6231,22 +6040,22 @@
         <v>50</v>
       </c>
       <c r="B1" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>38</v>
-      </c>
       <c r="D1" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>46</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>54</v>
       </c>
       <c r="H1" s="13" t="s">
         <v>52</v>
@@ -6260,34 +6069,34 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="14">
-        <v>0.2409</v>
+        <v>0.2359</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1783</v>
+        <v>0.1738</v>
       </c>
       <c r="C2" s="14">
-        <v>0.1782</v>
+        <v>0.1736</v>
       </c>
       <c r="D2" s="14">
-        <v>0.1633</v>
+        <v>0.1577</v>
       </c>
       <c r="E2" s="14">
-        <v>0.1399</v>
+        <v>0.1552</v>
       </c>
       <c r="F2" s="14">
-        <v>0.1175</v>
+        <v>0.1408</v>
       </c>
       <c r="G2" s="14">
-        <v>0.1122</v>
+        <v>0.1138</v>
       </c>
       <c r="H2" s="14">
-        <v>0.1045</v>
+        <v>0.0944</v>
       </c>
       <c r="I2" s="14">
-        <v>0.09449999999999999</v>
+        <v>0.0922</v>
       </c>
       <c r="J2" s="14">
-        <v>0.09390000000000001</v>
+        <v>0.08929999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6310,10 +6119,10 @@
         <v>44</v>
       </c>
       <c r="G3" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="13" t="s">
         <v>55</v>
-      </c>
-      <c r="H3" s="13" t="s">
-        <v>47</v>
       </c>
       <c r="I3" s="13" t="s">
         <v>45</v>
@@ -6324,34 +6133,34 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="14">
-        <v>0.0872</v>
+        <v>0.0827</v>
       </c>
       <c r="B4" s="14">
-        <v>0.0603</v>
+        <v>0.0564</v>
       </c>
       <c r="C4" s="14">
-        <v>0.0562</v>
+        <v>0.0539</v>
       </c>
       <c r="D4" s="14">
-        <v>0.0428</v>
+        <v>0.0418</v>
       </c>
       <c r="E4" s="14">
-        <v>0.028</v>
+        <v>0.0244</v>
       </c>
       <c r="F4" s="14">
-        <v>-0.0152</v>
+        <v>-0.0157</v>
       </c>
       <c r="G4" s="14">
-        <v>-0.0325</v>
+        <v>-0.0668</v>
       </c>
       <c r="H4" s="14">
-        <v>-0.0592</v>
+        <v>-0.08220000000000001</v>
       </c>
       <c r="I4" s="14">
-        <v>-0.1112</v>
+        <v>-0.1219</v>
       </c>
       <c r="J4" s="14">
-        <v>-0.1499</v>
+        <v>-0.1594</v>
       </c>
     </row>
   </sheetData>
